--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -641,50 +644,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24942.73</v>
+        <v>24816.96</v>
       </c>
       <c r="C2" t="n">
-        <v>25110.28</v>
+        <v>24956.48</v>
       </c>
       <c r="D2" t="n">
-        <v>24900.73</v>
+        <v>24763.53</v>
       </c>
       <c r="E2" t="n">
-        <v>24910.41</v>
+        <v>24934.67</v>
       </c>
       <c r="F2" t="n">
-        <v>16.4</v>
+        <v>24.26</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.001</v>
       </c>
       <c r="H2" t="n">
-        <v>209.55</v>
+        <v>192.95</v>
       </c>
       <c r="I2" t="n">
-        <v>24678.22</v>
+        <v>24691.18</v>
       </c>
       <c r="J2" t="n">
-        <v>24645.27</v>
+        <v>24653.31</v>
       </c>
       <c r="K2" t="n">
-        <v>24792.11</v>
+        <v>24805.64</v>
       </c>
       <c r="L2" t="n">
-        <v>24938.96</v>
+        <v>24957.96</v>
       </c>
       <c r="M2" t="n">
-        <v>24995.91</v>
+        <v>25015.18</v>
       </c>
       <c r="N2" t="n">
-        <v>25052.85</v>
+        <v>25072.41</v>
       </c>
       <c r="O2" t="n">
-        <v>25289.59</v>
+        <v>25319.83</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,23 +695,21 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -718,55 +719,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24816.96</v>
+        <v>24996.54</v>
       </c>
       <c r="C3" t="n">
-        <v>24956.48</v>
+        <v>25059.37</v>
       </c>
       <c r="D3" t="n">
-        <v>24763.53</v>
+        <v>24840.27</v>
       </c>
       <c r="E3" t="n">
-        <v>24934.67</v>
+        <v>25026.8</v>
       </c>
       <c r="F3" t="n">
-        <v>24.26</v>
+        <v>92.13</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0037</v>
       </c>
       <c r="H3" t="n">
-        <v>192.95</v>
+        <v>219.1</v>
       </c>
       <c r="I3" t="n">
-        <v>24691.18</v>
+        <v>24570.58</v>
       </c>
       <c r="J3" t="n">
-        <v>24653.31</v>
+        <v>24779.05</v>
       </c>
       <c r="K3" t="n">
-        <v>24805.64</v>
+        <v>24838.19</v>
       </c>
       <c r="L3" t="n">
-        <v>24957.96</v>
+        <v>24897.34</v>
       </c>
       <c r="M3" t="n">
-        <v>25015.18</v>
+        <v>25031.15</v>
       </c>
       <c r="N3" t="n">
-        <v>25072.41</v>
+        <v>25164.95</v>
       </c>
       <c r="O3" t="n">
-        <v>25319.83</v>
+        <v>25149.43</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -774,18 +779,18 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -798,59 +803,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24996.54</v>
+        <v>25075.33</v>
       </c>
       <c r="C4" t="n">
-        <v>25059.37</v>
+        <v>25173.02</v>
       </c>
       <c r="D4" t="n">
-        <v>24840.27</v>
+        <v>24951.54</v>
       </c>
       <c r="E4" t="n">
-        <v>25026.8</v>
+        <v>24985.82</v>
       </c>
       <c r="F4" t="n">
-        <v>92.13</v>
+        <v>-40.98</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0016</v>
       </c>
       <c r="H4" t="n">
-        <v>219.1</v>
+        <v>221.48</v>
       </c>
       <c r="I4" t="n">
-        <v>24570.58</v>
+        <v>24621.17</v>
       </c>
       <c r="J4" t="n">
-        <v>24779.05</v>
+        <v>24846.19</v>
       </c>
       <c r="K4" t="n">
-        <v>24838.19</v>
+        <v>24917.25</v>
       </c>
       <c r="L4" t="n">
-        <v>24897.34</v>
+        <v>24988.31</v>
       </c>
       <c r="M4" t="n">
-        <v>25031.15</v>
+        <v>25136.35</v>
       </c>
       <c r="N4" t="n">
-        <v>25164.95</v>
+        <v>25284.39</v>
       </c>
       <c r="O4" t="n">
-        <v>25149.43</v>
+        <v>25278.47</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -861,14 +862,14 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U4" s="8" t="n">
@@ -882,55 +883,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25075.33</v>
+        <v>25035.93</v>
       </c>
       <c r="C5" t="n">
-        <v>25173.02</v>
+        <v>25176.21</v>
       </c>
       <c r="D5" t="n">
-        <v>24951.54</v>
+        <v>24896.19</v>
       </c>
       <c r="E5" t="n">
-        <v>24985.82</v>
+        <v>25139.69</v>
       </c>
       <c r="F5" t="n">
-        <v>-40.98</v>
+        <v>153.87</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0062</v>
       </c>
       <c r="H5" t="n">
-        <v>221.48</v>
+        <v>280.02</v>
       </c>
       <c r="I5" t="n">
-        <v>24621.17</v>
+        <v>24730.06</v>
       </c>
       <c r="J5" t="n">
-        <v>24846.19</v>
+        <v>24726.11</v>
       </c>
       <c r="K5" t="n">
-        <v>24917.25</v>
+        <v>24875.08</v>
       </c>
       <c r="L5" t="n">
-        <v>24988.31</v>
+        <v>25024.05</v>
       </c>
       <c r="M5" t="n">
-        <v>25136.35</v>
+        <v>25096.56</v>
       </c>
       <c r="N5" t="n">
-        <v>25284.39</v>
+        <v>25169.07</v>
       </c>
       <c r="O5" t="n">
-        <v>25278.47</v>
+        <v>25394.5</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -941,9 +946,9 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
@@ -951,8 +956,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U5" s="8" t="n">
-        <v/>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -971,148 +978,144 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25035.93</v>
+        <v>24835.56</v>
       </c>
       <c r="C6" t="n">
-        <v>25176.21</v>
+        <v>24988.71</v>
       </c>
       <c r="D6" t="n">
-        <v>24896.19</v>
+        <v>24728.57</v>
       </c>
       <c r="E6" t="n">
-        <v>25139.69</v>
+        <v>24893.58</v>
       </c>
       <c r="F6" t="n">
-        <v>153.87</v>
+        <v>-246.11</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0098</v>
       </c>
       <c r="H6" t="n">
-        <v>280.02</v>
+        <v>260.14</v>
       </c>
       <c r="I6" t="n">
-        <v>24730.06</v>
+        <v>24616.17</v>
       </c>
       <c r="J6" t="n">
-        <v>24726.11</v>
+        <v>24911.41</v>
       </c>
       <c r="K6" t="n">
-        <v>24875.08</v>
+        <v>24999.68</v>
       </c>
       <c r="L6" t="n">
-        <v>25024.05</v>
+        <v>25087.94</v>
       </c>
       <c r="M6" t="n">
-        <v>25096.56</v>
+        <v>25279.7</v>
       </c>
       <c r="N6" t="n">
-        <v>25169.07</v>
+        <v>25471.46</v>
       </c>
       <c r="O6" t="n">
-        <v>25394.5</v>
+        <v>25456.23</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
+      <c r="Q6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24835.56</v>
+        <v>24790.7</v>
       </c>
       <c r="C7" t="n">
-        <v>24988.71</v>
+        <v>24800.66</v>
       </c>
       <c r="D7" t="n">
-        <v>24728.57</v>
+        <v>24593.48</v>
       </c>
       <c r="E7" t="n">
-        <v>24893.58</v>
+        <v>24740.36</v>
       </c>
       <c r="F7" t="n">
-        <v>-246.11</v>
+        <v>-153.22</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0062</v>
       </c>
       <c r="H7" t="n">
-        <v>260.14</v>
+        <v>207.18</v>
       </c>
       <c r="I7" t="n">
-        <v>24616.17</v>
+        <v>24468.43</v>
       </c>
       <c r="J7" t="n">
-        <v>24911.41</v>
+        <v>24650.91</v>
       </c>
       <c r="K7" t="n">
-        <v>24999.68</v>
+        <v>24763.51</v>
       </c>
       <c r="L7" t="n">
-        <v>25087.94</v>
+        <v>24876.11</v>
       </c>
       <c r="M7" t="n">
-        <v>25279.7</v>
+        <v>25023.65</v>
       </c>
       <c r="N7" t="n">
-        <v>25471.46</v>
+        <v>25171.19</v>
       </c>
       <c r="O7" t="n">
-        <v>25456.23</v>
+        <v>25248.85</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S7" s="7" t="inlineStr">
@@ -1139,81 +1142,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24790.7</v>
+        <v>24810</v>
       </c>
       <c r="C8" t="n">
-        <v>24800.66</v>
+        <v>25088.28</v>
       </c>
       <c r="D8" t="n">
-        <v>24593.48</v>
+        <v>24761.72</v>
       </c>
       <c r="E8" t="n">
-        <v>24740.36</v>
+        <v>24994.83</v>
       </c>
       <c r="F8" t="n">
-        <v>-153.22</v>
+        <v>254.47</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0103</v>
       </c>
       <c r="H8" t="n">
-        <v>207.18</v>
+        <v>326.56</v>
       </c>
       <c r="I8" t="n">
-        <v>24468.43</v>
+        <v>24386.3</v>
       </c>
       <c r="J8" t="n">
-        <v>24650.91</v>
+        <v>24554.82</v>
       </c>
       <c r="K8" t="n">
-        <v>24763.51</v>
+        <v>24636.77</v>
       </c>
       <c r="L8" t="n">
-        <v>24876.11</v>
+        <v>24718.71</v>
       </c>
       <c r="M8" t="n">
-        <v>25023.65</v>
+        <v>24843.95</v>
       </c>
       <c r="N8" t="n">
-        <v>25171.19</v>
+        <v>24969.18</v>
       </c>
       <c r="O8" t="n">
-        <v>25248.85</v>
+        <v>25007.84</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W8" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W8" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
@@ -1221,83 +1226,81 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24810</v>
+        <v>24848.51</v>
       </c>
       <c r="C9" t="n">
-        <v>25088.28</v>
+        <v>24869.63</v>
       </c>
       <c r="D9" t="n">
-        <v>24761.72</v>
+        <v>24547.7</v>
       </c>
       <c r="E9" t="n">
-        <v>24994.83</v>
+        <v>24671.22</v>
       </c>
       <c r="F9" t="n">
-        <v>254.47</v>
+        <v>-323.61</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.0129</v>
       </c>
       <c r="H9" t="n">
-        <v>326.56</v>
+        <v>321.93</v>
       </c>
       <c r="I9" t="n">
-        <v>24386.3</v>
+        <v>24435.16</v>
       </c>
       <c r="J9" t="n">
-        <v>24554.82</v>
+        <v>24703.19</v>
       </c>
       <c r="K9" t="n">
-        <v>24636.77</v>
+        <v>24831.55</v>
       </c>
       <c r="L9" t="n">
-        <v>24718.71</v>
+        <v>24959.92</v>
       </c>
       <c r="M9" t="n">
-        <v>24843.95</v>
+        <v>25158.11</v>
       </c>
       <c r="N9" t="n">
-        <v>24969.18</v>
+        <v>25356.3</v>
       </c>
       <c r="O9" t="n">
-        <v>25007.84</v>
+        <v>25414.84</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
+      <c r="Q9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W9" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W9" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
@@ -1305,67 +1308,63 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24848.51</v>
+        <v>24724.34</v>
       </c>
       <c r="C10" t="n">
-        <v>24869.63</v>
+        <v>24762.24</v>
       </c>
       <c r="D10" t="n">
-        <v>24547.7</v>
+        <v>24556.78</v>
       </c>
       <c r="E10" t="n">
-        <v>24671.22</v>
+        <v>24626.89</v>
       </c>
       <c r="F10" t="n">
-        <v>-323.61</v>
+        <v>-44.33</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0018</v>
       </c>
       <c r="H10" t="n">
-        <v>321.93</v>
+        <v>205.46</v>
       </c>
       <c r="I10" t="n">
-        <v>24435.16</v>
+        <v>24225.77</v>
       </c>
       <c r="J10" t="n">
-        <v>24703.19</v>
+        <v>24330.57</v>
       </c>
       <c r="K10" t="n">
-        <v>24831.55</v>
+        <v>24510.25</v>
       </c>
       <c r="L10" t="n">
-        <v>24959.92</v>
+        <v>24689.94</v>
       </c>
       <c r="M10" t="n">
-        <v>25158.11</v>
+        <v>24832.19</v>
       </c>
       <c r="N10" t="n">
-        <v>25356.3</v>
+        <v>24974.43</v>
       </c>
       <c r="O10" t="n">
-        <v>25414.84</v>
+        <v>25191.56</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1382,55 +1381,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24724.34</v>
+        <v>24815.22</v>
       </c>
       <c r="C11" t="n">
-        <v>24762.24</v>
+        <v>25024.27</v>
       </c>
       <c r="D11" t="n">
-        <v>24556.78</v>
+        <v>24794.84</v>
       </c>
       <c r="E11" t="n">
-        <v>24626.89</v>
+        <v>24995.81</v>
       </c>
       <c r="F11" t="n">
-        <v>-44.33</v>
+        <v>368.92</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.015</v>
       </c>
       <c r="H11" t="n">
-        <v>205.46</v>
+        <v>229.43</v>
       </c>
       <c r="I11" t="n">
-        <v>24225.77</v>
+        <v>24351.32</v>
       </c>
       <c r="J11" t="n">
-        <v>24330.57</v>
+        <v>24405.12</v>
       </c>
       <c r="K11" t="n">
-        <v>24510.25</v>
+        <v>24524.16</v>
       </c>
       <c r="L11" t="n">
-        <v>24689.94</v>
+        <v>24643.2</v>
       </c>
       <c r="M11" t="n">
-        <v>24832.19</v>
+        <v>24729.62</v>
       </c>
       <c r="N11" t="n">
-        <v>24974.43</v>
+        <v>24816.04</v>
       </c>
       <c r="O11" t="n">
-        <v>25191.56</v>
+        <v>24967.7</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1441,78 +1444,80 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W11" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W11" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24815.22</v>
+        <v>25028.93</v>
       </c>
       <c r="C12" t="n">
-        <v>25024.27</v>
+        <v>25095.66</v>
       </c>
       <c r="D12" t="n">
-        <v>24794.84</v>
+        <v>24887</v>
       </c>
       <c r="E12" t="n">
-        <v>24995.81</v>
+        <v>25040.28</v>
       </c>
       <c r="F12" t="n">
-        <v>368.92</v>
+        <v>44.47</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.015</v>
+        <v>0.0018</v>
       </c>
       <c r="H12" t="n">
-        <v>229.43</v>
+        <v>208.66</v>
       </c>
       <c r="I12" t="n">
-        <v>24351.32</v>
+        <v>24565.41</v>
       </c>
       <c r="J12" t="n">
-        <v>24405.12</v>
+        <v>24809.51</v>
       </c>
       <c r="K12" t="n">
-        <v>24524.16</v>
+        <v>24881.1</v>
       </c>
       <c r="L12" t="n">
-        <v>24643.2</v>
+        <v>24952.68</v>
       </c>
       <c r="M12" t="n">
-        <v>24729.62</v>
+        <v>25110.53</v>
       </c>
       <c r="N12" t="n">
-        <v>24816.04</v>
+        <v>25268.37</v>
       </c>
       <c r="O12" t="n">
-        <v>24967.7</v>
+        <v>25253.7</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1530,18 +1535,14 @@
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
@@ -1553,50 +1554,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25028.93</v>
+        <v>25025.13</v>
       </c>
       <c r="C13" t="n">
-        <v>25095.66</v>
+        <v>25655.82</v>
       </c>
       <c r="D13" t="n">
-        <v>24887</v>
+        <v>24994.64</v>
       </c>
       <c r="E13" t="n">
-        <v>25040.28</v>
+        <v>25580.88</v>
       </c>
       <c r="F13" t="n">
-        <v>44.47</v>
+        <v>540.6</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0216</v>
       </c>
       <c r="H13" t="n">
-        <v>208.66</v>
+        <v>661.1799999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>24565.41</v>
+        <v>24678.34</v>
       </c>
       <c r="J13" t="n">
-        <v>24809.51</v>
+        <v>24856.09</v>
       </c>
       <c r="K13" t="n">
-        <v>24881.1</v>
+        <v>24935.95</v>
       </c>
       <c r="L13" t="n">
-        <v>24952.68</v>
+        <v>25015.8</v>
       </c>
       <c r="M13" t="n">
-        <v>25110.53</v>
+        <v>25144.61</v>
       </c>
       <c r="N13" t="n">
-        <v>25268.37</v>
+        <v>25273.41</v>
       </c>
       <c r="O13" t="n">
-        <v>25253.7</v>
+        <v>25304.32</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1614,14 +1615,18 @@
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
@@ -1633,50 +1638,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25025.13</v>
+        <v>25763.97</v>
       </c>
       <c r="C14" t="n">
-        <v>25655.82</v>
+        <v>25826.78</v>
       </c>
       <c r="D14" t="n">
-        <v>24994.64</v>
+        <v>25611.69</v>
       </c>
       <c r="E14" t="n">
-        <v>25580.88</v>
+        <v>25779.31</v>
       </c>
       <c r="F14" t="n">
-        <v>540.6</v>
+        <v>198.43</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0216</v>
+        <v>0.0078</v>
       </c>
       <c r="H14" t="n">
-        <v>661.1799999999999</v>
+        <v>215.09</v>
       </c>
       <c r="I14" t="n">
-        <v>24678.34</v>
+        <v>24333.46</v>
       </c>
       <c r="J14" t="n">
-        <v>24856.09</v>
+        <v>25047.53</v>
       </c>
       <c r="K14" t="n">
-        <v>24935.95</v>
+        <v>25250.29</v>
       </c>
       <c r="L14" t="n">
-        <v>25015.8</v>
+        <v>25453.06</v>
       </c>
       <c r="M14" t="n">
-        <v>25144.61</v>
+        <v>25911.47</v>
       </c>
       <c r="N14" t="n">
-        <v>25273.41</v>
+        <v>26369.89</v>
       </c>
       <c r="O14" t="n">
-        <v>25304.32</v>
+        <v>26317</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1694,18 +1699,14 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
@@ -1717,50 +1718,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25763.97</v>
+        <v>25811.9</v>
       </c>
       <c r="C15" t="n">
-        <v>25826.78</v>
+        <v>25900.1</v>
       </c>
       <c r="D15" t="n">
-        <v>25611.69</v>
+        <v>25698.56</v>
       </c>
       <c r="E15" t="n">
-        <v>25779.31</v>
+        <v>25817.89</v>
       </c>
       <c r="F15" t="n">
-        <v>198.43</v>
+        <v>38.58</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0078</v>
+        <v>0.0015</v>
       </c>
       <c r="H15" t="n">
-        <v>215.09</v>
+        <v>201.54</v>
       </c>
       <c r="I15" t="n">
-        <v>24333.46</v>
+        <v>25396.6</v>
       </c>
       <c r="J15" t="n">
-        <v>25047.53</v>
+        <v>25594.26</v>
       </c>
       <c r="K15" t="n">
-        <v>25250.29</v>
+        <v>25671.77</v>
       </c>
       <c r="L15" t="n">
-        <v>25453.06</v>
+        <v>25749.27</v>
       </c>
       <c r="M15" t="n">
-        <v>25911.47</v>
+        <v>25886.86</v>
       </c>
       <c r="N15" t="n">
-        <v>26369.89</v>
+        <v>26024.44</v>
       </c>
       <c r="O15" t="n">
-        <v>26317</v>
+        <v>26041.87</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1773,12 +1774,12 @@
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U15" s="8" t="n">
@@ -1797,69 +1798,73 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25811.9</v>
+        <v>25770.45</v>
       </c>
       <c r="C16" t="n">
-        <v>25900.1</v>
+        <v>25811.97</v>
       </c>
       <c r="D16" t="n">
-        <v>25698.56</v>
+        <v>25465.12</v>
       </c>
       <c r="E16" t="n">
-        <v>25817.89</v>
+        <v>25465.25</v>
       </c>
       <c r="F16" t="n">
-        <v>38.58</v>
+        <v>-352.64</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0137</v>
       </c>
       <c r="H16" t="n">
-        <v>201.54</v>
+        <v>346.85</v>
       </c>
       <c r="I16" t="n">
-        <v>25396.6</v>
+        <v>25497.02</v>
       </c>
       <c r="J16" t="n">
-        <v>25594.26</v>
+        <v>25625.63</v>
       </c>
       <c r="K16" t="n">
-        <v>25671.77</v>
+        <v>25717.12</v>
       </c>
       <c r="L16" t="n">
-        <v>25749.27</v>
+        <v>25808.61</v>
       </c>
       <c r="M16" t="n">
-        <v>25886.86</v>
+        <v>25918.66</v>
       </c>
       <c r="N16" t="n">
-        <v>26024.44</v>
+        <v>26028.71</v>
       </c>
       <c r="O16" t="n">
-        <v>26041.87</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>26101.64</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1867,9 +1872,9 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W16" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
@@ -1877,59 +1882,59 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25770.45</v>
+        <v>25274.94</v>
       </c>
       <c r="C17" t="n">
-        <v>25811.97</v>
+        <v>25280.16</v>
       </c>
       <c r="D17" t="n">
-        <v>25465.12</v>
+        <v>24830.17</v>
       </c>
       <c r="E17" t="n">
-        <v>25465.25</v>
+        <v>24897.45</v>
       </c>
       <c r="F17" t="n">
-        <v>-352.64</v>
+        <v>-567.8</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0223</v>
       </c>
       <c r="H17" t="n">
-        <v>346.85</v>
+        <v>449.99</v>
       </c>
       <c r="I17" t="n">
-        <v>25497.02</v>
+        <v>25118.27</v>
       </c>
       <c r="J17" t="n">
-        <v>25625.63</v>
+        <v>25031.75</v>
       </c>
       <c r="K17" t="n">
-        <v>25717.12</v>
+        <v>25291.82</v>
       </c>
       <c r="L17" t="n">
-        <v>25808.61</v>
+        <v>25551.9</v>
       </c>
       <c r="M17" t="n">
-        <v>25918.66</v>
+        <v>25638.68</v>
       </c>
       <c r="N17" t="n">
-        <v>26028.71</v>
+        <v>25725.45</v>
       </c>
       <c r="O17" t="n">
-        <v>26101.64</v>
+        <v>26158.82</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
@@ -1961,74 +1966,70 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25274.94</v>
+        <v>25097.48</v>
       </c>
       <c r="C18" t="n">
-        <v>25280.16</v>
+        <v>25127.76</v>
       </c>
       <c r="D18" t="n">
-        <v>24830.17</v>
+        <v>24867.32</v>
       </c>
       <c r="E18" t="n">
-        <v>24897.45</v>
+        <v>25118.27</v>
       </c>
       <c r="F18" t="n">
-        <v>-567.8</v>
+        <v>220.82</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0089</v>
       </c>
       <c r="H18" t="n">
-        <v>449.99</v>
+        <v>260.44</v>
       </c>
       <c r="I18" t="n">
-        <v>25118.27</v>
+        <v>24380.18</v>
       </c>
       <c r="J18" t="n">
-        <v>25031.75</v>
+        <v>24368.6</v>
       </c>
       <c r="K18" t="n">
-        <v>25291.82</v>
+        <v>24672.45</v>
       </c>
       <c r="L18" t="n">
-        <v>25551.9</v>
+        <v>24976.31</v>
       </c>
       <c r="M18" t="n">
-        <v>25638.68</v>
+        <v>25122.44</v>
       </c>
       <c r="N18" t="n">
-        <v>25725.45</v>
+        <v>25268.58</v>
       </c>
       <c r="O18" t="n">
-        <v>26158.82</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q18" s="6" t="inlineStr">
+        <v>25730.15</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
@@ -2040,55 +2041,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25097.48</v>
+        <v>25081.19</v>
       </c>
       <c r="C19" t="n">
-        <v>25127.76</v>
+        <v>25195.83</v>
       </c>
       <c r="D19" t="n">
-        <v>24867.32</v>
+        <v>24937.52</v>
       </c>
       <c r="E19" t="n">
-        <v>25118.27</v>
+        <v>25067.09</v>
       </c>
       <c r="F19" t="n">
-        <v>220.82</v>
+        <v>-51.18</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.002</v>
       </c>
       <c r="H19" t="n">
-        <v>260.44</v>
+        <v>258.31</v>
       </c>
       <c r="I19" t="n">
-        <v>24380.18</v>
+        <v>24606.88</v>
       </c>
       <c r="J19" t="n">
-        <v>24368.6</v>
+        <v>24918.19</v>
       </c>
       <c r="K19" t="n">
-        <v>24672.45</v>
+        <v>24988.05</v>
       </c>
       <c r="L19" t="n">
-        <v>24976.31</v>
+        <v>25057.9</v>
       </c>
       <c r="M19" t="n">
-        <v>25122.44</v>
+        <v>25248.49</v>
       </c>
       <c r="N19" t="n">
-        <v>25268.58</v>
+        <v>25439.07</v>
       </c>
       <c r="O19" t="n">
-        <v>25730.15</v>
+        <v>25388.2</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2096,18 +2101,18 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2129,50 +2134,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25081.19</v>
+        <v>24963.8</v>
       </c>
       <c r="C20" t="n">
-        <v>25195.83</v>
+        <v>25154.58</v>
       </c>
       <c r="D20" t="n">
-        <v>24937.52</v>
+        <v>24963.8</v>
       </c>
       <c r="E20" t="n">
-        <v>25067.09</v>
+        <v>25114.25</v>
       </c>
       <c r="F20" t="n">
-        <v>-51.18</v>
+        <v>47.16</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="H20" t="n">
-        <v>258.31</v>
+        <v>190.78</v>
       </c>
       <c r="I20" t="n">
-        <v>24606.88</v>
+        <v>24679.21</v>
       </c>
       <c r="J20" t="n">
-        <v>24918.19</v>
+        <v>24808.99</v>
       </c>
       <c r="K20" t="n">
-        <v>24988.05</v>
+        <v>24937.93</v>
       </c>
       <c r="L20" t="n">
-        <v>25057.9</v>
+        <v>25066.88</v>
       </c>
       <c r="M20" t="n">
-        <v>25248.49</v>
+        <v>25196.25</v>
       </c>
       <c r="N20" t="n">
-        <v>25439.07</v>
+        <v>25325.61</v>
       </c>
       <c r="O20" t="n">
-        <v>25388.2</v>
+        <v>25454.14</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2180,10 +2185,8 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R20" s="6" t="n">
+        <v/>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
@@ -2213,59 +2216,63 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24963.8</v>
+        <v>24932.62</v>
       </c>
       <c r="C21" t="n">
-        <v>25154.58</v>
+        <v>25204.68</v>
       </c>
       <c r="D21" t="n">
-        <v>24963.8</v>
+        <v>24869.25</v>
       </c>
       <c r="E21" t="n">
-        <v>25114.25</v>
+        <v>25147.03</v>
       </c>
       <c r="F21" t="n">
-        <v>47.16</v>
+        <v>32.78</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0013</v>
       </c>
       <c r="H21" t="n">
-        <v>190.78</v>
+        <v>335.43</v>
       </c>
       <c r="I21" t="n">
-        <v>24679.21</v>
+        <v>24773.02</v>
       </c>
       <c r="J21" t="n">
-        <v>24808.99</v>
+        <v>24951</v>
       </c>
       <c r="K21" t="n">
-        <v>24937.93</v>
+        <v>25018.86</v>
       </c>
       <c r="L21" t="n">
-        <v>25066.88</v>
+        <v>25086.72</v>
       </c>
       <c r="M21" t="n">
-        <v>25196.25</v>
+        <v>25209.64</v>
       </c>
       <c r="N21" t="n">
-        <v>25325.61</v>
+        <v>25332.56</v>
       </c>
       <c r="O21" t="n">
-        <v>25454.14</v>
+        <v>25345.36</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
@@ -2295,50 +2302,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24932.62</v>
+        <v>24970.05</v>
       </c>
       <c r="C22" t="n">
-        <v>25204.68</v>
+        <v>25055.48</v>
       </c>
       <c r="D22" t="n">
-        <v>24869.25</v>
+        <v>24839.23</v>
       </c>
       <c r="E22" t="n">
-        <v>25147.03</v>
+        <v>24999.53</v>
       </c>
       <c r="F22" t="n">
-        <v>32.78</v>
+        <v>-147.5</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0059</v>
       </c>
       <c r="H22" t="n">
-        <v>335.43</v>
+        <v>216.25</v>
       </c>
       <c r="I22" t="n">
-        <v>24773.02</v>
+        <v>24533.82</v>
       </c>
       <c r="J22" t="n">
-        <v>24951</v>
+        <v>24866.63</v>
       </c>
       <c r="K22" t="n">
-        <v>25018.86</v>
+        <v>24979.31</v>
       </c>
       <c r="L22" t="n">
-        <v>25086.72</v>
+        <v>25092</v>
       </c>
       <c r="M22" t="n">
-        <v>25209.64</v>
+        <v>25314.74</v>
       </c>
       <c r="N22" t="n">
-        <v>25332.56</v>
+        <v>25537.49</v>
       </c>
       <c r="O22" t="n">
-        <v>25345.36</v>
+        <v>25540.11</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2350,12 +2357,12 @@
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2372,59 +2379,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24970.05</v>
+        <v>25018.95</v>
       </c>
       <c r="C23" t="n">
-        <v>25055.48</v>
+        <v>25021.51</v>
       </c>
       <c r="D23" t="n">
-        <v>24839.23</v>
+        <v>24696.17</v>
       </c>
       <c r="E23" t="n">
-        <v>24999.53</v>
+        <v>24915.49</v>
       </c>
       <c r="F23" t="n">
-        <v>-147.5</v>
+        <v>-84.04000000000001</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0059</v>
+        <v>-0.0034</v>
       </c>
       <c r="H23" t="n">
-        <v>216.25</v>
+        <v>325.34</v>
       </c>
       <c r="I23" t="n">
-        <v>24533.82</v>
+        <v>24622.98</v>
       </c>
       <c r="J23" t="n">
-        <v>24866.63</v>
+        <v>24809.37</v>
       </c>
       <c r="K23" t="n">
-        <v>24979.31</v>
+        <v>24891.4</v>
       </c>
       <c r="L23" t="n">
-        <v>25092</v>
+        <v>24973.44</v>
       </c>
       <c r="M23" t="n">
-        <v>25314.74</v>
+        <v>25107.65</v>
       </c>
       <c r="N23" t="n">
-        <v>25537.49</v>
+        <v>25241.87</v>
       </c>
       <c r="O23" t="n">
-        <v>25540.11</v>
+        <v>25271.73</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2463,67 +2466,65 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25018.95</v>
+        <v>24755.09</v>
       </c>
       <c r="C24" t="n">
-        <v>25021.51</v>
+        <v>24850.75</v>
       </c>
       <c r="D24" t="n">
-        <v>24696.17</v>
+        <v>24651.34</v>
       </c>
       <c r="E24" t="n">
-        <v>24915.49</v>
+        <v>24830.98</v>
       </c>
       <c r="F24" t="n">
-        <v>-84.04000000000001</v>
+        <v>-84.51000000000001</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>-0.0034</v>
       </c>
       <c r="H24" t="n">
-        <v>325.34</v>
+        <v>199.41</v>
       </c>
       <c r="I24" t="n">
-        <v>24622.98</v>
+        <v>24370.83</v>
       </c>
       <c r="J24" t="n">
-        <v>24809.37</v>
+        <v>24618.48</v>
       </c>
       <c r="K24" t="n">
-        <v>24891.4</v>
+        <v>24752.82</v>
       </c>
       <c r="L24" t="n">
-        <v>24973.44</v>
+        <v>24887.17</v>
       </c>
       <c r="M24" t="n">
-        <v>25107.65</v>
+        <v>25078.16</v>
       </c>
       <c r="N24" t="n">
-        <v>25241.87</v>
+        <v>25269.16</v>
       </c>
       <c r="O24" t="n">
-        <v>25271.73</v>
+        <v>25346.85</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q24" s="6" t="n">
+        <v/>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2545,50 +2546,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24755.09</v>
+        <v>24769.15</v>
       </c>
       <c r="C25" t="n">
-        <v>24850.75</v>
+        <v>24974.53</v>
       </c>
       <c r="D25" t="n">
-        <v>24651.34</v>
+        <v>24751.13</v>
       </c>
       <c r="E25" t="n">
-        <v>24830.98</v>
+        <v>24846.69</v>
       </c>
       <c r="F25" t="n">
-        <v>-84.51000000000001</v>
+        <v>15.71</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>199.41</v>
+        <v>223.4</v>
       </c>
       <c r="I25" t="n">
-        <v>24370.83</v>
+        <v>24451.93</v>
       </c>
       <c r="J25" t="n">
-        <v>24618.48</v>
+        <v>24671.54</v>
       </c>
       <c r="K25" t="n">
-        <v>24752.82</v>
+        <v>24731.28</v>
       </c>
       <c r="L25" t="n">
-        <v>24887.17</v>
+        <v>24791.01</v>
       </c>
       <c r="M25" t="n">
-        <v>25078.16</v>
+        <v>24930.69</v>
       </c>
       <c r="N25" t="n">
-        <v>25269.16</v>
+        <v>25070.36</v>
       </c>
       <c r="O25" t="n">
-        <v>25346.85</v>
+        <v>25050.16</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2596,18 +2597,18 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2620,55 +2621,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24769.15</v>
+        <v>24922.1</v>
       </c>
       <c r="C26" t="n">
-        <v>24974.53</v>
+        <v>25011.35</v>
       </c>
       <c r="D26" t="n">
-        <v>24751.13</v>
+        <v>24817.34</v>
       </c>
       <c r="E26" t="n">
-        <v>24846.69</v>
+        <v>25011.35</v>
       </c>
       <c r="F26" t="n">
-        <v>15.71</v>
+        <v>164.66</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0066</v>
       </c>
       <c r="H26" t="n">
-        <v>223.4</v>
+        <v>194.01</v>
       </c>
       <c r="I26" t="n">
-        <v>24451.93</v>
+        <v>24527.73</v>
       </c>
       <c r="J26" t="n">
-        <v>24671.54</v>
+        <v>24615.22</v>
       </c>
       <c r="K26" t="n">
-        <v>24731.28</v>
+        <v>24734.99</v>
       </c>
       <c r="L26" t="n">
-        <v>24791.01</v>
+        <v>24854.76</v>
       </c>
       <c r="M26" t="n">
-        <v>24930.69</v>
+        <v>24958.39</v>
       </c>
       <c r="N26" t="n">
-        <v>25070.36</v>
+        <v>25062.02</v>
       </c>
       <c r="O26" t="n">
-        <v>25050.16</v>
+        <v>25197.93</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2681,7 +2686,7 @@
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -2689,8 +2694,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2709,50 +2716,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>24922.1</v>
+        <v>25001.31</v>
       </c>
       <c r="C27" t="n">
-        <v>25011.35</v>
+        <v>25271.34</v>
       </c>
       <c r="D27" t="n">
-        <v>24817.34</v>
+        <v>24984.27</v>
       </c>
       <c r="E27" t="n">
-        <v>25011.35</v>
+        <v>25155.41</v>
       </c>
       <c r="F27" t="n">
-        <v>164.66</v>
+        <v>144.06</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0058</v>
       </c>
       <c r="H27" t="n">
-        <v>194.01</v>
+        <v>287.07</v>
       </c>
       <c r="I27" t="n">
-        <v>24527.73</v>
+        <v>24623.33</v>
       </c>
       <c r="J27" t="n">
-        <v>24615.22</v>
+        <v>24865.84</v>
       </c>
       <c r="K27" t="n">
-        <v>24734.99</v>
+        <v>24914.34</v>
       </c>
       <c r="L27" t="n">
-        <v>24854.76</v>
+        <v>24962.85</v>
       </c>
       <c r="M27" t="n">
-        <v>24958.39</v>
+        <v>25108.35</v>
       </c>
       <c r="N27" t="n">
-        <v>25062.02</v>
+        <v>25253.86</v>
       </c>
       <c r="O27" t="n">
-        <v>25197.93</v>
+        <v>25205.36</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2770,16 +2777,18 @@
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U27" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W27" s="11" t="inlineStr">
         <is>
@@ -2795,171 +2804,165 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25001.31</v>
+        <v>24994.05</v>
       </c>
       <c r="C28" t="n">
-        <v>25271.34</v>
+        <v>25074.28</v>
       </c>
       <c r="D28" t="n">
-        <v>24984.27</v>
+        <v>24696.59</v>
       </c>
       <c r="E28" t="n">
-        <v>25155.41</v>
+        <v>24763.12</v>
       </c>
       <c r="F28" t="n">
-        <v>144.06</v>
+        <v>-392.29</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0156</v>
       </c>
       <c r="H28" t="n">
-        <v>287.07</v>
+        <v>377.69</v>
       </c>
       <c r="I28" t="n">
-        <v>24623.33</v>
+        <v>24697.2</v>
       </c>
       <c r="J28" t="n">
-        <v>24865.84</v>
+        <v>24882.14</v>
       </c>
       <c r="K28" t="n">
-        <v>24914.34</v>
+        <v>25011.88</v>
       </c>
       <c r="L28" t="n">
-        <v>24962.85</v>
+        <v>25141.61</v>
       </c>
       <c r="M28" t="n">
-        <v>25108.35</v>
+        <v>25298.95</v>
       </c>
       <c r="N28" t="n">
-        <v>25253.86</v>
+        <v>25456.28</v>
       </c>
       <c r="O28" t="n">
-        <v>25205.36</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
+        <v>25558.41</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
       </c>
       <c r="W28" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>24994.05</v>
+        <v>24830.41</v>
       </c>
       <c r="C29" t="n">
-        <v>25074.28</v>
+        <v>25099.68</v>
       </c>
       <c r="D29" t="n">
-        <v>24696.59</v>
+        <v>24821.67</v>
       </c>
       <c r="E29" t="n">
-        <v>24763.12</v>
+        <v>25099</v>
       </c>
       <c r="F29" t="n">
-        <v>-392.29</v>
+        <v>335.88</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0136</v>
       </c>
       <c r="H29" t="n">
-        <v>377.69</v>
+        <v>278.01</v>
       </c>
       <c r="I29" t="n">
-        <v>24697.2</v>
+        <v>24318.9</v>
       </c>
       <c r="J29" t="n">
-        <v>24882.14</v>
+        <v>24324.27</v>
       </c>
       <c r="K29" t="n">
-        <v>25011.88</v>
+        <v>24574.27</v>
       </c>
       <c r="L29" t="n">
-        <v>25141.61</v>
+        <v>24824.28</v>
       </c>
       <c r="M29" t="n">
-        <v>25298.95</v>
+        <v>24951.96</v>
       </c>
       <c r="N29" t="n">
-        <v>25456.28</v>
+        <v>25079.65</v>
       </c>
       <c r="O29" t="n">
-        <v>25558.41</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
+        <v>25451.97</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W29" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
@@ -2967,50 +2970,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>24830.41</v>
+        <v>25459.32</v>
       </c>
       <c r="C30" t="n">
-        <v>25099.68</v>
+        <v>25560.4</v>
       </c>
       <c r="D30" t="n">
-        <v>24821.67</v>
+        <v>25361.03</v>
       </c>
       <c r="E30" t="n">
-        <v>25099</v>
+        <v>25361.03</v>
       </c>
       <c r="F30" t="n">
-        <v>335.88</v>
+        <v>262.03</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0104</v>
       </c>
       <c r="H30" t="n">
-        <v>278.01</v>
+        <v>199.37</v>
       </c>
       <c r="I30" t="n">
-        <v>24318.9</v>
+        <v>24543.66</v>
       </c>
       <c r="J30" t="n">
-        <v>24324.27</v>
+        <v>24890.15</v>
       </c>
       <c r="K30" t="n">
-        <v>24574.27</v>
+        <v>24960</v>
       </c>
       <c r="L30" t="n">
-        <v>24824.28</v>
+        <v>25029.84</v>
       </c>
       <c r="M30" t="n">
-        <v>24951.96</v>
+        <v>25238</v>
       </c>
       <c r="N30" t="n">
-        <v>25079.65</v>
+        <v>25446.17</v>
       </c>
       <c r="O30" t="n">
-        <v>25451.97</v>
+        <v>25377.69</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3033,11 +3036,13 @@
       </c>
       <c r="U30" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
@@ -3049,50 +3054,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25459.32</v>
+        <v>25496.13</v>
       </c>
       <c r="C31" t="n">
-        <v>25560.4</v>
+        <v>25553.47</v>
       </c>
       <c r="D31" t="n">
-        <v>25361.03</v>
+        <v>25307.17</v>
       </c>
       <c r="E31" t="n">
-        <v>25361.03</v>
+        <v>25464.01</v>
       </c>
       <c r="F31" t="n">
-        <v>262.03</v>
+        <v>102.98</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0104</v>
+        <v>0.0041</v>
       </c>
       <c r="H31" t="n">
-        <v>199.37</v>
+        <v>246.3</v>
       </c>
       <c r="I31" t="n">
-        <v>24543.66</v>
+        <v>25161.66</v>
       </c>
       <c r="J31" t="n">
-        <v>24890.15</v>
+        <v>25111.82</v>
       </c>
       <c r="K31" t="n">
-        <v>24960</v>
+        <v>25261.34</v>
       </c>
       <c r="L31" t="n">
-        <v>25029.84</v>
+        <v>25410.87</v>
       </c>
       <c r="M31" t="n">
-        <v>25238</v>
+        <v>25460.71</v>
       </c>
       <c r="N31" t="n">
-        <v>25446.17</v>
+        <v>25510.56</v>
       </c>
       <c r="O31" t="n">
-        <v>25377.69</v>
+        <v>25759.77</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3110,7 +3115,7 @@
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U31" s="8" t="inlineStr">
@@ -3118,65 +3123,67 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V31" s="8" t="n">
+        <v/>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25496.13</v>
+        <v>25551.97</v>
       </c>
       <c r="C32" t="n">
-        <v>25553.47</v>
+        <v>25571.45</v>
       </c>
       <c r="D32" t="n">
-        <v>25307.17</v>
+        <v>25336.39</v>
       </c>
       <c r="E32" t="n">
-        <v>25464.01</v>
+        <v>25460.48</v>
       </c>
       <c r="F32" t="n">
-        <v>102.98</v>
+        <v>-3.53</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0001</v>
       </c>
       <c r="H32" t="n">
-        <v>246.3</v>
+        <v>235.06</v>
       </c>
       <c r="I32" t="n">
-        <v>25161.66</v>
+        <v>25060.87</v>
       </c>
       <c r="J32" t="n">
-        <v>25111.82</v>
+        <v>25234.55</v>
       </c>
       <c r="K32" t="n">
-        <v>25261.34</v>
+        <v>25340.86</v>
       </c>
       <c r="L32" t="n">
-        <v>25410.87</v>
+        <v>25447.17</v>
       </c>
       <c r="M32" t="n">
-        <v>25460.71</v>
+        <v>25587.16</v>
       </c>
       <c r="N32" t="n">
-        <v>25510.56</v>
+        <v>25727.16</v>
       </c>
       <c r="O32" t="n">
-        <v>25759.77</v>
+        <v>25799.77</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3184,23 +3191,21 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3212,57 +3217,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25551.97</v>
+        <v>25487.45</v>
       </c>
       <c r="C33" t="n">
-        <v>25571.45</v>
+        <v>25651.16</v>
       </c>
       <c r="D33" t="n">
-        <v>25336.39</v>
+        <v>25303.11</v>
       </c>
       <c r="E33" t="n">
-        <v>25460.48</v>
+        <v>25612.03</v>
       </c>
       <c r="F33" t="n">
-        <v>-3.53</v>
+        <v>151.55</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.006</v>
       </c>
       <c r="H33" t="n">
-        <v>235.06</v>
+        <v>348.05</v>
       </c>
       <c r="I33" t="n">
-        <v>25060.87</v>
+        <v>25101.33</v>
       </c>
       <c r="J33" t="n">
-        <v>25234.55</v>
+        <v>25228.7</v>
       </c>
       <c r="K33" t="n">
-        <v>25340.86</v>
+        <v>25342.95</v>
       </c>
       <c r="L33" t="n">
-        <v>25447.17</v>
+        <v>25457.2</v>
       </c>
       <c r="M33" t="n">
-        <v>25587.16</v>
+        <v>25578.01</v>
       </c>
       <c r="N33" t="n">
-        <v>25727.16</v>
+        <v>25698.82</v>
       </c>
       <c r="O33" t="n">
-        <v>25799.77</v>
+        <v>25806.51</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3277,11 +3282,13 @@
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3303,50 +3310,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25487.45</v>
+        <v>25709.37</v>
       </c>
       <c r="C34" t="n">
-        <v>25651.16</v>
+        <v>25891.51</v>
       </c>
       <c r="D34" t="n">
-        <v>25303.11</v>
+        <v>25549.53</v>
       </c>
       <c r="E34" t="n">
-        <v>25612.03</v>
+        <v>25629.24</v>
       </c>
       <c r="F34" t="n">
-        <v>151.55</v>
+        <v>17.21</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0007</v>
       </c>
       <c r="H34" t="n">
-        <v>348.05</v>
+        <v>341.98</v>
       </c>
       <c r="I34" t="n">
-        <v>25101.33</v>
+        <v>24955.06</v>
       </c>
       <c r="J34" t="n">
-        <v>25228.7</v>
+        <v>25331.43</v>
       </c>
       <c r="K34" t="n">
-        <v>25342.95</v>
+        <v>25438</v>
       </c>
       <c r="L34" t="n">
-        <v>25457.2</v>
+        <v>25544.58</v>
       </c>
       <c r="M34" t="n">
-        <v>25578.01</v>
+        <v>25786.05</v>
       </c>
       <c r="N34" t="n">
-        <v>25698.82</v>
+        <v>26027.53</v>
       </c>
       <c r="O34" t="n">
-        <v>25806.51</v>
+        <v>25999.21</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3354,19 +3361,17 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R34" s="6" t="n">
+        <v/>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U34" s="8" t="n">
@@ -3380,59 +3385,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25709.37</v>
+        <v>25855.12</v>
       </c>
       <c r="C35" t="n">
-        <v>25891.51</v>
+        <v>26096.93</v>
       </c>
       <c r="D35" t="n">
-        <v>25549.53</v>
+        <v>25855.12</v>
       </c>
       <c r="E35" t="n">
-        <v>25629.24</v>
+        <v>26001.31</v>
       </c>
       <c r="F35" t="n">
-        <v>17.21</v>
+        <v>372.07</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0145</v>
       </c>
       <c r="H35" t="n">
-        <v>341.98</v>
+        <v>241.81</v>
       </c>
       <c r="I35" t="n">
-        <v>24955.06</v>
+        <v>25207.55</v>
       </c>
       <c r="J35" t="n">
-        <v>25331.43</v>
+        <v>25241.62</v>
       </c>
       <c r="K35" t="n">
-        <v>25438</v>
+        <v>25458.25</v>
       </c>
       <c r="L35" t="n">
-        <v>25544.58</v>
+        <v>25674.88</v>
       </c>
       <c r="M35" t="n">
-        <v>25786.05</v>
+        <v>25800.23</v>
       </c>
       <c r="N35" t="n">
-        <v>26027.53</v>
+        <v>25925.58</v>
       </c>
       <c r="O35" t="n">
-        <v>25999.21</v>
+        <v>26233.49</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3445,7 +3446,7 @@
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
@@ -3453,8 +3454,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U35" s="8" t="n">
-        <v/>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3469,50 +3472,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25855.12</v>
+        <v>26189.62</v>
       </c>
       <c r="C36" t="n">
-        <v>26096.93</v>
+        <v>26266.5</v>
       </c>
       <c r="D36" t="n">
-        <v>25855.12</v>
+        <v>26082.43</v>
       </c>
       <c r="E36" t="n">
-        <v>26001.31</v>
+        <v>26202.35</v>
       </c>
       <c r="F36" t="n">
-        <v>372.07</v>
+        <v>201.04</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0077</v>
       </c>
       <c r="H36" t="n">
-        <v>241.81</v>
+        <v>184.07</v>
       </c>
       <c r="I36" t="n">
-        <v>25207.55</v>
+        <v>25613.31</v>
       </c>
       <c r="J36" t="n">
-        <v>25241.62</v>
+        <v>25772.14</v>
       </c>
       <c r="K36" t="n">
-        <v>25458.25</v>
+        <v>25880.41</v>
       </c>
       <c r="L36" t="n">
-        <v>25674.88</v>
+        <v>25988.67</v>
       </c>
       <c r="M36" t="n">
-        <v>25800.23</v>
+        <v>26122.22</v>
       </c>
       <c r="N36" t="n">
-        <v>25925.58</v>
+        <v>26255.76</v>
       </c>
       <c r="O36" t="n">
-        <v>26233.49</v>
+        <v>26338.74</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3551,50 +3554,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26189.62</v>
+        <v>26393.43</v>
       </c>
       <c r="C37" t="n">
-        <v>26266.5</v>
+        <v>26403.81</v>
       </c>
       <c r="D37" t="n">
-        <v>26082.43</v>
+        <v>26123.18</v>
       </c>
       <c r="E37" t="n">
-        <v>26202.35</v>
+        <v>26126.3</v>
       </c>
       <c r="F37" t="n">
-        <v>201.04</v>
+        <v>-76.05</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0029</v>
       </c>
       <c r="H37" t="n">
-        <v>184.07</v>
+        <v>280.63</v>
       </c>
       <c r="I37" t="n">
-        <v>25613.31</v>
+        <v>25898.36</v>
       </c>
       <c r="J37" t="n">
-        <v>25772.14</v>
+        <v>26032.22</v>
       </c>
       <c r="K37" t="n">
-        <v>25880.41</v>
+        <v>26110.31</v>
       </c>
       <c r="L37" t="n">
-        <v>25988.67</v>
+        <v>26188.41</v>
       </c>
       <c r="M37" t="n">
-        <v>26122.22</v>
+        <v>26294.38</v>
       </c>
       <c r="N37" t="n">
-        <v>26255.76</v>
+        <v>26400.36</v>
       </c>
       <c r="O37" t="n">
-        <v>26338.74</v>
+        <v>26450.57</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3602,12 +3605,14 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
@@ -3617,7 +3622,7 @@
       </c>
       <c r="U37" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V37" s="8" t="n">
@@ -3628,55 +3633,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26393.43</v>
+        <v>26116.27</v>
       </c>
       <c r="C38" t="n">
-        <v>26403.81</v>
+        <v>26229.33</v>
       </c>
       <c r="D38" t="n">
-        <v>26123.18</v>
+        <v>26081.69</v>
       </c>
       <c r="E38" t="n">
-        <v>26126.3</v>
+        <v>26140.13</v>
       </c>
       <c r="F38" t="n">
-        <v>-76.05</v>
+        <v>13.83</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0005</v>
       </c>
       <c r="H38" t="n">
-        <v>280.63</v>
+        <v>147.64</v>
       </c>
       <c r="I38" t="n">
-        <v>25898.36</v>
+        <v>25842.55</v>
       </c>
       <c r="J38" t="n">
-        <v>26032.22</v>
+        <v>25777.07</v>
       </c>
       <c r="K38" t="n">
-        <v>26110.31</v>
+        <v>25985.99</v>
       </c>
       <c r="L38" t="n">
-        <v>26188.41</v>
+        <v>26194.9</v>
       </c>
       <c r="M38" t="n">
-        <v>26294.38</v>
+        <v>26266.62</v>
       </c>
       <c r="N38" t="n">
-        <v>26400.36</v>
+        <v>26338.33</v>
       </c>
       <c r="O38" t="n">
-        <v>26450.57</v>
+        <v>26684.44</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3684,25 +3693,19 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3714,57 +3717,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26116.27</v>
+        <v>26235.8</v>
       </c>
       <c r="C39" t="n">
-        <v>26229.33</v>
+        <v>26445.18</v>
       </c>
       <c r="D39" t="n">
-        <v>26081.69</v>
+        <v>26223.64</v>
       </c>
       <c r="E39" t="n">
-        <v>26140.13</v>
+        <v>26319.45</v>
       </c>
       <c r="F39" t="n">
-        <v>13.83</v>
+        <v>179.32</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0069</v>
       </c>
       <c r="H39" t="n">
-        <v>147.64</v>
+        <v>221.54</v>
       </c>
       <c r="I39" t="n">
-        <v>25842.55</v>
+        <v>25934.05</v>
       </c>
       <c r="J39" t="n">
-        <v>25777.07</v>
+        <v>25984.8</v>
       </c>
       <c r="K39" t="n">
-        <v>25985.99</v>
+        <v>26066.31</v>
       </c>
       <c r="L39" t="n">
-        <v>26194.9</v>
+        <v>26147.82</v>
       </c>
       <c r="M39" t="n">
-        <v>26266.62</v>
+        <v>26213.95</v>
       </c>
       <c r="N39" t="n">
-        <v>26338.33</v>
+        <v>26280.08</v>
       </c>
       <c r="O39" t="n">
-        <v>26684.44</v>
+        <v>26376.97</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3775,78 +3778,80 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v/>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>26235.8</v>
+        <v>26360.44</v>
       </c>
       <c r="C40" t="n">
-        <v>26445.18</v>
+        <v>26441.91</v>
       </c>
       <c r="D40" t="n">
-        <v>26223.64</v>
+        <v>26302.19</v>
       </c>
       <c r="E40" t="n">
-        <v>26319.45</v>
+        <v>26323.88</v>
       </c>
       <c r="F40" t="n">
-        <v>179.32</v>
+        <v>4.43</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0002</v>
       </c>
       <c r="H40" t="n">
-        <v>221.54</v>
+        <v>139.72</v>
       </c>
       <c r="I40" t="n">
-        <v>25934.05</v>
+        <v>26002.1</v>
       </c>
       <c r="J40" t="n">
-        <v>25984.8</v>
+        <v>26090.43</v>
       </c>
       <c r="K40" t="n">
-        <v>26066.31</v>
+        <v>26208.68</v>
       </c>
       <c r="L40" t="n">
-        <v>26147.82</v>
+        <v>26326.93</v>
       </c>
       <c r="M40" t="n">
-        <v>26213.95</v>
+        <v>26430.22</v>
       </c>
       <c r="N40" t="n">
-        <v>26280.08</v>
+        <v>26533.51</v>
       </c>
       <c r="O40" t="n">
-        <v>26376.97</v>
+        <v>26666.72</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3857,9 +3862,9 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
@@ -3867,70 +3872,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v/>
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26360.44</v>
+        <v>26378</v>
       </c>
       <c r="C41" t="n">
-        <v>26441.91</v>
+        <v>26504.54</v>
       </c>
       <c r="D41" t="n">
-        <v>26302.19</v>
+        <v>26245.57</v>
       </c>
       <c r="E41" t="n">
-        <v>26323.88</v>
+        <v>26391.42</v>
       </c>
       <c r="F41" t="n">
-        <v>4.43</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0026</v>
       </c>
       <c r="H41" t="n">
-        <v>139.72</v>
+        <v>258.97</v>
       </c>
       <c r="I41" t="n">
-        <v>26002.1</v>
+        <v>26162.47</v>
       </c>
       <c r="J41" t="n">
-        <v>26090.43</v>
+        <v>26160.08</v>
       </c>
       <c r="K41" t="n">
-        <v>26208.68</v>
+        <v>26254.02</v>
       </c>
       <c r="L41" t="n">
-        <v>26326.93</v>
+        <v>26347.97</v>
       </c>
       <c r="M41" t="n">
-        <v>26430.22</v>
+        <v>26393.74</v>
       </c>
       <c r="N41" t="n">
-        <v>26533.51</v>
+        <v>26439.52</v>
       </c>
       <c r="O41" t="n">
-        <v>26666.72</v>
+        <v>26581.63</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3938,21 +3943,25 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3971,50 +3980,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26378</v>
+        <v>26452</v>
       </c>
       <c r="C42" t="n">
-        <v>26504.54</v>
+        <v>26573.5</v>
       </c>
       <c r="D42" t="n">
-        <v>26245.57</v>
+        <v>26313.58</v>
       </c>
       <c r="E42" t="n">
-        <v>26391.42</v>
+        <v>26331.07</v>
       </c>
       <c r="F42" t="n">
-        <v>67.54000000000001</v>
+        <v>-60.35</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0023</v>
       </c>
       <c r="H42" t="n">
-        <v>258.97</v>
+        <v>259.92</v>
       </c>
       <c r="I42" t="n">
-        <v>26162.47</v>
+        <v>25986.6</v>
       </c>
       <c r="J42" t="n">
-        <v>26160.08</v>
+        <v>26140.63</v>
       </c>
       <c r="K42" t="n">
-        <v>26254.02</v>
+        <v>26261.94</v>
       </c>
       <c r="L42" t="n">
-        <v>26347.97</v>
+        <v>26383.24</v>
       </c>
       <c r="M42" t="n">
-        <v>26393.74</v>
+        <v>26520.9</v>
       </c>
       <c r="N42" t="n">
-        <v>26439.52</v>
+        <v>26658.57</v>
       </c>
       <c r="O42" t="n">
-        <v>26581.63</v>
+        <v>26763.51</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4022,25 +4031,21 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4059,50 +4064,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>26452</v>
+        <v>26437.35</v>
       </c>
       <c r="C43" t="n">
-        <v>26573.5</v>
+        <v>26489.78</v>
       </c>
       <c r="D43" t="n">
-        <v>26313.58</v>
+        <v>26285.23</v>
       </c>
       <c r="E43" t="n">
-        <v>26331.07</v>
+        <v>26299.74</v>
       </c>
       <c r="F43" t="n">
-        <v>-60.35</v>
+        <v>-31.33</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0012</v>
       </c>
       <c r="H43" t="n">
-        <v>259.92</v>
+        <v>204.55</v>
       </c>
       <c r="I43" t="n">
-        <v>25986.6</v>
+        <v>26053.66</v>
       </c>
       <c r="J43" t="n">
-        <v>26140.63</v>
+        <v>26014.92</v>
       </c>
       <c r="K43" t="n">
-        <v>26261.94</v>
+        <v>26201.11</v>
       </c>
       <c r="L43" t="n">
-        <v>26383.24</v>
+        <v>26387.31</v>
       </c>
       <c r="M43" t="n">
-        <v>26520.9</v>
+        <v>26461.03</v>
       </c>
       <c r="N43" t="n">
-        <v>26658.57</v>
+        <v>26534.76</v>
       </c>
       <c r="O43" t="n">
-        <v>26763.51</v>
+        <v>26833.42</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4136,57 +4141,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26437.35</v>
+        <v>26445.99</v>
       </c>
       <c r="C44" t="n">
-        <v>26489.78</v>
+        <v>26541.34</v>
       </c>
       <c r="D44" t="n">
-        <v>26285.23</v>
+        <v>26404.95</v>
       </c>
       <c r="E44" t="n">
-        <v>26299.74</v>
+        <v>26440.31</v>
       </c>
       <c r="F44" t="n">
-        <v>-31.33</v>
+        <v>140.57</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0053</v>
       </c>
       <c r="H44" t="n">
-        <v>204.55</v>
+        <v>136.39</v>
       </c>
       <c r="I44" t="n">
-        <v>26053.66</v>
+        <v>26080.68</v>
       </c>
       <c r="J44" t="n">
-        <v>26014.92</v>
+        <v>26051.31</v>
       </c>
       <c r="K44" t="n">
-        <v>26201.11</v>
+        <v>26197.47</v>
       </c>
       <c r="L44" t="n">
-        <v>26387.31</v>
+        <v>26343.62</v>
       </c>
       <c r="M44" t="n">
-        <v>26461.03</v>
+        <v>26402.01</v>
       </c>
       <c r="N44" t="n">
-        <v>26534.76</v>
+        <v>26460.41</v>
       </c>
       <c r="O44" t="n">
-        <v>26833.42</v>
+        <v>26694.33</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4197,9 +4202,9 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
@@ -4207,8 +4212,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4218,59 +4225,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>26445.99</v>
+        <v>26490.3</v>
       </c>
       <c r="C45" t="n">
-        <v>26541.34</v>
+        <v>26493.5</v>
       </c>
       <c r="D45" t="n">
-        <v>26404.95</v>
+        <v>26338.61</v>
       </c>
       <c r="E45" t="n">
-        <v>26440.31</v>
+        <v>26338.61</v>
       </c>
       <c r="F45" t="n">
-        <v>140.57</v>
+        <v>-101.7</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0038</v>
       </c>
       <c r="H45" t="n">
-        <v>136.39</v>
+        <v>154.89</v>
       </c>
       <c r="I45" t="n">
-        <v>26080.68</v>
+        <v>26268.56</v>
       </c>
       <c r="J45" t="n">
-        <v>26051.31</v>
+        <v>26287.5</v>
       </c>
       <c r="K45" t="n">
-        <v>26197.47</v>
+        <v>26372.12</v>
       </c>
       <c r="L45" t="n">
-        <v>26343.62</v>
+        <v>26456.73</v>
       </c>
       <c r="M45" t="n">
-        <v>26402.01</v>
+        <v>26508.51</v>
       </c>
       <c r="N45" t="n">
-        <v>26460.41</v>
+        <v>26560.28</v>
       </c>
       <c r="O45" t="n">
-        <v>26694.33</v>
+        <v>26677.73</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4278,24 +4281,22 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
@@ -4304,65 +4305,73 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>26490.3</v>
+        <v>26280.86</v>
       </c>
       <c r="C46" t="n">
-        <v>26493.5</v>
+        <v>26292.95</v>
       </c>
       <c r="D46" t="n">
-        <v>26338.61</v>
+        <v>26119.54</v>
       </c>
       <c r="E46" t="n">
-        <v>26338.61</v>
+        <v>26128.36</v>
       </c>
       <c r="F46" t="n">
-        <v>-101.7</v>
+        <v>-210.25</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.008</v>
       </c>
       <c r="H46" t="n">
-        <v>154.89</v>
+        <v>173.41</v>
       </c>
       <c r="I46" t="n">
-        <v>26268.56</v>
+        <v>26183.72</v>
       </c>
       <c r="J46" t="n">
-        <v>26287.5</v>
+        <v>26145</v>
       </c>
       <c r="K46" t="n">
-        <v>26372.12</v>
+        <v>26261.16</v>
       </c>
       <c r="L46" t="n">
-        <v>26456.73</v>
+        <v>26377.33</v>
       </c>
       <c r="M46" t="n">
-        <v>26508.51</v>
+        <v>26416.05</v>
       </c>
       <c r="N46" t="n">
-        <v>26560.28</v>
+        <v>26454.78</v>
       </c>
       <c r="O46" t="n">
-        <v>26677.73</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
+        <v>26648.39</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
@@ -4379,78 +4388,70 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W46" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>26280.86</v>
+        <v>26146.12</v>
       </c>
       <c r="C47" t="n">
-        <v>26292.95</v>
+        <v>26187.82</v>
       </c>
       <c r="D47" t="n">
-        <v>26119.54</v>
+        <v>26063.37</v>
       </c>
       <c r="E47" t="n">
-        <v>26128.36</v>
+        <v>26091.33</v>
       </c>
       <c r="F47" t="n">
-        <v>-210.25</v>
+        <v>-37.03</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0014</v>
       </c>
       <c r="H47" t="n">
-        <v>173.41</v>
+        <v>124.45</v>
       </c>
       <c r="I47" t="n">
-        <v>26183.72</v>
+        <v>25946.13</v>
       </c>
       <c r="J47" t="n">
-        <v>26145</v>
+        <v>25916.01</v>
       </c>
       <c r="K47" t="n">
-        <v>26261.16</v>
+        <v>26041.65</v>
       </c>
       <c r="L47" t="n">
-        <v>26377.33</v>
+        <v>26167.3</v>
       </c>
       <c r="M47" t="n">
-        <v>26416.05</v>
+        <v>26215.06</v>
       </c>
       <c r="N47" t="n">
-        <v>26454.78</v>
+        <v>26262.83</v>
       </c>
       <c r="O47" t="n">
-        <v>26648.39</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
+        <v>26466.36</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
@@ -4477,60 +4478,64 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>26146.12</v>
+        <v>26050.95</v>
       </c>
       <c r="C48" t="n">
-        <v>26187.82</v>
+        <v>26062.15</v>
       </c>
       <c r="D48" t="n">
-        <v>26063.37</v>
+        <v>25914.11</v>
       </c>
       <c r="E48" t="n">
-        <v>26091.33</v>
+        <v>25983.04</v>
       </c>
       <c r="F48" t="n">
-        <v>-37.03</v>
+        <v>-108.29</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0042</v>
       </c>
       <c r="H48" t="n">
-        <v>124.45</v>
+        <v>148.04</v>
       </c>
       <c r="I48" t="n">
-        <v>25946.13</v>
+        <v>25938.92</v>
       </c>
       <c r="J48" t="n">
-        <v>25916.01</v>
+        <v>25949.75</v>
       </c>
       <c r="K48" t="n">
-        <v>26041.65</v>
+        <v>26029.1</v>
       </c>
       <c r="L48" t="n">
-        <v>26167.3</v>
+        <v>26108.46</v>
       </c>
       <c r="M48" t="n">
-        <v>26215.06</v>
+        <v>26153.56</v>
       </c>
       <c r="N48" t="n">
-        <v>26262.83</v>
+        <v>26198.65</v>
       </c>
       <c r="O48" t="n">
-        <v>26466.36</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+        <v>26312.27</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
@@ -4557,83 +4562,81 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>26050.95</v>
+        <v>25998.95</v>
       </c>
       <c r="C49" t="n">
-        <v>26062.15</v>
+        <v>26166.25</v>
       </c>
       <c r="D49" t="n">
-        <v>25914.11</v>
+        <v>25969.52</v>
       </c>
       <c r="E49" t="n">
-        <v>25983.04</v>
+        <v>26136.56</v>
       </c>
       <c r="F49" t="n">
-        <v>-108.29</v>
+        <v>153.52</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.0059</v>
       </c>
       <c r="H49" t="n">
-        <v>148.04</v>
+        <v>196.73</v>
       </c>
       <c r="I49" t="n">
-        <v>25938.92</v>
+        <v>25766.07</v>
       </c>
       <c r="J49" t="n">
-        <v>25949.75</v>
+        <v>25832.45</v>
       </c>
       <c r="K49" t="n">
-        <v>26029.1</v>
+        <v>25909.02</v>
       </c>
       <c r="L49" t="n">
-        <v>26108.46</v>
+        <v>25985.58</v>
       </c>
       <c r="M49" t="n">
-        <v>26153.56</v>
+        <v>26057.06</v>
       </c>
       <c r="N49" t="n">
-        <v>26198.65</v>
+        <v>26128.53</v>
       </c>
       <c r="O49" t="n">
-        <v>26312.27</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="inlineStr">
+        <v>26210.19</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W49" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X49" t="inlineStr"/>
@@ -4641,50 +4644,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25998.95</v>
+        <v>26091.29</v>
       </c>
       <c r="C50" t="n">
-        <v>26166.25</v>
+        <v>26171.7</v>
       </c>
       <c r="D50" t="n">
-        <v>25969.52</v>
+        <v>26038.07</v>
       </c>
       <c r="E50" t="n">
-        <v>26136.56</v>
+        <v>26106.6</v>
       </c>
       <c r="F50" t="n">
-        <v>153.52</v>
+        <v>-29.96</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0011</v>
       </c>
       <c r="H50" t="n">
-        <v>196.73</v>
+        <v>133.63</v>
       </c>
       <c r="I50" t="n">
-        <v>25766.07</v>
+        <v>25772.79</v>
       </c>
       <c r="J50" t="n">
-        <v>25832.45</v>
+        <v>25974.17</v>
       </c>
       <c r="K50" t="n">
-        <v>25909.02</v>
+        <v>26038.2</v>
       </c>
       <c r="L50" t="n">
-        <v>25985.58</v>
+        <v>26102.22</v>
       </c>
       <c r="M50" t="n">
-        <v>26057.06</v>
+        <v>26234.93</v>
       </c>
       <c r="N50" t="n">
-        <v>26128.53</v>
+        <v>26367.63</v>
       </c>
       <c r="O50" t="n">
-        <v>26210.19</v>
+        <v>26362.98</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4692,23 +4695,21 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4718,55 +4719,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>26091.29</v>
+        <v>26206.01</v>
       </c>
       <c r="C51" t="n">
-        <v>26171.7</v>
+        <v>26341.52</v>
       </c>
       <c r="D51" t="n">
-        <v>26038.07</v>
+        <v>26164.11</v>
       </c>
       <c r="E51" t="n">
-        <v>26106.6</v>
+        <v>26266.14</v>
       </c>
       <c r="F51" t="n">
-        <v>-29.96</v>
+        <v>159.54</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0061</v>
       </c>
       <c r="H51" t="n">
-        <v>133.63</v>
+        <v>177.41</v>
       </c>
       <c r="I51" t="n">
-        <v>25772.79</v>
+        <v>25904.44</v>
       </c>
       <c r="J51" t="n">
-        <v>25974.17</v>
+        <v>25973.83</v>
       </c>
       <c r="K51" t="n">
-        <v>26038.2</v>
+        <v>26039.79</v>
       </c>
       <c r="L51" t="n">
-        <v>26102.22</v>
+        <v>26105.74</v>
       </c>
       <c r="M51" t="n">
-        <v>26234.93</v>
+        <v>26173.41</v>
       </c>
       <c r="N51" t="n">
-        <v>26367.63</v>
+        <v>26241.09</v>
       </c>
       <c r="O51" t="n">
-        <v>26362.98</v>
+        <v>26305.33</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4774,83 +4779,83 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R51" s="6" t="n">
+        <v/>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>26206.01</v>
+        <v>26255.41</v>
       </c>
       <c r="C52" t="n">
-        <v>26341.52</v>
+        <v>26466.76</v>
       </c>
       <c r="D52" t="n">
-        <v>26164.11</v>
+        <v>26196.92</v>
       </c>
       <c r="E52" t="n">
-        <v>26266.14</v>
+        <v>26285.96</v>
       </c>
       <c r="F52" t="n">
-        <v>159.54</v>
+        <v>19.82</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0061</v>
+        <v>0.0008</v>
       </c>
       <c r="H52" t="n">
-        <v>177.41</v>
+        <v>269.84</v>
       </c>
       <c r="I52" t="n">
-        <v>25904.44</v>
+        <v>25986.7</v>
       </c>
       <c r="J52" t="n">
-        <v>25973.83</v>
+        <v>26095.39</v>
       </c>
       <c r="K52" t="n">
-        <v>26039.79</v>
+        <v>26177.44</v>
       </c>
       <c r="L52" t="n">
-        <v>26105.74</v>
+        <v>26259.48</v>
       </c>
       <c r="M52" t="n">
-        <v>26173.41</v>
+        <v>26354.85</v>
       </c>
       <c r="N52" t="n">
-        <v>26241.09</v>
+        <v>26450.21</v>
       </c>
       <c r="O52" t="n">
-        <v>26305.33</v>
+        <v>26518.93</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4863,7 +4868,7 @@
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
@@ -4873,13 +4878,11 @@
       </c>
       <c r="U52" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
       </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
@@ -4891,50 +4894,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>26255.41</v>
+        <v>26354.37</v>
       </c>
       <c r="C53" t="n">
-        <v>26466.76</v>
+        <v>26402.81</v>
       </c>
       <c r="D53" t="n">
-        <v>26196.92</v>
+        <v>26241.77</v>
       </c>
       <c r="E53" t="n">
-        <v>26285.96</v>
+        <v>26367.24</v>
       </c>
       <c r="F53" t="n">
-        <v>19.82</v>
+        <v>81.28</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0031</v>
       </c>
       <c r="H53" t="n">
-        <v>269.84</v>
+        <v>161.04</v>
       </c>
       <c r="I53" t="n">
-        <v>25986.7</v>
+        <v>25927.08</v>
       </c>
       <c r="J53" t="n">
-        <v>26095.39</v>
+        <v>25993.18</v>
       </c>
       <c r="K53" t="n">
-        <v>26177.44</v>
+        <v>26151.04</v>
       </c>
       <c r="L53" t="n">
-        <v>26259.48</v>
+        <v>26308.9</v>
       </c>
       <c r="M53" t="n">
-        <v>26354.85</v>
+        <v>26420.88</v>
       </c>
       <c r="N53" t="n">
-        <v>26450.21</v>
+        <v>26532.86</v>
       </c>
       <c r="O53" t="n">
-        <v>26518.93</v>
+        <v>26736.6</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4947,18 +4950,16 @@
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4968,55 +4969,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>26354.37</v>
+        <v>26494.61</v>
       </c>
       <c r="C54" t="n">
-        <v>26402.81</v>
+        <v>26618.74</v>
       </c>
       <c r="D54" t="n">
-        <v>26241.77</v>
+        <v>26467.36</v>
       </c>
       <c r="E54" t="n">
-        <v>26367.24</v>
+        <v>26569.99</v>
       </c>
       <c r="F54" t="n">
-        <v>81.28</v>
+        <v>202.75</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0077</v>
       </c>
       <c r="H54" t="n">
-        <v>161.04</v>
+        <v>151.38</v>
       </c>
       <c r="I54" t="n">
-        <v>25927.08</v>
+        <v>26080.73</v>
       </c>
       <c r="J54" t="n">
-        <v>25993.18</v>
+        <v>26228.67</v>
       </c>
       <c r="K54" t="n">
-        <v>26151.04</v>
+        <v>26286.72</v>
       </c>
       <c r="L54" t="n">
-        <v>26308.9</v>
+        <v>26344.77</v>
       </c>
       <c r="M54" t="n">
-        <v>26420.88</v>
+        <v>26447.76</v>
       </c>
       <c r="N54" t="n">
-        <v>26532.86</v>
+        <v>26550.76</v>
       </c>
       <c r="O54" t="n">
-        <v>26736.6</v>
+        <v>26563.85</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5034,106 +5039,106 @@
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V54" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="8" t="n">
-        <v/>
-      </c>
       <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>26494.61</v>
+        <v>26464.14</v>
       </c>
       <c r="C55" t="n">
-        <v>26618.74</v>
+        <v>26471.79</v>
       </c>
       <c r="D55" t="n">
-        <v>26467.36</v>
+        <v>26249.59</v>
       </c>
       <c r="E55" t="n">
-        <v>26569.99</v>
+        <v>26258.11</v>
       </c>
       <c r="F55" t="n">
-        <v>202.75</v>
+        <v>-311.88</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0117</v>
       </c>
       <c r="H55" t="n">
-        <v>151.38</v>
+        <v>222.2</v>
       </c>
       <c r="I55" t="n">
-        <v>26080.73</v>
+        <v>26315.98</v>
       </c>
       <c r="J55" t="n">
-        <v>26228.67</v>
+        <v>26432.08</v>
       </c>
       <c r="K55" t="n">
-        <v>26286.72</v>
+        <v>26494.3</v>
       </c>
       <c r="L55" t="n">
-        <v>26344.77</v>
+        <v>26556.52</v>
       </c>
       <c r="M55" t="n">
-        <v>26447.76</v>
+        <v>26645.68</v>
       </c>
       <c r="N55" t="n">
-        <v>26550.76</v>
+        <v>26734.84</v>
       </c>
       <c r="O55" t="n">
-        <v>26563.85</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
+        <v>26770.12</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W55" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W55" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X55" t="inlineStr"/>
@@ -5141,59 +5146,59 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>26464.14</v>
+        <v>26150.75</v>
       </c>
       <c r="C56" t="n">
-        <v>26471.79</v>
+        <v>26206.13</v>
       </c>
       <c r="D56" t="n">
-        <v>26249.59</v>
+        <v>25916.76</v>
       </c>
       <c r="E56" t="n">
-        <v>26258.11</v>
+        <v>25970.11</v>
       </c>
       <c r="F56" t="n">
-        <v>-311.88</v>
+        <v>-288</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.011</v>
       </c>
       <c r="H56" t="n">
-        <v>222.2</v>
+        <v>289.37</v>
       </c>
       <c r="I56" t="n">
-        <v>26315.98</v>
+        <v>26027.39</v>
       </c>
       <c r="J56" t="n">
-        <v>26432.08</v>
+        <v>25984.62</v>
       </c>
       <c r="K56" t="n">
-        <v>26494.3</v>
+        <v>26147.01</v>
       </c>
       <c r="L56" t="n">
-        <v>26556.52</v>
+        <v>26309.4</v>
       </c>
       <c r="M56" t="n">
-        <v>26645.68</v>
+        <v>26369.21</v>
       </c>
       <c r="N56" t="n">
-        <v>26734.84</v>
+        <v>26429.02</v>
       </c>
       <c r="O56" t="n">
-        <v>26770.12</v>
+        <v>26693.99</v>
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
@@ -5225,64 +5230,60 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>26150.75</v>
+        <v>25886.67</v>
       </c>
       <c r="C57" t="n">
-        <v>26206.13</v>
+        <v>25924.21</v>
       </c>
       <c r="D57" t="n">
-        <v>25916.76</v>
+        <v>25727.93</v>
       </c>
       <c r="E57" t="n">
-        <v>25970.11</v>
+        <v>25839.33</v>
       </c>
       <c r="F57" t="n">
-        <v>-288</v>
+        <v>-130.78</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.005</v>
       </c>
       <c r="H57" t="n">
-        <v>289.37</v>
+        <v>196.28</v>
       </c>
       <c r="I57" t="n">
-        <v>26027.39</v>
+        <v>25627.39</v>
       </c>
       <c r="J57" t="n">
-        <v>25984.62</v>
+        <v>25635.07</v>
       </c>
       <c r="K57" t="n">
-        <v>26147.01</v>
+        <v>25825.42</v>
       </c>
       <c r="L57" t="n">
-        <v>26309.4</v>
+        <v>26015.78</v>
       </c>
       <c r="M57" t="n">
-        <v>26369.21</v>
+        <v>26114.79</v>
       </c>
       <c r="N57" t="n">
-        <v>26429.02</v>
+        <v>26213.81</v>
       </c>
       <c r="O57" t="n">
-        <v>26693.99</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="inlineStr">
+        <v>26495.5</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S57" s="7" t="inlineStr">
@@ -5309,50 +5310,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>25886.67</v>
+        <v>25840.92</v>
       </c>
       <c r="C58" t="n">
-        <v>25924.21</v>
+        <v>26007.79</v>
       </c>
       <c r="D58" t="n">
-        <v>25727.93</v>
+        <v>25784.84</v>
       </c>
       <c r="E58" t="n">
-        <v>25839.33</v>
+        <v>26003.32</v>
       </c>
       <c r="F58" t="n">
-        <v>-130.78</v>
+        <v>163.99</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0063</v>
       </c>
       <c r="H58" t="n">
-        <v>196.28</v>
+        <v>222.95</v>
       </c>
       <c r="I58" t="n">
-        <v>25627.39</v>
+        <v>25531.65</v>
       </c>
       <c r="J58" t="n">
-        <v>25635.07</v>
+        <v>25649.68</v>
       </c>
       <c r="K58" t="n">
-        <v>25825.42</v>
+        <v>25741.19</v>
       </c>
       <c r="L58" t="n">
-        <v>26015.78</v>
+        <v>25832.7</v>
       </c>
       <c r="M58" t="n">
-        <v>26114.79</v>
+        <v>25937.47</v>
       </c>
       <c r="N58" t="n">
-        <v>26213.81</v>
+        <v>26042.24</v>
       </c>
       <c r="O58" t="n">
-        <v>26495.5</v>
+        <v>26120.49</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5360,22 +5361,24 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
@@ -5384,55 +5387,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25840.92</v>
+        <v>25985.86</v>
       </c>
       <c r="C59" t="n">
-        <v>26007.79</v>
+        <v>26167.93</v>
       </c>
       <c r="D59" t="n">
-        <v>25784.84</v>
+        <v>25958.7</v>
       </c>
       <c r="E59" t="n">
-        <v>26003.32</v>
+        <v>26046.4</v>
       </c>
       <c r="F59" t="n">
-        <v>163.99</v>
+        <v>43.08</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0017</v>
       </c>
       <c r="H59" t="n">
-        <v>222.95</v>
+        <v>209.23</v>
       </c>
       <c r="I59" t="n">
-        <v>25531.65</v>
+        <v>25561.89</v>
       </c>
       <c r="J59" t="n">
-        <v>25649.68</v>
+        <v>25833.87</v>
       </c>
       <c r="K59" t="n">
-        <v>25741.19</v>
+        <v>25891.85</v>
       </c>
       <c r="L59" t="n">
-        <v>25832.7</v>
+        <v>25949.82</v>
       </c>
       <c r="M59" t="n">
-        <v>25937.47</v>
+        <v>26114.79</v>
       </c>
       <c r="N59" t="n">
-        <v>26042.24</v>
+        <v>26279.77</v>
       </c>
       <c r="O59" t="n">
-        <v>26120.49</v>
+        <v>26230.74</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5450,13 +5457,11 @@
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
@@ -5475,50 +5480,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25985.86</v>
+        <v>26039.54</v>
       </c>
       <c r="C60" t="n">
-        <v>26167.93</v>
+        <v>26069.99</v>
       </c>
       <c r="D60" t="n">
-        <v>25958.7</v>
+        <v>25919.61</v>
       </c>
       <c r="E60" t="n">
-        <v>26046.4</v>
+        <v>26006.53</v>
       </c>
       <c r="F60" t="n">
-        <v>43.08</v>
+        <v>-39.87</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0015</v>
       </c>
       <c r="H60" t="n">
-        <v>209.23</v>
+        <v>150.38</v>
       </c>
       <c r="I60" t="n">
-        <v>25561.89</v>
+        <v>25749.47</v>
       </c>
       <c r="J60" t="n">
-        <v>25833.87</v>
+        <v>25828.71</v>
       </c>
       <c r="K60" t="n">
-        <v>25891.85</v>
+        <v>25941.79</v>
       </c>
       <c r="L60" t="n">
-        <v>25949.82</v>
+        <v>26054.86</v>
       </c>
       <c r="M60" t="n">
-        <v>26114.79</v>
+        <v>26151.02</v>
       </c>
       <c r="N60" t="n">
-        <v>26279.77</v>
+        <v>26247.17</v>
       </c>
       <c r="O60" t="n">
-        <v>26230.74</v>
+        <v>26377.16</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5526,18 +5531,18 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5550,74 +5555,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>26039.54</v>
+        <v>25897.22</v>
       </c>
       <c r="C61" t="n">
-        <v>26069.99</v>
+        <v>26026.78</v>
       </c>
       <c r="D61" t="n">
-        <v>25919.61</v>
+        <v>25799.66</v>
       </c>
       <c r="E61" t="n">
-        <v>26006.53</v>
+        <v>26007.63</v>
       </c>
       <c r="F61" t="n">
-        <v>-39.87</v>
+        <v>1.1</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>150.38</v>
+        <v>227.12</v>
       </c>
       <c r="I61" t="n">
-        <v>25749.47</v>
+        <v>25769.23</v>
       </c>
       <c r="J61" t="n">
-        <v>25828.71</v>
+        <v>25862.01</v>
       </c>
       <c r="K61" t="n">
-        <v>25941.79</v>
+        <v>25931.34</v>
       </c>
       <c r="L61" t="n">
-        <v>26054.86</v>
+        <v>26000.66</v>
       </c>
       <c r="M61" t="n">
-        <v>26151.02</v>
+        <v>26081.72</v>
       </c>
       <c r="N61" t="n">
-        <v>26247.17</v>
+        <v>26162.77</v>
       </c>
       <c r="O61" t="n">
-        <v>26377.16</v>
+        <v>26220.37</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5634,58 +5637,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>25897.22</v>
+        <v>25870.98</v>
       </c>
       <c r="C62" t="n">
-        <v>26026.78</v>
+        <v>25909.66</v>
       </c>
       <c r="D62" t="n">
-        <v>25799.66</v>
+        <v>25512.39</v>
       </c>
       <c r="E62" t="n">
-        <v>26007.63</v>
+        <v>25576.45</v>
       </c>
       <c r="F62" t="n">
-        <v>1.1</v>
+        <v>-431.18</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0</v>
+        <v>-0.0166</v>
       </c>
       <c r="H62" t="n">
-        <v>227.12</v>
+        <v>397.27</v>
       </c>
       <c r="I62" t="n">
-        <v>25769.23</v>
+        <v>25572.54</v>
       </c>
       <c r="J62" t="n">
-        <v>25862.01</v>
+        <v>25827.72</v>
       </c>
       <c r="K62" t="n">
-        <v>25931.34</v>
+        <v>25894.07</v>
       </c>
       <c r="L62" t="n">
-        <v>26000.66</v>
+        <v>25960.43</v>
       </c>
       <c r="M62" t="n">
-        <v>26081.72</v>
+        <v>26121.19</v>
       </c>
       <c r="N62" t="n">
-        <v>26162.77</v>
+        <v>26281.96</v>
       </c>
       <c r="O62" t="n">
-        <v>26220.37</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
+        <v>26253.9</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q62" s="6" t="inlineStr">
         <is>
@@ -5697,9 +5706,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5716,73 +5725,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>25870.98</v>
+        <v>25555.66</v>
       </c>
       <c r="C63" t="n">
-        <v>25909.66</v>
+        <v>25612.09</v>
       </c>
       <c r="D63" t="n">
-        <v>25512.39</v>
+        <v>25361.15</v>
       </c>
       <c r="E63" t="n">
-        <v>25576.45</v>
+        <v>25361.15</v>
       </c>
       <c r="F63" t="n">
-        <v>-431.18</v>
+        <v>-215.3</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>397.27</v>
+        <v>250.94</v>
       </c>
       <c r="I63" t="n">
-        <v>25572.54</v>
+        <v>25115.12</v>
       </c>
       <c r="J63" t="n">
-        <v>25827.72</v>
+        <v>25111.89</v>
       </c>
       <c r="K63" t="n">
-        <v>25894.07</v>
+        <v>25377.81</v>
       </c>
       <c r="L63" t="n">
-        <v>25960.43</v>
+        <v>25643.74</v>
       </c>
       <c r="M63" t="n">
-        <v>26121.19</v>
+        <v>25775.08</v>
       </c>
       <c r="N63" t="n">
-        <v>26281.96</v>
+        <v>25906.43</v>
       </c>
       <c r="O63" t="n">
-        <v>26253.9</v>
-      </c>
-      <c r="P63" s="6" t="inlineStr">
+        <v>26306.93</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S63" s="7" t="inlineStr">
@@ -5809,50 +5810,50 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>25555.66</v>
+        <v>25478.84</v>
       </c>
       <c r="C64" t="n">
-        <v>25612.09</v>
+        <v>25581.22</v>
       </c>
       <c r="D64" t="n">
-        <v>25361.15</v>
+        <v>25396.38</v>
       </c>
       <c r="E64" t="n">
-        <v>25361.15</v>
+        <v>25568.56</v>
       </c>
       <c r="F64" t="n">
-        <v>-215.3</v>
+        <v>207.41</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H64" t="n">
-        <v>250.94</v>
+        <v>184.84</v>
       </c>
       <c r="I64" t="n">
-        <v>25115.12</v>
+        <v>25110.21</v>
       </c>
       <c r="J64" t="n">
-        <v>25111.89</v>
+        <v>25047.48</v>
       </c>
       <c r="K64" t="n">
-        <v>25377.81</v>
+        <v>25235.68</v>
       </c>
       <c r="L64" t="n">
-        <v>25643.74</v>
+        <v>25423.89</v>
       </c>
       <c r="M64" t="n">
-        <v>25775.08</v>
+        <v>25486.62</v>
       </c>
       <c r="N64" t="n">
-        <v>25906.43</v>
+        <v>25549.35</v>
       </c>
       <c r="O64" t="n">
-        <v>26306.93</v>
+        <v>25863.03</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5860,104 +5861,112 @@
       <c r="Q64" s="6" t="n">
         <v/>
       </c>
-      <c r="R64" s="6" t="inlineStr">
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U64" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
-      </c>
       <c r="V64" s="8" t="n">
         <v/>
       </c>
-      <c r="W64" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr"/>
+      <c r="W64" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>25478.84</v>
+        <v>25498.74</v>
       </c>
       <c r="C65" t="n">
-        <v>25581.22</v>
+        <v>25548.78</v>
       </c>
       <c r="D65" t="n">
-        <v>25396.38</v>
+        <v>25325.52</v>
       </c>
       <c r="E65" t="n">
-        <v>25568.56</v>
+        <v/>
       </c>
       <c r="F65" t="n">
-        <v>207.41</v>
+        <v/>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v/>
       </c>
       <c r="H65" t="n">
-        <v>184.84</v>
+        <v>223.26</v>
       </c>
       <c r="I65" t="n">
-        <v>25110.21</v>
+        <v>25211.54</v>
       </c>
       <c r="J65" t="n">
-        <v>25047.48</v>
+        <v>25423.6</v>
       </c>
       <c r="K65" t="n">
-        <v>25235.68</v>
+        <v>25476.14</v>
       </c>
       <c r="L65" t="n">
-        <v>25423.89</v>
+        <v>25528.68</v>
       </c>
       <c r="M65" t="n">
-        <v>25486.62</v>
+        <v>25660.98</v>
       </c>
       <c r="N65" t="n">
-        <v>25549.35</v>
+        <v>25793.28</v>
       </c>
       <c r="O65" t="n">
-        <v>25863.03</v>
-      </c>
-      <c r="P65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S65" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U65" s="8" t="inlineStr">
+        <v>25766.06</v>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q65" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S65" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U65" s="8" t="n">
+        <v/>
+      </c>
       <c r="V65" s="8" t="n">
         <v/>
       </c>
@@ -5968,36 +5977,36 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="12" t="inlineStr">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I66" s="13" t="n">
-        <v>25211.54</v>
-      </c>
-      <c r="J66" s="13" t="n">
-        <v>25423.6</v>
-      </c>
-      <c r="K66" s="13" t="n">
-        <v>25476.14</v>
-      </c>
-      <c r="L66" s="13" t="n">
-        <v>25528.68</v>
-      </c>
-      <c r="M66" s="13" t="n">
-        <v>25660.98</v>
-      </c>
-      <c r="N66" s="13" t="n">
-        <v>25793.28</v>
-      </c>
-      <c r="O66" s="13" t="n">
-        <v>25766.06</v>
+      <c r="I66" s="14" t="n">
+        <v>25102.26</v>
+      </c>
+      <c r="J66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O66" s="14" t="n">
+        <v>25772.04</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -109,20 +109,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -490,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X66"/>
+  <dimension ref="A1:X65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -644,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24816.96</v>
+        <v>24996.54</v>
       </c>
       <c r="C2" t="n">
-        <v>24956.48</v>
+        <v>25059.37</v>
       </c>
       <c r="D2" t="n">
-        <v>24763.53</v>
+        <v>24840.27</v>
       </c>
       <c r="E2" t="n">
-        <v>24934.67</v>
+        <v>25026.8</v>
       </c>
       <c r="F2" t="n">
-        <v>24.26</v>
+        <v>92.13</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0037</v>
       </c>
       <c r="H2" t="n">
-        <v>192.95</v>
+        <v>219.1</v>
       </c>
       <c r="I2" t="n">
-        <v>24691.18</v>
+        <v>24570.58</v>
       </c>
       <c r="J2" t="n">
-        <v>24653.31</v>
+        <v>24779.05</v>
       </c>
       <c r="K2" t="n">
-        <v>24805.64</v>
+        <v>24838.19</v>
       </c>
       <c r="L2" t="n">
-        <v>24957.96</v>
+        <v>24897.34</v>
       </c>
       <c r="M2" t="n">
-        <v>25015.18</v>
+        <v>25031.15</v>
       </c>
       <c r="N2" t="n">
-        <v>25072.41</v>
+        <v>25164.95</v>
       </c>
       <c r="O2" t="n">
-        <v>25319.83</v>
+        <v>25149.43</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,18 +692,18 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -719,59 +716,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24996.54</v>
+        <v>25075.33</v>
       </c>
       <c r="C3" t="n">
-        <v>25059.37</v>
+        <v>25173.02</v>
       </c>
       <c r="D3" t="n">
-        <v>24840.27</v>
+        <v>24951.54</v>
       </c>
       <c r="E3" t="n">
-        <v>25026.8</v>
+        <v>24985.82</v>
       </c>
       <c r="F3" t="n">
-        <v>92.13</v>
+        <v>-40.98</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0016</v>
       </c>
       <c r="H3" t="n">
-        <v>219.1</v>
+        <v>221.48</v>
       </c>
       <c r="I3" t="n">
-        <v>24570.58</v>
+        <v>24621.17</v>
       </c>
       <c r="J3" t="n">
-        <v>24779.05</v>
+        <v>24846.19</v>
       </c>
       <c r="K3" t="n">
-        <v>24838.19</v>
+        <v>24917.25</v>
       </c>
       <c r="L3" t="n">
-        <v>24897.34</v>
+        <v>24988.31</v>
       </c>
       <c r="M3" t="n">
-        <v>25031.15</v>
+        <v>25136.35</v>
       </c>
       <c r="N3" t="n">
-        <v>25164.95</v>
+        <v>25284.39</v>
       </c>
       <c r="O3" t="n">
-        <v>25149.43</v>
+        <v>25278.47</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -784,12 +777,12 @@
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U3" s="8" t="n">
@@ -803,55 +796,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25075.33</v>
+        <v>25035.93</v>
       </c>
       <c r="C4" t="n">
-        <v>25173.02</v>
+        <v>25176.21</v>
       </c>
       <c r="D4" t="n">
-        <v>24951.54</v>
+        <v>24896.19</v>
       </c>
       <c r="E4" t="n">
-        <v>24985.82</v>
+        <v>25139.69</v>
       </c>
       <c r="F4" t="n">
-        <v>-40.98</v>
+        <v>153.87</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0062</v>
       </c>
       <c r="H4" t="n">
-        <v>221.48</v>
+        <v>280.02</v>
       </c>
       <c r="I4" t="n">
-        <v>24621.17</v>
+        <v>24730.06</v>
       </c>
       <c r="J4" t="n">
-        <v>24846.19</v>
+        <v>24726.11</v>
       </c>
       <c r="K4" t="n">
-        <v>24917.25</v>
+        <v>24875.08</v>
       </c>
       <c r="L4" t="n">
-        <v>24988.31</v>
+        <v>25024.05</v>
       </c>
       <c r="M4" t="n">
-        <v>25136.35</v>
+        <v>25096.56</v>
       </c>
       <c r="N4" t="n">
-        <v>25284.39</v>
+        <v>25169.07</v>
       </c>
       <c r="O4" t="n">
-        <v>25278.47</v>
+        <v>25394.5</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -864,7 +861,7 @@
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
@@ -872,8 +869,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="8" t="n">
-        <v/>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -892,151 +891,147 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25035.93</v>
+        <v>24835.56</v>
       </c>
       <c r="C5" t="n">
-        <v>25176.21</v>
+        <v>24988.71</v>
       </c>
       <c r="D5" t="n">
-        <v>24896.19</v>
+        <v>24728.57</v>
       </c>
       <c r="E5" t="n">
-        <v>25139.69</v>
+        <v>24893.58</v>
       </c>
       <c r="F5" t="n">
-        <v>153.87</v>
+        <v>-246.11</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0098</v>
       </c>
       <c r="H5" t="n">
-        <v>280.02</v>
+        <v>260.14</v>
       </c>
       <c r="I5" t="n">
-        <v>24730.06</v>
+        <v>24616.17</v>
       </c>
       <c r="J5" t="n">
-        <v>24726.11</v>
+        <v>24911.41</v>
       </c>
       <c r="K5" t="n">
-        <v>24875.08</v>
+        <v>24999.68</v>
       </c>
       <c r="L5" t="n">
-        <v>25024.05</v>
+        <v>25087.94</v>
       </c>
       <c r="M5" t="n">
-        <v>25096.56</v>
+        <v>25279.7</v>
       </c>
       <c r="N5" t="n">
-        <v>25169.07</v>
+        <v>25471.46</v>
       </c>
       <c r="O5" t="n">
-        <v>25394.5</v>
+        <v>25456.23</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W5" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24835.56</v>
+        <v>24790.7</v>
       </c>
       <c r="C6" t="n">
-        <v>24988.71</v>
+        <v>24800.66</v>
       </c>
       <c r="D6" t="n">
-        <v>24728.57</v>
+        <v>24593.48</v>
       </c>
       <c r="E6" t="n">
-        <v>24893.58</v>
+        <v>24740.36</v>
       </c>
       <c r="F6" t="n">
-        <v>-246.11</v>
+        <v>-153.22</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0062</v>
       </c>
       <c r="H6" t="n">
-        <v>260.14</v>
+        <v>207.18</v>
       </c>
       <c r="I6" t="n">
-        <v>24616.17</v>
+        <v>24468.43</v>
       </c>
       <c r="J6" t="n">
-        <v>24911.41</v>
+        <v>24650.91</v>
       </c>
       <c r="K6" t="n">
-        <v>24999.68</v>
+        <v>24763.51</v>
       </c>
       <c r="L6" t="n">
-        <v>25087.94</v>
+        <v>24876.11</v>
       </c>
       <c r="M6" t="n">
-        <v>25279.7</v>
+        <v>25023.65</v>
       </c>
       <c r="N6" t="n">
-        <v>25471.46</v>
+        <v>25171.19</v>
       </c>
       <c r="O6" t="n">
-        <v>25456.23</v>
+        <v>25248.85</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1060,81 +1055,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24790.7</v>
+        <v>24810</v>
       </c>
       <c r="C7" t="n">
-        <v>24800.66</v>
+        <v>25088.28</v>
       </c>
       <c r="D7" t="n">
-        <v>24593.48</v>
+        <v>24761.72</v>
       </c>
       <c r="E7" t="n">
-        <v>24740.36</v>
+        <v>24994.83</v>
       </c>
       <c r="F7" t="n">
-        <v>-153.22</v>
+        <v>254.47</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0103</v>
       </c>
       <c r="H7" t="n">
-        <v>207.18</v>
+        <v>326.56</v>
       </c>
       <c r="I7" t="n">
-        <v>24468.43</v>
+        <v>24386.3</v>
       </c>
       <c r="J7" t="n">
-        <v>24650.91</v>
+        <v>24554.82</v>
       </c>
       <c r="K7" t="n">
-        <v>24763.51</v>
+        <v>24636.77</v>
       </c>
       <c r="L7" t="n">
-        <v>24876.11</v>
+        <v>24718.71</v>
       </c>
       <c r="M7" t="n">
-        <v>25023.65</v>
+        <v>24843.95</v>
       </c>
       <c r="N7" t="n">
-        <v>25171.19</v>
+        <v>24969.18</v>
       </c>
       <c r="O7" t="n">
-        <v>25248.85</v>
+        <v>25007.84</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W7" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W7" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
@@ -1142,83 +1139,81 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24810</v>
+        <v>24848.51</v>
       </c>
       <c r="C8" t="n">
-        <v>25088.28</v>
+        <v>24869.63</v>
       </c>
       <c r="D8" t="n">
-        <v>24761.72</v>
+        <v>24547.7</v>
       </c>
       <c r="E8" t="n">
-        <v>24994.83</v>
+        <v>24671.22</v>
       </c>
       <c r="F8" t="n">
-        <v>254.47</v>
+        <v>-323.61</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.0129</v>
       </c>
       <c r="H8" t="n">
-        <v>326.56</v>
+        <v>321.93</v>
       </c>
       <c r="I8" t="n">
-        <v>24386.3</v>
+        <v>24435.16</v>
       </c>
       <c r="J8" t="n">
-        <v>24554.82</v>
+        <v>24703.19</v>
       </c>
       <c r="K8" t="n">
-        <v>24636.77</v>
+        <v>24831.55</v>
       </c>
       <c r="L8" t="n">
-        <v>24718.71</v>
+        <v>24959.92</v>
       </c>
       <c r="M8" t="n">
-        <v>24843.95</v>
+        <v>25158.11</v>
       </c>
       <c r="N8" t="n">
-        <v>24969.18</v>
+        <v>25356.3</v>
       </c>
       <c r="O8" t="n">
-        <v>25007.84</v>
+        <v>25414.84</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W8" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W8" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
@@ -1226,67 +1221,63 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24848.51</v>
+        <v>24724.34</v>
       </c>
       <c r="C9" t="n">
-        <v>24869.63</v>
+        <v>24762.24</v>
       </c>
       <c r="D9" t="n">
-        <v>24547.7</v>
+        <v>24556.78</v>
       </c>
       <c r="E9" t="n">
-        <v>24671.22</v>
+        <v>24626.89</v>
       </c>
       <c r="F9" t="n">
-        <v>-323.61</v>
+        <v>-44.33</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0018</v>
       </c>
       <c r="H9" t="n">
-        <v>321.93</v>
+        <v>205.46</v>
       </c>
       <c r="I9" t="n">
-        <v>24435.16</v>
+        <v>24225.77</v>
       </c>
       <c r="J9" t="n">
-        <v>24703.19</v>
+        <v>24330.57</v>
       </c>
       <c r="K9" t="n">
-        <v>24831.55</v>
+        <v>24510.25</v>
       </c>
       <c r="L9" t="n">
-        <v>24959.92</v>
+        <v>24689.94</v>
       </c>
       <c r="M9" t="n">
-        <v>25158.11</v>
+        <v>24832.19</v>
       </c>
       <c r="N9" t="n">
-        <v>25356.3</v>
+        <v>24974.43</v>
       </c>
       <c r="O9" t="n">
-        <v>25414.84</v>
+        <v>25191.56</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1303,55 +1294,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24724.34</v>
+        <v>24815.22</v>
       </c>
       <c r="C10" t="n">
-        <v>24762.24</v>
+        <v>25024.27</v>
       </c>
       <c r="D10" t="n">
-        <v>24556.78</v>
+        <v>24794.84</v>
       </c>
       <c r="E10" t="n">
-        <v>24626.89</v>
+        <v>24995.81</v>
       </c>
       <c r="F10" t="n">
-        <v>-44.33</v>
+        <v>368.92</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.015</v>
       </c>
       <c r="H10" t="n">
-        <v>205.46</v>
+        <v>229.43</v>
       </c>
       <c r="I10" t="n">
-        <v>24225.77</v>
+        <v>24351.32</v>
       </c>
       <c r="J10" t="n">
-        <v>24330.57</v>
+        <v>24405.12</v>
       </c>
       <c r="K10" t="n">
-        <v>24510.25</v>
+        <v>24524.16</v>
       </c>
       <c r="L10" t="n">
-        <v>24689.94</v>
+        <v>24643.2</v>
       </c>
       <c r="M10" t="n">
-        <v>24832.19</v>
+        <v>24729.62</v>
       </c>
       <c r="N10" t="n">
-        <v>24974.43</v>
+        <v>24816.04</v>
       </c>
       <c r="O10" t="n">
-        <v>25191.56</v>
+        <v>24967.7</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1364,76 +1359,78 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W10" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W10" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24815.22</v>
+        <v>25028.93</v>
       </c>
       <c r="C11" t="n">
-        <v>25024.27</v>
+        <v>25095.66</v>
       </c>
       <c r="D11" t="n">
-        <v>24794.84</v>
+        <v>24887</v>
       </c>
       <c r="E11" t="n">
-        <v>24995.81</v>
+        <v>25040.28</v>
       </c>
       <c r="F11" t="n">
-        <v>368.92</v>
+        <v>44.47</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.015</v>
+        <v>0.0018</v>
       </c>
       <c r="H11" t="n">
-        <v>229.43</v>
+        <v>208.66</v>
       </c>
       <c r="I11" t="n">
-        <v>24351.32</v>
+        <v>24565.41</v>
       </c>
       <c r="J11" t="n">
-        <v>24405.12</v>
+        <v>24809.51</v>
       </c>
       <c r="K11" t="n">
-        <v>24524.16</v>
+        <v>24881.1</v>
       </c>
       <c r="L11" t="n">
-        <v>24643.2</v>
+        <v>24952.68</v>
       </c>
       <c r="M11" t="n">
-        <v>24729.62</v>
+        <v>25110.53</v>
       </c>
       <c r="N11" t="n">
-        <v>24816.04</v>
+        <v>25268.37</v>
       </c>
       <c r="O11" t="n">
-        <v>24967.7</v>
+        <v>25253.7</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1444,25 +1441,21 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v/>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
@@ -1474,50 +1467,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25028.93</v>
+        <v>25025.13</v>
       </c>
       <c r="C12" t="n">
-        <v>25095.66</v>
+        <v>25655.82</v>
       </c>
       <c r="D12" t="n">
-        <v>24887</v>
+        <v>24994.64</v>
       </c>
       <c r="E12" t="n">
-        <v>25040.28</v>
+        <v>25580.88</v>
       </c>
       <c r="F12" t="n">
-        <v>44.47</v>
+        <v>540.6</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0216</v>
       </c>
       <c r="H12" t="n">
-        <v>208.66</v>
+        <v>661.1799999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>24565.41</v>
+        <v>24678.34</v>
       </c>
       <c r="J12" t="n">
-        <v>24809.51</v>
+        <v>24856.09</v>
       </c>
       <c r="K12" t="n">
-        <v>24881.1</v>
+        <v>24935.95</v>
       </c>
       <c r="L12" t="n">
-        <v>24952.68</v>
+        <v>25015.8</v>
       </c>
       <c r="M12" t="n">
-        <v>25110.53</v>
+        <v>25144.61</v>
       </c>
       <c r="N12" t="n">
-        <v>25268.37</v>
+        <v>25273.41</v>
       </c>
       <c r="O12" t="n">
-        <v>25253.7</v>
+        <v>25304.32</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1528,21 +1521,25 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v/>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
@@ -1554,50 +1551,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25025.13</v>
+        <v>25763.97</v>
       </c>
       <c r="C13" t="n">
-        <v>25655.82</v>
+        <v>25826.78</v>
       </c>
       <c r="D13" t="n">
-        <v>24994.64</v>
+        <v>25611.69</v>
       </c>
       <c r="E13" t="n">
-        <v>25580.88</v>
+        <v>25779.31</v>
       </c>
       <c r="F13" t="n">
-        <v>540.6</v>
+        <v>198.43</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0216</v>
+        <v>0.0078</v>
       </c>
       <c r="H13" t="n">
-        <v>661.1799999999999</v>
+        <v>215.09</v>
       </c>
       <c r="I13" t="n">
-        <v>24678.34</v>
+        <v>24333.46</v>
       </c>
       <c r="J13" t="n">
-        <v>24856.09</v>
+        <v>25047.53</v>
       </c>
       <c r="K13" t="n">
-        <v>24935.95</v>
+        <v>25250.29</v>
       </c>
       <c r="L13" t="n">
-        <v>25015.8</v>
+        <v>25453.06</v>
       </c>
       <c r="M13" t="n">
-        <v>25144.61</v>
+        <v>25911.47</v>
       </c>
       <c r="N13" t="n">
-        <v>25273.41</v>
+        <v>26369.89</v>
       </c>
       <c r="O13" t="n">
-        <v>25304.32</v>
+        <v>26317</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1608,25 +1605,21 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v/>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
@@ -1638,50 +1631,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25763.97</v>
+        <v>25811.9</v>
       </c>
       <c r="C14" t="n">
-        <v>25826.78</v>
+        <v>25900.1</v>
       </c>
       <c r="D14" t="n">
-        <v>25611.69</v>
+        <v>25698.56</v>
       </c>
       <c r="E14" t="n">
-        <v>25779.31</v>
+        <v>25817.89</v>
       </c>
       <c r="F14" t="n">
-        <v>198.43</v>
+        <v>38.58</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0078</v>
+        <v>0.0015</v>
       </c>
       <c r="H14" t="n">
-        <v>215.09</v>
+        <v>201.54</v>
       </c>
       <c r="I14" t="n">
-        <v>24333.46</v>
+        <v>25396.6</v>
       </c>
       <c r="J14" t="n">
-        <v>25047.53</v>
+        <v>25594.26</v>
       </c>
       <c r="K14" t="n">
-        <v>25250.29</v>
+        <v>25671.77</v>
       </c>
       <c r="L14" t="n">
-        <v>25453.06</v>
+        <v>25749.27</v>
       </c>
       <c r="M14" t="n">
-        <v>25911.47</v>
+        <v>25886.86</v>
       </c>
       <c r="N14" t="n">
-        <v>26369.89</v>
+        <v>26024.44</v>
       </c>
       <c r="O14" t="n">
-        <v>26317</v>
+        <v>26041.87</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1692,14 +1685,14 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U14" s="8" t="n">
@@ -1718,69 +1711,73 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25811.9</v>
+        <v>25770.45</v>
       </c>
       <c r="C15" t="n">
-        <v>25900.1</v>
+        <v>25811.97</v>
       </c>
       <c r="D15" t="n">
-        <v>25698.56</v>
+        <v>25465.12</v>
       </c>
       <c r="E15" t="n">
-        <v>25817.89</v>
+        <v>25465.25</v>
       </c>
       <c r="F15" t="n">
-        <v>38.58</v>
+        <v>-352.64</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0137</v>
       </c>
       <c r="H15" t="n">
-        <v>201.54</v>
+        <v>346.85</v>
       </c>
       <c r="I15" t="n">
-        <v>25396.6</v>
+        <v>25497.02</v>
       </c>
       <c r="J15" t="n">
-        <v>25594.26</v>
+        <v>25625.63</v>
       </c>
       <c r="K15" t="n">
-        <v>25671.77</v>
+        <v>25717.12</v>
       </c>
       <c r="L15" t="n">
-        <v>25749.27</v>
+        <v>25808.61</v>
       </c>
       <c r="M15" t="n">
-        <v>25886.86</v>
+        <v>25918.66</v>
       </c>
       <c r="N15" t="n">
-        <v>26024.44</v>
+        <v>26028.71</v>
       </c>
       <c r="O15" t="n">
-        <v>26041.87</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+        <v>26101.64</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1788,9 +1785,9 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W15" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
@@ -1798,67 +1795,67 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25770.45</v>
+        <v>25274.94</v>
       </c>
       <c r="C16" t="n">
-        <v>25811.97</v>
+        <v>25280.16</v>
       </c>
       <c r="D16" t="n">
-        <v>25465.12</v>
+        <v>24830.17</v>
       </c>
       <c r="E16" t="n">
-        <v>25465.25</v>
+        <v>24897.45</v>
       </c>
       <c r="F16" t="n">
-        <v>-352.64</v>
+        <v>-567.8</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0223</v>
       </c>
       <c r="H16" t="n">
-        <v>346.85</v>
+        <v>449.99</v>
       </c>
       <c r="I16" t="n">
-        <v>25497.02</v>
+        <v>25118.27</v>
       </c>
       <c r="J16" t="n">
-        <v>25625.63</v>
+        <v>25031.75</v>
       </c>
       <c r="K16" t="n">
-        <v>25717.12</v>
+        <v>25291.82</v>
       </c>
       <c r="L16" t="n">
-        <v>25808.61</v>
+        <v>25551.9</v>
       </c>
       <c r="M16" t="n">
-        <v>25918.66</v>
+        <v>25638.68</v>
       </c>
       <c r="N16" t="n">
-        <v>26028.71</v>
+        <v>25725.45</v>
       </c>
       <c r="O16" t="n">
-        <v>26101.64</v>
+        <v>26158.82</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1882,74 +1879,70 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25274.94</v>
+        <v>25097.48</v>
       </c>
       <c r="C17" t="n">
-        <v>25280.16</v>
+        <v>25127.76</v>
       </c>
       <c r="D17" t="n">
-        <v>24830.17</v>
+        <v>24867.32</v>
       </c>
       <c r="E17" t="n">
-        <v>24897.45</v>
+        <v>25118.27</v>
       </c>
       <c r="F17" t="n">
-        <v>-567.8</v>
+        <v>220.82</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0089</v>
       </c>
       <c r="H17" t="n">
-        <v>449.99</v>
+        <v>260.44</v>
       </c>
       <c r="I17" t="n">
-        <v>25118.27</v>
+        <v>24380.18</v>
       </c>
       <c r="J17" t="n">
-        <v>25031.75</v>
+        <v>24368.6</v>
       </c>
       <c r="K17" t="n">
-        <v>25291.82</v>
+        <v>24672.45</v>
       </c>
       <c r="L17" t="n">
-        <v>25551.9</v>
+        <v>24976.31</v>
       </c>
       <c r="M17" t="n">
-        <v>25638.68</v>
+        <v>25122.44</v>
       </c>
       <c r="N17" t="n">
-        <v>25725.45</v>
+        <v>25268.58</v>
       </c>
       <c r="O17" t="n">
-        <v>26158.82</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
+        <v>25730.15</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
@@ -1961,55 +1954,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25097.48</v>
+        <v>25081.19</v>
       </c>
       <c r="C18" t="n">
-        <v>25127.76</v>
+        <v>25195.83</v>
       </c>
       <c r="D18" t="n">
-        <v>24867.32</v>
+        <v>24937.52</v>
       </c>
       <c r="E18" t="n">
-        <v>25118.27</v>
+        <v>25067.09</v>
       </c>
       <c r="F18" t="n">
-        <v>220.82</v>
+        <v>-51.18</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.002</v>
       </c>
       <c r="H18" t="n">
-        <v>260.44</v>
+        <v>258.31</v>
       </c>
       <c r="I18" t="n">
-        <v>24380.18</v>
+        <v>24606.88</v>
       </c>
       <c r="J18" t="n">
-        <v>24368.6</v>
+        <v>24918.19</v>
       </c>
       <c r="K18" t="n">
-        <v>24672.45</v>
+        <v>24988.05</v>
       </c>
       <c r="L18" t="n">
-        <v>24976.31</v>
+        <v>25057.9</v>
       </c>
       <c r="M18" t="n">
-        <v>25122.44</v>
+        <v>25248.49</v>
       </c>
       <c r="N18" t="n">
-        <v>25268.58</v>
+        <v>25439.07</v>
       </c>
       <c r="O18" t="n">
-        <v>25730.15</v>
+        <v>25388.2</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2017,18 +2014,18 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2050,50 +2047,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25081.19</v>
+        <v>24963.8</v>
       </c>
       <c r="C19" t="n">
-        <v>25195.83</v>
+        <v>25154.58</v>
       </c>
       <c r="D19" t="n">
-        <v>24937.52</v>
+        <v>24963.8</v>
       </c>
       <c r="E19" t="n">
-        <v>25067.09</v>
+        <v>25114.25</v>
       </c>
       <c r="F19" t="n">
-        <v>-51.18</v>
+        <v>47.16</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="H19" t="n">
-        <v>258.31</v>
+        <v>190.78</v>
       </c>
       <c r="I19" t="n">
-        <v>24606.88</v>
+        <v>24679.21</v>
       </c>
       <c r="J19" t="n">
-        <v>24918.19</v>
+        <v>24808.99</v>
       </c>
       <c r="K19" t="n">
-        <v>24988.05</v>
+        <v>24937.93</v>
       </c>
       <c r="L19" t="n">
-        <v>25057.9</v>
+        <v>25066.88</v>
       </c>
       <c r="M19" t="n">
-        <v>25248.49</v>
+        <v>25196.25</v>
       </c>
       <c r="N19" t="n">
-        <v>25439.07</v>
+        <v>25325.61</v>
       </c>
       <c r="O19" t="n">
-        <v>25388.2</v>
+        <v>25454.14</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2101,12 +2098,10 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2134,61 +2129,65 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24963.8</v>
+        <v>24932.62</v>
       </c>
       <c r="C20" t="n">
-        <v>25154.58</v>
+        <v>25204.68</v>
       </c>
       <c r="D20" t="n">
-        <v>24963.8</v>
+        <v>24869.25</v>
       </c>
       <c r="E20" t="n">
-        <v>25114.25</v>
+        <v>25147.03</v>
       </c>
       <c r="F20" t="n">
-        <v>47.16</v>
+        <v>32.78</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0013</v>
       </c>
       <c r="H20" t="n">
-        <v>190.78</v>
+        <v>335.43</v>
       </c>
       <c r="I20" t="n">
-        <v>24679.21</v>
+        <v>24773.02</v>
       </c>
       <c r="J20" t="n">
-        <v>24808.99</v>
+        <v>24951</v>
       </c>
       <c r="K20" t="n">
-        <v>24937.93</v>
+        <v>25018.86</v>
       </c>
       <c r="L20" t="n">
-        <v>25066.88</v>
+        <v>25086.72</v>
       </c>
       <c r="M20" t="n">
-        <v>25196.25</v>
+        <v>25209.64</v>
       </c>
       <c r="N20" t="n">
-        <v>25325.61</v>
+        <v>25332.56</v>
       </c>
       <c r="O20" t="n">
-        <v>25454.14</v>
+        <v>25345.36</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2216,50 +2215,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24932.62</v>
+        <v>24970.05</v>
       </c>
       <c r="C21" t="n">
-        <v>25204.68</v>
+        <v>25055.48</v>
       </c>
       <c r="D21" t="n">
-        <v>24869.25</v>
+        <v>24839.23</v>
       </c>
       <c r="E21" t="n">
-        <v>25147.03</v>
+        <v>24999.53</v>
       </c>
       <c r="F21" t="n">
-        <v>32.78</v>
+        <v>-147.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0059</v>
       </c>
       <c r="H21" t="n">
-        <v>335.43</v>
+        <v>216.25</v>
       </c>
       <c r="I21" t="n">
-        <v>24773.02</v>
+        <v>24533.82</v>
       </c>
       <c r="J21" t="n">
-        <v>24951</v>
+        <v>24866.63</v>
       </c>
       <c r="K21" t="n">
-        <v>25018.86</v>
+        <v>24979.31</v>
       </c>
       <c r="L21" t="n">
-        <v>25086.72</v>
+        <v>25092</v>
       </c>
       <c r="M21" t="n">
-        <v>25209.64</v>
+        <v>25314.74</v>
       </c>
       <c r="N21" t="n">
-        <v>25332.56</v>
+        <v>25537.49</v>
       </c>
       <c r="O21" t="n">
-        <v>25345.36</v>
+        <v>25540.11</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2271,12 +2270,12 @@
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2293,59 +2292,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24970.05</v>
+        <v>25018.95</v>
       </c>
       <c r="C22" t="n">
-        <v>25055.48</v>
+        <v>25021.51</v>
       </c>
       <c r="D22" t="n">
-        <v>24839.23</v>
+        <v>24696.17</v>
       </c>
       <c r="E22" t="n">
-        <v>24999.53</v>
+        <v>24915.49</v>
       </c>
       <c r="F22" t="n">
-        <v>-147.5</v>
+        <v>-84.04000000000001</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0059</v>
+        <v>-0.0034</v>
       </c>
       <c r="H22" t="n">
-        <v>216.25</v>
+        <v>325.34</v>
       </c>
       <c r="I22" t="n">
-        <v>24533.82</v>
+        <v>24622.98</v>
       </c>
       <c r="J22" t="n">
-        <v>24866.63</v>
+        <v>24809.37</v>
       </c>
       <c r="K22" t="n">
-        <v>24979.31</v>
+        <v>24891.4</v>
       </c>
       <c r="L22" t="n">
-        <v>25092</v>
+        <v>24973.44</v>
       </c>
       <c r="M22" t="n">
-        <v>25314.74</v>
+        <v>25107.65</v>
       </c>
       <c r="N22" t="n">
-        <v>25537.49</v>
+        <v>25241.87</v>
       </c>
       <c r="O22" t="n">
-        <v>25540.11</v>
+        <v>25271.73</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2360,7 +2355,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2384,67 +2379,65 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25018.95</v>
+        <v>24755.09</v>
       </c>
       <c r="C23" t="n">
-        <v>25021.51</v>
+        <v>24850.75</v>
       </c>
       <c r="D23" t="n">
-        <v>24696.17</v>
+        <v>24651.34</v>
       </c>
       <c r="E23" t="n">
-        <v>24915.49</v>
+        <v>24830.98</v>
       </c>
       <c r="F23" t="n">
-        <v>-84.04000000000001</v>
+        <v>-84.51000000000001</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>-0.0034</v>
       </c>
       <c r="H23" t="n">
-        <v>325.34</v>
+        <v>199.41</v>
       </c>
       <c r="I23" t="n">
-        <v>24622.98</v>
+        <v>24370.83</v>
       </c>
       <c r="J23" t="n">
-        <v>24809.37</v>
+        <v>24618.48</v>
       </c>
       <c r="K23" t="n">
-        <v>24891.4</v>
+        <v>24752.82</v>
       </c>
       <c r="L23" t="n">
-        <v>24973.44</v>
+        <v>24887.17</v>
       </c>
       <c r="M23" t="n">
-        <v>25107.65</v>
+        <v>25078.16</v>
       </c>
       <c r="N23" t="n">
-        <v>25241.87</v>
+        <v>25269.16</v>
       </c>
       <c r="O23" t="n">
-        <v>25271.73</v>
+        <v>25346.85</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q23" s="6" t="n">
+        <v/>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2466,50 +2459,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24755.09</v>
+        <v>24769.15</v>
       </c>
       <c r="C24" t="n">
-        <v>24850.75</v>
+        <v>24974.53</v>
       </c>
       <c r="D24" t="n">
-        <v>24651.34</v>
+        <v>24751.13</v>
       </c>
       <c r="E24" t="n">
-        <v>24830.98</v>
+        <v>24846.69</v>
       </c>
       <c r="F24" t="n">
-        <v>-84.51000000000001</v>
+        <v>15.71</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>199.41</v>
+        <v>223.4</v>
       </c>
       <c r="I24" t="n">
-        <v>24370.83</v>
+        <v>24451.93</v>
       </c>
       <c r="J24" t="n">
-        <v>24618.48</v>
+        <v>24671.54</v>
       </c>
       <c r="K24" t="n">
-        <v>24752.82</v>
+        <v>24731.28</v>
       </c>
       <c r="L24" t="n">
-        <v>24887.17</v>
+        <v>24791.01</v>
       </c>
       <c r="M24" t="n">
-        <v>25078.16</v>
+        <v>24930.69</v>
       </c>
       <c r="N24" t="n">
-        <v>25269.16</v>
+        <v>25070.36</v>
       </c>
       <c r="O24" t="n">
-        <v>25346.85</v>
+        <v>25050.16</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2517,18 +2510,18 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R24" s="6" t="n">
+        <v/>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2541,55 +2534,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24769.15</v>
+        <v>24922.1</v>
       </c>
       <c r="C25" t="n">
-        <v>24974.53</v>
+        <v>25011.35</v>
       </c>
       <c r="D25" t="n">
-        <v>24751.13</v>
+        <v>24817.34</v>
       </c>
       <c r="E25" t="n">
-        <v>24846.69</v>
+        <v>25011.35</v>
       </c>
       <c r="F25" t="n">
-        <v>15.71</v>
+        <v>164.66</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0066</v>
       </c>
       <c r="H25" t="n">
-        <v>223.4</v>
+        <v>194.01</v>
       </c>
       <c r="I25" t="n">
-        <v>24451.93</v>
+        <v>24527.73</v>
       </c>
       <c r="J25" t="n">
-        <v>24671.54</v>
+        <v>24615.22</v>
       </c>
       <c r="K25" t="n">
-        <v>24731.28</v>
+        <v>24734.99</v>
       </c>
       <c r="L25" t="n">
-        <v>24791.01</v>
+        <v>24854.76</v>
       </c>
       <c r="M25" t="n">
-        <v>24930.69</v>
+        <v>24958.39</v>
       </c>
       <c r="N25" t="n">
-        <v>25070.36</v>
+        <v>25062.02</v>
       </c>
       <c r="O25" t="n">
-        <v>25050.16</v>
+        <v>25197.93</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2600,9 +2597,9 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -2610,8 +2607,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2630,50 +2629,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24922.1</v>
+        <v>25001.31</v>
       </c>
       <c r="C26" t="n">
-        <v>25011.35</v>
+        <v>25271.34</v>
       </c>
       <c r="D26" t="n">
-        <v>24817.34</v>
+        <v>24984.27</v>
       </c>
       <c r="E26" t="n">
-        <v>25011.35</v>
+        <v>25155.41</v>
       </c>
       <c r="F26" t="n">
-        <v>164.66</v>
+        <v>144.06</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0058</v>
       </c>
       <c r="H26" t="n">
-        <v>194.01</v>
+        <v>287.07</v>
       </c>
       <c r="I26" t="n">
-        <v>24527.73</v>
+        <v>24623.33</v>
       </c>
       <c r="J26" t="n">
-        <v>24615.22</v>
+        <v>24865.84</v>
       </c>
       <c r="K26" t="n">
-        <v>24734.99</v>
+        <v>24914.34</v>
       </c>
       <c r="L26" t="n">
-        <v>24854.76</v>
+        <v>24962.85</v>
       </c>
       <c r="M26" t="n">
-        <v>24958.39</v>
+        <v>25108.35</v>
       </c>
       <c r="N26" t="n">
-        <v>25062.02</v>
+        <v>25253.86</v>
       </c>
       <c r="O26" t="n">
-        <v>25197.93</v>
+        <v>25205.36</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2684,23 +2683,25 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U26" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W26" s="11" t="inlineStr">
         <is>
@@ -2716,171 +2717,165 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25001.31</v>
+        <v>24994.05</v>
       </c>
       <c r="C27" t="n">
-        <v>25271.34</v>
+        <v>25074.28</v>
       </c>
       <c r="D27" t="n">
-        <v>24984.27</v>
+        <v>24696.59</v>
       </c>
       <c r="E27" t="n">
-        <v>25155.41</v>
+        <v>24763.12</v>
       </c>
       <c r="F27" t="n">
-        <v>144.06</v>
+        <v>-392.29</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0156</v>
       </c>
       <c r="H27" t="n">
-        <v>287.07</v>
+        <v>377.69</v>
       </c>
       <c r="I27" t="n">
-        <v>24623.33</v>
+        <v>24697.2</v>
       </c>
       <c r="J27" t="n">
-        <v>24865.84</v>
+        <v>24882.14</v>
       </c>
       <c r="K27" t="n">
-        <v>24914.34</v>
+        <v>25011.88</v>
       </c>
       <c r="L27" t="n">
-        <v>24962.85</v>
+        <v>25141.61</v>
       </c>
       <c r="M27" t="n">
-        <v>25108.35</v>
+        <v>25298.95</v>
       </c>
       <c r="N27" t="n">
-        <v>25253.86</v>
+        <v>25456.28</v>
       </c>
       <c r="O27" t="n">
-        <v>25205.36</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+        <v>25558.41</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
       </c>
       <c r="W27" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24994.05</v>
+        <v>24830.41</v>
       </c>
       <c r="C28" t="n">
-        <v>25074.28</v>
+        <v>25099.68</v>
       </c>
       <c r="D28" t="n">
-        <v>24696.59</v>
+        <v>24821.67</v>
       </c>
       <c r="E28" t="n">
-        <v>24763.12</v>
+        <v>25099</v>
       </c>
       <c r="F28" t="n">
-        <v>-392.29</v>
+        <v>335.88</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0136</v>
       </c>
       <c r="H28" t="n">
-        <v>377.69</v>
+        <v>278.01</v>
       </c>
       <c r="I28" t="n">
-        <v>24697.2</v>
+        <v>24318.9</v>
       </c>
       <c r="J28" t="n">
-        <v>24882.14</v>
+        <v>24324.27</v>
       </c>
       <c r="K28" t="n">
-        <v>25011.88</v>
+        <v>24574.27</v>
       </c>
       <c r="L28" t="n">
-        <v>25141.61</v>
+        <v>24824.28</v>
       </c>
       <c r="M28" t="n">
-        <v>25298.95</v>
+        <v>24951.96</v>
       </c>
       <c r="N28" t="n">
-        <v>25456.28</v>
+        <v>25079.65</v>
       </c>
       <c r="O28" t="n">
-        <v>25558.41</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
+        <v>25451.97</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr"/>
@@ -2888,50 +2883,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>24830.41</v>
+        <v>25459.32</v>
       </c>
       <c r="C29" t="n">
-        <v>25099.68</v>
+        <v>25560.4</v>
       </c>
       <c r="D29" t="n">
-        <v>24821.67</v>
+        <v>25361.03</v>
       </c>
       <c r="E29" t="n">
-        <v>25099</v>
+        <v>25361.03</v>
       </c>
       <c r="F29" t="n">
-        <v>335.88</v>
+        <v>262.03</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0104</v>
       </c>
       <c r="H29" t="n">
-        <v>278.01</v>
+        <v>199.37</v>
       </c>
       <c r="I29" t="n">
-        <v>24318.9</v>
+        <v>24543.66</v>
       </c>
       <c r="J29" t="n">
-        <v>24324.27</v>
+        <v>24890.15</v>
       </c>
       <c r="K29" t="n">
-        <v>24574.27</v>
+        <v>24960</v>
       </c>
       <c r="L29" t="n">
-        <v>24824.28</v>
+        <v>25029.84</v>
       </c>
       <c r="M29" t="n">
-        <v>24951.96</v>
+        <v>25238</v>
       </c>
       <c r="N29" t="n">
-        <v>25079.65</v>
+        <v>25446.17</v>
       </c>
       <c r="O29" t="n">
-        <v>25451.97</v>
+        <v>25377.69</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2942,7 +2937,7 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2954,11 +2949,13 @@
       </c>
       <c r="U29" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
@@ -2970,50 +2967,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25459.32</v>
+        <v>25496.13</v>
       </c>
       <c r="C30" t="n">
-        <v>25560.4</v>
+        <v>25553.47</v>
       </c>
       <c r="D30" t="n">
-        <v>25361.03</v>
+        <v>25307.17</v>
       </c>
       <c r="E30" t="n">
-        <v>25361.03</v>
+        <v>25464.01</v>
       </c>
       <c r="F30" t="n">
-        <v>262.03</v>
+        <v>102.98</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0104</v>
+        <v>0.0041</v>
       </c>
       <c r="H30" t="n">
-        <v>199.37</v>
+        <v>246.3</v>
       </c>
       <c r="I30" t="n">
-        <v>24543.66</v>
+        <v>25161.66</v>
       </c>
       <c r="J30" t="n">
-        <v>24890.15</v>
+        <v>25111.82</v>
       </c>
       <c r="K30" t="n">
-        <v>24960</v>
+        <v>25261.34</v>
       </c>
       <c r="L30" t="n">
-        <v>25029.84</v>
+        <v>25410.87</v>
       </c>
       <c r="M30" t="n">
-        <v>25238</v>
+        <v>25460.71</v>
       </c>
       <c r="N30" t="n">
-        <v>25446.17</v>
+        <v>25510.56</v>
       </c>
       <c r="O30" t="n">
-        <v>25377.69</v>
+        <v>25759.77</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3024,14 +3021,14 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U30" s="8" t="inlineStr">
@@ -3039,65 +3036,67 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V30" s="8" t="n">
+        <v/>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25496.13</v>
+        <v>25551.97</v>
       </c>
       <c r="C31" t="n">
-        <v>25553.47</v>
+        <v>25571.45</v>
       </c>
       <c r="D31" t="n">
-        <v>25307.17</v>
+        <v>25336.39</v>
       </c>
       <c r="E31" t="n">
-        <v>25464.01</v>
+        <v>25460.48</v>
       </c>
       <c r="F31" t="n">
-        <v>102.98</v>
+        <v>-3.53</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0001</v>
       </c>
       <c r="H31" t="n">
-        <v>246.3</v>
+        <v>235.06</v>
       </c>
       <c r="I31" t="n">
-        <v>25161.66</v>
+        <v>25060.87</v>
       </c>
       <c r="J31" t="n">
-        <v>25111.82</v>
+        <v>25234.55</v>
       </c>
       <c r="K31" t="n">
-        <v>25261.34</v>
+        <v>25340.86</v>
       </c>
       <c r="L31" t="n">
-        <v>25410.87</v>
+        <v>25447.17</v>
       </c>
       <c r="M31" t="n">
-        <v>25460.71</v>
+        <v>25587.16</v>
       </c>
       <c r="N31" t="n">
-        <v>25510.56</v>
+        <v>25727.16</v>
       </c>
       <c r="O31" t="n">
-        <v>25759.77</v>
+        <v>25799.77</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3105,23 +3104,21 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3133,57 +3130,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25551.97</v>
+        <v>25487.45</v>
       </c>
       <c r="C32" t="n">
-        <v>25571.45</v>
+        <v>25651.16</v>
       </c>
       <c r="D32" t="n">
-        <v>25336.39</v>
+        <v>25303.11</v>
       </c>
       <c r="E32" t="n">
-        <v>25460.48</v>
+        <v>25612.03</v>
       </c>
       <c r="F32" t="n">
-        <v>-3.53</v>
+        <v>151.55</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.006</v>
       </c>
       <c r="H32" t="n">
-        <v>235.06</v>
+        <v>348.05</v>
       </c>
       <c r="I32" t="n">
-        <v>25060.87</v>
+        <v>25101.33</v>
       </c>
       <c r="J32" t="n">
-        <v>25234.55</v>
+        <v>25228.7</v>
       </c>
       <c r="K32" t="n">
-        <v>25340.86</v>
+        <v>25342.95</v>
       </c>
       <c r="L32" t="n">
-        <v>25447.17</v>
+        <v>25457.2</v>
       </c>
       <c r="M32" t="n">
-        <v>25587.16</v>
+        <v>25578.01</v>
       </c>
       <c r="N32" t="n">
-        <v>25727.16</v>
+        <v>25698.82</v>
       </c>
       <c r="O32" t="n">
-        <v>25799.77</v>
+        <v>25806.51</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3196,13 +3193,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3224,50 +3223,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25487.45</v>
+        <v>25709.37</v>
       </c>
       <c r="C33" t="n">
-        <v>25651.16</v>
+        <v>25891.51</v>
       </c>
       <c r="D33" t="n">
-        <v>25303.11</v>
+        <v>25549.53</v>
       </c>
       <c r="E33" t="n">
-        <v>25612.03</v>
+        <v>25629.24</v>
       </c>
       <c r="F33" t="n">
-        <v>151.55</v>
+        <v>17.21</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0007</v>
       </c>
       <c r="H33" t="n">
-        <v>348.05</v>
+        <v>341.98</v>
       </c>
       <c r="I33" t="n">
-        <v>25101.33</v>
+        <v>24955.06</v>
       </c>
       <c r="J33" t="n">
-        <v>25228.7</v>
+        <v>25331.43</v>
       </c>
       <c r="K33" t="n">
-        <v>25342.95</v>
+        <v>25438</v>
       </c>
       <c r="L33" t="n">
-        <v>25457.2</v>
+        <v>25544.58</v>
       </c>
       <c r="M33" t="n">
-        <v>25578.01</v>
+        <v>25786.05</v>
       </c>
       <c r="N33" t="n">
-        <v>25698.82</v>
+        <v>26027.53</v>
       </c>
       <c r="O33" t="n">
-        <v>25806.51</v>
+        <v>25999.21</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3275,19 +3274,17 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U33" s="8" t="n">
@@ -3301,59 +3298,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25709.37</v>
+        <v>25855.12</v>
       </c>
       <c r="C34" t="n">
-        <v>25891.51</v>
+        <v>26096.93</v>
       </c>
       <c r="D34" t="n">
-        <v>25549.53</v>
+        <v>25855.12</v>
       </c>
       <c r="E34" t="n">
-        <v>25629.24</v>
+        <v>26001.31</v>
       </c>
       <c r="F34" t="n">
-        <v>17.21</v>
+        <v>372.07</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0145</v>
       </c>
       <c r="H34" t="n">
-        <v>341.98</v>
+        <v>241.81</v>
       </c>
       <c r="I34" t="n">
-        <v>24955.06</v>
+        <v>25207.55</v>
       </c>
       <c r="J34" t="n">
-        <v>25331.43</v>
+        <v>25241.62</v>
       </c>
       <c r="K34" t="n">
-        <v>25438</v>
+        <v>25458.25</v>
       </c>
       <c r="L34" t="n">
-        <v>25544.58</v>
+        <v>25674.88</v>
       </c>
       <c r="M34" t="n">
-        <v>25786.05</v>
+        <v>25800.23</v>
       </c>
       <c r="N34" t="n">
-        <v>26027.53</v>
+        <v>25925.58</v>
       </c>
       <c r="O34" t="n">
-        <v>25999.21</v>
+        <v>26233.49</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3364,9 +3357,9 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
@@ -3374,8 +3367,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3390,50 +3385,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25855.12</v>
+        <v>26189.62</v>
       </c>
       <c r="C35" t="n">
-        <v>26096.93</v>
+        <v>26266.5</v>
       </c>
       <c r="D35" t="n">
-        <v>25855.12</v>
+        <v>26082.43</v>
       </c>
       <c r="E35" t="n">
-        <v>26001.31</v>
+        <v>26202.35</v>
       </c>
       <c r="F35" t="n">
-        <v>372.07</v>
+        <v>201.04</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0077</v>
       </c>
       <c r="H35" t="n">
-        <v>241.81</v>
+        <v>184.07</v>
       </c>
       <c r="I35" t="n">
-        <v>25207.55</v>
+        <v>25613.31</v>
       </c>
       <c r="J35" t="n">
-        <v>25241.62</v>
+        <v>25772.14</v>
       </c>
       <c r="K35" t="n">
-        <v>25458.25</v>
+        <v>25880.41</v>
       </c>
       <c r="L35" t="n">
-        <v>25674.88</v>
+        <v>25988.67</v>
       </c>
       <c r="M35" t="n">
-        <v>25800.23</v>
+        <v>26122.22</v>
       </c>
       <c r="N35" t="n">
-        <v>25925.58</v>
+        <v>26255.76</v>
       </c>
       <c r="O35" t="n">
-        <v>26233.49</v>
+        <v>26338.74</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3444,7 +3439,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3472,50 +3467,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26189.62</v>
+        <v>26393.43</v>
       </c>
       <c r="C36" t="n">
-        <v>26266.5</v>
+        <v>26403.81</v>
       </c>
       <c r="D36" t="n">
-        <v>26082.43</v>
+        <v>26123.18</v>
       </c>
       <c r="E36" t="n">
-        <v>26202.35</v>
+        <v>26126.3</v>
       </c>
       <c r="F36" t="n">
-        <v>201.04</v>
+        <v>-76.05</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0029</v>
       </c>
       <c r="H36" t="n">
-        <v>184.07</v>
+        <v>280.63</v>
       </c>
       <c r="I36" t="n">
-        <v>25613.31</v>
+        <v>25898.36</v>
       </c>
       <c r="J36" t="n">
-        <v>25772.14</v>
+        <v>26032.22</v>
       </c>
       <c r="K36" t="n">
-        <v>25880.41</v>
+        <v>26110.31</v>
       </c>
       <c r="L36" t="n">
-        <v>25988.67</v>
+        <v>26188.41</v>
       </c>
       <c r="M36" t="n">
-        <v>26122.22</v>
+        <v>26294.38</v>
       </c>
       <c r="N36" t="n">
-        <v>26255.76</v>
+        <v>26400.36</v>
       </c>
       <c r="O36" t="n">
-        <v>26338.74</v>
+        <v>26450.57</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3523,12 +3518,14 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
@@ -3538,7 +3535,7 @@
       </c>
       <c r="U36" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V36" s="8" t="n">
@@ -3549,55 +3546,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26393.43</v>
+        <v>26116.27</v>
       </c>
       <c r="C37" t="n">
-        <v>26403.81</v>
+        <v>26229.33</v>
       </c>
       <c r="D37" t="n">
-        <v>26123.18</v>
+        <v>26081.69</v>
       </c>
       <c r="E37" t="n">
-        <v>26126.3</v>
+        <v>26140.13</v>
       </c>
       <c r="F37" t="n">
-        <v>-76.05</v>
+        <v>13.83</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0005</v>
       </c>
       <c r="H37" t="n">
-        <v>280.63</v>
+        <v>147.64</v>
       </c>
       <c r="I37" t="n">
-        <v>25898.36</v>
+        <v>25842.55</v>
       </c>
       <c r="J37" t="n">
-        <v>26032.22</v>
+        <v>25777.07</v>
       </c>
       <c r="K37" t="n">
-        <v>26110.31</v>
+        <v>25985.99</v>
       </c>
       <c r="L37" t="n">
-        <v>26188.41</v>
+        <v>26194.9</v>
       </c>
       <c r="M37" t="n">
-        <v>26294.38</v>
+        <v>26266.62</v>
       </c>
       <c r="N37" t="n">
-        <v>26400.36</v>
+        <v>26338.33</v>
       </c>
       <c r="O37" t="n">
-        <v>26450.57</v>
+        <v>26684.44</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3605,25 +3606,19 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3635,57 +3630,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26116.27</v>
+        <v>26235.8</v>
       </c>
       <c r="C38" t="n">
-        <v>26229.33</v>
+        <v>26445.18</v>
       </c>
       <c r="D38" t="n">
-        <v>26081.69</v>
+        <v>26223.64</v>
       </c>
       <c r="E38" t="n">
-        <v>26140.13</v>
+        <v>26319.45</v>
       </c>
       <c r="F38" t="n">
-        <v>13.83</v>
+        <v>179.32</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0069</v>
       </c>
       <c r="H38" t="n">
-        <v>147.64</v>
+        <v>221.54</v>
       </c>
       <c r="I38" t="n">
-        <v>25842.55</v>
+        <v>25934.05</v>
       </c>
       <c r="J38" t="n">
-        <v>25777.07</v>
+        <v>25984.8</v>
       </c>
       <c r="K38" t="n">
-        <v>25985.99</v>
+        <v>26066.31</v>
       </c>
       <c r="L38" t="n">
-        <v>26194.9</v>
+        <v>26147.82</v>
       </c>
       <c r="M38" t="n">
-        <v>26266.62</v>
+        <v>26213.95</v>
       </c>
       <c r="N38" t="n">
-        <v>26338.33</v>
+        <v>26280.08</v>
       </c>
       <c r="O38" t="n">
-        <v>26684.44</v>
+        <v>26376.97</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3698,76 +3693,78 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26235.8</v>
+        <v>26360.44</v>
       </c>
       <c r="C39" t="n">
-        <v>26445.18</v>
+        <v>26441.91</v>
       </c>
       <c r="D39" t="n">
-        <v>26223.64</v>
+        <v>26302.19</v>
       </c>
       <c r="E39" t="n">
-        <v>26319.45</v>
+        <v>26323.88</v>
       </c>
       <c r="F39" t="n">
-        <v>179.32</v>
+        <v>4.43</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0002</v>
       </c>
       <c r="H39" t="n">
-        <v>221.54</v>
+        <v>139.72</v>
       </c>
       <c r="I39" t="n">
-        <v>25934.05</v>
+        <v>26002.1</v>
       </c>
       <c r="J39" t="n">
-        <v>25984.8</v>
+        <v>26090.43</v>
       </c>
       <c r="K39" t="n">
-        <v>26066.31</v>
+        <v>26208.68</v>
       </c>
       <c r="L39" t="n">
-        <v>26147.82</v>
+        <v>26326.93</v>
       </c>
       <c r="M39" t="n">
-        <v>26213.95</v>
+        <v>26430.22</v>
       </c>
       <c r="N39" t="n">
-        <v>26280.08</v>
+        <v>26533.51</v>
       </c>
       <c r="O39" t="n">
-        <v>26376.97</v>
+        <v>26666.72</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3780,7 +3777,7 @@
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
@@ -3788,70 +3785,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>26360.44</v>
+        <v>26378</v>
       </c>
       <c r="C40" t="n">
-        <v>26441.91</v>
+        <v>26504.54</v>
       </c>
       <c r="D40" t="n">
-        <v>26302.19</v>
+        <v>26245.57</v>
       </c>
       <c r="E40" t="n">
-        <v>26323.88</v>
+        <v>26391.42</v>
       </c>
       <c r="F40" t="n">
-        <v>4.43</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0026</v>
       </c>
       <c r="H40" t="n">
-        <v>139.72</v>
+        <v>258.97</v>
       </c>
       <c r="I40" t="n">
-        <v>26002.1</v>
+        <v>26162.47</v>
       </c>
       <c r="J40" t="n">
-        <v>26090.43</v>
+        <v>26160.08</v>
       </c>
       <c r="K40" t="n">
-        <v>26208.68</v>
+        <v>26254.02</v>
       </c>
       <c r="L40" t="n">
-        <v>26326.93</v>
+        <v>26347.97</v>
       </c>
       <c r="M40" t="n">
-        <v>26430.22</v>
+        <v>26393.74</v>
       </c>
       <c r="N40" t="n">
-        <v>26533.51</v>
+        <v>26439.52</v>
       </c>
       <c r="O40" t="n">
-        <v>26666.72</v>
+        <v>26581.63</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3859,21 +3856,25 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3892,50 +3893,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26378</v>
+        <v>26452</v>
       </c>
       <c r="C41" t="n">
-        <v>26504.54</v>
+        <v>26573.5</v>
       </c>
       <c r="D41" t="n">
-        <v>26245.57</v>
+        <v>26313.58</v>
       </c>
       <c r="E41" t="n">
-        <v>26391.42</v>
+        <v>26331.07</v>
       </c>
       <c r="F41" t="n">
-        <v>67.54000000000001</v>
+        <v>-60.35</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0023</v>
       </c>
       <c r="H41" t="n">
-        <v>258.97</v>
+        <v>259.92</v>
       </c>
       <c r="I41" t="n">
-        <v>26162.47</v>
+        <v>25986.6</v>
       </c>
       <c r="J41" t="n">
-        <v>26160.08</v>
+        <v>26140.63</v>
       </c>
       <c r="K41" t="n">
-        <v>26254.02</v>
+        <v>26261.94</v>
       </c>
       <c r="L41" t="n">
-        <v>26347.97</v>
+        <v>26383.24</v>
       </c>
       <c r="M41" t="n">
-        <v>26393.74</v>
+        <v>26520.9</v>
       </c>
       <c r="N41" t="n">
-        <v>26439.52</v>
+        <v>26658.57</v>
       </c>
       <c r="O41" t="n">
-        <v>26581.63</v>
+        <v>26763.51</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3943,25 +3944,21 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3980,50 +3977,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26452</v>
+        <v>26437.35</v>
       </c>
       <c r="C42" t="n">
-        <v>26573.5</v>
+        <v>26489.78</v>
       </c>
       <c r="D42" t="n">
-        <v>26313.58</v>
+        <v>26285.23</v>
       </c>
       <c r="E42" t="n">
-        <v>26331.07</v>
+        <v>26299.74</v>
       </c>
       <c r="F42" t="n">
-        <v>-60.35</v>
+        <v>-31.33</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0012</v>
       </c>
       <c r="H42" t="n">
-        <v>259.92</v>
+        <v>204.55</v>
       </c>
       <c r="I42" t="n">
-        <v>25986.6</v>
+        <v>26053.66</v>
       </c>
       <c r="J42" t="n">
-        <v>26140.63</v>
+        <v>26014.92</v>
       </c>
       <c r="K42" t="n">
-        <v>26261.94</v>
+        <v>26201.11</v>
       </c>
       <c r="L42" t="n">
-        <v>26383.24</v>
+        <v>26387.31</v>
       </c>
       <c r="M42" t="n">
-        <v>26520.9</v>
+        <v>26461.03</v>
       </c>
       <c r="N42" t="n">
-        <v>26658.57</v>
+        <v>26534.76</v>
       </c>
       <c r="O42" t="n">
-        <v>26763.51</v>
+        <v>26833.42</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4034,7 +4031,7 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="7" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4057,57 +4054,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>26437.35</v>
+        <v>26445.99</v>
       </c>
       <c r="C43" t="n">
-        <v>26489.78</v>
+        <v>26541.34</v>
       </c>
       <c r="D43" t="n">
-        <v>26285.23</v>
+        <v>26404.95</v>
       </c>
       <c r="E43" t="n">
-        <v>26299.74</v>
+        <v>26440.31</v>
       </c>
       <c r="F43" t="n">
-        <v>-31.33</v>
+        <v>140.57</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0053</v>
       </c>
       <c r="H43" t="n">
-        <v>204.55</v>
+        <v>136.39</v>
       </c>
       <c r="I43" t="n">
-        <v>26053.66</v>
+        <v>26080.68</v>
       </c>
       <c r="J43" t="n">
-        <v>26014.92</v>
+        <v>26051.31</v>
       </c>
       <c r="K43" t="n">
-        <v>26201.11</v>
+        <v>26197.47</v>
       </c>
       <c r="L43" t="n">
-        <v>26387.31</v>
+        <v>26343.62</v>
       </c>
       <c r="M43" t="n">
-        <v>26461.03</v>
+        <v>26402.01</v>
       </c>
       <c r="N43" t="n">
-        <v>26534.76</v>
+        <v>26460.41</v>
       </c>
       <c r="O43" t="n">
-        <v>26833.42</v>
+        <v>26694.33</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4120,7 +4117,7 @@
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
@@ -4128,8 +4125,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U43" s="8" t="n">
-        <v/>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4139,59 +4138,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26445.99</v>
+        <v>26490.3</v>
       </c>
       <c r="C44" t="n">
-        <v>26541.34</v>
+        <v>26493.5</v>
       </c>
       <c r="D44" t="n">
-        <v>26404.95</v>
+        <v>26338.61</v>
       </c>
       <c r="E44" t="n">
-        <v>26440.31</v>
+        <v>26338.61</v>
       </c>
       <c r="F44" t="n">
-        <v>140.57</v>
+        <v>-101.7</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0038</v>
       </c>
       <c r="H44" t="n">
-        <v>136.39</v>
+        <v>154.89</v>
       </c>
       <c r="I44" t="n">
-        <v>26080.68</v>
+        <v>26268.56</v>
       </c>
       <c r="J44" t="n">
-        <v>26051.31</v>
+        <v>26287.5</v>
       </c>
       <c r="K44" t="n">
-        <v>26197.47</v>
+        <v>26372.12</v>
       </c>
       <c r="L44" t="n">
-        <v>26343.62</v>
+        <v>26456.73</v>
       </c>
       <c r="M44" t="n">
-        <v>26402.01</v>
+        <v>26508.51</v>
       </c>
       <c r="N44" t="n">
-        <v>26460.41</v>
+        <v>26560.28</v>
       </c>
       <c r="O44" t="n">
-        <v>26694.33</v>
+        <v>26677.73</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4199,23 +4194,21 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4225,68 +4218,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>26490.3</v>
+        <v>26280.86</v>
       </c>
       <c r="C45" t="n">
-        <v>26493.5</v>
+        <v>26292.95</v>
       </c>
       <c r="D45" t="n">
-        <v>26338.61</v>
+        <v>26119.54</v>
       </c>
       <c r="E45" t="n">
-        <v>26338.61</v>
+        <v>26128.36</v>
       </c>
       <c r="F45" t="n">
-        <v>-101.7</v>
+        <v>-210.25</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.008</v>
       </c>
       <c r="H45" t="n">
-        <v>154.89</v>
+        <v>173.41</v>
       </c>
       <c r="I45" t="n">
-        <v>26268.56</v>
+        <v>26183.72</v>
       </c>
       <c r="J45" t="n">
-        <v>26287.5</v>
+        <v>26145</v>
       </c>
       <c r="K45" t="n">
-        <v>26372.12</v>
+        <v>26261.16</v>
       </c>
       <c r="L45" t="n">
-        <v>26456.73</v>
+        <v>26377.33</v>
       </c>
       <c r="M45" t="n">
-        <v>26508.51</v>
+        <v>26416.05</v>
       </c>
       <c r="N45" t="n">
-        <v>26560.28</v>
+        <v>26454.78</v>
       </c>
       <c r="O45" t="n">
-        <v>26677.73</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
+        <v>26648.39</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4300,81 +4301,73 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W45" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>26280.86</v>
+        <v>26146.12</v>
       </c>
       <c r="C46" t="n">
-        <v>26292.95</v>
+        <v>26187.82</v>
       </c>
       <c r="D46" t="n">
-        <v>26119.54</v>
+        <v>26063.37</v>
       </c>
       <c r="E46" t="n">
-        <v>26128.36</v>
+        <v>26091.33</v>
       </c>
       <c r="F46" t="n">
-        <v>-210.25</v>
+        <v>-37.03</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0014</v>
       </c>
       <c r="H46" t="n">
-        <v>173.41</v>
+        <v>124.45</v>
       </c>
       <c r="I46" t="n">
-        <v>26183.72</v>
+        <v>25946.13</v>
       </c>
       <c r="J46" t="n">
-        <v>26145</v>
+        <v>25916.01</v>
       </c>
       <c r="K46" t="n">
-        <v>26261.16</v>
+        <v>26041.65</v>
       </c>
       <c r="L46" t="n">
-        <v>26377.33</v>
+        <v>26167.3</v>
       </c>
       <c r="M46" t="n">
-        <v>26416.05</v>
+        <v>26215.06</v>
       </c>
       <c r="N46" t="n">
-        <v>26454.78</v>
+        <v>26262.83</v>
       </c>
       <c r="O46" t="n">
-        <v>26648.39</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
+        <v>26466.36</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4398,63 +4391,67 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>26146.12</v>
+        <v>26050.95</v>
       </c>
       <c r="C47" t="n">
-        <v>26187.82</v>
+        <v>26062.15</v>
       </c>
       <c r="D47" t="n">
-        <v>26063.37</v>
+        <v>25914.11</v>
       </c>
       <c r="E47" t="n">
-        <v>26091.33</v>
+        <v>25983.04</v>
       </c>
       <c r="F47" t="n">
-        <v>-37.03</v>
+        <v>-108.29</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0042</v>
       </c>
       <c r="H47" t="n">
-        <v>124.45</v>
+        <v>148.04</v>
       </c>
       <c r="I47" t="n">
-        <v>25946.13</v>
+        <v>25938.92</v>
       </c>
       <c r="J47" t="n">
-        <v>25916.01</v>
+        <v>25949.75</v>
       </c>
       <c r="K47" t="n">
-        <v>26041.65</v>
+        <v>26029.1</v>
       </c>
       <c r="L47" t="n">
-        <v>26167.3</v>
+        <v>26108.46</v>
       </c>
       <c r="M47" t="n">
-        <v>26215.06</v>
+        <v>26153.56</v>
       </c>
       <c r="N47" t="n">
-        <v>26262.83</v>
+        <v>26198.65</v>
       </c>
       <c r="O47" t="n">
-        <v>26466.36</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
+        <v>26312.27</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4478,83 +4475,81 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>26050.95</v>
+        <v>25998.95</v>
       </c>
       <c r="C48" t="n">
-        <v>26062.15</v>
+        <v>26166.25</v>
       </c>
       <c r="D48" t="n">
-        <v>25914.11</v>
+        <v>25969.52</v>
       </c>
       <c r="E48" t="n">
-        <v>25983.04</v>
+        <v>26136.56</v>
       </c>
       <c r="F48" t="n">
-        <v>-108.29</v>
+        <v>153.52</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.0059</v>
       </c>
       <c r="H48" t="n">
-        <v>148.04</v>
+        <v>196.73</v>
       </c>
       <c r="I48" t="n">
-        <v>25938.92</v>
+        <v>25766.07</v>
       </c>
       <c r="J48" t="n">
-        <v>25949.75</v>
+        <v>25832.45</v>
       </c>
       <c r="K48" t="n">
-        <v>26029.1</v>
+        <v>25909.02</v>
       </c>
       <c r="L48" t="n">
-        <v>26108.46</v>
+        <v>25985.58</v>
       </c>
       <c r="M48" t="n">
-        <v>26153.56</v>
+        <v>26057.06</v>
       </c>
       <c r="N48" t="n">
-        <v>26198.65</v>
+        <v>26128.53</v>
       </c>
       <c r="O48" t="n">
-        <v>26312.27</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
+        <v>26210.19</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W48" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr"/>
@@ -4562,50 +4557,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25998.95</v>
+        <v>26091.29</v>
       </c>
       <c r="C49" t="n">
-        <v>26166.25</v>
+        <v>26171.7</v>
       </c>
       <c r="D49" t="n">
-        <v>25969.52</v>
+        <v>26038.07</v>
       </c>
       <c r="E49" t="n">
-        <v>26136.56</v>
+        <v>26106.6</v>
       </c>
       <c r="F49" t="n">
-        <v>153.52</v>
+        <v>-29.96</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0011</v>
       </c>
       <c r="H49" t="n">
-        <v>196.73</v>
+        <v>133.63</v>
       </c>
       <c r="I49" t="n">
-        <v>25766.07</v>
+        <v>25772.79</v>
       </c>
       <c r="J49" t="n">
-        <v>25832.45</v>
+        <v>25974.17</v>
       </c>
       <c r="K49" t="n">
-        <v>25909.02</v>
+        <v>26038.2</v>
       </c>
       <c r="L49" t="n">
-        <v>25985.58</v>
+        <v>26102.22</v>
       </c>
       <c r="M49" t="n">
-        <v>26057.06</v>
+        <v>26234.93</v>
       </c>
       <c r="N49" t="n">
-        <v>26128.53</v>
+        <v>26367.63</v>
       </c>
       <c r="O49" t="n">
-        <v>26210.19</v>
+        <v>26362.98</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4613,23 +4608,21 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4639,55 +4632,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>26091.29</v>
+        <v>26206.01</v>
       </c>
       <c r="C50" t="n">
-        <v>26171.7</v>
+        <v>26341.52</v>
       </c>
       <c r="D50" t="n">
-        <v>26038.07</v>
+        <v>26164.11</v>
       </c>
       <c r="E50" t="n">
-        <v>26106.6</v>
+        <v>26266.14</v>
       </c>
       <c r="F50" t="n">
-        <v>-29.96</v>
+        <v>159.54</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0061</v>
       </c>
       <c r="H50" t="n">
-        <v>133.63</v>
+        <v>177.41</v>
       </c>
       <c r="I50" t="n">
-        <v>25772.79</v>
+        <v>25904.44</v>
       </c>
       <c r="J50" t="n">
-        <v>25974.17</v>
+        <v>25973.83</v>
       </c>
       <c r="K50" t="n">
-        <v>26038.2</v>
+        <v>26039.79</v>
       </c>
       <c r="L50" t="n">
-        <v>26102.22</v>
+        <v>26105.74</v>
       </c>
       <c r="M50" t="n">
-        <v>26234.93</v>
+        <v>26173.41</v>
       </c>
       <c r="N50" t="n">
-        <v>26367.63</v>
+        <v>26241.09</v>
       </c>
       <c r="O50" t="n">
-        <v>26362.98</v>
+        <v>26305.33</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4695,83 +4692,83 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v/>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>26206.01</v>
+        <v>26255.41</v>
       </c>
       <c r="C51" t="n">
-        <v>26341.52</v>
+        <v>26466.76</v>
       </c>
       <c r="D51" t="n">
-        <v>26164.11</v>
+        <v>26196.92</v>
       </c>
       <c r="E51" t="n">
-        <v>26266.14</v>
+        <v>26285.96</v>
       </c>
       <c r="F51" t="n">
-        <v>159.54</v>
+        <v>19.82</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0061</v>
+        <v>0.0008</v>
       </c>
       <c r="H51" t="n">
-        <v>177.41</v>
+        <v>269.84</v>
       </c>
       <c r="I51" t="n">
-        <v>25904.44</v>
+        <v>25986.7</v>
       </c>
       <c r="J51" t="n">
-        <v>25973.83</v>
+        <v>26095.39</v>
       </c>
       <c r="K51" t="n">
-        <v>26039.79</v>
+        <v>26177.44</v>
       </c>
       <c r="L51" t="n">
-        <v>26105.74</v>
+        <v>26259.48</v>
       </c>
       <c r="M51" t="n">
-        <v>26173.41</v>
+        <v>26354.85</v>
       </c>
       <c r="N51" t="n">
-        <v>26241.09</v>
+        <v>26450.21</v>
       </c>
       <c r="O51" t="n">
-        <v>26305.33</v>
+        <v>26518.93</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4782,9 +4779,9 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
@@ -4794,13 +4791,11 @@
       </c>
       <c r="U51" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
@@ -4812,50 +4807,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>26255.41</v>
+        <v>26354.37</v>
       </c>
       <c r="C52" t="n">
-        <v>26466.76</v>
+        <v>26402.81</v>
       </c>
       <c r="D52" t="n">
-        <v>26196.92</v>
+        <v>26241.77</v>
       </c>
       <c r="E52" t="n">
-        <v>26285.96</v>
+        <v>26367.24</v>
       </c>
       <c r="F52" t="n">
-        <v>19.82</v>
+        <v>81.28</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0031</v>
       </c>
       <c r="H52" t="n">
-        <v>269.84</v>
+        <v>161.04</v>
       </c>
       <c r="I52" t="n">
-        <v>25986.7</v>
+        <v>25927.08</v>
       </c>
       <c r="J52" t="n">
-        <v>26095.39</v>
+        <v>25993.18</v>
       </c>
       <c r="K52" t="n">
-        <v>26177.44</v>
+        <v>26151.04</v>
       </c>
       <c r="L52" t="n">
-        <v>26259.48</v>
+        <v>26308.9</v>
       </c>
       <c r="M52" t="n">
-        <v>26354.85</v>
+        <v>26420.88</v>
       </c>
       <c r="N52" t="n">
-        <v>26450.21</v>
+        <v>26532.86</v>
       </c>
       <c r="O52" t="n">
-        <v>26518.93</v>
+        <v>26736.6</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4866,20 +4861,18 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4889,55 +4882,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>26354.37</v>
+        <v>26494.61</v>
       </c>
       <c r="C53" t="n">
-        <v>26402.81</v>
+        <v>26618.74</v>
       </c>
       <c r="D53" t="n">
-        <v>26241.77</v>
+        <v>26467.36</v>
       </c>
       <c r="E53" t="n">
-        <v>26367.24</v>
+        <v>26569.99</v>
       </c>
       <c r="F53" t="n">
-        <v>81.28</v>
+        <v>202.75</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0077</v>
       </c>
       <c r="H53" t="n">
-        <v>161.04</v>
+        <v>151.38</v>
       </c>
       <c r="I53" t="n">
-        <v>25927.08</v>
+        <v>26080.73</v>
       </c>
       <c r="J53" t="n">
-        <v>25993.18</v>
+        <v>26228.67</v>
       </c>
       <c r="K53" t="n">
-        <v>26151.04</v>
+        <v>26286.72</v>
       </c>
       <c r="L53" t="n">
-        <v>26308.9</v>
+        <v>26344.77</v>
       </c>
       <c r="M53" t="n">
-        <v>26420.88</v>
+        <v>26447.76</v>
       </c>
       <c r="N53" t="n">
-        <v>26532.86</v>
+        <v>26550.76</v>
       </c>
       <c r="O53" t="n">
-        <v>26736.6</v>
+        <v>26563.85</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4948,113 +4945,113 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
-      </c>
       <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>26494.61</v>
+        <v>26464.14</v>
       </c>
       <c r="C54" t="n">
-        <v>26618.74</v>
+        <v>26471.79</v>
       </c>
       <c r="D54" t="n">
-        <v>26467.36</v>
+        <v>26249.59</v>
       </c>
       <c r="E54" t="n">
-        <v>26569.99</v>
+        <v>26258.11</v>
       </c>
       <c r="F54" t="n">
-        <v>202.75</v>
+        <v>-311.88</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0117</v>
       </c>
       <c r="H54" t="n">
-        <v>151.38</v>
+        <v>222.2</v>
       </c>
       <c r="I54" t="n">
-        <v>26080.73</v>
+        <v>26315.98</v>
       </c>
       <c r="J54" t="n">
-        <v>26228.67</v>
+        <v>26432.08</v>
       </c>
       <c r="K54" t="n">
-        <v>26286.72</v>
+        <v>26494.3</v>
       </c>
       <c r="L54" t="n">
-        <v>26344.77</v>
+        <v>26556.52</v>
       </c>
       <c r="M54" t="n">
-        <v>26447.76</v>
+        <v>26645.68</v>
       </c>
       <c r="N54" t="n">
-        <v>26550.76</v>
+        <v>26734.84</v>
       </c>
       <c r="O54" t="n">
-        <v>26563.85</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+        <v>26770.12</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W54" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W54" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X54" t="inlineStr"/>
@@ -5062,67 +5059,67 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>26464.14</v>
+        <v>26150.75</v>
       </c>
       <c r="C55" t="n">
-        <v>26471.79</v>
+        <v>26206.13</v>
       </c>
       <c r="D55" t="n">
-        <v>26249.59</v>
+        <v>25916.76</v>
       </c>
       <c r="E55" t="n">
-        <v>26258.11</v>
+        <v>25970.11</v>
       </c>
       <c r="F55" t="n">
-        <v>-311.88</v>
+        <v>-288</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.011</v>
       </c>
       <c r="H55" t="n">
-        <v>222.2</v>
+        <v>289.37</v>
       </c>
       <c r="I55" t="n">
-        <v>26315.98</v>
+        <v>26027.39</v>
       </c>
       <c r="J55" t="n">
-        <v>26432.08</v>
+        <v>25984.62</v>
       </c>
       <c r="K55" t="n">
-        <v>26494.3</v>
+        <v>26147.01</v>
       </c>
       <c r="L55" t="n">
-        <v>26556.52</v>
+        <v>26309.4</v>
       </c>
       <c r="M55" t="n">
-        <v>26645.68</v>
+        <v>26369.21</v>
       </c>
       <c r="N55" t="n">
-        <v>26734.84</v>
+        <v>26429.02</v>
       </c>
       <c r="O55" t="n">
-        <v>26770.12</v>
+        <v>26693.99</v>
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5146,67 +5143,63 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>26150.75</v>
+        <v>25886.67</v>
       </c>
       <c r="C56" t="n">
-        <v>26206.13</v>
+        <v>25924.21</v>
       </c>
       <c r="D56" t="n">
-        <v>25916.76</v>
+        <v>25727.93</v>
       </c>
       <c r="E56" t="n">
-        <v>25970.11</v>
+        <v>25839.33</v>
       </c>
       <c r="F56" t="n">
-        <v>-288</v>
+        <v>-130.78</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.005</v>
       </c>
       <c r="H56" t="n">
-        <v>289.37</v>
+        <v>196.28</v>
       </c>
       <c r="I56" t="n">
-        <v>26027.39</v>
+        <v>25627.39</v>
       </c>
       <c r="J56" t="n">
-        <v>25984.62</v>
+        <v>25635.07</v>
       </c>
       <c r="K56" t="n">
-        <v>26147.01</v>
+        <v>25825.42</v>
       </c>
       <c r="L56" t="n">
-        <v>26309.4</v>
+        <v>26015.78</v>
       </c>
       <c r="M56" t="n">
-        <v>26369.21</v>
+        <v>26114.79</v>
       </c>
       <c r="N56" t="n">
-        <v>26429.02</v>
+        <v>26213.81</v>
       </c>
       <c r="O56" t="n">
-        <v>26693.99</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q56" s="6" t="inlineStr">
+        <v>26495.5</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5230,50 +5223,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25886.67</v>
+        <v>25840.92</v>
       </c>
       <c r="C57" t="n">
-        <v>25924.21</v>
+        <v>26007.79</v>
       </c>
       <c r="D57" t="n">
-        <v>25727.93</v>
+        <v>25784.84</v>
       </c>
       <c r="E57" t="n">
-        <v>25839.33</v>
+        <v>26003.32</v>
       </c>
       <c r="F57" t="n">
-        <v>-130.78</v>
+        <v>163.99</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0063</v>
       </c>
       <c r="H57" t="n">
-        <v>196.28</v>
+        <v>222.95</v>
       </c>
       <c r="I57" t="n">
-        <v>25627.39</v>
+        <v>25531.65</v>
       </c>
       <c r="J57" t="n">
-        <v>25635.07</v>
+        <v>25649.68</v>
       </c>
       <c r="K57" t="n">
-        <v>25825.42</v>
+        <v>25741.19</v>
       </c>
       <c r="L57" t="n">
-        <v>26015.78</v>
+        <v>25832.7</v>
       </c>
       <c r="M57" t="n">
-        <v>26114.79</v>
+        <v>25937.47</v>
       </c>
       <c r="N57" t="n">
-        <v>26213.81</v>
+        <v>26042.24</v>
       </c>
       <c r="O57" t="n">
-        <v>26495.5</v>
+        <v>26120.49</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5281,22 +5274,24 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
@@ -5305,55 +5300,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>25840.92</v>
+        <v>25985.86</v>
       </c>
       <c r="C58" t="n">
-        <v>26007.79</v>
+        <v>26167.93</v>
       </c>
       <c r="D58" t="n">
-        <v>25784.84</v>
+        <v>25958.7</v>
       </c>
       <c r="E58" t="n">
-        <v>26003.32</v>
+        <v>26046.4</v>
       </c>
       <c r="F58" t="n">
-        <v>163.99</v>
+        <v>43.08</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0017</v>
       </c>
       <c r="H58" t="n">
-        <v>222.95</v>
+        <v>209.23</v>
       </c>
       <c r="I58" t="n">
-        <v>25531.65</v>
+        <v>25561.89</v>
       </c>
       <c r="J58" t="n">
-        <v>25649.68</v>
+        <v>25833.87</v>
       </c>
       <c r="K58" t="n">
-        <v>25741.19</v>
+        <v>25891.85</v>
       </c>
       <c r="L58" t="n">
-        <v>25832.7</v>
+        <v>25949.82</v>
       </c>
       <c r="M58" t="n">
-        <v>25937.47</v>
+        <v>26114.79</v>
       </c>
       <c r="N58" t="n">
-        <v>26042.24</v>
+        <v>26279.77</v>
       </c>
       <c r="O58" t="n">
-        <v>26120.49</v>
+        <v>26230.74</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5364,20 +5363,18 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
+      <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5396,50 +5393,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25985.86</v>
+        <v>26039.54</v>
       </c>
       <c r="C59" t="n">
-        <v>26167.93</v>
+        <v>26069.99</v>
       </c>
       <c r="D59" t="n">
-        <v>25958.7</v>
+        <v>25919.61</v>
       </c>
       <c r="E59" t="n">
-        <v>26046.4</v>
+        <v>26006.53</v>
       </c>
       <c r="F59" t="n">
-        <v>43.08</v>
+        <v>-39.87</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0015</v>
       </c>
       <c r="H59" t="n">
-        <v>209.23</v>
+        <v>150.38</v>
       </c>
       <c r="I59" t="n">
-        <v>25561.89</v>
+        <v>25749.47</v>
       </c>
       <c r="J59" t="n">
-        <v>25833.87</v>
+        <v>25828.71</v>
       </c>
       <c r="K59" t="n">
-        <v>25891.85</v>
+        <v>25941.79</v>
       </c>
       <c r="L59" t="n">
-        <v>25949.82</v>
+        <v>26054.86</v>
       </c>
       <c r="M59" t="n">
-        <v>26114.79</v>
+        <v>26151.02</v>
       </c>
       <c r="N59" t="n">
-        <v>26279.77</v>
+        <v>26247.17</v>
       </c>
       <c r="O59" t="n">
-        <v>26230.74</v>
+        <v>26377.16</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5447,18 +5444,18 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5471,65 +5468,63 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>26039.54</v>
+        <v>25897.22</v>
       </c>
       <c r="C60" t="n">
-        <v>26069.99</v>
+        <v>26026.78</v>
       </c>
       <c r="D60" t="n">
-        <v>25919.61</v>
+        <v>25799.66</v>
       </c>
       <c r="E60" t="n">
-        <v>26006.53</v>
+        <v>26007.63</v>
       </c>
       <c r="F60" t="n">
-        <v>-39.87</v>
+        <v>1.1</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>150.38</v>
+        <v>227.12</v>
       </c>
       <c r="I60" t="n">
-        <v>25749.47</v>
+        <v>25769.23</v>
       </c>
       <c r="J60" t="n">
-        <v>25828.71</v>
+        <v>25862.01</v>
       </c>
       <c r="K60" t="n">
-        <v>25941.79</v>
+        <v>25931.34</v>
       </c>
       <c r="L60" t="n">
-        <v>26054.86</v>
+        <v>26000.66</v>
       </c>
       <c r="M60" t="n">
-        <v>26151.02</v>
+        <v>26081.72</v>
       </c>
       <c r="N60" t="n">
-        <v>26247.17</v>
+        <v>26162.77</v>
       </c>
       <c r="O60" t="n">
-        <v>26377.16</v>
+        <v>26220.37</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
@@ -5538,7 +5533,7 @@
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5555,58 +5550,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>25897.22</v>
+        <v>25870.98</v>
       </c>
       <c r="C61" t="n">
-        <v>26026.78</v>
+        <v>25909.66</v>
       </c>
       <c r="D61" t="n">
-        <v>25799.66</v>
+        <v>25512.39</v>
       </c>
       <c r="E61" t="n">
-        <v>26007.63</v>
+        <v>25576.45</v>
       </c>
       <c r="F61" t="n">
-        <v>1.1</v>
+        <v>-431.18</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0</v>
+        <v>-0.0166</v>
       </c>
       <c r="H61" t="n">
-        <v>227.12</v>
+        <v>397.27</v>
       </c>
       <c r="I61" t="n">
-        <v>25769.23</v>
+        <v>25572.54</v>
       </c>
       <c r="J61" t="n">
-        <v>25862.01</v>
+        <v>25827.72</v>
       </c>
       <c r="K61" t="n">
-        <v>25931.34</v>
+        <v>25894.07</v>
       </c>
       <c r="L61" t="n">
-        <v>26000.66</v>
+        <v>25960.43</v>
       </c>
       <c r="M61" t="n">
-        <v>26081.72</v>
+        <v>26121.19</v>
       </c>
       <c r="N61" t="n">
-        <v>26162.77</v>
+        <v>26281.96</v>
       </c>
       <c r="O61" t="n">
-        <v>26220.37</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
+        <v>26253.9</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q61" s="6" t="inlineStr">
         <is>
@@ -5620,7 +5621,7 @@
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5637,76 +5638,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>25870.98</v>
+        <v>25555.66</v>
       </c>
       <c r="C62" t="n">
-        <v>25909.66</v>
+        <v>25612.09</v>
       </c>
       <c r="D62" t="n">
-        <v>25512.39</v>
+        <v>25361.15</v>
       </c>
       <c r="E62" t="n">
-        <v>25576.45</v>
+        <v>25361.15</v>
       </c>
       <c r="F62" t="n">
-        <v>-431.18</v>
+        <v>-215.3</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>397.27</v>
+        <v>250.94</v>
       </c>
       <c r="I62" t="n">
-        <v>25572.54</v>
+        <v>25115.12</v>
       </c>
       <c r="J62" t="n">
-        <v>25827.72</v>
+        <v>25111.89</v>
       </c>
       <c r="K62" t="n">
-        <v>25894.07</v>
+        <v>25377.81</v>
       </c>
       <c r="L62" t="n">
-        <v>25960.43</v>
+        <v>25643.74</v>
       </c>
       <c r="M62" t="n">
-        <v>26121.19</v>
+        <v>25775.08</v>
       </c>
       <c r="N62" t="n">
-        <v>26281.96</v>
+        <v>25906.43</v>
       </c>
       <c r="O62" t="n">
-        <v>26253.9</v>
-      </c>
-      <c r="P62" s="6" t="inlineStr">
+        <v>26306.93</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
+      <c r="S62" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5730,50 +5723,50 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>25555.66</v>
+        <v>25478.84</v>
       </c>
       <c r="C63" t="n">
-        <v>25612.09</v>
+        <v>25581.22</v>
       </c>
       <c r="D63" t="n">
-        <v>25361.15</v>
+        <v>25396.38</v>
       </c>
       <c r="E63" t="n">
-        <v>25361.15</v>
+        <v>25568.56</v>
       </c>
       <c r="F63" t="n">
-        <v>-215.3</v>
+        <v>207.41</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H63" t="n">
-        <v>250.94</v>
+        <v>184.84</v>
       </c>
       <c r="I63" t="n">
-        <v>25115.12</v>
+        <v>25110.21</v>
       </c>
       <c r="J63" t="n">
-        <v>25111.89</v>
+        <v>25047.48</v>
       </c>
       <c r="K63" t="n">
-        <v>25377.81</v>
+        <v>25235.68</v>
       </c>
       <c r="L63" t="n">
-        <v>25643.74</v>
+        <v>25423.89</v>
       </c>
       <c r="M63" t="n">
-        <v>25775.08</v>
+        <v>25486.62</v>
       </c>
       <c r="N63" t="n">
-        <v>25906.43</v>
+        <v>25549.35</v>
       </c>
       <c r="O63" t="n">
-        <v>26306.93</v>
+        <v>25863.03</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5781,103 +5774,109 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="inlineStr">
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
       <c r="V63" s="8" t="n">
         <v/>
       </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>25478.84</v>
+        <v>25498.74</v>
       </c>
       <c r="C64" t="n">
-        <v>25581.22</v>
+        <v>25548.78</v>
       </c>
       <c r="D64" t="n">
-        <v>25396.38</v>
+        <v>25325.52</v>
       </c>
       <c r="E64" t="n">
-        <v>25568.56</v>
+        <v>25440.81</v>
       </c>
       <c r="F64" t="n">
-        <v>207.41</v>
+        <v>-127.75</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.005</v>
       </c>
       <c r="H64" t="n">
-        <v>184.84</v>
+        <v>223.26</v>
       </c>
       <c r="I64" t="n">
-        <v>25110.21</v>
+        <v>25211.54</v>
       </c>
       <c r="J64" t="n">
-        <v>25047.48</v>
+        <v>25423.6</v>
       </c>
       <c r="K64" t="n">
-        <v>25235.68</v>
+        <v>25476.14</v>
       </c>
       <c r="L64" t="n">
-        <v>25423.89</v>
+        <v>25528.68</v>
       </c>
       <c r="M64" t="n">
-        <v>25486.62</v>
+        <v>25660.98</v>
       </c>
       <c r="N64" t="n">
-        <v>25549.35</v>
+        <v>25793.28</v>
       </c>
       <c r="O64" t="n">
-        <v>25863.03</v>
+        <v>25766.06</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
       </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R64" s="6" t="n">
-        <v/>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S64" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
       </c>
       <c r="V64" s="8" t="n">
         <v/>
@@ -5889,123 +5888,35 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>25498.74</v>
-      </c>
-      <c r="C65" t="n">
-        <v>25548.78</v>
-      </c>
-      <c r="D65" t="n">
-        <v>25325.52</v>
-      </c>
-      <c r="E65" t="n">
-        <v/>
-      </c>
-      <c r="F65" t="n">
-        <v/>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H65" t="n">
-        <v>223.26</v>
-      </c>
-      <c r="I65" t="n">
-        <v>25211.54</v>
-      </c>
-      <c r="J65" t="n">
-        <v>25423.6</v>
-      </c>
-      <c r="K65" t="n">
-        <v>25476.14</v>
-      </c>
-      <c r="L65" t="n">
-        <v>25528.68</v>
-      </c>
-      <c r="M65" t="n">
-        <v>25660.98</v>
-      </c>
-      <c r="N65" t="n">
-        <v>25793.28</v>
-      </c>
-      <c r="O65" t="n">
-        <v>25766.06</v>
-      </c>
-      <c r="P65" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q65" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R65" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S65" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W65" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="13" t="inlineStr">
+      <c r="A65" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I66" s="14" t="n">
+      <c r="I65" s="13" t="n">
         <v>25102.26</v>
       </c>
-      <c r="J66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O66" s="14" t="n">
+      <c r="J65" s="13" t="n">
+        <v>25219.38</v>
+      </c>
+      <c r="K65" s="13" t="n">
+        <v>25329.18</v>
+      </c>
+      <c r="L65" s="13" t="n">
+        <v>25438.98</v>
+      </c>
+      <c r="M65" s="13" t="n">
+        <v>25552.44</v>
+      </c>
+      <c r="N65" s="13" t="n">
+        <v>25665.9</v>
+      </c>
+      <c r="O65" s="13" t="n">
         <v>25772.04</v>
       </c>
     </row>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -487,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X65"/>
+  <dimension ref="A1:X66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5893,31 +5896,119 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>25360.32</v>
+      </c>
+      <c r="C65" t="n">
+        <v>25478.98</v>
+      </c>
+      <c r="D65" t="n">
+        <v>25172.89</v>
+      </c>
+      <c r="E65" t="n">
+        <v/>
+      </c>
+      <c r="F65" t="n">
+        <v/>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H65" t="n">
+        <v>306.09</v>
+      </c>
+      <c r="I65" t="n">
+        <v>25102.26</v>
+      </c>
+      <c r="J65" t="n">
+        <v>25219.38</v>
+      </c>
+      <c r="K65" t="n">
+        <v>25329.18</v>
+      </c>
+      <c r="L65" t="n">
+        <v>25438.98</v>
+      </c>
+      <c r="M65" t="n">
+        <v>25552.44</v>
+      </c>
+      <c r="N65" t="n">
+        <v>25665.9</v>
+      </c>
+      <c r="O65" t="n">
+        <v>25772.04</v>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q65" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S65" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W65" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I65" s="13" t="n">
-        <v>25102.26</v>
-      </c>
-      <c r="J65" s="13" t="n">
-        <v>25219.38</v>
-      </c>
-      <c r="K65" s="13" t="n">
-        <v>25329.18</v>
-      </c>
-      <c r="L65" s="13" t="n">
-        <v>25438.98</v>
-      </c>
-      <c r="M65" s="13" t="n">
-        <v>25552.44</v>
-      </c>
-      <c r="N65" s="13" t="n">
-        <v>25665.9</v>
-      </c>
-      <c r="O65" s="13" t="n">
-        <v>25772.04</v>
+      <c r="I66" s="14" t="n">
+        <v>24866.8</v>
+      </c>
+      <c r="J66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O66" s="14" t="n">
+        <v>25785.07</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -109,14 +109,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X66"/>
+  <dimension ref="A1:X65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -644,50 +644,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24996.54</v>
+        <v>25075.33</v>
       </c>
       <c r="C2" t="n">
-        <v>25059.37</v>
+        <v>25173.02</v>
       </c>
       <c r="D2" t="n">
-        <v>24840.27</v>
+        <v>24951.54</v>
       </c>
       <c r="E2" t="n">
-        <v>25026.8</v>
+        <v>24985.82</v>
       </c>
       <c r="F2" t="n">
-        <v>92.13</v>
+        <v>-40.98</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0016</v>
       </c>
       <c r="H2" t="n">
-        <v>219.1</v>
+        <v>221.48</v>
       </c>
       <c r="I2" t="n">
-        <v>24570.58</v>
+        <v>24621.17</v>
       </c>
       <c r="J2" t="n">
-        <v>24779.05</v>
+        <v>24846.19</v>
       </c>
       <c r="K2" t="n">
-        <v>24838.19</v>
+        <v>24917.25</v>
       </c>
       <c r="L2" t="n">
-        <v>24897.34</v>
+        <v>24988.31</v>
       </c>
       <c r="M2" t="n">
-        <v>25031.15</v>
+        <v>25136.35</v>
       </c>
       <c r="N2" t="n">
-        <v>25164.95</v>
+        <v>25284.39</v>
       </c>
       <c r="O2" t="n">
-        <v>25149.43</v>
+        <v>25278.47</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -700,12 +700,12 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U2" s="8" t="n">
@@ -719,55 +719,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25075.33</v>
+        <v>25035.93</v>
       </c>
       <c r="C3" t="n">
-        <v>25173.02</v>
+        <v>25176.21</v>
       </c>
       <c r="D3" t="n">
-        <v>24951.54</v>
+        <v>24896.19</v>
       </c>
       <c r="E3" t="n">
-        <v>24985.82</v>
+        <v>25139.69</v>
       </c>
       <c r="F3" t="n">
-        <v>-40.98</v>
+        <v>153.87</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0062</v>
       </c>
       <c r="H3" t="n">
-        <v>221.48</v>
+        <v>280.02</v>
       </c>
       <c r="I3" t="n">
-        <v>24621.17</v>
+        <v>24730.06</v>
       </c>
       <c r="J3" t="n">
-        <v>24846.19</v>
+        <v>24726.11</v>
       </c>
       <c r="K3" t="n">
-        <v>24917.25</v>
+        <v>24875.08</v>
       </c>
       <c r="L3" t="n">
-        <v>24988.31</v>
+        <v>25024.05</v>
       </c>
       <c r="M3" t="n">
-        <v>25136.35</v>
+        <v>25096.56</v>
       </c>
       <c r="N3" t="n">
-        <v>25284.39</v>
+        <v>25169.07</v>
       </c>
       <c r="O3" t="n">
-        <v>25278.47</v>
+        <v>25394.5</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -780,7 +784,7 @@
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
@@ -788,8 +792,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U3" s="8" t="n">
-        <v/>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -808,151 +814,147 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25035.93</v>
+        <v>24835.56</v>
       </c>
       <c r="C4" t="n">
-        <v>25176.21</v>
+        <v>24988.71</v>
       </c>
       <c r="D4" t="n">
-        <v>24896.19</v>
+        <v>24728.57</v>
       </c>
       <c r="E4" t="n">
-        <v>25139.69</v>
+        <v>24893.58</v>
       </c>
       <c r="F4" t="n">
-        <v>153.87</v>
+        <v>-246.11</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0098</v>
       </c>
       <c r="H4" t="n">
-        <v>280.02</v>
+        <v>260.14</v>
       </c>
       <c r="I4" t="n">
-        <v>24730.06</v>
+        <v>24616.17</v>
       </c>
       <c r="J4" t="n">
-        <v>24726.11</v>
+        <v>24911.41</v>
       </c>
       <c r="K4" t="n">
-        <v>24875.08</v>
+        <v>24999.68</v>
       </c>
       <c r="L4" t="n">
-        <v>25024.05</v>
+        <v>25087.94</v>
       </c>
       <c r="M4" t="n">
-        <v>25096.56</v>
+        <v>25279.7</v>
       </c>
       <c r="N4" t="n">
-        <v>25169.07</v>
+        <v>25471.46</v>
       </c>
       <c r="O4" t="n">
-        <v>25394.5</v>
+        <v>25456.23</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24835.56</v>
+        <v>24790.7</v>
       </c>
       <c r="C5" t="n">
-        <v>24988.71</v>
+        <v>24800.66</v>
       </c>
       <c r="D5" t="n">
-        <v>24728.57</v>
+        <v>24593.48</v>
       </c>
       <c r="E5" t="n">
-        <v>24893.58</v>
+        <v>24740.36</v>
       </c>
       <c r="F5" t="n">
-        <v>-246.11</v>
+        <v>-153.22</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0062</v>
       </c>
       <c r="H5" t="n">
-        <v>260.14</v>
+        <v>207.18</v>
       </c>
       <c r="I5" t="n">
-        <v>24616.17</v>
+        <v>24468.43</v>
       </c>
       <c r="J5" t="n">
-        <v>24911.41</v>
+        <v>24650.91</v>
       </c>
       <c r="K5" t="n">
-        <v>24999.68</v>
+        <v>24763.51</v>
       </c>
       <c r="L5" t="n">
-        <v>25087.94</v>
+        <v>24876.11</v>
       </c>
       <c r="M5" t="n">
-        <v>25279.7</v>
+        <v>25023.65</v>
       </c>
       <c r="N5" t="n">
-        <v>25471.46</v>
+        <v>25171.19</v>
       </c>
       <c r="O5" t="n">
-        <v>25456.23</v>
+        <v>25248.85</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -976,81 +978,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24790.7</v>
+        <v>24810</v>
       </c>
       <c r="C6" t="n">
-        <v>24800.66</v>
+        <v>25088.28</v>
       </c>
       <c r="D6" t="n">
-        <v>24593.48</v>
+        <v>24761.72</v>
       </c>
       <c r="E6" t="n">
-        <v>24740.36</v>
+        <v>24994.83</v>
       </c>
       <c r="F6" t="n">
-        <v>-153.22</v>
+        <v>254.47</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0103</v>
       </c>
       <c r="H6" t="n">
-        <v>207.18</v>
+        <v>326.56</v>
       </c>
       <c r="I6" t="n">
-        <v>24468.43</v>
+        <v>24386.3</v>
       </c>
       <c r="J6" t="n">
-        <v>24650.91</v>
+        <v>24554.82</v>
       </c>
       <c r="K6" t="n">
-        <v>24763.51</v>
+        <v>24636.77</v>
       </c>
       <c r="L6" t="n">
-        <v>24876.11</v>
+        <v>24718.71</v>
       </c>
       <c r="M6" t="n">
-        <v>25023.65</v>
+        <v>24843.95</v>
       </c>
       <c r="N6" t="n">
-        <v>25171.19</v>
+        <v>24969.18</v>
       </c>
       <c r="O6" t="n">
-        <v>25248.85</v>
+        <v>25007.84</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W6" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W6" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1058,83 +1062,81 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24810</v>
+        <v>24848.51</v>
       </c>
       <c r="C7" t="n">
-        <v>25088.28</v>
+        <v>24869.63</v>
       </c>
       <c r="D7" t="n">
-        <v>24761.72</v>
+        <v>24547.7</v>
       </c>
       <c r="E7" t="n">
-        <v>24994.83</v>
+        <v>24671.22</v>
       </c>
       <c r="F7" t="n">
-        <v>254.47</v>
+        <v>-323.61</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.0129</v>
       </c>
       <c r="H7" t="n">
-        <v>326.56</v>
+        <v>321.93</v>
       </c>
       <c r="I7" t="n">
-        <v>24386.3</v>
+        <v>24435.16</v>
       </c>
       <c r="J7" t="n">
-        <v>24554.82</v>
+        <v>24703.19</v>
       </c>
       <c r="K7" t="n">
-        <v>24636.77</v>
+        <v>24831.55</v>
       </c>
       <c r="L7" t="n">
-        <v>24718.71</v>
+        <v>24959.92</v>
       </c>
       <c r="M7" t="n">
-        <v>24843.95</v>
+        <v>25158.11</v>
       </c>
       <c r="N7" t="n">
-        <v>24969.18</v>
+        <v>25356.3</v>
       </c>
       <c r="O7" t="n">
-        <v>25007.84</v>
+        <v>25414.84</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W7" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W7" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
@@ -1142,67 +1144,63 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24848.51</v>
+        <v>24724.34</v>
       </c>
       <c r="C8" t="n">
-        <v>24869.63</v>
+        <v>24762.24</v>
       </c>
       <c r="D8" t="n">
-        <v>24547.7</v>
+        <v>24556.78</v>
       </c>
       <c r="E8" t="n">
-        <v>24671.22</v>
+        <v>24626.89</v>
       </c>
       <c r="F8" t="n">
-        <v>-323.61</v>
+        <v>-44.33</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0018</v>
       </c>
       <c r="H8" t="n">
-        <v>321.93</v>
+        <v>205.46</v>
       </c>
       <c r="I8" t="n">
-        <v>24435.16</v>
+        <v>24225.77</v>
       </c>
       <c r="J8" t="n">
-        <v>24703.19</v>
+        <v>24330.57</v>
       </c>
       <c r="K8" t="n">
-        <v>24831.55</v>
+        <v>24510.25</v>
       </c>
       <c r="L8" t="n">
-        <v>24959.92</v>
+        <v>24689.94</v>
       </c>
       <c r="M8" t="n">
-        <v>25158.11</v>
+        <v>24832.19</v>
       </c>
       <c r="N8" t="n">
-        <v>25356.3</v>
+        <v>24974.43</v>
       </c>
       <c r="O8" t="n">
-        <v>25414.84</v>
+        <v>25191.56</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1219,55 +1217,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24724.34</v>
+        <v>24815.22</v>
       </c>
       <c r="C9" t="n">
-        <v>24762.24</v>
+        <v>25024.27</v>
       </c>
       <c r="D9" t="n">
-        <v>24556.78</v>
+        <v>24794.84</v>
       </c>
       <c r="E9" t="n">
-        <v>24626.89</v>
+        <v>24995.81</v>
       </c>
       <c r="F9" t="n">
-        <v>-44.33</v>
+        <v>368.92</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.015</v>
       </c>
       <c r="H9" t="n">
-        <v>205.46</v>
+        <v>229.43</v>
       </c>
       <c r="I9" t="n">
-        <v>24225.77</v>
+        <v>24351.32</v>
       </c>
       <c r="J9" t="n">
-        <v>24330.57</v>
+        <v>24405.12</v>
       </c>
       <c r="K9" t="n">
-        <v>24510.25</v>
+        <v>24524.16</v>
       </c>
       <c r="L9" t="n">
-        <v>24689.94</v>
+        <v>24643.2</v>
       </c>
       <c r="M9" t="n">
-        <v>24832.19</v>
+        <v>24729.62</v>
       </c>
       <c r="N9" t="n">
-        <v>24974.43</v>
+        <v>24816.04</v>
       </c>
       <c r="O9" t="n">
-        <v>25191.56</v>
+        <v>24967.7</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1280,76 +1282,78 @@
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W9" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W9" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24815.22</v>
+        <v>25028.93</v>
       </c>
       <c r="C10" t="n">
-        <v>25024.27</v>
+        <v>25095.66</v>
       </c>
       <c r="D10" t="n">
-        <v>24794.84</v>
+        <v>24887</v>
       </c>
       <c r="E10" t="n">
-        <v>24995.81</v>
+        <v>25040.28</v>
       </c>
       <c r="F10" t="n">
-        <v>368.92</v>
+        <v>44.47</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.015</v>
+        <v>0.0018</v>
       </c>
       <c r="H10" t="n">
-        <v>229.43</v>
+        <v>208.66</v>
       </c>
       <c r="I10" t="n">
-        <v>24351.32</v>
+        <v>24565.41</v>
       </c>
       <c r="J10" t="n">
-        <v>24405.12</v>
+        <v>24809.51</v>
       </c>
       <c r="K10" t="n">
-        <v>24524.16</v>
+        <v>24881.1</v>
       </c>
       <c r="L10" t="n">
-        <v>24643.2</v>
+        <v>24952.68</v>
       </c>
       <c r="M10" t="n">
-        <v>24729.62</v>
+        <v>25110.53</v>
       </c>
       <c r="N10" t="n">
-        <v>24816.04</v>
+        <v>25268.37</v>
       </c>
       <c r="O10" t="n">
-        <v>24967.7</v>
+        <v>25253.7</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1360,25 +1364,21 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
@@ -1390,50 +1390,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25028.93</v>
+        <v>25025.13</v>
       </c>
       <c r="C11" t="n">
-        <v>25095.66</v>
+        <v>25655.82</v>
       </c>
       <c r="D11" t="n">
-        <v>24887</v>
+        <v>24994.64</v>
       </c>
       <c r="E11" t="n">
-        <v>25040.28</v>
+        <v>25580.88</v>
       </c>
       <c r="F11" t="n">
-        <v>44.47</v>
+        <v>540.6</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0216</v>
       </c>
       <c r="H11" t="n">
-        <v>208.66</v>
+        <v>661.1799999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>24565.41</v>
+        <v>24678.34</v>
       </c>
       <c r="J11" t="n">
-        <v>24809.51</v>
+        <v>24856.09</v>
       </c>
       <c r="K11" t="n">
-        <v>24881.1</v>
+        <v>24935.95</v>
       </c>
       <c r="L11" t="n">
-        <v>24952.68</v>
+        <v>25015.8</v>
       </c>
       <c r="M11" t="n">
-        <v>25110.53</v>
+        <v>25144.61</v>
       </c>
       <c r="N11" t="n">
-        <v>25268.37</v>
+        <v>25273.41</v>
       </c>
       <c r="O11" t="n">
-        <v>25253.7</v>
+        <v>25304.32</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1444,21 +1444,25 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v/>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
@@ -1470,50 +1474,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25025.13</v>
+        <v>25763.97</v>
       </c>
       <c r="C12" t="n">
-        <v>25655.82</v>
+        <v>25826.78</v>
       </c>
       <c r="D12" t="n">
-        <v>24994.64</v>
+        <v>25611.69</v>
       </c>
       <c r="E12" t="n">
-        <v>25580.88</v>
+        <v>25779.31</v>
       </c>
       <c r="F12" t="n">
-        <v>540.6</v>
+        <v>198.43</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0216</v>
+        <v>0.0078</v>
       </c>
       <c r="H12" t="n">
-        <v>661.1799999999999</v>
+        <v>215.09</v>
       </c>
       <c r="I12" t="n">
-        <v>24678.34</v>
+        <v>24333.46</v>
       </c>
       <c r="J12" t="n">
-        <v>24856.09</v>
+        <v>25047.53</v>
       </c>
       <c r="K12" t="n">
-        <v>24935.95</v>
+        <v>25250.29</v>
       </c>
       <c r="L12" t="n">
-        <v>25015.8</v>
+        <v>25453.06</v>
       </c>
       <c r="M12" t="n">
-        <v>25144.61</v>
+        <v>25911.47</v>
       </c>
       <c r="N12" t="n">
-        <v>25273.41</v>
+        <v>26369.89</v>
       </c>
       <c r="O12" t="n">
-        <v>25304.32</v>
+        <v>26317</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1524,25 +1528,21 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
@@ -1554,50 +1554,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25763.97</v>
+        <v>25811.9</v>
       </c>
       <c r="C13" t="n">
-        <v>25826.78</v>
+        <v>25900.1</v>
       </c>
       <c r="D13" t="n">
-        <v>25611.69</v>
+        <v>25698.56</v>
       </c>
       <c r="E13" t="n">
-        <v>25779.31</v>
+        <v>25817.89</v>
       </c>
       <c r="F13" t="n">
-        <v>198.43</v>
+        <v>38.58</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0078</v>
+        <v>0.0015</v>
       </c>
       <c r="H13" t="n">
-        <v>215.09</v>
+        <v>201.54</v>
       </c>
       <c r="I13" t="n">
-        <v>24333.46</v>
+        <v>25396.6</v>
       </c>
       <c r="J13" t="n">
-        <v>25047.53</v>
+        <v>25594.26</v>
       </c>
       <c r="K13" t="n">
-        <v>25250.29</v>
+        <v>25671.77</v>
       </c>
       <c r="L13" t="n">
-        <v>25453.06</v>
+        <v>25749.27</v>
       </c>
       <c r="M13" t="n">
-        <v>25911.47</v>
+        <v>25886.86</v>
       </c>
       <c r="N13" t="n">
-        <v>26369.89</v>
+        <v>26024.44</v>
       </c>
       <c r="O13" t="n">
-        <v>26317</v>
+        <v>26041.87</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1608,14 +1608,14 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U13" s="8" t="n">
@@ -1634,69 +1634,73 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25811.9</v>
+        <v>25770.45</v>
       </c>
       <c r="C14" t="n">
-        <v>25900.1</v>
+        <v>25811.97</v>
       </c>
       <c r="D14" t="n">
-        <v>25698.56</v>
+        <v>25465.12</v>
       </c>
       <c r="E14" t="n">
-        <v>25817.89</v>
+        <v>25465.25</v>
       </c>
       <c r="F14" t="n">
-        <v>38.58</v>
+        <v>-352.64</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0137</v>
       </c>
       <c r="H14" t="n">
-        <v>201.54</v>
+        <v>346.85</v>
       </c>
       <c r="I14" t="n">
-        <v>25396.6</v>
+        <v>25497.02</v>
       </c>
       <c r="J14" t="n">
-        <v>25594.26</v>
+        <v>25625.63</v>
       </c>
       <c r="K14" t="n">
-        <v>25671.77</v>
+        <v>25717.12</v>
       </c>
       <c r="L14" t="n">
-        <v>25749.27</v>
+        <v>25808.61</v>
       </c>
       <c r="M14" t="n">
-        <v>25886.86</v>
+        <v>25918.66</v>
       </c>
       <c r="N14" t="n">
-        <v>26024.44</v>
+        <v>26028.71</v>
       </c>
       <c r="O14" t="n">
-        <v>26041.87</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+        <v>26101.64</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1704,9 +1708,9 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
@@ -1714,67 +1718,67 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25770.45</v>
+        <v>25274.94</v>
       </c>
       <c r="C15" t="n">
-        <v>25811.97</v>
+        <v>25280.16</v>
       </c>
       <c r="D15" t="n">
-        <v>25465.12</v>
+        <v>24830.17</v>
       </c>
       <c r="E15" t="n">
-        <v>25465.25</v>
+        <v>24897.45</v>
       </c>
       <c r="F15" t="n">
-        <v>-352.64</v>
+        <v>-567.8</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0223</v>
       </c>
       <c r="H15" t="n">
-        <v>346.85</v>
+        <v>449.99</v>
       </c>
       <c r="I15" t="n">
-        <v>25497.02</v>
+        <v>25118.27</v>
       </c>
       <c r="J15" t="n">
-        <v>25625.63</v>
+        <v>25031.75</v>
       </c>
       <c r="K15" t="n">
-        <v>25717.12</v>
+        <v>25291.82</v>
       </c>
       <c r="L15" t="n">
-        <v>25808.61</v>
+        <v>25551.9</v>
       </c>
       <c r="M15" t="n">
-        <v>25918.66</v>
+        <v>25638.68</v>
       </c>
       <c r="N15" t="n">
-        <v>26028.71</v>
+        <v>25725.45</v>
       </c>
       <c r="O15" t="n">
-        <v>26101.64</v>
+        <v>26158.82</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1798,74 +1802,70 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25274.94</v>
+        <v>25097.48</v>
       </c>
       <c r="C16" t="n">
-        <v>25280.16</v>
+        <v>25127.76</v>
       </c>
       <c r="D16" t="n">
-        <v>24830.17</v>
+        <v>24867.32</v>
       </c>
       <c r="E16" t="n">
-        <v>24897.45</v>
+        <v>25118.27</v>
       </c>
       <c r="F16" t="n">
-        <v>-567.8</v>
+        <v>220.82</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0089</v>
       </c>
       <c r="H16" t="n">
-        <v>449.99</v>
+        <v>260.44</v>
       </c>
       <c r="I16" t="n">
-        <v>25118.27</v>
+        <v>24380.18</v>
       </c>
       <c r="J16" t="n">
-        <v>25031.75</v>
+        <v>24368.6</v>
       </c>
       <c r="K16" t="n">
-        <v>25291.82</v>
+        <v>24672.45</v>
       </c>
       <c r="L16" t="n">
-        <v>25551.9</v>
+        <v>24976.31</v>
       </c>
       <c r="M16" t="n">
-        <v>25638.68</v>
+        <v>25122.44</v>
       </c>
       <c r="N16" t="n">
-        <v>25725.45</v>
+        <v>25268.58</v>
       </c>
       <c r="O16" t="n">
-        <v>26158.82</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
+        <v>25730.15</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
@@ -1877,55 +1877,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25097.48</v>
+        <v>25081.19</v>
       </c>
       <c r="C17" t="n">
-        <v>25127.76</v>
+        <v>25195.83</v>
       </c>
       <c r="D17" t="n">
-        <v>24867.32</v>
+        <v>24937.52</v>
       </c>
       <c r="E17" t="n">
-        <v>25118.27</v>
+        <v>25067.09</v>
       </c>
       <c r="F17" t="n">
-        <v>220.82</v>
+        <v>-51.18</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.002</v>
       </c>
       <c r="H17" t="n">
-        <v>260.44</v>
+        <v>258.31</v>
       </c>
       <c r="I17" t="n">
-        <v>24380.18</v>
+        <v>24606.88</v>
       </c>
       <c r="J17" t="n">
-        <v>24368.6</v>
+        <v>24918.19</v>
       </c>
       <c r="K17" t="n">
-        <v>24672.45</v>
+        <v>24988.05</v>
       </c>
       <c r="L17" t="n">
-        <v>24976.31</v>
+        <v>25057.9</v>
       </c>
       <c r="M17" t="n">
-        <v>25122.44</v>
+        <v>25248.49</v>
       </c>
       <c r="N17" t="n">
-        <v>25268.58</v>
+        <v>25439.07</v>
       </c>
       <c r="O17" t="n">
-        <v>25730.15</v>
+        <v>25388.2</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1933,18 +1937,18 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1966,50 +1970,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25081.19</v>
+        <v>24963.8</v>
       </c>
       <c r="C18" t="n">
-        <v>25195.83</v>
+        <v>25154.58</v>
       </c>
       <c r="D18" t="n">
-        <v>24937.52</v>
+        <v>24963.8</v>
       </c>
       <c r="E18" t="n">
-        <v>25067.09</v>
+        <v>25114.25</v>
       </c>
       <c r="F18" t="n">
-        <v>-51.18</v>
+        <v>47.16</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="H18" t="n">
-        <v>258.31</v>
+        <v>190.78</v>
       </c>
       <c r="I18" t="n">
-        <v>24606.88</v>
+        <v>24679.21</v>
       </c>
       <c r="J18" t="n">
-        <v>24918.19</v>
+        <v>24808.99</v>
       </c>
       <c r="K18" t="n">
-        <v>24988.05</v>
+        <v>24937.93</v>
       </c>
       <c r="L18" t="n">
-        <v>25057.9</v>
+        <v>25066.88</v>
       </c>
       <c r="M18" t="n">
-        <v>25248.49</v>
+        <v>25196.25</v>
       </c>
       <c r="N18" t="n">
-        <v>25439.07</v>
+        <v>25325.61</v>
       </c>
       <c r="O18" t="n">
-        <v>25388.2</v>
+        <v>25454.14</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2017,12 +2021,10 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2050,61 +2052,65 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24963.8</v>
+        <v>24932.62</v>
       </c>
       <c r="C19" t="n">
-        <v>25154.58</v>
+        <v>25204.68</v>
       </c>
       <c r="D19" t="n">
-        <v>24963.8</v>
+        <v>24869.25</v>
       </c>
       <c r="E19" t="n">
-        <v>25114.25</v>
+        <v>25147.03</v>
       </c>
       <c r="F19" t="n">
-        <v>47.16</v>
+        <v>32.78</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0013</v>
       </c>
       <c r="H19" t="n">
-        <v>190.78</v>
+        <v>335.43</v>
       </c>
       <c r="I19" t="n">
-        <v>24679.21</v>
+        <v>24773.02</v>
       </c>
       <c r="J19" t="n">
-        <v>24808.99</v>
+        <v>24951</v>
       </c>
       <c r="K19" t="n">
-        <v>24937.93</v>
+        <v>25018.86</v>
       </c>
       <c r="L19" t="n">
-        <v>25066.88</v>
+        <v>25086.72</v>
       </c>
       <c r="M19" t="n">
-        <v>25196.25</v>
+        <v>25209.64</v>
       </c>
       <c r="N19" t="n">
-        <v>25325.61</v>
+        <v>25332.56</v>
       </c>
       <c r="O19" t="n">
-        <v>25454.14</v>
+        <v>25345.36</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2132,50 +2138,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24932.62</v>
+        <v>24970.05</v>
       </c>
       <c r="C20" t="n">
-        <v>25204.68</v>
+        <v>25055.48</v>
       </c>
       <c r="D20" t="n">
-        <v>24869.25</v>
+        <v>24839.23</v>
       </c>
       <c r="E20" t="n">
-        <v>25147.03</v>
+        <v>24999.53</v>
       </c>
       <c r="F20" t="n">
-        <v>32.78</v>
+        <v>-147.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0059</v>
       </c>
       <c r="H20" t="n">
-        <v>335.43</v>
+        <v>216.25</v>
       </c>
       <c r="I20" t="n">
-        <v>24773.02</v>
+        <v>24533.82</v>
       </c>
       <c r="J20" t="n">
-        <v>24951</v>
+        <v>24866.63</v>
       </c>
       <c r="K20" t="n">
-        <v>25018.86</v>
+        <v>24979.31</v>
       </c>
       <c r="L20" t="n">
-        <v>25086.72</v>
+        <v>25092</v>
       </c>
       <c r="M20" t="n">
-        <v>25209.64</v>
+        <v>25314.74</v>
       </c>
       <c r="N20" t="n">
-        <v>25332.56</v>
+        <v>25537.49</v>
       </c>
       <c r="O20" t="n">
-        <v>25345.36</v>
+        <v>25540.11</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2187,12 +2193,12 @@
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2209,59 +2215,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24970.05</v>
+        <v>25018.95</v>
       </c>
       <c r="C21" t="n">
-        <v>25055.48</v>
+        <v>25021.51</v>
       </c>
       <c r="D21" t="n">
-        <v>24839.23</v>
+        <v>24696.17</v>
       </c>
       <c r="E21" t="n">
-        <v>24999.53</v>
+        <v>24915.49</v>
       </c>
       <c r="F21" t="n">
-        <v>-147.5</v>
+        <v>-84.04000000000001</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0059</v>
+        <v>-0.0034</v>
       </c>
       <c r="H21" t="n">
-        <v>216.25</v>
+        <v>325.34</v>
       </c>
       <c r="I21" t="n">
-        <v>24533.82</v>
+        <v>24622.98</v>
       </c>
       <c r="J21" t="n">
-        <v>24866.63</v>
+        <v>24809.37</v>
       </c>
       <c r="K21" t="n">
-        <v>24979.31</v>
+        <v>24891.4</v>
       </c>
       <c r="L21" t="n">
-        <v>25092</v>
+        <v>24973.44</v>
       </c>
       <c r="M21" t="n">
-        <v>25314.74</v>
+        <v>25107.65</v>
       </c>
       <c r="N21" t="n">
-        <v>25537.49</v>
+        <v>25241.87</v>
       </c>
       <c r="O21" t="n">
-        <v>25540.11</v>
+        <v>25271.73</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2276,7 +2278,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2300,67 +2302,65 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25018.95</v>
+        <v>24755.09</v>
       </c>
       <c r="C22" t="n">
-        <v>25021.51</v>
+        <v>24850.75</v>
       </c>
       <c r="D22" t="n">
-        <v>24696.17</v>
+        <v>24651.34</v>
       </c>
       <c r="E22" t="n">
-        <v>24915.49</v>
+        <v>24830.98</v>
       </c>
       <c r="F22" t="n">
-        <v>-84.04000000000001</v>
+        <v>-84.51000000000001</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>-0.0034</v>
       </c>
       <c r="H22" t="n">
-        <v>325.34</v>
+        <v>199.41</v>
       </c>
       <c r="I22" t="n">
-        <v>24622.98</v>
+        <v>24370.83</v>
       </c>
       <c r="J22" t="n">
-        <v>24809.37</v>
+        <v>24618.48</v>
       </c>
       <c r="K22" t="n">
-        <v>24891.4</v>
+        <v>24752.82</v>
       </c>
       <c r="L22" t="n">
-        <v>24973.44</v>
+        <v>24887.17</v>
       </c>
       <c r="M22" t="n">
-        <v>25107.65</v>
+        <v>25078.16</v>
       </c>
       <c r="N22" t="n">
-        <v>25241.87</v>
+        <v>25269.16</v>
       </c>
       <c r="O22" t="n">
-        <v>25271.73</v>
+        <v>25346.85</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q22" s="6" t="n">
+        <v/>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2382,50 +2382,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24755.09</v>
+        <v>24769.15</v>
       </c>
       <c r="C23" t="n">
-        <v>24850.75</v>
+        <v>24974.53</v>
       </c>
       <c r="D23" t="n">
-        <v>24651.34</v>
+        <v>24751.13</v>
       </c>
       <c r="E23" t="n">
-        <v>24830.98</v>
+        <v>24846.69</v>
       </c>
       <c r="F23" t="n">
-        <v>-84.51000000000001</v>
+        <v>15.71</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>199.41</v>
+        <v>223.4</v>
       </c>
       <c r="I23" t="n">
-        <v>24370.83</v>
+        <v>24451.93</v>
       </c>
       <c r="J23" t="n">
-        <v>24618.48</v>
+        <v>24671.54</v>
       </c>
       <c r="K23" t="n">
-        <v>24752.82</v>
+        <v>24731.28</v>
       </c>
       <c r="L23" t="n">
-        <v>24887.17</v>
+        <v>24791.01</v>
       </c>
       <c r="M23" t="n">
-        <v>25078.16</v>
+        <v>24930.69</v>
       </c>
       <c r="N23" t="n">
-        <v>25269.16</v>
+        <v>25070.36</v>
       </c>
       <c r="O23" t="n">
-        <v>25346.85</v>
+        <v>25050.16</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2433,18 +2433,18 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2457,55 +2457,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24769.15</v>
+        <v>24922.1</v>
       </c>
       <c r="C24" t="n">
-        <v>24974.53</v>
+        <v>25011.35</v>
       </c>
       <c r="D24" t="n">
-        <v>24751.13</v>
+        <v>24817.34</v>
       </c>
       <c r="E24" t="n">
-        <v>24846.69</v>
+        <v>25011.35</v>
       </c>
       <c r="F24" t="n">
-        <v>15.71</v>
+        <v>164.66</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0066</v>
       </c>
       <c r="H24" t="n">
-        <v>223.4</v>
+        <v>194.01</v>
       </c>
       <c r="I24" t="n">
-        <v>24451.93</v>
+        <v>24527.73</v>
       </c>
       <c r="J24" t="n">
-        <v>24671.54</v>
+        <v>24615.22</v>
       </c>
       <c r="K24" t="n">
-        <v>24731.28</v>
+        <v>24734.99</v>
       </c>
       <c r="L24" t="n">
-        <v>24791.01</v>
+        <v>24854.76</v>
       </c>
       <c r="M24" t="n">
-        <v>24930.69</v>
+        <v>24958.39</v>
       </c>
       <c r="N24" t="n">
-        <v>25070.36</v>
+        <v>25062.02</v>
       </c>
       <c r="O24" t="n">
-        <v>25050.16</v>
+        <v>25197.93</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2516,9 +2520,9 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
@@ -2526,8 +2530,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2546,50 +2552,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24922.1</v>
+        <v>25001.31</v>
       </c>
       <c r="C25" t="n">
-        <v>25011.35</v>
+        <v>25271.34</v>
       </c>
       <c r="D25" t="n">
-        <v>24817.34</v>
+        <v>24984.27</v>
       </c>
       <c r="E25" t="n">
-        <v>25011.35</v>
+        <v>25155.41</v>
       </c>
       <c r="F25" t="n">
-        <v>164.66</v>
+        <v>144.06</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0058</v>
       </c>
       <c r="H25" t="n">
-        <v>194.01</v>
+        <v>287.07</v>
       </c>
       <c r="I25" t="n">
-        <v>24527.73</v>
+        <v>24623.33</v>
       </c>
       <c r="J25" t="n">
-        <v>24615.22</v>
+        <v>24865.84</v>
       </c>
       <c r="K25" t="n">
-        <v>24734.99</v>
+        <v>24914.34</v>
       </c>
       <c r="L25" t="n">
-        <v>24854.76</v>
+        <v>24962.85</v>
       </c>
       <c r="M25" t="n">
-        <v>24958.39</v>
+        <v>25108.35</v>
       </c>
       <c r="N25" t="n">
-        <v>25062.02</v>
+        <v>25253.86</v>
       </c>
       <c r="O25" t="n">
-        <v>25197.93</v>
+        <v>25205.36</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2600,23 +2606,25 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U25" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W25" s="11" t="inlineStr">
         <is>
@@ -2632,171 +2640,165 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25001.31</v>
+        <v>24994.05</v>
       </c>
       <c r="C26" t="n">
-        <v>25271.34</v>
+        <v>25074.28</v>
       </c>
       <c r="D26" t="n">
-        <v>24984.27</v>
+        <v>24696.59</v>
       </c>
       <c r="E26" t="n">
-        <v>25155.41</v>
+        <v>24763.12</v>
       </c>
       <c r="F26" t="n">
-        <v>144.06</v>
+        <v>-392.29</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0156</v>
       </c>
       <c r="H26" t="n">
-        <v>287.07</v>
+        <v>377.69</v>
       </c>
       <c r="I26" t="n">
-        <v>24623.33</v>
+        <v>24697.2</v>
       </c>
       <c r="J26" t="n">
-        <v>24865.84</v>
+        <v>24882.14</v>
       </c>
       <c r="K26" t="n">
-        <v>24914.34</v>
+        <v>25011.88</v>
       </c>
       <c r="L26" t="n">
-        <v>24962.85</v>
+        <v>25141.61</v>
       </c>
       <c r="M26" t="n">
-        <v>25108.35</v>
+        <v>25298.95</v>
       </c>
       <c r="N26" t="n">
-        <v>25253.86</v>
+        <v>25456.28</v>
       </c>
       <c r="O26" t="n">
-        <v>25205.36</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+        <v>25558.41</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
       </c>
       <c r="W26" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>24994.05</v>
+        <v>24830.41</v>
       </c>
       <c r="C27" t="n">
-        <v>25074.28</v>
+        <v>25099.68</v>
       </c>
       <c r="D27" t="n">
-        <v>24696.59</v>
+        <v>24821.67</v>
       </c>
       <c r="E27" t="n">
-        <v>24763.12</v>
+        <v>25099</v>
       </c>
       <c r="F27" t="n">
-        <v>-392.29</v>
+        <v>335.88</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0136</v>
       </c>
       <c r="H27" t="n">
-        <v>377.69</v>
+        <v>278.01</v>
       </c>
       <c r="I27" t="n">
-        <v>24697.2</v>
+        <v>24318.9</v>
       </c>
       <c r="J27" t="n">
-        <v>24882.14</v>
+        <v>24324.27</v>
       </c>
       <c r="K27" t="n">
-        <v>25011.88</v>
+        <v>24574.27</v>
       </c>
       <c r="L27" t="n">
-        <v>25141.61</v>
+        <v>24824.28</v>
       </c>
       <c r="M27" t="n">
-        <v>25298.95</v>
+        <v>24951.96</v>
       </c>
       <c r="N27" t="n">
-        <v>25456.28</v>
+        <v>25079.65</v>
       </c>
       <c r="O27" t="n">
-        <v>25558.41</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
+        <v>25451.97</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr"/>
@@ -2804,50 +2806,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24830.41</v>
+        <v>25459.32</v>
       </c>
       <c r="C28" t="n">
-        <v>25099.68</v>
+        <v>25560.4</v>
       </c>
       <c r="D28" t="n">
-        <v>24821.67</v>
+        <v>25361.03</v>
       </c>
       <c r="E28" t="n">
-        <v>25099</v>
+        <v>25361.03</v>
       </c>
       <c r="F28" t="n">
-        <v>335.88</v>
+        <v>262.03</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0104</v>
       </c>
       <c r="H28" t="n">
-        <v>278.01</v>
+        <v>199.37</v>
       </c>
       <c r="I28" t="n">
-        <v>24318.9</v>
+        <v>24543.66</v>
       </c>
       <c r="J28" t="n">
-        <v>24324.27</v>
+        <v>24890.15</v>
       </c>
       <c r="K28" t="n">
-        <v>24574.27</v>
+        <v>24960</v>
       </c>
       <c r="L28" t="n">
-        <v>24824.28</v>
+        <v>25029.84</v>
       </c>
       <c r="M28" t="n">
-        <v>24951.96</v>
+        <v>25238</v>
       </c>
       <c r="N28" t="n">
-        <v>25079.65</v>
+        <v>25446.17</v>
       </c>
       <c r="O28" t="n">
-        <v>25451.97</v>
+        <v>25377.69</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2858,7 +2860,7 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2870,11 +2872,13 @@
       </c>
       <c r="U28" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
@@ -2886,50 +2890,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25459.32</v>
+        <v>25496.13</v>
       </c>
       <c r="C29" t="n">
-        <v>25560.4</v>
+        <v>25553.47</v>
       </c>
       <c r="D29" t="n">
-        <v>25361.03</v>
+        <v>25307.17</v>
       </c>
       <c r="E29" t="n">
-        <v>25361.03</v>
+        <v>25464.01</v>
       </c>
       <c r="F29" t="n">
-        <v>262.03</v>
+        <v>102.98</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0104</v>
+        <v>0.0041</v>
       </c>
       <c r="H29" t="n">
-        <v>199.37</v>
+        <v>246.3</v>
       </c>
       <c r="I29" t="n">
-        <v>24543.66</v>
+        <v>25161.66</v>
       </c>
       <c r="J29" t="n">
-        <v>24890.15</v>
+        <v>25111.82</v>
       </c>
       <c r="K29" t="n">
-        <v>24960</v>
+        <v>25261.34</v>
       </c>
       <c r="L29" t="n">
-        <v>25029.84</v>
+        <v>25410.87</v>
       </c>
       <c r="M29" t="n">
-        <v>25238</v>
+        <v>25460.71</v>
       </c>
       <c r="N29" t="n">
-        <v>25446.17</v>
+        <v>25510.56</v>
       </c>
       <c r="O29" t="n">
-        <v>25377.69</v>
+        <v>25759.77</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2940,14 +2944,14 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U29" s="8" t="inlineStr">
@@ -2955,65 +2959,67 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V29" s="8" t="n">
+        <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25496.13</v>
+        <v>25551.97</v>
       </c>
       <c r="C30" t="n">
-        <v>25553.47</v>
+        <v>25571.45</v>
       </c>
       <c r="D30" t="n">
-        <v>25307.17</v>
+        <v>25336.39</v>
       </c>
       <c r="E30" t="n">
-        <v>25464.01</v>
+        <v>25460.48</v>
       </c>
       <c r="F30" t="n">
-        <v>102.98</v>
+        <v>-3.53</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0001</v>
       </c>
       <c r="H30" t="n">
-        <v>246.3</v>
+        <v>235.06</v>
       </c>
       <c r="I30" t="n">
-        <v>25161.66</v>
+        <v>25060.87</v>
       </c>
       <c r="J30" t="n">
-        <v>25111.82</v>
+        <v>25234.55</v>
       </c>
       <c r="K30" t="n">
-        <v>25261.34</v>
+        <v>25340.86</v>
       </c>
       <c r="L30" t="n">
-        <v>25410.87</v>
+        <v>25447.17</v>
       </c>
       <c r="M30" t="n">
-        <v>25460.71</v>
+        <v>25587.16</v>
       </c>
       <c r="N30" t="n">
-        <v>25510.56</v>
+        <v>25727.16</v>
       </c>
       <c r="O30" t="n">
-        <v>25759.77</v>
+        <v>25799.77</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3021,23 +3027,21 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3049,57 +3053,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25551.97</v>
+        <v>25487.45</v>
       </c>
       <c r="C31" t="n">
-        <v>25571.45</v>
+        <v>25651.16</v>
       </c>
       <c r="D31" t="n">
-        <v>25336.39</v>
+        <v>25303.11</v>
       </c>
       <c r="E31" t="n">
-        <v>25460.48</v>
+        <v>25612.03</v>
       </c>
       <c r="F31" t="n">
-        <v>-3.53</v>
+        <v>151.55</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.006</v>
       </c>
       <c r="H31" t="n">
-        <v>235.06</v>
+        <v>348.05</v>
       </c>
       <c r="I31" t="n">
-        <v>25060.87</v>
+        <v>25101.33</v>
       </c>
       <c r="J31" t="n">
-        <v>25234.55</v>
+        <v>25228.7</v>
       </c>
       <c r="K31" t="n">
-        <v>25340.86</v>
+        <v>25342.95</v>
       </c>
       <c r="L31" t="n">
-        <v>25447.17</v>
+        <v>25457.2</v>
       </c>
       <c r="M31" t="n">
-        <v>25587.16</v>
+        <v>25578.01</v>
       </c>
       <c r="N31" t="n">
-        <v>25727.16</v>
+        <v>25698.82</v>
       </c>
       <c r="O31" t="n">
-        <v>25799.77</v>
+        <v>25806.51</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3112,13 +3116,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3140,50 +3146,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25487.45</v>
+        <v>25709.37</v>
       </c>
       <c r="C32" t="n">
-        <v>25651.16</v>
+        <v>25891.51</v>
       </c>
       <c r="D32" t="n">
-        <v>25303.11</v>
+        <v>25549.53</v>
       </c>
       <c r="E32" t="n">
-        <v>25612.03</v>
+        <v>25629.24</v>
       </c>
       <c r="F32" t="n">
-        <v>151.55</v>
+        <v>17.21</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0007</v>
       </c>
       <c r="H32" t="n">
-        <v>348.05</v>
+        <v>341.98</v>
       </c>
       <c r="I32" t="n">
-        <v>25101.33</v>
+        <v>24955.06</v>
       </c>
       <c r="J32" t="n">
-        <v>25228.7</v>
+        <v>25331.43</v>
       </c>
       <c r="K32" t="n">
-        <v>25342.95</v>
+        <v>25438</v>
       </c>
       <c r="L32" t="n">
-        <v>25457.2</v>
+        <v>25544.58</v>
       </c>
       <c r="M32" t="n">
-        <v>25578.01</v>
+        <v>25786.05</v>
       </c>
       <c r="N32" t="n">
-        <v>25698.82</v>
+        <v>26027.53</v>
       </c>
       <c r="O32" t="n">
-        <v>25806.51</v>
+        <v>25999.21</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3191,19 +3197,17 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U32" s="8" t="n">
@@ -3217,59 +3221,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25709.37</v>
+        <v>25855.12</v>
       </c>
       <c r="C33" t="n">
-        <v>25891.51</v>
+        <v>26096.93</v>
       </c>
       <c r="D33" t="n">
-        <v>25549.53</v>
+        <v>25855.12</v>
       </c>
       <c r="E33" t="n">
-        <v>25629.24</v>
+        <v>26001.31</v>
       </c>
       <c r="F33" t="n">
-        <v>17.21</v>
+        <v>372.07</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0145</v>
       </c>
       <c r="H33" t="n">
-        <v>341.98</v>
+        <v>241.81</v>
       </c>
       <c r="I33" t="n">
-        <v>24955.06</v>
+        <v>25207.55</v>
       </c>
       <c r="J33" t="n">
-        <v>25331.43</v>
+        <v>25241.62</v>
       </c>
       <c r="K33" t="n">
-        <v>25438</v>
+        <v>25458.25</v>
       </c>
       <c r="L33" t="n">
-        <v>25544.58</v>
+        <v>25674.88</v>
       </c>
       <c r="M33" t="n">
-        <v>25786.05</v>
+        <v>25800.23</v>
       </c>
       <c r="N33" t="n">
-        <v>26027.53</v>
+        <v>25925.58</v>
       </c>
       <c r="O33" t="n">
-        <v>25999.21</v>
+        <v>26233.49</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3280,9 +3280,9 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
@@ -3290,8 +3290,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3306,50 +3308,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25855.12</v>
+        <v>26189.62</v>
       </c>
       <c r="C34" t="n">
-        <v>26096.93</v>
+        <v>26266.5</v>
       </c>
       <c r="D34" t="n">
-        <v>25855.12</v>
+        <v>26082.43</v>
       </c>
       <c r="E34" t="n">
-        <v>26001.31</v>
+        <v>26202.35</v>
       </c>
       <c r="F34" t="n">
-        <v>372.07</v>
+        <v>201.04</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0077</v>
       </c>
       <c r="H34" t="n">
-        <v>241.81</v>
+        <v>184.07</v>
       </c>
       <c r="I34" t="n">
-        <v>25207.55</v>
+        <v>25613.31</v>
       </c>
       <c r="J34" t="n">
-        <v>25241.62</v>
+        <v>25772.14</v>
       </c>
       <c r="K34" t="n">
-        <v>25458.25</v>
+        <v>25880.41</v>
       </c>
       <c r="L34" t="n">
-        <v>25674.88</v>
+        <v>25988.67</v>
       </c>
       <c r="M34" t="n">
-        <v>25800.23</v>
+        <v>26122.22</v>
       </c>
       <c r="N34" t="n">
-        <v>25925.58</v>
+        <v>26255.76</v>
       </c>
       <c r="O34" t="n">
-        <v>26233.49</v>
+        <v>26338.74</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3360,7 +3362,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3388,50 +3390,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>26189.62</v>
+        <v>26393.43</v>
       </c>
       <c r="C35" t="n">
-        <v>26266.5</v>
+        <v>26403.81</v>
       </c>
       <c r="D35" t="n">
-        <v>26082.43</v>
+        <v>26123.18</v>
       </c>
       <c r="E35" t="n">
-        <v>26202.35</v>
+        <v>26126.3</v>
       </c>
       <c r="F35" t="n">
-        <v>201.04</v>
+        <v>-76.05</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0029</v>
       </c>
       <c r="H35" t="n">
-        <v>184.07</v>
+        <v>280.63</v>
       </c>
       <c r="I35" t="n">
-        <v>25613.31</v>
+        <v>25898.36</v>
       </c>
       <c r="J35" t="n">
-        <v>25772.14</v>
+        <v>26032.22</v>
       </c>
       <c r="K35" t="n">
-        <v>25880.41</v>
+        <v>26110.31</v>
       </c>
       <c r="L35" t="n">
-        <v>25988.67</v>
+        <v>26188.41</v>
       </c>
       <c r="M35" t="n">
-        <v>26122.22</v>
+        <v>26294.38</v>
       </c>
       <c r="N35" t="n">
-        <v>26255.76</v>
+        <v>26400.36</v>
       </c>
       <c r="O35" t="n">
-        <v>26338.74</v>
+        <v>26450.57</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3439,12 +3441,14 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
@@ -3454,7 +3458,7 @@
       </c>
       <c r="U35" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V35" s="8" t="n">
@@ -3465,55 +3469,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26393.43</v>
+        <v>26116.27</v>
       </c>
       <c r="C36" t="n">
-        <v>26403.81</v>
+        <v>26229.33</v>
       </c>
       <c r="D36" t="n">
-        <v>26123.18</v>
+        <v>26081.69</v>
       </c>
       <c r="E36" t="n">
-        <v>26126.3</v>
+        <v>26140.13</v>
       </c>
       <c r="F36" t="n">
-        <v>-76.05</v>
+        <v>13.83</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0005</v>
       </c>
       <c r="H36" t="n">
-        <v>280.63</v>
+        <v>147.64</v>
       </c>
       <c r="I36" t="n">
-        <v>25898.36</v>
+        <v>25842.55</v>
       </c>
       <c r="J36" t="n">
-        <v>26032.22</v>
+        <v>25777.07</v>
       </c>
       <c r="K36" t="n">
-        <v>26110.31</v>
+        <v>25985.99</v>
       </c>
       <c r="L36" t="n">
-        <v>26188.41</v>
+        <v>26194.9</v>
       </c>
       <c r="M36" t="n">
-        <v>26294.38</v>
+        <v>26266.62</v>
       </c>
       <c r="N36" t="n">
-        <v>26400.36</v>
+        <v>26338.33</v>
       </c>
       <c r="O36" t="n">
-        <v>26450.57</v>
+        <v>26684.44</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3521,25 +3529,19 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3551,57 +3553,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26116.27</v>
+        <v>26235.8</v>
       </c>
       <c r="C37" t="n">
-        <v>26229.33</v>
+        <v>26445.18</v>
       </c>
       <c r="D37" t="n">
-        <v>26081.69</v>
+        <v>26223.64</v>
       </c>
       <c r="E37" t="n">
-        <v>26140.13</v>
+        <v>26319.45</v>
       </c>
       <c r="F37" t="n">
-        <v>13.83</v>
+        <v>179.32</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0069</v>
       </c>
       <c r="H37" t="n">
-        <v>147.64</v>
+        <v>221.54</v>
       </c>
       <c r="I37" t="n">
-        <v>25842.55</v>
+        <v>25934.05</v>
       </c>
       <c r="J37" t="n">
-        <v>25777.07</v>
+        <v>25984.8</v>
       </c>
       <c r="K37" t="n">
-        <v>25985.99</v>
+        <v>26066.31</v>
       </c>
       <c r="L37" t="n">
-        <v>26194.9</v>
+        <v>26147.82</v>
       </c>
       <c r="M37" t="n">
-        <v>26266.62</v>
+        <v>26213.95</v>
       </c>
       <c r="N37" t="n">
-        <v>26338.33</v>
+        <v>26280.08</v>
       </c>
       <c r="O37" t="n">
-        <v>26684.44</v>
+        <v>26376.97</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3614,76 +3616,78 @@
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26235.8</v>
+        <v>26360.44</v>
       </c>
       <c r="C38" t="n">
-        <v>26445.18</v>
+        <v>26441.91</v>
       </c>
       <c r="D38" t="n">
-        <v>26223.64</v>
+        <v>26302.19</v>
       </c>
       <c r="E38" t="n">
-        <v>26319.45</v>
+        <v>26323.88</v>
       </c>
       <c r="F38" t="n">
-        <v>179.32</v>
+        <v>4.43</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0002</v>
       </c>
       <c r="H38" t="n">
-        <v>221.54</v>
+        <v>139.72</v>
       </c>
       <c r="I38" t="n">
-        <v>25934.05</v>
+        <v>26002.1</v>
       </c>
       <c r="J38" t="n">
-        <v>25984.8</v>
+        <v>26090.43</v>
       </c>
       <c r="K38" t="n">
-        <v>26066.31</v>
+        <v>26208.68</v>
       </c>
       <c r="L38" t="n">
-        <v>26147.82</v>
+        <v>26326.93</v>
       </c>
       <c r="M38" t="n">
-        <v>26213.95</v>
+        <v>26430.22</v>
       </c>
       <c r="N38" t="n">
-        <v>26280.08</v>
+        <v>26533.51</v>
       </c>
       <c r="O38" t="n">
-        <v>26376.97</v>
+        <v>26666.72</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3696,7 +3700,7 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
@@ -3704,70 +3708,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26360.44</v>
+        <v>26378</v>
       </c>
       <c r="C39" t="n">
-        <v>26441.91</v>
+        <v>26504.54</v>
       </c>
       <c r="D39" t="n">
-        <v>26302.19</v>
+        <v>26245.57</v>
       </c>
       <c r="E39" t="n">
-        <v>26323.88</v>
+        <v>26391.42</v>
       </c>
       <c r="F39" t="n">
-        <v>4.43</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0026</v>
       </c>
       <c r="H39" t="n">
-        <v>139.72</v>
+        <v>258.97</v>
       </c>
       <c r="I39" t="n">
-        <v>26002.1</v>
+        <v>26162.47</v>
       </c>
       <c r="J39" t="n">
-        <v>26090.43</v>
+        <v>26160.08</v>
       </c>
       <c r="K39" t="n">
-        <v>26208.68</v>
+        <v>26254.02</v>
       </c>
       <c r="L39" t="n">
-        <v>26326.93</v>
+        <v>26347.97</v>
       </c>
       <c r="M39" t="n">
-        <v>26430.22</v>
+        <v>26393.74</v>
       </c>
       <c r="N39" t="n">
-        <v>26533.51</v>
+        <v>26439.52</v>
       </c>
       <c r="O39" t="n">
-        <v>26666.72</v>
+        <v>26581.63</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3775,21 +3779,25 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3808,50 +3816,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>26378</v>
+        <v>26452</v>
       </c>
       <c r="C40" t="n">
-        <v>26504.54</v>
+        <v>26573.5</v>
       </c>
       <c r="D40" t="n">
-        <v>26245.57</v>
+        <v>26313.58</v>
       </c>
       <c r="E40" t="n">
-        <v>26391.42</v>
+        <v>26331.07</v>
       </c>
       <c r="F40" t="n">
-        <v>67.54000000000001</v>
+        <v>-60.35</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0023</v>
       </c>
       <c r="H40" t="n">
-        <v>258.97</v>
+        <v>259.92</v>
       </c>
       <c r="I40" t="n">
-        <v>26162.47</v>
+        <v>25986.6</v>
       </c>
       <c r="J40" t="n">
-        <v>26160.08</v>
+        <v>26140.63</v>
       </c>
       <c r="K40" t="n">
-        <v>26254.02</v>
+        <v>26261.94</v>
       </c>
       <c r="L40" t="n">
-        <v>26347.97</v>
+        <v>26383.24</v>
       </c>
       <c r="M40" t="n">
-        <v>26393.74</v>
+        <v>26520.9</v>
       </c>
       <c r="N40" t="n">
-        <v>26439.52</v>
+        <v>26658.57</v>
       </c>
       <c r="O40" t="n">
-        <v>26581.63</v>
+        <v>26763.51</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3859,25 +3867,21 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3896,50 +3900,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26452</v>
+        <v>26437.35</v>
       </c>
       <c r="C41" t="n">
-        <v>26573.5</v>
+        <v>26489.78</v>
       </c>
       <c r="D41" t="n">
-        <v>26313.58</v>
+        <v>26285.23</v>
       </c>
       <c r="E41" t="n">
-        <v>26331.07</v>
+        <v>26299.74</v>
       </c>
       <c r="F41" t="n">
-        <v>-60.35</v>
+        <v>-31.33</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0012</v>
       </c>
       <c r="H41" t="n">
-        <v>259.92</v>
+        <v>204.55</v>
       </c>
       <c r="I41" t="n">
-        <v>25986.6</v>
+        <v>26053.66</v>
       </c>
       <c r="J41" t="n">
-        <v>26140.63</v>
+        <v>26014.92</v>
       </c>
       <c r="K41" t="n">
-        <v>26261.94</v>
+        <v>26201.11</v>
       </c>
       <c r="L41" t="n">
-        <v>26383.24</v>
+        <v>26387.31</v>
       </c>
       <c r="M41" t="n">
-        <v>26520.9</v>
+        <v>26461.03</v>
       </c>
       <c r="N41" t="n">
-        <v>26658.57</v>
+        <v>26534.76</v>
       </c>
       <c r="O41" t="n">
-        <v>26763.51</v>
+        <v>26833.42</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3950,7 +3954,7 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3973,57 +3977,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26437.35</v>
+        <v>26445.99</v>
       </c>
       <c r="C42" t="n">
-        <v>26489.78</v>
+        <v>26541.34</v>
       </c>
       <c r="D42" t="n">
-        <v>26285.23</v>
+        <v>26404.95</v>
       </c>
       <c r="E42" t="n">
-        <v>26299.74</v>
+        <v>26440.31</v>
       </c>
       <c r="F42" t="n">
-        <v>-31.33</v>
+        <v>140.57</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0053</v>
       </c>
       <c r="H42" t="n">
-        <v>204.55</v>
+        <v>136.39</v>
       </c>
       <c r="I42" t="n">
-        <v>26053.66</v>
+        <v>26080.68</v>
       </c>
       <c r="J42" t="n">
-        <v>26014.92</v>
+        <v>26051.31</v>
       </c>
       <c r="K42" t="n">
-        <v>26201.11</v>
+        <v>26197.47</v>
       </c>
       <c r="L42" t="n">
-        <v>26387.31</v>
+        <v>26343.62</v>
       </c>
       <c r="M42" t="n">
-        <v>26461.03</v>
+        <v>26402.01</v>
       </c>
       <c r="N42" t="n">
-        <v>26534.76</v>
+        <v>26460.41</v>
       </c>
       <c r="O42" t="n">
-        <v>26833.42</v>
+        <v>26694.33</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4036,7 +4040,7 @@
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
@@ -4044,8 +4048,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U42" s="8" t="n">
-        <v/>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4055,59 +4061,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>26445.99</v>
+        <v>26490.3</v>
       </c>
       <c r="C43" t="n">
-        <v>26541.34</v>
+        <v>26493.5</v>
       </c>
       <c r="D43" t="n">
-        <v>26404.95</v>
+        <v>26338.61</v>
       </c>
       <c r="E43" t="n">
-        <v>26440.31</v>
+        <v>26338.61</v>
       </c>
       <c r="F43" t="n">
-        <v>140.57</v>
+        <v>-101.7</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0038</v>
       </c>
       <c r="H43" t="n">
-        <v>136.39</v>
+        <v>154.89</v>
       </c>
       <c r="I43" t="n">
-        <v>26080.68</v>
+        <v>26268.56</v>
       </c>
       <c r="J43" t="n">
-        <v>26051.31</v>
+        <v>26287.5</v>
       </c>
       <c r="K43" t="n">
-        <v>26197.47</v>
+        <v>26372.12</v>
       </c>
       <c r="L43" t="n">
-        <v>26343.62</v>
+        <v>26456.73</v>
       </c>
       <c r="M43" t="n">
-        <v>26402.01</v>
+        <v>26508.51</v>
       </c>
       <c r="N43" t="n">
-        <v>26460.41</v>
+        <v>26560.28</v>
       </c>
       <c r="O43" t="n">
-        <v>26694.33</v>
+        <v>26677.73</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4115,23 +4117,21 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4141,68 +4141,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26490.3</v>
+        <v>26280.86</v>
       </c>
       <c r="C44" t="n">
-        <v>26493.5</v>
+        <v>26292.95</v>
       </c>
       <c r="D44" t="n">
-        <v>26338.61</v>
+        <v>26119.54</v>
       </c>
       <c r="E44" t="n">
-        <v>26338.61</v>
+        <v>26128.36</v>
       </c>
       <c r="F44" t="n">
-        <v>-101.7</v>
+        <v>-210.25</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.008</v>
       </c>
       <c r="H44" t="n">
-        <v>154.89</v>
+        <v>173.41</v>
       </c>
       <c r="I44" t="n">
-        <v>26268.56</v>
+        <v>26183.72</v>
       </c>
       <c r="J44" t="n">
-        <v>26287.5</v>
+        <v>26145</v>
       </c>
       <c r="K44" t="n">
-        <v>26372.12</v>
+        <v>26261.16</v>
       </c>
       <c r="L44" t="n">
-        <v>26456.73</v>
+        <v>26377.33</v>
       </c>
       <c r="M44" t="n">
-        <v>26508.51</v>
+        <v>26416.05</v>
       </c>
       <c r="N44" t="n">
-        <v>26560.28</v>
+        <v>26454.78</v>
       </c>
       <c r="O44" t="n">
-        <v>26677.73</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
+        <v>26648.39</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4216,81 +4224,73 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W44" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>26280.86</v>
+        <v>26146.12</v>
       </c>
       <c r="C45" t="n">
-        <v>26292.95</v>
+        <v>26187.82</v>
       </c>
       <c r="D45" t="n">
-        <v>26119.54</v>
+        <v>26063.37</v>
       </c>
       <c r="E45" t="n">
-        <v>26128.36</v>
+        <v>26091.33</v>
       </c>
       <c r="F45" t="n">
-        <v>-210.25</v>
+        <v>-37.03</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0014</v>
       </c>
       <c r="H45" t="n">
-        <v>173.41</v>
+        <v>124.45</v>
       </c>
       <c r="I45" t="n">
-        <v>26183.72</v>
+        <v>25946.13</v>
       </c>
       <c r="J45" t="n">
-        <v>26145</v>
+        <v>25916.01</v>
       </c>
       <c r="K45" t="n">
-        <v>26261.16</v>
+        <v>26041.65</v>
       </c>
       <c r="L45" t="n">
-        <v>26377.33</v>
+        <v>26167.3</v>
       </c>
       <c r="M45" t="n">
-        <v>26416.05</v>
+        <v>26215.06</v>
       </c>
       <c r="N45" t="n">
-        <v>26454.78</v>
+        <v>26262.83</v>
       </c>
       <c r="O45" t="n">
-        <v>26648.39</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
+        <v>26466.36</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4314,63 +4314,67 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>26146.12</v>
+        <v>26050.95</v>
       </c>
       <c r="C46" t="n">
-        <v>26187.82</v>
+        <v>26062.15</v>
       </c>
       <c r="D46" t="n">
-        <v>26063.37</v>
+        <v>25914.11</v>
       </c>
       <c r="E46" t="n">
-        <v>26091.33</v>
+        <v>25983.04</v>
       </c>
       <c r="F46" t="n">
-        <v>-37.03</v>
+        <v>-108.29</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0042</v>
       </c>
       <c r="H46" t="n">
-        <v>124.45</v>
+        <v>148.04</v>
       </c>
       <c r="I46" t="n">
-        <v>25946.13</v>
+        <v>25938.92</v>
       </c>
       <c r="J46" t="n">
-        <v>25916.01</v>
+        <v>25949.75</v>
       </c>
       <c r="K46" t="n">
-        <v>26041.65</v>
+        <v>26029.1</v>
       </c>
       <c r="L46" t="n">
-        <v>26167.3</v>
+        <v>26108.46</v>
       </c>
       <c r="M46" t="n">
-        <v>26215.06</v>
+        <v>26153.56</v>
       </c>
       <c r="N46" t="n">
-        <v>26262.83</v>
+        <v>26198.65</v>
       </c>
       <c r="O46" t="n">
-        <v>26466.36</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
+        <v>26312.27</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4394,83 +4398,81 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>26050.95</v>
+        <v>25998.95</v>
       </c>
       <c r="C47" t="n">
-        <v>26062.15</v>
+        <v>26166.25</v>
       </c>
       <c r="D47" t="n">
-        <v>25914.11</v>
+        <v>25969.52</v>
       </c>
       <c r="E47" t="n">
-        <v>25983.04</v>
+        <v>26136.56</v>
       </c>
       <c r="F47" t="n">
-        <v>-108.29</v>
+        <v>153.52</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.0059</v>
       </c>
       <c r="H47" t="n">
-        <v>148.04</v>
+        <v>196.73</v>
       </c>
       <c r="I47" t="n">
-        <v>25938.92</v>
+        <v>25766.07</v>
       </c>
       <c r="J47" t="n">
-        <v>25949.75</v>
+        <v>25832.45</v>
       </c>
       <c r="K47" t="n">
-        <v>26029.1</v>
+        <v>25909.02</v>
       </c>
       <c r="L47" t="n">
-        <v>26108.46</v>
+        <v>25985.58</v>
       </c>
       <c r="M47" t="n">
-        <v>26153.56</v>
+        <v>26057.06</v>
       </c>
       <c r="N47" t="n">
-        <v>26198.65</v>
+        <v>26128.53</v>
       </c>
       <c r="O47" t="n">
-        <v>26312.27</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
+        <v>26210.19</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W47" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr"/>
@@ -4478,50 +4480,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25998.95</v>
+        <v>26091.29</v>
       </c>
       <c r="C48" t="n">
-        <v>26166.25</v>
+        <v>26171.7</v>
       </c>
       <c r="D48" t="n">
-        <v>25969.52</v>
+        <v>26038.07</v>
       </c>
       <c r="E48" t="n">
-        <v>26136.56</v>
+        <v>26106.6</v>
       </c>
       <c r="F48" t="n">
-        <v>153.52</v>
+        <v>-29.96</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0011</v>
       </c>
       <c r="H48" t="n">
-        <v>196.73</v>
+        <v>133.63</v>
       </c>
       <c r="I48" t="n">
-        <v>25766.07</v>
+        <v>25772.79</v>
       </c>
       <c r="J48" t="n">
-        <v>25832.45</v>
+        <v>25974.17</v>
       </c>
       <c r="K48" t="n">
-        <v>25909.02</v>
+        <v>26038.2</v>
       </c>
       <c r="L48" t="n">
-        <v>25985.58</v>
+        <v>26102.22</v>
       </c>
       <c r="M48" t="n">
-        <v>26057.06</v>
+        <v>26234.93</v>
       </c>
       <c r="N48" t="n">
-        <v>26128.53</v>
+        <v>26367.63</v>
       </c>
       <c r="O48" t="n">
-        <v>26210.19</v>
+        <v>26362.98</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4529,23 +4531,21 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4555,55 +4555,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>26091.29</v>
+        <v>26206.01</v>
       </c>
       <c r="C49" t="n">
-        <v>26171.7</v>
+        <v>26341.52</v>
       </c>
       <c r="D49" t="n">
-        <v>26038.07</v>
+        <v>26164.11</v>
       </c>
       <c r="E49" t="n">
-        <v>26106.6</v>
+        <v>26266.14</v>
       </c>
       <c r="F49" t="n">
-        <v>-29.96</v>
+        <v>159.54</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0061</v>
       </c>
       <c r="H49" t="n">
-        <v>133.63</v>
+        <v>177.41</v>
       </c>
       <c r="I49" t="n">
-        <v>25772.79</v>
+        <v>25904.44</v>
       </c>
       <c r="J49" t="n">
-        <v>25974.17</v>
+        <v>25973.83</v>
       </c>
       <c r="K49" t="n">
-        <v>26038.2</v>
+        <v>26039.79</v>
       </c>
       <c r="L49" t="n">
-        <v>26102.22</v>
+        <v>26105.74</v>
       </c>
       <c r="M49" t="n">
-        <v>26234.93</v>
+        <v>26173.41</v>
       </c>
       <c r="N49" t="n">
-        <v>26367.63</v>
+        <v>26241.09</v>
       </c>
       <c r="O49" t="n">
-        <v>26362.98</v>
+        <v>26305.33</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4611,83 +4615,83 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V49" s="8" t="n">
-        <v/>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>26206.01</v>
+        <v>26255.41</v>
       </c>
       <c r="C50" t="n">
-        <v>26341.52</v>
+        <v>26466.76</v>
       </c>
       <c r="D50" t="n">
-        <v>26164.11</v>
+        <v>26196.92</v>
       </c>
       <c r="E50" t="n">
-        <v>26266.14</v>
+        <v>26285.96</v>
       </c>
       <c r="F50" t="n">
-        <v>159.54</v>
+        <v>19.82</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0061</v>
+        <v>0.0008</v>
       </c>
       <c r="H50" t="n">
-        <v>177.41</v>
+        <v>269.84</v>
       </c>
       <c r="I50" t="n">
-        <v>25904.44</v>
+        <v>25986.7</v>
       </c>
       <c r="J50" t="n">
-        <v>25973.83</v>
+        <v>26095.39</v>
       </c>
       <c r="K50" t="n">
-        <v>26039.79</v>
+        <v>26177.44</v>
       </c>
       <c r="L50" t="n">
-        <v>26105.74</v>
+        <v>26259.48</v>
       </c>
       <c r="M50" t="n">
-        <v>26173.41</v>
+        <v>26354.85</v>
       </c>
       <c r="N50" t="n">
-        <v>26241.09</v>
+        <v>26450.21</v>
       </c>
       <c r="O50" t="n">
-        <v>26305.33</v>
+        <v>26518.93</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4698,9 +4702,9 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
@@ -4710,13 +4714,11 @@
       </c>
       <c r="U50" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
       </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
@@ -4728,50 +4730,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>26255.41</v>
+        <v>26354.37</v>
       </c>
       <c r="C51" t="n">
-        <v>26466.76</v>
+        <v>26402.81</v>
       </c>
       <c r="D51" t="n">
-        <v>26196.92</v>
+        <v>26241.77</v>
       </c>
       <c r="E51" t="n">
-        <v>26285.96</v>
+        <v>26367.24</v>
       </c>
       <c r="F51" t="n">
-        <v>19.82</v>
+        <v>81.28</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0031</v>
       </c>
       <c r="H51" t="n">
-        <v>269.84</v>
+        <v>161.04</v>
       </c>
       <c r="I51" t="n">
-        <v>25986.7</v>
+        <v>25927.08</v>
       </c>
       <c r="J51" t="n">
-        <v>26095.39</v>
+        <v>25993.18</v>
       </c>
       <c r="K51" t="n">
-        <v>26177.44</v>
+        <v>26151.04</v>
       </c>
       <c r="L51" t="n">
-        <v>26259.48</v>
+        <v>26308.9</v>
       </c>
       <c r="M51" t="n">
-        <v>26354.85</v>
+        <v>26420.88</v>
       </c>
       <c r="N51" t="n">
-        <v>26450.21</v>
+        <v>26532.86</v>
       </c>
       <c r="O51" t="n">
-        <v>26518.93</v>
+        <v>26736.6</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4782,20 +4784,18 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4805,55 +4805,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>26354.37</v>
+        <v>26494.61</v>
       </c>
       <c r="C52" t="n">
-        <v>26402.81</v>
+        <v>26618.74</v>
       </c>
       <c r="D52" t="n">
-        <v>26241.77</v>
+        <v>26467.36</v>
       </c>
       <c r="E52" t="n">
-        <v>26367.24</v>
+        <v>26569.99</v>
       </c>
       <c r="F52" t="n">
-        <v>81.28</v>
+        <v>202.75</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0077</v>
       </c>
       <c r="H52" t="n">
-        <v>161.04</v>
+        <v>151.38</v>
       </c>
       <c r="I52" t="n">
-        <v>25927.08</v>
+        <v>26080.73</v>
       </c>
       <c r="J52" t="n">
-        <v>25993.18</v>
+        <v>26228.67</v>
       </c>
       <c r="K52" t="n">
-        <v>26151.04</v>
+        <v>26286.72</v>
       </c>
       <c r="L52" t="n">
-        <v>26308.9</v>
+        <v>26344.77</v>
       </c>
       <c r="M52" t="n">
-        <v>26420.88</v>
+        <v>26447.76</v>
       </c>
       <c r="N52" t="n">
-        <v>26532.86</v>
+        <v>26550.76</v>
       </c>
       <c r="O52" t="n">
-        <v>26736.6</v>
+        <v>26563.85</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4864,113 +4868,113 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V52" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V52" s="8" t="n">
-        <v/>
-      </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>26494.61</v>
+        <v>26464.14</v>
       </c>
       <c r="C53" t="n">
-        <v>26618.74</v>
+        <v>26471.79</v>
       </c>
       <c r="D53" t="n">
-        <v>26467.36</v>
+        <v>26249.59</v>
       </c>
       <c r="E53" t="n">
-        <v>26569.99</v>
+        <v>26258.11</v>
       </c>
       <c r="F53" t="n">
-        <v>202.75</v>
+        <v>-311.88</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0117</v>
       </c>
       <c r="H53" t="n">
-        <v>151.38</v>
+        <v>222.2</v>
       </c>
       <c r="I53" t="n">
-        <v>26080.73</v>
+        <v>26315.98</v>
       </c>
       <c r="J53" t="n">
-        <v>26228.67</v>
+        <v>26432.08</v>
       </c>
       <c r="K53" t="n">
-        <v>26286.72</v>
+        <v>26494.3</v>
       </c>
       <c r="L53" t="n">
-        <v>26344.77</v>
+        <v>26556.52</v>
       </c>
       <c r="M53" t="n">
-        <v>26447.76</v>
+        <v>26645.68</v>
       </c>
       <c r="N53" t="n">
-        <v>26550.76</v>
+        <v>26734.84</v>
       </c>
       <c r="O53" t="n">
-        <v>26563.85</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+        <v>26770.12</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W53" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W53" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X53" t="inlineStr"/>
@@ -4978,67 +4982,67 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>26464.14</v>
+        <v>26150.75</v>
       </c>
       <c r="C54" t="n">
-        <v>26471.79</v>
+        <v>26206.13</v>
       </c>
       <c r="D54" t="n">
-        <v>26249.59</v>
+        <v>25916.76</v>
       </c>
       <c r="E54" t="n">
-        <v>26258.11</v>
+        <v>25970.11</v>
       </c>
       <c r="F54" t="n">
-        <v>-311.88</v>
+        <v>-288</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.011</v>
       </c>
       <c r="H54" t="n">
-        <v>222.2</v>
+        <v>289.37</v>
       </c>
       <c r="I54" t="n">
-        <v>26315.98</v>
+        <v>26027.39</v>
       </c>
       <c r="J54" t="n">
-        <v>26432.08</v>
+        <v>25984.62</v>
       </c>
       <c r="K54" t="n">
-        <v>26494.3</v>
+        <v>26147.01</v>
       </c>
       <c r="L54" t="n">
-        <v>26556.52</v>
+        <v>26309.4</v>
       </c>
       <c r="M54" t="n">
-        <v>26645.68</v>
+        <v>26369.21</v>
       </c>
       <c r="N54" t="n">
-        <v>26734.84</v>
+        <v>26429.02</v>
       </c>
       <c r="O54" t="n">
-        <v>26770.12</v>
+        <v>26693.99</v>
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
+      <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5062,67 +5066,63 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>26150.75</v>
+        <v>25886.67</v>
       </c>
       <c r="C55" t="n">
-        <v>26206.13</v>
+        <v>25924.21</v>
       </c>
       <c r="D55" t="n">
-        <v>25916.76</v>
+        <v>25727.93</v>
       </c>
       <c r="E55" t="n">
-        <v>25970.11</v>
+        <v>25839.33</v>
       </c>
       <c r="F55" t="n">
-        <v>-288</v>
+        <v>-130.78</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.005</v>
       </c>
       <c r="H55" t="n">
-        <v>289.37</v>
+        <v>196.28</v>
       </c>
       <c r="I55" t="n">
-        <v>26027.39</v>
+        <v>25627.39</v>
       </c>
       <c r="J55" t="n">
-        <v>25984.62</v>
+        <v>25635.07</v>
       </c>
       <c r="K55" t="n">
-        <v>26147.01</v>
+        <v>25825.42</v>
       </c>
       <c r="L55" t="n">
-        <v>26309.4</v>
+        <v>26015.78</v>
       </c>
       <c r="M55" t="n">
-        <v>26369.21</v>
+        <v>26114.79</v>
       </c>
       <c r="N55" t="n">
-        <v>26429.02</v>
+        <v>26213.81</v>
       </c>
       <c r="O55" t="n">
-        <v>26693.99</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q55" s="6" t="inlineStr">
+        <v>26495.5</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
+      <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5146,50 +5146,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25886.67</v>
+        <v>25840.92</v>
       </c>
       <c r="C56" t="n">
-        <v>25924.21</v>
+        <v>26007.79</v>
       </c>
       <c r="D56" t="n">
-        <v>25727.93</v>
+        <v>25784.84</v>
       </c>
       <c r="E56" t="n">
-        <v>25839.33</v>
+        <v>26003.32</v>
       </c>
       <c r="F56" t="n">
-        <v>-130.78</v>
+        <v>163.99</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0063</v>
       </c>
       <c r="H56" t="n">
-        <v>196.28</v>
+        <v>222.95</v>
       </c>
       <c r="I56" t="n">
-        <v>25627.39</v>
+        <v>25531.65</v>
       </c>
       <c r="J56" t="n">
-        <v>25635.07</v>
+        <v>25649.68</v>
       </c>
       <c r="K56" t="n">
-        <v>25825.42</v>
+        <v>25741.19</v>
       </c>
       <c r="L56" t="n">
-        <v>26015.78</v>
+        <v>25832.7</v>
       </c>
       <c r="M56" t="n">
-        <v>26114.79</v>
+        <v>25937.47</v>
       </c>
       <c r="N56" t="n">
-        <v>26213.81</v>
+        <v>26042.24</v>
       </c>
       <c r="O56" t="n">
-        <v>26495.5</v>
+        <v>26120.49</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5197,22 +5197,24 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
@@ -5221,55 +5223,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25840.92</v>
+        <v>25985.86</v>
       </c>
       <c r="C57" t="n">
-        <v>26007.79</v>
+        <v>26167.93</v>
       </c>
       <c r="D57" t="n">
-        <v>25784.84</v>
+        <v>25958.7</v>
       </c>
       <c r="E57" t="n">
-        <v>26003.32</v>
+        <v>26046.4</v>
       </c>
       <c r="F57" t="n">
-        <v>163.99</v>
+        <v>43.08</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0017</v>
       </c>
       <c r="H57" t="n">
-        <v>222.95</v>
+        <v>209.23</v>
       </c>
       <c r="I57" t="n">
-        <v>25531.65</v>
+        <v>25561.89</v>
       </c>
       <c r="J57" t="n">
-        <v>25649.68</v>
+        <v>25833.87</v>
       </c>
       <c r="K57" t="n">
-        <v>25741.19</v>
+        <v>25891.85</v>
       </c>
       <c r="L57" t="n">
-        <v>25832.7</v>
+        <v>25949.82</v>
       </c>
       <c r="M57" t="n">
-        <v>25937.47</v>
+        <v>26114.79</v>
       </c>
       <c r="N57" t="n">
-        <v>26042.24</v>
+        <v>26279.77</v>
       </c>
       <c r="O57" t="n">
-        <v>26120.49</v>
+        <v>26230.74</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5280,20 +5286,18 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5312,50 +5316,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>25985.86</v>
+        <v>26039.54</v>
       </c>
       <c r="C58" t="n">
-        <v>26167.93</v>
+        <v>26069.99</v>
       </c>
       <c r="D58" t="n">
-        <v>25958.7</v>
+        <v>25919.61</v>
       </c>
       <c r="E58" t="n">
-        <v>26046.4</v>
+        <v>26006.53</v>
       </c>
       <c r="F58" t="n">
-        <v>43.08</v>
+        <v>-39.87</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0015</v>
       </c>
       <c r="H58" t="n">
-        <v>209.23</v>
+        <v>150.38</v>
       </c>
       <c r="I58" t="n">
-        <v>25561.89</v>
+        <v>25749.47</v>
       </c>
       <c r="J58" t="n">
-        <v>25833.87</v>
+        <v>25828.71</v>
       </c>
       <c r="K58" t="n">
-        <v>25891.85</v>
+        <v>25941.79</v>
       </c>
       <c r="L58" t="n">
-        <v>25949.82</v>
+        <v>26054.86</v>
       </c>
       <c r="M58" t="n">
-        <v>26114.79</v>
+        <v>26151.02</v>
       </c>
       <c r="N58" t="n">
-        <v>26279.77</v>
+        <v>26247.17</v>
       </c>
       <c r="O58" t="n">
-        <v>26230.74</v>
+        <v>26377.16</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5363,18 +5367,18 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5387,65 +5391,63 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>26039.54</v>
+        <v>25897.22</v>
       </c>
       <c r="C59" t="n">
-        <v>26069.99</v>
+        <v>26026.78</v>
       </c>
       <c r="D59" t="n">
-        <v>25919.61</v>
+        <v>25799.66</v>
       </c>
       <c r="E59" t="n">
-        <v>26006.53</v>
+        <v>26007.63</v>
       </c>
       <c r="F59" t="n">
-        <v>-39.87</v>
+        <v>1.1</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>150.38</v>
+        <v>227.12</v>
       </c>
       <c r="I59" t="n">
-        <v>25749.47</v>
+        <v>25769.23</v>
       </c>
       <c r="J59" t="n">
-        <v>25828.71</v>
+        <v>25862.01</v>
       </c>
       <c r="K59" t="n">
-        <v>25941.79</v>
+        <v>25931.34</v>
       </c>
       <c r="L59" t="n">
-        <v>26054.86</v>
+        <v>26000.66</v>
       </c>
       <c r="M59" t="n">
-        <v>26151.02</v>
+        <v>26081.72</v>
       </c>
       <c r="N59" t="n">
-        <v>26247.17</v>
+        <v>26162.77</v>
       </c>
       <c r="O59" t="n">
-        <v>26377.16</v>
+        <v>26220.37</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
@@ -5454,7 +5456,7 @@
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5471,58 +5473,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25897.22</v>
+        <v>25870.98</v>
       </c>
       <c r="C60" t="n">
-        <v>26026.78</v>
+        <v>25909.66</v>
       </c>
       <c r="D60" t="n">
-        <v>25799.66</v>
+        <v>25512.39</v>
       </c>
       <c r="E60" t="n">
-        <v>26007.63</v>
+        <v>25576.45</v>
       </c>
       <c r="F60" t="n">
-        <v>1.1</v>
+        <v>-431.18</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0</v>
+        <v>-0.0166</v>
       </c>
       <c r="H60" t="n">
-        <v>227.12</v>
+        <v>397.27</v>
       </c>
       <c r="I60" t="n">
-        <v>25769.23</v>
+        <v>25572.54</v>
       </c>
       <c r="J60" t="n">
-        <v>25862.01</v>
+        <v>25827.72</v>
       </c>
       <c r="K60" t="n">
-        <v>25931.34</v>
+        <v>25894.07</v>
       </c>
       <c r="L60" t="n">
-        <v>26000.66</v>
+        <v>25960.43</v>
       </c>
       <c r="M60" t="n">
-        <v>26081.72</v>
+        <v>26121.19</v>
       </c>
       <c r="N60" t="n">
-        <v>26162.77</v>
+        <v>26281.96</v>
       </c>
       <c r="O60" t="n">
-        <v>26220.37</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
+        <v>26253.9</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q60" s="6" t="inlineStr">
         <is>
@@ -5536,7 +5544,7 @@
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5553,76 +5561,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>25870.98</v>
+        <v>25555.66</v>
       </c>
       <c r="C61" t="n">
-        <v>25909.66</v>
+        <v>25612.09</v>
       </c>
       <c r="D61" t="n">
-        <v>25512.39</v>
+        <v>25361.15</v>
       </c>
       <c r="E61" t="n">
-        <v>25576.45</v>
+        <v>25361.15</v>
       </c>
       <c r="F61" t="n">
-        <v>-431.18</v>
+        <v>-215.3</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>397.27</v>
+        <v>250.94</v>
       </c>
       <c r="I61" t="n">
-        <v>25572.54</v>
+        <v>25115.12</v>
       </c>
       <c r="J61" t="n">
-        <v>25827.72</v>
+        <v>25111.89</v>
       </c>
       <c r="K61" t="n">
-        <v>25894.07</v>
+        <v>25377.81</v>
       </c>
       <c r="L61" t="n">
-        <v>25960.43</v>
+        <v>25643.74</v>
       </c>
       <c r="M61" t="n">
-        <v>26121.19</v>
+        <v>25775.08</v>
       </c>
       <c r="N61" t="n">
-        <v>26281.96</v>
+        <v>25906.43</v>
       </c>
       <c r="O61" t="n">
-        <v>26253.9</v>
-      </c>
-      <c r="P61" s="6" t="inlineStr">
+        <v>26306.93</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="S61" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5646,50 +5646,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>25555.66</v>
+        <v>25478.84</v>
       </c>
       <c r="C62" t="n">
-        <v>25612.09</v>
+        <v>25581.22</v>
       </c>
       <c r="D62" t="n">
-        <v>25361.15</v>
+        <v>25396.38</v>
       </c>
       <c r="E62" t="n">
-        <v>25361.15</v>
+        <v>25568.56</v>
       </c>
       <c r="F62" t="n">
-        <v>-215.3</v>
+        <v>207.41</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>250.94</v>
+        <v>184.84</v>
       </c>
       <c r="I62" t="n">
-        <v>25115.12</v>
+        <v>25110.21</v>
       </c>
       <c r="J62" t="n">
-        <v>25111.89</v>
+        <v>25047.48</v>
       </c>
       <c r="K62" t="n">
-        <v>25377.81</v>
+        <v>25235.68</v>
       </c>
       <c r="L62" t="n">
-        <v>25643.74</v>
+        <v>25423.89</v>
       </c>
       <c r="M62" t="n">
-        <v>25775.08</v>
+        <v>25486.62</v>
       </c>
       <c r="N62" t="n">
-        <v>25906.43</v>
+        <v>25549.35</v>
       </c>
       <c r="O62" t="n">
-        <v>26306.93</v>
+        <v>25863.03</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5697,103 +5697,109 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>25478.84</v>
+        <v>25498.74</v>
       </c>
       <c r="C63" t="n">
-        <v>25581.22</v>
+        <v>25548.78</v>
       </c>
       <c r="D63" t="n">
-        <v>25396.38</v>
+        <v>25325.52</v>
       </c>
       <c r="E63" t="n">
-        <v>25568.56</v>
+        <v>25440.81</v>
       </c>
       <c r="F63" t="n">
-        <v>207.41</v>
+        <v>-127.75</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.005</v>
       </c>
       <c r="H63" t="n">
-        <v>184.84</v>
+        <v>223.26</v>
       </c>
       <c r="I63" t="n">
-        <v>25110.21</v>
+        <v>25211.54</v>
       </c>
       <c r="J63" t="n">
-        <v>25047.48</v>
+        <v>25423.6</v>
       </c>
       <c r="K63" t="n">
-        <v>25235.68</v>
+        <v>25476.14</v>
       </c>
       <c r="L63" t="n">
-        <v>25423.89</v>
+        <v>25528.68</v>
       </c>
       <c r="M63" t="n">
-        <v>25486.62</v>
+        <v>25660.98</v>
       </c>
       <c r="N63" t="n">
-        <v>25549.35</v>
+        <v>25793.28</v>
       </c>
       <c r="O63" t="n">
-        <v>25863.03</v>
+        <v>25766.06</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
       </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S63" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
       </c>
       <c r="V63" s="8" t="n">
         <v/>
@@ -5805,64 +5811,66 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>25498.74</v>
+        <v>25360.32</v>
       </c>
       <c r="C64" t="n">
-        <v>25548.78</v>
+        <v>25478.98</v>
       </c>
       <c r="D64" t="n">
-        <v>25325.52</v>
+        <v>25172.89</v>
       </c>
       <c r="E64" t="n">
-        <v>25440.81</v>
+        <v/>
       </c>
       <c r="F64" t="n">
-        <v>-127.75</v>
+        <v/>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.005</v>
+        <v/>
       </c>
       <c r="H64" t="n">
-        <v>223.26</v>
+        <v>306.09</v>
       </c>
       <c r="I64" t="n">
-        <v>25211.54</v>
+        <v>25102.26</v>
       </c>
       <c r="J64" t="n">
-        <v>25423.6</v>
+        <v>25219.38</v>
       </c>
       <c r="K64" t="n">
-        <v>25476.14</v>
+        <v>25329.18</v>
       </c>
       <c r="L64" t="n">
-        <v>25528.68</v>
+        <v>25438.98</v>
       </c>
       <c r="M64" t="n">
-        <v>25660.98</v>
+        <v>25552.44</v>
       </c>
       <c r="N64" t="n">
-        <v>25793.28</v>
+        <v>25665.9</v>
       </c>
       <c r="O64" t="n">
-        <v>25766.06</v>
-      </c>
-      <c r="P64" s="6" t="n">
-        <v/>
+        <v>25772.04</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q64" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
@@ -5870,9 +5878,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S64" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S64" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T64" s="8" t="n">
@@ -5891,123 +5899,35 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>25360.32</v>
-      </c>
-      <c r="C65" t="n">
-        <v>25478.98</v>
-      </c>
-      <c r="D65" t="n">
-        <v>25172.89</v>
-      </c>
-      <c r="E65" t="n">
-        <v/>
-      </c>
-      <c r="F65" t="n">
-        <v/>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H65" t="n">
-        <v>306.09</v>
-      </c>
-      <c r="I65" t="n">
-        <v>25102.26</v>
-      </c>
-      <c r="J65" t="n">
-        <v>25219.38</v>
-      </c>
-      <c r="K65" t="n">
-        <v>25329.18</v>
-      </c>
-      <c r="L65" t="n">
-        <v>25438.98</v>
-      </c>
-      <c r="M65" t="n">
-        <v>25552.44</v>
-      </c>
-      <c r="N65" t="n">
-        <v>25665.9</v>
-      </c>
-      <c r="O65" t="n">
-        <v>25772.04</v>
-      </c>
-      <c r="P65" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q65" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R65" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S65" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W65" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="13" t="inlineStr">
+      <c r="A65" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I66" s="14" t="n">
+      <c r="I65" s="14" t="n">
         <v>24866.8</v>
       </c>
-      <c r="J66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O66" s="14" t="n">
+      <c r="J65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O65" s="14" t="n">
         <v>25785.07</v>
       </c>
     </row>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,9 +120,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -5831,13 +5828,13 @@
         <v>25172.89</v>
       </c>
       <c r="E64" t="n">
-        <v/>
+        <v>25402.28</v>
       </c>
       <c r="F64" t="n">
-        <v/>
+        <v>-38.53</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v/>
+        <v>-0.0015</v>
       </c>
       <c r="H64" t="n">
         <v>306.09</v>
@@ -5863,10 +5860,8 @@
       <c r="O64" t="n">
         <v>25772.04</v>
       </c>
-      <c r="P64" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P64" s="6" t="n">
+        <v/>
       </c>
       <c r="Q64" s="6" t="inlineStr">
         <is>
@@ -5878,9 +5873,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S64" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T64" s="8" t="n">
@@ -5899,35 +5894,35 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="13" t="inlineStr">
+      <c r="A65" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I65" s="14" t="n">
+      <c r="I65" s="13" t="n">
         <v>24866.8</v>
       </c>
-      <c r="J65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O65" s="14" t="n">
+      <c r="J65" s="13" t="n">
+        <v>25134.36</v>
+      </c>
+      <c r="K65" s="13" t="n">
+        <v>25249.23</v>
+      </c>
+      <c r="L65" s="13" t="n">
+        <v>25364.11</v>
+      </c>
+      <c r="M65" s="13" t="n">
+        <v>25555.32</v>
+      </c>
+      <c r="N65" s="13" t="n">
+        <v>25746.54</v>
+      </c>
+      <c r="O65" s="13" t="n">
         <v>25785.07</v>
       </c>
     </row>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X65"/>
+  <dimension ref="A1:X66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5899,31 +5899,111 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>25515.96</v>
+      </c>
+      <c r="C65" t="n">
+        <v>25524.04</v>
+      </c>
+      <c r="D65" t="n">
+        <v>25361.7</v>
+      </c>
+      <c r="E65" t="n">
+        <v>25492</v>
+      </c>
+      <c r="F65" t="n">
+        <v>89.72</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="H65" t="n">
+        <v>162.34</v>
+      </c>
+      <c r="I65" t="n">
+        <v>24866.8</v>
+      </c>
+      <c r="J65" t="n">
+        <v>25134.36</v>
+      </c>
+      <c r="K65" t="n">
+        <v>25249.23</v>
+      </c>
+      <c r="L65" t="n">
+        <v>25364.11</v>
+      </c>
+      <c r="M65" t="n">
+        <v>25555.32</v>
+      </c>
+      <c r="N65" t="n">
+        <v>25746.54</v>
+      </c>
+      <c r="O65" t="n">
+        <v>25785.07</v>
+      </c>
+      <c r="P65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S65" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W65" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I65" s="13" t="n">
-        <v>24866.8</v>
-      </c>
-      <c r="J65" s="13" t="n">
-        <v>25134.36</v>
-      </c>
-      <c r="K65" s="13" t="n">
-        <v>25249.23</v>
-      </c>
-      <c r="L65" s="13" t="n">
-        <v>25364.11</v>
-      </c>
-      <c r="M65" s="13" t="n">
-        <v>25555.32</v>
-      </c>
-      <c r="N65" s="13" t="n">
-        <v>25746.54</v>
-      </c>
-      <c r="O65" s="13" t="n">
-        <v>25785.07</v>
+      <c r="I66" s="13" t="n">
+        <v>25199.36</v>
+      </c>
+      <c r="J66" s="13" t="n">
+        <v>25354.23</v>
+      </c>
+      <c r="K66" s="13" t="n">
+        <v>25410.83</v>
+      </c>
+      <c r="L66" s="13" t="n">
+        <v>25467.43</v>
+      </c>
+      <c r="M66" s="13" t="n">
+        <v>25573.17</v>
+      </c>
+      <c r="N66" s="13" t="n">
+        <v>25678.91</v>
+      </c>
+      <c r="O66" s="13" t="n">
+        <v>25686.38</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -5914,13 +5914,13 @@
         <v>25361.7</v>
       </c>
       <c r="E65" t="n">
-        <v>25492</v>
+        <v>25499.35</v>
       </c>
       <c r="F65" t="n">
-        <v>89.72</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0038</v>
       </c>
       <c r="H65" t="n">
         <v>162.34</v>
@@ -5988,19 +5988,19 @@
         <v>25199.36</v>
       </c>
       <c r="J66" s="13" t="n">
-        <v>25354.23</v>
+        <v>25365.25</v>
       </c>
       <c r="K66" s="13" t="n">
-        <v>25410.83</v>
+        <v>25418.18</v>
       </c>
       <c r="L66" s="13" t="n">
-        <v>25467.43</v>
+        <v>25471.11</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>25573.17</v>
+        <v>25580.52</v>
       </c>
       <c r="N66" s="13" t="n">
-        <v>25678.91</v>
+        <v>25689.93</v>
       </c>
       <c r="O66" s="13" t="n">
         <v>25686.38</v>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -5914,13 +5914,13 @@
         <v>25361.7</v>
       </c>
       <c r="E65" t="n">
-        <v>25499.35</v>
+        <v>25509.65</v>
       </c>
       <c r="F65" t="n">
-        <v>97.06999999999999</v>
+        <v>107.37</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0042</v>
       </c>
       <c r="H65" t="n">
         <v>162.34</v>
@@ -5988,19 +5988,19 @@
         <v>25199.36</v>
       </c>
       <c r="J66" s="13" t="n">
-        <v>25365.25</v>
+        <v>25380.7</v>
       </c>
       <c r="K66" s="13" t="n">
-        <v>25418.18</v>
+        <v>25428.48</v>
       </c>
       <c r="L66" s="13" t="n">
-        <v>25471.11</v>
+        <v>25476.26</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>25580.52</v>
+        <v>25590.82</v>
       </c>
       <c r="N66" s="13" t="n">
-        <v>25689.93</v>
+        <v>25705.38</v>
       </c>
       <c r="O66" s="13" t="n">
         <v>25686.38</v>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -5908,22 +5911,22 @@
         <v>25515.96</v>
       </c>
       <c r="C65" t="n">
-        <v>25524.04</v>
+        <v>25599.07</v>
       </c>
       <c r="D65" t="n">
         <v>25361.7</v>
       </c>
       <c r="E65" t="n">
-        <v>25509.65</v>
+        <v/>
       </c>
       <c r="F65" t="n">
-        <v>107.37</v>
+        <v/>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0042</v>
+        <v/>
       </c>
       <c r="H65" t="n">
-        <v>162.34</v>
+        <v>237.37</v>
       </c>
       <c r="I65" t="n">
         <v>24866.8</v>
@@ -5946,8 +5949,10 @@
       <c r="O65" t="n">
         <v>25785.07</v>
       </c>
-      <c r="P65" s="6" t="n">
-        <v/>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q65" s="6" t="n">
         <v/>
@@ -5955,14 +5960,14 @@
       <c r="R65" s="6" t="n">
         <v/>
       </c>
-      <c r="S65" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S65" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T65" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U65" s="8" t="n">
@@ -5979,31 +5984,31 @@
       <c r="X65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="12" t="inlineStr">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I66" s="13" t="n">
-        <v>25199.36</v>
-      </c>
-      <c r="J66" s="13" t="n">
-        <v>25380.7</v>
-      </c>
-      <c r="K66" s="13" t="n">
-        <v>25428.48</v>
-      </c>
-      <c r="L66" s="13" t="n">
-        <v>25476.26</v>
-      </c>
-      <c r="M66" s="13" t="n">
-        <v>25590.82</v>
-      </c>
-      <c r="N66" s="13" t="n">
-        <v>25705.38</v>
-      </c>
-      <c r="O66" s="13" t="n">
-        <v>25686.38</v>
+      <c r="I66" s="14" t="n">
+        <v>25124.33</v>
+      </c>
+      <c r="J66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O66" s="14" t="n">
+        <v>25836.44</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -109,14 +109,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X66"/>
+  <dimension ref="A1:X65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -644,50 +644,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25075.33</v>
+        <v>25035.93</v>
       </c>
       <c r="C2" t="n">
-        <v>25173.02</v>
+        <v>25176.21</v>
       </c>
       <c r="D2" t="n">
-        <v>24951.54</v>
+        <v>24896.19</v>
       </c>
       <c r="E2" t="n">
-        <v>24985.82</v>
+        <v>25139.69</v>
       </c>
       <c r="F2" t="n">
-        <v>-40.98</v>
+        <v>153.87</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0062</v>
       </c>
       <c r="H2" t="n">
-        <v>221.48</v>
+        <v>280.02</v>
       </c>
       <c r="I2" t="n">
-        <v>24621.17</v>
+        <v>24730.06</v>
       </c>
       <c r="J2" t="n">
-        <v>24846.19</v>
+        <v>24726.11</v>
       </c>
       <c r="K2" t="n">
-        <v>24917.25</v>
+        <v>24875.08</v>
       </c>
       <c r="L2" t="n">
-        <v>24988.31</v>
+        <v>25024.05</v>
       </c>
       <c r="M2" t="n">
-        <v>25136.35</v>
+        <v>25096.56</v>
       </c>
       <c r="N2" t="n">
-        <v>25284.39</v>
+        <v>25169.07</v>
       </c>
       <c r="O2" t="n">
-        <v>25278.47</v>
+        <v>25394.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -700,7 +700,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
@@ -708,8 +708,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -728,151 +730,147 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25035.93</v>
+        <v>24835.56</v>
       </c>
       <c r="C3" t="n">
-        <v>25176.21</v>
+        <v>24988.71</v>
       </c>
       <c r="D3" t="n">
-        <v>24896.19</v>
+        <v>24728.57</v>
       </c>
       <c r="E3" t="n">
-        <v>25139.69</v>
+        <v>24893.58</v>
       </c>
       <c r="F3" t="n">
-        <v>153.87</v>
+        <v>-246.11</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0098</v>
       </c>
       <c r="H3" t="n">
-        <v>280.02</v>
+        <v>260.14</v>
       </c>
       <c r="I3" t="n">
-        <v>24730.06</v>
+        <v>24616.17</v>
       </c>
       <c r="J3" t="n">
-        <v>24726.11</v>
+        <v>24911.41</v>
       </c>
       <c r="K3" t="n">
-        <v>24875.08</v>
+        <v>24999.68</v>
       </c>
       <c r="L3" t="n">
-        <v>25024.05</v>
+        <v>25087.94</v>
       </c>
       <c r="M3" t="n">
-        <v>25096.56</v>
+        <v>25279.7</v>
       </c>
       <c r="N3" t="n">
-        <v>25169.07</v>
+        <v>25471.46</v>
       </c>
       <c r="O3" t="n">
-        <v>25394.5</v>
+        <v>25456.23</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24835.56</v>
+        <v>24790.7</v>
       </c>
       <c r="C4" t="n">
-        <v>24988.71</v>
+        <v>24800.66</v>
       </c>
       <c r="D4" t="n">
-        <v>24728.57</v>
+        <v>24593.48</v>
       </c>
       <c r="E4" t="n">
-        <v>24893.58</v>
+        <v>24740.36</v>
       </c>
       <c r="F4" t="n">
-        <v>-246.11</v>
+        <v>-153.22</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0062</v>
       </c>
       <c r="H4" t="n">
-        <v>260.14</v>
+        <v>207.18</v>
       </c>
       <c r="I4" t="n">
-        <v>24616.17</v>
+        <v>24468.43</v>
       </c>
       <c r="J4" t="n">
-        <v>24911.41</v>
+        <v>24650.91</v>
       </c>
       <c r="K4" t="n">
-        <v>24999.68</v>
+        <v>24763.51</v>
       </c>
       <c r="L4" t="n">
-        <v>25087.94</v>
+        <v>24876.11</v>
       </c>
       <c r="M4" t="n">
-        <v>25279.7</v>
+        <v>25023.65</v>
       </c>
       <c r="N4" t="n">
-        <v>25471.46</v>
+        <v>25171.19</v>
       </c>
       <c r="O4" t="n">
-        <v>25456.23</v>
+        <v>25248.85</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
       <c r="Q4" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -896,81 +894,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24790.7</v>
+        <v>24810</v>
       </c>
       <c r="C5" t="n">
-        <v>24800.66</v>
+        <v>25088.28</v>
       </c>
       <c r="D5" t="n">
-        <v>24593.48</v>
+        <v>24761.72</v>
       </c>
       <c r="E5" t="n">
-        <v>24740.36</v>
+        <v>24994.83</v>
       </c>
       <c r="F5" t="n">
-        <v>-153.22</v>
+        <v>254.47</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0103</v>
       </c>
       <c r="H5" t="n">
-        <v>207.18</v>
+        <v>326.56</v>
       </c>
       <c r="I5" t="n">
-        <v>24468.43</v>
+        <v>24386.3</v>
       </c>
       <c r="J5" t="n">
-        <v>24650.91</v>
+        <v>24554.82</v>
       </c>
       <c r="K5" t="n">
-        <v>24763.51</v>
+        <v>24636.77</v>
       </c>
       <c r="L5" t="n">
-        <v>24876.11</v>
+        <v>24718.71</v>
       </c>
       <c r="M5" t="n">
-        <v>25023.65</v>
+        <v>24843.95</v>
       </c>
       <c r="N5" t="n">
-        <v>25171.19</v>
+        <v>24969.18</v>
       </c>
       <c r="O5" t="n">
-        <v>25248.85</v>
+        <v>25007.84</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W5" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W5" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -978,83 +978,81 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24810</v>
+        <v>24848.51</v>
       </c>
       <c r="C6" t="n">
-        <v>25088.28</v>
+        <v>24869.63</v>
       </c>
       <c r="D6" t="n">
-        <v>24761.72</v>
+        <v>24547.7</v>
       </c>
       <c r="E6" t="n">
-        <v>24994.83</v>
+        <v>24671.22</v>
       </c>
       <c r="F6" t="n">
-        <v>254.47</v>
+        <v>-323.61</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.0129</v>
       </c>
       <c r="H6" t="n">
-        <v>326.56</v>
+        <v>321.93</v>
       </c>
       <c r="I6" t="n">
-        <v>24386.3</v>
+        <v>24435.16</v>
       </c>
       <c r="J6" t="n">
-        <v>24554.82</v>
+        <v>24703.19</v>
       </c>
       <c r="K6" t="n">
-        <v>24636.77</v>
+        <v>24831.55</v>
       </c>
       <c r="L6" t="n">
-        <v>24718.71</v>
+        <v>24959.92</v>
       </c>
       <c r="M6" t="n">
-        <v>24843.95</v>
+        <v>25158.11</v>
       </c>
       <c r="N6" t="n">
-        <v>24969.18</v>
+        <v>25356.3</v>
       </c>
       <c r="O6" t="n">
-        <v>25007.84</v>
+        <v>25414.84</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1062,67 +1060,63 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24848.51</v>
+        <v>24724.34</v>
       </c>
       <c r="C7" t="n">
-        <v>24869.63</v>
+        <v>24762.24</v>
       </c>
       <c r="D7" t="n">
-        <v>24547.7</v>
+        <v>24556.78</v>
       </c>
       <c r="E7" t="n">
-        <v>24671.22</v>
+        <v>24626.89</v>
       </c>
       <c r="F7" t="n">
-        <v>-323.61</v>
+        <v>-44.33</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0018</v>
       </c>
       <c r="H7" t="n">
-        <v>321.93</v>
+        <v>205.46</v>
       </c>
       <c r="I7" t="n">
-        <v>24435.16</v>
+        <v>24225.77</v>
       </c>
       <c r="J7" t="n">
-        <v>24703.19</v>
+        <v>24330.57</v>
       </c>
       <c r="K7" t="n">
-        <v>24831.55</v>
+        <v>24510.25</v>
       </c>
       <c r="L7" t="n">
-        <v>24959.92</v>
+        <v>24689.94</v>
       </c>
       <c r="M7" t="n">
-        <v>25158.11</v>
+        <v>24832.19</v>
       </c>
       <c r="N7" t="n">
-        <v>25356.3</v>
+        <v>24974.43</v>
       </c>
       <c r="O7" t="n">
-        <v>25414.84</v>
+        <v>25191.56</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1139,55 +1133,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24724.34</v>
+        <v>24815.22</v>
       </c>
       <c r="C8" t="n">
-        <v>24762.24</v>
+        <v>25024.27</v>
       </c>
       <c r="D8" t="n">
-        <v>24556.78</v>
+        <v>24794.84</v>
       </c>
       <c r="E8" t="n">
-        <v>24626.89</v>
+        <v>24995.81</v>
       </c>
       <c r="F8" t="n">
-        <v>-44.33</v>
+        <v>368.92</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.015</v>
       </c>
       <c r="H8" t="n">
-        <v>205.46</v>
+        <v>229.43</v>
       </c>
       <c r="I8" t="n">
-        <v>24225.77</v>
+        <v>24351.32</v>
       </c>
       <c r="J8" t="n">
-        <v>24330.57</v>
+        <v>24405.12</v>
       </c>
       <c r="K8" t="n">
-        <v>24510.25</v>
+        <v>24524.16</v>
       </c>
       <c r="L8" t="n">
-        <v>24689.94</v>
+        <v>24643.2</v>
       </c>
       <c r="M8" t="n">
-        <v>24832.19</v>
+        <v>24729.62</v>
       </c>
       <c r="N8" t="n">
-        <v>24974.43</v>
+        <v>24816.04</v>
       </c>
       <c r="O8" t="n">
-        <v>25191.56</v>
+        <v>24967.7</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1200,76 +1198,78 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W8" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W8" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24815.22</v>
+        <v>25028.93</v>
       </c>
       <c r="C9" t="n">
-        <v>25024.27</v>
+        <v>25095.66</v>
       </c>
       <c r="D9" t="n">
-        <v>24794.84</v>
+        <v>24887</v>
       </c>
       <c r="E9" t="n">
-        <v>24995.81</v>
+        <v>25040.28</v>
       </c>
       <c r="F9" t="n">
-        <v>368.92</v>
+        <v>44.47</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.015</v>
+        <v>0.0018</v>
       </c>
       <c r="H9" t="n">
-        <v>229.43</v>
+        <v>208.66</v>
       </c>
       <c r="I9" t="n">
-        <v>24351.32</v>
+        <v>24565.41</v>
       </c>
       <c r="J9" t="n">
-        <v>24405.12</v>
+        <v>24809.51</v>
       </c>
       <c r="K9" t="n">
-        <v>24524.16</v>
+        <v>24881.1</v>
       </c>
       <c r="L9" t="n">
-        <v>24643.2</v>
+        <v>24952.68</v>
       </c>
       <c r="M9" t="n">
-        <v>24729.62</v>
+        <v>25110.53</v>
       </c>
       <c r="N9" t="n">
-        <v>24816.04</v>
+        <v>25268.37</v>
       </c>
       <c r="O9" t="n">
-        <v>24967.7</v>
+        <v>25253.7</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1280,25 +1280,21 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
@@ -1310,50 +1306,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25028.93</v>
+        <v>25025.13</v>
       </c>
       <c r="C10" t="n">
-        <v>25095.66</v>
+        <v>25655.82</v>
       </c>
       <c r="D10" t="n">
-        <v>24887</v>
+        <v>24994.64</v>
       </c>
       <c r="E10" t="n">
-        <v>25040.28</v>
+        <v>25580.88</v>
       </c>
       <c r="F10" t="n">
-        <v>44.47</v>
+        <v>540.6</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0216</v>
       </c>
       <c r="H10" t="n">
-        <v>208.66</v>
+        <v>661.1799999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>24565.41</v>
+        <v>24678.34</v>
       </c>
       <c r="J10" t="n">
-        <v>24809.51</v>
+        <v>24856.09</v>
       </c>
       <c r="K10" t="n">
-        <v>24881.1</v>
+        <v>24935.95</v>
       </c>
       <c r="L10" t="n">
-        <v>24952.68</v>
+        <v>25015.8</v>
       </c>
       <c r="M10" t="n">
-        <v>25110.53</v>
+        <v>25144.61</v>
       </c>
       <c r="N10" t="n">
-        <v>25268.37</v>
+        <v>25273.41</v>
       </c>
       <c r="O10" t="n">
-        <v>25253.7</v>
+        <v>25304.32</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1364,21 +1360,25 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v/>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
@@ -1390,50 +1390,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25025.13</v>
+        <v>25763.97</v>
       </c>
       <c r="C11" t="n">
-        <v>25655.82</v>
+        <v>25826.78</v>
       </c>
       <c r="D11" t="n">
-        <v>24994.64</v>
+        <v>25611.69</v>
       </c>
       <c r="E11" t="n">
-        <v>25580.88</v>
+        <v>25779.31</v>
       </c>
       <c r="F11" t="n">
-        <v>540.6</v>
+        <v>198.43</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0216</v>
+        <v>0.0078</v>
       </c>
       <c r="H11" t="n">
-        <v>661.1799999999999</v>
+        <v>215.09</v>
       </c>
       <c r="I11" t="n">
-        <v>24678.34</v>
+        <v>24333.46</v>
       </c>
       <c r="J11" t="n">
-        <v>24856.09</v>
+        <v>25047.53</v>
       </c>
       <c r="K11" t="n">
-        <v>24935.95</v>
+        <v>25250.29</v>
       </c>
       <c r="L11" t="n">
-        <v>25015.8</v>
+        <v>25453.06</v>
       </c>
       <c r="M11" t="n">
-        <v>25144.61</v>
+        <v>25911.47</v>
       </c>
       <c r="N11" t="n">
-        <v>25273.41</v>
+        <v>26369.89</v>
       </c>
       <c r="O11" t="n">
-        <v>25304.32</v>
+        <v>26317</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1444,25 +1444,21 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v/>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
@@ -1474,50 +1470,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25763.97</v>
+        <v>25811.9</v>
       </c>
       <c r="C12" t="n">
-        <v>25826.78</v>
+        <v>25900.1</v>
       </c>
       <c r="D12" t="n">
-        <v>25611.69</v>
+        <v>25698.56</v>
       </c>
       <c r="E12" t="n">
-        <v>25779.31</v>
+        <v>25817.89</v>
       </c>
       <c r="F12" t="n">
-        <v>198.43</v>
+        <v>38.58</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0078</v>
+        <v>0.0015</v>
       </c>
       <c r="H12" t="n">
-        <v>215.09</v>
+        <v>201.54</v>
       </c>
       <c r="I12" t="n">
-        <v>24333.46</v>
+        <v>25396.6</v>
       </c>
       <c r="J12" t="n">
-        <v>25047.53</v>
+        <v>25594.26</v>
       </c>
       <c r="K12" t="n">
-        <v>25250.29</v>
+        <v>25671.77</v>
       </c>
       <c r="L12" t="n">
-        <v>25453.06</v>
+        <v>25749.27</v>
       </c>
       <c r="M12" t="n">
-        <v>25911.47</v>
+        <v>25886.86</v>
       </c>
       <c r="N12" t="n">
-        <v>26369.89</v>
+        <v>26024.44</v>
       </c>
       <c r="O12" t="n">
-        <v>26317</v>
+        <v>26041.87</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1528,14 +1524,14 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U12" s="8" t="n">
@@ -1554,69 +1550,73 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25811.9</v>
+        <v>25770.45</v>
       </c>
       <c r="C13" t="n">
-        <v>25900.1</v>
+        <v>25811.97</v>
       </c>
       <c r="D13" t="n">
-        <v>25698.56</v>
+        <v>25465.12</v>
       </c>
       <c r="E13" t="n">
-        <v>25817.89</v>
+        <v>25465.25</v>
       </c>
       <c r="F13" t="n">
-        <v>38.58</v>
+        <v>-352.64</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0137</v>
       </c>
       <c r="H13" t="n">
-        <v>201.54</v>
+        <v>346.85</v>
       </c>
       <c r="I13" t="n">
-        <v>25396.6</v>
+        <v>25497.02</v>
       </c>
       <c r="J13" t="n">
-        <v>25594.26</v>
+        <v>25625.63</v>
       </c>
       <c r="K13" t="n">
-        <v>25671.77</v>
+        <v>25717.12</v>
       </c>
       <c r="L13" t="n">
-        <v>25749.27</v>
+        <v>25808.61</v>
       </c>
       <c r="M13" t="n">
-        <v>25886.86</v>
+        <v>25918.66</v>
       </c>
       <c r="N13" t="n">
-        <v>26024.44</v>
+        <v>26028.71</v>
       </c>
       <c r="O13" t="n">
-        <v>26041.87</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+        <v>26101.64</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1624,9 +1624,9 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W13" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
@@ -1634,67 +1634,67 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25770.45</v>
+        <v>25274.94</v>
       </c>
       <c r="C14" t="n">
-        <v>25811.97</v>
+        <v>25280.16</v>
       </c>
       <c r="D14" t="n">
-        <v>25465.12</v>
+        <v>24830.17</v>
       </c>
       <c r="E14" t="n">
-        <v>25465.25</v>
+        <v>24897.45</v>
       </c>
       <c r="F14" t="n">
-        <v>-352.64</v>
+        <v>-567.8</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0223</v>
       </c>
       <c r="H14" t="n">
-        <v>346.85</v>
+        <v>449.99</v>
       </c>
       <c r="I14" t="n">
-        <v>25497.02</v>
+        <v>25118.27</v>
       </c>
       <c r="J14" t="n">
-        <v>25625.63</v>
+        <v>25031.75</v>
       </c>
       <c r="K14" t="n">
-        <v>25717.12</v>
+        <v>25291.82</v>
       </c>
       <c r="L14" t="n">
-        <v>25808.61</v>
+        <v>25551.9</v>
       </c>
       <c r="M14" t="n">
-        <v>25918.66</v>
+        <v>25638.68</v>
       </c>
       <c r="N14" t="n">
-        <v>26028.71</v>
+        <v>25725.45</v>
       </c>
       <c r="O14" t="n">
-        <v>26101.64</v>
+        <v>26158.82</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1718,74 +1718,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25274.94</v>
+        <v>25097.48</v>
       </c>
       <c r="C15" t="n">
-        <v>25280.16</v>
+        <v>25127.76</v>
       </c>
       <c r="D15" t="n">
-        <v>24830.17</v>
+        <v>24867.32</v>
       </c>
       <c r="E15" t="n">
-        <v>24897.45</v>
+        <v>25118.27</v>
       </c>
       <c r="F15" t="n">
-        <v>-567.8</v>
+        <v>220.82</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0089</v>
       </c>
       <c r="H15" t="n">
-        <v>449.99</v>
+        <v>260.44</v>
       </c>
       <c r="I15" t="n">
-        <v>25118.27</v>
+        <v>24380.18</v>
       </c>
       <c r="J15" t="n">
-        <v>25031.75</v>
+        <v>24368.6</v>
       </c>
       <c r="K15" t="n">
-        <v>25291.82</v>
+        <v>24672.45</v>
       </c>
       <c r="L15" t="n">
-        <v>25551.9</v>
+        <v>24976.31</v>
       </c>
       <c r="M15" t="n">
-        <v>25638.68</v>
+        <v>25122.44</v>
       </c>
       <c r="N15" t="n">
-        <v>25725.45</v>
+        <v>25268.58</v>
       </c>
       <c r="O15" t="n">
-        <v>26158.82</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
+        <v>25730.15</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1797,55 +1793,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25097.48</v>
+        <v>25081.19</v>
       </c>
       <c r="C16" t="n">
-        <v>25127.76</v>
+        <v>25195.83</v>
       </c>
       <c r="D16" t="n">
-        <v>24867.32</v>
+        <v>24937.52</v>
       </c>
       <c r="E16" t="n">
-        <v>25118.27</v>
+        <v>25067.09</v>
       </c>
       <c r="F16" t="n">
-        <v>220.82</v>
+        <v>-51.18</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.002</v>
       </c>
       <c r="H16" t="n">
-        <v>260.44</v>
+        <v>258.31</v>
       </c>
       <c r="I16" t="n">
-        <v>24380.18</v>
+        <v>24606.88</v>
       </c>
       <c r="J16" t="n">
-        <v>24368.6</v>
+        <v>24918.19</v>
       </c>
       <c r="K16" t="n">
-        <v>24672.45</v>
+        <v>24988.05</v>
       </c>
       <c r="L16" t="n">
-        <v>24976.31</v>
+        <v>25057.9</v>
       </c>
       <c r="M16" t="n">
-        <v>25122.44</v>
+        <v>25248.49</v>
       </c>
       <c r="N16" t="n">
-        <v>25268.58</v>
+        <v>25439.07</v>
       </c>
       <c r="O16" t="n">
-        <v>25730.15</v>
+        <v>25388.2</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1853,18 +1853,18 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1886,50 +1886,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25081.19</v>
+        <v>24963.8</v>
       </c>
       <c r="C17" t="n">
-        <v>25195.83</v>
+        <v>25154.58</v>
       </c>
       <c r="D17" t="n">
-        <v>24937.52</v>
+        <v>24963.8</v>
       </c>
       <c r="E17" t="n">
-        <v>25067.09</v>
+        <v>25114.25</v>
       </c>
       <c r="F17" t="n">
-        <v>-51.18</v>
+        <v>47.16</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="H17" t="n">
-        <v>258.31</v>
+        <v>190.78</v>
       </c>
       <c r="I17" t="n">
-        <v>24606.88</v>
+        <v>24679.21</v>
       </c>
       <c r="J17" t="n">
-        <v>24918.19</v>
+        <v>24808.99</v>
       </c>
       <c r="K17" t="n">
-        <v>24988.05</v>
+        <v>24937.93</v>
       </c>
       <c r="L17" t="n">
-        <v>25057.9</v>
+        <v>25066.88</v>
       </c>
       <c r="M17" t="n">
-        <v>25248.49</v>
+        <v>25196.25</v>
       </c>
       <c r="N17" t="n">
-        <v>25439.07</v>
+        <v>25325.61</v>
       </c>
       <c r="O17" t="n">
-        <v>25388.2</v>
+        <v>25454.14</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1937,12 +1937,10 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1970,61 +1968,65 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24963.8</v>
+        <v>24932.62</v>
       </c>
       <c r="C18" t="n">
-        <v>25154.58</v>
+        <v>25204.68</v>
       </c>
       <c r="D18" t="n">
-        <v>24963.8</v>
+        <v>24869.25</v>
       </c>
       <c r="E18" t="n">
-        <v>25114.25</v>
+        <v>25147.03</v>
       </c>
       <c r="F18" t="n">
-        <v>47.16</v>
+        <v>32.78</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0013</v>
       </c>
       <c r="H18" t="n">
-        <v>190.78</v>
+        <v>335.43</v>
       </c>
       <c r="I18" t="n">
-        <v>24679.21</v>
+        <v>24773.02</v>
       </c>
       <c r="J18" t="n">
-        <v>24808.99</v>
+        <v>24951</v>
       </c>
       <c r="K18" t="n">
-        <v>24937.93</v>
+        <v>25018.86</v>
       </c>
       <c r="L18" t="n">
-        <v>25066.88</v>
+        <v>25086.72</v>
       </c>
       <c r="M18" t="n">
-        <v>25196.25</v>
+        <v>25209.64</v>
       </c>
       <c r="N18" t="n">
-        <v>25325.61</v>
+        <v>25332.56</v>
       </c>
       <c r="O18" t="n">
-        <v>25454.14</v>
+        <v>25345.36</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2052,50 +2054,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24932.62</v>
+        <v>24970.05</v>
       </c>
       <c r="C19" t="n">
-        <v>25204.68</v>
+        <v>25055.48</v>
       </c>
       <c r="D19" t="n">
-        <v>24869.25</v>
+        <v>24839.23</v>
       </c>
       <c r="E19" t="n">
-        <v>25147.03</v>
+        <v>24999.53</v>
       </c>
       <c r="F19" t="n">
-        <v>32.78</v>
+        <v>-147.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0059</v>
       </c>
       <c r="H19" t="n">
-        <v>335.43</v>
+        <v>216.25</v>
       </c>
       <c r="I19" t="n">
-        <v>24773.02</v>
+        <v>24533.82</v>
       </c>
       <c r="J19" t="n">
-        <v>24951</v>
+        <v>24866.63</v>
       </c>
       <c r="K19" t="n">
-        <v>25018.86</v>
+        <v>24979.31</v>
       </c>
       <c r="L19" t="n">
-        <v>25086.72</v>
+        <v>25092</v>
       </c>
       <c r="M19" t="n">
-        <v>25209.64</v>
+        <v>25314.74</v>
       </c>
       <c r="N19" t="n">
-        <v>25332.56</v>
+        <v>25537.49</v>
       </c>
       <c r="O19" t="n">
-        <v>25345.36</v>
+        <v>25540.11</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2107,12 +2109,12 @@
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2129,59 +2131,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24970.05</v>
+        <v>25018.95</v>
       </c>
       <c r="C20" t="n">
-        <v>25055.48</v>
+        <v>25021.51</v>
       </c>
       <c r="D20" t="n">
-        <v>24839.23</v>
+        <v>24696.17</v>
       </c>
       <c r="E20" t="n">
-        <v>24999.53</v>
+        <v>24915.49</v>
       </c>
       <c r="F20" t="n">
-        <v>-147.5</v>
+        <v>-84.04000000000001</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0059</v>
+        <v>-0.0034</v>
       </c>
       <c r="H20" t="n">
-        <v>216.25</v>
+        <v>325.34</v>
       </c>
       <c r="I20" t="n">
-        <v>24533.82</v>
+        <v>24622.98</v>
       </c>
       <c r="J20" t="n">
-        <v>24866.63</v>
+        <v>24809.37</v>
       </c>
       <c r="K20" t="n">
-        <v>24979.31</v>
+        <v>24891.4</v>
       </c>
       <c r="L20" t="n">
-        <v>25092</v>
+        <v>24973.44</v>
       </c>
       <c r="M20" t="n">
-        <v>25314.74</v>
+        <v>25107.65</v>
       </c>
       <c r="N20" t="n">
-        <v>25537.49</v>
+        <v>25241.87</v>
       </c>
       <c r="O20" t="n">
-        <v>25540.11</v>
+        <v>25271.73</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2196,7 +2194,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2220,67 +2218,65 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25018.95</v>
+        <v>24755.09</v>
       </c>
       <c r="C21" t="n">
-        <v>25021.51</v>
+        <v>24850.75</v>
       </c>
       <c r="D21" t="n">
-        <v>24696.17</v>
+        <v>24651.34</v>
       </c>
       <c r="E21" t="n">
-        <v>24915.49</v>
+        <v>24830.98</v>
       </c>
       <c r="F21" t="n">
-        <v>-84.04000000000001</v>
+        <v>-84.51000000000001</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>-0.0034</v>
       </c>
       <c r="H21" t="n">
-        <v>325.34</v>
+        <v>199.41</v>
       </c>
       <c r="I21" t="n">
-        <v>24622.98</v>
+        <v>24370.83</v>
       </c>
       <c r="J21" t="n">
-        <v>24809.37</v>
+        <v>24618.48</v>
       </c>
       <c r="K21" t="n">
-        <v>24891.4</v>
+        <v>24752.82</v>
       </c>
       <c r="L21" t="n">
-        <v>24973.44</v>
+        <v>24887.17</v>
       </c>
       <c r="M21" t="n">
-        <v>25107.65</v>
+        <v>25078.16</v>
       </c>
       <c r="N21" t="n">
-        <v>25241.87</v>
+        <v>25269.16</v>
       </c>
       <c r="O21" t="n">
-        <v>25271.73</v>
+        <v>25346.85</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q21" s="6" t="n">
+        <v/>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2302,50 +2298,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24755.09</v>
+        <v>24769.15</v>
       </c>
       <c r="C22" t="n">
-        <v>24850.75</v>
+        <v>24974.53</v>
       </c>
       <c r="D22" t="n">
-        <v>24651.34</v>
+        <v>24751.13</v>
       </c>
       <c r="E22" t="n">
-        <v>24830.98</v>
+        <v>24846.69</v>
       </c>
       <c r="F22" t="n">
-        <v>-84.51000000000001</v>
+        <v>15.71</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>199.41</v>
+        <v>223.4</v>
       </c>
       <c r="I22" t="n">
-        <v>24370.83</v>
+        <v>24451.93</v>
       </c>
       <c r="J22" t="n">
-        <v>24618.48</v>
+        <v>24671.54</v>
       </c>
       <c r="K22" t="n">
-        <v>24752.82</v>
+        <v>24731.28</v>
       </c>
       <c r="L22" t="n">
-        <v>24887.17</v>
+        <v>24791.01</v>
       </c>
       <c r="M22" t="n">
-        <v>25078.16</v>
+        <v>24930.69</v>
       </c>
       <c r="N22" t="n">
-        <v>25269.16</v>
+        <v>25070.36</v>
       </c>
       <c r="O22" t="n">
-        <v>25346.85</v>
+        <v>25050.16</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2353,18 +2349,18 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2377,55 +2373,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24769.15</v>
+        <v>24922.1</v>
       </c>
       <c r="C23" t="n">
-        <v>24974.53</v>
+        <v>25011.35</v>
       </c>
       <c r="D23" t="n">
-        <v>24751.13</v>
+        <v>24817.34</v>
       </c>
       <c r="E23" t="n">
-        <v>24846.69</v>
+        <v>25011.35</v>
       </c>
       <c r="F23" t="n">
-        <v>15.71</v>
+        <v>164.66</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0066</v>
       </c>
       <c r="H23" t="n">
-        <v>223.4</v>
+        <v>194.01</v>
       </c>
       <c r="I23" t="n">
-        <v>24451.93</v>
+        <v>24527.73</v>
       </c>
       <c r="J23" t="n">
-        <v>24671.54</v>
+        <v>24615.22</v>
       </c>
       <c r="K23" t="n">
-        <v>24731.28</v>
+        <v>24734.99</v>
       </c>
       <c r="L23" t="n">
-        <v>24791.01</v>
+        <v>24854.76</v>
       </c>
       <c r="M23" t="n">
-        <v>24930.69</v>
+        <v>24958.39</v>
       </c>
       <c r="N23" t="n">
-        <v>25070.36</v>
+        <v>25062.02</v>
       </c>
       <c r="O23" t="n">
-        <v>25050.16</v>
+        <v>25197.93</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2436,9 +2436,9 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
@@ -2446,8 +2446,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2466,50 +2468,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24922.1</v>
+        <v>25001.31</v>
       </c>
       <c r="C24" t="n">
-        <v>25011.35</v>
+        <v>25271.34</v>
       </c>
       <c r="D24" t="n">
-        <v>24817.34</v>
+        <v>24984.27</v>
       </c>
       <c r="E24" t="n">
-        <v>25011.35</v>
+        <v>25155.41</v>
       </c>
       <c r="F24" t="n">
-        <v>164.66</v>
+        <v>144.06</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0058</v>
       </c>
       <c r="H24" t="n">
-        <v>194.01</v>
+        <v>287.07</v>
       </c>
       <c r="I24" t="n">
-        <v>24527.73</v>
+        <v>24623.33</v>
       </c>
       <c r="J24" t="n">
-        <v>24615.22</v>
+        <v>24865.84</v>
       </c>
       <c r="K24" t="n">
-        <v>24734.99</v>
+        <v>24914.34</v>
       </c>
       <c r="L24" t="n">
-        <v>24854.76</v>
+        <v>24962.85</v>
       </c>
       <c r="M24" t="n">
-        <v>24958.39</v>
+        <v>25108.35</v>
       </c>
       <c r="N24" t="n">
-        <v>25062.02</v>
+        <v>25253.86</v>
       </c>
       <c r="O24" t="n">
-        <v>25197.93</v>
+        <v>25205.36</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2520,23 +2522,25 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U24" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W24" s="11" t="inlineStr">
         <is>
@@ -2552,171 +2556,165 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25001.31</v>
+        <v>24994.05</v>
       </c>
       <c r="C25" t="n">
-        <v>25271.34</v>
+        <v>25074.28</v>
       </c>
       <c r="D25" t="n">
-        <v>24984.27</v>
+        <v>24696.59</v>
       </c>
       <c r="E25" t="n">
-        <v>25155.41</v>
+        <v>24763.12</v>
       </c>
       <c r="F25" t="n">
-        <v>144.06</v>
+        <v>-392.29</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0156</v>
       </c>
       <c r="H25" t="n">
-        <v>287.07</v>
+        <v>377.69</v>
       </c>
       <c r="I25" t="n">
-        <v>24623.33</v>
+        <v>24697.2</v>
       </c>
       <c r="J25" t="n">
-        <v>24865.84</v>
+        <v>24882.14</v>
       </c>
       <c r="K25" t="n">
-        <v>24914.34</v>
+        <v>25011.88</v>
       </c>
       <c r="L25" t="n">
-        <v>24962.85</v>
+        <v>25141.61</v>
       </c>
       <c r="M25" t="n">
-        <v>25108.35</v>
+        <v>25298.95</v>
       </c>
       <c r="N25" t="n">
-        <v>25253.86</v>
+        <v>25456.28</v>
       </c>
       <c r="O25" t="n">
-        <v>25205.36</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+        <v>25558.41</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
       </c>
       <c r="W25" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24994.05</v>
+        <v>24830.41</v>
       </c>
       <c r="C26" t="n">
-        <v>25074.28</v>
+        <v>25099.68</v>
       </c>
       <c r="D26" t="n">
-        <v>24696.59</v>
+        <v>24821.67</v>
       </c>
       <c r="E26" t="n">
-        <v>24763.12</v>
+        <v>25099</v>
       </c>
       <c r="F26" t="n">
-        <v>-392.29</v>
+        <v>335.88</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0136</v>
       </c>
       <c r="H26" t="n">
-        <v>377.69</v>
+        <v>278.01</v>
       </c>
       <c r="I26" t="n">
-        <v>24697.2</v>
+        <v>24318.9</v>
       </c>
       <c r="J26" t="n">
-        <v>24882.14</v>
+        <v>24324.27</v>
       </c>
       <c r="K26" t="n">
-        <v>25011.88</v>
+        <v>24574.27</v>
       </c>
       <c r="L26" t="n">
-        <v>25141.61</v>
+        <v>24824.28</v>
       </c>
       <c r="M26" t="n">
-        <v>25298.95</v>
+        <v>24951.96</v>
       </c>
       <c r="N26" t="n">
-        <v>25456.28</v>
+        <v>25079.65</v>
       </c>
       <c r="O26" t="n">
-        <v>25558.41</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
+        <v>25451.97</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
@@ -2724,50 +2722,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>24830.41</v>
+        <v>25459.32</v>
       </c>
       <c r="C27" t="n">
-        <v>25099.68</v>
+        <v>25560.4</v>
       </c>
       <c r="D27" t="n">
-        <v>24821.67</v>
+        <v>25361.03</v>
       </c>
       <c r="E27" t="n">
-        <v>25099</v>
+        <v>25361.03</v>
       </c>
       <c r="F27" t="n">
-        <v>335.88</v>
+        <v>262.03</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0104</v>
       </c>
       <c r="H27" t="n">
-        <v>278.01</v>
+        <v>199.37</v>
       </c>
       <c r="I27" t="n">
-        <v>24318.9</v>
+        <v>24543.66</v>
       </c>
       <c r="J27" t="n">
-        <v>24324.27</v>
+        <v>24890.15</v>
       </c>
       <c r="K27" t="n">
-        <v>24574.27</v>
+        <v>24960</v>
       </c>
       <c r="L27" t="n">
-        <v>24824.28</v>
+        <v>25029.84</v>
       </c>
       <c r="M27" t="n">
-        <v>24951.96</v>
+        <v>25238</v>
       </c>
       <c r="N27" t="n">
-        <v>25079.65</v>
+        <v>25446.17</v>
       </c>
       <c r="O27" t="n">
-        <v>25451.97</v>
+        <v>25377.69</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2778,7 +2776,7 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2790,11 +2788,13 @@
       </c>
       <c r="U27" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
@@ -2806,50 +2806,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25459.32</v>
+        <v>25496.13</v>
       </c>
       <c r="C28" t="n">
-        <v>25560.4</v>
+        <v>25553.47</v>
       </c>
       <c r="D28" t="n">
-        <v>25361.03</v>
+        <v>25307.17</v>
       </c>
       <c r="E28" t="n">
-        <v>25361.03</v>
+        <v>25464.01</v>
       </c>
       <c r="F28" t="n">
-        <v>262.03</v>
+        <v>102.98</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0104</v>
+        <v>0.0041</v>
       </c>
       <c r="H28" t="n">
-        <v>199.37</v>
+        <v>246.3</v>
       </c>
       <c r="I28" t="n">
-        <v>24543.66</v>
+        <v>25161.66</v>
       </c>
       <c r="J28" t="n">
-        <v>24890.15</v>
+        <v>25111.82</v>
       </c>
       <c r="K28" t="n">
-        <v>24960</v>
+        <v>25261.34</v>
       </c>
       <c r="L28" t="n">
-        <v>25029.84</v>
+        <v>25410.87</v>
       </c>
       <c r="M28" t="n">
-        <v>25238</v>
+        <v>25460.71</v>
       </c>
       <c r="N28" t="n">
-        <v>25446.17</v>
+        <v>25510.56</v>
       </c>
       <c r="O28" t="n">
-        <v>25377.69</v>
+        <v>25759.77</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2860,14 +2860,14 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U28" s="8" t="inlineStr">
@@ -2875,65 +2875,67 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V28" s="8" t="n">
+        <v/>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25496.13</v>
+        <v>25551.97</v>
       </c>
       <c r="C29" t="n">
-        <v>25553.47</v>
+        <v>25571.45</v>
       </c>
       <c r="D29" t="n">
-        <v>25307.17</v>
+        <v>25336.39</v>
       </c>
       <c r="E29" t="n">
-        <v>25464.01</v>
+        <v>25460.48</v>
       </c>
       <c r="F29" t="n">
-        <v>102.98</v>
+        <v>-3.53</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0001</v>
       </c>
       <c r="H29" t="n">
-        <v>246.3</v>
+        <v>235.06</v>
       </c>
       <c r="I29" t="n">
-        <v>25161.66</v>
+        <v>25060.87</v>
       </c>
       <c r="J29" t="n">
-        <v>25111.82</v>
+        <v>25234.55</v>
       </c>
       <c r="K29" t="n">
-        <v>25261.34</v>
+        <v>25340.86</v>
       </c>
       <c r="L29" t="n">
-        <v>25410.87</v>
+        <v>25447.17</v>
       </c>
       <c r="M29" t="n">
-        <v>25460.71</v>
+        <v>25587.16</v>
       </c>
       <c r="N29" t="n">
-        <v>25510.56</v>
+        <v>25727.16</v>
       </c>
       <c r="O29" t="n">
-        <v>25759.77</v>
+        <v>25799.77</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2941,23 +2943,21 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2969,57 +2969,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25551.97</v>
+        <v>25487.45</v>
       </c>
       <c r="C30" t="n">
-        <v>25571.45</v>
+        <v>25651.16</v>
       </c>
       <c r="D30" t="n">
-        <v>25336.39</v>
+        <v>25303.11</v>
       </c>
       <c r="E30" t="n">
-        <v>25460.48</v>
+        <v>25612.03</v>
       </c>
       <c r="F30" t="n">
-        <v>-3.53</v>
+        <v>151.55</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.006</v>
       </c>
       <c r="H30" t="n">
-        <v>235.06</v>
+        <v>348.05</v>
       </c>
       <c r="I30" t="n">
-        <v>25060.87</v>
+        <v>25101.33</v>
       </c>
       <c r="J30" t="n">
-        <v>25234.55</v>
+        <v>25228.7</v>
       </c>
       <c r="K30" t="n">
-        <v>25340.86</v>
+        <v>25342.95</v>
       </c>
       <c r="L30" t="n">
-        <v>25447.17</v>
+        <v>25457.2</v>
       </c>
       <c r="M30" t="n">
-        <v>25587.16</v>
+        <v>25578.01</v>
       </c>
       <c r="N30" t="n">
-        <v>25727.16</v>
+        <v>25698.82</v>
       </c>
       <c r="O30" t="n">
-        <v>25799.77</v>
+        <v>25806.51</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3032,13 +3032,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3060,50 +3062,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25487.45</v>
+        <v>25709.37</v>
       </c>
       <c r="C31" t="n">
-        <v>25651.16</v>
+        <v>25891.51</v>
       </c>
       <c r="D31" t="n">
-        <v>25303.11</v>
+        <v>25549.53</v>
       </c>
       <c r="E31" t="n">
-        <v>25612.03</v>
+        <v>25629.24</v>
       </c>
       <c r="F31" t="n">
-        <v>151.55</v>
+        <v>17.21</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0007</v>
       </c>
       <c r="H31" t="n">
-        <v>348.05</v>
+        <v>341.98</v>
       </c>
       <c r="I31" t="n">
-        <v>25101.33</v>
+        <v>24955.06</v>
       </c>
       <c r="J31" t="n">
-        <v>25228.7</v>
+        <v>25331.43</v>
       </c>
       <c r="K31" t="n">
-        <v>25342.95</v>
+        <v>25438</v>
       </c>
       <c r="L31" t="n">
-        <v>25457.2</v>
+        <v>25544.58</v>
       </c>
       <c r="M31" t="n">
-        <v>25578.01</v>
+        <v>25786.05</v>
       </c>
       <c r="N31" t="n">
-        <v>25698.82</v>
+        <v>26027.53</v>
       </c>
       <c r="O31" t="n">
-        <v>25806.51</v>
+        <v>25999.21</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3111,19 +3113,17 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U31" s="8" t="n">
@@ -3137,59 +3137,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25709.37</v>
+        <v>25855.12</v>
       </c>
       <c r="C32" t="n">
-        <v>25891.51</v>
+        <v>26096.93</v>
       </c>
       <c r="D32" t="n">
-        <v>25549.53</v>
+        <v>25855.12</v>
       </c>
       <c r="E32" t="n">
-        <v>25629.24</v>
+        <v>26001.31</v>
       </c>
       <c r="F32" t="n">
-        <v>17.21</v>
+        <v>372.07</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0145</v>
       </c>
       <c r="H32" t="n">
-        <v>341.98</v>
+        <v>241.81</v>
       </c>
       <c r="I32" t="n">
-        <v>24955.06</v>
+        <v>25207.55</v>
       </c>
       <c r="J32" t="n">
-        <v>25331.43</v>
+        <v>25241.62</v>
       </c>
       <c r="K32" t="n">
-        <v>25438</v>
+        <v>25458.25</v>
       </c>
       <c r="L32" t="n">
-        <v>25544.58</v>
+        <v>25674.88</v>
       </c>
       <c r="M32" t="n">
-        <v>25786.05</v>
+        <v>25800.23</v>
       </c>
       <c r="N32" t="n">
-        <v>26027.53</v>
+        <v>25925.58</v>
       </c>
       <c r="O32" t="n">
-        <v>25999.21</v>
+        <v>26233.49</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3200,9 +3196,9 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
@@ -3210,8 +3206,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3226,50 +3224,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25855.12</v>
+        <v>26189.62</v>
       </c>
       <c r="C33" t="n">
-        <v>26096.93</v>
+        <v>26266.5</v>
       </c>
       <c r="D33" t="n">
-        <v>25855.12</v>
+        <v>26082.43</v>
       </c>
       <c r="E33" t="n">
-        <v>26001.31</v>
+        <v>26202.35</v>
       </c>
       <c r="F33" t="n">
-        <v>372.07</v>
+        <v>201.04</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0077</v>
       </c>
       <c r="H33" t="n">
-        <v>241.81</v>
+        <v>184.07</v>
       </c>
       <c r="I33" t="n">
-        <v>25207.55</v>
+        <v>25613.31</v>
       </c>
       <c r="J33" t="n">
-        <v>25241.62</v>
+        <v>25772.14</v>
       </c>
       <c r="K33" t="n">
-        <v>25458.25</v>
+        <v>25880.41</v>
       </c>
       <c r="L33" t="n">
-        <v>25674.88</v>
+        <v>25988.67</v>
       </c>
       <c r="M33" t="n">
-        <v>25800.23</v>
+        <v>26122.22</v>
       </c>
       <c r="N33" t="n">
-        <v>25925.58</v>
+        <v>26255.76</v>
       </c>
       <c r="O33" t="n">
-        <v>26233.49</v>
+        <v>26338.74</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3280,7 +3278,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3308,50 +3306,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26189.62</v>
+        <v>26393.43</v>
       </c>
       <c r="C34" t="n">
-        <v>26266.5</v>
+        <v>26403.81</v>
       </c>
       <c r="D34" t="n">
-        <v>26082.43</v>
+        <v>26123.18</v>
       </c>
       <c r="E34" t="n">
-        <v>26202.35</v>
+        <v>26126.3</v>
       </c>
       <c r="F34" t="n">
-        <v>201.04</v>
+        <v>-76.05</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0029</v>
       </c>
       <c r="H34" t="n">
-        <v>184.07</v>
+        <v>280.63</v>
       </c>
       <c r="I34" t="n">
-        <v>25613.31</v>
+        <v>25898.36</v>
       </c>
       <c r="J34" t="n">
-        <v>25772.14</v>
+        <v>26032.22</v>
       </c>
       <c r="K34" t="n">
-        <v>25880.41</v>
+        <v>26110.31</v>
       </c>
       <c r="L34" t="n">
-        <v>25988.67</v>
+        <v>26188.41</v>
       </c>
       <c r="M34" t="n">
-        <v>26122.22</v>
+        <v>26294.38</v>
       </c>
       <c r="N34" t="n">
-        <v>26255.76</v>
+        <v>26400.36</v>
       </c>
       <c r="O34" t="n">
-        <v>26338.74</v>
+        <v>26450.57</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3359,12 +3357,14 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="U34" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V34" s="8" t="n">
@@ -3385,55 +3385,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>26393.43</v>
+        <v>26116.27</v>
       </c>
       <c r="C35" t="n">
-        <v>26403.81</v>
+        <v>26229.33</v>
       </c>
       <c r="D35" t="n">
-        <v>26123.18</v>
+        <v>26081.69</v>
       </c>
       <c r="E35" t="n">
-        <v>26126.3</v>
+        <v>26140.13</v>
       </c>
       <c r="F35" t="n">
-        <v>-76.05</v>
+        <v>13.83</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0005</v>
       </c>
       <c r="H35" t="n">
-        <v>280.63</v>
+        <v>147.64</v>
       </c>
       <c r="I35" t="n">
-        <v>25898.36</v>
+        <v>25842.55</v>
       </c>
       <c r="J35" t="n">
-        <v>26032.22</v>
+        <v>25777.07</v>
       </c>
       <c r="K35" t="n">
-        <v>26110.31</v>
+        <v>25985.99</v>
       </c>
       <c r="L35" t="n">
-        <v>26188.41</v>
+        <v>26194.9</v>
       </c>
       <c r="M35" t="n">
-        <v>26294.38</v>
+        <v>26266.62</v>
       </c>
       <c r="N35" t="n">
-        <v>26400.36</v>
+        <v>26338.33</v>
       </c>
       <c r="O35" t="n">
-        <v>26450.57</v>
+        <v>26684.44</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3441,25 +3445,19 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3471,57 +3469,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26116.27</v>
+        <v>26235.8</v>
       </c>
       <c r="C36" t="n">
-        <v>26229.33</v>
+        <v>26445.18</v>
       </c>
       <c r="D36" t="n">
-        <v>26081.69</v>
+        <v>26223.64</v>
       </c>
       <c r="E36" t="n">
-        <v>26140.13</v>
+        <v>26319.45</v>
       </c>
       <c r="F36" t="n">
-        <v>13.83</v>
+        <v>179.32</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0069</v>
       </c>
       <c r="H36" t="n">
-        <v>147.64</v>
+        <v>221.54</v>
       </c>
       <c r="I36" t="n">
-        <v>25842.55</v>
+        <v>25934.05</v>
       </c>
       <c r="J36" t="n">
-        <v>25777.07</v>
+        <v>25984.8</v>
       </c>
       <c r="K36" t="n">
-        <v>25985.99</v>
+        <v>26066.31</v>
       </c>
       <c r="L36" t="n">
-        <v>26194.9</v>
+        <v>26147.82</v>
       </c>
       <c r="M36" t="n">
-        <v>26266.62</v>
+        <v>26213.95</v>
       </c>
       <c r="N36" t="n">
-        <v>26338.33</v>
+        <v>26280.08</v>
       </c>
       <c r="O36" t="n">
-        <v>26684.44</v>
+        <v>26376.97</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3534,76 +3532,78 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26235.8</v>
+        <v>26360.44</v>
       </c>
       <c r="C37" t="n">
-        <v>26445.18</v>
+        <v>26441.91</v>
       </c>
       <c r="D37" t="n">
-        <v>26223.64</v>
+        <v>26302.19</v>
       </c>
       <c r="E37" t="n">
-        <v>26319.45</v>
+        <v>26323.88</v>
       </c>
       <c r="F37" t="n">
-        <v>179.32</v>
+        <v>4.43</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0002</v>
       </c>
       <c r="H37" t="n">
-        <v>221.54</v>
+        <v>139.72</v>
       </c>
       <c r="I37" t="n">
-        <v>25934.05</v>
+        <v>26002.1</v>
       </c>
       <c r="J37" t="n">
-        <v>25984.8</v>
+        <v>26090.43</v>
       </c>
       <c r="K37" t="n">
-        <v>26066.31</v>
+        <v>26208.68</v>
       </c>
       <c r="L37" t="n">
-        <v>26147.82</v>
+        <v>26326.93</v>
       </c>
       <c r="M37" t="n">
-        <v>26213.95</v>
+        <v>26430.22</v>
       </c>
       <c r="N37" t="n">
-        <v>26280.08</v>
+        <v>26533.51</v>
       </c>
       <c r="O37" t="n">
-        <v>26376.97</v>
+        <v>26666.72</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
@@ -3624,70 +3624,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26360.44</v>
+        <v>26378</v>
       </c>
       <c r="C38" t="n">
-        <v>26441.91</v>
+        <v>26504.54</v>
       </c>
       <c r="D38" t="n">
-        <v>26302.19</v>
+        <v>26245.57</v>
       </c>
       <c r="E38" t="n">
-        <v>26323.88</v>
+        <v>26391.42</v>
       </c>
       <c r="F38" t="n">
-        <v>4.43</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0026</v>
       </c>
       <c r="H38" t="n">
-        <v>139.72</v>
+        <v>258.97</v>
       </c>
       <c r="I38" t="n">
-        <v>26002.1</v>
+        <v>26162.47</v>
       </c>
       <c r="J38" t="n">
-        <v>26090.43</v>
+        <v>26160.08</v>
       </c>
       <c r="K38" t="n">
-        <v>26208.68</v>
+        <v>26254.02</v>
       </c>
       <c r="L38" t="n">
-        <v>26326.93</v>
+        <v>26347.97</v>
       </c>
       <c r="M38" t="n">
-        <v>26430.22</v>
+        <v>26393.74</v>
       </c>
       <c r="N38" t="n">
-        <v>26533.51</v>
+        <v>26439.52</v>
       </c>
       <c r="O38" t="n">
-        <v>26666.72</v>
+        <v>26581.63</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3695,21 +3695,25 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3728,50 +3732,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26378</v>
+        <v>26452</v>
       </c>
       <c r="C39" t="n">
-        <v>26504.54</v>
+        <v>26573.5</v>
       </c>
       <c r="D39" t="n">
-        <v>26245.57</v>
+        <v>26313.58</v>
       </c>
       <c r="E39" t="n">
-        <v>26391.42</v>
+        <v>26331.07</v>
       </c>
       <c r="F39" t="n">
-        <v>67.54000000000001</v>
+        <v>-60.35</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0023</v>
       </c>
       <c r="H39" t="n">
-        <v>258.97</v>
+        <v>259.92</v>
       </c>
       <c r="I39" t="n">
-        <v>26162.47</v>
+        <v>25986.6</v>
       </c>
       <c r="J39" t="n">
-        <v>26160.08</v>
+        <v>26140.63</v>
       </c>
       <c r="K39" t="n">
-        <v>26254.02</v>
+        <v>26261.94</v>
       </c>
       <c r="L39" t="n">
-        <v>26347.97</v>
+        <v>26383.24</v>
       </c>
       <c r="M39" t="n">
-        <v>26393.74</v>
+        <v>26520.9</v>
       </c>
       <c r="N39" t="n">
-        <v>26439.52</v>
+        <v>26658.57</v>
       </c>
       <c r="O39" t="n">
-        <v>26581.63</v>
+        <v>26763.51</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3779,25 +3783,21 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3816,50 +3816,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>26452</v>
+        <v>26437.35</v>
       </c>
       <c r="C40" t="n">
-        <v>26573.5</v>
+        <v>26489.78</v>
       </c>
       <c r="D40" t="n">
-        <v>26313.58</v>
+        <v>26285.23</v>
       </c>
       <c r="E40" t="n">
-        <v>26331.07</v>
+        <v>26299.74</v>
       </c>
       <c r="F40" t="n">
-        <v>-60.35</v>
+        <v>-31.33</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0012</v>
       </c>
       <c r="H40" t="n">
-        <v>259.92</v>
+        <v>204.55</v>
       </c>
       <c r="I40" t="n">
-        <v>25986.6</v>
+        <v>26053.66</v>
       </c>
       <c r="J40" t="n">
-        <v>26140.63</v>
+        <v>26014.92</v>
       </c>
       <c r="K40" t="n">
-        <v>26261.94</v>
+        <v>26201.11</v>
       </c>
       <c r="L40" t="n">
-        <v>26383.24</v>
+        <v>26387.31</v>
       </c>
       <c r="M40" t="n">
-        <v>26520.9</v>
+        <v>26461.03</v>
       </c>
       <c r="N40" t="n">
-        <v>26658.57</v>
+        <v>26534.76</v>
       </c>
       <c r="O40" t="n">
-        <v>26763.51</v>
+        <v>26833.42</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3870,7 +3870,7 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3893,57 +3893,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26437.35</v>
+        <v>26445.99</v>
       </c>
       <c r="C41" t="n">
-        <v>26489.78</v>
+        <v>26541.34</v>
       </c>
       <c r="D41" t="n">
-        <v>26285.23</v>
+        <v>26404.95</v>
       </c>
       <c r="E41" t="n">
-        <v>26299.74</v>
+        <v>26440.31</v>
       </c>
       <c r="F41" t="n">
-        <v>-31.33</v>
+        <v>140.57</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0053</v>
       </c>
       <c r="H41" t="n">
-        <v>204.55</v>
+        <v>136.39</v>
       </c>
       <c r="I41" t="n">
-        <v>26053.66</v>
+        <v>26080.68</v>
       </c>
       <c r="J41" t="n">
-        <v>26014.92</v>
+        <v>26051.31</v>
       </c>
       <c r="K41" t="n">
-        <v>26201.11</v>
+        <v>26197.47</v>
       </c>
       <c r="L41" t="n">
-        <v>26387.31</v>
+        <v>26343.62</v>
       </c>
       <c r="M41" t="n">
-        <v>26461.03</v>
+        <v>26402.01</v>
       </c>
       <c r="N41" t="n">
-        <v>26534.76</v>
+        <v>26460.41</v>
       </c>
       <c r="O41" t="n">
-        <v>26833.42</v>
+        <v>26694.33</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
@@ -3964,8 +3964,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U41" s="8" t="n">
-        <v/>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3975,59 +3977,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26445.99</v>
+        <v>26490.3</v>
       </c>
       <c r="C42" t="n">
-        <v>26541.34</v>
+        <v>26493.5</v>
       </c>
       <c r="D42" t="n">
-        <v>26404.95</v>
+        <v>26338.61</v>
       </c>
       <c r="E42" t="n">
-        <v>26440.31</v>
+        <v>26338.61</v>
       </c>
       <c r="F42" t="n">
-        <v>140.57</v>
+        <v>-101.7</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0038</v>
       </c>
       <c r="H42" t="n">
-        <v>136.39</v>
+        <v>154.89</v>
       </c>
       <c r="I42" t="n">
-        <v>26080.68</v>
+        <v>26268.56</v>
       </c>
       <c r="J42" t="n">
-        <v>26051.31</v>
+        <v>26287.5</v>
       </c>
       <c r="K42" t="n">
-        <v>26197.47</v>
+        <v>26372.12</v>
       </c>
       <c r="L42" t="n">
-        <v>26343.62</v>
+        <v>26456.73</v>
       </c>
       <c r="M42" t="n">
-        <v>26402.01</v>
+        <v>26508.51</v>
       </c>
       <c r="N42" t="n">
-        <v>26460.41</v>
+        <v>26560.28</v>
       </c>
       <c r="O42" t="n">
-        <v>26694.33</v>
+        <v>26677.73</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4035,23 +4033,21 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4061,68 +4057,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>26490.3</v>
+        <v>26280.86</v>
       </c>
       <c r="C43" t="n">
-        <v>26493.5</v>
+        <v>26292.95</v>
       </c>
       <c r="D43" t="n">
-        <v>26338.61</v>
+        <v>26119.54</v>
       </c>
       <c r="E43" t="n">
-        <v>26338.61</v>
+        <v>26128.36</v>
       </c>
       <c r="F43" t="n">
-        <v>-101.7</v>
+        <v>-210.25</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.008</v>
       </c>
       <c r="H43" t="n">
-        <v>154.89</v>
+        <v>173.41</v>
       </c>
       <c r="I43" t="n">
-        <v>26268.56</v>
+        <v>26183.72</v>
       </c>
       <c r="J43" t="n">
-        <v>26287.5</v>
+        <v>26145</v>
       </c>
       <c r="K43" t="n">
-        <v>26372.12</v>
+        <v>26261.16</v>
       </c>
       <c r="L43" t="n">
-        <v>26456.73</v>
+        <v>26377.33</v>
       </c>
       <c r="M43" t="n">
-        <v>26508.51</v>
+        <v>26416.05</v>
       </c>
       <c r="N43" t="n">
-        <v>26560.28</v>
+        <v>26454.78</v>
       </c>
       <c r="O43" t="n">
-        <v>26677.73</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
+        <v>26648.39</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4136,81 +4140,73 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W43" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26280.86</v>
+        <v>26146.12</v>
       </c>
       <c r="C44" t="n">
-        <v>26292.95</v>
+        <v>26187.82</v>
       </c>
       <c r="D44" t="n">
-        <v>26119.54</v>
+        <v>26063.37</v>
       </c>
       <c r="E44" t="n">
-        <v>26128.36</v>
+        <v>26091.33</v>
       </c>
       <c r="F44" t="n">
-        <v>-210.25</v>
+        <v>-37.03</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0014</v>
       </c>
       <c r="H44" t="n">
-        <v>173.41</v>
+        <v>124.45</v>
       </c>
       <c r="I44" t="n">
-        <v>26183.72</v>
+        <v>25946.13</v>
       </c>
       <c r="J44" t="n">
-        <v>26145</v>
+        <v>25916.01</v>
       </c>
       <c r="K44" t="n">
-        <v>26261.16</v>
+        <v>26041.65</v>
       </c>
       <c r="L44" t="n">
-        <v>26377.33</v>
+        <v>26167.3</v>
       </c>
       <c r="M44" t="n">
-        <v>26416.05</v>
+        <v>26215.06</v>
       </c>
       <c r="N44" t="n">
-        <v>26454.78</v>
+        <v>26262.83</v>
       </c>
       <c r="O44" t="n">
-        <v>26648.39</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
+        <v>26466.36</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4234,63 +4230,67 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>26146.12</v>
+        <v>26050.95</v>
       </c>
       <c r="C45" t="n">
-        <v>26187.82</v>
+        <v>26062.15</v>
       </c>
       <c r="D45" t="n">
-        <v>26063.37</v>
+        <v>25914.11</v>
       </c>
       <c r="E45" t="n">
-        <v>26091.33</v>
+        <v>25983.04</v>
       </c>
       <c r="F45" t="n">
-        <v>-37.03</v>
+        <v>-108.29</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0042</v>
       </c>
       <c r="H45" t="n">
-        <v>124.45</v>
+        <v>148.04</v>
       </c>
       <c r="I45" t="n">
-        <v>25946.13</v>
+        <v>25938.92</v>
       </c>
       <c r="J45" t="n">
-        <v>25916.01</v>
+        <v>25949.75</v>
       </c>
       <c r="K45" t="n">
-        <v>26041.65</v>
+        <v>26029.1</v>
       </c>
       <c r="L45" t="n">
-        <v>26167.3</v>
+        <v>26108.46</v>
       </c>
       <c r="M45" t="n">
-        <v>26215.06</v>
+        <v>26153.56</v>
       </c>
       <c r="N45" t="n">
-        <v>26262.83</v>
+        <v>26198.65</v>
       </c>
       <c r="O45" t="n">
-        <v>26466.36</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
+        <v>26312.27</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4314,83 +4314,81 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>26050.95</v>
+        <v>25998.95</v>
       </c>
       <c r="C46" t="n">
-        <v>26062.15</v>
+        <v>26166.25</v>
       </c>
       <c r="D46" t="n">
-        <v>25914.11</v>
+        <v>25969.52</v>
       </c>
       <c r="E46" t="n">
-        <v>25983.04</v>
+        <v>26136.56</v>
       </c>
       <c r="F46" t="n">
-        <v>-108.29</v>
+        <v>153.52</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.0059</v>
       </c>
       <c r="H46" t="n">
-        <v>148.04</v>
+        <v>196.73</v>
       </c>
       <c r="I46" t="n">
-        <v>25938.92</v>
+        <v>25766.07</v>
       </c>
       <c r="J46" t="n">
-        <v>25949.75</v>
+        <v>25832.45</v>
       </c>
       <c r="K46" t="n">
-        <v>26029.1</v>
+        <v>25909.02</v>
       </c>
       <c r="L46" t="n">
-        <v>26108.46</v>
+        <v>25985.58</v>
       </c>
       <c r="M46" t="n">
-        <v>26153.56</v>
+        <v>26057.06</v>
       </c>
       <c r="N46" t="n">
-        <v>26198.65</v>
+        <v>26128.53</v>
       </c>
       <c r="O46" t="n">
-        <v>26312.27</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
+        <v>26210.19</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W46" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr"/>
@@ -4398,50 +4396,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25998.95</v>
+        <v>26091.29</v>
       </c>
       <c r="C47" t="n">
-        <v>26166.25</v>
+        <v>26171.7</v>
       </c>
       <c r="D47" t="n">
-        <v>25969.52</v>
+        <v>26038.07</v>
       </c>
       <c r="E47" t="n">
-        <v>26136.56</v>
+        <v>26106.6</v>
       </c>
       <c r="F47" t="n">
-        <v>153.52</v>
+        <v>-29.96</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0011</v>
       </c>
       <c r="H47" t="n">
-        <v>196.73</v>
+        <v>133.63</v>
       </c>
       <c r="I47" t="n">
-        <v>25766.07</v>
+        <v>25772.79</v>
       </c>
       <c r="J47" t="n">
-        <v>25832.45</v>
+        <v>25974.17</v>
       </c>
       <c r="K47" t="n">
-        <v>25909.02</v>
+        <v>26038.2</v>
       </c>
       <c r="L47" t="n">
-        <v>25985.58</v>
+        <v>26102.22</v>
       </c>
       <c r="M47" t="n">
-        <v>26057.06</v>
+        <v>26234.93</v>
       </c>
       <c r="N47" t="n">
-        <v>26128.53</v>
+        <v>26367.63</v>
       </c>
       <c r="O47" t="n">
-        <v>26210.19</v>
+        <v>26362.98</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4449,23 +4447,21 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4475,55 +4471,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>26091.29</v>
+        <v>26206.01</v>
       </c>
       <c r="C48" t="n">
-        <v>26171.7</v>
+        <v>26341.52</v>
       </c>
       <c r="D48" t="n">
-        <v>26038.07</v>
+        <v>26164.11</v>
       </c>
       <c r="E48" t="n">
-        <v>26106.6</v>
+        <v>26266.14</v>
       </c>
       <c r="F48" t="n">
-        <v>-29.96</v>
+        <v>159.54</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0061</v>
       </c>
       <c r="H48" t="n">
-        <v>133.63</v>
+        <v>177.41</v>
       </c>
       <c r="I48" t="n">
-        <v>25772.79</v>
+        <v>25904.44</v>
       </c>
       <c r="J48" t="n">
-        <v>25974.17</v>
+        <v>25973.83</v>
       </c>
       <c r="K48" t="n">
-        <v>26038.2</v>
+        <v>26039.79</v>
       </c>
       <c r="L48" t="n">
-        <v>26102.22</v>
+        <v>26105.74</v>
       </c>
       <c r="M48" t="n">
-        <v>26234.93</v>
+        <v>26173.41</v>
       </c>
       <c r="N48" t="n">
-        <v>26367.63</v>
+        <v>26241.09</v>
       </c>
       <c r="O48" t="n">
-        <v>26362.98</v>
+        <v>26305.33</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4531,83 +4531,83 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V48" s="8" t="n">
-        <v/>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>26206.01</v>
+        <v>26255.41</v>
       </c>
       <c r="C49" t="n">
-        <v>26341.52</v>
+        <v>26466.76</v>
       </c>
       <c r="D49" t="n">
-        <v>26164.11</v>
+        <v>26196.92</v>
       </c>
       <c r="E49" t="n">
-        <v>26266.14</v>
+        <v>26285.96</v>
       </c>
       <c r="F49" t="n">
-        <v>159.54</v>
+        <v>19.82</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0061</v>
+        <v>0.0008</v>
       </c>
       <c r="H49" t="n">
-        <v>177.41</v>
+        <v>269.84</v>
       </c>
       <c r="I49" t="n">
-        <v>25904.44</v>
+        <v>25986.7</v>
       </c>
       <c r="J49" t="n">
-        <v>25973.83</v>
+        <v>26095.39</v>
       </c>
       <c r="K49" t="n">
-        <v>26039.79</v>
+        <v>26177.44</v>
       </c>
       <c r="L49" t="n">
-        <v>26105.74</v>
+        <v>26259.48</v>
       </c>
       <c r="M49" t="n">
-        <v>26173.41</v>
+        <v>26354.85</v>
       </c>
       <c r="N49" t="n">
-        <v>26241.09</v>
+        <v>26450.21</v>
       </c>
       <c r="O49" t="n">
-        <v>26305.33</v>
+        <v>26518.93</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4618,9 +4618,9 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
@@ -4630,13 +4630,11 @@
       </c>
       <c r="U49" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
       </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
@@ -4648,50 +4646,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>26255.41</v>
+        <v>26354.37</v>
       </c>
       <c r="C50" t="n">
-        <v>26466.76</v>
+        <v>26402.81</v>
       </c>
       <c r="D50" t="n">
-        <v>26196.92</v>
+        <v>26241.77</v>
       </c>
       <c r="E50" t="n">
-        <v>26285.96</v>
+        <v>26367.24</v>
       </c>
       <c r="F50" t="n">
-        <v>19.82</v>
+        <v>81.28</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0031</v>
       </c>
       <c r="H50" t="n">
-        <v>269.84</v>
+        <v>161.04</v>
       </c>
       <c r="I50" t="n">
-        <v>25986.7</v>
+        <v>25927.08</v>
       </c>
       <c r="J50" t="n">
-        <v>26095.39</v>
+        <v>25993.18</v>
       </c>
       <c r="K50" t="n">
-        <v>26177.44</v>
+        <v>26151.04</v>
       </c>
       <c r="L50" t="n">
-        <v>26259.48</v>
+        <v>26308.9</v>
       </c>
       <c r="M50" t="n">
-        <v>26354.85</v>
+        <v>26420.88</v>
       </c>
       <c r="N50" t="n">
-        <v>26450.21</v>
+        <v>26532.86</v>
       </c>
       <c r="O50" t="n">
-        <v>26518.93</v>
+        <v>26736.6</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4702,20 +4700,18 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4725,55 +4721,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>26354.37</v>
+        <v>26494.61</v>
       </c>
       <c r="C51" t="n">
-        <v>26402.81</v>
+        <v>26618.74</v>
       </c>
       <c r="D51" t="n">
-        <v>26241.77</v>
+        <v>26467.36</v>
       </c>
       <c r="E51" t="n">
-        <v>26367.24</v>
+        <v>26569.99</v>
       </c>
       <c r="F51" t="n">
-        <v>81.28</v>
+        <v>202.75</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0077</v>
       </c>
       <c r="H51" t="n">
-        <v>161.04</v>
+        <v>151.38</v>
       </c>
       <c r="I51" t="n">
-        <v>25927.08</v>
+        <v>26080.73</v>
       </c>
       <c r="J51" t="n">
-        <v>25993.18</v>
+        <v>26228.67</v>
       </c>
       <c r="K51" t="n">
-        <v>26151.04</v>
+        <v>26286.72</v>
       </c>
       <c r="L51" t="n">
-        <v>26308.9</v>
+        <v>26344.77</v>
       </c>
       <c r="M51" t="n">
-        <v>26420.88</v>
+        <v>26447.76</v>
       </c>
       <c r="N51" t="n">
-        <v>26532.86</v>
+        <v>26550.76</v>
       </c>
       <c r="O51" t="n">
-        <v>26736.6</v>
+        <v>26563.85</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4784,113 +4784,113 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="10" t="inlineStr">
+      <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
-      </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>26494.61</v>
+        <v>26464.14</v>
       </c>
       <c r="C52" t="n">
-        <v>26618.74</v>
+        <v>26471.79</v>
       </c>
       <c r="D52" t="n">
-        <v>26467.36</v>
+        <v>26249.59</v>
       </c>
       <c r="E52" t="n">
-        <v>26569.99</v>
+        <v>26258.11</v>
       </c>
       <c r="F52" t="n">
-        <v>202.75</v>
+        <v>-311.88</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0117</v>
       </c>
       <c r="H52" t="n">
-        <v>151.38</v>
+        <v>222.2</v>
       </c>
       <c r="I52" t="n">
-        <v>26080.73</v>
+        <v>26315.98</v>
       </c>
       <c r="J52" t="n">
-        <v>26228.67</v>
+        <v>26432.08</v>
       </c>
       <c r="K52" t="n">
-        <v>26286.72</v>
+        <v>26494.3</v>
       </c>
       <c r="L52" t="n">
-        <v>26344.77</v>
+        <v>26556.52</v>
       </c>
       <c r="M52" t="n">
-        <v>26447.76</v>
+        <v>26645.68</v>
       </c>
       <c r="N52" t="n">
-        <v>26550.76</v>
+        <v>26734.84</v>
       </c>
       <c r="O52" t="n">
-        <v>26563.85</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+        <v>26770.12</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W52" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W52" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X52" t="inlineStr"/>
@@ -4898,67 +4898,67 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>26464.14</v>
+        <v>26150.75</v>
       </c>
       <c r="C53" t="n">
-        <v>26471.79</v>
+        <v>26206.13</v>
       </c>
       <c r="D53" t="n">
-        <v>26249.59</v>
+        <v>25916.76</v>
       </c>
       <c r="E53" t="n">
-        <v>26258.11</v>
+        <v>25970.11</v>
       </c>
       <c r="F53" t="n">
-        <v>-311.88</v>
+        <v>-288</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.011</v>
       </c>
       <c r="H53" t="n">
-        <v>222.2</v>
+        <v>289.37</v>
       </c>
       <c r="I53" t="n">
-        <v>26315.98</v>
+        <v>26027.39</v>
       </c>
       <c r="J53" t="n">
-        <v>26432.08</v>
+        <v>25984.62</v>
       </c>
       <c r="K53" t="n">
-        <v>26494.3</v>
+        <v>26147.01</v>
       </c>
       <c r="L53" t="n">
-        <v>26556.52</v>
+        <v>26309.4</v>
       </c>
       <c r="M53" t="n">
-        <v>26645.68</v>
+        <v>26369.21</v>
       </c>
       <c r="N53" t="n">
-        <v>26734.84</v>
+        <v>26429.02</v>
       </c>
       <c r="O53" t="n">
-        <v>26770.12</v>
+        <v>26693.99</v>
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4982,67 +4982,63 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>26150.75</v>
+        <v>25886.67</v>
       </c>
       <c r="C54" t="n">
-        <v>26206.13</v>
+        <v>25924.21</v>
       </c>
       <c r="D54" t="n">
-        <v>25916.76</v>
+        <v>25727.93</v>
       </c>
       <c r="E54" t="n">
-        <v>25970.11</v>
+        <v>25839.33</v>
       </c>
       <c r="F54" t="n">
-        <v>-288</v>
+        <v>-130.78</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.005</v>
       </c>
       <c r="H54" t="n">
-        <v>289.37</v>
+        <v>196.28</v>
       </c>
       <c r="I54" t="n">
-        <v>26027.39</v>
+        <v>25627.39</v>
       </c>
       <c r="J54" t="n">
-        <v>25984.62</v>
+        <v>25635.07</v>
       </c>
       <c r="K54" t="n">
-        <v>26147.01</v>
+        <v>25825.42</v>
       </c>
       <c r="L54" t="n">
-        <v>26309.4</v>
+        <v>26015.78</v>
       </c>
       <c r="M54" t="n">
-        <v>26369.21</v>
+        <v>26114.79</v>
       </c>
       <c r="N54" t="n">
-        <v>26429.02</v>
+        <v>26213.81</v>
       </c>
       <c r="O54" t="n">
-        <v>26693.99</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
+        <v>26495.5</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5066,50 +5062,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25886.67</v>
+        <v>25840.92</v>
       </c>
       <c r="C55" t="n">
-        <v>25924.21</v>
+        <v>26007.79</v>
       </c>
       <c r="D55" t="n">
-        <v>25727.93</v>
+        <v>25784.84</v>
       </c>
       <c r="E55" t="n">
-        <v>25839.33</v>
+        <v>26003.32</v>
       </c>
       <c r="F55" t="n">
-        <v>-130.78</v>
+        <v>163.99</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0063</v>
       </c>
       <c r="H55" t="n">
-        <v>196.28</v>
+        <v>222.95</v>
       </c>
       <c r="I55" t="n">
-        <v>25627.39</v>
+        <v>25531.65</v>
       </c>
       <c r="J55" t="n">
-        <v>25635.07</v>
+        <v>25649.68</v>
       </c>
       <c r="K55" t="n">
-        <v>25825.42</v>
+        <v>25741.19</v>
       </c>
       <c r="L55" t="n">
-        <v>26015.78</v>
+        <v>25832.7</v>
       </c>
       <c r="M55" t="n">
-        <v>26114.79</v>
+        <v>25937.47</v>
       </c>
       <c r="N55" t="n">
-        <v>26213.81</v>
+        <v>26042.24</v>
       </c>
       <c r="O55" t="n">
-        <v>26495.5</v>
+        <v>26120.49</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5117,22 +5113,24 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
@@ -5141,55 +5139,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25840.92</v>
+        <v>25985.86</v>
       </c>
       <c r="C56" t="n">
-        <v>26007.79</v>
+        <v>26167.93</v>
       </c>
       <c r="D56" t="n">
-        <v>25784.84</v>
+        <v>25958.7</v>
       </c>
       <c r="E56" t="n">
-        <v>26003.32</v>
+        <v>26046.4</v>
       </c>
       <c r="F56" t="n">
-        <v>163.99</v>
+        <v>43.08</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0017</v>
       </c>
       <c r="H56" t="n">
-        <v>222.95</v>
+        <v>209.23</v>
       </c>
       <c r="I56" t="n">
-        <v>25531.65</v>
+        <v>25561.89</v>
       </c>
       <c r="J56" t="n">
-        <v>25649.68</v>
+        <v>25833.87</v>
       </c>
       <c r="K56" t="n">
-        <v>25741.19</v>
+        <v>25891.85</v>
       </c>
       <c r="L56" t="n">
-        <v>25832.7</v>
+        <v>25949.82</v>
       </c>
       <c r="M56" t="n">
-        <v>25937.47</v>
+        <v>26114.79</v>
       </c>
       <c r="N56" t="n">
-        <v>26042.24</v>
+        <v>26279.77</v>
       </c>
       <c r="O56" t="n">
-        <v>26120.49</v>
+        <v>26230.74</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5200,20 +5202,18 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5232,50 +5232,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25985.86</v>
+        <v>26039.54</v>
       </c>
       <c r="C57" t="n">
-        <v>26167.93</v>
+        <v>26069.99</v>
       </c>
       <c r="D57" t="n">
-        <v>25958.7</v>
+        <v>25919.61</v>
       </c>
       <c r="E57" t="n">
-        <v>26046.4</v>
+        <v>26006.53</v>
       </c>
       <c r="F57" t="n">
-        <v>43.08</v>
+        <v>-39.87</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0015</v>
       </c>
       <c r="H57" t="n">
-        <v>209.23</v>
+        <v>150.38</v>
       </c>
       <c r="I57" t="n">
-        <v>25561.89</v>
+        <v>25749.47</v>
       </c>
       <c r="J57" t="n">
-        <v>25833.87</v>
+        <v>25828.71</v>
       </c>
       <c r="K57" t="n">
-        <v>25891.85</v>
+        <v>25941.79</v>
       </c>
       <c r="L57" t="n">
-        <v>25949.82</v>
+        <v>26054.86</v>
       </c>
       <c r="M57" t="n">
-        <v>26114.79</v>
+        <v>26151.02</v>
       </c>
       <c r="N57" t="n">
-        <v>26279.77</v>
+        <v>26247.17</v>
       </c>
       <c r="O57" t="n">
-        <v>26230.74</v>
+        <v>26377.16</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5283,18 +5283,18 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5307,65 +5307,63 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>26039.54</v>
+        <v>25897.22</v>
       </c>
       <c r="C58" t="n">
-        <v>26069.99</v>
+        <v>26026.78</v>
       </c>
       <c r="D58" t="n">
-        <v>25919.61</v>
+        <v>25799.66</v>
       </c>
       <c r="E58" t="n">
-        <v>26006.53</v>
+        <v>26007.63</v>
       </c>
       <c r="F58" t="n">
-        <v>-39.87</v>
+        <v>1.1</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>150.38</v>
+        <v>227.12</v>
       </c>
       <c r="I58" t="n">
-        <v>25749.47</v>
+        <v>25769.23</v>
       </c>
       <c r="J58" t="n">
-        <v>25828.71</v>
+        <v>25862.01</v>
       </c>
       <c r="K58" t="n">
-        <v>25941.79</v>
+        <v>25931.34</v>
       </c>
       <c r="L58" t="n">
-        <v>26054.86</v>
+        <v>26000.66</v>
       </c>
       <c r="M58" t="n">
-        <v>26151.02</v>
+        <v>26081.72</v>
       </c>
       <c r="N58" t="n">
-        <v>26247.17</v>
+        <v>26162.77</v>
       </c>
       <c r="O58" t="n">
-        <v>26377.16</v>
+        <v>26220.37</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
@@ -5374,7 +5372,7 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5391,58 +5389,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25897.22</v>
+        <v>25870.98</v>
       </c>
       <c r="C59" t="n">
-        <v>26026.78</v>
+        <v>25909.66</v>
       </c>
       <c r="D59" t="n">
-        <v>25799.66</v>
+        <v>25512.39</v>
       </c>
       <c r="E59" t="n">
-        <v>26007.63</v>
+        <v>25576.45</v>
       </c>
       <c r="F59" t="n">
-        <v>1.1</v>
+        <v>-431.18</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0</v>
+        <v>-0.0166</v>
       </c>
       <c r="H59" t="n">
-        <v>227.12</v>
+        <v>397.27</v>
       </c>
       <c r="I59" t="n">
-        <v>25769.23</v>
+        <v>25572.54</v>
       </c>
       <c r="J59" t="n">
-        <v>25862.01</v>
+        <v>25827.72</v>
       </c>
       <c r="K59" t="n">
-        <v>25931.34</v>
+        <v>25894.07</v>
       </c>
       <c r="L59" t="n">
-        <v>26000.66</v>
+        <v>25960.43</v>
       </c>
       <c r="M59" t="n">
-        <v>26081.72</v>
+        <v>26121.19</v>
       </c>
       <c r="N59" t="n">
-        <v>26162.77</v>
+        <v>26281.96</v>
       </c>
       <c r="O59" t="n">
-        <v>26220.37</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v/>
+        <v>26253.9</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q59" s="6" t="inlineStr">
         <is>
@@ -5456,7 +5460,7 @@
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5473,76 +5477,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25870.98</v>
+        <v>25555.66</v>
       </c>
       <c r="C60" t="n">
-        <v>25909.66</v>
+        <v>25612.09</v>
       </c>
       <c r="D60" t="n">
-        <v>25512.39</v>
+        <v>25361.15</v>
       </c>
       <c r="E60" t="n">
-        <v>25576.45</v>
+        <v>25361.15</v>
       </c>
       <c r="F60" t="n">
-        <v>-431.18</v>
+        <v>-215.3</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>397.27</v>
+        <v>250.94</v>
       </c>
       <c r="I60" t="n">
-        <v>25572.54</v>
+        <v>25115.12</v>
       </c>
       <c r="J60" t="n">
-        <v>25827.72</v>
+        <v>25111.89</v>
       </c>
       <c r="K60" t="n">
-        <v>25894.07</v>
+        <v>25377.81</v>
       </c>
       <c r="L60" t="n">
-        <v>25960.43</v>
+        <v>25643.74</v>
       </c>
       <c r="M60" t="n">
-        <v>26121.19</v>
+        <v>25775.08</v>
       </c>
       <c r="N60" t="n">
-        <v>26281.96</v>
+        <v>25906.43</v>
       </c>
       <c r="O60" t="n">
-        <v>26253.9</v>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
+        <v>26306.93</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
+      <c r="S60" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5566,50 +5562,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>25555.66</v>
+        <v>25478.84</v>
       </c>
       <c r="C61" t="n">
-        <v>25612.09</v>
+        <v>25581.22</v>
       </c>
       <c r="D61" t="n">
-        <v>25361.15</v>
+        <v>25396.38</v>
       </c>
       <c r="E61" t="n">
-        <v>25361.15</v>
+        <v>25568.56</v>
       </c>
       <c r="F61" t="n">
-        <v>-215.3</v>
+        <v>207.41</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>250.94</v>
+        <v>184.84</v>
       </c>
       <c r="I61" t="n">
-        <v>25115.12</v>
+        <v>25110.21</v>
       </c>
       <c r="J61" t="n">
-        <v>25111.89</v>
+        <v>25047.48</v>
       </c>
       <c r="K61" t="n">
-        <v>25377.81</v>
+        <v>25235.68</v>
       </c>
       <c r="L61" t="n">
-        <v>25643.74</v>
+        <v>25423.89</v>
       </c>
       <c r="M61" t="n">
-        <v>25775.08</v>
+        <v>25486.62</v>
       </c>
       <c r="N61" t="n">
-        <v>25906.43</v>
+        <v>25549.35</v>
       </c>
       <c r="O61" t="n">
-        <v>26306.93</v>
+        <v>25863.03</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5617,103 +5613,109 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="W61" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>25478.84</v>
+        <v>25498.74</v>
       </c>
       <c r="C62" t="n">
-        <v>25581.22</v>
+        <v>25548.78</v>
       </c>
       <c r="D62" t="n">
-        <v>25396.38</v>
+        <v>25325.52</v>
       </c>
       <c r="E62" t="n">
-        <v>25568.56</v>
+        <v>25440.81</v>
       </c>
       <c r="F62" t="n">
-        <v>207.41</v>
+        <v>-127.75</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.005</v>
       </c>
       <c r="H62" t="n">
-        <v>184.84</v>
+        <v>223.26</v>
       </c>
       <c r="I62" t="n">
-        <v>25110.21</v>
+        <v>25211.54</v>
       </c>
       <c r="J62" t="n">
-        <v>25047.48</v>
+        <v>25423.6</v>
       </c>
       <c r="K62" t="n">
-        <v>25235.68</v>
+        <v>25476.14</v>
       </c>
       <c r="L62" t="n">
-        <v>25423.89</v>
+        <v>25528.68</v>
       </c>
       <c r="M62" t="n">
-        <v>25486.62</v>
+        <v>25660.98</v>
       </c>
       <c r="N62" t="n">
-        <v>25549.35</v>
+        <v>25793.28</v>
       </c>
       <c r="O62" t="n">
-        <v>25863.03</v>
+        <v>25766.06</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
@@ -5725,64 +5727,64 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>25498.74</v>
+        <v>25360.32</v>
       </c>
       <c r="C63" t="n">
-        <v>25548.78</v>
+        <v>25478.98</v>
       </c>
       <c r="D63" t="n">
-        <v>25325.52</v>
+        <v>25172.89</v>
       </c>
       <c r="E63" t="n">
-        <v>25440.81</v>
+        <v>25402.28</v>
       </c>
       <c r="F63" t="n">
-        <v>-127.75</v>
+        <v>-38.53</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.005</v>
+        <v>-0.0015</v>
       </c>
       <c r="H63" t="n">
-        <v>223.26</v>
+        <v>306.09</v>
       </c>
       <c r="I63" t="n">
-        <v>25211.54</v>
+        <v>25102.26</v>
       </c>
       <c r="J63" t="n">
-        <v>25423.6</v>
+        <v>25219.38</v>
       </c>
       <c r="K63" t="n">
-        <v>25476.14</v>
+        <v>25329.18</v>
       </c>
       <c r="L63" t="n">
-        <v>25528.68</v>
+        <v>25438.98</v>
       </c>
       <c r="M63" t="n">
-        <v>25660.98</v>
+        <v>25552.44</v>
       </c>
       <c r="N63" t="n">
-        <v>25793.28</v>
+        <v>25665.9</v>
       </c>
       <c r="O63" t="n">
-        <v>25766.06</v>
+        <v>25772.04</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
       </c>
       <c r="Q63" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
@@ -5790,9 +5792,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T63" s="8" t="n">
@@ -5818,71 +5820,71 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>25360.32</v>
+        <v>25515.96</v>
       </c>
       <c r="C64" t="n">
-        <v>25478.98</v>
+        <v>25599.07</v>
       </c>
       <c r="D64" t="n">
-        <v>25172.89</v>
+        <v>25361.7</v>
       </c>
       <c r="E64" t="n">
-        <v>25402.28</v>
+        <v/>
       </c>
       <c r="F64" t="n">
-        <v>-38.53</v>
+        <v/>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0015</v>
+        <v/>
       </c>
       <c r="H64" t="n">
-        <v>306.09</v>
+        <v>237.37</v>
       </c>
       <c r="I64" t="n">
-        <v>25102.26</v>
+        <v>24866.8</v>
       </c>
       <c r="J64" t="n">
-        <v>25219.38</v>
+        <v>25134.36</v>
       </c>
       <c r="K64" t="n">
-        <v>25329.18</v>
+        <v>25249.23</v>
       </c>
       <c r="L64" t="n">
-        <v>25438.98</v>
+        <v>25364.11</v>
       </c>
       <c r="M64" t="n">
-        <v>25552.44</v>
+        <v>25555.32</v>
       </c>
       <c r="N64" t="n">
-        <v>25665.9</v>
+        <v>25746.54</v>
       </c>
       <c r="O64" t="n">
-        <v>25772.04</v>
-      </c>
-      <c r="P64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q64" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R64" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
+        <v>25785.07</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U64" s="8" t="n">
         <v/>
@@ -5895,119 +5897,33 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>25515.96</v>
-      </c>
-      <c r="C65" t="n">
-        <v>25599.07</v>
-      </c>
-      <c r="D65" t="n">
-        <v>25361.7</v>
-      </c>
-      <c r="E65" t="n">
-        <v/>
-      </c>
-      <c r="F65" t="n">
-        <v/>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H65" t="n">
-        <v>237.37</v>
-      </c>
-      <c r="I65" t="n">
-        <v>24866.8</v>
-      </c>
-      <c r="J65" t="n">
-        <v>25134.36</v>
-      </c>
-      <c r="K65" t="n">
-        <v>25249.23</v>
-      </c>
-      <c r="L65" t="n">
-        <v>25364.11</v>
-      </c>
-      <c r="M65" t="n">
-        <v>25555.32</v>
-      </c>
-      <c r="N65" t="n">
-        <v>25746.54</v>
-      </c>
-      <c r="O65" t="n">
-        <v>25785.07</v>
-      </c>
-      <c r="P65" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S65" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W65" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="13" t="inlineStr">
+      <c r="A65" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I66" s="14" t="n">
+      <c r="I65" s="14" t="n">
         <v>25124.33</v>
       </c>
-      <c r="J66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O66" s="14" t="n">
+      <c r="J65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O65" s="14" t="n">
         <v>25836.44</v>
       </c>
     </row>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X65"/>
+  <dimension ref="A1:X66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5833,13 +5833,13 @@
         <v>25361.7</v>
       </c>
       <c r="E64" t="n">
-        <v/>
+        <v>25537.75</v>
       </c>
       <c r="F64" t="n">
-        <v/>
+        <v>135.47</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v/>
+        <v>0.0053</v>
       </c>
       <c r="H64" t="n">
         <v>237.37</v>
@@ -5865,66 +5865,146 @@
       <c r="O64" t="n">
         <v>25785.07</v>
       </c>
-      <c r="P64" s="6" t="inlineStr">
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S64" s="12" t="inlineStr">
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W64" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>25681.6</v>
+      </c>
+      <c r="C65" t="n">
+        <v>25800.62</v>
+      </c>
+      <c r="D65" t="n">
+        <v>25596.05</v>
+      </c>
+      <c r="E65" t="n">
+        <v/>
+      </c>
+      <c r="F65" t="n">
+        <v/>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H65" t="n">
+        <v>204.57</v>
+      </c>
+      <c r="I65" t="n">
+        <v>25124.33</v>
+      </c>
+      <c r="J65" t="n">
+        <v>25329.06</v>
+      </c>
+      <c r="K65" t="n">
+        <v>25419.06</v>
+      </c>
+      <c r="L65" t="n">
+        <v>25509.07</v>
+      </c>
+      <c r="M65" t="n">
+        <v>25656.44</v>
+      </c>
+      <c r="N65" t="n">
+        <v>25803.8</v>
+      </c>
+      <c r="O65" t="n">
+        <v>25836.44</v>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S65" s="12" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W64" s="9" t="inlineStr">
+      <c r="T65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W65" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="13" t="inlineStr">
+      <c r="X65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I65" s="14" t="n">
-        <v>25124.33</v>
-      </c>
-      <c r="J65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O65" s="14" t="n">
-        <v>25836.44</v>
+      <c r="I66" s="14" t="n">
+        <v>25391.48</v>
+      </c>
+      <c r="J66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O66" s="14" t="n">
+        <v>26005.19</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -109,22 +104,20 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -490,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X66"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -644,151 +637,147 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25035.93</v>
+        <v>24835.56</v>
       </c>
       <c r="C2" t="n">
-        <v>25176.21</v>
+        <v>24988.71</v>
       </c>
       <c r="D2" t="n">
-        <v>24896.19</v>
+        <v>24728.57</v>
       </c>
       <c r="E2" t="n">
-        <v>25139.69</v>
+        <v>24893.58</v>
       </c>
       <c r="F2" t="n">
-        <v>153.87</v>
+        <v>-246.11</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0098</v>
       </c>
       <c r="H2" t="n">
-        <v>280.02</v>
+        <v>260.14</v>
       </c>
       <c r="I2" t="n">
-        <v>24730.06</v>
+        <v>24616.17</v>
       </c>
       <c r="J2" t="n">
-        <v>24726.11</v>
+        <v>24911.41</v>
       </c>
       <c r="K2" t="n">
-        <v>24875.08</v>
+        <v>24999.68</v>
       </c>
       <c r="L2" t="n">
-        <v>25024.05</v>
+        <v>25087.94</v>
       </c>
       <c r="M2" t="n">
-        <v>25096.56</v>
+        <v>25279.7</v>
       </c>
       <c r="N2" t="n">
-        <v>25169.07</v>
+        <v>25471.46</v>
       </c>
       <c r="O2" t="n">
-        <v>25394.5</v>
+        <v>25456.23</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24835.56</v>
+        <v>24790.7</v>
       </c>
       <c r="C3" t="n">
-        <v>24988.71</v>
+        <v>24800.66</v>
       </c>
       <c r="D3" t="n">
-        <v>24728.57</v>
+        <v>24593.48</v>
       </c>
       <c r="E3" t="n">
-        <v>24893.58</v>
+        <v>24740.36</v>
       </c>
       <c r="F3" t="n">
-        <v>-246.11</v>
+        <v>-153.22</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0062</v>
       </c>
       <c r="H3" t="n">
-        <v>260.14</v>
+        <v>207.18</v>
       </c>
       <c r="I3" t="n">
-        <v>24616.17</v>
+        <v>24468.43</v>
       </c>
       <c r="J3" t="n">
-        <v>24911.41</v>
+        <v>24650.91</v>
       </c>
       <c r="K3" t="n">
-        <v>24999.68</v>
+        <v>24763.51</v>
       </c>
       <c r="L3" t="n">
-        <v>25087.94</v>
+        <v>24876.11</v>
       </c>
       <c r="M3" t="n">
-        <v>25279.7</v>
+        <v>25023.65</v>
       </c>
       <c r="N3" t="n">
-        <v>25471.46</v>
+        <v>25171.19</v>
       </c>
       <c r="O3" t="n">
-        <v>25456.23</v>
+        <v>25248.85</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
       <c r="Q3" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -802,7 +791,7 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -812,81 +801,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24790.7</v>
+        <v>24810</v>
       </c>
       <c r="C4" t="n">
-        <v>24800.66</v>
+        <v>25088.28</v>
       </c>
       <c r="D4" t="n">
-        <v>24593.48</v>
+        <v>24761.72</v>
       </c>
       <c r="E4" t="n">
-        <v>24740.36</v>
+        <v>24994.83</v>
       </c>
       <c r="F4" t="n">
-        <v>-153.22</v>
+        <v>254.47</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0103</v>
       </c>
       <c r="H4" t="n">
-        <v>207.18</v>
+        <v>326.56</v>
       </c>
       <c r="I4" t="n">
-        <v>24468.43</v>
+        <v>24386.3</v>
       </c>
       <c r="J4" t="n">
-        <v>24650.91</v>
+        <v>24554.82</v>
       </c>
       <c r="K4" t="n">
-        <v>24763.51</v>
+        <v>24636.77</v>
       </c>
       <c r="L4" t="n">
-        <v>24876.11</v>
+        <v>24718.71</v>
       </c>
       <c r="M4" t="n">
-        <v>25023.65</v>
+        <v>24843.95</v>
       </c>
       <c r="N4" t="n">
-        <v>25171.19</v>
+        <v>24969.18</v>
       </c>
       <c r="O4" t="n">
-        <v>25248.85</v>
+        <v>25007.84</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
-      </c>
       <c r="W4" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -894,83 +885,81 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24810</v>
+        <v>24848.51</v>
       </c>
       <c r="C5" t="n">
-        <v>25088.28</v>
+        <v>24869.63</v>
       </c>
       <c r="D5" t="n">
-        <v>24761.72</v>
+        <v>24547.7</v>
       </c>
       <c r="E5" t="n">
-        <v>24994.83</v>
+        <v>24671.22</v>
       </c>
       <c r="F5" t="n">
-        <v>254.47</v>
+        <v>-323.61</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.0129</v>
       </c>
       <c r="H5" t="n">
-        <v>326.56</v>
+        <v>321.93</v>
       </c>
       <c r="I5" t="n">
-        <v>24386.3</v>
+        <v>24435.16</v>
       </c>
       <c r="J5" t="n">
-        <v>24554.82</v>
+        <v>24703.19</v>
       </c>
       <c r="K5" t="n">
-        <v>24636.77</v>
+        <v>24831.55</v>
       </c>
       <c r="L5" t="n">
-        <v>24718.71</v>
+        <v>24959.92</v>
       </c>
       <c r="M5" t="n">
-        <v>24843.95</v>
+        <v>25158.11</v>
       </c>
       <c r="N5" t="n">
-        <v>24969.18</v>
+        <v>25356.3</v>
       </c>
       <c r="O5" t="n">
-        <v>25007.84</v>
+        <v>25414.84</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -978,67 +967,63 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24848.51</v>
+        <v>24724.34</v>
       </c>
       <c r="C6" t="n">
-        <v>24869.63</v>
+        <v>24762.24</v>
       </c>
       <c r="D6" t="n">
-        <v>24547.7</v>
+        <v>24556.78</v>
       </c>
       <c r="E6" t="n">
-        <v>24671.22</v>
+        <v>24626.89</v>
       </c>
       <c r="F6" t="n">
-        <v>-323.61</v>
+        <v>-44.33</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0018</v>
       </c>
       <c r="H6" t="n">
-        <v>321.93</v>
+        <v>205.46</v>
       </c>
       <c r="I6" t="n">
-        <v>24435.16</v>
+        <v>24225.77</v>
       </c>
       <c r="J6" t="n">
-        <v>24703.19</v>
+        <v>24330.57</v>
       </c>
       <c r="K6" t="n">
-        <v>24831.55</v>
+        <v>24510.25</v>
       </c>
       <c r="L6" t="n">
-        <v>24959.92</v>
+        <v>24689.94</v>
       </c>
       <c r="M6" t="n">
-        <v>25158.11</v>
+        <v>24832.19</v>
       </c>
       <c r="N6" t="n">
-        <v>25356.3</v>
+        <v>24974.43</v>
       </c>
       <c r="O6" t="n">
-        <v>25414.84</v>
+        <v>25191.56</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1050,60 +1035,64 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24724.34</v>
+        <v>24815.22</v>
       </c>
       <c r="C7" t="n">
-        <v>24762.24</v>
+        <v>25024.27</v>
       </c>
       <c r="D7" t="n">
-        <v>24556.78</v>
+        <v>24794.84</v>
       </c>
       <c r="E7" t="n">
-        <v>24626.89</v>
+        <v>24995.81</v>
       </c>
       <c r="F7" t="n">
-        <v>-44.33</v>
+        <v>368.92</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.015</v>
       </c>
       <c r="H7" t="n">
-        <v>205.46</v>
+        <v>229.43</v>
       </c>
       <c r="I7" t="n">
-        <v>24225.77</v>
+        <v>24351.32</v>
       </c>
       <c r="J7" t="n">
-        <v>24330.57</v>
+        <v>24405.12</v>
       </c>
       <c r="K7" t="n">
-        <v>24510.25</v>
+        <v>24524.16</v>
       </c>
       <c r="L7" t="n">
-        <v>24689.94</v>
+        <v>24643.2</v>
       </c>
       <c r="M7" t="n">
-        <v>24832.19</v>
+        <v>24729.62</v>
       </c>
       <c r="N7" t="n">
-        <v>24974.43</v>
+        <v>24816.04</v>
       </c>
       <c r="O7" t="n">
-        <v>25191.56</v>
+        <v>24967.7</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1116,76 +1105,78 @@
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W7" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24815.22</v>
+        <v>25028.93</v>
       </c>
       <c r="C8" t="n">
-        <v>25024.27</v>
+        <v>25095.66</v>
       </c>
       <c r="D8" t="n">
-        <v>24794.84</v>
+        <v>24887</v>
       </c>
       <c r="E8" t="n">
-        <v>24995.81</v>
+        <v>25040.28</v>
       </c>
       <c r="F8" t="n">
-        <v>368.92</v>
+        <v>44.47</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.015</v>
+        <v>0.0018</v>
       </c>
       <c r="H8" t="n">
-        <v>229.43</v>
+        <v>208.66</v>
       </c>
       <c r="I8" t="n">
-        <v>24351.32</v>
+        <v>24565.41</v>
       </c>
       <c r="J8" t="n">
-        <v>24405.12</v>
+        <v>24809.51</v>
       </c>
       <c r="K8" t="n">
-        <v>24524.16</v>
+        <v>24881.1</v>
       </c>
       <c r="L8" t="n">
-        <v>24643.2</v>
+        <v>24952.68</v>
       </c>
       <c r="M8" t="n">
-        <v>24729.62</v>
+        <v>25110.53</v>
       </c>
       <c r="N8" t="n">
-        <v>24816.04</v>
+        <v>25268.37</v>
       </c>
       <c r="O8" t="n">
-        <v>24967.7</v>
+        <v>25253.7</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1196,27 +1187,23 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1226,50 +1213,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25028.93</v>
+        <v>25025.13</v>
       </c>
       <c r="C9" t="n">
-        <v>25095.66</v>
+        <v>25655.82</v>
       </c>
       <c r="D9" t="n">
-        <v>24887</v>
+        <v>24994.64</v>
       </c>
       <c r="E9" t="n">
-        <v>25040.28</v>
+        <v>25580.88</v>
       </c>
       <c r="F9" t="n">
-        <v>44.47</v>
+        <v>540.6</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0216</v>
       </c>
       <c r="H9" t="n">
-        <v>208.66</v>
+        <v>661.1799999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>24565.41</v>
+        <v>24678.34</v>
       </c>
       <c r="J9" t="n">
-        <v>24809.51</v>
+        <v>24856.09</v>
       </c>
       <c r="K9" t="n">
-        <v>24881.1</v>
+        <v>24935.95</v>
       </c>
       <c r="L9" t="n">
-        <v>24952.68</v>
+        <v>25015.8</v>
       </c>
       <c r="M9" t="n">
-        <v>25110.53</v>
+        <v>25144.61</v>
       </c>
       <c r="N9" t="n">
-        <v>25268.37</v>
+        <v>25273.41</v>
       </c>
       <c r="O9" t="n">
-        <v>25253.7</v>
+        <v>25304.32</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1280,23 +1267,27 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1306,50 +1297,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25025.13</v>
+        <v>25763.97</v>
       </c>
       <c r="C10" t="n">
-        <v>25655.82</v>
+        <v>25826.78</v>
       </c>
       <c r="D10" t="n">
-        <v>24994.64</v>
+        <v>25611.69</v>
       </c>
       <c r="E10" t="n">
-        <v>25580.88</v>
+        <v>25779.31</v>
       </c>
       <c r="F10" t="n">
-        <v>540.6</v>
+        <v>198.43</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0216</v>
+        <v>0.0078</v>
       </c>
       <c r="H10" t="n">
-        <v>661.1799999999999</v>
+        <v>215.09</v>
       </c>
       <c r="I10" t="n">
-        <v>24678.34</v>
+        <v>24333.46</v>
       </c>
       <c r="J10" t="n">
-        <v>24856.09</v>
+        <v>25047.53</v>
       </c>
       <c r="K10" t="n">
-        <v>24935.95</v>
+        <v>25250.29</v>
       </c>
       <c r="L10" t="n">
-        <v>25015.8</v>
+        <v>25453.06</v>
       </c>
       <c r="M10" t="n">
-        <v>25144.61</v>
+        <v>25911.47</v>
       </c>
       <c r="N10" t="n">
-        <v>25273.41</v>
+        <v>26369.89</v>
       </c>
       <c r="O10" t="n">
-        <v>25304.32</v>
+        <v>26317</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1360,27 +1351,23 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1390,50 +1377,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25763.97</v>
+        <v>25811.9</v>
       </c>
       <c r="C11" t="n">
-        <v>25826.78</v>
+        <v>25900.1</v>
       </c>
       <c r="D11" t="n">
-        <v>25611.69</v>
+        <v>25698.56</v>
       </c>
       <c r="E11" t="n">
-        <v>25779.31</v>
+        <v>25817.89</v>
       </c>
       <c r="F11" t="n">
-        <v>198.43</v>
+        <v>38.58</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0078</v>
+        <v>0.0015</v>
       </c>
       <c r="H11" t="n">
-        <v>215.09</v>
+        <v>201.54</v>
       </c>
       <c r="I11" t="n">
-        <v>24333.46</v>
+        <v>25396.6</v>
       </c>
       <c r="J11" t="n">
-        <v>25047.53</v>
+        <v>25594.26</v>
       </c>
       <c r="K11" t="n">
-        <v>25250.29</v>
+        <v>25671.77</v>
       </c>
       <c r="L11" t="n">
-        <v>25453.06</v>
+        <v>25749.27</v>
       </c>
       <c r="M11" t="n">
-        <v>25911.47</v>
+        <v>25886.86</v>
       </c>
       <c r="N11" t="n">
-        <v>26369.89</v>
+        <v>26024.44</v>
       </c>
       <c r="O11" t="n">
-        <v>26317</v>
+        <v>26041.87</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1444,14 +1431,14 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U11" s="8" t="n">
@@ -1460,7 +1447,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1470,69 +1457,73 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25811.9</v>
+        <v>25770.45</v>
       </c>
       <c r="C12" t="n">
-        <v>25900.1</v>
+        <v>25811.97</v>
       </c>
       <c r="D12" t="n">
-        <v>25698.56</v>
+        <v>25465.12</v>
       </c>
       <c r="E12" t="n">
-        <v>25817.89</v>
+        <v>25465.25</v>
       </c>
       <c r="F12" t="n">
-        <v>38.58</v>
+        <v>-352.64</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0137</v>
       </c>
       <c r="H12" t="n">
-        <v>201.54</v>
+        <v>346.85</v>
       </c>
       <c r="I12" t="n">
-        <v>25396.6</v>
+        <v>25497.02</v>
       </c>
       <c r="J12" t="n">
-        <v>25594.26</v>
+        <v>25625.63</v>
       </c>
       <c r="K12" t="n">
-        <v>25671.77</v>
+        <v>25717.12</v>
       </c>
       <c r="L12" t="n">
-        <v>25749.27</v>
+        <v>25808.61</v>
       </c>
       <c r="M12" t="n">
-        <v>25886.86</v>
+        <v>25918.66</v>
       </c>
       <c r="N12" t="n">
-        <v>26024.44</v>
+        <v>26028.71</v>
       </c>
       <c r="O12" t="n">
-        <v>26041.87</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+        <v>26101.64</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1542,7 +1533,7 @@
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
@@ -1550,67 +1541,67 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25770.45</v>
+        <v>25274.94</v>
       </c>
       <c r="C13" t="n">
-        <v>25811.97</v>
+        <v>25280.16</v>
       </c>
       <c r="D13" t="n">
-        <v>25465.12</v>
+        <v>24830.17</v>
       </c>
       <c r="E13" t="n">
-        <v>25465.25</v>
+        <v>24897.45</v>
       </c>
       <c r="F13" t="n">
-        <v>-352.64</v>
+        <v>-567.8</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0223</v>
       </c>
       <c r="H13" t="n">
-        <v>346.85</v>
+        <v>449.99</v>
       </c>
       <c r="I13" t="n">
-        <v>25497.02</v>
+        <v>25118.27</v>
       </c>
       <c r="J13" t="n">
-        <v>25625.63</v>
+        <v>25031.75</v>
       </c>
       <c r="K13" t="n">
-        <v>25717.12</v>
+        <v>25291.82</v>
       </c>
       <c r="L13" t="n">
-        <v>25808.61</v>
+        <v>25551.9</v>
       </c>
       <c r="M13" t="n">
-        <v>25918.66</v>
+        <v>25638.68</v>
       </c>
       <c r="N13" t="n">
-        <v>26028.71</v>
+        <v>25725.45</v>
       </c>
       <c r="O13" t="n">
-        <v>26101.64</v>
+        <v>26158.82</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1624,7 +1615,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1634,134 +1625,134 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25274.94</v>
+        <v>25097.48</v>
       </c>
       <c r="C14" t="n">
-        <v>25280.16</v>
+        <v>25127.76</v>
       </c>
       <c r="D14" t="n">
-        <v>24830.17</v>
+        <v>24867.32</v>
       </c>
       <c r="E14" t="n">
-        <v>24897.45</v>
+        <v>25118.27</v>
       </c>
       <c r="F14" t="n">
-        <v>-567.8</v>
+        <v>220.82</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0089</v>
       </c>
       <c r="H14" t="n">
-        <v>449.99</v>
+        <v>260.44</v>
       </c>
       <c r="I14" t="n">
-        <v>25118.27</v>
+        <v>24380.18</v>
       </c>
       <c r="J14" t="n">
-        <v>25031.75</v>
+        <v>24368.6</v>
       </c>
       <c r="K14" t="n">
-        <v>25291.82</v>
+        <v>24672.45</v>
       </c>
       <c r="L14" t="n">
-        <v>25551.9</v>
+        <v>24976.31</v>
       </c>
       <c r="M14" t="n">
-        <v>25638.68</v>
+        <v>25122.44</v>
       </c>
       <c r="N14" t="n">
-        <v>25725.45</v>
+        <v>25268.58</v>
       </c>
       <c r="O14" t="n">
-        <v>26158.82</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
+        <v>25730.15</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25097.48</v>
+        <v>25081.19</v>
       </c>
       <c r="C15" t="n">
-        <v>25127.76</v>
+        <v>25195.83</v>
       </c>
       <c r="D15" t="n">
-        <v>24867.32</v>
+        <v>24937.52</v>
       </c>
       <c r="E15" t="n">
-        <v>25118.27</v>
+        <v>25067.09</v>
       </c>
       <c r="F15" t="n">
-        <v>220.82</v>
+        <v>-51.18</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.002</v>
       </c>
       <c r="H15" t="n">
-        <v>260.44</v>
+        <v>258.31</v>
       </c>
       <c r="I15" t="n">
-        <v>24380.18</v>
+        <v>24606.88</v>
       </c>
       <c r="J15" t="n">
-        <v>24368.6</v>
+        <v>24918.19</v>
       </c>
       <c r="K15" t="n">
-        <v>24672.45</v>
+        <v>24988.05</v>
       </c>
       <c r="L15" t="n">
-        <v>24976.31</v>
+        <v>25057.9</v>
       </c>
       <c r="M15" t="n">
-        <v>25122.44</v>
+        <v>25248.49</v>
       </c>
       <c r="N15" t="n">
-        <v>25268.58</v>
+        <v>25439.07</v>
       </c>
       <c r="O15" t="n">
-        <v>25730.15</v>
+        <v>25388.2</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1769,18 +1760,18 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1788,7 +1779,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1802,50 +1793,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25081.19</v>
+        <v>24963.8</v>
       </c>
       <c r="C16" t="n">
-        <v>25195.83</v>
+        <v>25154.58</v>
       </c>
       <c r="D16" t="n">
-        <v>24937.52</v>
+        <v>24963.8</v>
       </c>
       <c r="E16" t="n">
-        <v>25067.09</v>
+        <v>25114.25</v>
       </c>
       <c r="F16" t="n">
-        <v>-51.18</v>
+        <v>47.16</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="H16" t="n">
-        <v>258.31</v>
+        <v>190.78</v>
       </c>
       <c r="I16" t="n">
-        <v>24606.88</v>
+        <v>24679.21</v>
       </c>
       <c r="J16" t="n">
-        <v>24918.19</v>
+        <v>24808.99</v>
       </c>
       <c r="K16" t="n">
-        <v>24988.05</v>
+        <v>24937.93</v>
       </c>
       <c r="L16" t="n">
-        <v>25057.9</v>
+        <v>25066.88</v>
       </c>
       <c r="M16" t="n">
-        <v>25248.49</v>
+        <v>25196.25</v>
       </c>
       <c r="N16" t="n">
-        <v>25439.07</v>
+        <v>25325.61</v>
       </c>
       <c r="O16" t="n">
-        <v>25388.2</v>
+        <v>25454.14</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1853,12 +1844,10 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1872,7 +1861,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1886,61 +1875,65 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24963.8</v>
+        <v>24932.62</v>
       </c>
       <c r="C17" t="n">
-        <v>25154.58</v>
+        <v>25204.68</v>
       </c>
       <c r="D17" t="n">
-        <v>24963.8</v>
+        <v>24869.25</v>
       </c>
       <c r="E17" t="n">
-        <v>25114.25</v>
+        <v>25147.03</v>
       </c>
       <c r="F17" t="n">
-        <v>47.16</v>
+        <v>32.78</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0013</v>
       </c>
       <c r="H17" t="n">
-        <v>190.78</v>
+        <v>335.43</v>
       </c>
       <c r="I17" t="n">
-        <v>24679.21</v>
+        <v>24773.02</v>
       </c>
       <c r="J17" t="n">
-        <v>24808.99</v>
+        <v>24951</v>
       </c>
       <c r="K17" t="n">
-        <v>24937.93</v>
+        <v>25018.86</v>
       </c>
       <c r="L17" t="n">
-        <v>25066.88</v>
+        <v>25086.72</v>
       </c>
       <c r="M17" t="n">
-        <v>25196.25</v>
+        <v>25209.64</v>
       </c>
       <c r="N17" t="n">
-        <v>25325.61</v>
+        <v>25332.56</v>
       </c>
       <c r="O17" t="n">
-        <v>25454.14</v>
+        <v>25345.36</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1954,7 +1947,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1968,50 +1961,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24932.62</v>
+        <v>24970.05</v>
       </c>
       <c r="C18" t="n">
-        <v>25204.68</v>
+        <v>25055.48</v>
       </c>
       <c r="D18" t="n">
-        <v>24869.25</v>
+        <v>24839.23</v>
       </c>
       <c r="E18" t="n">
-        <v>25147.03</v>
+        <v>24999.53</v>
       </c>
       <c r="F18" t="n">
-        <v>32.78</v>
+        <v>-147.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0059</v>
       </c>
       <c r="H18" t="n">
-        <v>335.43</v>
+        <v>216.25</v>
       </c>
       <c r="I18" t="n">
-        <v>24773.02</v>
+        <v>24533.82</v>
       </c>
       <c r="J18" t="n">
-        <v>24951</v>
+        <v>24866.63</v>
       </c>
       <c r="K18" t="n">
-        <v>25018.86</v>
+        <v>24979.31</v>
       </c>
       <c r="L18" t="n">
-        <v>25086.72</v>
+        <v>25092</v>
       </c>
       <c r="M18" t="n">
-        <v>25209.64</v>
+        <v>25314.74</v>
       </c>
       <c r="N18" t="n">
-        <v>25332.56</v>
+        <v>25537.49</v>
       </c>
       <c r="O18" t="n">
-        <v>25345.36</v>
+        <v>25540.11</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2023,12 +2016,12 @@
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2040,64 +2033,60 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24970.05</v>
+        <v>25018.95</v>
       </c>
       <c r="C19" t="n">
-        <v>25055.48</v>
+        <v>25021.51</v>
       </c>
       <c r="D19" t="n">
-        <v>24839.23</v>
+        <v>24696.17</v>
       </c>
       <c r="E19" t="n">
-        <v>24999.53</v>
+        <v>24915.49</v>
       </c>
       <c r="F19" t="n">
-        <v>-147.5</v>
+        <v>-84.04000000000001</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0059</v>
+        <v>-0.0034</v>
       </c>
       <c r="H19" t="n">
-        <v>216.25</v>
+        <v>325.34</v>
       </c>
       <c r="I19" t="n">
-        <v>24533.82</v>
+        <v>24622.98</v>
       </c>
       <c r="J19" t="n">
-        <v>24866.63</v>
+        <v>24809.37</v>
       </c>
       <c r="K19" t="n">
-        <v>24979.31</v>
+        <v>24891.4</v>
       </c>
       <c r="L19" t="n">
-        <v>25092</v>
+        <v>24973.44</v>
       </c>
       <c r="M19" t="n">
-        <v>25314.74</v>
+        <v>25107.65</v>
       </c>
       <c r="N19" t="n">
-        <v>25537.49</v>
+        <v>25241.87</v>
       </c>
       <c r="O19" t="n">
-        <v>25540.11</v>
+        <v>25271.73</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2112,7 +2101,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2126,7 +2115,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2136,67 +2125,65 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25018.95</v>
+        <v>24755.09</v>
       </c>
       <c r="C20" t="n">
-        <v>25021.51</v>
+        <v>24850.75</v>
       </c>
       <c r="D20" t="n">
-        <v>24696.17</v>
+        <v>24651.34</v>
       </c>
       <c r="E20" t="n">
-        <v>24915.49</v>
+        <v>24830.98</v>
       </c>
       <c r="F20" t="n">
-        <v>-84.04000000000001</v>
+        <v>-84.51000000000001</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>-0.0034</v>
       </c>
       <c r="H20" t="n">
-        <v>325.34</v>
+        <v>199.41</v>
       </c>
       <c r="I20" t="n">
-        <v>24622.98</v>
+        <v>24370.83</v>
       </c>
       <c r="J20" t="n">
-        <v>24809.37</v>
+        <v>24618.48</v>
       </c>
       <c r="K20" t="n">
-        <v>24891.4</v>
+        <v>24752.82</v>
       </c>
       <c r="L20" t="n">
-        <v>24973.44</v>
+        <v>24887.17</v>
       </c>
       <c r="M20" t="n">
-        <v>25107.65</v>
+        <v>25078.16</v>
       </c>
       <c r="N20" t="n">
-        <v>25241.87</v>
+        <v>25269.16</v>
       </c>
       <c r="O20" t="n">
-        <v>25271.73</v>
+        <v>25346.85</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q20" s="6" t="n">
+        <v/>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2208,7 +2195,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2218,50 +2205,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24755.09</v>
+        <v>24769.15</v>
       </c>
       <c r="C21" t="n">
-        <v>24850.75</v>
+        <v>24974.53</v>
       </c>
       <c r="D21" t="n">
-        <v>24651.34</v>
+        <v>24751.13</v>
       </c>
       <c r="E21" t="n">
-        <v>24830.98</v>
+        <v>24846.69</v>
       </c>
       <c r="F21" t="n">
-        <v>-84.51000000000001</v>
+        <v>15.71</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>199.41</v>
+        <v>223.4</v>
       </c>
       <c r="I21" t="n">
-        <v>24370.83</v>
+        <v>24451.93</v>
       </c>
       <c r="J21" t="n">
-        <v>24618.48</v>
+        <v>24671.54</v>
       </c>
       <c r="K21" t="n">
-        <v>24752.82</v>
+        <v>24731.28</v>
       </c>
       <c r="L21" t="n">
-        <v>24887.17</v>
+        <v>24791.01</v>
       </c>
       <c r="M21" t="n">
-        <v>25078.16</v>
+        <v>24930.69</v>
       </c>
       <c r="N21" t="n">
-        <v>25269.16</v>
+        <v>25070.36</v>
       </c>
       <c r="O21" t="n">
-        <v>25346.85</v>
+        <v>25050.16</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2269,18 +2256,18 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R21" s="6" t="n">
+        <v/>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2288,60 +2275,64 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24769.15</v>
+        <v>24922.1</v>
       </c>
       <c r="C22" t="n">
-        <v>24974.53</v>
+        <v>25011.35</v>
       </c>
       <c r="D22" t="n">
-        <v>24751.13</v>
+        <v>24817.34</v>
       </c>
       <c r="E22" t="n">
-        <v>24846.69</v>
+        <v>25011.35</v>
       </c>
       <c r="F22" t="n">
-        <v>15.71</v>
+        <v>164.66</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0066</v>
       </c>
       <c r="H22" t="n">
-        <v>223.4</v>
+        <v>194.01</v>
       </c>
       <c r="I22" t="n">
-        <v>24451.93</v>
+        <v>24527.73</v>
       </c>
       <c r="J22" t="n">
-        <v>24671.54</v>
+        <v>24615.22</v>
       </c>
       <c r="K22" t="n">
-        <v>24731.28</v>
+        <v>24734.99</v>
       </c>
       <c r="L22" t="n">
-        <v>24791.01</v>
+        <v>24854.76</v>
       </c>
       <c r="M22" t="n">
-        <v>24930.69</v>
+        <v>24958.39</v>
       </c>
       <c r="N22" t="n">
-        <v>25070.36</v>
+        <v>25062.02</v>
       </c>
       <c r="O22" t="n">
-        <v>25050.16</v>
+        <v>25197.93</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2352,9 +2343,9 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -2362,13 +2353,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2382,50 +2375,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24922.1</v>
+        <v>25001.31</v>
       </c>
       <c r="C23" t="n">
-        <v>25011.35</v>
+        <v>25271.34</v>
       </c>
       <c r="D23" t="n">
-        <v>24817.34</v>
+        <v>24984.27</v>
       </c>
       <c r="E23" t="n">
-        <v>25011.35</v>
+        <v>25155.41</v>
       </c>
       <c r="F23" t="n">
-        <v>164.66</v>
+        <v>144.06</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0058</v>
       </c>
       <c r="H23" t="n">
-        <v>194.01</v>
+        <v>287.07</v>
       </c>
       <c r="I23" t="n">
-        <v>24527.73</v>
+        <v>24623.33</v>
       </c>
       <c r="J23" t="n">
-        <v>24615.22</v>
+        <v>24865.84</v>
       </c>
       <c r="K23" t="n">
-        <v>24734.99</v>
+        <v>24914.34</v>
       </c>
       <c r="L23" t="n">
-        <v>24854.76</v>
+        <v>24962.85</v>
       </c>
       <c r="M23" t="n">
-        <v>24958.39</v>
+        <v>25108.35</v>
       </c>
       <c r="N23" t="n">
-        <v>25062.02</v>
+        <v>25253.86</v>
       </c>
       <c r="O23" t="n">
-        <v>25197.93</v>
+        <v>25205.36</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2436,25 +2429,27 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U23" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="11" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2468,171 +2463,165 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25001.31</v>
+        <v>24994.05</v>
       </c>
       <c r="C24" t="n">
-        <v>25271.34</v>
+        <v>25074.28</v>
       </c>
       <c r="D24" t="n">
-        <v>24984.27</v>
+        <v>24696.59</v>
       </c>
       <c r="E24" t="n">
-        <v>25155.41</v>
+        <v>24763.12</v>
       </c>
       <c r="F24" t="n">
-        <v>144.06</v>
+        <v>-392.29</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0156</v>
       </c>
       <c r="H24" t="n">
-        <v>287.07</v>
+        <v>377.69</v>
       </c>
       <c r="I24" t="n">
-        <v>24623.33</v>
+        <v>24697.2</v>
       </c>
       <c r="J24" t="n">
-        <v>24865.84</v>
+        <v>24882.14</v>
       </c>
       <c r="K24" t="n">
-        <v>24914.34</v>
+        <v>25011.88</v>
       </c>
       <c r="L24" t="n">
-        <v>24962.85</v>
+        <v>25141.61</v>
       </c>
       <c r="M24" t="n">
-        <v>25108.35</v>
+        <v>25298.95</v>
       </c>
       <c r="N24" t="n">
-        <v>25253.86</v>
+        <v>25456.28</v>
       </c>
       <c r="O24" t="n">
-        <v>25205.36</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+        <v>25558.41</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W24" s="11" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24994.05</v>
+        <v>24830.41</v>
       </c>
       <c r="C25" t="n">
-        <v>25074.28</v>
+        <v>25099.68</v>
       </c>
       <c r="D25" t="n">
-        <v>24696.59</v>
+        <v>24821.67</v>
       </c>
       <c r="E25" t="n">
-        <v>24763.12</v>
+        <v>25099</v>
       </c>
       <c r="F25" t="n">
-        <v>-392.29</v>
+        <v>335.88</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0136</v>
       </c>
       <c r="H25" t="n">
-        <v>377.69</v>
+        <v>278.01</v>
       </c>
       <c r="I25" t="n">
-        <v>24697.2</v>
+        <v>24318.9</v>
       </c>
       <c r="J25" t="n">
-        <v>24882.14</v>
+        <v>24324.27</v>
       </c>
       <c r="K25" t="n">
-        <v>25011.88</v>
+        <v>24574.27</v>
       </c>
       <c r="L25" t="n">
-        <v>25141.61</v>
+        <v>24824.28</v>
       </c>
       <c r="M25" t="n">
-        <v>25298.95</v>
+        <v>24951.96</v>
       </c>
       <c r="N25" t="n">
-        <v>25456.28</v>
+        <v>25079.65</v>
       </c>
       <c r="O25" t="n">
-        <v>25558.41</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
+        <v>25451.97</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
       <c r="W25" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
@@ -2640,50 +2629,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24830.41</v>
+        <v>25459.32</v>
       </c>
       <c r="C26" t="n">
-        <v>25099.68</v>
+        <v>25560.4</v>
       </c>
       <c r="D26" t="n">
-        <v>24821.67</v>
+        <v>25361.03</v>
       </c>
       <c r="E26" t="n">
-        <v>25099</v>
+        <v>25361.03</v>
       </c>
       <c r="F26" t="n">
-        <v>335.88</v>
+        <v>262.03</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0104</v>
       </c>
       <c r="H26" t="n">
-        <v>278.01</v>
+        <v>199.37</v>
       </c>
       <c r="I26" t="n">
-        <v>24318.9</v>
+        <v>24543.66</v>
       </c>
       <c r="J26" t="n">
-        <v>24324.27</v>
+        <v>24890.15</v>
       </c>
       <c r="K26" t="n">
-        <v>24574.27</v>
+        <v>24960</v>
       </c>
       <c r="L26" t="n">
-        <v>24824.28</v>
+        <v>25029.84</v>
       </c>
       <c r="M26" t="n">
-        <v>24951.96</v>
+        <v>25238</v>
       </c>
       <c r="N26" t="n">
-        <v>25079.65</v>
+        <v>25446.17</v>
       </c>
       <c r="O26" t="n">
-        <v>25451.97</v>
+        <v>25377.69</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2694,7 +2683,7 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2706,13 +2695,15 @@
       </c>
       <c r="U26" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2722,50 +2713,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25459.32</v>
+        <v>25496.13</v>
       </c>
       <c r="C27" t="n">
-        <v>25560.4</v>
+        <v>25553.47</v>
       </c>
       <c r="D27" t="n">
-        <v>25361.03</v>
+        <v>25307.17</v>
       </c>
       <c r="E27" t="n">
-        <v>25361.03</v>
+        <v>25464.01</v>
       </c>
       <c r="F27" t="n">
-        <v>262.03</v>
+        <v>102.98</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0104</v>
+        <v>0.0041</v>
       </c>
       <c r="H27" t="n">
-        <v>199.37</v>
+        <v>246.3</v>
       </c>
       <c r="I27" t="n">
-        <v>24543.66</v>
+        <v>25161.66</v>
       </c>
       <c r="J27" t="n">
-        <v>24890.15</v>
+        <v>25111.82</v>
       </c>
       <c r="K27" t="n">
-        <v>24960</v>
+        <v>25261.34</v>
       </c>
       <c r="L27" t="n">
-        <v>25029.84</v>
+        <v>25410.87</v>
       </c>
       <c r="M27" t="n">
-        <v>25238</v>
+        <v>25460.71</v>
       </c>
       <c r="N27" t="n">
-        <v>25446.17</v>
+        <v>25510.56</v>
       </c>
       <c r="O27" t="n">
-        <v>25377.69</v>
+        <v>25759.77</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2776,14 +2767,14 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U27" s="8" t="inlineStr">
@@ -2791,65 +2782,67 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="V27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25496.13</v>
+        <v>25551.97</v>
       </c>
       <c r="C28" t="n">
-        <v>25553.47</v>
+        <v>25571.45</v>
       </c>
       <c r="D28" t="n">
-        <v>25307.17</v>
+        <v>25336.39</v>
       </c>
       <c r="E28" t="n">
-        <v>25464.01</v>
+        <v>25460.48</v>
       </c>
       <c r="F28" t="n">
-        <v>102.98</v>
+        <v>-3.53</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0001</v>
       </c>
       <c r="H28" t="n">
-        <v>246.3</v>
+        <v>235.06</v>
       </c>
       <c r="I28" t="n">
-        <v>25161.66</v>
+        <v>25060.87</v>
       </c>
       <c r="J28" t="n">
-        <v>25111.82</v>
+        <v>25234.55</v>
       </c>
       <c r="K28" t="n">
-        <v>25261.34</v>
+        <v>25340.86</v>
       </c>
       <c r="L28" t="n">
-        <v>25410.87</v>
+        <v>25447.17</v>
       </c>
       <c r="M28" t="n">
-        <v>25460.71</v>
+        <v>25587.16</v>
       </c>
       <c r="N28" t="n">
-        <v>25510.56</v>
+        <v>25727.16</v>
       </c>
       <c r="O28" t="n">
-        <v>25759.77</v>
+        <v>25799.77</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2857,85 +2850,83 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25551.97</v>
+        <v>25487.45</v>
       </c>
       <c r="C29" t="n">
-        <v>25571.45</v>
+        <v>25651.16</v>
       </c>
       <c r="D29" t="n">
-        <v>25336.39</v>
+        <v>25303.11</v>
       </c>
       <c r="E29" t="n">
-        <v>25460.48</v>
+        <v>25612.03</v>
       </c>
       <c r="F29" t="n">
-        <v>-3.53</v>
+        <v>151.55</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.006</v>
       </c>
       <c r="H29" t="n">
-        <v>235.06</v>
+        <v>348.05</v>
       </c>
       <c r="I29" t="n">
-        <v>25060.87</v>
+        <v>25101.33</v>
       </c>
       <c r="J29" t="n">
-        <v>25234.55</v>
+        <v>25228.7</v>
       </c>
       <c r="K29" t="n">
-        <v>25340.86</v>
+        <v>25342.95</v>
       </c>
       <c r="L29" t="n">
-        <v>25447.17</v>
+        <v>25457.2</v>
       </c>
       <c r="M29" t="n">
-        <v>25587.16</v>
+        <v>25578.01</v>
       </c>
       <c r="N29" t="n">
-        <v>25727.16</v>
+        <v>25698.82</v>
       </c>
       <c r="O29" t="n">
-        <v>25799.77</v>
+        <v>25806.51</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2948,13 +2939,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2962,7 +2955,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2976,50 +2969,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25487.45</v>
+        <v>25709.37</v>
       </c>
       <c r="C30" t="n">
-        <v>25651.16</v>
+        <v>25891.51</v>
       </c>
       <c r="D30" t="n">
-        <v>25303.11</v>
+        <v>25549.53</v>
       </c>
       <c r="E30" t="n">
-        <v>25612.03</v>
+        <v>25629.24</v>
       </c>
       <c r="F30" t="n">
-        <v>151.55</v>
+        <v>17.21</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0007</v>
       </c>
       <c r="H30" t="n">
-        <v>348.05</v>
+        <v>341.98</v>
       </c>
       <c r="I30" t="n">
-        <v>25101.33</v>
+        <v>24955.06</v>
       </c>
       <c r="J30" t="n">
-        <v>25228.7</v>
+        <v>25331.43</v>
       </c>
       <c r="K30" t="n">
-        <v>25342.95</v>
+        <v>25438</v>
       </c>
       <c r="L30" t="n">
-        <v>25457.2</v>
+        <v>25544.58</v>
       </c>
       <c r="M30" t="n">
-        <v>25578.01</v>
+        <v>25786.05</v>
       </c>
       <c r="N30" t="n">
-        <v>25698.82</v>
+        <v>26027.53</v>
       </c>
       <c r="O30" t="n">
-        <v>25806.51</v>
+        <v>25999.21</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3027,19 +3020,17 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U30" s="8" t="n">
@@ -3048,64 +3039,60 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25709.37</v>
+        <v>25855.12</v>
       </c>
       <c r="C31" t="n">
-        <v>25891.51</v>
+        <v>26096.93</v>
       </c>
       <c r="D31" t="n">
-        <v>25549.53</v>
+        <v>25855.12</v>
       </c>
       <c r="E31" t="n">
-        <v>25629.24</v>
+        <v>26001.31</v>
       </c>
       <c r="F31" t="n">
-        <v>17.21</v>
+        <v>372.07</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0145</v>
       </c>
       <c r="H31" t="n">
-        <v>341.98</v>
+        <v>241.81</v>
       </c>
       <c r="I31" t="n">
-        <v>24955.06</v>
+        <v>25207.55</v>
       </c>
       <c r="J31" t="n">
-        <v>25331.43</v>
+        <v>25241.62</v>
       </c>
       <c r="K31" t="n">
-        <v>25438</v>
+        <v>25458.25</v>
       </c>
       <c r="L31" t="n">
-        <v>25544.58</v>
+        <v>25674.88</v>
       </c>
       <c r="M31" t="n">
-        <v>25786.05</v>
+        <v>25800.23</v>
       </c>
       <c r="N31" t="n">
-        <v>26027.53</v>
+        <v>25925.58</v>
       </c>
       <c r="O31" t="n">
-        <v>25999.21</v>
+        <v>26233.49</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3116,9 +3103,9 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
@@ -3126,13 +3113,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3142,50 +3131,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25855.12</v>
+        <v>26189.62</v>
       </c>
       <c r="C32" t="n">
-        <v>26096.93</v>
+        <v>26266.5</v>
       </c>
       <c r="D32" t="n">
-        <v>25855.12</v>
+        <v>26082.43</v>
       </c>
       <c r="E32" t="n">
-        <v>26001.31</v>
+        <v>26202.35</v>
       </c>
       <c r="F32" t="n">
-        <v>372.07</v>
+        <v>201.04</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0077</v>
       </c>
       <c r="H32" t="n">
-        <v>241.81</v>
+        <v>184.07</v>
       </c>
       <c r="I32" t="n">
-        <v>25207.55</v>
+        <v>25613.31</v>
       </c>
       <c r="J32" t="n">
-        <v>25241.62</v>
+        <v>25772.14</v>
       </c>
       <c r="K32" t="n">
-        <v>25458.25</v>
+        <v>25880.41</v>
       </c>
       <c r="L32" t="n">
-        <v>25674.88</v>
+        <v>25988.67</v>
       </c>
       <c r="M32" t="n">
-        <v>25800.23</v>
+        <v>26122.22</v>
       </c>
       <c r="N32" t="n">
-        <v>25925.58</v>
+        <v>26255.76</v>
       </c>
       <c r="O32" t="n">
-        <v>26233.49</v>
+        <v>26338.74</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3196,7 +3185,7 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3214,7 +3203,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3224,50 +3213,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>26189.62</v>
+        <v>26393.43</v>
       </c>
       <c r="C33" t="n">
-        <v>26266.5</v>
+        <v>26403.81</v>
       </c>
       <c r="D33" t="n">
-        <v>26082.43</v>
+        <v>26123.18</v>
       </c>
       <c r="E33" t="n">
-        <v>26202.35</v>
+        <v>26126.3</v>
       </c>
       <c r="F33" t="n">
-        <v>201.04</v>
+        <v>-76.05</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0029</v>
       </c>
       <c r="H33" t="n">
-        <v>184.07</v>
+        <v>280.63</v>
       </c>
       <c r="I33" t="n">
-        <v>25613.31</v>
+        <v>25898.36</v>
       </c>
       <c r="J33" t="n">
-        <v>25772.14</v>
+        <v>26032.22</v>
       </c>
       <c r="K33" t="n">
-        <v>25880.41</v>
+        <v>26110.31</v>
       </c>
       <c r="L33" t="n">
-        <v>25988.67</v>
+        <v>26188.41</v>
       </c>
       <c r="M33" t="n">
-        <v>26122.22</v>
+        <v>26294.38</v>
       </c>
       <c r="N33" t="n">
-        <v>26255.76</v>
+        <v>26400.36</v>
       </c>
       <c r="O33" t="n">
-        <v>26338.74</v>
+        <v>26450.57</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3275,12 +3264,14 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
@@ -3290,66 +3281,70 @@
       </c>
       <c r="U33" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26393.43</v>
+        <v>26116.27</v>
       </c>
       <c r="C34" t="n">
-        <v>26403.81</v>
+        <v>26229.33</v>
       </c>
       <c r="D34" t="n">
-        <v>26123.18</v>
+        <v>26081.69</v>
       </c>
       <c r="E34" t="n">
-        <v>26126.3</v>
+        <v>26140.13</v>
       </c>
       <c r="F34" t="n">
-        <v>-76.05</v>
+        <v>13.83</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0005</v>
       </c>
       <c r="H34" t="n">
-        <v>280.63</v>
+        <v>147.64</v>
       </c>
       <c r="I34" t="n">
-        <v>25898.36</v>
+        <v>25842.55</v>
       </c>
       <c r="J34" t="n">
-        <v>26032.22</v>
+        <v>25777.07</v>
       </c>
       <c r="K34" t="n">
-        <v>26110.31</v>
+        <v>25985.99</v>
       </c>
       <c r="L34" t="n">
-        <v>26188.41</v>
+        <v>26194.9</v>
       </c>
       <c r="M34" t="n">
-        <v>26294.38</v>
+        <v>26266.62</v>
       </c>
       <c r="N34" t="n">
-        <v>26400.36</v>
+        <v>26338.33</v>
       </c>
       <c r="O34" t="n">
-        <v>26450.57</v>
+        <v>26684.44</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3357,87 +3352,81 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>26116.27</v>
+        <v>26235.8</v>
       </c>
       <c r="C35" t="n">
-        <v>26229.33</v>
+        <v>26445.18</v>
       </c>
       <c r="D35" t="n">
-        <v>26081.69</v>
+        <v>26223.64</v>
       </c>
       <c r="E35" t="n">
-        <v>26140.13</v>
+        <v>26319.45</v>
       </c>
       <c r="F35" t="n">
-        <v>13.83</v>
+        <v>179.32</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0069</v>
       </c>
       <c r="H35" t="n">
-        <v>147.64</v>
+        <v>221.54</v>
       </c>
       <c r="I35" t="n">
-        <v>25842.55</v>
+        <v>25934.05</v>
       </c>
       <c r="J35" t="n">
-        <v>25777.07</v>
+        <v>25984.8</v>
       </c>
       <c r="K35" t="n">
-        <v>25985.99</v>
+        <v>26066.31</v>
       </c>
       <c r="L35" t="n">
-        <v>26194.9</v>
+        <v>26147.82</v>
       </c>
       <c r="M35" t="n">
-        <v>26266.62</v>
+        <v>26213.95</v>
       </c>
       <c r="N35" t="n">
-        <v>26338.33</v>
+        <v>26280.08</v>
       </c>
       <c r="O35" t="n">
-        <v>26684.44</v>
+        <v>26376.97</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3450,76 +3439,78 @@
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W35" s="9" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26235.8</v>
+        <v>26360.44</v>
       </c>
       <c r="C36" t="n">
-        <v>26445.18</v>
+        <v>26441.91</v>
       </c>
       <c r="D36" t="n">
-        <v>26223.64</v>
+        <v>26302.19</v>
       </c>
       <c r="E36" t="n">
-        <v>26319.45</v>
+        <v>26323.88</v>
       </c>
       <c r="F36" t="n">
-        <v>179.32</v>
+        <v>4.43</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0002</v>
       </c>
       <c r="H36" t="n">
-        <v>221.54</v>
+        <v>139.72</v>
       </c>
       <c r="I36" t="n">
-        <v>25934.05</v>
+        <v>26002.1</v>
       </c>
       <c r="J36" t="n">
-        <v>25984.8</v>
+        <v>26090.43</v>
       </c>
       <c r="K36" t="n">
-        <v>26066.31</v>
+        <v>26208.68</v>
       </c>
       <c r="L36" t="n">
-        <v>26147.82</v>
+        <v>26326.93</v>
       </c>
       <c r="M36" t="n">
-        <v>26213.95</v>
+        <v>26430.22</v>
       </c>
       <c r="N36" t="n">
-        <v>26280.08</v>
+        <v>26533.51</v>
       </c>
       <c r="O36" t="n">
-        <v>26376.97</v>
+        <v>26666.72</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3532,7 +3523,7 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
@@ -3540,70 +3531,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26360.44</v>
+        <v>26378</v>
       </c>
       <c r="C37" t="n">
-        <v>26441.91</v>
+        <v>26504.54</v>
       </c>
       <c r="D37" t="n">
-        <v>26302.19</v>
+        <v>26245.57</v>
       </c>
       <c r="E37" t="n">
-        <v>26323.88</v>
+        <v>26391.42</v>
       </c>
       <c r="F37" t="n">
-        <v>4.43</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0026</v>
       </c>
       <c r="H37" t="n">
-        <v>139.72</v>
+        <v>258.97</v>
       </c>
       <c r="I37" t="n">
-        <v>26002.1</v>
+        <v>26162.47</v>
       </c>
       <c r="J37" t="n">
-        <v>26090.43</v>
+        <v>26160.08</v>
       </c>
       <c r="K37" t="n">
-        <v>26208.68</v>
+        <v>26254.02</v>
       </c>
       <c r="L37" t="n">
-        <v>26326.93</v>
+        <v>26347.97</v>
       </c>
       <c r="M37" t="n">
-        <v>26430.22</v>
+        <v>26393.74</v>
       </c>
       <c r="N37" t="n">
-        <v>26533.51</v>
+        <v>26439.52</v>
       </c>
       <c r="O37" t="n">
-        <v>26666.72</v>
+        <v>26581.63</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3611,26 +3602,30 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3644,50 +3639,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26378</v>
+        <v>26452</v>
       </c>
       <c r="C38" t="n">
-        <v>26504.54</v>
+        <v>26573.5</v>
       </c>
       <c r="D38" t="n">
-        <v>26245.57</v>
+        <v>26313.58</v>
       </c>
       <c r="E38" t="n">
-        <v>26391.42</v>
+        <v>26331.07</v>
       </c>
       <c r="F38" t="n">
-        <v>67.54000000000001</v>
+        <v>-60.35</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0023</v>
       </c>
       <c r="H38" t="n">
-        <v>258.97</v>
+        <v>259.92</v>
       </c>
       <c r="I38" t="n">
-        <v>26162.47</v>
+        <v>25986.6</v>
       </c>
       <c r="J38" t="n">
-        <v>26160.08</v>
+        <v>26140.63</v>
       </c>
       <c r="K38" t="n">
-        <v>26254.02</v>
+        <v>26261.94</v>
       </c>
       <c r="L38" t="n">
-        <v>26347.97</v>
+        <v>26383.24</v>
       </c>
       <c r="M38" t="n">
-        <v>26393.74</v>
+        <v>26520.9</v>
       </c>
       <c r="N38" t="n">
-        <v>26439.52</v>
+        <v>26658.57</v>
       </c>
       <c r="O38" t="n">
-        <v>26581.63</v>
+        <v>26763.51</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3695,30 +3690,26 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3732,50 +3723,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26452</v>
+        <v>26437.35</v>
       </c>
       <c r="C39" t="n">
-        <v>26573.5</v>
+        <v>26489.78</v>
       </c>
       <c r="D39" t="n">
-        <v>26313.58</v>
+        <v>26285.23</v>
       </c>
       <c r="E39" t="n">
-        <v>26331.07</v>
+        <v>26299.74</v>
       </c>
       <c r="F39" t="n">
-        <v>-60.35</v>
+        <v>-31.33</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0012</v>
       </c>
       <c r="H39" t="n">
-        <v>259.92</v>
+        <v>204.55</v>
       </c>
       <c r="I39" t="n">
-        <v>25986.6</v>
+        <v>26053.66</v>
       </c>
       <c r="J39" t="n">
-        <v>26140.63</v>
+        <v>26014.92</v>
       </c>
       <c r="K39" t="n">
-        <v>26261.94</v>
+        <v>26201.11</v>
       </c>
       <c r="L39" t="n">
-        <v>26383.24</v>
+        <v>26387.31</v>
       </c>
       <c r="M39" t="n">
-        <v>26520.9</v>
+        <v>26461.03</v>
       </c>
       <c r="N39" t="n">
-        <v>26658.57</v>
+        <v>26534.76</v>
       </c>
       <c r="O39" t="n">
-        <v>26763.51</v>
+        <v>26833.42</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3786,7 +3777,7 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
+      <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3802,64 +3793,64 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>26437.35</v>
+        <v>26445.99</v>
       </c>
       <c r="C40" t="n">
-        <v>26489.78</v>
+        <v>26541.34</v>
       </c>
       <c r="D40" t="n">
-        <v>26285.23</v>
+        <v>26404.95</v>
       </c>
       <c r="E40" t="n">
-        <v>26299.74</v>
+        <v>26440.31</v>
       </c>
       <c r="F40" t="n">
-        <v>-31.33</v>
+        <v>140.57</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0053</v>
       </c>
       <c r="H40" t="n">
-        <v>204.55</v>
+        <v>136.39</v>
       </c>
       <c r="I40" t="n">
-        <v>26053.66</v>
+        <v>26080.68</v>
       </c>
       <c r="J40" t="n">
-        <v>26014.92</v>
+        <v>26051.31</v>
       </c>
       <c r="K40" t="n">
-        <v>26201.11</v>
+        <v>26197.47</v>
       </c>
       <c r="L40" t="n">
-        <v>26387.31</v>
+        <v>26343.62</v>
       </c>
       <c r="M40" t="n">
-        <v>26461.03</v>
+        <v>26402.01</v>
       </c>
       <c r="N40" t="n">
-        <v>26534.76</v>
+        <v>26460.41</v>
       </c>
       <c r="O40" t="n">
-        <v>26833.42</v>
+        <v>26694.33</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3872,7 +3863,7 @@
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
@@ -3880,70 +3871,68 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U40" s="8" t="n">
-        <v/>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26445.99</v>
+        <v>26490.3</v>
       </c>
       <c r="C41" t="n">
-        <v>26541.34</v>
+        <v>26493.5</v>
       </c>
       <c r="D41" t="n">
-        <v>26404.95</v>
+        <v>26338.61</v>
       </c>
       <c r="E41" t="n">
-        <v>26440.31</v>
+        <v>26338.61</v>
       </c>
       <c r="F41" t="n">
-        <v>140.57</v>
+        <v>-101.7</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0038</v>
       </c>
       <c r="H41" t="n">
-        <v>136.39</v>
+        <v>154.89</v>
       </c>
       <c r="I41" t="n">
-        <v>26080.68</v>
+        <v>26268.56</v>
       </c>
       <c r="J41" t="n">
-        <v>26051.31</v>
+        <v>26287.5</v>
       </c>
       <c r="K41" t="n">
-        <v>26197.47</v>
+        <v>26372.12</v>
       </c>
       <c r="L41" t="n">
-        <v>26343.62</v>
+        <v>26456.73</v>
       </c>
       <c r="M41" t="n">
-        <v>26402.01</v>
+        <v>26508.51</v>
       </c>
       <c r="N41" t="n">
-        <v>26460.41</v>
+        <v>26560.28</v>
       </c>
       <c r="O41" t="n">
-        <v>26694.33</v>
+        <v>26677.73</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3951,94 +3940,100 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26490.3</v>
+        <v>26280.86</v>
       </c>
       <c r="C42" t="n">
-        <v>26493.5</v>
+        <v>26292.95</v>
       </c>
       <c r="D42" t="n">
-        <v>26338.61</v>
+        <v>26119.54</v>
       </c>
       <c r="E42" t="n">
-        <v>26338.61</v>
+        <v>26128.36</v>
       </c>
       <c r="F42" t="n">
-        <v>-101.7</v>
+        <v>-210.25</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.008</v>
       </c>
       <c r="H42" t="n">
-        <v>154.89</v>
+        <v>173.41</v>
       </c>
       <c r="I42" t="n">
-        <v>26268.56</v>
+        <v>26183.72</v>
       </c>
       <c r="J42" t="n">
-        <v>26287.5</v>
+        <v>26145</v>
       </c>
       <c r="K42" t="n">
-        <v>26372.12</v>
+        <v>26261.16</v>
       </c>
       <c r="L42" t="n">
-        <v>26456.73</v>
+        <v>26377.33</v>
       </c>
       <c r="M42" t="n">
-        <v>26508.51</v>
+        <v>26416.05</v>
       </c>
       <c r="N42" t="n">
-        <v>26560.28</v>
+        <v>26454.78</v>
       </c>
       <c r="O42" t="n">
-        <v>26677.73</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+        <v>26648.39</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4054,79 +4049,71 @@
       </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>26280.86</v>
+        <v>26146.12</v>
       </c>
       <c r="C43" t="n">
-        <v>26292.95</v>
+        <v>26187.82</v>
       </c>
       <c r="D43" t="n">
-        <v>26119.54</v>
+        <v>26063.37</v>
       </c>
       <c r="E43" t="n">
-        <v>26128.36</v>
+        <v>26091.33</v>
       </c>
       <c r="F43" t="n">
-        <v>-210.25</v>
+        <v>-37.03</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0014</v>
       </c>
       <c r="H43" t="n">
-        <v>173.41</v>
+        <v>124.45</v>
       </c>
       <c r="I43" t="n">
-        <v>26183.72</v>
+        <v>25946.13</v>
       </c>
       <c r="J43" t="n">
-        <v>26145</v>
+        <v>25916.01</v>
       </c>
       <c r="K43" t="n">
-        <v>26261.16</v>
+        <v>26041.65</v>
       </c>
       <c r="L43" t="n">
-        <v>26377.33</v>
+        <v>26167.3</v>
       </c>
       <c r="M43" t="n">
-        <v>26416.05</v>
+        <v>26215.06</v>
       </c>
       <c r="N43" t="n">
-        <v>26454.78</v>
+        <v>26262.83</v>
       </c>
       <c r="O43" t="n">
-        <v>26648.39</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
+        <v>26466.36</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4140,7 +4127,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4150,63 +4137,67 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26146.12</v>
+        <v>26050.95</v>
       </c>
       <c r="C44" t="n">
-        <v>26187.82</v>
+        <v>26062.15</v>
       </c>
       <c r="D44" t="n">
-        <v>26063.37</v>
+        <v>25914.11</v>
       </c>
       <c r="E44" t="n">
-        <v>26091.33</v>
+        <v>25983.04</v>
       </c>
       <c r="F44" t="n">
-        <v>-37.03</v>
+        <v>-108.29</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0042</v>
       </c>
       <c r="H44" t="n">
-        <v>124.45</v>
+        <v>148.04</v>
       </c>
       <c r="I44" t="n">
-        <v>25946.13</v>
+        <v>25938.92</v>
       </c>
       <c r="J44" t="n">
-        <v>25916.01</v>
+        <v>25949.75</v>
       </c>
       <c r="K44" t="n">
-        <v>26041.65</v>
+        <v>26029.1</v>
       </c>
       <c r="L44" t="n">
-        <v>26167.3</v>
+        <v>26108.46</v>
       </c>
       <c r="M44" t="n">
-        <v>26215.06</v>
+        <v>26153.56</v>
       </c>
       <c r="N44" t="n">
-        <v>26262.83</v>
+        <v>26198.65</v>
       </c>
       <c r="O44" t="n">
-        <v>26466.36</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
+        <v>26312.27</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4220,7 +4211,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4230,83 +4221,81 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>26050.95</v>
+        <v>25998.95</v>
       </c>
       <c r="C45" t="n">
-        <v>26062.15</v>
+        <v>26166.25</v>
       </c>
       <c r="D45" t="n">
-        <v>25914.11</v>
+        <v>25969.52</v>
       </c>
       <c r="E45" t="n">
-        <v>25983.04</v>
+        <v>26136.56</v>
       </c>
       <c r="F45" t="n">
-        <v>-108.29</v>
+        <v>153.52</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.0059</v>
       </c>
       <c r="H45" t="n">
-        <v>148.04</v>
+        <v>196.73</v>
       </c>
       <c r="I45" t="n">
-        <v>25938.92</v>
+        <v>25766.07</v>
       </c>
       <c r="J45" t="n">
-        <v>25949.75</v>
+        <v>25832.45</v>
       </c>
       <c r="K45" t="n">
-        <v>26029.1</v>
+        <v>25909.02</v>
       </c>
       <c r="L45" t="n">
-        <v>26108.46</v>
+        <v>25985.58</v>
       </c>
       <c r="M45" t="n">
-        <v>26153.56</v>
+        <v>26057.06</v>
       </c>
       <c r="N45" t="n">
-        <v>26198.65</v>
+        <v>26128.53</v>
       </c>
       <c r="O45" t="n">
-        <v>26312.27</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
+        <v>26210.19</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
       <c r="W45" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr"/>
@@ -4314,50 +4303,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25998.95</v>
+        <v>26091.29</v>
       </c>
       <c r="C46" t="n">
-        <v>26166.25</v>
+        <v>26171.7</v>
       </c>
       <c r="D46" t="n">
-        <v>25969.52</v>
+        <v>26038.07</v>
       </c>
       <c r="E46" t="n">
-        <v>26136.56</v>
+        <v>26106.6</v>
       </c>
       <c r="F46" t="n">
-        <v>153.52</v>
+        <v>-29.96</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0011</v>
       </c>
       <c r="H46" t="n">
-        <v>196.73</v>
+        <v>133.63</v>
       </c>
       <c r="I46" t="n">
-        <v>25766.07</v>
+        <v>25772.79</v>
       </c>
       <c r="J46" t="n">
-        <v>25832.45</v>
+        <v>25974.17</v>
       </c>
       <c r="K46" t="n">
-        <v>25909.02</v>
+        <v>26038.2</v>
       </c>
       <c r="L46" t="n">
-        <v>25985.58</v>
+        <v>26102.22</v>
       </c>
       <c r="M46" t="n">
-        <v>26057.06</v>
+        <v>26234.93</v>
       </c>
       <c r="N46" t="n">
-        <v>26128.53</v>
+        <v>26367.63</v>
       </c>
       <c r="O46" t="n">
-        <v>26210.19</v>
+        <v>26362.98</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4365,81 +4354,83 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>26091.29</v>
+        <v>26206.01</v>
       </c>
       <c r="C47" t="n">
-        <v>26171.7</v>
+        <v>26341.52</v>
       </c>
       <c r="D47" t="n">
-        <v>26038.07</v>
+        <v>26164.11</v>
       </c>
       <c r="E47" t="n">
-        <v>26106.6</v>
+        <v>26266.14</v>
       </c>
       <c r="F47" t="n">
-        <v>-29.96</v>
+        <v>159.54</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0061</v>
       </c>
       <c r="H47" t="n">
-        <v>133.63</v>
+        <v>177.41</v>
       </c>
       <c r="I47" t="n">
-        <v>25772.79</v>
+        <v>25904.44</v>
       </c>
       <c r="J47" t="n">
-        <v>25974.17</v>
+        <v>25973.83</v>
       </c>
       <c r="K47" t="n">
-        <v>26038.2</v>
+        <v>26039.79</v>
       </c>
       <c r="L47" t="n">
-        <v>26102.22</v>
+        <v>26105.74</v>
       </c>
       <c r="M47" t="n">
-        <v>26234.93</v>
+        <v>26173.41</v>
       </c>
       <c r="N47" t="n">
-        <v>26367.63</v>
+        <v>26241.09</v>
       </c>
       <c r="O47" t="n">
-        <v>26362.98</v>
+        <v>26305.33</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4447,83 +4438,83 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>26206.01</v>
+        <v>26255.41</v>
       </c>
       <c r="C48" t="n">
-        <v>26341.52</v>
+        <v>26466.76</v>
       </c>
       <c r="D48" t="n">
-        <v>26164.11</v>
+        <v>26196.92</v>
       </c>
       <c r="E48" t="n">
-        <v>26266.14</v>
+        <v>26285.96</v>
       </c>
       <c r="F48" t="n">
-        <v>159.54</v>
+        <v>19.82</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0061</v>
+        <v>0.0008</v>
       </c>
       <c r="H48" t="n">
-        <v>177.41</v>
+        <v>269.84</v>
       </c>
       <c r="I48" t="n">
-        <v>25904.44</v>
+        <v>25986.7</v>
       </c>
       <c r="J48" t="n">
-        <v>25973.83</v>
+        <v>26095.39</v>
       </c>
       <c r="K48" t="n">
-        <v>26039.79</v>
+        <v>26177.44</v>
       </c>
       <c r="L48" t="n">
-        <v>26105.74</v>
+        <v>26259.48</v>
       </c>
       <c r="M48" t="n">
-        <v>26173.41</v>
+        <v>26354.85</v>
       </c>
       <c r="N48" t="n">
-        <v>26241.09</v>
+        <v>26450.21</v>
       </c>
       <c r="O48" t="n">
-        <v>26305.33</v>
+        <v>26518.93</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4534,9 +4525,9 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
@@ -4546,15 +4537,13 @@
       </c>
       <c r="U48" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W48" s="9" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4564,50 +4553,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>26255.41</v>
+        <v>26354.37</v>
       </c>
       <c r="C49" t="n">
-        <v>26466.76</v>
+        <v>26402.81</v>
       </c>
       <c r="D49" t="n">
-        <v>26196.92</v>
+        <v>26241.77</v>
       </c>
       <c r="E49" t="n">
-        <v>26285.96</v>
+        <v>26367.24</v>
       </c>
       <c r="F49" t="n">
-        <v>19.82</v>
+        <v>81.28</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0031</v>
       </c>
       <c r="H49" t="n">
-        <v>269.84</v>
+        <v>161.04</v>
       </c>
       <c r="I49" t="n">
-        <v>25986.7</v>
+        <v>25927.08</v>
       </c>
       <c r="J49" t="n">
-        <v>26095.39</v>
+        <v>25993.18</v>
       </c>
       <c r="K49" t="n">
-        <v>26177.44</v>
+        <v>26151.04</v>
       </c>
       <c r="L49" t="n">
-        <v>26259.48</v>
+        <v>26308.9</v>
       </c>
       <c r="M49" t="n">
-        <v>26354.85</v>
+        <v>26420.88</v>
       </c>
       <c r="N49" t="n">
-        <v>26450.21</v>
+        <v>26532.86</v>
       </c>
       <c r="O49" t="n">
-        <v>26518.93</v>
+        <v>26736.6</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4618,78 +4607,80 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>26354.37</v>
+        <v>26494.61</v>
       </c>
       <c r="C50" t="n">
-        <v>26402.81</v>
+        <v>26618.74</v>
       </c>
       <c r="D50" t="n">
-        <v>26241.77</v>
+        <v>26467.36</v>
       </c>
       <c r="E50" t="n">
-        <v>26367.24</v>
+        <v>26569.99</v>
       </c>
       <c r="F50" t="n">
-        <v>81.28</v>
+        <v>202.75</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0077</v>
       </c>
       <c r="H50" t="n">
-        <v>161.04</v>
+        <v>151.38</v>
       </c>
       <c r="I50" t="n">
-        <v>25927.08</v>
+        <v>26080.73</v>
       </c>
       <c r="J50" t="n">
-        <v>25993.18</v>
+        <v>26228.67</v>
       </c>
       <c r="K50" t="n">
-        <v>26151.04</v>
+        <v>26286.72</v>
       </c>
       <c r="L50" t="n">
-        <v>26308.9</v>
+        <v>26344.77</v>
       </c>
       <c r="M50" t="n">
-        <v>26420.88</v>
+        <v>26447.76</v>
       </c>
       <c r="N50" t="n">
-        <v>26532.86</v>
+        <v>26550.76</v>
       </c>
       <c r="O50" t="n">
-        <v>26736.6</v>
+        <v>26563.85</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4700,113 +4691,113 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>26494.61</v>
+        <v>26464.14</v>
       </c>
       <c r="C51" t="n">
-        <v>26618.74</v>
+        <v>26471.79</v>
       </c>
       <c r="D51" t="n">
-        <v>26467.36</v>
+        <v>26249.59</v>
       </c>
       <c r="E51" t="n">
-        <v>26569.99</v>
+        <v>26258.11</v>
       </c>
       <c r="F51" t="n">
-        <v>202.75</v>
+        <v>-311.88</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0117</v>
       </c>
       <c r="H51" t="n">
-        <v>151.38</v>
+        <v>222.2</v>
       </c>
       <c r="I51" t="n">
-        <v>26080.73</v>
+        <v>26315.98</v>
       </c>
       <c r="J51" t="n">
-        <v>26228.67</v>
+        <v>26432.08</v>
       </c>
       <c r="K51" t="n">
-        <v>26286.72</v>
+        <v>26494.3</v>
       </c>
       <c r="L51" t="n">
-        <v>26344.77</v>
+        <v>26556.52</v>
       </c>
       <c r="M51" t="n">
-        <v>26447.76</v>
+        <v>26645.68</v>
       </c>
       <c r="N51" t="n">
-        <v>26550.76</v>
+        <v>26734.84</v>
       </c>
       <c r="O51" t="n">
-        <v>26563.85</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+        <v>26770.12</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X51" t="inlineStr"/>
@@ -4814,67 +4805,67 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>26464.14</v>
+        <v>26150.75</v>
       </c>
       <c r="C52" t="n">
-        <v>26471.79</v>
+        <v>26206.13</v>
       </c>
       <c r="D52" t="n">
-        <v>26249.59</v>
+        <v>25916.76</v>
       </c>
       <c r="E52" t="n">
-        <v>26258.11</v>
+        <v>25970.11</v>
       </c>
       <c r="F52" t="n">
-        <v>-311.88</v>
+        <v>-288</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.011</v>
       </c>
       <c r="H52" t="n">
-        <v>222.2</v>
+        <v>289.37</v>
       </c>
       <c r="I52" t="n">
-        <v>26315.98</v>
+        <v>26027.39</v>
       </c>
       <c r="J52" t="n">
-        <v>26432.08</v>
+        <v>25984.62</v>
       </c>
       <c r="K52" t="n">
-        <v>26494.3</v>
+        <v>26147.01</v>
       </c>
       <c r="L52" t="n">
-        <v>26556.52</v>
+        <v>26309.4</v>
       </c>
       <c r="M52" t="n">
-        <v>26645.68</v>
+        <v>26369.21</v>
       </c>
       <c r="N52" t="n">
-        <v>26734.84</v>
+        <v>26429.02</v>
       </c>
       <c r="O52" t="n">
-        <v>26770.12</v>
+        <v>26693.99</v>
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S52" s="10" t="inlineStr">
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4888,7 +4879,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4898,67 +4889,63 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>26150.75</v>
+        <v>25886.67</v>
       </c>
       <c r="C53" t="n">
-        <v>26206.13</v>
+        <v>25924.21</v>
       </c>
       <c r="D53" t="n">
-        <v>25916.76</v>
+        <v>25727.93</v>
       </c>
       <c r="E53" t="n">
-        <v>25970.11</v>
+        <v>25839.33</v>
       </c>
       <c r="F53" t="n">
-        <v>-288</v>
+        <v>-130.78</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.005</v>
       </c>
       <c r="H53" t="n">
-        <v>289.37</v>
+        <v>196.28</v>
       </c>
       <c r="I53" t="n">
-        <v>26027.39</v>
+        <v>25627.39</v>
       </c>
       <c r="J53" t="n">
-        <v>25984.62</v>
+        <v>25635.07</v>
       </c>
       <c r="K53" t="n">
-        <v>26147.01</v>
+        <v>25825.42</v>
       </c>
       <c r="L53" t="n">
-        <v>26309.4</v>
+        <v>26015.78</v>
       </c>
       <c r="M53" t="n">
-        <v>26369.21</v>
+        <v>26114.79</v>
       </c>
       <c r="N53" t="n">
-        <v>26429.02</v>
+        <v>26213.81</v>
       </c>
       <c r="O53" t="n">
-        <v>26693.99</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="inlineStr">
+        <v>26495.5</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4972,7 +4959,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4982,50 +4969,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25886.67</v>
+        <v>25840.92</v>
       </c>
       <c r="C54" t="n">
-        <v>25924.21</v>
+        <v>26007.79</v>
       </c>
       <c r="D54" t="n">
-        <v>25727.93</v>
+        <v>25784.84</v>
       </c>
       <c r="E54" t="n">
-        <v>25839.33</v>
+        <v>26003.32</v>
       </c>
       <c r="F54" t="n">
-        <v>-130.78</v>
+        <v>163.99</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0063</v>
       </c>
       <c r="H54" t="n">
-        <v>196.28</v>
+        <v>222.95</v>
       </c>
       <c r="I54" t="n">
-        <v>25627.39</v>
+        <v>25531.65</v>
       </c>
       <c r="J54" t="n">
-        <v>25635.07</v>
+        <v>25649.68</v>
       </c>
       <c r="K54" t="n">
-        <v>25825.42</v>
+        <v>25741.19</v>
       </c>
       <c r="L54" t="n">
-        <v>26015.78</v>
+        <v>25832.7</v>
       </c>
       <c r="M54" t="n">
-        <v>26114.79</v>
+        <v>25937.47</v>
       </c>
       <c r="N54" t="n">
-        <v>26213.81</v>
+        <v>26042.24</v>
       </c>
       <c r="O54" t="n">
-        <v>26495.5</v>
+        <v>26120.49</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5033,79 +5020,85 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25840.92</v>
+        <v>25985.86</v>
       </c>
       <c r="C55" t="n">
-        <v>26007.79</v>
+        <v>26167.93</v>
       </c>
       <c r="D55" t="n">
-        <v>25784.84</v>
+        <v>25958.7</v>
       </c>
       <c r="E55" t="n">
-        <v>26003.32</v>
+        <v>26046.4</v>
       </c>
       <c r="F55" t="n">
-        <v>163.99</v>
+        <v>43.08</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0017</v>
       </c>
       <c r="H55" t="n">
-        <v>222.95</v>
+        <v>209.23</v>
       </c>
       <c r="I55" t="n">
-        <v>25531.65</v>
+        <v>25561.89</v>
       </c>
       <c r="J55" t="n">
-        <v>25649.68</v>
+        <v>25833.87</v>
       </c>
       <c r="K55" t="n">
-        <v>25741.19</v>
+        <v>25891.85</v>
       </c>
       <c r="L55" t="n">
-        <v>25832.7</v>
+        <v>25949.82</v>
       </c>
       <c r="M55" t="n">
-        <v>25937.47</v>
+        <v>26114.79</v>
       </c>
       <c r="N55" t="n">
-        <v>26042.24</v>
+        <v>26279.77</v>
       </c>
       <c r="O55" t="n">
-        <v>26120.49</v>
+        <v>26230.74</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5116,25 +5109,23 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5148,50 +5139,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25985.86</v>
+        <v>26039.54</v>
       </c>
       <c r="C56" t="n">
-        <v>26167.93</v>
+        <v>26069.99</v>
       </c>
       <c r="D56" t="n">
-        <v>25958.7</v>
+        <v>25919.61</v>
       </c>
       <c r="E56" t="n">
-        <v>26046.4</v>
+        <v>26006.53</v>
       </c>
       <c r="F56" t="n">
-        <v>43.08</v>
+        <v>-39.87</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0015</v>
       </c>
       <c r="H56" t="n">
-        <v>209.23</v>
+        <v>150.38</v>
       </c>
       <c r="I56" t="n">
-        <v>25561.89</v>
+        <v>25749.47</v>
       </c>
       <c r="J56" t="n">
-        <v>25833.87</v>
+        <v>25828.71</v>
       </c>
       <c r="K56" t="n">
-        <v>25891.85</v>
+        <v>25941.79</v>
       </c>
       <c r="L56" t="n">
-        <v>25949.82</v>
+        <v>26054.86</v>
       </c>
       <c r="M56" t="n">
-        <v>26114.79</v>
+        <v>26151.02</v>
       </c>
       <c r="N56" t="n">
-        <v>26279.77</v>
+        <v>26247.17</v>
       </c>
       <c r="O56" t="n">
-        <v>26230.74</v>
+        <v>26377.16</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5199,18 +5190,18 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5218,70 +5209,68 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>26039.54</v>
+        <v>25897.22</v>
       </c>
       <c r="C57" t="n">
-        <v>26069.99</v>
+        <v>26026.78</v>
       </c>
       <c r="D57" t="n">
-        <v>25919.61</v>
+        <v>25799.66</v>
       </c>
       <c r="E57" t="n">
-        <v>26006.53</v>
+        <v>26007.63</v>
       </c>
       <c r="F57" t="n">
-        <v>-39.87</v>
+        <v>1.1</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>150.38</v>
+        <v>227.12</v>
       </c>
       <c r="I57" t="n">
-        <v>25749.47</v>
+        <v>25769.23</v>
       </c>
       <c r="J57" t="n">
-        <v>25828.71</v>
+        <v>25862.01</v>
       </c>
       <c r="K57" t="n">
-        <v>25941.79</v>
+        <v>25931.34</v>
       </c>
       <c r="L57" t="n">
-        <v>26054.86</v>
+        <v>26000.66</v>
       </c>
       <c r="M57" t="n">
-        <v>26151.02</v>
+        <v>26081.72</v>
       </c>
       <c r="N57" t="n">
-        <v>26247.17</v>
+        <v>26162.77</v>
       </c>
       <c r="O57" t="n">
-        <v>26377.16</v>
+        <v>26220.37</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
@@ -5290,7 +5279,7 @@
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5302,63 +5291,69 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>25897.22</v>
+        <v>25870.98</v>
       </c>
       <c r="C58" t="n">
-        <v>26026.78</v>
+        <v>25909.66</v>
       </c>
       <c r="D58" t="n">
-        <v>25799.66</v>
+        <v>25512.39</v>
       </c>
       <c r="E58" t="n">
-        <v>26007.63</v>
+        <v>25576.45</v>
       </c>
       <c r="F58" t="n">
-        <v>1.1</v>
+        <v>-431.18</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0</v>
+        <v>-0.0166</v>
       </c>
       <c r="H58" t="n">
-        <v>227.12</v>
+        <v>397.27</v>
       </c>
       <c r="I58" t="n">
-        <v>25769.23</v>
+        <v>25572.54</v>
       </c>
       <c r="J58" t="n">
-        <v>25862.01</v>
+        <v>25827.72</v>
       </c>
       <c r="K58" t="n">
-        <v>25931.34</v>
+        <v>25894.07</v>
       </c>
       <c r="L58" t="n">
-        <v>26000.66</v>
+        <v>25960.43</v>
       </c>
       <c r="M58" t="n">
-        <v>26081.72</v>
+        <v>26121.19</v>
       </c>
       <c r="N58" t="n">
-        <v>26162.77</v>
+        <v>26281.96</v>
       </c>
       <c r="O58" t="n">
-        <v>26220.37</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
+        <v>26253.9</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q58" s="6" t="inlineStr">
         <is>
@@ -5372,7 +5367,7 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5384,81 +5379,73 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25870.98</v>
+        <v>25555.66</v>
       </c>
       <c r="C59" t="n">
-        <v>25909.66</v>
+        <v>25612.09</v>
       </c>
       <c r="D59" t="n">
-        <v>25512.39</v>
+        <v>25361.15</v>
       </c>
       <c r="E59" t="n">
-        <v>25576.45</v>
+        <v>25361.15</v>
       </c>
       <c r="F59" t="n">
-        <v>-431.18</v>
+        <v>-215.3</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>397.27</v>
+        <v>250.94</v>
       </c>
       <c r="I59" t="n">
-        <v>25572.54</v>
+        <v>25115.12</v>
       </c>
       <c r="J59" t="n">
-        <v>25827.72</v>
+        <v>25111.89</v>
       </c>
       <c r="K59" t="n">
-        <v>25894.07</v>
+        <v>25377.81</v>
       </c>
       <c r="L59" t="n">
-        <v>25960.43</v>
+        <v>25643.74</v>
       </c>
       <c r="M59" t="n">
-        <v>26121.19</v>
+        <v>25775.08</v>
       </c>
       <c r="N59" t="n">
-        <v>26281.96</v>
+        <v>25906.43</v>
       </c>
       <c r="O59" t="n">
-        <v>26253.9</v>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
+        <v>26306.93</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
+      <c r="S59" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5472,7 +5459,7 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="11" t="inlineStr">
+      <c r="W59" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5482,50 +5469,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25555.66</v>
+        <v>25478.84</v>
       </c>
       <c r="C60" t="n">
-        <v>25612.09</v>
+        <v>25581.22</v>
       </c>
       <c r="D60" t="n">
-        <v>25361.15</v>
+        <v>25396.38</v>
       </c>
       <c r="E60" t="n">
-        <v>25361.15</v>
+        <v>25568.56</v>
       </c>
       <c r="F60" t="n">
-        <v>-215.3</v>
+        <v>207.41</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>250.94</v>
+        <v>184.84</v>
       </c>
       <c r="I60" t="n">
-        <v>25115.12</v>
+        <v>25110.21</v>
       </c>
       <c r="J60" t="n">
-        <v>25111.89</v>
+        <v>25047.48</v>
       </c>
       <c r="K60" t="n">
-        <v>25377.81</v>
+        <v>25235.68</v>
       </c>
       <c r="L60" t="n">
-        <v>25643.74</v>
+        <v>25423.89</v>
       </c>
       <c r="M60" t="n">
-        <v>25775.08</v>
+        <v>25486.62</v>
       </c>
       <c r="N60" t="n">
-        <v>25906.43</v>
+        <v>25549.35</v>
       </c>
       <c r="O60" t="n">
-        <v>26306.93</v>
+        <v>25863.03</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5533,172 +5520,178 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
       <c r="W60" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>25478.84</v>
+        <v>25498.74</v>
       </c>
       <c r="C61" t="n">
-        <v>25581.22</v>
+        <v>25548.78</v>
       </c>
       <c r="D61" t="n">
-        <v>25396.38</v>
+        <v>25325.52</v>
       </c>
       <c r="E61" t="n">
-        <v>25568.56</v>
+        <v>25440.81</v>
       </c>
       <c r="F61" t="n">
-        <v>207.41</v>
+        <v>-127.75</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.005</v>
       </c>
       <c r="H61" t="n">
-        <v>184.84</v>
+        <v>223.26</v>
       </c>
       <c r="I61" t="n">
-        <v>25110.21</v>
+        <v>25211.54</v>
       </c>
       <c r="J61" t="n">
-        <v>25047.48</v>
+        <v>25423.6</v>
       </c>
       <c r="K61" t="n">
-        <v>25235.68</v>
+        <v>25476.14</v>
       </c>
       <c r="L61" t="n">
-        <v>25423.89</v>
+        <v>25528.68</v>
       </c>
       <c r="M61" t="n">
-        <v>25486.62</v>
+        <v>25660.98</v>
       </c>
       <c r="N61" t="n">
-        <v>25549.35</v>
+        <v>25793.28</v>
       </c>
       <c r="O61" t="n">
-        <v>25863.03</v>
+        <v>25766.06</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="9" t="inlineStr">
+      <c r="W61" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>25498.74</v>
+        <v>25360.32</v>
       </c>
       <c r="C62" t="n">
-        <v>25548.78</v>
+        <v>25478.98</v>
       </c>
       <c r="D62" t="n">
-        <v>25325.52</v>
+        <v>25172.89</v>
       </c>
       <c r="E62" t="n">
-        <v>25440.81</v>
+        <v>25402.28</v>
       </c>
       <c r="F62" t="n">
-        <v>-127.75</v>
+        <v>-38.53</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.005</v>
+        <v>-0.0015</v>
       </c>
       <c r="H62" t="n">
-        <v>223.26</v>
+        <v>306.09</v>
       </c>
       <c r="I62" t="n">
-        <v>25211.54</v>
+        <v>25102.26</v>
       </c>
       <c r="J62" t="n">
-        <v>25423.6</v>
+        <v>25219.38</v>
       </c>
       <c r="K62" t="n">
-        <v>25476.14</v>
+        <v>25329.18</v>
       </c>
       <c r="L62" t="n">
-        <v>25528.68</v>
+        <v>25438.98</v>
       </c>
       <c r="M62" t="n">
-        <v>25660.98</v>
+        <v>25552.44</v>
       </c>
       <c r="N62" t="n">
-        <v>25793.28</v>
+        <v>25665.9</v>
       </c>
       <c r="O62" t="n">
-        <v>25766.06</v>
+        <v>25772.04</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
       <c r="Q62" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
@@ -5706,9 +5699,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5720,7 +5713,7 @@
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="9" t="inlineStr">
+      <c r="W62" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5734,71 +5727,69 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>25360.32</v>
+        <v>25515.96</v>
       </c>
       <c r="C63" t="n">
-        <v>25478.98</v>
+        <v>25599.07</v>
       </c>
       <c r="D63" t="n">
-        <v>25172.89</v>
+        <v>25361.7</v>
       </c>
       <c r="E63" t="n">
-        <v>25402.28</v>
+        <v>25537.75</v>
       </c>
       <c r="F63" t="n">
-        <v>-38.53</v>
+        <v>135.47</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0053</v>
       </c>
       <c r="H63" t="n">
-        <v>306.09</v>
+        <v>237.37</v>
       </c>
       <c r="I63" t="n">
-        <v>25102.26</v>
+        <v>24866.8</v>
       </c>
       <c r="J63" t="n">
-        <v>25219.38</v>
+        <v>25134.36</v>
       </c>
       <c r="K63" t="n">
-        <v>25329.18</v>
+        <v>25249.23</v>
       </c>
       <c r="L63" t="n">
-        <v>25438.98</v>
+        <v>25364.11</v>
       </c>
       <c r="M63" t="n">
-        <v>25552.44</v>
+        <v>25555.32</v>
       </c>
       <c r="N63" t="n">
-        <v>25665.9</v>
+        <v>25746.54</v>
       </c>
       <c r="O63" t="n">
-        <v>25772.04</v>
+        <v>25785.07</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
       </c>
-      <c r="Q63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
       </c>
       <c r="S63" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U63" s="8" t="n">
         <v/>
@@ -5806,67 +5797,65 @@
       <c r="V63" s="8" t="n">
         <v/>
       </c>
-      <c r="W63" s="9" t="inlineStr">
+      <c r="W63" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>25515.96</v>
+        <v>25681.6</v>
       </c>
       <c r="C64" t="n">
-        <v>25599.07</v>
+        <v>25800.62</v>
       </c>
       <c r="D64" t="n">
-        <v>25361.7</v>
+        <v>25596.05</v>
       </c>
       <c r="E64" t="n">
-        <v>25537.75</v>
+        <v/>
       </c>
       <c r="F64" t="n">
-        <v>135.47</v>
+        <v/>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0053</v>
+        <v/>
       </c>
       <c r="H64" t="n">
-        <v>237.37</v>
+        <v>204.57</v>
       </c>
       <c r="I64" t="n">
-        <v>24866.8</v>
+        <v>25124.33</v>
       </c>
       <c r="J64" t="n">
-        <v>25134.36</v>
+        <v>25329.06</v>
       </c>
       <c r="K64" t="n">
-        <v>25249.23</v>
+        <v>25419.06</v>
       </c>
       <c r="L64" t="n">
-        <v>25364.11</v>
+        <v>25509.07</v>
       </c>
       <c r="M64" t="n">
-        <v>25555.32</v>
+        <v>25656.44</v>
       </c>
       <c r="N64" t="n">
-        <v>25746.54</v>
+        <v>25803.8</v>
       </c>
       <c r="O64" t="n">
-        <v>25785.07</v>
-      </c>
-      <c r="P64" s="6" t="n">
-        <v/>
+        <v>25836.44</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q64" s="6" t="n">
         <v/>
@@ -5874,14 +5863,14 @@
       <c r="R64" s="6" t="n">
         <v/>
       </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S64" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T64" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U64" s="8" t="n">
@@ -5890,122 +5879,12 @@
       <c r="V64" s="8" t="n">
         <v/>
       </c>
-      <c r="W64" s="9" t="inlineStr">
+      <c r="W64" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>25681.6</v>
-      </c>
-      <c r="C65" t="n">
-        <v>25800.62</v>
-      </c>
-      <c r="D65" t="n">
-        <v>25596.05</v>
-      </c>
-      <c r="E65" t="n">
-        <v/>
-      </c>
-      <c r="F65" t="n">
-        <v/>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H65" t="n">
-        <v>204.57</v>
-      </c>
-      <c r="I65" t="n">
-        <v>25124.33</v>
-      </c>
-      <c r="J65" t="n">
-        <v>25329.06</v>
-      </c>
-      <c r="K65" t="n">
-        <v>25419.06</v>
-      </c>
-      <c r="L65" t="n">
-        <v>25509.07</v>
-      </c>
-      <c r="M65" t="n">
-        <v>25656.44</v>
-      </c>
-      <c r="N65" t="n">
-        <v>25803.8</v>
-      </c>
-      <c r="O65" t="n">
-        <v>25836.44</v>
-      </c>
-      <c r="P65" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S65" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W65" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="13" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I66" s="14" t="n">
-        <v>25391.48</v>
-      </c>
-      <c r="J66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O66" s="14" t="n">
-        <v>26005.19</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -483,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5820,13 +5817,13 @@
         <v>25596.05</v>
       </c>
       <c r="E64" t="n">
-        <v/>
+        <v>25716.71</v>
       </c>
       <c r="F64" t="n">
-        <v/>
+        <v>178.96</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v/>
+        <v>0.007</v>
       </c>
       <c r="H64" t="n">
         <v>204.57</v>
@@ -5852,27 +5849,25 @@
       <c r="O64" t="n">
         <v>25836.44</v>
       </c>
-      <c r="P64" s="6" t="inlineStr">
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S64" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U64" s="8" t="n">
         <v/>
       </c>
@@ -5885,6 +5880,90 @@
         </is>
       </c>
       <c r="X64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>25596.46</v>
+      </c>
+      <c r="C65" t="n">
+        <v>25656.22</v>
+      </c>
+      <c r="D65" t="n">
+        <v>25285.9</v>
+      </c>
+      <c r="E65" t="n">
+        <v>25304.06</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-412.65</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="H65" t="n">
+        <v>370.32</v>
+      </c>
+      <c r="I65" t="n">
+        <v>25391.48</v>
+      </c>
+      <c r="J65" t="n">
+        <v>25521.33</v>
+      </c>
+      <c r="K65" t="n">
+        <v>25614.43</v>
+      </c>
+      <c r="L65" t="n">
+        <v>25707.52</v>
+      </c>
+      <c r="M65" t="n">
+        <v>25819</v>
+      </c>
+      <c r="N65" t="n">
+        <v>25930.47</v>
+      </c>
+      <c r="O65" t="n">
+        <v>26005.19</v>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q65" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S65" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W65" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -110,11 +110,14 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,64 +637,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24835.56</v>
+        <v>24790.7</v>
       </c>
       <c r="C2" t="n">
-        <v>24988.71</v>
+        <v>24800.66</v>
       </c>
       <c r="D2" t="n">
-        <v>24728.57</v>
+        <v>24593.48</v>
       </c>
       <c r="E2" t="n">
-        <v>24893.58</v>
+        <v>24740.36</v>
       </c>
       <c r="F2" t="n">
-        <v>-246.11</v>
+        <v>-153.22</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0062</v>
       </c>
       <c r="H2" t="n">
-        <v>260.14</v>
+        <v>207.18</v>
       </c>
       <c r="I2" t="n">
-        <v>24616.17</v>
+        <v>24468.43</v>
       </c>
       <c r="J2" t="n">
-        <v>24911.41</v>
+        <v>24650.91</v>
       </c>
       <c r="K2" t="n">
-        <v>24999.68</v>
+        <v>24763.51</v>
       </c>
       <c r="L2" t="n">
-        <v>25087.94</v>
+        <v>24876.11</v>
       </c>
       <c r="M2" t="n">
-        <v>25279.7</v>
+        <v>25023.65</v>
       </c>
       <c r="N2" t="n">
-        <v>25471.46</v>
+        <v>25171.19</v>
       </c>
       <c r="O2" t="n">
-        <v>25456.23</v>
+        <v>25248.85</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -708,89 +711,95 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24790.7</v>
+        <v>24810</v>
       </c>
       <c r="C3" t="n">
-        <v>24800.66</v>
+        <v>25088.28</v>
       </c>
       <c r="D3" t="n">
-        <v>24593.48</v>
+        <v>24761.72</v>
       </c>
       <c r="E3" t="n">
-        <v>24740.36</v>
+        <v>24994.83</v>
       </c>
       <c r="F3" t="n">
-        <v>-153.22</v>
+        <v>254.47</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0103</v>
       </c>
       <c r="H3" t="n">
-        <v>207.18</v>
+        <v>326.56</v>
       </c>
       <c r="I3" t="n">
-        <v>24468.43</v>
+        <v>24386.3</v>
       </c>
       <c r="J3" t="n">
-        <v>24650.91</v>
+        <v>24554.82</v>
       </c>
       <c r="K3" t="n">
-        <v>24763.51</v>
+        <v>24636.77</v>
       </c>
       <c r="L3" t="n">
-        <v>24876.11</v>
+        <v>24718.71</v>
       </c>
       <c r="M3" t="n">
-        <v>25023.65</v>
+        <v>24843.95</v>
       </c>
       <c r="N3" t="n">
-        <v>25171.19</v>
+        <v>24969.18</v>
       </c>
       <c r="O3" t="n">
-        <v>25248.85</v>
+        <v>25007.84</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
-      </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -798,83 +807,81 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24810</v>
+        <v>24848.51</v>
       </c>
       <c r="C4" t="n">
-        <v>25088.28</v>
+        <v>24869.63</v>
       </c>
       <c r="D4" t="n">
-        <v>24761.72</v>
+        <v>24547.7</v>
       </c>
       <c r="E4" t="n">
-        <v>24994.83</v>
+        <v>24671.22</v>
       </c>
       <c r="F4" t="n">
-        <v>254.47</v>
+        <v>-323.61</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.0129</v>
       </c>
       <c r="H4" t="n">
-        <v>326.56</v>
+        <v>321.93</v>
       </c>
       <c r="I4" t="n">
-        <v>24386.3</v>
+        <v>24435.16</v>
       </c>
       <c r="J4" t="n">
-        <v>24554.82</v>
+        <v>24703.19</v>
       </c>
       <c r="K4" t="n">
-        <v>24636.77</v>
+        <v>24831.55</v>
       </c>
       <c r="L4" t="n">
-        <v>24718.71</v>
+        <v>24959.92</v>
       </c>
       <c r="M4" t="n">
-        <v>24843.95</v>
+        <v>25158.11</v>
       </c>
       <c r="N4" t="n">
-        <v>24969.18</v>
+        <v>25356.3</v>
       </c>
       <c r="O4" t="n">
-        <v>25007.84</v>
+        <v>25414.84</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
+      </c>
       <c r="W4" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -882,67 +889,63 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24848.51</v>
+        <v>24724.34</v>
       </c>
       <c r="C5" t="n">
-        <v>24869.63</v>
+        <v>24762.24</v>
       </c>
       <c r="D5" t="n">
-        <v>24547.7</v>
+        <v>24556.78</v>
       </c>
       <c r="E5" t="n">
-        <v>24671.22</v>
+        <v>24626.89</v>
       </c>
       <c r="F5" t="n">
-        <v>-323.61</v>
+        <v>-44.33</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0018</v>
       </c>
       <c r="H5" t="n">
-        <v>321.93</v>
+        <v>205.46</v>
       </c>
       <c r="I5" t="n">
-        <v>24435.16</v>
+        <v>24225.77</v>
       </c>
       <c r="J5" t="n">
-        <v>24703.19</v>
+        <v>24330.57</v>
       </c>
       <c r="K5" t="n">
-        <v>24831.55</v>
+        <v>24510.25</v>
       </c>
       <c r="L5" t="n">
-        <v>24959.92</v>
+        <v>24689.94</v>
       </c>
       <c r="M5" t="n">
-        <v>25158.11</v>
+        <v>24832.19</v>
       </c>
       <c r="N5" t="n">
-        <v>25356.3</v>
+        <v>24974.43</v>
       </c>
       <c r="O5" t="n">
-        <v>25414.84</v>
+        <v>25191.56</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -954,60 +957,64 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="W5" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24724.34</v>
+        <v>24815.22</v>
       </c>
       <c r="C6" t="n">
-        <v>24762.24</v>
+        <v>25024.27</v>
       </c>
       <c r="D6" t="n">
-        <v>24556.78</v>
+        <v>24794.84</v>
       </c>
       <c r="E6" t="n">
-        <v>24626.89</v>
+        <v>24995.81</v>
       </c>
       <c r="F6" t="n">
-        <v>-44.33</v>
+        <v>368.92</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.015</v>
       </c>
       <c r="H6" t="n">
-        <v>205.46</v>
+        <v>229.43</v>
       </c>
       <c r="I6" t="n">
-        <v>24225.77</v>
+        <v>24351.32</v>
       </c>
       <c r="J6" t="n">
-        <v>24330.57</v>
+        <v>24405.12</v>
       </c>
       <c r="K6" t="n">
-        <v>24510.25</v>
+        <v>24524.16</v>
       </c>
       <c r="L6" t="n">
-        <v>24689.94</v>
+        <v>24643.2</v>
       </c>
       <c r="M6" t="n">
-        <v>24832.19</v>
+        <v>24729.62</v>
       </c>
       <c r="N6" t="n">
-        <v>24974.43</v>
+        <v>24816.04</v>
       </c>
       <c r="O6" t="n">
-        <v>25191.56</v>
+        <v>24967.7</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1018,78 +1025,80 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24815.22</v>
+        <v>25028.93</v>
       </c>
       <c r="C7" t="n">
-        <v>25024.27</v>
+        <v>25095.66</v>
       </c>
       <c r="D7" t="n">
-        <v>24794.84</v>
+        <v>24887</v>
       </c>
       <c r="E7" t="n">
-        <v>24995.81</v>
+        <v>25040.28</v>
       </c>
       <c r="F7" t="n">
-        <v>368.92</v>
+        <v>44.47</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.015</v>
+        <v>0.0018</v>
       </c>
       <c r="H7" t="n">
-        <v>229.43</v>
+        <v>208.66</v>
       </c>
       <c r="I7" t="n">
-        <v>24351.32</v>
+        <v>24565.41</v>
       </c>
       <c r="J7" t="n">
-        <v>24405.12</v>
+        <v>24809.51</v>
       </c>
       <c r="K7" t="n">
-        <v>24524.16</v>
+        <v>24881.1</v>
       </c>
       <c r="L7" t="n">
-        <v>24643.2</v>
+        <v>24952.68</v>
       </c>
       <c r="M7" t="n">
-        <v>24729.62</v>
+        <v>25110.53</v>
       </c>
       <c r="N7" t="n">
-        <v>24816.04</v>
+        <v>25268.37</v>
       </c>
       <c r="O7" t="n">
-        <v>24967.7</v>
+        <v>25253.7</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1107,20 +1116,16 @@
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1130,50 +1135,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25028.93</v>
+        <v>25025.13</v>
       </c>
       <c r="C8" t="n">
-        <v>25095.66</v>
+        <v>25655.82</v>
       </c>
       <c r="D8" t="n">
-        <v>24887</v>
+        <v>24994.64</v>
       </c>
       <c r="E8" t="n">
-        <v>25040.28</v>
+        <v>25580.88</v>
       </c>
       <c r="F8" t="n">
-        <v>44.47</v>
+        <v>540.6</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0216</v>
       </c>
       <c r="H8" t="n">
-        <v>208.66</v>
+        <v>661.1799999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>24565.41</v>
+        <v>24678.34</v>
       </c>
       <c r="J8" t="n">
-        <v>24809.51</v>
+        <v>24856.09</v>
       </c>
       <c r="K8" t="n">
-        <v>24881.1</v>
+        <v>24935.95</v>
       </c>
       <c r="L8" t="n">
-        <v>24952.68</v>
+        <v>25015.8</v>
       </c>
       <c r="M8" t="n">
-        <v>25110.53</v>
+        <v>25144.61</v>
       </c>
       <c r="N8" t="n">
-        <v>25268.37</v>
+        <v>25273.41</v>
       </c>
       <c r="O8" t="n">
-        <v>25253.7</v>
+        <v>25304.32</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1191,16 +1196,20 @@
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1210,50 +1219,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25025.13</v>
+        <v>25763.97</v>
       </c>
       <c r="C9" t="n">
-        <v>25655.82</v>
+        <v>25826.78</v>
       </c>
       <c r="D9" t="n">
-        <v>24994.64</v>
+        <v>25611.69</v>
       </c>
       <c r="E9" t="n">
-        <v>25580.88</v>
+        <v>25779.31</v>
       </c>
       <c r="F9" t="n">
-        <v>540.6</v>
+        <v>198.43</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0216</v>
+        <v>0.0078</v>
       </c>
       <c r="H9" t="n">
-        <v>661.1799999999999</v>
+        <v>215.09</v>
       </c>
       <c r="I9" t="n">
-        <v>24678.34</v>
+        <v>24333.46</v>
       </c>
       <c r="J9" t="n">
-        <v>24856.09</v>
+        <v>25047.53</v>
       </c>
       <c r="K9" t="n">
-        <v>24935.95</v>
+        <v>25250.29</v>
       </c>
       <c r="L9" t="n">
-        <v>25015.8</v>
+        <v>25453.06</v>
       </c>
       <c r="M9" t="n">
-        <v>25144.61</v>
+        <v>25911.47</v>
       </c>
       <c r="N9" t="n">
-        <v>25273.41</v>
+        <v>26369.89</v>
       </c>
       <c r="O9" t="n">
-        <v>25304.32</v>
+        <v>26317</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1271,20 +1280,16 @@
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1294,50 +1299,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25763.97</v>
+        <v>25811.9</v>
       </c>
       <c r="C10" t="n">
-        <v>25826.78</v>
+        <v>25900.1</v>
       </c>
       <c r="D10" t="n">
-        <v>25611.69</v>
+        <v>25698.56</v>
       </c>
       <c r="E10" t="n">
-        <v>25779.31</v>
+        <v>25817.89</v>
       </c>
       <c r="F10" t="n">
-        <v>198.43</v>
+        <v>38.58</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0078</v>
+        <v>0.0015</v>
       </c>
       <c r="H10" t="n">
-        <v>215.09</v>
+        <v>201.54</v>
       </c>
       <c r="I10" t="n">
-        <v>24333.46</v>
+        <v>25396.6</v>
       </c>
       <c r="J10" t="n">
-        <v>25047.53</v>
+        <v>25594.26</v>
       </c>
       <c r="K10" t="n">
-        <v>25250.29</v>
+        <v>25671.77</v>
       </c>
       <c r="L10" t="n">
-        <v>25453.06</v>
+        <v>25749.27</v>
       </c>
       <c r="M10" t="n">
-        <v>25911.47</v>
+        <v>25886.86</v>
       </c>
       <c r="N10" t="n">
-        <v>26369.89</v>
+        <v>26024.44</v>
       </c>
       <c r="O10" t="n">
-        <v>26317</v>
+        <v>26041.87</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1350,12 +1355,12 @@
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U10" s="8" t="n">
@@ -1364,7 +1369,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1374,69 +1379,73 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25811.9</v>
+        <v>25770.45</v>
       </c>
       <c r="C11" t="n">
-        <v>25900.1</v>
+        <v>25811.97</v>
       </c>
       <c r="D11" t="n">
-        <v>25698.56</v>
+        <v>25465.12</v>
       </c>
       <c r="E11" t="n">
-        <v>25817.89</v>
+        <v>25465.25</v>
       </c>
       <c r="F11" t="n">
-        <v>38.58</v>
+        <v>-352.64</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0137</v>
       </c>
       <c r="H11" t="n">
-        <v>201.54</v>
+        <v>346.85</v>
       </c>
       <c r="I11" t="n">
-        <v>25396.6</v>
+        <v>25497.02</v>
       </c>
       <c r="J11" t="n">
-        <v>25594.26</v>
+        <v>25625.63</v>
       </c>
       <c r="K11" t="n">
-        <v>25671.77</v>
+        <v>25717.12</v>
       </c>
       <c r="L11" t="n">
-        <v>25749.27</v>
+        <v>25808.61</v>
       </c>
       <c r="M11" t="n">
-        <v>25886.86</v>
+        <v>25918.66</v>
       </c>
       <c r="N11" t="n">
-        <v>26024.44</v>
+        <v>26028.71</v>
       </c>
       <c r="O11" t="n">
-        <v>26041.87</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>26101.64</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1446,7 +1455,7 @@
       </c>
       <c r="W11" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
@@ -1454,61 +1463,61 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25770.45</v>
+        <v>25274.94</v>
       </c>
       <c r="C12" t="n">
-        <v>25811.97</v>
+        <v>25280.16</v>
       </c>
       <c r="D12" t="n">
-        <v>25465.12</v>
+        <v>24830.17</v>
       </c>
       <c r="E12" t="n">
-        <v>25465.25</v>
+        <v>24897.45</v>
       </c>
       <c r="F12" t="n">
-        <v>-352.64</v>
+        <v>-567.8</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0223</v>
       </c>
       <c r="H12" t="n">
-        <v>346.85</v>
+        <v>449.99</v>
       </c>
       <c r="I12" t="n">
-        <v>25497.02</v>
+        <v>25118.27</v>
       </c>
       <c r="J12" t="n">
-        <v>25625.63</v>
+        <v>25031.75</v>
       </c>
       <c r="K12" t="n">
-        <v>25717.12</v>
+        <v>25291.82</v>
       </c>
       <c r="L12" t="n">
-        <v>25808.61</v>
+        <v>25551.9</v>
       </c>
       <c r="M12" t="n">
-        <v>25918.66</v>
+        <v>25638.68</v>
       </c>
       <c r="N12" t="n">
-        <v>26028.71</v>
+        <v>25725.45</v>
       </c>
       <c r="O12" t="n">
-        <v>26101.64</v>
+        <v>26158.82</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -1528,7 +1537,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1538,134 +1547,134 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25274.94</v>
+        <v>25097.48</v>
       </c>
       <c r="C13" t="n">
-        <v>25280.16</v>
+        <v>25127.76</v>
       </c>
       <c r="D13" t="n">
-        <v>24830.17</v>
+        <v>24867.32</v>
       </c>
       <c r="E13" t="n">
-        <v>24897.45</v>
+        <v>25118.27</v>
       </c>
       <c r="F13" t="n">
-        <v>-567.8</v>
+        <v>220.82</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0089</v>
       </c>
       <c r="H13" t="n">
-        <v>449.99</v>
+        <v>260.44</v>
       </c>
       <c r="I13" t="n">
-        <v>25118.27</v>
+        <v>24380.18</v>
       </c>
       <c r="J13" t="n">
-        <v>25031.75</v>
+        <v>24368.6</v>
       </c>
       <c r="K13" t="n">
-        <v>25291.82</v>
+        <v>24672.45</v>
       </c>
       <c r="L13" t="n">
-        <v>25551.9</v>
+        <v>24976.31</v>
       </c>
       <c r="M13" t="n">
-        <v>25638.68</v>
+        <v>25122.44</v>
       </c>
       <c r="N13" t="n">
-        <v>25725.45</v>
+        <v>25268.58</v>
       </c>
       <c r="O13" t="n">
-        <v>26158.82</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
+        <v>25730.15</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25097.48</v>
+        <v>25081.19</v>
       </c>
       <c r="C14" t="n">
-        <v>25127.76</v>
+        <v>25195.83</v>
       </c>
       <c r="D14" t="n">
-        <v>24867.32</v>
+        <v>24937.52</v>
       </c>
       <c r="E14" t="n">
-        <v>25118.27</v>
+        <v>25067.09</v>
       </c>
       <c r="F14" t="n">
-        <v>220.82</v>
+        <v>-51.18</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.002</v>
       </c>
       <c r="H14" t="n">
-        <v>260.44</v>
+        <v>258.31</v>
       </c>
       <c r="I14" t="n">
-        <v>24380.18</v>
+        <v>24606.88</v>
       </c>
       <c r="J14" t="n">
-        <v>24368.6</v>
+        <v>24918.19</v>
       </c>
       <c r="K14" t="n">
-        <v>24672.45</v>
+        <v>24988.05</v>
       </c>
       <c r="L14" t="n">
-        <v>24976.31</v>
+        <v>25057.9</v>
       </c>
       <c r="M14" t="n">
-        <v>25122.44</v>
+        <v>25248.49</v>
       </c>
       <c r="N14" t="n">
-        <v>25268.58</v>
+        <v>25439.07</v>
       </c>
       <c r="O14" t="n">
-        <v>25730.15</v>
+        <v>25388.2</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1673,18 +1682,18 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1692,7 +1701,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1706,50 +1715,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25081.19</v>
+        <v>24963.8</v>
       </c>
       <c r="C15" t="n">
-        <v>25195.83</v>
+        <v>25154.58</v>
       </c>
       <c r="D15" t="n">
-        <v>24937.52</v>
+        <v>24963.8</v>
       </c>
       <c r="E15" t="n">
-        <v>25067.09</v>
+        <v>25114.25</v>
       </c>
       <c r="F15" t="n">
-        <v>-51.18</v>
+        <v>47.16</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="H15" t="n">
-        <v>258.31</v>
+        <v>190.78</v>
       </c>
       <c r="I15" t="n">
-        <v>24606.88</v>
+        <v>24679.21</v>
       </c>
       <c r="J15" t="n">
-        <v>24918.19</v>
+        <v>24808.99</v>
       </c>
       <c r="K15" t="n">
-        <v>24988.05</v>
+        <v>24937.93</v>
       </c>
       <c r="L15" t="n">
-        <v>25057.9</v>
+        <v>25066.88</v>
       </c>
       <c r="M15" t="n">
-        <v>25248.49</v>
+        <v>25196.25</v>
       </c>
       <c r="N15" t="n">
-        <v>25439.07</v>
+        <v>25325.61</v>
       </c>
       <c r="O15" t="n">
-        <v>25388.2</v>
+        <v>25454.14</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1757,10 +1766,8 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R15" s="6" t="n">
+        <v/>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
@@ -1776,7 +1783,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1790,59 +1797,63 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24963.8</v>
+        <v>24932.62</v>
       </c>
       <c r="C16" t="n">
-        <v>25154.58</v>
+        <v>25204.68</v>
       </c>
       <c r="D16" t="n">
-        <v>24963.8</v>
+        <v>24869.25</v>
       </c>
       <c r="E16" t="n">
-        <v>25114.25</v>
+        <v>25147.03</v>
       </c>
       <c r="F16" t="n">
-        <v>47.16</v>
+        <v>32.78</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0013</v>
       </c>
       <c r="H16" t="n">
-        <v>190.78</v>
+        <v>335.43</v>
       </c>
       <c r="I16" t="n">
-        <v>24679.21</v>
+        <v>24773.02</v>
       </c>
       <c r="J16" t="n">
-        <v>24808.99</v>
+        <v>24951</v>
       </c>
       <c r="K16" t="n">
-        <v>24937.93</v>
+        <v>25018.86</v>
       </c>
       <c r="L16" t="n">
-        <v>25066.88</v>
+        <v>25086.72</v>
       </c>
       <c r="M16" t="n">
-        <v>25196.25</v>
+        <v>25209.64</v>
       </c>
       <c r="N16" t="n">
-        <v>25325.61</v>
+        <v>25332.56</v>
       </c>
       <c r="O16" t="n">
-        <v>25454.14</v>
+        <v>25345.36</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
@@ -1858,7 +1869,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1872,50 +1883,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24932.62</v>
+        <v>24970.05</v>
       </c>
       <c r="C17" t="n">
-        <v>25204.68</v>
+        <v>25055.48</v>
       </c>
       <c r="D17" t="n">
-        <v>24869.25</v>
+        <v>24839.23</v>
       </c>
       <c r="E17" t="n">
-        <v>25147.03</v>
+        <v>24999.53</v>
       </c>
       <c r="F17" t="n">
-        <v>32.78</v>
+        <v>-147.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0059</v>
       </c>
       <c r="H17" t="n">
-        <v>335.43</v>
+        <v>216.25</v>
       </c>
       <c r="I17" t="n">
-        <v>24773.02</v>
+        <v>24533.82</v>
       </c>
       <c r="J17" t="n">
-        <v>24951</v>
+        <v>24866.63</v>
       </c>
       <c r="K17" t="n">
-        <v>25018.86</v>
+        <v>24979.31</v>
       </c>
       <c r="L17" t="n">
-        <v>25086.72</v>
+        <v>25092</v>
       </c>
       <c r="M17" t="n">
-        <v>25209.64</v>
+        <v>25314.74</v>
       </c>
       <c r="N17" t="n">
-        <v>25332.56</v>
+        <v>25537.49</v>
       </c>
       <c r="O17" t="n">
-        <v>25345.36</v>
+        <v>25540.11</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1927,12 +1938,12 @@
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1944,64 +1955,60 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24970.05</v>
+        <v>25018.95</v>
       </c>
       <c r="C18" t="n">
-        <v>25055.48</v>
+        <v>25021.51</v>
       </c>
       <c r="D18" t="n">
-        <v>24839.23</v>
+        <v>24696.17</v>
       </c>
       <c r="E18" t="n">
-        <v>24999.53</v>
+        <v>24915.49</v>
       </c>
       <c r="F18" t="n">
-        <v>-147.5</v>
+        <v>-84.04000000000001</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0059</v>
+        <v>-0.0034</v>
       </c>
       <c r="H18" t="n">
-        <v>216.25</v>
+        <v>325.34</v>
       </c>
       <c r="I18" t="n">
-        <v>24533.82</v>
+        <v>24622.98</v>
       </c>
       <c r="J18" t="n">
-        <v>24866.63</v>
+        <v>24809.37</v>
       </c>
       <c r="K18" t="n">
-        <v>24979.31</v>
+        <v>24891.4</v>
       </c>
       <c r="L18" t="n">
-        <v>25092</v>
+        <v>24973.44</v>
       </c>
       <c r="M18" t="n">
-        <v>25314.74</v>
+        <v>25107.65</v>
       </c>
       <c r="N18" t="n">
-        <v>25537.49</v>
+        <v>25241.87</v>
       </c>
       <c r="O18" t="n">
-        <v>25540.11</v>
+        <v>25271.73</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2030,7 +2037,7 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2040,67 +2047,65 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25018.95</v>
+        <v>24755.09</v>
       </c>
       <c r="C19" t="n">
-        <v>25021.51</v>
+        <v>24850.75</v>
       </c>
       <c r="D19" t="n">
-        <v>24696.17</v>
+        <v>24651.34</v>
       </c>
       <c r="E19" t="n">
-        <v>24915.49</v>
+        <v>24830.98</v>
       </c>
       <c r="F19" t="n">
-        <v>-84.04000000000001</v>
+        <v>-84.51000000000001</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>-0.0034</v>
       </c>
       <c r="H19" t="n">
-        <v>325.34</v>
+        <v>199.41</v>
       </c>
       <c r="I19" t="n">
-        <v>24622.98</v>
+        <v>24370.83</v>
       </c>
       <c r="J19" t="n">
-        <v>24809.37</v>
+        <v>24618.48</v>
       </c>
       <c r="K19" t="n">
-        <v>24891.4</v>
+        <v>24752.82</v>
       </c>
       <c r="L19" t="n">
-        <v>24973.44</v>
+        <v>24887.17</v>
       </c>
       <c r="M19" t="n">
-        <v>25107.65</v>
+        <v>25078.16</v>
       </c>
       <c r="N19" t="n">
-        <v>25241.87</v>
+        <v>25269.16</v>
       </c>
       <c r="O19" t="n">
-        <v>25271.73</v>
+        <v>25346.85</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q19" s="6" t="n">
+        <v/>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2112,7 +2117,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2122,50 +2127,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24755.09</v>
+        <v>24769.15</v>
       </c>
       <c r="C20" t="n">
-        <v>24850.75</v>
+        <v>24974.53</v>
       </c>
       <c r="D20" t="n">
-        <v>24651.34</v>
+        <v>24751.13</v>
       </c>
       <c r="E20" t="n">
-        <v>24830.98</v>
+        <v>24846.69</v>
       </c>
       <c r="F20" t="n">
-        <v>-84.51000000000001</v>
+        <v>15.71</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>199.41</v>
+        <v>223.4</v>
       </c>
       <c r="I20" t="n">
-        <v>24370.83</v>
+        <v>24451.93</v>
       </c>
       <c r="J20" t="n">
-        <v>24618.48</v>
+        <v>24671.54</v>
       </c>
       <c r="K20" t="n">
-        <v>24752.82</v>
+        <v>24731.28</v>
       </c>
       <c r="L20" t="n">
-        <v>24887.17</v>
+        <v>24791.01</v>
       </c>
       <c r="M20" t="n">
-        <v>25078.16</v>
+        <v>24930.69</v>
       </c>
       <c r="N20" t="n">
-        <v>25269.16</v>
+        <v>25070.36</v>
       </c>
       <c r="O20" t="n">
-        <v>25346.85</v>
+        <v>25050.16</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2173,18 +2178,18 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2192,60 +2197,64 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24769.15</v>
+        <v>24922.1</v>
       </c>
       <c r="C21" t="n">
-        <v>24974.53</v>
+        <v>25011.35</v>
       </c>
       <c r="D21" t="n">
-        <v>24751.13</v>
+        <v>24817.34</v>
       </c>
       <c r="E21" t="n">
-        <v>24846.69</v>
+        <v>25011.35</v>
       </c>
       <c r="F21" t="n">
-        <v>15.71</v>
+        <v>164.66</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0066</v>
       </c>
       <c r="H21" t="n">
-        <v>223.4</v>
+        <v>194.01</v>
       </c>
       <c r="I21" t="n">
-        <v>24451.93</v>
+        <v>24527.73</v>
       </c>
       <c r="J21" t="n">
-        <v>24671.54</v>
+        <v>24615.22</v>
       </c>
       <c r="K21" t="n">
-        <v>24731.28</v>
+        <v>24734.99</v>
       </c>
       <c r="L21" t="n">
-        <v>24791.01</v>
+        <v>24854.76</v>
       </c>
       <c r="M21" t="n">
-        <v>24930.69</v>
+        <v>24958.39</v>
       </c>
       <c r="N21" t="n">
-        <v>25070.36</v>
+        <v>25062.02</v>
       </c>
       <c r="O21" t="n">
-        <v>25050.16</v>
+        <v>25197.93</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2258,7 +2267,7 @@
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -2266,13 +2275,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2286,50 +2297,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24922.1</v>
+        <v>25001.31</v>
       </c>
       <c r="C22" t="n">
-        <v>25011.35</v>
+        <v>25271.34</v>
       </c>
       <c r="D22" t="n">
-        <v>24817.34</v>
+        <v>24984.27</v>
       </c>
       <c r="E22" t="n">
-        <v>25011.35</v>
+        <v>25155.41</v>
       </c>
       <c r="F22" t="n">
-        <v>164.66</v>
+        <v>144.06</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0058</v>
       </c>
       <c r="H22" t="n">
-        <v>194.01</v>
+        <v>287.07</v>
       </c>
       <c r="I22" t="n">
-        <v>24527.73</v>
+        <v>24623.33</v>
       </c>
       <c r="J22" t="n">
-        <v>24615.22</v>
+        <v>24865.84</v>
       </c>
       <c r="K22" t="n">
-        <v>24734.99</v>
+        <v>24914.34</v>
       </c>
       <c r="L22" t="n">
-        <v>24854.76</v>
+        <v>24962.85</v>
       </c>
       <c r="M22" t="n">
-        <v>24958.39</v>
+        <v>25108.35</v>
       </c>
       <c r="N22" t="n">
-        <v>25062.02</v>
+        <v>25253.86</v>
       </c>
       <c r="O22" t="n">
-        <v>25197.93</v>
+        <v>25205.36</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2347,18 +2358,20 @@
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U22" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W22" s="9" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2372,171 +2385,165 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25001.31</v>
+        <v>24994.05</v>
       </c>
       <c r="C23" t="n">
-        <v>25271.34</v>
+        <v>25074.28</v>
       </c>
       <c r="D23" t="n">
-        <v>24984.27</v>
+        <v>24696.59</v>
       </c>
       <c r="E23" t="n">
-        <v>25155.41</v>
+        <v>24763.12</v>
       </c>
       <c r="F23" t="n">
-        <v>144.06</v>
+        <v>-392.29</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0156</v>
       </c>
       <c r="H23" t="n">
-        <v>287.07</v>
+        <v>377.69</v>
       </c>
       <c r="I23" t="n">
-        <v>24623.33</v>
+        <v>24697.2</v>
       </c>
       <c r="J23" t="n">
-        <v>24865.84</v>
+        <v>24882.14</v>
       </c>
       <c r="K23" t="n">
-        <v>24914.34</v>
+        <v>25011.88</v>
       </c>
       <c r="L23" t="n">
-        <v>24962.85</v>
+        <v>25141.61</v>
       </c>
       <c r="M23" t="n">
-        <v>25108.35</v>
+        <v>25298.95</v>
       </c>
       <c r="N23" t="n">
-        <v>25253.86</v>
+        <v>25456.28</v>
       </c>
       <c r="O23" t="n">
-        <v>25205.36</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
+        <v>25558.41</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24994.05</v>
+        <v>24830.41</v>
       </c>
       <c r="C24" t="n">
-        <v>25074.28</v>
+        <v>25099.68</v>
       </c>
       <c r="D24" t="n">
-        <v>24696.59</v>
+        <v>24821.67</v>
       </c>
       <c r="E24" t="n">
-        <v>24763.12</v>
+        <v>25099</v>
       </c>
       <c r="F24" t="n">
-        <v>-392.29</v>
+        <v>335.88</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0136</v>
       </c>
       <c r="H24" t="n">
-        <v>377.69</v>
+        <v>278.01</v>
       </c>
       <c r="I24" t="n">
-        <v>24697.2</v>
+        <v>24318.9</v>
       </c>
       <c r="J24" t="n">
-        <v>24882.14</v>
+        <v>24324.27</v>
       </c>
       <c r="K24" t="n">
-        <v>25011.88</v>
+        <v>24574.27</v>
       </c>
       <c r="L24" t="n">
-        <v>25141.61</v>
+        <v>24824.28</v>
       </c>
       <c r="M24" t="n">
-        <v>25298.95</v>
+        <v>24951.96</v>
       </c>
       <c r="N24" t="n">
-        <v>25456.28</v>
+        <v>25079.65</v>
       </c>
       <c r="O24" t="n">
-        <v>25558.41</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
+        <v>25451.97</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
@@ -2544,50 +2551,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24830.41</v>
+        <v>25459.32</v>
       </c>
       <c r="C25" t="n">
-        <v>25099.68</v>
+        <v>25560.4</v>
       </c>
       <c r="D25" t="n">
-        <v>24821.67</v>
+        <v>25361.03</v>
       </c>
       <c r="E25" t="n">
-        <v>25099</v>
+        <v>25361.03</v>
       </c>
       <c r="F25" t="n">
-        <v>335.88</v>
+        <v>262.03</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0104</v>
       </c>
       <c r="H25" t="n">
-        <v>278.01</v>
+        <v>199.37</v>
       </c>
       <c r="I25" t="n">
-        <v>24318.9</v>
+        <v>24543.66</v>
       </c>
       <c r="J25" t="n">
-        <v>24324.27</v>
+        <v>24890.15</v>
       </c>
       <c r="K25" t="n">
-        <v>24574.27</v>
+        <v>24960</v>
       </c>
       <c r="L25" t="n">
-        <v>24824.28</v>
+        <v>25029.84</v>
       </c>
       <c r="M25" t="n">
-        <v>24951.96</v>
+        <v>25238</v>
       </c>
       <c r="N25" t="n">
-        <v>25079.65</v>
+        <v>25446.17</v>
       </c>
       <c r="O25" t="n">
-        <v>25451.97</v>
+        <v>25377.69</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2610,13 +2617,15 @@
       </c>
       <c r="U25" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2626,50 +2635,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25459.32</v>
+        <v>25496.13</v>
       </c>
       <c r="C26" t="n">
-        <v>25560.4</v>
+        <v>25553.47</v>
       </c>
       <c r="D26" t="n">
-        <v>25361.03</v>
+        <v>25307.17</v>
       </c>
       <c r="E26" t="n">
-        <v>25361.03</v>
+        <v>25464.01</v>
       </c>
       <c r="F26" t="n">
-        <v>262.03</v>
+        <v>102.98</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0104</v>
+        <v>0.0041</v>
       </c>
       <c r="H26" t="n">
-        <v>199.37</v>
+        <v>246.3</v>
       </c>
       <c r="I26" t="n">
-        <v>24543.66</v>
+        <v>25161.66</v>
       </c>
       <c r="J26" t="n">
-        <v>24890.15</v>
+        <v>25111.82</v>
       </c>
       <c r="K26" t="n">
-        <v>24960</v>
+        <v>25261.34</v>
       </c>
       <c r="L26" t="n">
-        <v>25029.84</v>
+        <v>25410.87</v>
       </c>
       <c r="M26" t="n">
-        <v>25238</v>
+        <v>25460.71</v>
       </c>
       <c r="N26" t="n">
-        <v>25446.17</v>
+        <v>25510.56</v>
       </c>
       <c r="O26" t="n">
-        <v>25377.69</v>
+        <v>25759.77</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2687,7 +2696,7 @@
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U26" s="8" t="inlineStr">
@@ -2695,65 +2704,67 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="V26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25496.13</v>
+        <v>25551.97</v>
       </c>
       <c r="C27" t="n">
-        <v>25553.47</v>
+        <v>25571.45</v>
       </c>
       <c r="D27" t="n">
-        <v>25307.17</v>
+        <v>25336.39</v>
       </c>
       <c r="E27" t="n">
-        <v>25464.01</v>
+        <v>25460.48</v>
       </c>
       <c r="F27" t="n">
-        <v>102.98</v>
+        <v>-3.53</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0001</v>
       </c>
       <c r="H27" t="n">
-        <v>246.3</v>
+        <v>235.06</v>
       </c>
       <c r="I27" t="n">
-        <v>25161.66</v>
+        <v>25060.87</v>
       </c>
       <c r="J27" t="n">
-        <v>25111.82</v>
+        <v>25234.55</v>
       </c>
       <c r="K27" t="n">
-        <v>25261.34</v>
+        <v>25340.86</v>
       </c>
       <c r="L27" t="n">
-        <v>25410.87</v>
+        <v>25447.17</v>
       </c>
       <c r="M27" t="n">
-        <v>25460.71</v>
+        <v>25587.16</v>
       </c>
       <c r="N27" t="n">
-        <v>25510.56</v>
+        <v>25727.16</v>
       </c>
       <c r="O27" t="n">
-        <v>25759.77</v>
+        <v>25799.77</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2761,85 +2772,83 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25551.97</v>
+        <v>25487.45</v>
       </c>
       <c r="C28" t="n">
-        <v>25571.45</v>
+        <v>25651.16</v>
       </c>
       <c r="D28" t="n">
-        <v>25336.39</v>
+        <v>25303.11</v>
       </c>
       <c r="E28" t="n">
-        <v>25460.48</v>
+        <v>25612.03</v>
       </c>
       <c r="F28" t="n">
-        <v>-3.53</v>
+        <v>151.55</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.006</v>
       </c>
       <c r="H28" t="n">
-        <v>235.06</v>
+        <v>348.05</v>
       </c>
       <c r="I28" t="n">
-        <v>25060.87</v>
+        <v>25101.33</v>
       </c>
       <c r="J28" t="n">
-        <v>25234.55</v>
+        <v>25228.7</v>
       </c>
       <c r="K28" t="n">
-        <v>25340.86</v>
+        <v>25342.95</v>
       </c>
       <c r="L28" t="n">
-        <v>25447.17</v>
+        <v>25457.2</v>
       </c>
       <c r="M28" t="n">
-        <v>25587.16</v>
+        <v>25578.01</v>
       </c>
       <c r="N28" t="n">
-        <v>25727.16</v>
+        <v>25698.82</v>
       </c>
       <c r="O28" t="n">
-        <v>25799.77</v>
+        <v>25806.51</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2854,11 +2863,13 @@
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2866,7 +2877,7 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2880,50 +2891,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25487.45</v>
+        <v>25709.37</v>
       </c>
       <c r="C29" t="n">
-        <v>25651.16</v>
+        <v>25891.51</v>
       </c>
       <c r="D29" t="n">
-        <v>25303.11</v>
+        <v>25549.53</v>
       </c>
       <c r="E29" t="n">
-        <v>25612.03</v>
+        <v>25629.24</v>
       </c>
       <c r="F29" t="n">
-        <v>151.55</v>
+        <v>17.21</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0007</v>
       </c>
       <c r="H29" t="n">
-        <v>348.05</v>
+        <v>341.98</v>
       </c>
       <c r="I29" t="n">
-        <v>25101.33</v>
+        <v>24955.06</v>
       </c>
       <c r="J29" t="n">
-        <v>25228.7</v>
+        <v>25331.43</v>
       </c>
       <c r="K29" t="n">
-        <v>25342.95</v>
+        <v>25438</v>
       </c>
       <c r="L29" t="n">
-        <v>25457.2</v>
+        <v>25544.58</v>
       </c>
       <c r="M29" t="n">
-        <v>25578.01</v>
+        <v>25786.05</v>
       </c>
       <c r="N29" t="n">
-        <v>25698.82</v>
+        <v>26027.53</v>
       </c>
       <c r="O29" t="n">
-        <v>25806.51</v>
+        <v>25999.21</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2931,19 +2942,17 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U29" s="8" t="n">
@@ -2952,64 +2961,60 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25709.37</v>
+        <v>25855.12</v>
       </c>
       <c r="C30" t="n">
-        <v>25891.51</v>
+        <v>26096.93</v>
       </c>
       <c r="D30" t="n">
-        <v>25549.53</v>
+        <v>25855.12</v>
       </c>
       <c r="E30" t="n">
-        <v>25629.24</v>
+        <v>26001.31</v>
       </c>
       <c r="F30" t="n">
-        <v>17.21</v>
+        <v>372.07</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0145</v>
       </c>
       <c r="H30" t="n">
-        <v>341.98</v>
+        <v>241.81</v>
       </c>
       <c r="I30" t="n">
-        <v>24955.06</v>
+        <v>25207.55</v>
       </c>
       <c r="J30" t="n">
-        <v>25331.43</v>
+        <v>25241.62</v>
       </c>
       <c r="K30" t="n">
-        <v>25438</v>
+        <v>25458.25</v>
       </c>
       <c r="L30" t="n">
-        <v>25544.58</v>
+        <v>25674.88</v>
       </c>
       <c r="M30" t="n">
-        <v>25786.05</v>
+        <v>25800.23</v>
       </c>
       <c r="N30" t="n">
-        <v>26027.53</v>
+        <v>25925.58</v>
       </c>
       <c r="O30" t="n">
-        <v>25999.21</v>
+        <v>26233.49</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3022,7 +3027,7 @@
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
@@ -3030,13 +3035,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U30" s="8" t="n">
-        <v/>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3046,50 +3053,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25855.12</v>
+        <v>26189.62</v>
       </c>
       <c r="C31" t="n">
-        <v>26096.93</v>
+        <v>26266.5</v>
       </c>
       <c r="D31" t="n">
-        <v>25855.12</v>
+        <v>26082.43</v>
       </c>
       <c r="E31" t="n">
-        <v>26001.31</v>
+        <v>26202.35</v>
       </c>
       <c r="F31" t="n">
-        <v>372.07</v>
+        <v>201.04</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0077</v>
       </c>
       <c r="H31" t="n">
-        <v>241.81</v>
+        <v>184.07</v>
       </c>
       <c r="I31" t="n">
-        <v>25207.55</v>
+        <v>25613.31</v>
       </c>
       <c r="J31" t="n">
-        <v>25241.62</v>
+        <v>25772.14</v>
       </c>
       <c r="K31" t="n">
-        <v>25458.25</v>
+        <v>25880.41</v>
       </c>
       <c r="L31" t="n">
-        <v>25674.88</v>
+        <v>25988.67</v>
       </c>
       <c r="M31" t="n">
-        <v>25800.23</v>
+        <v>26122.22</v>
       </c>
       <c r="N31" t="n">
-        <v>25925.58</v>
+        <v>26255.76</v>
       </c>
       <c r="O31" t="n">
-        <v>26233.49</v>
+        <v>26338.74</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3118,7 +3125,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3128,50 +3135,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26189.62</v>
+        <v>26393.43</v>
       </c>
       <c r="C32" t="n">
-        <v>26266.5</v>
+        <v>26403.81</v>
       </c>
       <c r="D32" t="n">
-        <v>26082.43</v>
+        <v>26123.18</v>
       </c>
       <c r="E32" t="n">
-        <v>26202.35</v>
+        <v>26126.3</v>
       </c>
       <c r="F32" t="n">
-        <v>201.04</v>
+        <v>-76.05</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0029</v>
       </c>
       <c r="H32" t="n">
-        <v>184.07</v>
+        <v>280.63</v>
       </c>
       <c r="I32" t="n">
-        <v>25613.31</v>
+        <v>25898.36</v>
       </c>
       <c r="J32" t="n">
-        <v>25772.14</v>
+        <v>26032.22</v>
       </c>
       <c r="K32" t="n">
-        <v>25880.41</v>
+        <v>26110.31</v>
       </c>
       <c r="L32" t="n">
-        <v>25988.67</v>
+        <v>26188.41</v>
       </c>
       <c r="M32" t="n">
-        <v>26122.22</v>
+        <v>26294.38</v>
       </c>
       <c r="N32" t="n">
-        <v>26255.76</v>
+        <v>26400.36</v>
       </c>
       <c r="O32" t="n">
-        <v>26338.74</v>
+        <v>26450.57</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3179,12 +3186,14 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
@@ -3194,66 +3203,70 @@
       </c>
       <c r="U32" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>26393.43</v>
+        <v>26116.27</v>
       </c>
       <c r="C33" t="n">
-        <v>26403.81</v>
+        <v>26229.33</v>
       </c>
       <c r="D33" t="n">
-        <v>26123.18</v>
+        <v>26081.69</v>
       </c>
       <c r="E33" t="n">
-        <v>26126.3</v>
+        <v>26140.13</v>
       </c>
       <c r="F33" t="n">
-        <v>-76.05</v>
+        <v>13.83</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0005</v>
       </c>
       <c r="H33" t="n">
-        <v>280.63</v>
+        <v>147.64</v>
       </c>
       <c r="I33" t="n">
-        <v>25898.36</v>
+        <v>25842.55</v>
       </c>
       <c r="J33" t="n">
-        <v>26032.22</v>
+        <v>25777.07</v>
       </c>
       <c r="K33" t="n">
-        <v>26110.31</v>
+        <v>25985.99</v>
       </c>
       <c r="L33" t="n">
-        <v>26188.41</v>
+        <v>26194.9</v>
       </c>
       <c r="M33" t="n">
-        <v>26294.38</v>
+        <v>26266.62</v>
       </c>
       <c r="N33" t="n">
-        <v>26400.36</v>
+        <v>26338.33</v>
       </c>
       <c r="O33" t="n">
-        <v>26450.57</v>
+        <v>26684.44</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3261,87 +3274,81 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R33" s="6" t="n">
+        <v/>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26116.27</v>
+        <v>26235.8</v>
       </c>
       <c r="C34" t="n">
-        <v>26229.33</v>
+        <v>26445.18</v>
       </c>
       <c r="D34" t="n">
-        <v>26081.69</v>
+        <v>26223.64</v>
       </c>
       <c r="E34" t="n">
-        <v>26140.13</v>
+        <v>26319.45</v>
       </c>
       <c r="F34" t="n">
-        <v>13.83</v>
+        <v>179.32</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0069</v>
       </c>
       <c r="H34" t="n">
-        <v>147.64</v>
+        <v>221.54</v>
       </c>
       <c r="I34" t="n">
-        <v>25842.55</v>
+        <v>25934.05</v>
       </c>
       <c r="J34" t="n">
-        <v>25777.07</v>
+        <v>25984.8</v>
       </c>
       <c r="K34" t="n">
-        <v>25985.99</v>
+        <v>26066.31</v>
       </c>
       <c r="L34" t="n">
-        <v>26194.9</v>
+        <v>26147.82</v>
       </c>
       <c r="M34" t="n">
-        <v>26266.62</v>
+        <v>26213.95</v>
       </c>
       <c r="N34" t="n">
-        <v>26338.33</v>
+        <v>26280.08</v>
       </c>
       <c r="O34" t="n">
-        <v>26684.44</v>
+        <v>26376.97</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3352,78 +3359,80 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>26235.8</v>
+        <v>26360.44</v>
       </c>
       <c r="C35" t="n">
-        <v>26445.18</v>
+        <v>26441.91</v>
       </c>
       <c r="D35" t="n">
-        <v>26223.64</v>
+        <v>26302.19</v>
       </c>
       <c r="E35" t="n">
-        <v>26319.45</v>
+        <v>26323.88</v>
       </c>
       <c r="F35" t="n">
-        <v>179.32</v>
+        <v>4.43</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0002</v>
       </c>
       <c r="H35" t="n">
-        <v>221.54</v>
+        <v>139.72</v>
       </c>
       <c r="I35" t="n">
-        <v>25934.05</v>
+        <v>26002.1</v>
       </c>
       <c r="J35" t="n">
-        <v>25984.8</v>
+        <v>26090.43</v>
       </c>
       <c r="K35" t="n">
-        <v>26066.31</v>
+        <v>26208.68</v>
       </c>
       <c r="L35" t="n">
-        <v>26147.82</v>
+        <v>26326.93</v>
       </c>
       <c r="M35" t="n">
-        <v>26213.95</v>
+        <v>26430.22</v>
       </c>
       <c r="N35" t="n">
-        <v>26280.08</v>
+        <v>26533.51</v>
       </c>
       <c r="O35" t="n">
-        <v>26376.97</v>
+        <v>26666.72</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3434,9 +3443,9 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
@@ -3444,70 +3453,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26360.44</v>
+        <v>26378</v>
       </c>
       <c r="C36" t="n">
-        <v>26441.91</v>
+        <v>26504.54</v>
       </c>
       <c r="D36" t="n">
-        <v>26302.19</v>
+        <v>26245.57</v>
       </c>
       <c r="E36" t="n">
-        <v>26323.88</v>
+        <v>26391.42</v>
       </c>
       <c r="F36" t="n">
-        <v>4.43</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0026</v>
       </c>
       <c r="H36" t="n">
-        <v>139.72</v>
+        <v>258.97</v>
       </c>
       <c r="I36" t="n">
-        <v>26002.1</v>
+        <v>26162.47</v>
       </c>
       <c r="J36" t="n">
-        <v>26090.43</v>
+        <v>26160.08</v>
       </c>
       <c r="K36" t="n">
-        <v>26208.68</v>
+        <v>26254.02</v>
       </c>
       <c r="L36" t="n">
-        <v>26326.93</v>
+        <v>26347.97</v>
       </c>
       <c r="M36" t="n">
-        <v>26430.22</v>
+        <v>26393.74</v>
       </c>
       <c r="N36" t="n">
-        <v>26533.51</v>
+        <v>26439.52</v>
       </c>
       <c r="O36" t="n">
-        <v>26666.72</v>
+        <v>26581.63</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3515,26 +3524,30 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3548,50 +3561,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26378</v>
+        <v>26452</v>
       </c>
       <c r="C37" t="n">
-        <v>26504.54</v>
+        <v>26573.5</v>
       </c>
       <c r="D37" t="n">
-        <v>26245.57</v>
+        <v>26313.58</v>
       </c>
       <c r="E37" t="n">
-        <v>26391.42</v>
+        <v>26331.07</v>
       </c>
       <c r="F37" t="n">
-        <v>67.54000000000001</v>
+        <v>-60.35</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0023</v>
       </c>
       <c r="H37" t="n">
-        <v>258.97</v>
+        <v>259.92</v>
       </c>
       <c r="I37" t="n">
-        <v>26162.47</v>
+        <v>25986.6</v>
       </c>
       <c r="J37" t="n">
-        <v>26160.08</v>
+        <v>26140.63</v>
       </c>
       <c r="K37" t="n">
-        <v>26254.02</v>
+        <v>26261.94</v>
       </c>
       <c r="L37" t="n">
-        <v>26347.97</v>
+        <v>26383.24</v>
       </c>
       <c r="M37" t="n">
-        <v>26393.74</v>
+        <v>26520.9</v>
       </c>
       <c r="N37" t="n">
-        <v>26439.52</v>
+        <v>26658.57</v>
       </c>
       <c r="O37" t="n">
-        <v>26581.63</v>
+        <v>26763.51</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3599,30 +3612,26 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3636,50 +3645,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26452</v>
+        <v>26437.35</v>
       </c>
       <c r="C38" t="n">
-        <v>26573.5</v>
+        <v>26489.78</v>
       </c>
       <c r="D38" t="n">
-        <v>26313.58</v>
+        <v>26285.23</v>
       </c>
       <c r="E38" t="n">
-        <v>26331.07</v>
+        <v>26299.74</v>
       </c>
       <c r="F38" t="n">
-        <v>-60.35</v>
+        <v>-31.33</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0012</v>
       </c>
       <c r="H38" t="n">
-        <v>259.92</v>
+        <v>204.55</v>
       </c>
       <c r="I38" t="n">
-        <v>25986.6</v>
+        <v>26053.66</v>
       </c>
       <c r="J38" t="n">
-        <v>26140.63</v>
+        <v>26014.92</v>
       </c>
       <c r="K38" t="n">
-        <v>26261.94</v>
+        <v>26201.11</v>
       </c>
       <c r="L38" t="n">
-        <v>26383.24</v>
+        <v>26387.31</v>
       </c>
       <c r="M38" t="n">
-        <v>26520.9</v>
+        <v>26461.03</v>
       </c>
       <c r="N38" t="n">
-        <v>26658.57</v>
+        <v>26534.76</v>
       </c>
       <c r="O38" t="n">
-        <v>26763.51</v>
+        <v>26833.42</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3706,64 +3715,64 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26437.35</v>
+        <v>26445.99</v>
       </c>
       <c r="C39" t="n">
-        <v>26489.78</v>
+        <v>26541.34</v>
       </c>
       <c r="D39" t="n">
-        <v>26285.23</v>
+        <v>26404.95</v>
       </c>
       <c r="E39" t="n">
-        <v>26299.74</v>
+        <v>26440.31</v>
       </c>
       <c r="F39" t="n">
-        <v>-31.33</v>
+        <v>140.57</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0053</v>
       </c>
       <c r="H39" t="n">
-        <v>204.55</v>
+        <v>136.39</v>
       </c>
       <c r="I39" t="n">
-        <v>26053.66</v>
+        <v>26080.68</v>
       </c>
       <c r="J39" t="n">
-        <v>26014.92</v>
+        <v>26051.31</v>
       </c>
       <c r="K39" t="n">
-        <v>26201.11</v>
+        <v>26197.47</v>
       </c>
       <c r="L39" t="n">
-        <v>26387.31</v>
+        <v>26343.62</v>
       </c>
       <c r="M39" t="n">
-        <v>26461.03</v>
+        <v>26402.01</v>
       </c>
       <c r="N39" t="n">
-        <v>26534.76</v>
+        <v>26460.41</v>
       </c>
       <c r="O39" t="n">
-        <v>26833.42</v>
+        <v>26694.33</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3774,9 +3783,9 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
@@ -3784,70 +3793,68 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>26445.99</v>
+        <v>26490.3</v>
       </c>
       <c r="C40" t="n">
-        <v>26541.34</v>
+        <v>26493.5</v>
       </c>
       <c r="D40" t="n">
-        <v>26404.95</v>
+        <v>26338.61</v>
       </c>
       <c r="E40" t="n">
-        <v>26440.31</v>
+        <v>26338.61</v>
       </c>
       <c r="F40" t="n">
-        <v>140.57</v>
+        <v>-101.7</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0038</v>
       </c>
       <c r="H40" t="n">
-        <v>136.39</v>
+        <v>154.89</v>
       </c>
       <c r="I40" t="n">
-        <v>26080.68</v>
+        <v>26268.56</v>
       </c>
       <c r="J40" t="n">
-        <v>26051.31</v>
+        <v>26287.5</v>
       </c>
       <c r="K40" t="n">
-        <v>26197.47</v>
+        <v>26372.12</v>
       </c>
       <c r="L40" t="n">
-        <v>26343.62</v>
+        <v>26456.73</v>
       </c>
       <c r="M40" t="n">
-        <v>26402.01</v>
+        <v>26508.51</v>
       </c>
       <c r="N40" t="n">
-        <v>26460.41</v>
+        <v>26560.28</v>
       </c>
       <c r="O40" t="n">
-        <v>26694.33</v>
+        <v>26677.73</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3855,91 +3862,97 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26490.3</v>
+        <v>26280.86</v>
       </c>
       <c r="C41" t="n">
-        <v>26493.5</v>
+        <v>26292.95</v>
       </c>
       <c r="D41" t="n">
-        <v>26338.61</v>
+        <v>26119.54</v>
       </c>
       <c r="E41" t="n">
-        <v>26338.61</v>
+        <v>26128.36</v>
       </c>
       <c r="F41" t="n">
-        <v>-101.7</v>
+        <v>-210.25</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.008</v>
       </c>
       <c r="H41" t="n">
-        <v>154.89</v>
+        <v>173.41</v>
       </c>
       <c r="I41" t="n">
-        <v>26268.56</v>
+        <v>26183.72</v>
       </c>
       <c r="J41" t="n">
-        <v>26287.5</v>
+        <v>26145</v>
       </c>
       <c r="K41" t="n">
-        <v>26372.12</v>
+        <v>26261.16</v>
       </c>
       <c r="L41" t="n">
-        <v>26456.73</v>
+        <v>26377.33</v>
       </c>
       <c r="M41" t="n">
-        <v>26508.51</v>
+        <v>26416.05</v>
       </c>
       <c r="N41" t="n">
-        <v>26560.28</v>
+        <v>26454.78</v>
       </c>
       <c r="O41" t="n">
-        <v>26677.73</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+        <v>26648.39</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
@@ -3958,78 +3971,70 @@
       </c>
       <c r="W41" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26280.86</v>
+        <v>26146.12</v>
       </c>
       <c r="C42" t="n">
-        <v>26292.95</v>
+        <v>26187.82</v>
       </c>
       <c r="D42" t="n">
-        <v>26119.54</v>
+        <v>26063.37</v>
       </c>
       <c r="E42" t="n">
-        <v>26128.36</v>
+        <v>26091.33</v>
       </c>
       <c r="F42" t="n">
-        <v>-210.25</v>
+        <v>-37.03</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0014</v>
       </c>
       <c r="H42" t="n">
-        <v>173.41</v>
+        <v>124.45</v>
       </c>
       <c r="I42" t="n">
-        <v>26183.72</v>
+        <v>25946.13</v>
       </c>
       <c r="J42" t="n">
-        <v>26145</v>
+        <v>25916.01</v>
       </c>
       <c r="K42" t="n">
-        <v>26261.16</v>
+        <v>26041.65</v>
       </c>
       <c r="L42" t="n">
-        <v>26377.33</v>
+        <v>26167.3</v>
       </c>
       <c r="M42" t="n">
-        <v>26416.05</v>
+        <v>26215.06</v>
       </c>
       <c r="N42" t="n">
-        <v>26454.78</v>
+        <v>26262.83</v>
       </c>
       <c r="O42" t="n">
-        <v>26648.39</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
+        <v>26466.36</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4044,7 +4049,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4054,60 +4059,64 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>26146.12</v>
+        <v>26050.95</v>
       </c>
       <c r="C43" t="n">
-        <v>26187.82</v>
+        <v>26062.15</v>
       </c>
       <c r="D43" t="n">
-        <v>26063.37</v>
+        <v>25914.11</v>
       </c>
       <c r="E43" t="n">
-        <v>26091.33</v>
+        <v>25983.04</v>
       </c>
       <c r="F43" t="n">
-        <v>-37.03</v>
+        <v>-108.29</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0042</v>
       </c>
       <c r="H43" t="n">
-        <v>124.45</v>
+        <v>148.04</v>
       </c>
       <c r="I43" t="n">
-        <v>25946.13</v>
+        <v>25938.92</v>
       </c>
       <c r="J43" t="n">
-        <v>25916.01</v>
+        <v>25949.75</v>
       </c>
       <c r="K43" t="n">
-        <v>26041.65</v>
+        <v>26029.1</v>
       </c>
       <c r="L43" t="n">
-        <v>26167.3</v>
+        <v>26108.46</v>
       </c>
       <c r="M43" t="n">
-        <v>26215.06</v>
+        <v>26153.56</v>
       </c>
       <c r="N43" t="n">
-        <v>26262.83</v>
+        <v>26198.65</v>
       </c>
       <c r="O43" t="n">
-        <v>26466.36</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
+        <v>26312.27</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
@@ -4124,7 +4133,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4134,83 +4143,81 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26050.95</v>
+        <v>25998.95</v>
       </c>
       <c r="C44" t="n">
-        <v>26062.15</v>
+        <v>26166.25</v>
       </c>
       <c r="D44" t="n">
-        <v>25914.11</v>
+        <v>25969.52</v>
       </c>
       <c r="E44" t="n">
-        <v>25983.04</v>
+        <v>26136.56</v>
       </c>
       <c r="F44" t="n">
-        <v>-108.29</v>
+        <v>153.52</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.0059</v>
       </c>
       <c r="H44" t="n">
-        <v>148.04</v>
+        <v>196.73</v>
       </c>
       <c r="I44" t="n">
-        <v>25938.92</v>
+        <v>25766.07</v>
       </c>
       <c r="J44" t="n">
-        <v>25949.75</v>
+        <v>25832.45</v>
       </c>
       <c r="K44" t="n">
-        <v>26029.1</v>
+        <v>25909.02</v>
       </c>
       <c r="L44" t="n">
-        <v>26108.46</v>
+        <v>25985.58</v>
       </c>
       <c r="M44" t="n">
-        <v>26153.56</v>
+        <v>26057.06</v>
       </c>
       <c r="N44" t="n">
-        <v>26198.65</v>
+        <v>26128.53</v>
       </c>
       <c r="O44" t="n">
-        <v>26312.27</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
+        <v>26210.19</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
       <c r="W44" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr"/>
@@ -4218,50 +4225,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>25998.95</v>
+        <v>26091.29</v>
       </c>
       <c r="C45" t="n">
-        <v>26166.25</v>
+        <v>26171.7</v>
       </c>
       <c r="D45" t="n">
-        <v>25969.52</v>
+        <v>26038.07</v>
       </c>
       <c r="E45" t="n">
-        <v>26136.56</v>
+        <v>26106.6</v>
       </c>
       <c r="F45" t="n">
-        <v>153.52</v>
+        <v>-29.96</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0011</v>
       </c>
       <c r="H45" t="n">
-        <v>196.73</v>
+        <v>133.63</v>
       </c>
       <c r="I45" t="n">
-        <v>25766.07</v>
+        <v>25772.79</v>
       </c>
       <c r="J45" t="n">
-        <v>25832.45</v>
+        <v>25974.17</v>
       </c>
       <c r="K45" t="n">
-        <v>25909.02</v>
+        <v>26038.2</v>
       </c>
       <c r="L45" t="n">
-        <v>25985.58</v>
+        <v>26102.22</v>
       </c>
       <c r="M45" t="n">
-        <v>26057.06</v>
+        <v>26234.93</v>
       </c>
       <c r="N45" t="n">
-        <v>26128.53</v>
+        <v>26367.63</v>
       </c>
       <c r="O45" t="n">
-        <v>26210.19</v>
+        <v>26362.98</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4269,81 +4276,83 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>26091.29</v>
+        <v>26206.01</v>
       </c>
       <c r="C46" t="n">
-        <v>26171.7</v>
+        <v>26341.52</v>
       </c>
       <c r="D46" t="n">
-        <v>26038.07</v>
+        <v>26164.11</v>
       </c>
       <c r="E46" t="n">
-        <v>26106.6</v>
+        <v>26266.14</v>
       </c>
       <c r="F46" t="n">
-        <v>-29.96</v>
+        <v>159.54</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0061</v>
       </c>
       <c r="H46" t="n">
-        <v>133.63</v>
+        <v>177.41</v>
       </c>
       <c r="I46" t="n">
-        <v>25772.79</v>
+        <v>25904.44</v>
       </c>
       <c r="J46" t="n">
-        <v>25974.17</v>
+        <v>25973.83</v>
       </c>
       <c r="K46" t="n">
-        <v>26038.2</v>
+        <v>26039.79</v>
       </c>
       <c r="L46" t="n">
-        <v>26102.22</v>
+        <v>26105.74</v>
       </c>
       <c r="M46" t="n">
-        <v>26234.93</v>
+        <v>26173.41</v>
       </c>
       <c r="N46" t="n">
-        <v>26367.63</v>
+        <v>26241.09</v>
       </c>
       <c r="O46" t="n">
-        <v>26362.98</v>
+        <v>26305.33</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4351,83 +4360,83 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R46" s="6" t="n">
+        <v/>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W46" s="11" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>26206.01</v>
+        <v>26255.41</v>
       </c>
       <c r="C47" t="n">
-        <v>26341.52</v>
+        <v>26466.76</v>
       </c>
       <c r="D47" t="n">
-        <v>26164.11</v>
+        <v>26196.92</v>
       </c>
       <c r="E47" t="n">
-        <v>26266.14</v>
+        <v>26285.96</v>
       </c>
       <c r="F47" t="n">
-        <v>159.54</v>
+        <v>19.82</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0061</v>
+        <v>0.0008</v>
       </c>
       <c r="H47" t="n">
-        <v>177.41</v>
+        <v>269.84</v>
       </c>
       <c r="I47" t="n">
-        <v>25904.44</v>
+        <v>25986.7</v>
       </c>
       <c r="J47" t="n">
-        <v>25973.83</v>
+        <v>26095.39</v>
       </c>
       <c r="K47" t="n">
-        <v>26039.79</v>
+        <v>26177.44</v>
       </c>
       <c r="L47" t="n">
-        <v>26105.74</v>
+        <v>26259.48</v>
       </c>
       <c r="M47" t="n">
-        <v>26173.41</v>
+        <v>26354.85</v>
       </c>
       <c r="N47" t="n">
-        <v>26241.09</v>
+        <v>26450.21</v>
       </c>
       <c r="O47" t="n">
-        <v>26305.33</v>
+        <v>26518.93</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4440,7 +4449,7 @@
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
@@ -4450,15 +4459,13 @@
       </c>
       <c r="U47" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W47" s="11" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4468,50 +4475,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>26255.41</v>
+        <v>26354.37</v>
       </c>
       <c r="C48" t="n">
-        <v>26466.76</v>
+        <v>26402.81</v>
       </c>
       <c r="D48" t="n">
-        <v>26196.92</v>
+        <v>26241.77</v>
       </c>
       <c r="E48" t="n">
-        <v>26285.96</v>
+        <v>26367.24</v>
       </c>
       <c r="F48" t="n">
-        <v>19.82</v>
+        <v>81.28</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0031</v>
       </c>
       <c r="H48" t="n">
-        <v>269.84</v>
+        <v>161.04</v>
       </c>
       <c r="I48" t="n">
-        <v>25986.7</v>
+        <v>25927.08</v>
       </c>
       <c r="J48" t="n">
-        <v>26095.39</v>
+        <v>25993.18</v>
       </c>
       <c r="K48" t="n">
-        <v>26177.44</v>
+        <v>26151.04</v>
       </c>
       <c r="L48" t="n">
-        <v>26259.48</v>
+        <v>26308.9</v>
       </c>
       <c r="M48" t="n">
-        <v>26354.85</v>
+        <v>26420.88</v>
       </c>
       <c r="N48" t="n">
-        <v>26450.21</v>
+        <v>26532.86</v>
       </c>
       <c r="O48" t="n">
-        <v>26518.93</v>
+        <v>26736.6</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4524,76 +4531,78 @@
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>26354.37</v>
+        <v>26494.61</v>
       </c>
       <c r="C49" t="n">
-        <v>26402.81</v>
+        <v>26618.74</v>
       </c>
       <c r="D49" t="n">
-        <v>26241.77</v>
+        <v>26467.36</v>
       </c>
       <c r="E49" t="n">
-        <v>26367.24</v>
+        <v>26569.99</v>
       </c>
       <c r="F49" t="n">
-        <v>81.28</v>
+        <v>202.75</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0077</v>
       </c>
       <c r="H49" t="n">
-        <v>161.04</v>
+        <v>151.38</v>
       </c>
       <c r="I49" t="n">
-        <v>25927.08</v>
+        <v>26080.73</v>
       </c>
       <c r="J49" t="n">
-        <v>25993.18</v>
+        <v>26228.67</v>
       </c>
       <c r="K49" t="n">
-        <v>26151.04</v>
+        <v>26286.72</v>
       </c>
       <c r="L49" t="n">
-        <v>26308.9</v>
+        <v>26344.77</v>
       </c>
       <c r="M49" t="n">
-        <v>26420.88</v>
+        <v>26447.76</v>
       </c>
       <c r="N49" t="n">
-        <v>26532.86</v>
+        <v>26550.76</v>
       </c>
       <c r="O49" t="n">
-        <v>26736.6</v>
+        <v>26563.85</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4611,106 +4620,106 @@
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>26494.61</v>
+        <v>26464.14</v>
       </c>
       <c r="C50" t="n">
-        <v>26618.74</v>
+        <v>26471.79</v>
       </c>
       <c r="D50" t="n">
-        <v>26467.36</v>
+        <v>26249.59</v>
       </c>
       <c r="E50" t="n">
-        <v>26569.99</v>
+        <v>26258.11</v>
       </c>
       <c r="F50" t="n">
-        <v>202.75</v>
+        <v>-311.88</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0117</v>
       </c>
       <c r="H50" t="n">
-        <v>151.38</v>
+        <v>222.2</v>
       </c>
       <c r="I50" t="n">
-        <v>26080.73</v>
+        <v>26315.98</v>
       </c>
       <c r="J50" t="n">
-        <v>26228.67</v>
+        <v>26432.08</v>
       </c>
       <c r="K50" t="n">
-        <v>26286.72</v>
+        <v>26494.3</v>
       </c>
       <c r="L50" t="n">
-        <v>26344.77</v>
+        <v>26556.52</v>
       </c>
       <c r="M50" t="n">
-        <v>26447.76</v>
+        <v>26645.68</v>
       </c>
       <c r="N50" t="n">
-        <v>26550.76</v>
+        <v>26734.84</v>
       </c>
       <c r="O50" t="n">
-        <v>26563.85</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
+        <v>26770.12</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
+      </c>
       <c r="W50" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X50" t="inlineStr"/>
@@ -4718,61 +4727,61 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>26464.14</v>
+        <v>26150.75</v>
       </c>
       <c r="C51" t="n">
-        <v>26471.79</v>
+        <v>26206.13</v>
       </c>
       <c r="D51" t="n">
-        <v>26249.59</v>
+        <v>25916.76</v>
       </c>
       <c r="E51" t="n">
-        <v>26258.11</v>
+        <v>25970.11</v>
       </c>
       <c r="F51" t="n">
-        <v>-311.88</v>
+        <v>-288</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.011</v>
       </c>
       <c r="H51" t="n">
-        <v>222.2</v>
+        <v>289.37</v>
       </c>
       <c r="I51" t="n">
-        <v>26315.98</v>
+        <v>26027.39</v>
       </c>
       <c r="J51" t="n">
-        <v>26432.08</v>
+        <v>25984.62</v>
       </c>
       <c r="K51" t="n">
-        <v>26494.3</v>
+        <v>26147.01</v>
       </c>
       <c r="L51" t="n">
-        <v>26556.52</v>
+        <v>26309.4</v>
       </c>
       <c r="M51" t="n">
-        <v>26645.68</v>
+        <v>26369.21</v>
       </c>
       <c r="N51" t="n">
-        <v>26734.84</v>
+        <v>26429.02</v>
       </c>
       <c r="O51" t="n">
-        <v>26770.12</v>
+        <v>26693.99</v>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -4792,7 +4801,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4802,66 +4811,62 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>26150.75</v>
+        <v>25886.67</v>
       </c>
       <c r="C52" t="n">
-        <v>26206.13</v>
+        <v>25924.21</v>
       </c>
       <c r="D52" t="n">
-        <v>25916.76</v>
+        <v>25727.93</v>
       </c>
       <c r="E52" t="n">
-        <v>25970.11</v>
+        <v>25839.33</v>
       </c>
       <c r="F52" t="n">
-        <v>-288</v>
+        <v>-130.78</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.005</v>
       </c>
       <c r="H52" t="n">
-        <v>289.37</v>
+        <v>196.28</v>
       </c>
       <c r="I52" t="n">
-        <v>26027.39</v>
+        <v>25627.39</v>
       </c>
       <c r="J52" t="n">
-        <v>25984.62</v>
+        <v>25635.07</v>
       </c>
       <c r="K52" t="n">
-        <v>26147.01</v>
+        <v>25825.42</v>
       </c>
       <c r="L52" t="n">
-        <v>26309.4</v>
+        <v>26015.78</v>
       </c>
       <c r="M52" t="n">
-        <v>26369.21</v>
+        <v>26114.79</v>
       </c>
       <c r="N52" t="n">
-        <v>26429.02</v>
+        <v>26213.81</v>
       </c>
       <c r="O52" t="n">
-        <v>26693.99</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
+        <v>26495.5</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4876,7 +4881,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4886,50 +4891,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25886.67</v>
+        <v>25840.92</v>
       </c>
       <c r="C53" t="n">
-        <v>25924.21</v>
+        <v>26007.79</v>
       </c>
       <c r="D53" t="n">
-        <v>25727.93</v>
+        <v>25784.84</v>
       </c>
       <c r="E53" t="n">
-        <v>25839.33</v>
+        <v>26003.32</v>
       </c>
       <c r="F53" t="n">
-        <v>-130.78</v>
+        <v>163.99</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0063</v>
       </c>
       <c r="H53" t="n">
-        <v>196.28</v>
+        <v>222.95</v>
       </c>
       <c r="I53" t="n">
-        <v>25627.39</v>
+        <v>25531.65</v>
       </c>
       <c r="J53" t="n">
-        <v>25635.07</v>
+        <v>25649.68</v>
       </c>
       <c r="K53" t="n">
-        <v>25825.42</v>
+        <v>25741.19</v>
       </c>
       <c r="L53" t="n">
-        <v>26015.78</v>
+        <v>25832.7</v>
       </c>
       <c r="M53" t="n">
-        <v>26114.79</v>
+        <v>25937.47</v>
       </c>
       <c r="N53" t="n">
-        <v>26213.81</v>
+        <v>26042.24</v>
       </c>
       <c r="O53" t="n">
-        <v>26495.5</v>
+        <v>26120.49</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4937,79 +4942,85 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25840.92</v>
+        <v>25985.86</v>
       </c>
       <c r="C54" t="n">
-        <v>26007.79</v>
+        <v>26167.93</v>
       </c>
       <c r="D54" t="n">
-        <v>25784.84</v>
+        <v>25958.7</v>
       </c>
       <c r="E54" t="n">
-        <v>26003.32</v>
+        <v>26046.4</v>
       </c>
       <c r="F54" t="n">
-        <v>163.99</v>
+        <v>43.08</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0017</v>
       </c>
       <c r="H54" t="n">
-        <v>222.95</v>
+        <v>209.23</v>
       </c>
       <c r="I54" t="n">
-        <v>25531.65</v>
+        <v>25561.89</v>
       </c>
       <c r="J54" t="n">
-        <v>25649.68</v>
+        <v>25833.87</v>
       </c>
       <c r="K54" t="n">
-        <v>25741.19</v>
+        <v>25891.85</v>
       </c>
       <c r="L54" t="n">
-        <v>25832.7</v>
+        <v>25949.82</v>
       </c>
       <c r="M54" t="n">
-        <v>25937.47</v>
+        <v>26114.79</v>
       </c>
       <c r="N54" t="n">
-        <v>26042.24</v>
+        <v>26279.77</v>
       </c>
       <c r="O54" t="n">
-        <v>26120.49</v>
+        <v>26230.74</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5027,18 +5038,16 @@
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5052,50 +5061,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25985.86</v>
+        <v>26039.54</v>
       </c>
       <c r="C55" t="n">
-        <v>26167.93</v>
+        <v>26069.99</v>
       </c>
       <c r="D55" t="n">
-        <v>25958.7</v>
+        <v>25919.61</v>
       </c>
       <c r="E55" t="n">
-        <v>26046.4</v>
+        <v>26006.53</v>
       </c>
       <c r="F55" t="n">
-        <v>43.08</v>
+        <v>-39.87</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0015</v>
       </c>
       <c r="H55" t="n">
-        <v>209.23</v>
+        <v>150.38</v>
       </c>
       <c r="I55" t="n">
-        <v>25561.89</v>
+        <v>25749.47</v>
       </c>
       <c r="J55" t="n">
-        <v>25833.87</v>
+        <v>25828.71</v>
       </c>
       <c r="K55" t="n">
-        <v>25891.85</v>
+        <v>25941.79</v>
       </c>
       <c r="L55" t="n">
-        <v>25949.82</v>
+        <v>26054.86</v>
       </c>
       <c r="M55" t="n">
-        <v>26114.79</v>
+        <v>26151.02</v>
       </c>
       <c r="N55" t="n">
-        <v>26279.77</v>
+        <v>26247.17</v>
       </c>
       <c r="O55" t="n">
-        <v>26230.74</v>
+        <v>26377.16</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5103,18 +5112,18 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5122,79 +5131,77 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>26039.54</v>
+        <v>25897.22</v>
       </c>
       <c r="C56" t="n">
-        <v>26069.99</v>
+        <v>26026.78</v>
       </c>
       <c r="D56" t="n">
-        <v>25919.61</v>
+        <v>25799.66</v>
       </c>
       <c r="E56" t="n">
-        <v>26006.53</v>
+        <v>26007.63</v>
       </c>
       <c r="F56" t="n">
-        <v>-39.87</v>
+        <v>1.1</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>150.38</v>
+        <v>227.12</v>
       </c>
       <c r="I56" t="n">
-        <v>25749.47</v>
+        <v>25769.23</v>
       </c>
       <c r="J56" t="n">
-        <v>25828.71</v>
+        <v>25862.01</v>
       </c>
       <c r="K56" t="n">
-        <v>25941.79</v>
+        <v>25931.34</v>
       </c>
       <c r="L56" t="n">
-        <v>26054.86</v>
+        <v>26000.66</v>
       </c>
       <c r="M56" t="n">
-        <v>26151.02</v>
+        <v>26081.72</v>
       </c>
       <c r="N56" t="n">
-        <v>26247.17</v>
+        <v>26162.77</v>
       </c>
       <c r="O56" t="n">
-        <v>26377.16</v>
+        <v>26220.37</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5206,63 +5213,69 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25897.22</v>
+        <v>25870.98</v>
       </c>
       <c r="C57" t="n">
-        <v>26026.78</v>
+        <v>25909.66</v>
       </c>
       <c r="D57" t="n">
-        <v>25799.66</v>
+        <v>25512.39</v>
       </c>
       <c r="E57" t="n">
-        <v>26007.63</v>
+        <v>25576.45</v>
       </c>
       <c r="F57" t="n">
-        <v>1.1</v>
+        <v>-431.18</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0</v>
+        <v>-0.0166</v>
       </c>
       <c r="H57" t="n">
-        <v>227.12</v>
+        <v>397.27</v>
       </c>
       <c r="I57" t="n">
-        <v>25769.23</v>
+        <v>25572.54</v>
       </c>
       <c r="J57" t="n">
-        <v>25862.01</v>
+        <v>25827.72</v>
       </c>
       <c r="K57" t="n">
-        <v>25931.34</v>
+        <v>25894.07</v>
       </c>
       <c r="L57" t="n">
-        <v>26000.66</v>
+        <v>25960.43</v>
       </c>
       <c r="M57" t="n">
-        <v>26081.72</v>
+        <v>26121.19</v>
       </c>
       <c r="N57" t="n">
-        <v>26162.77</v>
+        <v>26281.96</v>
       </c>
       <c r="O57" t="n">
-        <v>26220.37</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
+        <v>26253.9</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q57" s="6" t="inlineStr">
         <is>
@@ -5274,9 +5287,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5288,80 +5301,72 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>25870.98</v>
+        <v>25555.66</v>
       </c>
       <c r="C58" t="n">
-        <v>25909.66</v>
+        <v>25612.09</v>
       </c>
       <c r="D58" t="n">
-        <v>25512.39</v>
+        <v>25361.15</v>
       </c>
       <c r="E58" t="n">
-        <v>25576.45</v>
+        <v>25361.15</v>
       </c>
       <c r="F58" t="n">
-        <v>-431.18</v>
+        <v>-215.3</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>397.27</v>
+        <v>250.94</v>
       </c>
       <c r="I58" t="n">
-        <v>25572.54</v>
+        <v>25115.12</v>
       </c>
       <c r="J58" t="n">
-        <v>25827.72</v>
+        <v>25111.89</v>
       </c>
       <c r="K58" t="n">
-        <v>25894.07</v>
+        <v>25377.81</v>
       </c>
       <c r="L58" t="n">
-        <v>25960.43</v>
+        <v>25643.74</v>
       </c>
       <c r="M58" t="n">
-        <v>26121.19</v>
+        <v>25775.08</v>
       </c>
       <c r="N58" t="n">
-        <v>26281.96</v>
+        <v>25906.43</v>
       </c>
       <c r="O58" t="n">
-        <v>26253.9</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
+        <v>26306.93</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5376,7 +5381,7 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5386,50 +5391,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25555.66</v>
+        <v>25478.84</v>
       </c>
       <c r="C59" t="n">
-        <v>25612.09</v>
+        <v>25581.22</v>
       </c>
       <c r="D59" t="n">
-        <v>25361.15</v>
+        <v>25396.38</v>
       </c>
       <c r="E59" t="n">
-        <v>25361.15</v>
+        <v>25568.56</v>
       </c>
       <c r="F59" t="n">
-        <v>-215.3</v>
+        <v>207.41</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>250.94</v>
+        <v>184.84</v>
       </c>
       <c r="I59" t="n">
-        <v>25115.12</v>
+        <v>25110.21</v>
       </c>
       <c r="J59" t="n">
-        <v>25111.89</v>
+        <v>25047.48</v>
       </c>
       <c r="K59" t="n">
-        <v>25377.81</v>
+        <v>25235.68</v>
       </c>
       <c r="L59" t="n">
-        <v>25643.74</v>
+        <v>25423.89</v>
       </c>
       <c r="M59" t="n">
-        <v>25775.08</v>
+        <v>25486.62</v>
       </c>
       <c r="N59" t="n">
-        <v>25906.43</v>
+        <v>25549.35</v>
       </c>
       <c r="O59" t="n">
-        <v>26306.93</v>
+        <v>25863.03</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5437,172 +5442,178 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
       <c r="V59" s="8" t="n">
         <v/>
       </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25478.84</v>
+        <v>25498.74</v>
       </c>
       <c r="C60" t="n">
-        <v>25581.22</v>
+        <v>25548.78</v>
       </c>
       <c r="D60" t="n">
-        <v>25396.38</v>
+        <v>25325.52</v>
       </c>
       <c r="E60" t="n">
-        <v>25568.56</v>
+        <v>25440.81</v>
       </c>
       <c r="F60" t="n">
-        <v>207.41</v>
+        <v>-127.75</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.005</v>
       </c>
       <c r="H60" t="n">
-        <v>184.84</v>
+        <v>223.26</v>
       </c>
       <c r="I60" t="n">
-        <v>25110.21</v>
+        <v>25211.54</v>
       </c>
       <c r="J60" t="n">
-        <v>25047.48</v>
+        <v>25423.6</v>
       </c>
       <c r="K60" t="n">
-        <v>25235.68</v>
+        <v>25476.14</v>
       </c>
       <c r="L60" t="n">
-        <v>25423.89</v>
+        <v>25528.68</v>
       </c>
       <c r="M60" t="n">
-        <v>25486.62</v>
+        <v>25660.98</v>
       </c>
       <c r="N60" t="n">
-        <v>25549.35</v>
+        <v>25793.28</v>
       </c>
       <c r="O60" t="n">
-        <v>25863.03</v>
+        <v>25766.06</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
+      <c r="Q60" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
+      </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="11" t="inlineStr">
+      <c r="W60" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>25498.74</v>
+        <v>25360.32</v>
       </c>
       <c r="C61" t="n">
-        <v>25548.78</v>
+        <v>25478.98</v>
       </c>
       <c r="D61" t="n">
-        <v>25325.52</v>
+        <v>25172.89</v>
       </c>
       <c r="E61" t="n">
-        <v>25440.81</v>
+        <v>25402.28</v>
       </c>
       <c r="F61" t="n">
-        <v>-127.75</v>
+        <v>-38.53</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.005</v>
+        <v>-0.0015</v>
       </c>
       <c r="H61" t="n">
-        <v>223.26</v>
+        <v>306.09</v>
       </c>
       <c r="I61" t="n">
-        <v>25211.54</v>
+        <v>25102.26</v>
       </c>
       <c r="J61" t="n">
-        <v>25423.6</v>
+        <v>25219.38</v>
       </c>
       <c r="K61" t="n">
-        <v>25476.14</v>
+        <v>25329.18</v>
       </c>
       <c r="L61" t="n">
-        <v>25528.68</v>
+        <v>25438.98</v>
       </c>
       <c r="M61" t="n">
-        <v>25660.98</v>
+        <v>25552.44</v>
       </c>
       <c r="N61" t="n">
-        <v>25793.28</v>
+        <v>25665.9</v>
       </c>
       <c r="O61" t="n">
-        <v>25766.06</v>
+        <v>25772.04</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
       <c r="Q61" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
@@ -5612,7 +5623,7 @@
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5624,7 +5635,7 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="11" t="inlineStr">
+      <c r="W61" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5638,71 +5649,69 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>25360.32</v>
+        <v>25515.96</v>
       </c>
       <c r="C62" t="n">
-        <v>25478.98</v>
+        <v>25599.07</v>
       </c>
       <c r="D62" t="n">
-        <v>25172.89</v>
+        <v>25361.7</v>
       </c>
       <c r="E62" t="n">
-        <v>25402.28</v>
+        <v>25537.75</v>
       </c>
       <c r="F62" t="n">
-        <v>-38.53</v>
+        <v>135.47</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0053</v>
       </c>
       <c r="H62" t="n">
-        <v>306.09</v>
+        <v>237.37</v>
       </c>
       <c r="I62" t="n">
-        <v>25102.26</v>
+        <v>24866.8</v>
       </c>
       <c r="J62" t="n">
-        <v>25219.38</v>
+        <v>25134.36</v>
       </c>
       <c r="K62" t="n">
-        <v>25329.18</v>
+        <v>25249.23</v>
       </c>
       <c r="L62" t="n">
-        <v>25438.98</v>
+        <v>25364.11</v>
       </c>
       <c r="M62" t="n">
-        <v>25552.44</v>
+        <v>25555.32</v>
       </c>
       <c r="N62" t="n">
-        <v>25665.9</v>
+        <v>25746.54</v>
       </c>
       <c r="O62" t="n">
-        <v>25772.04</v>
+        <v>25785.07</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5710,64 +5719,60 @@
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="11" t="inlineStr">
+      <c r="W62" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>25515.96</v>
+        <v>25681.6</v>
       </c>
       <c r="C63" t="n">
-        <v>25599.07</v>
+        <v>25800.62</v>
       </c>
       <c r="D63" t="n">
-        <v>25361.7</v>
+        <v>25596.05</v>
       </c>
       <c r="E63" t="n">
-        <v>25537.75</v>
+        <v>25716.71</v>
       </c>
       <c r="F63" t="n">
-        <v>135.47</v>
+        <v>178.96</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0053</v>
+        <v>0.007</v>
       </c>
       <c r="H63" t="n">
-        <v>237.37</v>
+        <v>204.57</v>
       </c>
       <c r="I63" t="n">
-        <v>24866.8</v>
+        <v>25124.33</v>
       </c>
       <c r="J63" t="n">
-        <v>25134.36</v>
+        <v>25329.06</v>
       </c>
       <c r="K63" t="n">
-        <v>25249.23</v>
+        <v>25419.06</v>
       </c>
       <c r="L63" t="n">
-        <v>25364.11</v>
+        <v>25509.07</v>
       </c>
       <c r="M63" t="n">
-        <v>25555.32</v>
+        <v>25656.44</v>
       </c>
       <c r="N63" t="n">
-        <v>25746.54</v>
+        <v>25803.8</v>
       </c>
       <c r="O63" t="n">
-        <v>25785.07</v>
+        <v>25836.44</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5794,7 +5799,7 @@
       <c r="V63" s="8" t="n">
         <v/>
       </c>
-      <c r="W63" s="11" t="inlineStr">
+      <c r="W63" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5804,70 +5809,74 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>25681.6</v>
+        <v>25596.46</v>
       </c>
       <c r="C64" t="n">
-        <v>25800.62</v>
+        <v>25656.22</v>
       </c>
       <c r="D64" t="n">
-        <v>25596.05</v>
+        <v>25285.9</v>
       </c>
       <c r="E64" t="n">
-        <v>25716.71</v>
+        <v>25304.06</v>
       </c>
       <c r="F64" t="n">
-        <v>178.96</v>
+        <v>-412.65</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.007</v>
+        <v>-0.016</v>
       </c>
       <c r="H64" t="n">
-        <v>204.57</v>
+        <v>370.32</v>
       </c>
       <c r="I64" t="n">
-        <v>25124.33</v>
+        <v>25391.48</v>
       </c>
       <c r="J64" t="n">
-        <v>25329.06</v>
+        <v>25521.33</v>
       </c>
       <c r="K64" t="n">
-        <v>25419.06</v>
+        <v>25614.43</v>
       </c>
       <c r="L64" t="n">
-        <v>25509.07</v>
+        <v>25707.52</v>
       </c>
       <c r="M64" t="n">
-        <v>25656.44</v>
+        <v>25819</v>
       </c>
       <c r="N64" t="n">
-        <v>25803.8</v>
+        <v>25930.47</v>
       </c>
       <c r="O64" t="n">
-        <v>25836.44</v>
-      </c>
-      <c r="P64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S64" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="inlineStr">
+        <v>26005.19</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
       <c r="U64" s="8" t="n">
         <v/>
       </c>
@@ -5876,7 +5885,7 @@
       </c>
       <c r="W64" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X64" t="inlineStr"/>
@@ -5884,86 +5893,90 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>25596.46</v>
+        <v>25491.35</v>
       </c>
       <c r="C65" t="n">
-        <v>25656.22</v>
+        <v>25617.99</v>
       </c>
       <c r="D65" t="n">
-        <v>25285.9</v>
+        <v>25434.16</v>
       </c>
       <c r="E65" t="n">
-        <v>25304.06</v>
+        <v/>
       </c>
       <c r="F65" t="n">
-        <v>-412.65</v>
+        <v/>
       </c>
       <c r="G65" s="5" t="n">
-        <v>-0.016</v>
+        <v/>
       </c>
       <c r="H65" t="n">
-        <v>370.32</v>
+        <v>183.83</v>
       </c>
       <c r="I65" t="n">
-        <v>25391.48</v>
+        <v>24915.58</v>
       </c>
       <c r="J65" t="n">
-        <v>25521.33</v>
+        <v>24850.24</v>
       </c>
       <c r="K65" t="n">
-        <v>25614.43</v>
+        <v>25118.9</v>
       </c>
       <c r="L65" t="n">
-        <v>25707.52</v>
+        <v>25387.56</v>
       </c>
       <c r="M65" t="n">
-        <v>25819</v>
+        <v>25489.22</v>
       </c>
       <c r="N65" t="n">
-        <v>25930.47</v>
+        <v>25590.88</v>
       </c>
       <c r="O65" t="n">
-        <v>26005.19</v>
+        <v>26026.54</v>
       </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q65" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R65" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S65" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U65" s="8" t="n">
-        <v/>
+      <c r="Q65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S65" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V65" s="8" t="n">
         <v/>
       </c>
-      <c r="W65" s="9" t="inlineStr">
+      <c r="W65" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr"/>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -104,20 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -637,169 +634,165 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24790.7</v>
+        <v>24810</v>
       </c>
       <c r="C2" t="n">
-        <v>24800.66</v>
+        <v>25088.28</v>
       </c>
       <c r="D2" t="n">
-        <v>24593.48</v>
+        <v>24761.72</v>
       </c>
       <c r="E2" t="n">
-        <v>24740.36</v>
+        <v>24994.83</v>
       </c>
       <c r="F2" t="n">
-        <v>-153.22</v>
+        <v>254.47</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0103</v>
       </c>
       <c r="H2" t="n">
-        <v>207.18</v>
+        <v>326.56</v>
       </c>
       <c r="I2" t="n">
-        <v>24468.43</v>
+        <v>24386.3</v>
       </c>
       <c r="J2" t="n">
-        <v>24650.91</v>
+        <v>24554.82</v>
       </c>
       <c r="K2" t="n">
-        <v>24763.51</v>
+        <v>24636.77</v>
       </c>
       <c r="L2" t="n">
-        <v>24876.11</v>
+        <v>24718.71</v>
       </c>
       <c r="M2" t="n">
-        <v>25023.65</v>
+        <v>24843.95</v>
       </c>
       <c r="N2" t="n">
-        <v>25171.19</v>
+        <v>24969.18</v>
       </c>
       <c r="O2" t="n">
-        <v>25248.85</v>
+        <v>25007.84</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
-      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24810</v>
+        <v>24848.51</v>
       </c>
       <c r="C3" t="n">
-        <v>25088.28</v>
+        <v>24869.63</v>
       </c>
       <c r="D3" t="n">
-        <v>24761.72</v>
+        <v>24547.7</v>
       </c>
       <c r="E3" t="n">
-        <v>24994.83</v>
+        <v>24671.22</v>
       </c>
       <c r="F3" t="n">
-        <v>254.47</v>
+        <v>-323.61</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.0129</v>
       </c>
       <c r="H3" t="n">
-        <v>326.56</v>
+        <v>321.93</v>
       </c>
       <c r="I3" t="n">
-        <v>24386.3</v>
+        <v>24435.16</v>
       </c>
       <c r="J3" t="n">
-        <v>24554.82</v>
+        <v>24703.19</v>
       </c>
       <c r="K3" t="n">
-        <v>24636.77</v>
+        <v>24831.55</v>
       </c>
       <c r="L3" t="n">
-        <v>24718.71</v>
+        <v>24959.92</v>
       </c>
       <c r="M3" t="n">
-        <v>24843.95</v>
+        <v>25158.11</v>
       </c>
       <c r="N3" t="n">
-        <v>24969.18</v>
+        <v>25356.3</v>
       </c>
       <c r="O3" t="n">
-        <v>25007.84</v>
+        <v>25414.84</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -807,67 +800,63 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24848.51</v>
+        <v>24724.34</v>
       </c>
       <c r="C4" t="n">
-        <v>24869.63</v>
+        <v>24762.24</v>
       </c>
       <c r="D4" t="n">
-        <v>24547.7</v>
+        <v>24556.78</v>
       </c>
       <c r="E4" t="n">
-        <v>24671.22</v>
+        <v>24626.89</v>
       </c>
       <c r="F4" t="n">
-        <v>-323.61</v>
+        <v>-44.33</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0018</v>
       </c>
       <c r="H4" t="n">
-        <v>321.93</v>
+        <v>205.46</v>
       </c>
       <c r="I4" t="n">
-        <v>24435.16</v>
+        <v>24225.77</v>
       </c>
       <c r="J4" t="n">
-        <v>24703.19</v>
+        <v>24330.57</v>
       </c>
       <c r="K4" t="n">
-        <v>24831.55</v>
+        <v>24510.25</v>
       </c>
       <c r="L4" t="n">
-        <v>24959.92</v>
+        <v>24689.94</v>
       </c>
       <c r="M4" t="n">
-        <v>25158.11</v>
+        <v>24832.19</v>
       </c>
       <c r="N4" t="n">
-        <v>25356.3</v>
+        <v>24974.43</v>
       </c>
       <c r="O4" t="n">
-        <v>25414.84</v>
+        <v>25191.56</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -884,55 +873,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24724.34</v>
+        <v>24815.22</v>
       </c>
       <c r="C5" t="n">
-        <v>24762.24</v>
+        <v>25024.27</v>
       </c>
       <c r="D5" t="n">
-        <v>24556.78</v>
+        <v>24794.84</v>
       </c>
       <c r="E5" t="n">
-        <v>24626.89</v>
+        <v>24995.81</v>
       </c>
       <c r="F5" t="n">
-        <v>-44.33</v>
+        <v>368.92</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.015</v>
       </c>
       <c r="H5" t="n">
-        <v>205.46</v>
+        <v>229.43</v>
       </c>
       <c r="I5" t="n">
-        <v>24225.77</v>
+        <v>24351.32</v>
       </c>
       <c r="J5" t="n">
-        <v>24330.57</v>
+        <v>24405.12</v>
       </c>
       <c r="K5" t="n">
-        <v>24510.25</v>
+        <v>24524.16</v>
       </c>
       <c r="L5" t="n">
-        <v>24689.94</v>
+        <v>24643.2</v>
       </c>
       <c r="M5" t="n">
-        <v>24832.19</v>
+        <v>24729.62</v>
       </c>
       <c r="N5" t="n">
-        <v>24974.43</v>
+        <v>24816.04</v>
       </c>
       <c r="O5" t="n">
-        <v>25191.56</v>
+        <v>24967.7</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -945,76 +938,78 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W5" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W5" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24815.22</v>
+        <v>25028.93</v>
       </c>
       <c r="C6" t="n">
-        <v>25024.27</v>
+        <v>25095.66</v>
       </c>
       <c r="D6" t="n">
-        <v>24794.84</v>
+        <v>24887</v>
       </c>
       <c r="E6" t="n">
-        <v>24995.81</v>
+        <v>25040.28</v>
       </c>
       <c r="F6" t="n">
-        <v>368.92</v>
+        <v>44.47</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.015</v>
+        <v>0.0018</v>
       </c>
       <c r="H6" t="n">
-        <v>229.43</v>
+        <v>208.66</v>
       </c>
       <c r="I6" t="n">
-        <v>24351.32</v>
+        <v>24565.41</v>
       </c>
       <c r="J6" t="n">
-        <v>24405.12</v>
+        <v>24809.51</v>
       </c>
       <c r="K6" t="n">
-        <v>24524.16</v>
+        <v>24881.1</v>
       </c>
       <c r="L6" t="n">
-        <v>24643.2</v>
+        <v>24952.68</v>
       </c>
       <c r="M6" t="n">
-        <v>24729.62</v>
+        <v>25110.53</v>
       </c>
       <c r="N6" t="n">
-        <v>24816.04</v>
+        <v>25268.37</v>
       </c>
       <c r="O6" t="n">
-        <v>24967.7</v>
+        <v>25253.7</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1025,25 +1020,21 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
@@ -1055,50 +1046,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25028.93</v>
+        <v>25025.13</v>
       </c>
       <c r="C7" t="n">
-        <v>25095.66</v>
+        <v>25655.82</v>
       </c>
       <c r="D7" t="n">
-        <v>24887</v>
+        <v>24994.64</v>
       </c>
       <c r="E7" t="n">
-        <v>25040.28</v>
+        <v>25580.88</v>
       </c>
       <c r="F7" t="n">
-        <v>44.47</v>
+        <v>540.6</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0216</v>
       </c>
       <c r="H7" t="n">
-        <v>208.66</v>
+        <v>661.1799999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>24565.41</v>
+        <v>24678.34</v>
       </c>
       <c r="J7" t="n">
-        <v>24809.51</v>
+        <v>24856.09</v>
       </c>
       <c r="K7" t="n">
-        <v>24881.1</v>
+        <v>24935.95</v>
       </c>
       <c r="L7" t="n">
-        <v>24952.68</v>
+        <v>25015.8</v>
       </c>
       <c r="M7" t="n">
-        <v>25110.53</v>
+        <v>25144.61</v>
       </c>
       <c r="N7" t="n">
-        <v>25268.37</v>
+        <v>25273.41</v>
       </c>
       <c r="O7" t="n">
-        <v>25253.7</v>
+        <v>25304.32</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1109,21 +1100,25 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="10" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
@@ -1135,50 +1130,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25025.13</v>
+        <v>25763.97</v>
       </c>
       <c r="C8" t="n">
-        <v>25655.82</v>
+        <v>25826.78</v>
       </c>
       <c r="D8" t="n">
-        <v>24994.64</v>
+        <v>25611.69</v>
       </c>
       <c r="E8" t="n">
-        <v>25580.88</v>
+        <v>25779.31</v>
       </c>
       <c r="F8" t="n">
-        <v>540.6</v>
+        <v>198.43</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0216</v>
+        <v>0.0078</v>
       </c>
       <c r="H8" t="n">
-        <v>661.1799999999999</v>
+        <v>215.09</v>
       </c>
       <c r="I8" t="n">
-        <v>24678.34</v>
+        <v>24333.46</v>
       </c>
       <c r="J8" t="n">
-        <v>24856.09</v>
+        <v>25047.53</v>
       </c>
       <c r="K8" t="n">
-        <v>24935.95</v>
+        <v>25250.29</v>
       </c>
       <c r="L8" t="n">
-        <v>25015.8</v>
+        <v>25453.06</v>
       </c>
       <c r="M8" t="n">
-        <v>25144.61</v>
+        <v>25911.47</v>
       </c>
       <c r="N8" t="n">
-        <v>25273.41</v>
+        <v>26369.89</v>
       </c>
       <c r="O8" t="n">
-        <v>25304.32</v>
+        <v>26317</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1189,25 +1184,21 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
@@ -1219,50 +1210,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25763.97</v>
+        <v>25811.9</v>
       </c>
       <c r="C9" t="n">
-        <v>25826.78</v>
+        <v>25900.1</v>
       </c>
       <c r="D9" t="n">
-        <v>25611.69</v>
+        <v>25698.56</v>
       </c>
       <c r="E9" t="n">
-        <v>25779.31</v>
+        <v>25817.89</v>
       </c>
       <c r="F9" t="n">
-        <v>198.43</v>
+        <v>38.58</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0078</v>
+        <v>0.0015</v>
       </c>
       <c r="H9" t="n">
-        <v>215.09</v>
+        <v>201.54</v>
       </c>
       <c r="I9" t="n">
-        <v>24333.46</v>
+        <v>25396.6</v>
       </c>
       <c r="J9" t="n">
-        <v>25047.53</v>
+        <v>25594.26</v>
       </c>
       <c r="K9" t="n">
-        <v>25250.29</v>
+        <v>25671.77</v>
       </c>
       <c r="L9" t="n">
-        <v>25453.06</v>
+        <v>25749.27</v>
       </c>
       <c r="M9" t="n">
-        <v>25911.47</v>
+        <v>25886.86</v>
       </c>
       <c r="N9" t="n">
-        <v>26369.89</v>
+        <v>26024.44</v>
       </c>
       <c r="O9" t="n">
-        <v>26317</v>
+        <v>26041.87</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1273,14 +1264,14 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U9" s="8" t="n">
@@ -1299,69 +1290,73 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25811.9</v>
+        <v>25770.45</v>
       </c>
       <c r="C10" t="n">
-        <v>25900.1</v>
+        <v>25811.97</v>
       </c>
       <c r="D10" t="n">
-        <v>25698.56</v>
+        <v>25465.12</v>
       </c>
       <c r="E10" t="n">
-        <v>25817.89</v>
+        <v>25465.25</v>
       </c>
       <c r="F10" t="n">
-        <v>38.58</v>
+        <v>-352.64</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0137</v>
       </c>
       <c r="H10" t="n">
-        <v>201.54</v>
+        <v>346.85</v>
       </c>
       <c r="I10" t="n">
-        <v>25396.6</v>
+        <v>25497.02</v>
       </c>
       <c r="J10" t="n">
-        <v>25594.26</v>
+        <v>25625.63</v>
       </c>
       <c r="K10" t="n">
-        <v>25671.77</v>
+        <v>25717.12</v>
       </c>
       <c r="L10" t="n">
-        <v>25749.27</v>
+        <v>25808.61</v>
       </c>
       <c r="M10" t="n">
-        <v>25886.86</v>
+        <v>25918.66</v>
       </c>
       <c r="N10" t="n">
-        <v>26024.44</v>
+        <v>26028.71</v>
       </c>
       <c r="O10" t="n">
-        <v>26041.87</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+        <v>26101.64</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1369,9 +1364,9 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W10" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
@@ -1379,67 +1374,67 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25770.45</v>
+        <v>25274.94</v>
       </c>
       <c r="C11" t="n">
-        <v>25811.97</v>
+        <v>25280.16</v>
       </c>
       <c r="D11" t="n">
-        <v>25465.12</v>
+        <v>24830.17</v>
       </c>
       <c r="E11" t="n">
-        <v>25465.25</v>
+        <v>24897.45</v>
       </c>
       <c r="F11" t="n">
-        <v>-352.64</v>
+        <v>-567.8</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0223</v>
       </c>
       <c r="H11" t="n">
-        <v>346.85</v>
+        <v>449.99</v>
       </c>
       <c r="I11" t="n">
-        <v>25497.02</v>
+        <v>25118.27</v>
       </c>
       <c r="J11" t="n">
-        <v>25625.63</v>
+        <v>25031.75</v>
       </c>
       <c r="K11" t="n">
-        <v>25717.12</v>
+        <v>25291.82</v>
       </c>
       <c r="L11" t="n">
-        <v>25808.61</v>
+        <v>25551.9</v>
       </c>
       <c r="M11" t="n">
-        <v>25918.66</v>
+        <v>25638.68</v>
       </c>
       <c r="N11" t="n">
-        <v>26028.71</v>
+        <v>25725.45</v>
       </c>
       <c r="O11" t="n">
-        <v>26101.64</v>
+        <v>26158.82</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1463,74 +1458,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25274.94</v>
+        <v>25097.48</v>
       </c>
       <c r="C12" t="n">
-        <v>25280.16</v>
+        <v>25127.76</v>
       </c>
       <c r="D12" t="n">
-        <v>24830.17</v>
+        <v>24867.32</v>
       </c>
       <c r="E12" t="n">
-        <v>24897.45</v>
+        <v>25118.27</v>
       </c>
       <c r="F12" t="n">
-        <v>-567.8</v>
+        <v>220.82</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0089</v>
       </c>
       <c r="H12" t="n">
-        <v>449.99</v>
+        <v>260.44</v>
       </c>
       <c r="I12" t="n">
-        <v>25118.27</v>
+        <v>24380.18</v>
       </c>
       <c r="J12" t="n">
-        <v>25031.75</v>
+        <v>24368.6</v>
       </c>
       <c r="K12" t="n">
-        <v>25291.82</v>
+        <v>24672.45</v>
       </c>
       <c r="L12" t="n">
-        <v>25551.9</v>
+        <v>24976.31</v>
       </c>
       <c r="M12" t="n">
-        <v>25638.68</v>
+        <v>25122.44</v>
       </c>
       <c r="N12" t="n">
-        <v>25725.45</v>
+        <v>25268.58</v>
       </c>
       <c r="O12" t="n">
-        <v>26158.82</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
+        <v>25730.15</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1542,55 +1533,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25097.48</v>
+        <v>25081.19</v>
       </c>
       <c r="C13" t="n">
-        <v>25127.76</v>
+        <v>25195.83</v>
       </c>
       <c r="D13" t="n">
-        <v>24867.32</v>
+        <v>24937.52</v>
       </c>
       <c r="E13" t="n">
-        <v>25118.27</v>
+        <v>25067.09</v>
       </c>
       <c r="F13" t="n">
-        <v>220.82</v>
+        <v>-51.18</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.002</v>
       </c>
       <c r="H13" t="n">
-        <v>260.44</v>
+        <v>258.31</v>
       </c>
       <c r="I13" t="n">
-        <v>24380.18</v>
+        <v>24606.88</v>
       </c>
       <c r="J13" t="n">
-        <v>24368.6</v>
+        <v>24918.19</v>
       </c>
       <c r="K13" t="n">
-        <v>24672.45</v>
+        <v>24988.05</v>
       </c>
       <c r="L13" t="n">
-        <v>24976.31</v>
+        <v>25057.9</v>
       </c>
       <c r="M13" t="n">
-        <v>25122.44</v>
+        <v>25248.49</v>
       </c>
       <c r="N13" t="n">
-        <v>25268.58</v>
+        <v>25439.07</v>
       </c>
       <c r="O13" t="n">
-        <v>25730.15</v>
+        <v>25388.2</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1598,18 +1593,18 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1631,50 +1626,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25081.19</v>
+        <v>24963.8</v>
       </c>
       <c r="C14" t="n">
-        <v>25195.83</v>
+        <v>25154.58</v>
       </c>
       <c r="D14" t="n">
-        <v>24937.52</v>
+        <v>24963.8</v>
       </c>
       <c r="E14" t="n">
-        <v>25067.09</v>
+        <v>25114.25</v>
       </c>
       <c r="F14" t="n">
-        <v>-51.18</v>
+        <v>47.16</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="H14" t="n">
-        <v>258.31</v>
+        <v>190.78</v>
       </c>
       <c r="I14" t="n">
-        <v>24606.88</v>
+        <v>24679.21</v>
       </c>
       <c r="J14" t="n">
-        <v>24918.19</v>
+        <v>24808.99</v>
       </c>
       <c r="K14" t="n">
-        <v>24988.05</v>
+        <v>24937.93</v>
       </c>
       <c r="L14" t="n">
-        <v>25057.9</v>
+        <v>25066.88</v>
       </c>
       <c r="M14" t="n">
-        <v>25248.49</v>
+        <v>25196.25</v>
       </c>
       <c r="N14" t="n">
-        <v>25439.07</v>
+        <v>25325.61</v>
       </c>
       <c r="O14" t="n">
-        <v>25388.2</v>
+        <v>25454.14</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1682,12 +1677,10 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1715,61 +1708,65 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24963.8</v>
+        <v>24932.62</v>
       </c>
       <c r="C15" t="n">
-        <v>25154.58</v>
+        <v>25204.68</v>
       </c>
       <c r="D15" t="n">
-        <v>24963.8</v>
+        <v>24869.25</v>
       </c>
       <c r="E15" t="n">
-        <v>25114.25</v>
+        <v>25147.03</v>
       </c>
       <c r="F15" t="n">
-        <v>47.16</v>
+        <v>32.78</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0013</v>
       </c>
       <c r="H15" t="n">
-        <v>190.78</v>
+        <v>335.43</v>
       </c>
       <c r="I15" t="n">
-        <v>24679.21</v>
+        <v>24773.02</v>
       </c>
       <c r="J15" t="n">
-        <v>24808.99</v>
+        <v>24951</v>
       </c>
       <c r="K15" t="n">
-        <v>24937.93</v>
+        <v>25018.86</v>
       </c>
       <c r="L15" t="n">
-        <v>25066.88</v>
+        <v>25086.72</v>
       </c>
       <c r="M15" t="n">
-        <v>25196.25</v>
+        <v>25209.64</v>
       </c>
       <c r="N15" t="n">
-        <v>25325.61</v>
+        <v>25332.56</v>
       </c>
       <c r="O15" t="n">
-        <v>25454.14</v>
+        <v>25345.36</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1797,50 +1794,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24932.62</v>
+        <v>24970.05</v>
       </c>
       <c r="C16" t="n">
-        <v>25204.68</v>
+        <v>25055.48</v>
       </c>
       <c r="D16" t="n">
-        <v>24869.25</v>
+        <v>24839.23</v>
       </c>
       <c r="E16" t="n">
-        <v>25147.03</v>
+        <v>24999.53</v>
       </c>
       <c r="F16" t="n">
-        <v>32.78</v>
+        <v>-147.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0059</v>
       </c>
       <c r="H16" t="n">
-        <v>335.43</v>
+        <v>216.25</v>
       </c>
       <c r="I16" t="n">
-        <v>24773.02</v>
+        <v>24533.82</v>
       </c>
       <c r="J16" t="n">
-        <v>24951</v>
+        <v>24866.63</v>
       </c>
       <c r="K16" t="n">
-        <v>25018.86</v>
+        <v>24979.31</v>
       </c>
       <c r="L16" t="n">
-        <v>25086.72</v>
+        <v>25092</v>
       </c>
       <c r="M16" t="n">
-        <v>25209.64</v>
+        <v>25314.74</v>
       </c>
       <c r="N16" t="n">
-        <v>25332.56</v>
+        <v>25537.49</v>
       </c>
       <c r="O16" t="n">
-        <v>25345.36</v>
+        <v>25540.11</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1852,12 +1849,12 @@
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1874,59 +1871,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24970.05</v>
+        <v>25018.95</v>
       </c>
       <c r="C17" t="n">
-        <v>25055.48</v>
+        <v>25021.51</v>
       </c>
       <c r="D17" t="n">
-        <v>24839.23</v>
+        <v>24696.17</v>
       </c>
       <c r="E17" t="n">
-        <v>24999.53</v>
+        <v>24915.49</v>
       </c>
       <c r="F17" t="n">
-        <v>-147.5</v>
+        <v>-84.04000000000001</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0059</v>
+        <v>-0.0034</v>
       </c>
       <c r="H17" t="n">
-        <v>216.25</v>
+        <v>325.34</v>
       </c>
       <c r="I17" t="n">
-        <v>24533.82</v>
+        <v>24622.98</v>
       </c>
       <c r="J17" t="n">
-        <v>24866.63</v>
+        <v>24809.37</v>
       </c>
       <c r="K17" t="n">
-        <v>24979.31</v>
+        <v>24891.4</v>
       </c>
       <c r="L17" t="n">
-        <v>25092</v>
+        <v>24973.44</v>
       </c>
       <c r="M17" t="n">
-        <v>25314.74</v>
+        <v>25107.65</v>
       </c>
       <c r="N17" t="n">
-        <v>25537.49</v>
+        <v>25241.87</v>
       </c>
       <c r="O17" t="n">
-        <v>25540.11</v>
+        <v>25271.73</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1941,7 +1934,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1965,67 +1958,65 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25018.95</v>
+        <v>24755.09</v>
       </c>
       <c r="C18" t="n">
-        <v>25021.51</v>
+        <v>24850.75</v>
       </c>
       <c r="D18" t="n">
-        <v>24696.17</v>
+        <v>24651.34</v>
       </c>
       <c r="E18" t="n">
-        <v>24915.49</v>
+        <v>24830.98</v>
       </c>
       <c r="F18" t="n">
-        <v>-84.04000000000001</v>
+        <v>-84.51000000000001</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>-0.0034</v>
       </c>
       <c r="H18" t="n">
-        <v>325.34</v>
+        <v>199.41</v>
       </c>
       <c r="I18" t="n">
-        <v>24622.98</v>
+        <v>24370.83</v>
       </c>
       <c r="J18" t="n">
-        <v>24809.37</v>
+        <v>24618.48</v>
       </c>
       <c r="K18" t="n">
-        <v>24891.4</v>
+        <v>24752.82</v>
       </c>
       <c r="L18" t="n">
-        <v>24973.44</v>
+        <v>24887.17</v>
       </c>
       <c r="M18" t="n">
-        <v>25107.65</v>
+        <v>25078.16</v>
       </c>
       <c r="N18" t="n">
-        <v>25241.87</v>
+        <v>25269.16</v>
       </c>
       <c r="O18" t="n">
-        <v>25271.73</v>
+        <v>25346.85</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q18" s="6" t="n">
+        <v/>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2047,50 +2038,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24755.09</v>
+        <v>24769.15</v>
       </c>
       <c r="C19" t="n">
-        <v>24850.75</v>
+        <v>24974.53</v>
       </c>
       <c r="D19" t="n">
-        <v>24651.34</v>
+        <v>24751.13</v>
       </c>
       <c r="E19" t="n">
-        <v>24830.98</v>
+        <v>24846.69</v>
       </c>
       <c r="F19" t="n">
-        <v>-84.51000000000001</v>
+        <v>15.71</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>199.41</v>
+        <v>223.4</v>
       </c>
       <c r="I19" t="n">
-        <v>24370.83</v>
+        <v>24451.93</v>
       </c>
       <c r="J19" t="n">
-        <v>24618.48</v>
+        <v>24671.54</v>
       </c>
       <c r="K19" t="n">
-        <v>24752.82</v>
+        <v>24731.28</v>
       </c>
       <c r="L19" t="n">
-        <v>24887.17</v>
+        <v>24791.01</v>
       </c>
       <c r="M19" t="n">
-        <v>25078.16</v>
+        <v>24930.69</v>
       </c>
       <c r="N19" t="n">
-        <v>25269.16</v>
+        <v>25070.36</v>
       </c>
       <c r="O19" t="n">
-        <v>25346.85</v>
+        <v>25050.16</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2098,18 +2089,18 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R19" s="6" t="n">
+        <v/>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2122,55 +2113,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24769.15</v>
+        <v>24922.1</v>
       </c>
       <c r="C20" t="n">
-        <v>24974.53</v>
+        <v>25011.35</v>
       </c>
       <c r="D20" t="n">
-        <v>24751.13</v>
+        <v>24817.34</v>
       </c>
       <c r="E20" t="n">
-        <v>24846.69</v>
+        <v>25011.35</v>
       </c>
       <c r="F20" t="n">
-        <v>15.71</v>
+        <v>164.66</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0066</v>
       </c>
       <c r="H20" t="n">
-        <v>223.4</v>
+        <v>194.01</v>
       </c>
       <c r="I20" t="n">
-        <v>24451.93</v>
+        <v>24527.73</v>
       </c>
       <c r="J20" t="n">
-        <v>24671.54</v>
+        <v>24615.22</v>
       </c>
       <c r="K20" t="n">
-        <v>24731.28</v>
+        <v>24734.99</v>
       </c>
       <c r="L20" t="n">
-        <v>24791.01</v>
+        <v>24854.76</v>
       </c>
       <c r="M20" t="n">
-        <v>24930.69</v>
+        <v>24958.39</v>
       </c>
       <c r="N20" t="n">
-        <v>25070.36</v>
+        <v>25062.02</v>
       </c>
       <c r="O20" t="n">
-        <v>25050.16</v>
+        <v>25197.93</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2181,9 +2176,9 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2191,8 +2186,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2211,50 +2208,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24922.1</v>
+        <v>25001.31</v>
       </c>
       <c r="C21" t="n">
-        <v>25011.35</v>
+        <v>25271.34</v>
       </c>
       <c r="D21" t="n">
-        <v>24817.34</v>
+        <v>24984.27</v>
       </c>
       <c r="E21" t="n">
-        <v>25011.35</v>
+        <v>25155.41</v>
       </c>
       <c r="F21" t="n">
-        <v>164.66</v>
+        <v>144.06</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0058</v>
       </c>
       <c r="H21" t="n">
-        <v>194.01</v>
+        <v>287.07</v>
       </c>
       <c r="I21" t="n">
-        <v>24527.73</v>
+        <v>24623.33</v>
       </c>
       <c r="J21" t="n">
-        <v>24615.22</v>
+        <v>24865.84</v>
       </c>
       <c r="K21" t="n">
-        <v>24734.99</v>
+        <v>24914.34</v>
       </c>
       <c r="L21" t="n">
-        <v>24854.76</v>
+        <v>24962.85</v>
       </c>
       <c r="M21" t="n">
-        <v>24958.39</v>
+        <v>25108.35</v>
       </c>
       <c r="N21" t="n">
-        <v>25062.02</v>
+        <v>25253.86</v>
       </c>
       <c r="O21" t="n">
-        <v>25197.93</v>
+        <v>25205.36</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2265,23 +2262,25 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U21" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W21" s="11" t="inlineStr">
         <is>
@@ -2297,171 +2296,165 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25001.31</v>
+        <v>24994.05</v>
       </c>
       <c r="C22" t="n">
-        <v>25271.34</v>
+        <v>25074.28</v>
       </c>
       <c r="D22" t="n">
-        <v>24984.27</v>
+        <v>24696.59</v>
       </c>
       <c r="E22" t="n">
-        <v>25155.41</v>
+        <v>24763.12</v>
       </c>
       <c r="F22" t="n">
-        <v>144.06</v>
+        <v>-392.29</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0156</v>
       </c>
       <c r="H22" t="n">
-        <v>287.07</v>
+        <v>377.69</v>
       </c>
       <c r="I22" t="n">
-        <v>24623.33</v>
+        <v>24697.2</v>
       </c>
       <c r="J22" t="n">
-        <v>24865.84</v>
+        <v>24882.14</v>
       </c>
       <c r="K22" t="n">
-        <v>24914.34</v>
+        <v>25011.88</v>
       </c>
       <c r="L22" t="n">
-        <v>24962.85</v>
+        <v>25141.61</v>
       </c>
       <c r="M22" t="n">
-        <v>25108.35</v>
+        <v>25298.95</v>
       </c>
       <c r="N22" t="n">
-        <v>25253.86</v>
+        <v>25456.28</v>
       </c>
       <c r="O22" t="n">
-        <v>25205.36</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+        <v>25558.41</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24994.05</v>
+        <v>24830.41</v>
       </c>
       <c r="C23" t="n">
-        <v>25074.28</v>
+        <v>25099.68</v>
       </c>
       <c r="D23" t="n">
-        <v>24696.59</v>
+        <v>24821.67</v>
       </c>
       <c r="E23" t="n">
-        <v>24763.12</v>
+        <v>25099</v>
       </c>
       <c r="F23" t="n">
-        <v>-392.29</v>
+        <v>335.88</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0136</v>
       </c>
       <c r="H23" t="n">
-        <v>377.69</v>
+        <v>278.01</v>
       </c>
       <c r="I23" t="n">
-        <v>24697.2</v>
+        <v>24318.9</v>
       </c>
       <c r="J23" t="n">
-        <v>24882.14</v>
+        <v>24324.27</v>
       </c>
       <c r="K23" t="n">
-        <v>25011.88</v>
+        <v>24574.27</v>
       </c>
       <c r="L23" t="n">
-        <v>25141.61</v>
+        <v>24824.28</v>
       </c>
       <c r="M23" t="n">
-        <v>25298.95</v>
+        <v>24951.96</v>
       </c>
       <c r="N23" t="n">
-        <v>25456.28</v>
+        <v>25079.65</v>
       </c>
       <c r="O23" t="n">
-        <v>25558.41</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
+        <v>25451.97</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W23" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -2469,50 +2462,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24830.41</v>
+        <v>25459.32</v>
       </c>
       <c r="C24" t="n">
-        <v>25099.68</v>
+        <v>25560.4</v>
       </c>
       <c r="D24" t="n">
-        <v>24821.67</v>
+        <v>25361.03</v>
       </c>
       <c r="E24" t="n">
-        <v>25099</v>
+        <v>25361.03</v>
       </c>
       <c r="F24" t="n">
-        <v>335.88</v>
+        <v>262.03</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0104</v>
       </c>
       <c r="H24" t="n">
-        <v>278.01</v>
+        <v>199.37</v>
       </c>
       <c r="I24" t="n">
-        <v>24318.9</v>
+        <v>24543.66</v>
       </c>
       <c r="J24" t="n">
-        <v>24324.27</v>
+        <v>24890.15</v>
       </c>
       <c r="K24" t="n">
-        <v>24574.27</v>
+        <v>24960</v>
       </c>
       <c r="L24" t="n">
-        <v>24824.28</v>
+        <v>25029.84</v>
       </c>
       <c r="M24" t="n">
-        <v>24951.96</v>
+        <v>25238</v>
       </c>
       <c r="N24" t="n">
-        <v>25079.65</v>
+        <v>25446.17</v>
       </c>
       <c r="O24" t="n">
-        <v>25451.97</v>
+        <v>25377.69</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2523,7 +2516,7 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2535,11 +2528,13 @@
       </c>
       <c r="U24" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
@@ -2551,50 +2546,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25459.32</v>
+        <v>25496.13</v>
       </c>
       <c r="C25" t="n">
-        <v>25560.4</v>
+        <v>25553.47</v>
       </c>
       <c r="D25" t="n">
-        <v>25361.03</v>
+        <v>25307.17</v>
       </c>
       <c r="E25" t="n">
-        <v>25361.03</v>
+        <v>25464.01</v>
       </c>
       <c r="F25" t="n">
-        <v>262.03</v>
+        <v>102.98</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0104</v>
+        <v>0.0041</v>
       </c>
       <c r="H25" t="n">
-        <v>199.37</v>
+        <v>246.3</v>
       </c>
       <c r="I25" t="n">
-        <v>24543.66</v>
+        <v>25161.66</v>
       </c>
       <c r="J25" t="n">
-        <v>24890.15</v>
+        <v>25111.82</v>
       </c>
       <c r="K25" t="n">
-        <v>24960</v>
+        <v>25261.34</v>
       </c>
       <c r="L25" t="n">
-        <v>25029.84</v>
+        <v>25410.87</v>
       </c>
       <c r="M25" t="n">
-        <v>25238</v>
+        <v>25460.71</v>
       </c>
       <c r="N25" t="n">
-        <v>25446.17</v>
+        <v>25510.56</v>
       </c>
       <c r="O25" t="n">
-        <v>25377.69</v>
+        <v>25759.77</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2605,14 +2600,14 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U25" s="8" t="inlineStr">
@@ -2620,65 +2615,67 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V25" s="8" t="n">
+        <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25496.13</v>
+        <v>25551.97</v>
       </c>
       <c r="C26" t="n">
-        <v>25553.47</v>
+        <v>25571.45</v>
       </c>
       <c r="D26" t="n">
-        <v>25307.17</v>
+        <v>25336.39</v>
       </c>
       <c r="E26" t="n">
-        <v>25464.01</v>
+        <v>25460.48</v>
       </c>
       <c r="F26" t="n">
-        <v>102.98</v>
+        <v>-3.53</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0001</v>
       </c>
       <c r="H26" t="n">
-        <v>246.3</v>
+        <v>235.06</v>
       </c>
       <c r="I26" t="n">
-        <v>25161.66</v>
+        <v>25060.87</v>
       </c>
       <c r="J26" t="n">
-        <v>25111.82</v>
+        <v>25234.55</v>
       </c>
       <c r="K26" t="n">
-        <v>25261.34</v>
+        <v>25340.86</v>
       </c>
       <c r="L26" t="n">
-        <v>25410.87</v>
+        <v>25447.17</v>
       </c>
       <c r="M26" t="n">
-        <v>25460.71</v>
+        <v>25587.16</v>
       </c>
       <c r="N26" t="n">
-        <v>25510.56</v>
+        <v>25727.16</v>
       </c>
       <c r="O26" t="n">
-        <v>25759.77</v>
+        <v>25799.77</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2686,23 +2683,21 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2714,57 +2709,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25551.97</v>
+        <v>25487.45</v>
       </c>
       <c r="C27" t="n">
-        <v>25571.45</v>
+        <v>25651.16</v>
       </c>
       <c r="D27" t="n">
-        <v>25336.39</v>
+        <v>25303.11</v>
       </c>
       <c r="E27" t="n">
-        <v>25460.48</v>
+        <v>25612.03</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.53</v>
+        <v>151.55</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.006</v>
       </c>
       <c r="H27" t="n">
-        <v>235.06</v>
+        <v>348.05</v>
       </c>
       <c r="I27" t="n">
-        <v>25060.87</v>
+        <v>25101.33</v>
       </c>
       <c r="J27" t="n">
-        <v>25234.55</v>
+        <v>25228.7</v>
       </c>
       <c r="K27" t="n">
-        <v>25340.86</v>
+        <v>25342.95</v>
       </c>
       <c r="L27" t="n">
-        <v>25447.17</v>
+        <v>25457.2</v>
       </c>
       <c r="M27" t="n">
-        <v>25587.16</v>
+        <v>25578.01</v>
       </c>
       <c r="N27" t="n">
-        <v>25727.16</v>
+        <v>25698.82</v>
       </c>
       <c r="O27" t="n">
-        <v>25799.77</v>
+        <v>25806.51</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2777,13 +2772,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2805,50 +2802,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25487.45</v>
+        <v>25709.37</v>
       </c>
       <c r="C28" t="n">
-        <v>25651.16</v>
+        <v>25891.51</v>
       </c>
       <c r="D28" t="n">
-        <v>25303.11</v>
+        <v>25549.53</v>
       </c>
       <c r="E28" t="n">
-        <v>25612.03</v>
+        <v>25629.24</v>
       </c>
       <c r="F28" t="n">
-        <v>151.55</v>
+        <v>17.21</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0007</v>
       </c>
       <c r="H28" t="n">
-        <v>348.05</v>
+        <v>341.98</v>
       </c>
       <c r="I28" t="n">
-        <v>25101.33</v>
+        <v>24955.06</v>
       </c>
       <c r="J28" t="n">
-        <v>25228.7</v>
+        <v>25331.43</v>
       </c>
       <c r="K28" t="n">
-        <v>25342.95</v>
+        <v>25438</v>
       </c>
       <c r="L28" t="n">
-        <v>25457.2</v>
+        <v>25544.58</v>
       </c>
       <c r="M28" t="n">
-        <v>25578.01</v>
+        <v>25786.05</v>
       </c>
       <c r="N28" t="n">
-        <v>25698.82</v>
+        <v>26027.53</v>
       </c>
       <c r="O28" t="n">
-        <v>25806.51</v>
+        <v>25999.21</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2856,19 +2853,17 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U28" s="8" t="n">
@@ -2882,59 +2877,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25709.37</v>
+        <v>25855.12</v>
       </c>
       <c r="C29" t="n">
-        <v>25891.51</v>
+        <v>26096.93</v>
       </c>
       <c r="D29" t="n">
-        <v>25549.53</v>
+        <v>25855.12</v>
       </c>
       <c r="E29" t="n">
-        <v>25629.24</v>
+        <v>26001.31</v>
       </c>
       <c r="F29" t="n">
-        <v>17.21</v>
+        <v>372.07</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0145</v>
       </c>
       <c r="H29" t="n">
-        <v>341.98</v>
+        <v>241.81</v>
       </c>
       <c r="I29" t="n">
-        <v>24955.06</v>
+        <v>25207.55</v>
       </c>
       <c r="J29" t="n">
-        <v>25331.43</v>
+        <v>25241.62</v>
       </c>
       <c r="K29" t="n">
-        <v>25438</v>
+        <v>25458.25</v>
       </c>
       <c r="L29" t="n">
-        <v>25544.58</v>
+        <v>25674.88</v>
       </c>
       <c r="M29" t="n">
-        <v>25786.05</v>
+        <v>25800.23</v>
       </c>
       <c r="N29" t="n">
-        <v>26027.53</v>
+        <v>25925.58</v>
       </c>
       <c r="O29" t="n">
-        <v>25999.21</v>
+        <v>26233.49</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2945,9 +2936,9 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
@@ -2955,8 +2946,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2971,50 +2964,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25855.12</v>
+        <v>26189.62</v>
       </c>
       <c r="C30" t="n">
-        <v>26096.93</v>
+        <v>26266.5</v>
       </c>
       <c r="D30" t="n">
-        <v>25855.12</v>
+        <v>26082.43</v>
       </c>
       <c r="E30" t="n">
-        <v>26001.31</v>
+        <v>26202.35</v>
       </c>
       <c r="F30" t="n">
-        <v>372.07</v>
+        <v>201.04</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0077</v>
       </c>
       <c r="H30" t="n">
-        <v>241.81</v>
+        <v>184.07</v>
       </c>
       <c r="I30" t="n">
-        <v>25207.55</v>
+        <v>25613.31</v>
       </c>
       <c r="J30" t="n">
-        <v>25241.62</v>
+        <v>25772.14</v>
       </c>
       <c r="K30" t="n">
-        <v>25458.25</v>
+        <v>25880.41</v>
       </c>
       <c r="L30" t="n">
-        <v>25674.88</v>
+        <v>25988.67</v>
       </c>
       <c r="M30" t="n">
-        <v>25800.23</v>
+        <v>26122.22</v>
       </c>
       <c r="N30" t="n">
-        <v>25925.58</v>
+        <v>26255.76</v>
       </c>
       <c r="O30" t="n">
-        <v>26233.49</v>
+        <v>26338.74</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3025,7 +3018,7 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3053,50 +3046,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>26189.62</v>
+        <v>26393.43</v>
       </c>
       <c r="C31" t="n">
-        <v>26266.5</v>
+        <v>26403.81</v>
       </c>
       <c r="D31" t="n">
-        <v>26082.43</v>
+        <v>26123.18</v>
       </c>
       <c r="E31" t="n">
-        <v>26202.35</v>
+        <v>26126.3</v>
       </c>
       <c r="F31" t="n">
-        <v>201.04</v>
+        <v>-76.05</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0029</v>
       </c>
       <c r="H31" t="n">
-        <v>184.07</v>
+        <v>280.63</v>
       </c>
       <c r="I31" t="n">
-        <v>25613.31</v>
+        <v>25898.36</v>
       </c>
       <c r="J31" t="n">
-        <v>25772.14</v>
+        <v>26032.22</v>
       </c>
       <c r="K31" t="n">
-        <v>25880.41</v>
+        <v>26110.31</v>
       </c>
       <c r="L31" t="n">
-        <v>25988.67</v>
+        <v>26188.41</v>
       </c>
       <c r="M31" t="n">
-        <v>26122.22</v>
+        <v>26294.38</v>
       </c>
       <c r="N31" t="n">
-        <v>26255.76</v>
+        <v>26400.36</v>
       </c>
       <c r="O31" t="n">
-        <v>26338.74</v>
+        <v>26450.57</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3104,12 +3097,14 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
@@ -3119,7 +3114,7 @@
       </c>
       <c r="U31" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V31" s="8" t="n">
@@ -3130,55 +3125,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26393.43</v>
+        <v>26116.27</v>
       </c>
       <c r="C32" t="n">
-        <v>26403.81</v>
+        <v>26229.33</v>
       </c>
       <c r="D32" t="n">
-        <v>26123.18</v>
+        <v>26081.69</v>
       </c>
       <c r="E32" t="n">
-        <v>26126.3</v>
+        <v>26140.13</v>
       </c>
       <c r="F32" t="n">
-        <v>-76.05</v>
+        <v>13.83</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0005</v>
       </c>
       <c r="H32" t="n">
-        <v>280.63</v>
+        <v>147.64</v>
       </c>
       <c r="I32" t="n">
-        <v>25898.36</v>
+        <v>25842.55</v>
       </c>
       <c r="J32" t="n">
-        <v>26032.22</v>
+        <v>25777.07</v>
       </c>
       <c r="K32" t="n">
-        <v>26110.31</v>
+        <v>25985.99</v>
       </c>
       <c r="L32" t="n">
-        <v>26188.41</v>
+        <v>26194.9</v>
       </c>
       <c r="M32" t="n">
-        <v>26294.38</v>
+        <v>26266.62</v>
       </c>
       <c r="N32" t="n">
-        <v>26400.36</v>
+        <v>26338.33</v>
       </c>
       <c r="O32" t="n">
-        <v>26450.57</v>
+        <v>26684.44</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3186,25 +3185,19 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3216,57 +3209,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>26116.27</v>
+        <v>26235.8</v>
       </c>
       <c r="C33" t="n">
-        <v>26229.33</v>
+        <v>26445.18</v>
       </c>
       <c r="D33" t="n">
-        <v>26081.69</v>
+        <v>26223.64</v>
       </c>
       <c r="E33" t="n">
-        <v>26140.13</v>
+        <v>26319.45</v>
       </c>
       <c r="F33" t="n">
-        <v>13.83</v>
+        <v>179.32</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0069</v>
       </c>
       <c r="H33" t="n">
-        <v>147.64</v>
+        <v>221.54</v>
       </c>
       <c r="I33" t="n">
-        <v>25842.55</v>
+        <v>25934.05</v>
       </c>
       <c r="J33" t="n">
-        <v>25777.07</v>
+        <v>25984.8</v>
       </c>
       <c r="K33" t="n">
-        <v>25985.99</v>
+        <v>26066.31</v>
       </c>
       <c r="L33" t="n">
-        <v>26194.9</v>
+        <v>26147.82</v>
       </c>
       <c r="M33" t="n">
-        <v>26266.62</v>
+        <v>26213.95</v>
       </c>
       <c r="N33" t="n">
-        <v>26338.33</v>
+        <v>26280.08</v>
       </c>
       <c r="O33" t="n">
-        <v>26684.44</v>
+        <v>26376.97</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3279,76 +3272,78 @@
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26235.8</v>
+        <v>26360.44</v>
       </c>
       <c r="C34" t="n">
-        <v>26445.18</v>
+        <v>26441.91</v>
       </c>
       <c r="D34" t="n">
-        <v>26223.64</v>
+        <v>26302.19</v>
       </c>
       <c r="E34" t="n">
-        <v>26319.45</v>
+        <v>26323.88</v>
       </c>
       <c r="F34" t="n">
-        <v>179.32</v>
+        <v>4.43</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0002</v>
       </c>
       <c r="H34" t="n">
-        <v>221.54</v>
+        <v>139.72</v>
       </c>
       <c r="I34" t="n">
-        <v>25934.05</v>
+        <v>26002.1</v>
       </c>
       <c r="J34" t="n">
-        <v>25984.8</v>
+        <v>26090.43</v>
       </c>
       <c r="K34" t="n">
-        <v>26066.31</v>
+        <v>26208.68</v>
       </c>
       <c r="L34" t="n">
-        <v>26147.82</v>
+        <v>26326.93</v>
       </c>
       <c r="M34" t="n">
-        <v>26213.95</v>
+        <v>26430.22</v>
       </c>
       <c r="N34" t="n">
-        <v>26280.08</v>
+        <v>26533.51</v>
       </c>
       <c r="O34" t="n">
-        <v>26376.97</v>
+        <v>26666.72</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3361,7 +3356,7 @@
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
@@ -3369,70 +3364,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>26360.44</v>
+        <v>26378</v>
       </c>
       <c r="C35" t="n">
-        <v>26441.91</v>
+        <v>26504.54</v>
       </c>
       <c r="D35" t="n">
-        <v>26302.19</v>
+        <v>26245.57</v>
       </c>
       <c r="E35" t="n">
-        <v>26323.88</v>
+        <v>26391.42</v>
       </c>
       <c r="F35" t="n">
-        <v>4.43</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0026</v>
       </c>
       <c r="H35" t="n">
-        <v>139.72</v>
+        <v>258.97</v>
       </c>
       <c r="I35" t="n">
-        <v>26002.1</v>
+        <v>26162.47</v>
       </c>
       <c r="J35" t="n">
-        <v>26090.43</v>
+        <v>26160.08</v>
       </c>
       <c r="K35" t="n">
-        <v>26208.68</v>
+        <v>26254.02</v>
       </c>
       <c r="L35" t="n">
-        <v>26326.93</v>
+        <v>26347.97</v>
       </c>
       <c r="M35" t="n">
-        <v>26430.22</v>
+        <v>26393.74</v>
       </c>
       <c r="N35" t="n">
-        <v>26533.51</v>
+        <v>26439.52</v>
       </c>
       <c r="O35" t="n">
-        <v>26666.72</v>
+        <v>26581.63</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3440,21 +3435,25 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3473,50 +3472,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26378</v>
+        <v>26452</v>
       </c>
       <c r="C36" t="n">
-        <v>26504.54</v>
+        <v>26573.5</v>
       </c>
       <c r="D36" t="n">
-        <v>26245.57</v>
+        <v>26313.58</v>
       </c>
       <c r="E36" t="n">
-        <v>26391.42</v>
+        <v>26331.07</v>
       </c>
       <c r="F36" t="n">
-        <v>67.54000000000001</v>
+        <v>-60.35</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0023</v>
       </c>
       <c r="H36" t="n">
-        <v>258.97</v>
+        <v>259.92</v>
       </c>
       <c r="I36" t="n">
-        <v>26162.47</v>
+        <v>25986.6</v>
       </c>
       <c r="J36" t="n">
-        <v>26160.08</v>
+        <v>26140.63</v>
       </c>
       <c r="K36" t="n">
-        <v>26254.02</v>
+        <v>26261.94</v>
       </c>
       <c r="L36" t="n">
-        <v>26347.97</v>
+        <v>26383.24</v>
       </c>
       <c r="M36" t="n">
-        <v>26393.74</v>
+        <v>26520.9</v>
       </c>
       <c r="N36" t="n">
-        <v>26439.52</v>
+        <v>26658.57</v>
       </c>
       <c r="O36" t="n">
-        <v>26581.63</v>
+        <v>26763.51</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3524,25 +3523,21 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3561,50 +3556,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26452</v>
+        <v>26437.35</v>
       </c>
       <c r="C37" t="n">
-        <v>26573.5</v>
+        <v>26489.78</v>
       </c>
       <c r="D37" t="n">
-        <v>26313.58</v>
+        <v>26285.23</v>
       </c>
       <c r="E37" t="n">
-        <v>26331.07</v>
+        <v>26299.74</v>
       </c>
       <c r="F37" t="n">
-        <v>-60.35</v>
+        <v>-31.33</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0012</v>
       </c>
       <c r="H37" t="n">
-        <v>259.92</v>
+        <v>204.55</v>
       </c>
       <c r="I37" t="n">
-        <v>25986.6</v>
+        <v>26053.66</v>
       </c>
       <c r="J37" t="n">
-        <v>26140.63</v>
+        <v>26014.92</v>
       </c>
       <c r="K37" t="n">
-        <v>26261.94</v>
+        <v>26201.11</v>
       </c>
       <c r="L37" t="n">
-        <v>26383.24</v>
+        <v>26387.31</v>
       </c>
       <c r="M37" t="n">
-        <v>26520.9</v>
+        <v>26461.03</v>
       </c>
       <c r="N37" t="n">
-        <v>26658.57</v>
+        <v>26534.76</v>
       </c>
       <c r="O37" t="n">
-        <v>26763.51</v>
+        <v>26833.42</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3615,7 +3610,7 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3638,57 +3633,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26437.35</v>
+        <v>26445.99</v>
       </c>
       <c r="C38" t="n">
-        <v>26489.78</v>
+        <v>26541.34</v>
       </c>
       <c r="D38" t="n">
-        <v>26285.23</v>
+        <v>26404.95</v>
       </c>
       <c r="E38" t="n">
-        <v>26299.74</v>
+        <v>26440.31</v>
       </c>
       <c r="F38" t="n">
-        <v>-31.33</v>
+        <v>140.57</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0053</v>
       </c>
       <c r="H38" t="n">
-        <v>204.55</v>
+        <v>136.39</v>
       </c>
       <c r="I38" t="n">
-        <v>26053.66</v>
+        <v>26080.68</v>
       </c>
       <c r="J38" t="n">
-        <v>26014.92</v>
+        <v>26051.31</v>
       </c>
       <c r="K38" t="n">
-        <v>26201.11</v>
+        <v>26197.47</v>
       </c>
       <c r="L38" t="n">
-        <v>26387.31</v>
+        <v>26343.62</v>
       </c>
       <c r="M38" t="n">
-        <v>26461.03</v>
+        <v>26402.01</v>
       </c>
       <c r="N38" t="n">
-        <v>26534.76</v>
+        <v>26460.41</v>
       </c>
       <c r="O38" t="n">
-        <v>26833.42</v>
+        <v>26694.33</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3701,7 +3696,7 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
@@ -3709,8 +3704,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U38" s="8" t="n">
-        <v/>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3720,59 +3717,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26445.99</v>
+        <v>26490.3</v>
       </c>
       <c r="C39" t="n">
-        <v>26541.34</v>
+        <v>26493.5</v>
       </c>
       <c r="D39" t="n">
-        <v>26404.95</v>
+        <v>26338.61</v>
       </c>
       <c r="E39" t="n">
-        <v>26440.31</v>
+        <v>26338.61</v>
       </c>
       <c r="F39" t="n">
-        <v>140.57</v>
+        <v>-101.7</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0038</v>
       </c>
       <c r="H39" t="n">
-        <v>136.39</v>
+        <v>154.89</v>
       </c>
       <c r="I39" t="n">
-        <v>26080.68</v>
+        <v>26268.56</v>
       </c>
       <c r="J39" t="n">
-        <v>26051.31</v>
+        <v>26287.5</v>
       </c>
       <c r="K39" t="n">
-        <v>26197.47</v>
+        <v>26372.12</v>
       </c>
       <c r="L39" t="n">
-        <v>26343.62</v>
+        <v>26456.73</v>
       </c>
       <c r="M39" t="n">
-        <v>26402.01</v>
+        <v>26508.51</v>
       </c>
       <c r="N39" t="n">
-        <v>26460.41</v>
+        <v>26560.28</v>
       </c>
       <c r="O39" t="n">
-        <v>26694.33</v>
+        <v>26677.73</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3780,23 +3773,21 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3806,68 +3797,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>26490.3</v>
+        <v>26280.86</v>
       </c>
       <c r="C40" t="n">
-        <v>26493.5</v>
+        <v>26292.95</v>
       </c>
       <c r="D40" t="n">
-        <v>26338.61</v>
+        <v>26119.54</v>
       </c>
       <c r="E40" t="n">
-        <v>26338.61</v>
+        <v>26128.36</v>
       </c>
       <c r="F40" t="n">
-        <v>-101.7</v>
+        <v>-210.25</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.008</v>
       </c>
       <c r="H40" t="n">
-        <v>154.89</v>
+        <v>173.41</v>
       </c>
       <c r="I40" t="n">
-        <v>26268.56</v>
+        <v>26183.72</v>
       </c>
       <c r="J40" t="n">
-        <v>26287.5</v>
+        <v>26145</v>
       </c>
       <c r="K40" t="n">
-        <v>26372.12</v>
+        <v>26261.16</v>
       </c>
       <c r="L40" t="n">
-        <v>26456.73</v>
+        <v>26377.33</v>
       </c>
       <c r="M40" t="n">
-        <v>26508.51</v>
+        <v>26416.05</v>
       </c>
       <c r="N40" t="n">
-        <v>26560.28</v>
+        <v>26454.78</v>
       </c>
       <c r="O40" t="n">
-        <v>26677.73</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+        <v>26648.39</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3881,81 +3880,73 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W40" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26280.86</v>
+        <v>26146.12</v>
       </c>
       <c r="C41" t="n">
-        <v>26292.95</v>
+        <v>26187.82</v>
       </c>
       <c r="D41" t="n">
-        <v>26119.54</v>
+        <v>26063.37</v>
       </c>
       <c r="E41" t="n">
-        <v>26128.36</v>
+        <v>26091.33</v>
       </c>
       <c r="F41" t="n">
-        <v>-210.25</v>
+        <v>-37.03</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0014</v>
       </c>
       <c r="H41" t="n">
-        <v>173.41</v>
+        <v>124.45</v>
       </c>
       <c r="I41" t="n">
-        <v>26183.72</v>
+        <v>25946.13</v>
       </c>
       <c r="J41" t="n">
-        <v>26145</v>
+        <v>25916.01</v>
       </c>
       <c r="K41" t="n">
-        <v>26261.16</v>
+        <v>26041.65</v>
       </c>
       <c r="L41" t="n">
-        <v>26377.33</v>
+        <v>26167.3</v>
       </c>
       <c r="M41" t="n">
-        <v>26416.05</v>
+        <v>26215.06</v>
       </c>
       <c r="N41" t="n">
-        <v>26454.78</v>
+        <v>26262.83</v>
       </c>
       <c r="O41" t="n">
-        <v>26648.39</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
+        <v>26466.36</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3979,63 +3970,67 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26146.12</v>
+        <v>26050.95</v>
       </c>
       <c r="C42" t="n">
-        <v>26187.82</v>
+        <v>26062.15</v>
       </c>
       <c r="D42" t="n">
-        <v>26063.37</v>
+        <v>25914.11</v>
       </c>
       <c r="E42" t="n">
-        <v>26091.33</v>
+        <v>25983.04</v>
       </c>
       <c r="F42" t="n">
-        <v>-37.03</v>
+        <v>-108.29</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0042</v>
       </c>
       <c r="H42" t="n">
-        <v>124.45</v>
+        <v>148.04</v>
       </c>
       <c r="I42" t="n">
-        <v>25946.13</v>
+        <v>25938.92</v>
       </c>
       <c r="J42" t="n">
-        <v>25916.01</v>
+        <v>25949.75</v>
       </c>
       <c r="K42" t="n">
-        <v>26041.65</v>
+        <v>26029.1</v>
       </c>
       <c r="L42" t="n">
-        <v>26167.3</v>
+        <v>26108.46</v>
       </c>
       <c r="M42" t="n">
-        <v>26215.06</v>
+        <v>26153.56</v>
       </c>
       <c r="N42" t="n">
-        <v>26262.83</v>
+        <v>26198.65</v>
       </c>
       <c r="O42" t="n">
-        <v>26466.36</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+        <v>26312.27</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4059,83 +4054,81 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>26050.95</v>
+        <v>25998.95</v>
       </c>
       <c r="C43" t="n">
-        <v>26062.15</v>
+        <v>26166.25</v>
       </c>
       <c r="D43" t="n">
-        <v>25914.11</v>
+        <v>25969.52</v>
       </c>
       <c r="E43" t="n">
-        <v>25983.04</v>
+        <v>26136.56</v>
       </c>
       <c r="F43" t="n">
-        <v>-108.29</v>
+        <v>153.52</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.0059</v>
       </c>
       <c r="H43" t="n">
-        <v>148.04</v>
+        <v>196.73</v>
       </c>
       <c r="I43" t="n">
-        <v>25938.92</v>
+        <v>25766.07</v>
       </c>
       <c r="J43" t="n">
-        <v>25949.75</v>
+        <v>25832.45</v>
       </c>
       <c r="K43" t="n">
-        <v>26029.1</v>
+        <v>25909.02</v>
       </c>
       <c r="L43" t="n">
-        <v>26108.46</v>
+        <v>25985.58</v>
       </c>
       <c r="M43" t="n">
-        <v>26153.56</v>
+        <v>26057.06</v>
       </c>
       <c r="N43" t="n">
-        <v>26198.65</v>
+        <v>26128.53</v>
       </c>
       <c r="O43" t="n">
-        <v>26312.27</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
+        <v>26210.19</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W43" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr"/>
@@ -4143,50 +4136,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25998.95</v>
+        <v>26091.29</v>
       </c>
       <c r="C44" t="n">
-        <v>26166.25</v>
+        <v>26171.7</v>
       </c>
       <c r="D44" t="n">
-        <v>25969.52</v>
+        <v>26038.07</v>
       </c>
       <c r="E44" t="n">
-        <v>26136.56</v>
+        <v>26106.6</v>
       </c>
       <c r="F44" t="n">
-        <v>153.52</v>
+        <v>-29.96</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0011</v>
       </c>
       <c r="H44" t="n">
-        <v>196.73</v>
+        <v>133.63</v>
       </c>
       <c r="I44" t="n">
-        <v>25766.07</v>
+        <v>25772.79</v>
       </c>
       <c r="J44" t="n">
-        <v>25832.45</v>
+        <v>25974.17</v>
       </c>
       <c r="K44" t="n">
-        <v>25909.02</v>
+        <v>26038.2</v>
       </c>
       <c r="L44" t="n">
-        <v>25985.58</v>
+        <v>26102.22</v>
       </c>
       <c r="M44" t="n">
-        <v>26057.06</v>
+        <v>26234.93</v>
       </c>
       <c r="N44" t="n">
-        <v>26128.53</v>
+        <v>26367.63</v>
       </c>
       <c r="O44" t="n">
-        <v>26210.19</v>
+        <v>26362.98</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4194,23 +4187,21 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4220,55 +4211,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>26091.29</v>
+        <v>26206.01</v>
       </c>
       <c r="C45" t="n">
-        <v>26171.7</v>
+        <v>26341.52</v>
       </c>
       <c r="D45" t="n">
-        <v>26038.07</v>
+        <v>26164.11</v>
       </c>
       <c r="E45" t="n">
-        <v>26106.6</v>
+        <v>26266.14</v>
       </c>
       <c r="F45" t="n">
-        <v>-29.96</v>
+        <v>159.54</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0061</v>
       </c>
       <c r="H45" t="n">
-        <v>133.63</v>
+        <v>177.41</v>
       </c>
       <c r="I45" t="n">
-        <v>25772.79</v>
+        <v>25904.44</v>
       </c>
       <c r="J45" t="n">
-        <v>25974.17</v>
+        <v>25973.83</v>
       </c>
       <c r="K45" t="n">
-        <v>26038.2</v>
+        <v>26039.79</v>
       </c>
       <c r="L45" t="n">
-        <v>26102.22</v>
+        <v>26105.74</v>
       </c>
       <c r="M45" t="n">
-        <v>26234.93</v>
+        <v>26173.41</v>
       </c>
       <c r="N45" t="n">
-        <v>26367.63</v>
+        <v>26241.09</v>
       </c>
       <c r="O45" t="n">
-        <v>26362.98</v>
+        <v>26305.33</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4276,83 +4271,83 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v/>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>26206.01</v>
+        <v>26255.41</v>
       </c>
       <c r="C46" t="n">
-        <v>26341.52</v>
+        <v>26466.76</v>
       </c>
       <c r="D46" t="n">
-        <v>26164.11</v>
+        <v>26196.92</v>
       </c>
       <c r="E46" t="n">
-        <v>26266.14</v>
+        <v>26285.96</v>
       </c>
       <c r="F46" t="n">
-        <v>159.54</v>
+        <v>19.82</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0061</v>
+        <v>0.0008</v>
       </c>
       <c r="H46" t="n">
-        <v>177.41</v>
+        <v>269.84</v>
       </c>
       <c r="I46" t="n">
-        <v>25904.44</v>
+        <v>25986.7</v>
       </c>
       <c r="J46" t="n">
-        <v>25973.83</v>
+        <v>26095.39</v>
       </c>
       <c r="K46" t="n">
-        <v>26039.79</v>
+        <v>26177.44</v>
       </c>
       <c r="L46" t="n">
-        <v>26105.74</v>
+        <v>26259.48</v>
       </c>
       <c r="M46" t="n">
-        <v>26173.41</v>
+        <v>26354.85</v>
       </c>
       <c r="N46" t="n">
-        <v>26241.09</v>
+        <v>26450.21</v>
       </c>
       <c r="O46" t="n">
-        <v>26305.33</v>
+        <v>26518.93</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4363,9 +4358,9 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
@@ -4375,13 +4370,11 @@
       </c>
       <c r="U46" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v/>
       </c>
       <c r="W46" s="9" t="inlineStr">
         <is>
@@ -4393,50 +4386,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>26255.41</v>
+        <v>26354.37</v>
       </c>
       <c r="C47" t="n">
-        <v>26466.76</v>
+        <v>26402.81</v>
       </c>
       <c r="D47" t="n">
-        <v>26196.92</v>
+        <v>26241.77</v>
       </c>
       <c r="E47" t="n">
-        <v>26285.96</v>
+        <v>26367.24</v>
       </c>
       <c r="F47" t="n">
-        <v>19.82</v>
+        <v>81.28</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0031</v>
       </c>
       <c r="H47" t="n">
-        <v>269.84</v>
+        <v>161.04</v>
       </c>
       <c r="I47" t="n">
-        <v>25986.7</v>
+        <v>25927.08</v>
       </c>
       <c r="J47" t="n">
-        <v>26095.39</v>
+        <v>25993.18</v>
       </c>
       <c r="K47" t="n">
-        <v>26177.44</v>
+        <v>26151.04</v>
       </c>
       <c r="L47" t="n">
-        <v>26259.48</v>
+        <v>26308.9</v>
       </c>
       <c r="M47" t="n">
-        <v>26354.85</v>
+        <v>26420.88</v>
       </c>
       <c r="N47" t="n">
-        <v>26450.21</v>
+        <v>26532.86</v>
       </c>
       <c r="O47" t="n">
-        <v>26518.93</v>
+        <v>26736.6</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4447,20 +4440,18 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4470,55 +4461,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>26354.37</v>
+        <v>26494.61</v>
       </c>
       <c r="C48" t="n">
-        <v>26402.81</v>
+        <v>26618.74</v>
       </c>
       <c r="D48" t="n">
-        <v>26241.77</v>
+        <v>26467.36</v>
       </c>
       <c r="E48" t="n">
-        <v>26367.24</v>
+        <v>26569.99</v>
       </c>
       <c r="F48" t="n">
-        <v>81.28</v>
+        <v>202.75</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0077</v>
       </c>
       <c r="H48" t="n">
-        <v>161.04</v>
+        <v>151.38</v>
       </c>
       <c r="I48" t="n">
-        <v>25927.08</v>
+        <v>26080.73</v>
       </c>
       <c r="J48" t="n">
-        <v>25993.18</v>
+        <v>26228.67</v>
       </c>
       <c r="K48" t="n">
-        <v>26151.04</v>
+        <v>26286.72</v>
       </c>
       <c r="L48" t="n">
-        <v>26308.9</v>
+        <v>26344.77</v>
       </c>
       <c r="M48" t="n">
-        <v>26420.88</v>
+        <v>26447.76</v>
       </c>
       <c r="N48" t="n">
-        <v>26532.86</v>
+        <v>26550.76</v>
       </c>
       <c r="O48" t="n">
-        <v>26736.6</v>
+        <v>26563.85</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4529,113 +4524,113 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="10" t="inlineStr">
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V48" s="8" t="n">
-        <v/>
-      </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>26494.61</v>
+        <v>26464.14</v>
       </c>
       <c r="C49" t="n">
-        <v>26618.74</v>
+        <v>26471.79</v>
       </c>
       <c r="D49" t="n">
-        <v>26467.36</v>
+        <v>26249.59</v>
       </c>
       <c r="E49" t="n">
-        <v>26569.99</v>
+        <v>26258.11</v>
       </c>
       <c r="F49" t="n">
-        <v>202.75</v>
+        <v>-311.88</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0117</v>
       </c>
       <c r="H49" t="n">
-        <v>151.38</v>
+        <v>222.2</v>
       </c>
       <c r="I49" t="n">
-        <v>26080.73</v>
+        <v>26315.98</v>
       </c>
       <c r="J49" t="n">
-        <v>26228.67</v>
+        <v>26432.08</v>
       </c>
       <c r="K49" t="n">
-        <v>26286.72</v>
+        <v>26494.3</v>
       </c>
       <c r="L49" t="n">
-        <v>26344.77</v>
+        <v>26556.52</v>
       </c>
       <c r="M49" t="n">
-        <v>26447.76</v>
+        <v>26645.68</v>
       </c>
       <c r="N49" t="n">
-        <v>26550.76</v>
+        <v>26734.84</v>
       </c>
       <c r="O49" t="n">
-        <v>26563.85</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+        <v>26770.12</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W49" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W49" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X49" t="inlineStr"/>
@@ -4643,67 +4638,67 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>26464.14</v>
+        <v>26150.75</v>
       </c>
       <c r="C50" t="n">
-        <v>26471.79</v>
+        <v>26206.13</v>
       </c>
       <c r="D50" t="n">
-        <v>26249.59</v>
+        <v>25916.76</v>
       </c>
       <c r="E50" t="n">
-        <v>26258.11</v>
+        <v>25970.11</v>
       </c>
       <c r="F50" t="n">
-        <v>-311.88</v>
+        <v>-288</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.011</v>
       </c>
       <c r="H50" t="n">
-        <v>222.2</v>
+        <v>289.37</v>
       </c>
       <c r="I50" t="n">
-        <v>26315.98</v>
+        <v>26027.39</v>
       </c>
       <c r="J50" t="n">
-        <v>26432.08</v>
+        <v>25984.62</v>
       </c>
       <c r="K50" t="n">
-        <v>26494.3</v>
+        <v>26147.01</v>
       </c>
       <c r="L50" t="n">
-        <v>26556.52</v>
+        <v>26309.4</v>
       </c>
       <c r="M50" t="n">
-        <v>26645.68</v>
+        <v>26369.21</v>
       </c>
       <c r="N50" t="n">
-        <v>26734.84</v>
+        <v>26429.02</v>
       </c>
       <c r="O50" t="n">
-        <v>26770.12</v>
+        <v>26693.99</v>
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4727,67 +4722,63 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>26150.75</v>
+        <v>25886.67</v>
       </c>
       <c r="C51" t="n">
-        <v>26206.13</v>
+        <v>25924.21</v>
       </c>
       <c r="D51" t="n">
-        <v>25916.76</v>
+        <v>25727.93</v>
       </c>
       <c r="E51" t="n">
-        <v>25970.11</v>
+        <v>25839.33</v>
       </c>
       <c r="F51" t="n">
-        <v>-288</v>
+        <v>-130.78</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.005</v>
       </c>
       <c r="H51" t="n">
-        <v>289.37</v>
+        <v>196.28</v>
       </c>
       <c r="I51" t="n">
-        <v>26027.39</v>
+        <v>25627.39</v>
       </c>
       <c r="J51" t="n">
-        <v>25984.62</v>
+        <v>25635.07</v>
       </c>
       <c r="K51" t="n">
-        <v>26147.01</v>
+        <v>25825.42</v>
       </c>
       <c r="L51" t="n">
-        <v>26309.4</v>
+        <v>26015.78</v>
       </c>
       <c r="M51" t="n">
-        <v>26369.21</v>
+        <v>26114.79</v>
       </c>
       <c r="N51" t="n">
-        <v>26429.02</v>
+        <v>26213.81</v>
       </c>
       <c r="O51" t="n">
-        <v>26693.99</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
+        <v>26495.5</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4811,50 +4802,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25886.67</v>
+        <v>25840.92</v>
       </c>
       <c r="C52" t="n">
-        <v>25924.21</v>
+        <v>26007.79</v>
       </c>
       <c r="D52" t="n">
-        <v>25727.93</v>
+        <v>25784.84</v>
       </c>
       <c r="E52" t="n">
-        <v>25839.33</v>
+        <v>26003.32</v>
       </c>
       <c r="F52" t="n">
-        <v>-130.78</v>
+        <v>163.99</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0063</v>
       </c>
       <c r="H52" t="n">
-        <v>196.28</v>
+        <v>222.95</v>
       </c>
       <c r="I52" t="n">
-        <v>25627.39</v>
+        <v>25531.65</v>
       </c>
       <c r="J52" t="n">
-        <v>25635.07</v>
+        <v>25649.68</v>
       </c>
       <c r="K52" t="n">
-        <v>25825.42</v>
+        <v>25741.19</v>
       </c>
       <c r="L52" t="n">
-        <v>26015.78</v>
+        <v>25832.7</v>
       </c>
       <c r="M52" t="n">
-        <v>26114.79</v>
+        <v>25937.47</v>
       </c>
       <c r="N52" t="n">
-        <v>26213.81</v>
+        <v>26042.24</v>
       </c>
       <c r="O52" t="n">
-        <v>26495.5</v>
+        <v>26120.49</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4862,22 +4853,24 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
@@ -4886,55 +4879,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25840.92</v>
+        <v>25985.86</v>
       </c>
       <c r="C53" t="n">
-        <v>26007.79</v>
+        <v>26167.93</v>
       </c>
       <c r="D53" t="n">
-        <v>25784.84</v>
+        <v>25958.7</v>
       </c>
       <c r="E53" t="n">
-        <v>26003.32</v>
+        <v>26046.4</v>
       </c>
       <c r="F53" t="n">
-        <v>163.99</v>
+        <v>43.08</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0017</v>
       </c>
       <c r="H53" t="n">
-        <v>222.95</v>
+        <v>209.23</v>
       </c>
       <c r="I53" t="n">
-        <v>25531.65</v>
+        <v>25561.89</v>
       </c>
       <c r="J53" t="n">
-        <v>25649.68</v>
+        <v>25833.87</v>
       </c>
       <c r="K53" t="n">
-        <v>25741.19</v>
+        <v>25891.85</v>
       </c>
       <c r="L53" t="n">
-        <v>25832.7</v>
+        <v>25949.82</v>
       </c>
       <c r="M53" t="n">
-        <v>25937.47</v>
+        <v>26114.79</v>
       </c>
       <c r="N53" t="n">
-        <v>26042.24</v>
+        <v>26279.77</v>
       </c>
       <c r="O53" t="n">
-        <v>26120.49</v>
+        <v>26230.74</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4945,20 +4942,18 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4977,50 +4972,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25985.86</v>
+        <v>26039.54</v>
       </c>
       <c r="C54" t="n">
-        <v>26167.93</v>
+        <v>26069.99</v>
       </c>
       <c r="D54" t="n">
-        <v>25958.7</v>
+        <v>25919.61</v>
       </c>
       <c r="E54" t="n">
-        <v>26046.4</v>
+        <v>26006.53</v>
       </c>
       <c r="F54" t="n">
-        <v>43.08</v>
+        <v>-39.87</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0015</v>
       </c>
       <c r="H54" t="n">
-        <v>209.23</v>
+        <v>150.38</v>
       </c>
       <c r="I54" t="n">
-        <v>25561.89</v>
+        <v>25749.47</v>
       </c>
       <c r="J54" t="n">
-        <v>25833.87</v>
+        <v>25828.71</v>
       </c>
       <c r="K54" t="n">
-        <v>25891.85</v>
+        <v>25941.79</v>
       </c>
       <c r="L54" t="n">
-        <v>25949.82</v>
+        <v>26054.86</v>
       </c>
       <c r="M54" t="n">
-        <v>26114.79</v>
+        <v>26151.02</v>
       </c>
       <c r="N54" t="n">
-        <v>26279.77</v>
+        <v>26247.17</v>
       </c>
       <c r="O54" t="n">
-        <v>26230.74</v>
+        <v>26377.16</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5028,18 +5023,18 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5052,65 +5047,63 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>26039.54</v>
+        <v>25897.22</v>
       </c>
       <c r="C55" t="n">
-        <v>26069.99</v>
+        <v>26026.78</v>
       </c>
       <c r="D55" t="n">
-        <v>25919.61</v>
+        <v>25799.66</v>
       </c>
       <c r="E55" t="n">
-        <v>26006.53</v>
+        <v>26007.63</v>
       </c>
       <c r="F55" t="n">
-        <v>-39.87</v>
+        <v>1.1</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>150.38</v>
+        <v>227.12</v>
       </c>
       <c r="I55" t="n">
-        <v>25749.47</v>
+        <v>25769.23</v>
       </c>
       <c r="J55" t="n">
-        <v>25828.71</v>
+        <v>25862.01</v>
       </c>
       <c r="K55" t="n">
-        <v>25941.79</v>
+        <v>25931.34</v>
       </c>
       <c r="L55" t="n">
-        <v>26054.86</v>
+        <v>26000.66</v>
       </c>
       <c r="M55" t="n">
-        <v>26151.02</v>
+        <v>26081.72</v>
       </c>
       <c r="N55" t="n">
-        <v>26247.17</v>
+        <v>26162.77</v>
       </c>
       <c r="O55" t="n">
-        <v>26377.16</v>
+        <v>26220.37</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
@@ -5119,7 +5112,7 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5136,58 +5129,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25897.22</v>
+        <v>25870.98</v>
       </c>
       <c r="C56" t="n">
-        <v>26026.78</v>
+        <v>25909.66</v>
       </c>
       <c r="D56" t="n">
-        <v>25799.66</v>
+        <v>25512.39</v>
       </c>
       <c r="E56" t="n">
-        <v>26007.63</v>
+        <v>25576.45</v>
       </c>
       <c r="F56" t="n">
-        <v>1.1</v>
+        <v>-431.18</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0</v>
+        <v>-0.0166</v>
       </c>
       <c r="H56" t="n">
-        <v>227.12</v>
+        <v>397.27</v>
       </c>
       <c r="I56" t="n">
-        <v>25769.23</v>
+        <v>25572.54</v>
       </c>
       <c r="J56" t="n">
-        <v>25862.01</v>
+        <v>25827.72</v>
       </c>
       <c r="K56" t="n">
-        <v>25931.34</v>
+        <v>25894.07</v>
       </c>
       <c r="L56" t="n">
-        <v>26000.66</v>
+        <v>25960.43</v>
       </c>
       <c r="M56" t="n">
-        <v>26081.72</v>
+        <v>26121.19</v>
       </c>
       <c r="N56" t="n">
-        <v>26162.77</v>
+        <v>26281.96</v>
       </c>
       <c r="O56" t="n">
-        <v>26220.37</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
+        <v>26253.9</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q56" s="6" t="inlineStr">
         <is>
@@ -5201,7 +5200,7 @@
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5218,76 +5217,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25870.98</v>
+        <v>25555.66</v>
       </c>
       <c r="C57" t="n">
-        <v>25909.66</v>
+        <v>25612.09</v>
       </c>
       <c r="D57" t="n">
-        <v>25512.39</v>
+        <v>25361.15</v>
       </c>
       <c r="E57" t="n">
-        <v>25576.45</v>
+        <v>25361.15</v>
       </c>
       <c r="F57" t="n">
-        <v>-431.18</v>
+        <v>-215.3</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>397.27</v>
+        <v>250.94</v>
       </c>
       <c r="I57" t="n">
-        <v>25572.54</v>
+        <v>25115.12</v>
       </c>
       <c r="J57" t="n">
-        <v>25827.72</v>
+        <v>25111.89</v>
       </c>
       <c r="K57" t="n">
-        <v>25894.07</v>
+        <v>25377.81</v>
       </c>
       <c r="L57" t="n">
-        <v>25960.43</v>
+        <v>25643.74</v>
       </c>
       <c r="M57" t="n">
-        <v>26121.19</v>
+        <v>25775.08</v>
       </c>
       <c r="N57" t="n">
-        <v>26281.96</v>
+        <v>25906.43</v>
       </c>
       <c r="O57" t="n">
-        <v>26253.9</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
+        <v>26306.93</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5311,50 +5302,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>25555.66</v>
+        <v>25478.84</v>
       </c>
       <c r="C58" t="n">
-        <v>25612.09</v>
+        <v>25581.22</v>
       </c>
       <c r="D58" t="n">
-        <v>25361.15</v>
+        <v>25396.38</v>
       </c>
       <c r="E58" t="n">
-        <v>25361.15</v>
+        <v>25568.56</v>
       </c>
       <c r="F58" t="n">
-        <v>-215.3</v>
+        <v>207.41</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>250.94</v>
+        <v>184.84</v>
       </c>
       <c r="I58" t="n">
-        <v>25115.12</v>
+        <v>25110.21</v>
       </c>
       <c r="J58" t="n">
-        <v>25111.89</v>
+        <v>25047.48</v>
       </c>
       <c r="K58" t="n">
-        <v>25377.81</v>
+        <v>25235.68</v>
       </c>
       <c r="L58" t="n">
-        <v>25643.74</v>
+        <v>25423.89</v>
       </c>
       <c r="M58" t="n">
-        <v>25775.08</v>
+        <v>25486.62</v>
       </c>
       <c r="N58" t="n">
-        <v>25906.43</v>
+        <v>25549.35</v>
       </c>
       <c r="O58" t="n">
-        <v>26306.93</v>
+        <v>25863.03</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5362,103 +5353,109 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25478.84</v>
+        <v>25498.74</v>
       </c>
       <c r="C59" t="n">
-        <v>25581.22</v>
+        <v>25548.78</v>
       </c>
       <c r="D59" t="n">
-        <v>25396.38</v>
+        <v>25325.52</v>
       </c>
       <c r="E59" t="n">
-        <v>25568.56</v>
+        <v>25440.81</v>
       </c>
       <c r="F59" t="n">
-        <v>207.41</v>
+        <v>-127.75</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.005</v>
       </c>
       <c r="H59" t="n">
-        <v>184.84</v>
+        <v>223.26</v>
       </c>
       <c r="I59" t="n">
-        <v>25110.21</v>
+        <v>25211.54</v>
       </c>
       <c r="J59" t="n">
-        <v>25047.48</v>
+        <v>25423.6</v>
       </c>
       <c r="K59" t="n">
-        <v>25235.68</v>
+        <v>25476.14</v>
       </c>
       <c r="L59" t="n">
-        <v>25423.89</v>
+        <v>25528.68</v>
       </c>
       <c r="M59" t="n">
-        <v>25486.62</v>
+        <v>25660.98</v>
       </c>
       <c r="N59" t="n">
-        <v>25549.35</v>
+        <v>25793.28</v>
       </c>
       <c r="O59" t="n">
-        <v>25863.03</v>
+        <v>25766.06</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
@@ -5470,64 +5467,64 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25498.74</v>
+        <v>25360.32</v>
       </c>
       <c r="C60" t="n">
-        <v>25548.78</v>
+        <v>25478.98</v>
       </c>
       <c r="D60" t="n">
-        <v>25325.52</v>
+        <v>25172.89</v>
       </c>
       <c r="E60" t="n">
-        <v>25440.81</v>
+        <v>25402.28</v>
       </c>
       <c r="F60" t="n">
-        <v>-127.75</v>
+        <v>-38.53</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.005</v>
+        <v>-0.0015</v>
       </c>
       <c r="H60" t="n">
-        <v>223.26</v>
+        <v>306.09</v>
       </c>
       <c r="I60" t="n">
-        <v>25211.54</v>
+        <v>25102.26</v>
       </c>
       <c r="J60" t="n">
-        <v>25423.6</v>
+        <v>25219.38</v>
       </c>
       <c r="K60" t="n">
-        <v>25476.14</v>
+        <v>25329.18</v>
       </c>
       <c r="L60" t="n">
-        <v>25528.68</v>
+        <v>25438.98</v>
       </c>
       <c r="M60" t="n">
-        <v>25660.98</v>
+        <v>25552.44</v>
       </c>
       <c r="N60" t="n">
-        <v>25793.28</v>
+        <v>25665.9</v>
       </c>
       <c r="O60" t="n">
-        <v>25766.06</v>
+        <v>25772.04</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
       <c r="Q60" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
@@ -5535,9 +5532,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5563,71 +5560,69 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>25360.32</v>
+        <v>25515.96</v>
       </c>
       <c r="C61" t="n">
-        <v>25478.98</v>
+        <v>25599.07</v>
       </c>
       <c r="D61" t="n">
-        <v>25172.89</v>
+        <v>25361.7</v>
       </c>
       <c r="E61" t="n">
-        <v>25402.28</v>
+        <v>25537.75</v>
       </c>
       <c r="F61" t="n">
-        <v>-38.53</v>
+        <v>135.47</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0053</v>
       </c>
       <c r="H61" t="n">
-        <v>306.09</v>
+        <v>237.37</v>
       </c>
       <c r="I61" t="n">
-        <v>25102.26</v>
+        <v>24866.8</v>
       </c>
       <c r="J61" t="n">
-        <v>25219.38</v>
+        <v>25134.36</v>
       </c>
       <c r="K61" t="n">
-        <v>25329.18</v>
+        <v>25249.23</v>
       </c>
       <c r="L61" t="n">
-        <v>25438.98</v>
+        <v>25364.11</v>
       </c>
       <c r="M61" t="n">
-        <v>25552.44</v>
+        <v>25555.32</v>
       </c>
       <c r="N61" t="n">
-        <v>25665.9</v>
+        <v>25746.54</v>
       </c>
       <c r="O61" t="n">
-        <v>25772.04</v>
+        <v>25785.07</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5640,59 +5635,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>25515.96</v>
+        <v>25681.6</v>
       </c>
       <c r="C62" t="n">
-        <v>25599.07</v>
+        <v>25800.62</v>
       </c>
       <c r="D62" t="n">
-        <v>25361.7</v>
+        <v>25596.05</v>
       </c>
       <c r="E62" t="n">
-        <v>25537.75</v>
+        <v>25716.71</v>
       </c>
       <c r="F62" t="n">
-        <v>135.47</v>
+        <v>178.96</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0053</v>
+        <v>0.007</v>
       </c>
       <c r="H62" t="n">
-        <v>237.37</v>
+        <v>204.57</v>
       </c>
       <c r="I62" t="n">
-        <v>24866.8</v>
+        <v>25124.33</v>
       </c>
       <c r="J62" t="n">
-        <v>25134.36</v>
+        <v>25329.06</v>
       </c>
       <c r="K62" t="n">
-        <v>25249.23</v>
+        <v>25419.06</v>
       </c>
       <c r="L62" t="n">
-        <v>25364.11</v>
+        <v>25509.07</v>
       </c>
       <c r="M62" t="n">
-        <v>25555.32</v>
+        <v>25656.44</v>
       </c>
       <c r="N62" t="n">
-        <v>25746.54</v>
+        <v>25803.8</v>
       </c>
       <c r="O62" t="n">
-        <v>25785.07</v>
+        <v>25836.44</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5703,7 +5694,7 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="10" t="inlineStr">
+      <c r="S62" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5729,69 +5720,73 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>25681.6</v>
+        <v>25596.46</v>
       </c>
       <c r="C63" t="n">
-        <v>25800.62</v>
+        <v>25656.22</v>
       </c>
       <c r="D63" t="n">
-        <v>25596.05</v>
+        <v>25285.9</v>
       </c>
       <c r="E63" t="n">
-        <v>25716.71</v>
+        <v>25304.06</v>
       </c>
       <c r="F63" t="n">
-        <v>178.96</v>
+        <v>-412.65</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.007</v>
+        <v>-0.016</v>
       </c>
       <c r="H63" t="n">
-        <v>204.57</v>
+        <v>370.32</v>
       </c>
       <c r="I63" t="n">
-        <v>25124.33</v>
+        <v>25391.48</v>
       </c>
       <c r="J63" t="n">
-        <v>25329.06</v>
+        <v>25521.33</v>
       </c>
       <c r="K63" t="n">
-        <v>25419.06</v>
+        <v>25614.43</v>
       </c>
       <c r="L63" t="n">
-        <v>25509.07</v>
+        <v>25707.52</v>
       </c>
       <c r="M63" t="n">
-        <v>25656.44</v>
+        <v>25819</v>
       </c>
       <c r="N63" t="n">
-        <v>25803.8</v>
+        <v>25930.47</v>
       </c>
       <c r="O63" t="n">
-        <v>25836.44</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
+        <v>26005.19</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S63" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
       </c>
       <c r="U63" s="8" t="n">
         <v/>
@@ -5799,9 +5794,9 @@
       <c r="V63" s="8" t="n">
         <v/>
       </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X63" t="inlineStr"/>
@@ -5809,77 +5804,75 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>25596.46</v>
+        <v>25491.35</v>
       </c>
       <c r="C64" t="n">
-        <v>25656.22</v>
+        <v>25617.99</v>
       </c>
       <c r="D64" t="n">
-        <v>25285.9</v>
+        <v>25434.16</v>
       </c>
       <c r="E64" t="n">
-        <v>25304.06</v>
+        <v>25575.01</v>
       </c>
       <c r="F64" t="n">
-        <v>-412.65</v>
+        <v>270.95</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.016</v>
+        <v>0.0107</v>
       </c>
       <c r="H64" t="n">
-        <v>370.32</v>
+        <v>183.83</v>
       </c>
       <c r="I64" t="n">
-        <v>25391.48</v>
+        <v>24915.58</v>
       </c>
       <c r="J64" t="n">
-        <v>25521.33</v>
+        <v>24850.24</v>
       </c>
       <c r="K64" t="n">
-        <v>25614.43</v>
+        <v>25118.9</v>
       </c>
       <c r="L64" t="n">
-        <v>25707.52</v>
+        <v>25387.56</v>
       </c>
       <c r="M64" t="n">
-        <v>25819</v>
+        <v>25489.22</v>
       </c>
       <c r="N64" t="n">
-        <v>25930.47</v>
+        <v>25590.88</v>
       </c>
       <c r="O64" t="n">
-        <v>26005.19</v>
-      </c>
-      <c r="P64" s="6" t="inlineStr">
+        <v>26026.54</v>
+      </c>
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U64" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q64" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R64" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
-      </c>
       <c r="V64" s="8" t="n">
         <v/>
       </c>
@@ -5888,81 +5881,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>25491.35</v>
+        <v>25592.98</v>
       </c>
       <c r="C65" t="n">
-        <v>25617.99</v>
+        <v>25783.16</v>
       </c>
       <c r="D65" t="n">
-        <v>25434.16</v>
+        <v>25423.07</v>
       </c>
       <c r="E65" t="n">
-        <v/>
+        <v>25668.34</v>
       </c>
       <c r="F65" t="n">
-        <v/>
+        <v>93.33</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v/>
+        <v>0.0036</v>
       </c>
       <c r="H65" t="n">
-        <v>183.83</v>
+        <v>360.09</v>
       </c>
       <c r="I65" t="n">
-        <v>24915.58</v>
+        <v>25250.33</v>
       </c>
       <c r="J65" t="n">
-        <v>24850.24</v>
+        <v>25415.65</v>
       </c>
       <c r="K65" t="n">
-        <v>25118.9</v>
+        <v>25483.09</v>
       </c>
       <c r="L65" t="n">
-        <v>25387.56</v>
+        <v>25550.54</v>
       </c>
       <c r="M65" t="n">
-        <v>25489.22</v>
+        <v>25666.92</v>
       </c>
       <c r="N65" t="n">
-        <v>25590.88</v>
+        <v>25783.31</v>
       </c>
       <c r="O65" t="n">
-        <v>26026.54</v>
-      </c>
-      <c r="P65" s="6" t="inlineStr">
+        <v>25801.82</v>
+      </c>
+      <c r="P65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S65" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S65" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U65" s="8" t="n">
+        <v/>
       </c>
       <c r="V65" s="8" t="n">
         <v/>
@@ -5974,7 +5969,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -5903,13 +5903,13 @@
         <v>25423.07</v>
       </c>
       <c r="E65" t="n">
-        <v>25668.34</v>
+        <v>25574.73</v>
       </c>
       <c r="F65" t="n">
-        <v>93.33</v>
+        <v>-0.28</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0</v>
       </c>
       <c r="H65" t="n">
         <v>360.09</v>
@@ -5948,12 +5948,12 @@
       </c>
       <c r="S65" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T65" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U65" s="8" t="n">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5903,13 +5906,13 @@
         <v>25423.07</v>
       </c>
       <c r="E65" t="n">
-        <v>25574.73</v>
+        <v/>
       </c>
       <c r="F65" t="n">
-        <v>-0.28</v>
+        <v/>
       </c>
       <c r="G65" s="5" t="n">
-        <v>-0</v>
+        <v/>
       </c>
       <c r="H65" t="n">
         <v>360.09</v>
@@ -5935,8 +5938,10 @@
       <c r="O65" t="n">
         <v>25801.82</v>
       </c>
-      <c r="P65" s="6" t="n">
-        <v/>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q65" s="6" t="n">
         <v/>
@@ -5946,9 +5951,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S65" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S65" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T65" s="8" t="inlineStr">

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X65"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -637,83 +637,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24810</v>
+        <v>24848.51</v>
       </c>
       <c r="C2" t="n">
-        <v>25088.28</v>
+        <v>24869.63</v>
       </c>
       <c r="D2" t="n">
-        <v>24761.72</v>
+        <v>24547.7</v>
       </c>
       <c r="E2" t="n">
-        <v>24994.83</v>
+        <v>24671.22</v>
       </c>
       <c r="F2" t="n">
-        <v>254.47</v>
+        <v>-323.61</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.0129</v>
       </c>
       <c r="H2" t="n">
-        <v>326.56</v>
+        <v>321.93</v>
       </c>
       <c r="I2" t="n">
-        <v>24386.3</v>
+        <v>24435.16</v>
       </c>
       <c r="J2" t="n">
-        <v>24554.82</v>
+        <v>24703.19</v>
       </c>
       <c r="K2" t="n">
-        <v>24636.77</v>
+        <v>24831.55</v>
       </c>
       <c r="L2" t="n">
-        <v>24718.71</v>
+        <v>24959.92</v>
       </c>
       <c r="M2" t="n">
-        <v>24843.95</v>
+        <v>25158.11</v>
       </c>
       <c r="N2" t="n">
-        <v>24969.18</v>
+        <v>25356.3</v>
       </c>
       <c r="O2" t="n">
-        <v>25007.84</v>
+        <v>25414.84</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -721,67 +719,63 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24848.51</v>
+        <v>24724.34</v>
       </c>
       <c r="C3" t="n">
-        <v>24869.63</v>
+        <v>24762.24</v>
       </c>
       <c r="D3" t="n">
-        <v>24547.7</v>
+        <v>24556.78</v>
       </c>
       <c r="E3" t="n">
-        <v>24671.22</v>
+        <v>24626.89</v>
       </c>
       <c r="F3" t="n">
-        <v>-323.61</v>
+        <v>-44.33</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0018</v>
       </c>
       <c r="H3" t="n">
-        <v>321.93</v>
+        <v>205.46</v>
       </c>
       <c r="I3" t="n">
-        <v>24435.16</v>
+        <v>24225.77</v>
       </c>
       <c r="J3" t="n">
-        <v>24703.19</v>
+        <v>24330.57</v>
       </c>
       <c r="K3" t="n">
-        <v>24831.55</v>
+        <v>24510.25</v>
       </c>
       <c r="L3" t="n">
-        <v>24959.92</v>
+        <v>24689.94</v>
       </c>
       <c r="M3" t="n">
-        <v>25158.11</v>
+        <v>24832.19</v>
       </c>
       <c r="N3" t="n">
-        <v>25356.3</v>
+        <v>24974.43</v>
       </c>
       <c r="O3" t="n">
-        <v>25414.84</v>
+        <v>25191.56</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -793,60 +787,64 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24724.34</v>
+        <v>24815.22</v>
       </c>
       <c r="C4" t="n">
-        <v>24762.24</v>
+        <v>25024.27</v>
       </c>
       <c r="D4" t="n">
-        <v>24556.78</v>
+        <v>24794.84</v>
       </c>
       <c r="E4" t="n">
-        <v>24626.89</v>
+        <v>24995.81</v>
       </c>
       <c r="F4" t="n">
-        <v>-44.33</v>
+        <v>368.92</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.015</v>
       </c>
       <c r="H4" t="n">
-        <v>205.46</v>
+        <v>229.43</v>
       </c>
       <c r="I4" t="n">
-        <v>24225.77</v>
+        <v>24351.32</v>
       </c>
       <c r="J4" t="n">
-        <v>24330.57</v>
+        <v>24405.12</v>
       </c>
       <c r="K4" t="n">
-        <v>24510.25</v>
+        <v>24524.16</v>
       </c>
       <c r="L4" t="n">
-        <v>24689.94</v>
+        <v>24643.2</v>
       </c>
       <c r="M4" t="n">
-        <v>24832.19</v>
+        <v>24729.62</v>
       </c>
       <c r="N4" t="n">
-        <v>24974.43</v>
+        <v>24816.04</v>
       </c>
       <c r="O4" t="n">
-        <v>25191.56</v>
+        <v>24967.7</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -859,76 +857,78 @@
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W4" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24815.22</v>
+        <v>25028.93</v>
       </c>
       <c r="C5" t="n">
-        <v>25024.27</v>
+        <v>25095.66</v>
       </c>
       <c r="D5" t="n">
-        <v>24794.84</v>
+        <v>24887</v>
       </c>
       <c r="E5" t="n">
-        <v>24995.81</v>
+        <v>25040.28</v>
       </c>
       <c r="F5" t="n">
-        <v>368.92</v>
+        <v>44.47</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.015</v>
+        <v>0.0018</v>
       </c>
       <c r="H5" t="n">
-        <v>229.43</v>
+        <v>208.66</v>
       </c>
       <c r="I5" t="n">
-        <v>24351.32</v>
+        <v>24565.41</v>
       </c>
       <c r="J5" t="n">
-        <v>24405.12</v>
+        <v>24809.51</v>
       </c>
       <c r="K5" t="n">
-        <v>24524.16</v>
+        <v>24881.1</v>
       </c>
       <c r="L5" t="n">
-        <v>24643.2</v>
+        <v>24952.68</v>
       </c>
       <c r="M5" t="n">
-        <v>24729.62</v>
+        <v>25110.53</v>
       </c>
       <c r="N5" t="n">
-        <v>24816.04</v>
+        <v>25268.37</v>
       </c>
       <c r="O5" t="n">
-        <v>24967.7</v>
+        <v>25253.7</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -939,27 +939,23 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W5" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -969,50 +965,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25028.93</v>
+        <v>25025.13</v>
       </c>
       <c r="C6" t="n">
-        <v>25095.66</v>
+        <v>25655.82</v>
       </c>
       <c r="D6" t="n">
-        <v>24887</v>
+        <v>24994.64</v>
       </c>
       <c r="E6" t="n">
-        <v>25040.28</v>
+        <v>25580.88</v>
       </c>
       <c r="F6" t="n">
-        <v>44.47</v>
+        <v>540.6</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0216</v>
       </c>
       <c r="H6" t="n">
-        <v>208.66</v>
+        <v>661.1799999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>24565.41</v>
+        <v>24678.34</v>
       </c>
       <c r="J6" t="n">
-        <v>24809.51</v>
+        <v>24856.09</v>
       </c>
       <c r="K6" t="n">
-        <v>24881.1</v>
+        <v>24935.95</v>
       </c>
       <c r="L6" t="n">
-        <v>24952.68</v>
+        <v>25015.8</v>
       </c>
       <c r="M6" t="n">
-        <v>25110.53</v>
+        <v>25144.61</v>
       </c>
       <c r="N6" t="n">
-        <v>25268.37</v>
+        <v>25273.41</v>
       </c>
       <c r="O6" t="n">
-        <v>25253.7</v>
+        <v>25304.32</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1023,23 +1019,27 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1049,50 +1049,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25025.13</v>
+        <v>25763.97</v>
       </c>
       <c r="C7" t="n">
-        <v>25655.82</v>
+        <v>25826.78</v>
       </c>
       <c r="D7" t="n">
-        <v>24994.64</v>
+        <v>25611.69</v>
       </c>
       <c r="E7" t="n">
-        <v>25580.88</v>
+        <v>25779.31</v>
       </c>
       <c r="F7" t="n">
-        <v>540.6</v>
+        <v>198.43</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0216</v>
+        <v>0.0078</v>
       </c>
       <c r="H7" t="n">
-        <v>661.1799999999999</v>
+        <v>215.09</v>
       </c>
       <c r="I7" t="n">
-        <v>24678.34</v>
+        <v>24333.46</v>
       </c>
       <c r="J7" t="n">
-        <v>24856.09</v>
+        <v>25047.53</v>
       </c>
       <c r="K7" t="n">
-        <v>24935.95</v>
+        <v>25250.29</v>
       </c>
       <c r="L7" t="n">
-        <v>25015.8</v>
+        <v>25453.06</v>
       </c>
       <c r="M7" t="n">
-        <v>25144.61</v>
+        <v>25911.47</v>
       </c>
       <c r="N7" t="n">
-        <v>25273.41</v>
+        <v>26369.89</v>
       </c>
       <c r="O7" t="n">
-        <v>25304.32</v>
+        <v>26317</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1103,27 +1103,23 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1133,50 +1129,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25763.97</v>
+        <v>25811.9</v>
       </c>
       <c r="C8" t="n">
-        <v>25826.78</v>
+        <v>25900.1</v>
       </c>
       <c r="D8" t="n">
-        <v>25611.69</v>
+        <v>25698.56</v>
       </c>
       <c r="E8" t="n">
-        <v>25779.31</v>
+        <v>25817.89</v>
       </c>
       <c r="F8" t="n">
-        <v>198.43</v>
+        <v>38.58</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0078</v>
+        <v>0.0015</v>
       </c>
       <c r="H8" t="n">
-        <v>215.09</v>
+        <v>201.54</v>
       </c>
       <c r="I8" t="n">
-        <v>24333.46</v>
+        <v>25396.6</v>
       </c>
       <c r="J8" t="n">
-        <v>25047.53</v>
+        <v>25594.26</v>
       </c>
       <c r="K8" t="n">
-        <v>25250.29</v>
+        <v>25671.77</v>
       </c>
       <c r="L8" t="n">
-        <v>25453.06</v>
+        <v>25749.27</v>
       </c>
       <c r="M8" t="n">
-        <v>25911.47</v>
+        <v>25886.86</v>
       </c>
       <c r="N8" t="n">
-        <v>26369.89</v>
+        <v>26024.44</v>
       </c>
       <c r="O8" t="n">
-        <v>26317</v>
+        <v>26041.87</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1187,14 +1183,14 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U8" s="8" t="n">
@@ -1203,7 +1199,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1213,69 +1209,73 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25811.9</v>
+        <v>25770.45</v>
       </c>
       <c r="C9" t="n">
-        <v>25900.1</v>
+        <v>25811.97</v>
       </c>
       <c r="D9" t="n">
-        <v>25698.56</v>
+        <v>25465.12</v>
       </c>
       <c r="E9" t="n">
-        <v>25817.89</v>
+        <v>25465.25</v>
       </c>
       <c r="F9" t="n">
-        <v>38.58</v>
+        <v>-352.64</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0137</v>
       </c>
       <c r="H9" t="n">
-        <v>201.54</v>
+        <v>346.85</v>
       </c>
       <c r="I9" t="n">
-        <v>25396.6</v>
+        <v>25497.02</v>
       </c>
       <c r="J9" t="n">
-        <v>25594.26</v>
+        <v>25625.63</v>
       </c>
       <c r="K9" t="n">
-        <v>25671.77</v>
+        <v>25717.12</v>
       </c>
       <c r="L9" t="n">
-        <v>25749.27</v>
+        <v>25808.61</v>
       </c>
       <c r="M9" t="n">
-        <v>25886.86</v>
+        <v>25918.66</v>
       </c>
       <c r="N9" t="n">
-        <v>26024.44</v>
+        <v>26028.71</v>
       </c>
       <c r="O9" t="n">
-        <v>26041.87</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+        <v>26101.64</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
@@ -1293,67 +1293,67 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25770.45</v>
+        <v>25274.94</v>
       </c>
       <c r="C10" t="n">
-        <v>25811.97</v>
+        <v>25280.16</v>
       </c>
       <c r="D10" t="n">
-        <v>25465.12</v>
+        <v>24830.17</v>
       </c>
       <c r="E10" t="n">
-        <v>25465.25</v>
+        <v>24897.45</v>
       </c>
       <c r="F10" t="n">
-        <v>-352.64</v>
+        <v>-567.8</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0223</v>
       </c>
       <c r="H10" t="n">
-        <v>346.85</v>
+        <v>449.99</v>
       </c>
       <c r="I10" t="n">
-        <v>25497.02</v>
+        <v>25118.27</v>
       </c>
       <c r="J10" t="n">
-        <v>25625.63</v>
+        <v>25031.75</v>
       </c>
       <c r="K10" t="n">
-        <v>25717.12</v>
+        <v>25291.82</v>
       </c>
       <c r="L10" t="n">
-        <v>25808.61</v>
+        <v>25551.9</v>
       </c>
       <c r="M10" t="n">
-        <v>25918.66</v>
+        <v>25638.68</v>
       </c>
       <c r="N10" t="n">
-        <v>26028.71</v>
+        <v>25725.45</v>
       </c>
       <c r="O10" t="n">
-        <v>26101.64</v>
+        <v>26158.82</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1367,7 +1367,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1377,134 +1377,134 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25274.94</v>
+        <v>25097.48</v>
       </c>
       <c r="C11" t="n">
-        <v>25280.16</v>
+        <v>25127.76</v>
       </c>
       <c r="D11" t="n">
-        <v>24830.17</v>
+        <v>24867.32</v>
       </c>
       <c r="E11" t="n">
-        <v>24897.45</v>
+        <v>25118.27</v>
       </c>
       <c r="F11" t="n">
-        <v>-567.8</v>
+        <v>220.82</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0089</v>
       </c>
       <c r="H11" t="n">
-        <v>449.99</v>
+        <v>260.44</v>
       </c>
       <c r="I11" t="n">
-        <v>25118.27</v>
+        <v>24380.18</v>
       </c>
       <c r="J11" t="n">
-        <v>25031.75</v>
+        <v>24368.6</v>
       </c>
       <c r="K11" t="n">
-        <v>25291.82</v>
+        <v>24672.45</v>
       </c>
       <c r="L11" t="n">
-        <v>25551.9</v>
+        <v>24976.31</v>
       </c>
       <c r="M11" t="n">
-        <v>25638.68</v>
+        <v>25122.44</v>
       </c>
       <c r="N11" t="n">
-        <v>25725.45</v>
+        <v>25268.58</v>
       </c>
       <c r="O11" t="n">
-        <v>26158.82</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
+        <v>25730.15</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25097.48</v>
+        <v>25081.19</v>
       </c>
       <c r="C12" t="n">
-        <v>25127.76</v>
+        <v>25195.83</v>
       </c>
       <c r="D12" t="n">
-        <v>24867.32</v>
+        <v>24937.52</v>
       </c>
       <c r="E12" t="n">
-        <v>25118.27</v>
+        <v>25067.09</v>
       </c>
       <c r="F12" t="n">
-        <v>220.82</v>
+        <v>-51.18</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.002</v>
       </c>
       <c r="H12" t="n">
-        <v>260.44</v>
+        <v>258.31</v>
       </c>
       <c r="I12" t="n">
-        <v>24380.18</v>
+        <v>24606.88</v>
       </c>
       <c r="J12" t="n">
-        <v>24368.6</v>
+        <v>24918.19</v>
       </c>
       <c r="K12" t="n">
-        <v>24672.45</v>
+        <v>24988.05</v>
       </c>
       <c r="L12" t="n">
-        <v>24976.31</v>
+        <v>25057.9</v>
       </c>
       <c r="M12" t="n">
-        <v>25122.44</v>
+        <v>25248.49</v>
       </c>
       <c r="N12" t="n">
-        <v>25268.58</v>
+        <v>25439.07</v>
       </c>
       <c r="O12" t="n">
-        <v>25730.15</v>
+        <v>25388.2</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1512,18 +1512,18 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1531,7 +1531,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1545,50 +1545,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25081.19</v>
+        <v>24963.8</v>
       </c>
       <c r="C13" t="n">
-        <v>25195.83</v>
+        <v>25154.58</v>
       </c>
       <c r="D13" t="n">
-        <v>24937.52</v>
+        <v>24963.8</v>
       </c>
       <c r="E13" t="n">
-        <v>25067.09</v>
+        <v>25114.25</v>
       </c>
       <c r="F13" t="n">
-        <v>-51.18</v>
+        <v>47.16</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="H13" t="n">
-        <v>258.31</v>
+        <v>190.78</v>
       </c>
       <c r="I13" t="n">
-        <v>24606.88</v>
+        <v>24679.21</v>
       </c>
       <c r="J13" t="n">
-        <v>24918.19</v>
+        <v>24808.99</v>
       </c>
       <c r="K13" t="n">
-        <v>24988.05</v>
+        <v>24937.93</v>
       </c>
       <c r="L13" t="n">
-        <v>25057.9</v>
+        <v>25066.88</v>
       </c>
       <c r="M13" t="n">
-        <v>25248.49</v>
+        <v>25196.25</v>
       </c>
       <c r="N13" t="n">
-        <v>25439.07</v>
+        <v>25325.61</v>
       </c>
       <c r="O13" t="n">
-        <v>25388.2</v>
+        <v>25454.14</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1596,12 +1596,10 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1615,7 +1613,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1629,61 +1627,65 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24963.8</v>
+        <v>24932.62</v>
       </c>
       <c r="C14" t="n">
-        <v>25154.58</v>
+        <v>25204.68</v>
       </c>
       <c r="D14" t="n">
-        <v>24963.8</v>
+        <v>24869.25</v>
       </c>
       <c r="E14" t="n">
-        <v>25114.25</v>
+        <v>25147.03</v>
       </c>
       <c r="F14" t="n">
-        <v>47.16</v>
+        <v>32.78</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0013</v>
       </c>
       <c r="H14" t="n">
-        <v>190.78</v>
+        <v>335.43</v>
       </c>
       <c r="I14" t="n">
-        <v>24679.21</v>
+        <v>24773.02</v>
       </c>
       <c r="J14" t="n">
-        <v>24808.99</v>
+        <v>24951</v>
       </c>
       <c r="K14" t="n">
-        <v>24937.93</v>
+        <v>25018.86</v>
       </c>
       <c r="L14" t="n">
-        <v>25066.88</v>
+        <v>25086.72</v>
       </c>
       <c r="M14" t="n">
-        <v>25196.25</v>
+        <v>25209.64</v>
       </c>
       <c r="N14" t="n">
-        <v>25325.61</v>
+        <v>25332.56</v>
       </c>
       <c r="O14" t="n">
-        <v>25454.14</v>
+        <v>25345.36</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1697,7 +1699,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1711,50 +1713,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24932.62</v>
+        <v>24970.05</v>
       </c>
       <c r="C15" t="n">
-        <v>25204.68</v>
+        <v>25055.48</v>
       </c>
       <c r="D15" t="n">
-        <v>24869.25</v>
+        <v>24839.23</v>
       </c>
       <c r="E15" t="n">
-        <v>25147.03</v>
+        <v>24999.53</v>
       </c>
       <c r="F15" t="n">
-        <v>32.78</v>
+        <v>-147.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0059</v>
       </c>
       <c r="H15" t="n">
-        <v>335.43</v>
+        <v>216.25</v>
       </c>
       <c r="I15" t="n">
-        <v>24773.02</v>
+        <v>24533.82</v>
       </c>
       <c r="J15" t="n">
-        <v>24951</v>
+        <v>24866.63</v>
       </c>
       <c r="K15" t="n">
-        <v>25018.86</v>
+        <v>24979.31</v>
       </c>
       <c r="L15" t="n">
-        <v>25086.72</v>
+        <v>25092</v>
       </c>
       <c r="M15" t="n">
-        <v>25209.64</v>
+        <v>25314.74</v>
       </c>
       <c r="N15" t="n">
-        <v>25332.56</v>
+        <v>25537.49</v>
       </c>
       <c r="O15" t="n">
-        <v>25345.36</v>
+        <v>25540.11</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1766,12 +1768,12 @@
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1783,64 +1785,60 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24970.05</v>
+        <v>25018.95</v>
       </c>
       <c r="C16" t="n">
-        <v>25055.48</v>
+        <v>25021.51</v>
       </c>
       <c r="D16" t="n">
-        <v>24839.23</v>
+        <v>24696.17</v>
       </c>
       <c r="E16" t="n">
-        <v>24999.53</v>
+        <v>24915.49</v>
       </c>
       <c r="F16" t="n">
-        <v>-147.5</v>
+        <v>-84.04000000000001</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0059</v>
+        <v>-0.0034</v>
       </c>
       <c r="H16" t="n">
-        <v>216.25</v>
+        <v>325.34</v>
       </c>
       <c r="I16" t="n">
-        <v>24533.82</v>
+        <v>24622.98</v>
       </c>
       <c r="J16" t="n">
-        <v>24866.63</v>
+        <v>24809.37</v>
       </c>
       <c r="K16" t="n">
-        <v>24979.31</v>
+        <v>24891.4</v>
       </c>
       <c r="L16" t="n">
-        <v>25092</v>
+        <v>24973.44</v>
       </c>
       <c r="M16" t="n">
-        <v>25314.74</v>
+        <v>25107.65</v>
       </c>
       <c r="N16" t="n">
-        <v>25537.49</v>
+        <v>25241.87</v>
       </c>
       <c r="O16" t="n">
-        <v>25540.11</v>
+        <v>25271.73</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1855,7 +1853,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1869,7 +1867,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1879,67 +1877,65 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25018.95</v>
+        <v>24755.09</v>
       </c>
       <c r="C17" t="n">
-        <v>25021.51</v>
+        <v>24850.75</v>
       </c>
       <c r="D17" t="n">
-        <v>24696.17</v>
+        <v>24651.34</v>
       </c>
       <c r="E17" t="n">
-        <v>24915.49</v>
+        <v>24830.98</v>
       </c>
       <c r="F17" t="n">
-        <v>-84.04000000000001</v>
+        <v>-84.51000000000001</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>-0.0034</v>
       </c>
       <c r="H17" t="n">
-        <v>325.34</v>
+        <v>199.41</v>
       </c>
       <c r="I17" t="n">
-        <v>24622.98</v>
+        <v>24370.83</v>
       </c>
       <c r="J17" t="n">
-        <v>24809.37</v>
+        <v>24618.48</v>
       </c>
       <c r="K17" t="n">
-        <v>24891.4</v>
+        <v>24752.82</v>
       </c>
       <c r="L17" t="n">
-        <v>24973.44</v>
+        <v>24887.17</v>
       </c>
       <c r="M17" t="n">
-        <v>25107.65</v>
+        <v>25078.16</v>
       </c>
       <c r="N17" t="n">
-        <v>25241.87</v>
+        <v>25269.16</v>
       </c>
       <c r="O17" t="n">
-        <v>25271.73</v>
+        <v>25346.85</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q17" s="6" t="n">
+        <v/>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1951,7 +1947,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1961,50 +1957,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24755.09</v>
+        <v>24769.15</v>
       </c>
       <c r="C18" t="n">
-        <v>24850.75</v>
+        <v>24974.53</v>
       </c>
       <c r="D18" t="n">
-        <v>24651.34</v>
+        <v>24751.13</v>
       </c>
       <c r="E18" t="n">
-        <v>24830.98</v>
+        <v>24846.69</v>
       </c>
       <c r="F18" t="n">
-        <v>-84.51000000000001</v>
+        <v>15.71</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>199.41</v>
+        <v>223.4</v>
       </c>
       <c r="I18" t="n">
-        <v>24370.83</v>
+        <v>24451.93</v>
       </c>
       <c r="J18" t="n">
-        <v>24618.48</v>
+        <v>24671.54</v>
       </c>
       <c r="K18" t="n">
-        <v>24752.82</v>
+        <v>24731.28</v>
       </c>
       <c r="L18" t="n">
-        <v>24887.17</v>
+        <v>24791.01</v>
       </c>
       <c r="M18" t="n">
-        <v>25078.16</v>
+        <v>24930.69</v>
       </c>
       <c r="N18" t="n">
-        <v>25269.16</v>
+        <v>25070.36</v>
       </c>
       <c r="O18" t="n">
-        <v>25346.85</v>
+        <v>25050.16</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2012,18 +2008,18 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R18" s="6" t="n">
+        <v/>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2031,60 +2027,64 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24769.15</v>
+        <v>24922.1</v>
       </c>
       <c r="C19" t="n">
-        <v>24974.53</v>
+        <v>25011.35</v>
       </c>
       <c r="D19" t="n">
-        <v>24751.13</v>
+        <v>24817.34</v>
       </c>
       <c r="E19" t="n">
-        <v>24846.69</v>
+        <v>25011.35</v>
       </c>
       <c r="F19" t="n">
-        <v>15.71</v>
+        <v>164.66</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0066</v>
       </c>
       <c r="H19" t="n">
-        <v>223.4</v>
+        <v>194.01</v>
       </c>
       <c r="I19" t="n">
-        <v>24451.93</v>
+        <v>24527.73</v>
       </c>
       <c r="J19" t="n">
-        <v>24671.54</v>
+        <v>24615.22</v>
       </c>
       <c r="K19" t="n">
-        <v>24731.28</v>
+        <v>24734.99</v>
       </c>
       <c r="L19" t="n">
-        <v>24791.01</v>
+        <v>24854.76</v>
       </c>
       <c r="M19" t="n">
-        <v>24930.69</v>
+        <v>24958.39</v>
       </c>
       <c r="N19" t="n">
-        <v>25070.36</v>
+        <v>25062.02</v>
       </c>
       <c r="O19" t="n">
-        <v>25050.16</v>
+        <v>25197.93</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2095,9 +2095,9 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -2105,13 +2105,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2125,50 +2127,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24922.1</v>
+        <v>25001.31</v>
       </c>
       <c r="C20" t="n">
-        <v>25011.35</v>
+        <v>25271.34</v>
       </c>
       <c r="D20" t="n">
-        <v>24817.34</v>
+        <v>24984.27</v>
       </c>
       <c r="E20" t="n">
-        <v>25011.35</v>
+        <v>25155.41</v>
       </c>
       <c r="F20" t="n">
-        <v>164.66</v>
+        <v>144.06</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0058</v>
       </c>
       <c r="H20" t="n">
-        <v>194.01</v>
+        <v>287.07</v>
       </c>
       <c r="I20" t="n">
-        <v>24527.73</v>
+        <v>24623.33</v>
       </c>
       <c r="J20" t="n">
-        <v>24615.22</v>
+        <v>24865.84</v>
       </c>
       <c r="K20" t="n">
-        <v>24734.99</v>
+        <v>24914.34</v>
       </c>
       <c r="L20" t="n">
-        <v>24854.76</v>
+        <v>24962.85</v>
       </c>
       <c r="M20" t="n">
-        <v>24958.39</v>
+        <v>25108.35</v>
       </c>
       <c r="N20" t="n">
-        <v>25062.02</v>
+        <v>25253.86</v>
       </c>
       <c r="O20" t="n">
-        <v>25197.93</v>
+        <v>25205.36</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2179,25 +2181,27 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U20" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W20" s="11" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2211,171 +2215,165 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25001.31</v>
+        <v>24994.05</v>
       </c>
       <c r="C21" t="n">
-        <v>25271.34</v>
+        <v>25074.28</v>
       </c>
       <c r="D21" t="n">
-        <v>24984.27</v>
+        <v>24696.59</v>
       </c>
       <c r="E21" t="n">
-        <v>25155.41</v>
+        <v>24763.12</v>
       </c>
       <c r="F21" t="n">
-        <v>144.06</v>
+        <v>-392.29</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0156</v>
       </c>
       <c r="H21" t="n">
-        <v>287.07</v>
+        <v>377.69</v>
       </c>
       <c r="I21" t="n">
-        <v>24623.33</v>
+        <v>24697.2</v>
       </c>
       <c r="J21" t="n">
-        <v>24865.84</v>
+        <v>24882.14</v>
       </c>
       <c r="K21" t="n">
-        <v>24914.34</v>
+        <v>25011.88</v>
       </c>
       <c r="L21" t="n">
-        <v>24962.85</v>
+        <v>25141.61</v>
       </c>
       <c r="M21" t="n">
-        <v>25108.35</v>
+        <v>25298.95</v>
       </c>
       <c r="N21" t="n">
-        <v>25253.86</v>
+        <v>25456.28</v>
       </c>
       <c r="O21" t="n">
-        <v>25205.36</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+        <v>25558.41</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W21" s="11" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24994.05</v>
+        <v>24830.41</v>
       </c>
       <c r="C22" t="n">
-        <v>25074.28</v>
+        <v>25099.68</v>
       </c>
       <c r="D22" t="n">
-        <v>24696.59</v>
+        <v>24821.67</v>
       </c>
       <c r="E22" t="n">
-        <v>24763.12</v>
+        <v>25099</v>
       </c>
       <c r="F22" t="n">
-        <v>-392.29</v>
+        <v>335.88</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0136</v>
       </c>
       <c r="H22" t="n">
-        <v>377.69</v>
+        <v>278.01</v>
       </c>
       <c r="I22" t="n">
-        <v>24697.2</v>
+        <v>24318.9</v>
       </c>
       <c r="J22" t="n">
-        <v>24882.14</v>
+        <v>24324.27</v>
       </c>
       <c r="K22" t="n">
-        <v>25011.88</v>
+        <v>24574.27</v>
       </c>
       <c r="L22" t="n">
-        <v>25141.61</v>
+        <v>24824.28</v>
       </c>
       <c r="M22" t="n">
-        <v>25298.95</v>
+        <v>24951.96</v>
       </c>
       <c r="N22" t="n">
-        <v>25456.28</v>
+        <v>25079.65</v>
       </c>
       <c r="O22" t="n">
-        <v>25558.41</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
+        <v>25451.97</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
       <c r="W22" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
@@ -2383,50 +2381,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24830.41</v>
+        <v>25459.32</v>
       </c>
       <c r="C23" t="n">
-        <v>25099.68</v>
+        <v>25560.4</v>
       </c>
       <c r="D23" t="n">
-        <v>24821.67</v>
+        <v>25361.03</v>
       </c>
       <c r="E23" t="n">
-        <v>25099</v>
+        <v>25361.03</v>
       </c>
       <c r="F23" t="n">
-        <v>335.88</v>
+        <v>262.03</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0104</v>
       </c>
       <c r="H23" t="n">
-        <v>278.01</v>
+        <v>199.37</v>
       </c>
       <c r="I23" t="n">
-        <v>24318.9</v>
+        <v>24543.66</v>
       </c>
       <c r="J23" t="n">
-        <v>24324.27</v>
+        <v>24890.15</v>
       </c>
       <c r="K23" t="n">
-        <v>24574.27</v>
+        <v>24960</v>
       </c>
       <c r="L23" t="n">
-        <v>24824.28</v>
+        <v>25029.84</v>
       </c>
       <c r="M23" t="n">
-        <v>24951.96</v>
+        <v>25238</v>
       </c>
       <c r="N23" t="n">
-        <v>25079.65</v>
+        <v>25446.17</v>
       </c>
       <c r="O23" t="n">
-        <v>25451.97</v>
+        <v>25377.69</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2437,7 +2435,7 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2449,13 +2447,15 @@
       </c>
       <c r="U23" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2465,50 +2465,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25459.32</v>
+        <v>25496.13</v>
       </c>
       <c r="C24" t="n">
-        <v>25560.4</v>
+        <v>25553.47</v>
       </c>
       <c r="D24" t="n">
-        <v>25361.03</v>
+        <v>25307.17</v>
       </c>
       <c r="E24" t="n">
-        <v>25361.03</v>
+        <v>25464.01</v>
       </c>
       <c r="F24" t="n">
-        <v>262.03</v>
+        <v>102.98</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0104</v>
+        <v>0.0041</v>
       </c>
       <c r="H24" t="n">
-        <v>199.37</v>
+        <v>246.3</v>
       </c>
       <c r="I24" t="n">
-        <v>24543.66</v>
+        <v>25161.66</v>
       </c>
       <c r="J24" t="n">
-        <v>24890.15</v>
+        <v>25111.82</v>
       </c>
       <c r="K24" t="n">
-        <v>24960</v>
+        <v>25261.34</v>
       </c>
       <c r="L24" t="n">
-        <v>25029.84</v>
+        <v>25410.87</v>
       </c>
       <c r="M24" t="n">
-        <v>25238</v>
+        <v>25460.71</v>
       </c>
       <c r="N24" t="n">
-        <v>25446.17</v>
+        <v>25510.56</v>
       </c>
       <c r="O24" t="n">
-        <v>25377.69</v>
+        <v>25759.77</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2519,14 +2519,14 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U24" s="8" t="inlineStr">
@@ -2534,65 +2534,67 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="V24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25496.13</v>
+        <v>25551.97</v>
       </c>
       <c r="C25" t="n">
-        <v>25553.47</v>
+        <v>25571.45</v>
       </c>
       <c r="D25" t="n">
-        <v>25307.17</v>
+        <v>25336.39</v>
       </c>
       <c r="E25" t="n">
-        <v>25464.01</v>
+        <v>25460.48</v>
       </c>
       <c r="F25" t="n">
-        <v>102.98</v>
+        <v>-3.53</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0001</v>
       </c>
       <c r="H25" t="n">
-        <v>246.3</v>
+        <v>235.06</v>
       </c>
       <c r="I25" t="n">
-        <v>25161.66</v>
+        <v>25060.87</v>
       </c>
       <c r="J25" t="n">
-        <v>25111.82</v>
+        <v>25234.55</v>
       </c>
       <c r="K25" t="n">
-        <v>25261.34</v>
+        <v>25340.86</v>
       </c>
       <c r="L25" t="n">
-        <v>25410.87</v>
+        <v>25447.17</v>
       </c>
       <c r="M25" t="n">
-        <v>25460.71</v>
+        <v>25587.16</v>
       </c>
       <c r="N25" t="n">
-        <v>25510.56</v>
+        <v>25727.16</v>
       </c>
       <c r="O25" t="n">
-        <v>25759.77</v>
+        <v>25799.77</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2600,85 +2602,83 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25551.97</v>
+        <v>25487.45</v>
       </c>
       <c r="C26" t="n">
-        <v>25571.45</v>
+        <v>25651.16</v>
       </c>
       <c r="D26" t="n">
-        <v>25336.39</v>
+        <v>25303.11</v>
       </c>
       <c r="E26" t="n">
-        <v>25460.48</v>
+        <v>25612.03</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.53</v>
+        <v>151.55</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.006</v>
       </c>
       <c r="H26" t="n">
-        <v>235.06</v>
+        <v>348.05</v>
       </c>
       <c r="I26" t="n">
-        <v>25060.87</v>
+        <v>25101.33</v>
       </c>
       <c r="J26" t="n">
-        <v>25234.55</v>
+        <v>25228.7</v>
       </c>
       <c r="K26" t="n">
-        <v>25340.86</v>
+        <v>25342.95</v>
       </c>
       <c r="L26" t="n">
-        <v>25447.17</v>
+        <v>25457.2</v>
       </c>
       <c r="M26" t="n">
-        <v>25587.16</v>
+        <v>25578.01</v>
       </c>
       <c r="N26" t="n">
-        <v>25727.16</v>
+        <v>25698.82</v>
       </c>
       <c r="O26" t="n">
-        <v>25799.77</v>
+        <v>25806.51</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2691,13 +2691,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2705,7 +2707,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2719,50 +2721,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25487.45</v>
+        <v>25709.37</v>
       </c>
       <c r="C27" t="n">
-        <v>25651.16</v>
+        <v>25891.51</v>
       </c>
       <c r="D27" t="n">
-        <v>25303.11</v>
+        <v>25549.53</v>
       </c>
       <c r="E27" t="n">
-        <v>25612.03</v>
+        <v>25629.24</v>
       </c>
       <c r="F27" t="n">
-        <v>151.55</v>
+        <v>17.21</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0007</v>
       </c>
       <c r="H27" t="n">
-        <v>348.05</v>
+        <v>341.98</v>
       </c>
       <c r="I27" t="n">
-        <v>25101.33</v>
+        <v>24955.06</v>
       </c>
       <c r="J27" t="n">
-        <v>25228.7</v>
+        <v>25331.43</v>
       </c>
       <c r="K27" t="n">
-        <v>25342.95</v>
+        <v>25438</v>
       </c>
       <c r="L27" t="n">
-        <v>25457.2</v>
+        <v>25544.58</v>
       </c>
       <c r="M27" t="n">
-        <v>25578.01</v>
+        <v>25786.05</v>
       </c>
       <c r="N27" t="n">
-        <v>25698.82</v>
+        <v>26027.53</v>
       </c>
       <c r="O27" t="n">
-        <v>25806.51</v>
+        <v>25999.21</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2770,19 +2772,17 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U27" s="8" t="n">
@@ -2791,64 +2791,60 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25709.37</v>
+        <v>25855.12</v>
       </c>
       <c r="C28" t="n">
-        <v>25891.51</v>
+        <v>26096.93</v>
       </c>
       <c r="D28" t="n">
-        <v>25549.53</v>
+        <v>25855.12</v>
       </c>
       <c r="E28" t="n">
-        <v>25629.24</v>
+        <v>26001.31</v>
       </c>
       <c r="F28" t="n">
-        <v>17.21</v>
+        <v>372.07</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0145</v>
       </c>
       <c r="H28" t="n">
-        <v>341.98</v>
+        <v>241.81</v>
       </c>
       <c r="I28" t="n">
-        <v>24955.06</v>
+        <v>25207.55</v>
       </c>
       <c r="J28" t="n">
-        <v>25331.43</v>
+        <v>25241.62</v>
       </c>
       <c r="K28" t="n">
-        <v>25438</v>
+        <v>25458.25</v>
       </c>
       <c r="L28" t="n">
-        <v>25544.58</v>
+        <v>25674.88</v>
       </c>
       <c r="M28" t="n">
-        <v>25786.05</v>
+        <v>25800.23</v>
       </c>
       <c r="N28" t="n">
-        <v>26027.53</v>
+        <v>25925.58</v>
       </c>
       <c r="O28" t="n">
-        <v>25999.21</v>
+        <v>26233.49</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2859,9 +2855,9 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
@@ -2869,13 +2865,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2885,50 +2883,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25855.12</v>
+        <v>26189.62</v>
       </c>
       <c r="C29" t="n">
-        <v>26096.93</v>
+        <v>26266.5</v>
       </c>
       <c r="D29" t="n">
-        <v>25855.12</v>
+        <v>26082.43</v>
       </c>
       <c r="E29" t="n">
-        <v>26001.31</v>
+        <v>26202.35</v>
       </c>
       <c r="F29" t="n">
-        <v>372.07</v>
+        <v>201.04</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0077</v>
       </c>
       <c r="H29" t="n">
-        <v>241.81</v>
+        <v>184.07</v>
       </c>
       <c r="I29" t="n">
-        <v>25207.55</v>
+        <v>25613.31</v>
       </c>
       <c r="J29" t="n">
-        <v>25241.62</v>
+        <v>25772.14</v>
       </c>
       <c r="K29" t="n">
-        <v>25458.25</v>
+        <v>25880.41</v>
       </c>
       <c r="L29" t="n">
-        <v>25674.88</v>
+        <v>25988.67</v>
       </c>
       <c r="M29" t="n">
-        <v>25800.23</v>
+        <v>26122.22</v>
       </c>
       <c r="N29" t="n">
-        <v>25925.58</v>
+        <v>26255.76</v>
       </c>
       <c r="O29" t="n">
-        <v>26233.49</v>
+        <v>26338.74</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2939,7 +2937,7 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2957,7 +2955,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2967,50 +2965,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26189.62</v>
+        <v>26393.43</v>
       </c>
       <c r="C30" t="n">
-        <v>26266.5</v>
+        <v>26403.81</v>
       </c>
       <c r="D30" t="n">
-        <v>26082.43</v>
+        <v>26123.18</v>
       </c>
       <c r="E30" t="n">
-        <v>26202.35</v>
+        <v>26126.3</v>
       </c>
       <c r="F30" t="n">
-        <v>201.04</v>
+        <v>-76.05</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0029</v>
       </c>
       <c r="H30" t="n">
-        <v>184.07</v>
+        <v>280.63</v>
       </c>
       <c r="I30" t="n">
-        <v>25613.31</v>
+        <v>25898.36</v>
       </c>
       <c r="J30" t="n">
-        <v>25772.14</v>
+        <v>26032.22</v>
       </c>
       <c r="K30" t="n">
-        <v>25880.41</v>
+        <v>26110.31</v>
       </c>
       <c r="L30" t="n">
-        <v>25988.67</v>
+        <v>26188.41</v>
       </c>
       <c r="M30" t="n">
-        <v>26122.22</v>
+        <v>26294.38</v>
       </c>
       <c r="N30" t="n">
-        <v>26255.76</v>
+        <v>26400.36</v>
       </c>
       <c r="O30" t="n">
-        <v>26338.74</v>
+        <v>26450.57</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3018,12 +3016,14 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
@@ -3033,66 +3033,70 @@
       </c>
       <c r="U30" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>26393.43</v>
+        <v>26116.27</v>
       </c>
       <c r="C31" t="n">
-        <v>26403.81</v>
+        <v>26229.33</v>
       </c>
       <c r="D31" t="n">
-        <v>26123.18</v>
+        <v>26081.69</v>
       </c>
       <c r="E31" t="n">
-        <v>26126.3</v>
+        <v>26140.13</v>
       </c>
       <c r="F31" t="n">
-        <v>-76.05</v>
+        <v>13.83</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0005</v>
       </c>
       <c r="H31" t="n">
-        <v>280.63</v>
+        <v>147.64</v>
       </c>
       <c r="I31" t="n">
-        <v>25898.36</v>
+        <v>25842.55</v>
       </c>
       <c r="J31" t="n">
-        <v>26032.22</v>
+        <v>25777.07</v>
       </c>
       <c r="K31" t="n">
-        <v>26110.31</v>
+        <v>25985.99</v>
       </c>
       <c r="L31" t="n">
-        <v>26188.41</v>
+        <v>26194.9</v>
       </c>
       <c r="M31" t="n">
-        <v>26294.38</v>
+        <v>26266.62</v>
       </c>
       <c r="N31" t="n">
-        <v>26400.36</v>
+        <v>26338.33</v>
       </c>
       <c r="O31" t="n">
-        <v>26450.57</v>
+        <v>26684.44</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3100,87 +3104,81 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26116.27</v>
+        <v>26235.8</v>
       </c>
       <c r="C32" t="n">
-        <v>26229.33</v>
+        <v>26445.18</v>
       </c>
       <c r="D32" t="n">
-        <v>26081.69</v>
+        <v>26223.64</v>
       </c>
       <c r="E32" t="n">
-        <v>26140.13</v>
+        <v>26319.45</v>
       </c>
       <c r="F32" t="n">
-        <v>13.83</v>
+        <v>179.32</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0069</v>
       </c>
       <c r="H32" t="n">
-        <v>147.64</v>
+        <v>221.54</v>
       </c>
       <c r="I32" t="n">
-        <v>25842.55</v>
+        <v>25934.05</v>
       </c>
       <c r="J32" t="n">
-        <v>25777.07</v>
+        <v>25984.8</v>
       </c>
       <c r="K32" t="n">
-        <v>25985.99</v>
+        <v>26066.31</v>
       </c>
       <c r="L32" t="n">
-        <v>26194.9</v>
+        <v>26147.82</v>
       </c>
       <c r="M32" t="n">
-        <v>26266.62</v>
+        <v>26213.95</v>
       </c>
       <c r="N32" t="n">
-        <v>26338.33</v>
+        <v>26280.08</v>
       </c>
       <c r="O32" t="n">
-        <v>26684.44</v>
+        <v>26376.97</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3193,76 +3191,78 @@
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="9" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>26235.8</v>
+        <v>26360.44</v>
       </c>
       <c r="C33" t="n">
-        <v>26445.18</v>
+        <v>26441.91</v>
       </c>
       <c r="D33" t="n">
-        <v>26223.64</v>
+        <v>26302.19</v>
       </c>
       <c r="E33" t="n">
-        <v>26319.45</v>
+        <v>26323.88</v>
       </c>
       <c r="F33" t="n">
-        <v>179.32</v>
+        <v>4.43</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0002</v>
       </c>
       <c r="H33" t="n">
-        <v>221.54</v>
+        <v>139.72</v>
       </c>
       <c r="I33" t="n">
-        <v>25934.05</v>
+        <v>26002.1</v>
       </c>
       <c r="J33" t="n">
-        <v>25984.8</v>
+        <v>26090.43</v>
       </c>
       <c r="K33" t="n">
-        <v>26066.31</v>
+        <v>26208.68</v>
       </c>
       <c r="L33" t="n">
-        <v>26147.82</v>
+        <v>26326.93</v>
       </c>
       <c r="M33" t="n">
-        <v>26213.95</v>
+        <v>26430.22</v>
       </c>
       <c r="N33" t="n">
-        <v>26280.08</v>
+        <v>26533.51</v>
       </c>
       <c r="O33" t="n">
-        <v>26376.97</v>
+        <v>26666.72</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
@@ -3283,70 +3283,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26360.44</v>
+        <v>26378</v>
       </c>
       <c r="C34" t="n">
-        <v>26441.91</v>
+        <v>26504.54</v>
       </c>
       <c r="D34" t="n">
-        <v>26302.19</v>
+        <v>26245.57</v>
       </c>
       <c r="E34" t="n">
-        <v>26323.88</v>
+        <v>26391.42</v>
       </c>
       <c r="F34" t="n">
-        <v>4.43</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0026</v>
       </c>
       <c r="H34" t="n">
-        <v>139.72</v>
+        <v>258.97</v>
       </c>
       <c r="I34" t="n">
-        <v>26002.1</v>
+        <v>26162.47</v>
       </c>
       <c r="J34" t="n">
-        <v>26090.43</v>
+        <v>26160.08</v>
       </c>
       <c r="K34" t="n">
-        <v>26208.68</v>
+        <v>26254.02</v>
       </c>
       <c r="L34" t="n">
-        <v>26326.93</v>
+        <v>26347.97</v>
       </c>
       <c r="M34" t="n">
-        <v>26430.22</v>
+        <v>26393.74</v>
       </c>
       <c r="N34" t="n">
-        <v>26533.51</v>
+        <v>26439.52</v>
       </c>
       <c r="O34" t="n">
-        <v>26666.72</v>
+        <v>26581.63</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3354,26 +3354,30 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3387,50 +3391,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>26378</v>
+        <v>26452</v>
       </c>
       <c r="C35" t="n">
-        <v>26504.54</v>
+        <v>26573.5</v>
       </c>
       <c r="D35" t="n">
-        <v>26245.57</v>
+        <v>26313.58</v>
       </c>
       <c r="E35" t="n">
-        <v>26391.42</v>
+        <v>26331.07</v>
       </c>
       <c r="F35" t="n">
-        <v>67.54000000000001</v>
+        <v>-60.35</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0023</v>
       </c>
       <c r="H35" t="n">
-        <v>258.97</v>
+        <v>259.92</v>
       </c>
       <c r="I35" t="n">
-        <v>26162.47</v>
+        <v>25986.6</v>
       </c>
       <c r="J35" t="n">
-        <v>26160.08</v>
+        <v>26140.63</v>
       </c>
       <c r="K35" t="n">
-        <v>26254.02</v>
+        <v>26261.94</v>
       </c>
       <c r="L35" t="n">
-        <v>26347.97</v>
+        <v>26383.24</v>
       </c>
       <c r="M35" t="n">
-        <v>26393.74</v>
+        <v>26520.9</v>
       </c>
       <c r="N35" t="n">
-        <v>26439.52</v>
+        <v>26658.57</v>
       </c>
       <c r="O35" t="n">
-        <v>26581.63</v>
+        <v>26763.51</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3438,30 +3442,26 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R35" s="6" t="n">
+        <v/>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3475,50 +3475,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26452</v>
+        <v>26437.35</v>
       </c>
       <c r="C36" t="n">
-        <v>26573.5</v>
+        <v>26489.78</v>
       </c>
       <c r="D36" t="n">
-        <v>26313.58</v>
+        <v>26285.23</v>
       </c>
       <c r="E36" t="n">
-        <v>26331.07</v>
+        <v>26299.74</v>
       </c>
       <c r="F36" t="n">
-        <v>-60.35</v>
+        <v>-31.33</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0012</v>
       </c>
       <c r="H36" t="n">
-        <v>259.92</v>
+        <v>204.55</v>
       </c>
       <c r="I36" t="n">
-        <v>25986.6</v>
+        <v>26053.66</v>
       </c>
       <c r="J36" t="n">
-        <v>26140.63</v>
+        <v>26014.92</v>
       </c>
       <c r="K36" t="n">
-        <v>26261.94</v>
+        <v>26201.11</v>
       </c>
       <c r="L36" t="n">
-        <v>26383.24</v>
+        <v>26387.31</v>
       </c>
       <c r="M36" t="n">
-        <v>26520.9</v>
+        <v>26461.03</v>
       </c>
       <c r="N36" t="n">
-        <v>26658.57</v>
+        <v>26534.76</v>
       </c>
       <c r="O36" t="n">
-        <v>26763.51</v>
+        <v>26833.42</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3529,7 +3529,7 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="S36" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3545,64 +3545,64 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26437.35</v>
+        <v>26445.99</v>
       </c>
       <c r="C37" t="n">
-        <v>26489.78</v>
+        <v>26541.34</v>
       </c>
       <c r="D37" t="n">
-        <v>26285.23</v>
+        <v>26404.95</v>
       </c>
       <c r="E37" t="n">
-        <v>26299.74</v>
+        <v>26440.31</v>
       </c>
       <c r="F37" t="n">
-        <v>-31.33</v>
+        <v>140.57</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0053</v>
       </c>
       <c r="H37" t="n">
-        <v>204.55</v>
+        <v>136.39</v>
       </c>
       <c r="I37" t="n">
-        <v>26053.66</v>
+        <v>26080.68</v>
       </c>
       <c r="J37" t="n">
-        <v>26014.92</v>
+        <v>26051.31</v>
       </c>
       <c r="K37" t="n">
-        <v>26201.11</v>
+        <v>26197.47</v>
       </c>
       <c r="L37" t="n">
-        <v>26387.31</v>
+        <v>26343.62</v>
       </c>
       <c r="M37" t="n">
-        <v>26461.03</v>
+        <v>26402.01</v>
       </c>
       <c r="N37" t="n">
-        <v>26534.76</v>
+        <v>26460.41</v>
       </c>
       <c r="O37" t="n">
-        <v>26833.42</v>
+        <v>26694.33</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
@@ -3623,70 +3623,68 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U37" s="8" t="n">
-        <v/>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26445.99</v>
+        <v>26490.3</v>
       </c>
       <c r="C38" t="n">
-        <v>26541.34</v>
+        <v>26493.5</v>
       </c>
       <c r="D38" t="n">
-        <v>26404.95</v>
+        <v>26338.61</v>
       </c>
       <c r="E38" t="n">
-        <v>26440.31</v>
+        <v>26338.61</v>
       </c>
       <c r="F38" t="n">
-        <v>140.57</v>
+        <v>-101.7</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0038</v>
       </c>
       <c r="H38" t="n">
-        <v>136.39</v>
+        <v>154.89</v>
       </c>
       <c r="I38" t="n">
-        <v>26080.68</v>
+        <v>26268.56</v>
       </c>
       <c r="J38" t="n">
-        <v>26051.31</v>
+        <v>26287.5</v>
       </c>
       <c r="K38" t="n">
-        <v>26197.47</v>
+        <v>26372.12</v>
       </c>
       <c r="L38" t="n">
-        <v>26343.62</v>
+        <v>26456.73</v>
       </c>
       <c r="M38" t="n">
-        <v>26402.01</v>
+        <v>26508.51</v>
       </c>
       <c r="N38" t="n">
-        <v>26460.41</v>
+        <v>26560.28</v>
       </c>
       <c r="O38" t="n">
-        <v>26694.33</v>
+        <v>26677.73</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3694,94 +3692,100 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26490.3</v>
+        <v>26280.86</v>
       </c>
       <c r="C39" t="n">
-        <v>26493.5</v>
+        <v>26292.95</v>
       </c>
       <c r="D39" t="n">
-        <v>26338.61</v>
+        <v>26119.54</v>
       </c>
       <c r="E39" t="n">
-        <v>26338.61</v>
+        <v>26128.36</v>
       </c>
       <c r="F39" t="n">
-        <v>-101.7</v>
+        <v>-210.25</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.008</v>
       </c>
       <c r="H39" t="n">
-        <v>154.89</v>
+        <v>173.41</v>
       </c>
       <c r="I39" t="n">
-        <v>26268.56</v>
+        <v>26183.72</v>
       </c>
       <c r="J39" t="n">
-        <v>26287.5</v>
+        <v>26145</v>
       </c>
       <c r="K39" t="n">
-        <v>26372.12</v>
+        <v>26261.16</v>
       </c>
       <c r="L39" t="n">
-        <v>26456.73</v>
+        <v>26377.33</v>
       </c>
       <c r="M39" t="n">
-        <v>26508.51</v>
+        <v>26416.05</v>
       </c>
       <c r="N39" t="n">
-        <v>26560.28</v>
+        <v>26454.78</v>
       </c>
       <c r="O39" t="n">
-        <v>26677.73</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
+        <v>26648.39</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3797,79 +3801,71 @@
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>26280.86</v>
+        <v>26146.12</v>
       </c>
       <c r="C40" t="n">
-        <v>26292.95</v>
+        <v>26187.82</v>
       </c>
       <c r="D40" t="n">
-        <v>26119.54</v>
+        <v>26063.37</v>
       </c>
       <c r="E40" t="n">
-        <v>26128.36</v>
+        <v>26091.33</v>
       </c>
       <c r="F40" t="n">
-        <v>-210.25</v>
+        <v>-37.03</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0014</v>
       </c>
       <c r="H40" t="n">
-        <v>173.41</v>
+        <v>124.45</v>
       </c>
       <c r="I40" t="n">
-        <v>26183.72</v>
+        <v>25946.13</v>
       </c>
       <c r="J40" t="n">
-        <v>26145</v>
+        <v>25916.01</v>
       </c>
       <c r="K40" t="n">
-        <v>26261.16</v>
+        <v>26041.65</v>
       </c>
       <c r="L40" t="n">
-        <v>26377.33</v>
+        <v>26167.3</v>
       </c>
       <c r="M40" t="n">
-        <v>26416.05</v>
+        <v>26215.06</v>
       </c>
       <c r="N40" t="n">
-        <v>26454.78</v>
+        <v>26262.83</v>
       </c>
       <c r="O40" t="n">
-        <v>26648.39</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
+        <v>26466.36</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3883,7 +3879,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3893,63 +3889,67 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26146.12</v>
+        <v>26050.95</v>
       </c>
       <c r="C41" t="n">
-        <v>26187.82</v>
+        <v>26062.15</v>
       </c>
       <c r="D41" t="n">
-        <v>26063.37</v>
+        <v>25914.11</v>
       </c>
       <c r="E41" t="n">
-        <v>26091.33</v>
+        <v>25983.04</v>
       </c>
       <c r="F41" t="n">
-        <v>-37.03</v>
+        <v>-108.29</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0042</v>
       </c>
       <c r="H41" t="n">
-        <v>124.45</v>
+        <v>148.04</v>
       </c>
       <c r="I41" t="n">
-        <v>25946.13</v>
+        <v>25938.92</v>
       </c>
       <c r="J41" t="n">
-        <v>25916.01</v>
+        <v>25949.75</v>
       </c>
       <c r="K41" t="n">
-        <v>26041.65</v>
+        <v>26029.1</v>
       </c>
       <c r="L41" t="n">
-        <v>26167.3</v>
+        <v>26108.46</v>
       </c>
       <c r="M41" t="n">
-        <v>26215.06</v>
+        <v>26153.56</v>
       </c>
       <c r="N41" t="n">
-        <v>26262.83</v>
+        <v>26198.65</v>
       </c>
       <c r="O41" t="n">
-        <v>26466.36</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+        <v>26312.27</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3963,7 +3963,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3973,83 +3973,81 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26050.95</v>
+        <v>25998.95</v>
       </c>
       <c r="C42" t="n">
-        <v>26062.15</v>
+        <v>26166.25</v>
       </c>
       <c r="D42" t="n">
-        <v>25914.11</v>
+        <v>25969.52</v>
       </c>
       <c r="E42" t="n">
-        <v>25983.04</v>
+        <v>26136.56</v>
       </c>
       <c r="F42" t="n">
-        <v>-108.29</v>
+        <v>153.52</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.0059</v>
       </c>
       <c r="H42" t="n">
-        <v>148.04</v>
+        <v>196.73</v>
       </c>
       <c r="I42" t="n">
-        <v>25938.92</v>
+        <v>25766.07</v>
       </c>
       <c r="J42" t="n">
-        <v>25949.75</v>
+        <v>25832.45</v>
       </c>
       <c r="K42" t="n">
-        <v>26029.1</v>
+        <v>25909.02</v>
       </c>
       <c r="L42" t="n">
-        <v>26108.46</v>
+        <v>25985.58</v>
       </c>
       <c r="M42" t="n">
-        <v>26153.56</v>
+        <v>26057.06</v>
       </c>
       <c r="N42" t="n">
-        <v>26198.65</v>
+        <v>26128.53</v>
       </c>
       <c r="O42" t="n">
-        <v>26312.27</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
+        <v>26210.19</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
       <c r="W42" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr"/>
@@ -4057,50 +4055,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25998.95</v>
+        <v>26091.29</v>
       </c>
       <c r="C43" t="n">
-        <v>26166.25</v>
+        <v>26171.7</v>
       </c>
       <c r="D43" t="n">
-        <v>25969.52</v>
+        <v>26038.07</v>
       </c>
       <c r="E43" t="n">
-        <v>26136.56</v>
+        <v>26106.6</v>
       </c>
       <c r="F43" t="n">
-        <v>153.52</v>
+        <v>-29.96</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0011</v>
       </c>
       <c r="H43" t="n">
-        <v>196.73</v>
+        <v>133.63</v>
       </c>
       <c r="I43" t="n">
-        <v>25766.07</v>
+        <v>25772.79</v>
       </c>
       <c r="J43" t="n">
-        <v>25832.45</v>
+        <v>25974.17</v>
       </c>
       <c r="K43" t="n">
-        <v>25909.02</v>
+        <v>26038.2</v>
       </c>
       <c r="L43" t="n">
-        <v>25985.58</v>
+        <v>26102.22</v>
       </c>
       <c r="M43" t="n">
-        <v>26057.06</v>
+        <v>26234.93</v>
       </c>
       <c r="N43" t="n">
-        <v>26128.53</v>
+        <v>26367.63</v>
       </c>
       <c r="O43" t="n">
-        <v>26210.19</v>
+        <v>26362.98</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4108,81 +4106,83 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26091.29</v>
+        <v>26206.01</v>
       </c>
       <c r="C44" t="n">
-        <v>26171.7</v>
+        <v>26341.52</v>
       </c>
       <c r="D44" t="n">
-        <v>26038.07</v>
+        <v>26164.11</v>
       </c>
       <c r="E44" t="n">
-        <v>26106.6</v>
+        <v>26266.14</v>
       </c>
       <c r="F44" t="n">
-        <v>-29.96</v>
+        <v>159.54</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0061</v>
       </c>
       <c r="H44" t="n">
-        <v>133.63</v>
+        <v>177.41</v>
       </c>
       <c r="I44" t="n">
-        <v>25772.79</v>
+        <v>25904.44</v>
       </c>
       <c r="J44" t="n">
-        <v>25974.17</v>
+        <v>25973.83</v>
       </c>
       <c r="K44" t="n">
-        <v>26038.2</v>
+        <v>26039.79</v>
       </c>
       <c r="L44" t="n">
-        <v>26102.22</v>
+        <v>26105.74</v>
       </c>
       <c r="M44" t="n">
-        <v>26234.93</v>
+        <v>26173.41</v>
       </c>
       <c r="N44" t="n">
-        <v>26367.63</v>
+        <v>26241.09</v>
       </c>
       <c r="O44" t="n">
-        <v>26362.98</v>
+        <v>26305.33</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4190,83 +4190,83 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>26206.01</v>
+        <v>26255.41</v>
       </c>
       <c r="C45" t="n">
-        <v>26341.52</v>
+        <v>26466.76</v>
       </c>
       <c r="D45" t="n">
-        <v>26164.11</v>
+        <v>26196.92</v>
       </c>
       <c r="E45" t="n">
-        <v>26266.14</v>
+        <v>26285.96</v>
       </c>
       <c r="F45" t="n">
-        <v>159.54</v>
+        <v>19.82</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0061</v>
+        <v>0.0008</v>
       </c>
       <c r="H45" t="n">
-        <v>177.41</v>
+        <v>269.84</v>
       </c>
       <c r="I45" t="n">
-        <v>25904.44</v>
+        <v>25986.7</v>
       </c>
       <c r="J45" t="n">
-        <v>25973.83</v>
+        <v>26095.39</v>
       </c>
       <c r="K45" t="n">
-        <v>26039.79</v>
+        <v>26177.44</v>
       </c>
       <c r="L45" t="n">
-        <v>26105.74</v>
+        <v>26259.48</v>
       </c>
       <c r="M45" t="n">
-        <v>26173.41</v>
+        <v>26354.85</v>
       </c>
       <c r="N45" t="n">
-        <v>26241.09</v>
+        <v>26450.21</v>
       </c>
       <c r="O45" t="n">
-        <v>26305.33</v>
+        <v>26518.93</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4277,9 +4277,9 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
@@ -4289,15 +4289,13 @@
       </c>
       <c r="U45" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W45" s="9" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4307,50 +4305,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>26255.41</v>
+        <v>26354.37</v>
       </c>
       <c r="C46" t="n">
-        <v>26466.76</v>
+        <v>26402.81</v>
       </c>
       <c r="D46" t="n">
-        <v>26196.92</v>
+        <v>26241.77</v>
       </c>
       <c r="E46" t="n">
-        <v>26285.96</v>
+        <v>26367.24</v>
       </c>
       <c r="F46" t="n">
-        <v>19.82</v>
+        <v>81.28</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0031</v>
       </c>
       <c r="H46" t="n">
-        <v>269.84</v>
+        <v>161.04</v>
       </c>
       <c r="I46" t="n">
-        <v>25986.7</v>
+        <v>25927.08</v>
       </c>
       <c r="J46" t="n">
-        <v>26095.39</v>
+        <v>25993.18</v>
       </c>
       <c r="K46" t="n">
-        <v>26177.44</v>
+        <v>26151.04</v>
       </c>
       <c r="L46" t="n">
-        <v>26259.48</v>
+        <v>26308.9</v>
       </c>
       <c r="M46" t="n">
-        <v>26354.85</v>
+        <v>26420.88</v>
       </c>
       <c r="N46" t="n">
-        <v>26450.21</v>
+        <v>26532.86</v>
       </c>
       <c r="O46" t="n">
-        <v>26518.93</v>
+        <v>26736.6</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4361,78 +4359,80 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>26354.37</v>
+        <v>26494.61</v>
       </c>
       <c r="C47" t="n">
-        <v>26402.81</v>
+        <v>26618.74</v>
       </c>
       <c r="D47" t="n">
-        <v>26241.77</v>
+        <v>26467.36</v>
       </c>
       <c r="E47" t="n">
-        <v>26367.24</v>
+        <v>26569.99</v>
       </c>
       <c r="F47" t="n">
-        <v>81.28</v>
+        <v>202.75</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0077</v>
       </c>
       <c r="H47" t="n">
-        <v>161.04</v>
+        <v>151.38</v>
       </c>
       <c r="I47" t="n">
-        <v>25927.08</v>
+        <v>26080.73</v>
       </c>
       <c r="J47" t="n">
-        <v>25993.18</v>
+        <v>26228.67</v>
       </c>
       <c r="K47" t="n">
-        <v>26151.04</v>
+        <v>26286.72</v>
       </c>
       <c r="L47" t="n">
-        <v>26308.9</v>
+        <v>26344.77</v>
       </c>
       <c r="M47" t="n">
-        <v>26420.88</v>
+        <v>26447.76</v>
       </c>
       <c r="N47" t="n">
-        <v>26532.86</v>
+        <v>26550.76</v>
       </c>
       <c r="O47" t="n">
-        <v>26736.6</v>
+        <v>26563.85</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4443,113 +4443,113 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>26494.61</v>
+        <v>26464.14</v>
       </c>
       <c r="C48" t="n">
-        <v>26618.74</v>
+        <v>26471.79</v>
       </c>
       <c r="D48" t="n">
-        <v>26467.36</v>
+        <v>26249.59</v>
       </c>
       <c r="E48" t="n">
-        <v>26569.99</v>
+        <v>26258.11</v>
       </c>
       <c r="F48" t="n">
-        <v>202.75</v>
+        <v>-311.88</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0117</v>
       </c>
       <c r="H48" t="n">
-        <v>151.38</v>
+        <v>222.2</v>
       </c>
       <c r="I48" t="n">
-        <v>26080.73</v>
+        <v>26315.98</v>
       </c>
       <c r="J48" t="n">
-        <v>26228.67</v>
+        <v>26432.08</v>
       </c>
       <c r="K48" t="n">
-        <v>26286.72</v>
+        <v>26494.3</v>
       </c>
       <c r="L48" t="n">
-        <v>26344.77</v>
+        <v>26556.52</v>
       </c>
       <c r="M48" t="n">
-        <v>26447.76</v>
+        <v>26645.68</v>
       </c>
       <c r="N48" t="n">
-        <v>26550.76</v>
+        <v>26734.84</v>
       </c>
       <c r="O48" t="n">
-        <v>26563.85</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+        <v>26770.12</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr"/>
@@ -4557,67 +4557,67 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>26464.14</v>
+        <v>26150.75</v>
       </c>
       <c r="C49" t="n">
-        <v>26471.79</v>
+        <v>26206.13</v>
       </c>
       <c r="D49" t="n">
-        <v>26249.59</v>
+        <v>25916.76</v>
       </c>
       <c r="E49" t="n">
-        <v>26258.11</v>
+        <v>25970.11</v>
       </c>
       <c r="F49" t="n">
-        <v>-311.88</v>
+        <v>-288</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.011</v>
       </c>
       <c r="H49" t="n">
-        <v>222.2</v>
+        <v>289.37</v>
       </c>
       <c r="I49" t="n">
-        <v>26315.98</v>
+        <v>26027.39</v>
       </c>
       <c r="J49" t="n">
-        <v>26432.08</v>
+        <v>25984.62</v>
       </c>
       <c r="K49" t="n">
-        <v>26494.3</v>
+        <v>26147.01</v>
       </c>
       <c r="L49" t="n">
-        <v>26556.52</v>
+        <v>26309.4</v>
       </c>
       <c r="M49" t="n">
-        <v>26645.68</v>
+        <v>26369.21</v>
       </c>
       <c r="N49" t="n">
-        <v>26734.84</v>
+        <v>26429.02</v>
       </c>
       <c r="O49" t="n">
-        <v>26770.12</v>
+        <v>26693.99</v>
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4631,7 +4631,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4641,67 +4641,63 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>26150.75</v>
+        <v>25886.67</v>
       </c>
       <c r="C50" t="n">
-        <v>26206.13</v>
+        <v>25924.21</v>
       </c>
       <c r="D50" t="n">
-        <v>25916.76</v>
+        <v>25727.93</v>
       </c>
       <c r="E50" t="n">
-        <v>25970.11</v>
+        <v>25839.33</v>
       </c>
       <c r="F50" t="n">
-        <v>-288</v>
+        <v>-130.78</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.005</v>
       </c>
       <c r="H50" t="n">
-        <v>289.37</v>
+        <v>196.28</v>
       </c>
       <c r="I50" t="n">
-        <v>26027.39</v>
+        <v>25627.39</v>
       </c>
       <c r="J50" t="n">
-        <v>25984.62</v>
+        <v>25635.07</v>
       </c>
       <c r="K50" t="n">
-        <v>26147.01</v>
+        <v>25825.42</v>
       </c>
       <c r="L50" t="n">
-        <v>26309.4</v>
+        <v>26015.78</v>
       </c>
       <c r="M50" t="n">
-        <v>26369.21</v>
+        <v>26114.79</v>
       </c>
       <c r="N50" t="n">
-        <v>26429.02</v>
+        <v>26213.81</v>
       </c>
       <c r="O50" t="n">
-        <v>26693.99</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
+        <v>26495.5</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4715,7 +4711,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4725,50 +4721,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25886.67</v>
+        <v>25840.92</v>
       </c>
       <c r="C51" t="n">
-        <v>25924.21</v>
+        <v>26007.79</v>
       </c>
       <c r="D51" t="n">
-        <v>25727.93</v>
+        <v>25784.84</v>
       </c>
       <c r="E51" t="n">
-        <v>25839.33</v>
+        <v>26003.32</v>
       </c>
       <c r="F51" t="n">
-        <v>-130.78</v>
+        <v>163.99</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0063</v>
       </c>
       <c r="H51" t="n">
-        <v>196.28</v>
+        <v>222.95</v>
       </c>
       <c r="I51" t="n">
-        <v>25627.39</v>
+        <v>25531.65</v>
       </c>
       <c r="J51" t="n">
-        <v>25635.07</v>
+        <v>25649.68</v>
       </c>
       <c r="K51" t="n">
-        <v>25825.42</v>
+        <v>25741.19</v>
       </c>
       <c r="L51" t="n">
-        <v>26015.78</v>
+        <v>25832.7</v>
       </c>
       <c r="M51" t="n">
-        <v>26114.79</v>
+        <v>25937.47</v>
       </c>
       <c r="N51" t="n">
-        <v>26213.81</v>
+        <v>26042.24</v>
       </c>
       <c r="O51" t="n">
-        <v>26495.5</v>
+        <v>26120.49</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4776,79 +4772,85 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25840.92</v>
+        <v>25985.86</v>
       </c>
       <c r="C52" t="n">
-        <v>26007.79</v>
+        <v>26167.93</v>
       </c>
       <c r="D52" t="n">
-        <v>25784.84</v>
+        <v>25958.7</v>
       </c>
       <c r="E52" t="n">
-        <v>26003.32</v>
+        <v>26046.4</v>
       </c>
       <c r="F52" t="n">
-        <v>163.99</v>
+        <v>43.08</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0017</v>
       </c>
       <c r="H52" t="n">
-        <v>222.95</v>
+        <v>209.23</v>
       </c>
       <c r="I52" t="n">
-        <v>25531.65</v>
+        <v>25561.89</v>
       </c>
       <c r="J52" t="n">
-        <v>25649.68</v>
+        <v>25833.87</v>
       </c>
       <c r="K52" t="n">
-        <v>25741.19</v>
+        <v>25891.85</v>
       </c>
       <c r="L52" t="n">
-        <v>25832.7</v>
+        <v>25949.82</v>
       </c>
       <c r="M52" t="n">
-        <v>25937.47</v>
+        <v>26114.79</v>
       </c>
       <c r="N52" t="n">
-        <v>26042.24</v>
+        <v>26279.77</v>
       </c>
       <c r="O52" t="n">
-        <v>26120.49</v>
+        <v>26230.74</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4859,25 +4861,23 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4891,50 +4891,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25985.86</v>
+        <v>26039.54</v>
       </c>
       <c r="C53" t="n">
-        <v>26167.93</v>
+        <v>26069.99</v>
       </c>
       <c r="D53" t="n">
-        <v>25958.7</v>
+        <v>25919.61</v>
       </c>
       <c r="E53" t="n">
-        <v>26046.4</v>
+        <v>26006.53</v>
       </c>
       <c r="F53" t="n">
-        <v>43.08</v>
+        <v>-39.87</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0015</v>
       </c>
       <c r="H53" t="n">
-        <v>209.23</v>
+        <v>150.38</v>
       </c>
       <c r="I53" t="n">
-        <v>25561.89</v>
+        <v>25749.47</v>
       </c>
       <c r="J53" t="n">
-        <v>25833.87</v>
+        <v>25828.71</v>
       </c>
       <c r="K53" t="n">
-        <v>25891.85</v>
+        <v>25941.79</v>
       </c>
       <c r="L53" t="n">
-        <v>25949.82</v>
+        <v>26054.86</v>
       </c>
       <c r="M53" t="n">
-        <v>26114.79</v>
+        <v>26151.02</v>
       </c>
       <c r="N53" t="n">
-        <v>26279.77</v>
+        <v>26247.17</v>
       </c>
       <c r="O53" t="n">
-        <v>26230.74</v>
+        <v>26377.16</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4942,18 +4942,18 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4961,70 +4961,68 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>26039.54</v>
+        <v>25897.22</v>
       </c>
       <c r="C54" t="n">
-        <v>26069.99</v>
+        <v>26026.78</v>
       </c>
       <c r="D54" t="n">
-        <v>25919.61</v>
+        <v>25799.66</v>
       </c>
       <c r="E54" t="n">
-        <v>26006.53</v>
+        <v>26007.63</v>
       </c>
       <c r="F54" t="n">
-        <v>-39.87</v>
+        <v>1.1</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>150.38</v>
+        <v>227.12</v>
       </c>
       <c r="I54" t="n">
-        <v>25749.47</v>
+        <v>25769.23</v>
       </c>
       <c r="J54" t="n">
-        <v>25828.71</v>
+        <v>25862.01</v>
       </c>
       <c r="K54" t="n">
-        <v>25941.79</v>
+        <v>25931.34</v>
       </c>
       <c r="L54" t="n">
-        <v>26054.86</v>
+        <v>26000.66</v>
       </c>
       <c r="M54" t="n">
-        <v>26151.02</v>
+        <v>26081.72</v>
       </c>
       <c r="N54" t="n">
-        <v>26247.17</v>
+        <v>26162.77</v>
       </c>
       <c r="O54" t="n">
-        <v>26377.16</v>
+        <v>26220.37</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
@@ -5033,7 +5031,7 @@
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5045,63 +5043,69 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25897.22</v>
+        <v>25870.98</v>
       </c>
       <c r="C55" t="n">
-        <v>26026.78</v>
+        <v>25909.66</v>
       </c>
       <c r="D55" t="n">
-        <v>25799.66</v>
+        <v>25512.39</v>
       </c>
       <c r="E55" t="n">
-        <v>26007.63</v>
+        <v>25576.45</v>
       </c>
       <c r="F55" t="n">
-        <v>1.1</v>
+        <v>-431.18</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0</v>
+        <v>-0.0166</v>
       </c>
       <c r="H55" t="n">
-        <v>227.12</v>
+        <v>397.27</v>
       </c>
       <c r="I55" t="n">
-        <v>25769.23</v>
+        <v>25572.54</v>
       </c>
       <c r="J55" t="n">
-        <v>25862.01</v>
+        <v>25827.72</v>
       </c>
       <c r="K55" t="n">
-        <v>25931.34</v>
+        <v>25894.07</v>
       </c>
       <c r="L55" t="n">
-        <v>26000.66</v>
+        <v>25960.43</v>
       </c>
       <c r="M55" t="n">
-        <v>26081.72</v>
+        <v>26121.19</v>
       </c>
       <c r="N55" t="n">
-        <v>26162.77</v>
+        <v>26281.96</v>
       </c>
       <c r="O55" t="n">
-        <v>26220.37</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
+        <v>26253.9</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q55" s="6" t="inlineStr">
         <is>
@@ -5115,7 +5119,7 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5127,81 +5131,73 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25870.98</v>
+        <v>25555.66</v>
       </c>
       <c r="C56" t="n">
-        <v>25909.66</v>
+        <v>25612.09</v>
       </c>
       <c r="D56" t="n">
-        <v>25512.39</v>
+        <v>25361.15</v>
       </c>
       <c r="E56" t="n">
-        <v>25576.45</v>
+        <v>25361.15</v>
       </c>
       <c r="F56" t="n">
-        <v>-431.18</v>
+        <v>-215.3</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>397.27</v>
+        <v>250.94</v>
       </c>
       <c r="I56" t="n">
-        <v>25572.54</v>
+        <v>25115.12</v>
       </c>
       <c r="J56" t="n">
-        <v>25827.72</v>
+        <v>25111.89</v>
       </c>
       <c r="K56" t="n">
-        <v>25894.07</v>
+        <v>25377.81</v>
       </c>
       <c r="L56" t="n">
-        <v>25960.43</v>
+        <v>25643.74</v>
       </c>
       <c r="M56" t="n">
-        <v>26121.19</v>
+        <v>25775.08</v>
       </c>
       <c r="N56" t="n">
-        <v>26281.96</v>
+        <v>25906.43</v>
       </c>
       <c r="O56" t="n">
-        <v>26253.9</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
+        <v>26306.93</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5215,7 +5211,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5225,50 +5221,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25555.66</v>
+        <v>25478.84</v>
       </c>
       <c r="C57" t="n">
-        <v>25612.09</v>
+        <v>25581.22</v>
       </c>
       <c r="D57" t="n">
-        <v>25361.15</v>
+        <v>25396.38</v>
       </c>
       <c r="E57" t="n">
-        <v>25361.15</v>
+        <v>25568.56</v>
       </c>
       <c r="F57" t="n">
-        <v>-215.3</v>
+        <v>207.41</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>250.94</v>
+        <v>184.84</v>
       </c>
       <c r="I57" t="n">
-        <v>25115.12</v>
+        <v>25110.21</v>
       </c>
       <c r="J57" t="n">
-        <v>25111.89</v>
+        <v>25047.48</v>
       </c>
       <c r="K57" t="n">
-        <v>25377.81</v>
+        <v>25235.68</v>
       </c>
       <c r="L57" t="n">
-        <v>25643.74</v>
+        <v>25423.89</v>
       </c>
       <c r="M57" t="n">
-        <v>25775.08</v>
+        <v>25486.62</v>
       </c>
       <c r="N57" t="n">
-        <v>25906.43</v>
+        <v>25549.35</v>
       </c>
       <c r="O57" t="n">
-        <v>26306.93</v>
+        <v>25863.03</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5276,172 +5272,178 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
       <c r="W57" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>25478.84</v>
+        <v>25498.74</v>
       </c>
       <c r="C58" t="n">
-        <v>25581.22</v>
+        <v>25548.78</v>
       </c>
       <c r="D58" t="n">
-        <v>25396.38</v>
+        <v>25325.52</v>
       </c>
       <c r="E58" t="n">
-        <v>25568.56</v>
+        <v>25440.81</v>
       </c>
       <c r="F58" t="n">
-        <v>207.41</v>
+        <v>-127.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.005</v>
       </c>
       <c r="H58" t="n">
-        <v>184.84</v>
+        <v>223.26</v>
       </c>
       <c r="I58" t="n">
-        <v>25110.21</v>
+        <v>25211.54</v>
       </c>
       <c r="J58" t="n">
-        <v>25047.48</v>
+        <v>25423.6</v>
       </c>
       <c r="K58" t="n">
-        <v>25235.68</v>
+        <v>25476.14</v>
       </c>
       <c r="L58" t="n">
-        <v>25423.89</v>
+        <v>25528.68</v>
       </c>
       <c r="M58" t="n">
-        <v>25486.62</v>
+        <v>25660.98</v>
       </c>
       <c r="N58" t="n">
-        <v>25549.35</v>
+        <v>25793.28</v>
       </c>
       <c r="O58" t="n">
-        <v>25863.03</v>
+        <v>25766.06</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25498.74</v>
+        <v>25360.32</v>
       </c>
       <c r="C59" t="n">
-        <v>25548.78</v>
+        <v>25478.98</v>
       </c>
       <c r="D59" t="n">
-        <v>25325.52</v>
+        <v>25172.89</v>
       </c>
       <c r="E59" t="n">
-        <v>25440.81</v>
+        <v>25402.28</v>
       </c>
       <c r="F59" t="n">
-        <v>-127.75</v>
+        <v>-38.53</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.005</v>
+        <v>-0.0015</v>
       </c>
       <c r="H59" t="n">
-        <v>223.26</v>
+        <v>306.09</v>
       </c>
       <c r="I59" t="n">
-        <v>25211.54</v>
+        <v>25102.26</v>
       </c>
       <c r="J59" t="n">
-        <v>25423.6</v>
+        <v>25219.38</v>
       </c>
       <c r="K59" t="n">
-        <v>25476.14</v>
+        <v>25329.18</v>
       </c>
       <c r="L59" t="n">
-        <v>25528.68</v>
+        <v>25438.98</v>
       </c>
       <c r="M59" t="n">
-        <v>25660.98</v>
+        <v>25552.44</v>
       </c>
       <c r="N59" t="n">
-        <v>25793.28</v>
+        <v>25665.9</v>
       </c>
       <c r="O59" t="n">
-        <v>25766.06</v>
+        <v>25772.04</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
       <c r="Q59" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
@@ -5449,9 +5451,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5463,7 +5465,7 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="9" t="inlineStr">
+      <c r="W59" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5477,71 +5479,69 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25360.32</v>
+        <v>25515.96</v>
       </c>
       <c r="C60" t="n">
-        <v>25478.98</v>
+        <v>25599.07</v>
       </c>
       <c r="D60" t="n">
-        <v>25172.89</v>
+        <v>25361.7</v>
       </c>
       <c r="E60" t="n">
-        <v>25402.28</v>
+        <v>25537.75</v>
       </c>
       <c r="F60" t="n">
-        <v>-38.53</v>
+        <v>135.47</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0053</v>
       </c>
       <c r="H60" t="n">
-        <v>306.09</v>
+        <v>237.37</v>
       </c>
       <c r="I60" t="n">
-        <v>25102.26</v>
+        <v>24866.8</v>
       </c>
       <c r="J60" t="n">
-        <v>25219.38</v>
+        <v>25134.36</v>
       </c>
       <c r="K60" t="n">
-        <v>25329.18</v>
+        <v>25249.23</v>
       </c>
       <c r="L60" t="n">
-        <v>25438.98</v>
+        <v>25364.11</v>
       </c>
       <c r="M60" t="n">
-        <v>25552.44</v>
+        <v>25555.32</v>
       </c>
       <c r="N60" t="n">
-        <v>25665.9</v>
+        <v>25746.54</v>
       </c>
       <c r="O60" t="n">
-        <v>25772.04</v>
+        <v>25785.07</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5549,64 +5549,60 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
+      <c r="W60" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>25515.96</v>
+        <v>25681.6</v>
       </c>
       <c r="C61" t="n">
-        <v>25599.07</v>
+        <v>25800.62</v>
       </c>
       <c r="D61" t="n">
-        <v>25361.7</v>
+        <v>25596.05</v>
       </c>
       <c r="E61" t="n">
-        <v>25537.75</v>
+        <v>25716.71</v>
       </c>
       <c r="F61" t="n">
-        <v>135.47</v>
+        <v>178.96</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0053</v>
+        <v>0.007</v>
       </c>
       <c r="H61" t="n">
-        <v>237.37</v>
+        <v>204.57</v>
       </c>
       <c r="I61" t="n">
-        <v>24866.8</v>
+        <v>25124.33</v>
       </c>
       <c r="J61" t="n">
-        <v>25134.36</v>
+        <v>25329.06</v>
       </c>
       <c r="K61" t="n">
-        <v>25249.23</v>
+        <v>25419.06</v>
       </c>
       <c r="L61" t="n">
-        <v>25364.11</v>
+        <v>25509.07</v>
       </c>
       <c r="M61" t="n">
-        <v>25555.32</v>
+        <v>25656.44</v>
       </c>
       <c r="N61" t="n">
-        <v>25746.54</v>
+        <v>25803.8</v>
       </c>
       <c r="O61" t="n">
-        <v>25785.07</v>
+        <v>25836.44</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5617,7 +5613,7 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="7" t="inlineStr">
+      <c r="S61" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5633,7 +5629,7 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="9" t="inlineStr">
+      <c r="W61" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5643,69 +5639,73 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>25681.6</v>
+        <v>25596.46</v>
       </c>
       <c r="C62" t="n">
-        <v>25800.62</v>
+        <v>25656.22</v>
       </c>
       <c r="D62" t="n">
-        <v>25596.05</v>
+        <v>25285.9</v>
       </c>
       <c r="E62" t="n">
-        <v>25716.71</v>
+        <v>25304.06</v>
       </c>
       <c r="F62" t="n">
-        <v>178.96</v>
+        <v>-412.65</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.007</v>
+        <v>-0.016</v>
       </c>
       <c r="H62" t="n">
-        <v>204.57</v>
+        <v>370.32</v>
       </c>
       <c r="I62" t="n">
-        <v>25124.33</v>
+        <v>25391.48</v>
       </c>
       <c r="J62" t="n">
-        <v>25329.06</v>
+        <v>25521.33</v>
       </c>
       <c r="K62" t="n">
-        <v>25419.06</v>
+        <v>25614.43</v>
       </c>
       <c r="L62" t="n">
-        <v>25509.07</v>
+        <v>25707.52</v>
       </c>
       <c r="M62" t="n">
-        <v>25656.44</v>
+        <v>25819</v>
       </c>
       <c r="N62" t="n">
-        <v>25803.8</v>
+        <v>25930.47</v>
       </c>
       <c r="O62" t="n">
-        <v>25836.44</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+        <v>26005.19</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="W62" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X62" t="inlineStr"/>
@@ -5723,147 +5723,153 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>25596.46</v>
+        <v>25491.35</v>
       </c>
       <c r="C63" t="n">
-        <v>25656.22</v>
+        <v>25617.99</v>
       </c>
       <c r="D63" t="n">
-        <v>25285.9</v>
+        <v>25434.16</v>
       </c>
       <c r="E63" t="n">
-        <v>25304.06</v>
+        <v>25575.01</v>
       </c>
       <c r="F63" t="n">
-        <v>-412.65</v>
+        <v>270.95</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.016</v>
+        <v>0.0107</v>
       </c>
       <c r="H63" t="n">
-        <v>370.32</v>
+        <v>183.83</v>
       </c>
       <c r="I63" t="n">
-        <v>25391.48</v>
+        <v>24915.58</v>
       </c>
       <c r="J63" t="n">
-        <v>25521.33</v>
+        <v>24850.24</v>
       </c>
       <c r="K63" t="n">
-        <v>25614.43</v>
+        <v>25118.9</v>
       </c>
       <c r="L63" t="n">
-        <v>25707.52</v>
+        <v>25387.56</v>
       </c>
       <c r="M63" t="n">
-        <v>25819</v>
+        <v>25489.22</v>
       </c>
       <c r="N63" t="n">
-        <v>25930.47</v>
+        <v>25590.88</v>
       </c>
       <c r="O63" t="n">
-        <v>26005.19</v>
-      </c>
-      <c r="P63" s="6" t="inlineStr">
+        <v>26026.54</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
       <c r="V63" s="8" t="n">
         <v/>
       </c>
-      <c r="W63" s="11" t="inlineStr">
+      <c r="W63" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>25491.35</v>
+        <v>25592.98</v>
       </c>
       <c r="C64" t="n">
-        <v>25617.99</v>
+        <v>25783.16</v>
       </c>
       <c r="D64" t="n">
-        <v>25434.16</v>
+        <v>25423.07</v>
       </c>
       <c r="E64" t="n">
-        <v>25575.01</v>
+        <v/>
       </c>
       <c r="F64" t="n">
-        <v>270.95</v>
+        <v/>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0107</v>
+        <v/>
       </c>
       <c r="H64" t="n">
-        <v>183.83</v>
+        <v>360.09</v>
       </c>
       <c r="I64" t="n">
-        <v>24915.58</v>
+        <v>25250.33</v>
       </c>
       <c r="J64" t="n">
-        <v>24850.24</v>
+        <v>25415.65</v>
       </c>
       <c r="K64" t="n">
-        <v>25118.9</v>
+        <v>25483.09</v>
       </c>
       <c r="L64" t="n">
-        <v>25387.56</v>
+        <v>25550.54</v>
       </c>
       <c r="M64" t="n">
-        <v>25489.22</v>
+        <v>25666.92</v>
       </c>
       <c r="N64" t="n">
-        <v>25590.88</v>
+        <v>25783.31</v>
       </c>
       <c r="O64" t="n">
-        <v>26026.54</v>
-      </c>
-      <c r="P64" s="6" t="n">
-        <v/>
+        <v>25801.82</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q64" s="6" t="n">
         <v/>
       </c>
-      <c r="R64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S64" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T64" s="8" t="inlineStr">
@@ -5871,108 +5877,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U64" s="8" t="n">
+        <v/>
       </c>
       <c r="V64" s="8" t="n">
         <v/>
       </c>
-      <c r="W64" s="11" t="inlineStr">
+      <c r="W64" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>25592.98</v>
-      </c>
-      <c r="C65" t="n">
-        <v>25783.16</v>
-      </c>
-      <c r="D65" t="n">
-        <v>25423.07</v>
-      </c>
-      <c r="E65" t="n">
-        <v/>
-      </c>
-      <c r="F65" t="n">
-        <v/>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H65" t="n">
-        <v>360.09</v>
-      </c>
-      <c r="I65" t="n">
-        <v>25250.33</v>
-      </c>
-      <c r="J65" t="n">
-        <v>25415.65</v>
-      </c>
-      <c r="K65" t="n">
-        <v>25483.09</v>
-      </c>
-      <c r="L65" t="n">
-        <v>25550.54</v>
-      </c>
-      <c r="M65" t="n">
-        <v>25666.92</v>
-      </c>
-      <c r="N65" t="n">
-        <v>25783.31</v>
-      </c>
-      <c r="O65" t="n">
-        <v>25801.82</v>
-      </c>
-      <c r="P65" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R65" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S65" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W65" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5809,29 +5806,29 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>25592.98</v>
+        <v>25724.13</v>
       </c>
       <c r="C64" t="n">
-        <v>25783.16</v>
+        <v>25729.05</v>
       </c>
       <c r="D64" t="n">
-        <v>25423.07</v>
+        <v>25365.21</v>
       </c>
       <c r="E64" t="n">
-        <v/>
+        <v>25445.63</v>
       </c>
       <c r="F64" t="n">
-        <v/>
+        <v>-129.38</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v/>
+        <v>-0.0051</v>
       </c>
       <c r="H64" t="n">
-        <v>360.09</v>
+        <v>363.84</v>
       </c>
       <c r="I64" t="n">
         <v>25250.33</v>
@@ -5854,22 +5851,22 @@
       <c r="O64" t="n">
         <v>25801.82</v>
       </c>
-      <c r="P64" s="6" t="inlineStr">
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
       <c r="R64" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S64" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T64" s="8" t="inlineStr">

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5819,13 +5822,13 @@
         <v>25365.21</v>
       </c>
       <c r="E64" t="n">
-        <v>25445.63</v>
+        <v/>
       </c>
       <c r="F64" t="n">
-        <v>-129.38</v>
+        <v/>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0051</v>
+        <v/>
       </c>
       <c r="H64" t="n">
         <v>363.84</v>
@@ -5851,12 +5854,14 @@
       <c r="O64" t="n">
         <v>25801.82</v>
       </c>
-      <c r="P64" s="6" t="n">
-        <v/>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q64" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
@@ -5864,9 +5869,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S64" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T64" s="8" t="inlineStr">

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -637,67 +637,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24848.51</v>
+        <v>24724.34</v>
       </c>
       <c r="C2" t="n">
-        <v>24869.63</v>
+        <v>24762.24</v>
       </c>
       <c r="D2" t="n">
-        <v>24547.7</v>
+        <v>24556.78</v>
       </c>
       <c r="E2" t="n">
-        <v>24671.22</v>
+        <v>24626.89</v>
       </c>
       <c r="F2" t="n">
-        <v>-323.61</v>
+        <v>-44.33</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0018</v>
       </c>
       <c r="H2" t="n">
-        <v>321.93</v>
+        <v>205.46</v>
       </c>
       <c r="I2" t="n">
-        <v>24435.16</v>
+        <v>24225.77</v>
       </c>
       <c r="J2" t="n">
-        <v>24703.19</v>
+        <v>24330.57</v>
       </c>
       <c r="K2" t="n">
-        <v>24831.55</v>
+        <v>24510.25</v>
       </c>
       <c r="L2" t="n">
-        <v>24959.92</v>
+        <v>24689.94</v>
       </c>
       <c r="M2" t="n">
-        <v>25158.11</v>
+        <v>24832.19</v>
       </c>
       <c r="N2" t="n">
-        <v>25356.3</v>
+        <v>24974.43</v>
       </c>
       <c r="O2" t="n">
-        <v>25414.84</v>
+        <v>25191.56</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -711,58 +707,62 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24724.34</v>
+        <v>24815.22</v>
       </c>
       <c r="C3" t="n">
-        <v>24762.24</v>
+        <v>25024.27</v>
       </c>
       <c r="D3" t="n">
-        <v>24556.78</v>
+        <v>24794.84</v>
       </c>
       <c r="E3" t="n">
-        <v>24626.89</v>
+        <v>24995.81</v>
       </c>
       <c r="F3" t="n">
-        <v>-44.33</v>
+        <v>368.92</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.015</v>
       </c>
       <c r="H3" t="n">
-        <v>205.46</v>
+        <v>229.43</v>
       </c>
       <c r="I3" t="n">
-        <v>24225.77</v>
+        <v>24351.32</v>
       </c>
       <c r="J3" t="n">
-        <v>24330.57</v>
+        <v>24405.12</v>
       </c>
       <c r="K3" t="n">
-        <v>24510.25</v>
+        <v>24524.16</v>
       </c>
       <c r="L3" t="n">
-        <v>24689.94</v>
+        <v>24643.2</v>
       </c>
       <c r="M3" t="n">
-        <v>24832.19</v>
+        <v>24729.62</v>
       </c>
       <c r="N3" t="n">
-        <v>24974.43</v>
+        <v>24816.04</v>
       </c>
       <c r="O3" t="n">
-        <v>25191.56</v>
+        <v>24967.7</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -773,78 +773,80 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24815.22</v>
+        <v>25028.93</v>
       </c>
       <c r="C4" t="n">
-        <v>25024.27</v>
+        <v>25095.66</v>
       </c>
       <c r="D4" t="n">
-        <v>24794.84</v>
+        <v>24887</v>
       </c>
       <c r="E4" t="n">
-        <v>24995.81</v>
+        <v>25040.28</v>
       </c>
       <c r="F4" t="n">
-        <v>368.92</v>
+        <v>44.47</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.015</v>
+        <v>0.0018</v>
       </c>
       <c r="H4" t="n">
-        <v>229.43</v>
+        <v>208.66</v>
       </c>
       <c r="I4" t="n">
-        <v>24351.32</v>
+        <v>24565.41</v>
       </c>
       <c r="J4" t="n">
-        <v>24405.12</v>
+        <v>24809.51</v>
       </c>
       <c r="K4" t="n">
-        <v>24524.16</v>
+        <v>24881.1</v>
       </c>
       <c r="L4" t="n">
-        <v>24643.2</v>
+        <v>24952.68</v>
       </c>
       <c r="M4" t="n">
-        <v>24729.62</v>
+        <v>25110.53</v>
       </c>
       <c r="N4" t="n">
-        <v>24816.04</v>
+        <v>25268.37</v>
       </c>
       <c r="O4" t="n">
-        <v>24967.7</v>
+        <v>25253.7</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -862,20 +864,16 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -885,50 +883,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25028.93</v>
+        <v>25025.13</v>
       </c>
       <c r="C5" t="n">
-        <v>25095.66</v>
+        <v>25655.82</v>
       </c>
       <c r="D5" t="n">
-        <v>24887</v>
+        <v>24994.64</v>
       </c>
       <c r="E5" t="n">
-        <v>25040.28</v>
+        <v>25580.88</v>
       </c>
       <c r="F5" t="n">
-        <v>44.47</v>
+        <v>540.6</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0216</v>
       </c>
       <c r="H5" t="n">
-        <v>208.66</v>
+        <v>661.1799999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>24565.41</v>
+        <v>24678.34</v>
       </c>
       <c r="J5" t="n">
-        <v>24809.51</v>
+        <v>24856.09</v>
       </c>
       <c r="K5" t="n">
-        <v>24881.1</v>
+        <v>24935.95</v>
       </c>
       <c r="L5" t="n">
-        <v>24952.68</v>
+        <v>25015.8</v>
       </c>
       <c r="M5" t="n">
-        <v>25110.53</v>
+        <v>25144.61</v>
       </c>
       <c r="N5" t="n">
-        <v>25268.37</v>
+        <v>25273.41</v>
       </c>
       <c r="O5" t="n">
-        <v>25253.7</v>
+        <v>25304.32</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -946,16 +944,20 @@
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -965,50 +967,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25025.13</v>
+        <v>25763.97</v>
       </c>
       <c r="C6" t="n">
-        <v>25655.82</v>
+        <v>25826.78</v>
       </c>
       <c r="D6" t="n">
-        <v>24994.64</v>
+        <v>25611.69</v>
       </c>
       <c r="E6" t="n">
-        <v>25580.88</v>
+        <v>25779.31</v>
       </c>
       <c r="F6" t="n">
-        <v>540.6</v>
+        <v>198.43</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0216</v>
+        <v>0.0078</v>
       </c>
       <c r="H6" t="n">
-        <v>661.1799999999999</v>
+        <v>215.09</v>
       </c>
       <c r="I6" t="n">
-        <v>24678.34</v>
+        <v>24333.46</v>
       </c>
       <c r="J6" t="n">
-        <v>24856.09</v>
+        <v>25047.53</v>
       </c>
       <c r="K6" t="n">
-        <v>24935.95</v>
+        <v>25250.29</v>
       </c>
       <c r="L6" t="n">
-        <v>25015.8</v>
+        <v>25453.06</v>
       </c>
       <c r="M6" t="n">
-        <v>25144.61</v>
+        <v>25911.47</v>
       </c>
       <c r="N6" t="n">
-        <v>25273.41</v>
+        <v>26369.89</v>
       </c>
       <c r="O6" t="n">
-        <v>25304.32</v>
+        <v>26317</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1026,20 +1028,16 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1049,50 +1047,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25763.97</v>
+        <v>25811.9</v>
       </c>
       <c r="C7" t="n">
-        <v>25826.78</v>
+        <v>25900.1</v>
       </c>
       <c r="D7" t="n">
-        <v>25611.69</v>
+        <v>25698.56</v>
       </c>
       <c r="E7" t="n">
-        <v>25779.31</v>
+        <v>25817.89</v>
       </c>
       <c r="F7" t="n">
-        <v>198.43</v>
+        <v>38.58</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0078</v>
+        <v>0.0015</v>
       </c>
       <c r="H7" t="n">
-        <v>215.09</v>
+        <v>201.54</v>
       </c>
       <c r="I7" t="n">
-        <v>24333.46</v>
+        <v>25396.6</v>
       </c>
       <c r="J7" t="n">
-        <v>25047.53</v>
+        <v>25594.26</v>
       </c>
       <c r="K7" t="n">
-        <v>25250.29</v>
+        <v>25671.77</v>
       </c>
       <c r="L7" t="n">
-        <v>25453.06</v>
+        <v>25749.27</v>
       </c>
       <c r="M7" t="n">
-        <v>25911.47</v>
+        <v>25886.86</v>
       </c>
       <c r="N7" t="n">
-        <v>26369.89</v>
+        <v>26024.44</v>
       </c>
       <c r="O7" t="n">
-        <v>26317</v>
+        <v>26041.87</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1105,12 +1103,12 @@
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U7" s="8" t="n">
@@ -1119,7 +1117,7 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1129,69 +1127,73 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25811.9</v>
+        <v>25770.45</v>
       </c>
       <c r="C8" t="n">
-        <v>25900.1</v>
+        <v>25811.97</v>
       </c>
       <c r="D8" t="n">
-        <v>25698.56</v>
+        <v>25465.12</v>
       </c>
       <c r="E8" t="n">
-        <v>25817.89</v>
+        <v>25465.25</v>
       </c>
       <c r="F8" t="n">
-        <v>38.58</v>
+        <v>-352.64</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0137</v>
       </c>
       <c r="H8" t="n">
-        <v>201.54</v>
+        <v>346.85</v>
       </c>
       <c r="I8" t="n">
-        <v>25396.6</v>
+        <v>25497.02</v>
       </c>
       <c r="J8" t="n">
-        <v>25594.26</v>
+        <v>25625.63</v>
       </c>
       <c r="K8" t="n">
-        <v>25671.77</v>
+        <v>25717.12</v>
       </c>
       <c r="L8" t="n">
-        <v>25749.27</v>
+        <v>25808.61</v>
       </c>
       <c r="M8" t="n">
-        <v>25886.86</v>
+        <v>25918.66</v>
       </c>
       <c r="N8" t="n">
-        <v>26024.44</v>
+        <v>26028.71</v>
       </c>
       <c r="O8" t="n">
-        <v>26041.87</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>26101.64</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1201,7 +1203,7 @@
       </c>
       <c r="W8" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
@@ -1209,61 +1211,61 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25770.45</v>
+        <v>25274.94</v>
       </c>
       <c r="C9" t="n">
-        <v>25811.97</v>
+        <v>25280.16</v>
       </c>
       <c r="D9" t="n">
-        <v>25465.12</v>
+        <v>24830.17</v>
       </c>
       <c r="E9" t="n">
-        <v>25465.25</v>
+        <v>24897.45</v>
       </c>
       <c r="F9" t="n">
-        <v>-352.64</v>
+        <v>-567.8</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0223</v>
       </c>
       <c r="H9" t="n">
-        <v>346.85</v>
+        <v>449.99</v>
       </c>
       <c r="I9" t="n">
-        <v>25497.02</v>
+        <v>25118.27</v>
       </c>
       <c r="J9" t="n">
-        <v>25625.63</v>
+        <v>25031.75</v>
       </c>
       <c r="K9" t="n">
-        <v>25717.12</v>
+        <v>25291.82</v>
       </c>
       <c r="L9" t="n">
-        <v>25808.61</v>
+        <v>25551.9</v>
       </c>
       <c r="M9" t="n">
-        <v>25918.66</v>
+        <v>25638.68</v>
       </c>
       <c r="N9" t="n">
-        <v>26028.71</v>
+        <v>25725.45</v>
       </c>
       <c r="O9" t="n">
-        <v>26101.64</v>
+        <v>26158.82</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -1283,7 +1285,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1293,134 +1295,134 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25274.94</v>
+        <v>25097.48</v>
       </c>
       <c r="C10" t="n">
-        <v>25280.16</v>
+        <v>25127.76</v>
       </c>
       <c r="D10" t="n">
-        <v>24830.17</v>
+        <v>24867.32</v>
       </c>
       <c r="E10" t="n">
-        <v>24897.45</v>
+        <v>25118.27</v>
       </c>
       <c r="F10" t="n">
-        <v>-567.8</v>
+        <v>220.82</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0089</v>
       </c>
       <c r="H10" t="n">
-        <v>449.99</v>
+        <v>260.44</v>
       </c>
       <c r="I10" t="n">
-        <v>25118.27</v>
+        <v>24380.18</v>
       </c>
       <c r="J10" t="n">
-        <v>25031.75</v>
+        <v>24368.6</v>
       </c>
       <c r="K10" t="n">
-        <v>25291.82</v>
+        <v>24672.45</v>
       </c>
       <c r="L10" t="n">
-        <v>25551.9</v>
+        <v>24976.31</v>
       </c>
       <c r="M10" t="n">
-        <v>25638.68</v>
+        <v>25122.44</v>
       </c>
       <c r="N10" t="n">
-        <v>25725.45</v>
+        <v>25268.58</v>
       </c>
       <c r="O10" t="n">
-        <v>26158.82</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
+        <v>25730.15</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25097.48</v>
+        <v>25081.19</v>
       </c>
       <c r="C11" t="n">
-        <v>25127.76</v>
+        <v>25195.83</v>
       </c>
       <c r="D11" t="n">
-        <v>24867.32</v>
+        <v>24937.52</v>
       </c>
       <c r="E11" t="n">
-        <v>25118.27</v>
+        <v>25067.09</v>
       </c>
       <c r="F11" t="n">
-        <v>220.82</v>
+        <v>-51.18</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.002</v>
       </c>
       <c r="H11" t="n">
-        <v>260.44</v>
+        <v>258.31</v>
       </c>
       <c r="I11" t="n">
-        <v>24380.18</v>
+        <v>24606.88</v>
       </c>
       <c r="J11" t="n">
-        <v>24368.6</v>
+        <v>24918.19</v>
       </c>
       <c r="K11" t="n">
-        <v>24672.45</v>
+        <v>24988.05</v>
       </c>
       <c r="L11" t="n">
-        <v>24976.31</v>
+        <v>25057.9</v>
       </c>
       <c r="M11" t="n">
-        <v>25122.44</v>
+        <v>25248.49</v>
       </c>
       <c r="N11" t="n">
-        <v>25268.58</v>
+        <v>25439.07</v>
       </c>
       <c r="O11" t="n">
-        <v>25730.15</v>
+        <v>25388.2</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1428,18 +1430,18 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1447,7 +1449,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1461,50 +1463,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25081.19</v>
+        <v>24963.8</v>
       </c>
       <c r="C12" t="n">
-        <v>25195.83</v>
+        <v>25154.58</v>
       </c>
       <c r="D12" t="n">
-        <v>24937.52</v>
+        <v>24963.8</v>
       </c>
       <c r="E12" t="n">
-        <v>25067.09</v>
+        <v>25114.25</v>
       </c>
       <c r="F12" t="n">
-        <v>-51.18</v>
+        <v>47.16</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="H12" t="n">
-        <v>258.31</v>
+        <v>190.78</v>
       </c>
       <c r="I12" t="n">
-        <v>24606.88</v>
+        <v>24679.21</v>
       </c>
       <c r="J12" t="n">
-        <v>24918.19</v>
+        <v>24808.99</v>
       </c>
       <c r="K12" t="n">
-        <v>24988.05</v>
+        <v>24937.93</v>
       </c>
       <c r="L12" t="n">
-        <v>25057.9</v>
+        <v>25066.88</v>
       </c>
       <c r="M12" t="n">
-        <v>25248.49</v>
+        <v>25196.25</v>
       </c>
       <c r="N12" t="n">
-        <v>25439.07</v>
+        <v>25325.61</v>
       </c>
       <c r="O12" t="n">
-        <v>25388.2</v>
+        <v>25454.14</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1512,10 +1514,8 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R12" s="6" t="n">
+        <v/>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1545,59 +1545,63 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24963.8</v>
+        <v>24932.62</v>
       </c>
       <c r="C13" t="n">
-        <v>25154.58</v>
+        <v>25204.68</v>
       </c>
       <c r="D13" t="n">
-        <v>24963.8</v>
+        <v>24869.25</v>
       </c>
       <c r="E13" t="n">
-        <v>25114.25</v>
+        <v>25147.03</v>
       </c>
       <c r="F13" t="n">
-        <v>47.16</v>
+        <v>32.78</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0013</v>
       </c>
       <c r="H13" t="n">
-        <v>190.78</v>
+        <v>335.43</v>
       </c>
       <c r="I13" t="n">
-        <v>24679.21</v>
+        <v>24773.02</v>
       </c>
       <c r="J13" t="n">
-        <v>24808.99</v>
+        <v>24951</v>
       </c>
       <c r="K13" t="n">
-        <v>24937.93</v>
+        <v>25018.86</v>
       </c>
       <c r="L13" t="n">
-        <v>25066.88</v>
+        <v>25086.72</v>
       </c>
       <c r="M13" t="n">
-        <v>25196.25</v>
+        <v>25209.64</v>
       </c>
       <c r="N13" t="n">
-        <v>25325.61</v>
+        <v>25332.56</v>
       </c>
       <c r="O13" t="n">
-        <v>25454.14</v>
+        <v>25345.36</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
@@ -1613,7 +1617,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1627,50 +1631,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24932.62</v>
+        <v>24970.05</v>
       </c>
       <c r="C14" t="n">
-        <v>25204.68</v>
+        <v>25055.48</v>
       </c>
       <c r="D14" t="n">
-        <v>24869.25</v>
+        <v>24839.23</v>
       </c>
       <c r="E14" t="n">
-        <v>25147.03</v>
+        <v>24999.53</v>
       </c>
       <c r="F14" t="n">
-        <v>32.78</v>
+        <v>-147.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0059</v>
       </c>
       <c r="H14" t="n">
-        <v>335.43</v>
+        <v>216.25</v>
       </c>
       <c r="I14" t="n">
-        <v>24773.02</v>
+        <v>24533.82</v>
       </c>
       <c r="J14" t="n">
-        <v>24951</v>
+        <v>24866.63</v>
       </c>
       <c r="K14" t="n">
-        <v>25018.86</v>
+        <v>24979.31</v>
       </c>
       <c r="L14" t="n">
-        <v>25086.72</v>
+        <v>25092</v>
       </c>
       <c r="M14" t="n">
-        <v>25209.64</v>
+        <v>25314.74</v>
       </c>
       <c r="N14" t="n">
-        <v>25332.56</v>
+        <v>25537.49</v>
       </c>
       <c r="O14" t="n">
-        <v>25345.36</v>
+        <v>25540.11</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1682,12 +1686,12 @@
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1699,64 +1703,60 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24970.05</v>
+        <v>25018.95</v>
       </c>
       <c r="C15" t="n">
-        <v>25055.48</v>
+        <v>25021.51</v>
       </c>
       <c r="D15" t="n">
-        <v>24839.23</v>
+        <v>24696.17</v>
       </c>
       <c r="E15" t="n">
-        <v>24999.53</v>
+        <v>24915.49</v>
       </c>
       <c r="F15" t="n">
-        <v>-147.5</v>
+        <v>-84.04000000000001</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0059</v>
+        <v>-0.0034</v>
       </c>
       <c r="H15" t="n">
-        <v>216.25</v>
+        <v>325.34</v>
       </c>
       <c r="I15" t="n">
-        <v>24533.82</v>
+        <v>24622.98</v>
       </c>
       <c r="J15" t="n">
-        <v>24866.63</v>
+        <v>24809.37</v>
       </c>
       <c r="K15" t="n">
-        <v>24979.31</v>
+        <v>24891.4</v>
       </c>
       <c r="L15" t="n">
-        <v>25092</v>
+        <v>24973.44</v>
       </c>
       <c r="M15" t="n">
-        <v>25314.74</v>
+        <v>25107.65</v>
       </c>
       <c r="N15" t="n">
-        <v>25537.49</v>
+        <v>25241.87</v>
       </c>
       <c r="O15" t="n">
-        <v>25540.11</v>
+        <v>25271.73</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1785,7 +1785,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1795,67 +1795,65 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25018.95</v>
+        <v>24755.09</v>
       </c>
       <c r="C16" t="n">
-        <v>25021.51</v>
+        <v>24850.75</v>
       </c>
       <c r="D16" t="n">
-        <v>24696.17</v>
+        <v>24651.34</v>
       </c>
       <c r="E16" t="n">
-        <v>24915.49</v>
+        <v>24830.98</v>
       </c>
       <c r="F16" t="n">
-        <v>-84.04000000000001</v>
+        <v>-84.51000000000001</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>-0.0034</v>
       </c>
       <c r="H16" t="n">
-        <v>325.34</v>
+        <v>199.41</v>
       </c>
       <c r="I16" t="n">
-        <v>24622.98</v>
+        <v>24370.83</v>
       </c>
       <c r="J16" t="n">
-        <v>24809.37</v>
+        <v>24618.48</v>
       </c>
       <c r="K16" t="n">
-        <v>24891.4</v>
+        <v>24752.82</v>
       </c>
       <c r="L16" t="n">
-        <v>24973.44</v>
+        <v>24887.17</v>
       </c>
       <c r="M16" t="n">
-        <v>25107.65</v>
+        <v>25078.16</v>
       </c>
       <c r="N16" t="n">
-        <v>25241.87</v>
+        <v>25269.16</v>
       </c>
       <c r="O16" t="n">
-        <v>25271.73</v>
+        <v>25346.85</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q16" s="6" t="n">
+        <v/>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1867,7 +1865,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1877,50 +1875,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24755.09</v>
+        <v>24769.15</v>
       </c>
       <c r="C17" t="n">
-        <v>24850.75</v>
+        <v>24974.53</v>
       </c>
       <c r="D17" t="n">
-        <v>24651.34</v>
+        <v>24751.13</v>
       </c>
       <c r="E17" t="n">
-        <v>24830.98</v>
+        <v>24846.69</v>
       </c>
       <c r="F17" t="n">
-        <v>-84.51000000000001</v>
+        <v>15.71</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>199.41</v>
+        <v>223.4</v>
       </c>
       <c r="I17" t="n">
-        <v>24370.83</v>
+        <v>24451.93</v>
       </c>
       <c r="J17" t="n">
-        <v>24618.48</v>
+        <v>24671.54</v>
       </c>
       <c r="K17" t="n">
-        <v>24752.82</v>
+        <v>24731.28</v>
       </c>
       <c r="L17" t="n">
-        <v>24887.17</v>
+        <v>24791.01</v>
       </c>
       <c r="M17" t="n">
-        <v>25078.16</v>
+        <v>24930.69</v>
       </c>
       <c r="N17" t="n">
-        <v>25269.16</v>
+        <v>25070.36</v>
       </c>
       <c r="O17" t="n">
-        <v>25346.85</v>
+        <v>25050.16</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1928,18 +1926,18 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1947,60 +1945,64 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24769.15</v>
+        <v>24922.1</v>
       </c>
       <c r="C18" t="n">
-        <v>24974.53</v>
+        <v>25011.35</v>
       </c>
       <c r="D18" t="n">
-        <v>24751.13</v>
+        <v>24817.34</v>
       </c>
       <c r="E18" t="n">
-        <v>24846.69</v>
+        <v>25011.35</v>
       </c>
       <c r="F18" t="n">
-        <v>15.71</v>
+        <v>164.66</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0066</v>
       </c>
       <c r="H18" t="n">
-        <v>223.4</v>
+        <v>194.01</v>
       </c>
       <c r="I18" t="n">
-        <v>24451.93</v>
+        <v>24527.73</v>
       </c>
       <c r="J18" t="n">
-        <v>24671.54</v>
+        <v>24615.22</v>
       </c>
       <c r="K18" t="n">
-        <v>24731.28</v>
+        <v>24734.99</v>
       </c>
       <c r="L18" t="n">
-        <v>24791.01</v>
+        <v>24854.76</v>
       </c>
       <c r="M18" t="n">
-        <v>24930.69</v>
+        <v>24958.39</v>
       </c>
       <c r="N18" t="n">
-        <v>25070.36</v>
+        <v>25062.02</v>
       </c>
       <c r="O18" t="n">
-        <v>25050.16</v>
+        <v>25197.93</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2013,7 +2015,7 @@
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
@@ -2021,13 +2023,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2041,50 +2045,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24922.1</v>
+        <v>25001.31</v>
       </c>
       <c r="C19" t="n">
-        <v>25011.35</v>
+        <v>25271.34</v>
       </c>
       <c r="D19" t="n">
-        <v>24817.34</v>
+        <v>24984.27</v>
       </c>
       <c r="E19" t="n">
-        <v>25011.35</v>
+        <v>25155.41</v>
       </c>
       <c r="F19" t="n">
-        <v>164.66</v>
+        <v>144.06</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0058</v>
       </c>
       <c r="H19" t="n">
-        <v>194.01</v>
+        <v>287.07</v>
       </c>
       <c r="I19" t="n">
-        <v>24527.73</v>
+        <v>24623.33</v>
       </c>
       <c r="J19" t="n">
-        <v>24615.22</v>
+        <v>24865.84</v>
       </c>
       <c r="K19" t="n">
-        <v>24734.99</v>
+        <v>24914.34</v>
       </c>
       <c r="L19" t="n">
-        <v>24854.76</v>
+        <v>24962.85</v>
       </c>
       <c r="M19" t="n">
-        <v>24958.39</v>
+        <v>25108.35</v>
       </c>
       <c r="N19" t="n">
-        <v>25062.02</v>
+        <v>25253.86</v>
       </c>
       <c r="O19" t="n">
-        <v>25197.93</v>
+        <v>25205.36</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2102,18 +2106,20 @@
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U19" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W19" s="9" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2127,171 +2133,165 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25001.31</v>
+        <v>24994.05</v>
       </c>
       <c r="C20" t="n">
-        <v>25271.34</v>
+        <v>25074.28</v>
       </c>
       <c r="D20" t="n">
-        <v>24984.27</v>
+        <v>24696.59</v>
       </c>
       <c r="E20" t="n">
-        <v>25155.41</v>
+        <v>24763.12</v>
       </c>
       <c r="F20" t="n">
-        <v>144.06</v>
+        <v>-392.29</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0156</v>
       </c>
       <c r="H20" t="n">
-        <v>287.07</v>
+        <v>377.69</v>
       </c>
       <c r="I20" t="n">
-        <v>24623.33</v>
+        <v>24697.2</v>
       </c>
       <c r="J20" t="n">
-        <v>24865.84</v>
+        <v>24882.14</v>
       </c>
       <c r="K20" t="n">
-        <v>24914.34</v>
+        <v>25011.88</v>
       </c>
       <c r="L20" t="n">
-        <v>24962.85</v>
+        <v>25141.61</v>
       </c>
       <c r="M20" t="n">
-        <v>25108.35</v>
+        <v>25298.95</v>
       </c>
       <c r="N20" t="n">
-        <v>25253.86</v>
+        <v>25456.28</v>
       </c>
       <c r="O20" t="n">
-        <v>25205.36</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+        <v>25558.41</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24994.05</v>
+        <v>24830.41</v>
       </c>
       <c r="C21" t="n">
-        <v>25074.28</v>
+        <v>25099.68</v>
       </c>
       <c r="D21" t="n">
-        <v>24696.59</v>
+        <v>24821.67</v>
       </c>
       <c r="E21" t="n">
-        <v>24763.12</v>
+        <v>25099</v>
       </c>
       <c r="F21" t="n">
-        <v>-392.29</v>
+        <v>335.88</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0136</v>
       </c>
       <c r="H21" t="n">
-        <v>377.69</v>
+        <v>278.01</v>
       </c>
       <c r="I21" t="n">
-        <v>24697.2</v>
+        <v>24318.9</v>
       </c>
       <c r="J21" t="n">
-        <v>24882.14</v>
+        <v>24324.27</v>
       </c>
       <c r="K21" t="n">
-        <v>25011.88</v>
+        <v>24574.27</v>
       </c>
       <c r="L21" t="n">
-        <v>25141.61</v>
+        <v>24824.28</v>
       </c>
       <c r="M21" t="n">
-        <v>25298.95</v>
+        <v>24951.96</v>
       </c>
       <c r="N21" t="n">
-        <v>25456.28</v>
+        <v>25079.65</v>
       </c>
       <c r="O21" t="n">
-        <v>25558.41</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
+        <v>25451.97</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
@@ -2299,50 +2299,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24830.41</v>
+        <v>25459.32</v>
       </c>
       <c r="C22" t="n">
-        <v>25099.68</v>
+        <v>25560.4</v>
       </c>
       <c r="D22" t="n">
-        <v>24821.67</v>
+        <v>25361.03</v>
       </c>
       <c r="E22" t="n">
-        <v>25099</v>
+        <v>25361.03</v>
       </c>
       <c r="F22" t="n">
-        <v>335.88</v>
+        <v>262.03</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0104</v>
       </c>
       <c r="H22" t="n">
-        <v>278.01</v>
+        <v>199.37</v>
       </c>
       <c r="I22" t="n">
-        <v>24318.9</v>
+        <v>24543.66</v>
       </c>
       <c r="J22" t="n">
-        <v>24324.27</v>
+        <v>24890.15</v>
       </c>
       <c r="K22" t="n">
-        <v>24574.27</v>
+        <v>24960</v>
       </c>
       <c r="L22" t="n">
-        <v>24824.28</v>
+        <v>25029.84</v>
       </c>
       <c r="M22" t="n">
-        <v>24951.96</v>
+        <v>25238</v>
       </c>
       <c r="N22" t="n">
-        <v>25079.65</v>
+        <v>25446.17</v>
       </c>
       <c r="O22" t="n">
-        <v>25451.97</v>
+        <v>25377.69</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2365,13 +2365,15 @@
       </c>
       <c r="U22" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2381,50 +2383,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25459.32</v>
+        <v>25496.13</v>
       </c>
       <c r="C23" t="n">
-        <v>25560.4</v>
+        <v>25553.47</v>
       </c>
       <c r="D23" t="n">
-        <v>25361.03</v>
+        <v>25307.17</v>
       </c>
       <c r="E23" t="n">
-        <v>25361.03</v>
+        <v>25464.01</v>
       </c>
       <c r="F23" t="n">
-        <v>262.03</v>
+        <v>102.98</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0104</v>
+        <v>0.0041</v>
       </c>
       <c r="H23" t="n">
-        <v>199.37</v>
+        <v>246.3</v>
       </c>
       <c r="I23" t="n">
-        <v>24543.66</v>
+        <v>25161.66</v>
       </c>
       <c r="J23" t="n">
-        <v>24890.15</v>
+        <v>25111.82</v>
       </c>
       <c r="K23" t="n">
-        <v>24960</v>
+        <v>25261.34</v>
       </c>
       <c r="L23" t="n">
-        <v>25029.84</v>
+        <v>25410.87</v>
       </c>
       <c r="M23" t="n">
-        <v>25238</v>
+        <v>25460.71</v>
       </c>
       <c r="N23" t="n">
-        <v>25446.17</v>
+        <v>25510.56</v>
       </c>
       <c r="O23" t="n">
-        <v>25377.69</v>
+        <v>25759.77</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2442,7 +2444,7 @@
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U23" s="8" t="inlineStr">
@@ -2450,65 +2452,67 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="V23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25496.13</v>
+        <v>25551.97</v>
       </c>
       <c r="C24" t="n">
-        <v>25553.47</v>
+        <v>25571.45</v>
       </c>
       <c r="D24" t="n">
-        <v>25307.17</v>
+        <v>25336.39</v>
       </c>
       <c r="E24" t="n">
-        <v>25464.01</v>
+        <v>25460.48</v>
       </c>
       <c r="F24" t="n">
-        <v>102.98</v>
+        <v>-3.53</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0001</v>
       </c>
       <c r="H24" t="n">
-        <v>246.3</v>
+        <v>235.06</v>
       </c>
       <c r="I24" t="n">
-        <v>25161.66</v>
+        <v>25060.87</v>
       </c>
       <c r="J24" t="n">
-        <v>25111.82</v>
+        <v>25234.55</v>
       </c>
       <c r="K24" t="n">
-        <v>25261.34</v>
+        <v>25340.86</v>
       </c>
       <c r="L24" t="n">
-        <v>25410.87</v>
+        <v>25447.17</v>
       </c>
       <c r="M24" t="n">
-        <v>25460.71</v>
+        <v>25587.16</v>
       </c>
       <c r="N24" t="n">
-        <v>25510.56</v>
+        <v>25727.16</v>
       </c>
       <c r="O24" t="n">
-        <v>25759.77</v>
+        <v>25799.77</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2516,85 +2520,83 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25551.97</v>
+        <v>25487.45</v>
       </c>
       <c r="C25" t="n">
-        <v>25571.45</v>
+        <v>25651.16</v>
       </c>
       <c r="D25" t="n">
-        <v>25336.39</v>
+        <v>25303.11</v>
       </c>
       <c r="E25" t="n">
-        <v>25460.48</v>
+        <v>25612.03</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.53</v>
+        <v>151.55</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.006</v>
       </c>
       <c r="H25" t="n">
-        <v>235.06</v>
+        <v>348.05</v>
       </c>
       <c r="I25" t="n">
-        <v>25060.87</v>
+        <v>25101.33</v>
       </c>
       <c r="J25" t="n">
-        <v>25234.55</v>
+        <v>25228.7</v>
       </c>
       <c r="K25" t="n">
-        <v>25340.86</v>
+        <v>25342.95</v>
       </c>
       <c r="L25" t="n">
-        <v>25447.17</v>
+        <v>25457.2</v>
       </c>
       <c r="M25" t="n">
-        <v>25587.16</v>
+        <v>25578.01</v>
       </c>
       <c r="N25" t="n">
-        <v>25727.16</v>
+        <v>25698.82</v>
       </c>
       <c r="O25" t="n">
-        <v>25799.77</v>
+        <v>25806.51</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2609,11 +2611,13 @@
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2621,7 +2625,7 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2635,50 +2639,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25487.45</v>
+        <v>25709.37</v>
       </c>
       <c r="C26" t="n">
-        <v>25651.16</v>
+        <v>25891.51</v>
       </c>
       <c r="D26" t="n">
-        <v>25303.11</v>
+        <v>25549.53</v>
       </c>
       <c r="E26" t="n">
-        <v>25612.03</v>
+        <v>25629.24</v>
       </c>
       <c r="F26" t="n">
-        <v>151.55</v>
+        <v>17.21</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0007</v>
       </c>
       <c r="H26" t="n">
-        <v>348.05</v>
+        <v>341.98</v>
       </c>
       <c r="I26" t="n">
-        <v>25101.33</v>
+        <v>24955.06</v>
       </c>
       <c r="J26" t="n">
-        <v>25228.7</v>
+        <v>25331.43</v>
       </c>
       <c r="K26" t="n">
-        <v>25342.95</v>
+        <v>25438</v>
       </c>
       <c r="L26" t="n">
-        <v>25457.2</v>
+        <v>25544.58</v>
       </c>
       <c r="M26" t="n">
-        <v>25578.01</v>
+        <v>25786.05</v>
       </c>
       <c r="N26" t="n">
-        <v>25698.82</v>
+        <v>26027.53</v>
       </c>
       <c r="O26" t="n">
-        <v>25806.51</v>
+        <v>25999.21</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2686,19 +2690,17 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U26" s="8" t="n">
@@ -2707,64 +2709,60 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25709.37</v>
+        <v>25855.12</v>
       </c>
       <c r="C27" t="n">
-        <v>25891.51</v>
+        <v>26096.93</v>
       </c>
       <c r="D27" t="n">
-        <v>25549.53</v>
+        <v>25855.12</v>
       </c>
       <c r="E27" t="n">
-        <v>25629.24</v>
+        <v>26001.31</v>
       </c>
       <c r="F27" t="n">
-        <v>17.21</v>
+        <v>372.07</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0145</v>
       </c>
       <c r="H27" t="n">
-        <v>341.98</v>
+        <v>241.81</v>
       </c>
       <c r="I27" t="n">
-        <v>24955.06</v>
+        <v>25207.55</v>
       </c>
       <c r="J27" t="n">
-        <v>25331.43</v>
+        <v>25241.62</v>
       </c>
       <c r="K27" t="n">
-        <v>25438</v>
+        <v>25458.25</v>
       </c>
       <c r="L27" t="n">
-        <v>25544.58</v>
+        <v>25674.88</v>
       </c>
       <c r="M27" t="n">
-        <v>25786.05</v>
+        <v>25800.23</v>
       </c>
       <c r="N27" t="n">
-        <v>26027.53</v>
+        <v>25925.58</v>
       </c>
       <c r="O27" t="n">
-        <v>25999.21</v>
+        <v>26233.49</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2777,7 +2775,7 @@
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
@@ -2785,13 +2783,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2801,50 +2801,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25855.12</v>
+        <v>26189.62</v>
       </c>
       <c r="C28" t="n">
-        <v>26096.93</v>
+        <v>26266.5</v>
       </c>
       <c r="D28" t="n">
-        <v>25855.12</v>
+        <v>26082.43</v>
       </c>
       <c r="E28" t="n">
-        <v>26001.31</v>
+        <v>26202.35</v>
       </c>
       <c r="F28" t="n">
-        <v>372.07</v>
+        <v>201.04</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0077</v>
       </c>
       <c r="H28" t="n">
-        <v>241.81</v>
+        <v>184.07</v>
       </c>
       <c r="I28" t="n">
-        <v>25207.55</v>
+        <v>25613.31</v>
       </c>
       <c r="J28" t="n">
-        <v>25241.62</v>
+        <v>25772.14</v>
       </c>
       <c r="K28" t="n">
-        <v>25458.25</v>
+        <v>25880.41</v>
       </c>
       <c r="L28" t="n">
-        <v>25674.88</v>
+        <v>25988.67</v>
       </c>
       <c r="M28" t="n">
-        <v>25800.23</v>
+        <v>26122.22</v>
       </c>
       <c r="N28" t="n">
-        <v>25925.58</v>
+        <v>26255.76</v>
       </c>
       <c r="O28" t="n">
-        <v>26233.49</v>
+        <v>26338.74</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2873,7 +2873,7 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2883,50 +2883,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>26189.62</v>
+        <v>26393.43</v>
       </c>
       <c r="C29" t="n">
-        <v>26266.5</v>
+        <v>26403.81</v>
       </c>
       <c r="D29" t="n">
-        <v>26082.43</v>
+        <v>26123.18</v>
       </c>
       <c r="E29" t="n">
-        <v>26202.35</v>
+        <v>26126.3</v>
       </c>
       <c r="F29" t="n">
-        <v>201.04</v>
+        <v>-76.05</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0029</v>
       </c>
       <c r="H29" t="n">
-        <v>184.07</v>
+        <v>280.63</v>
       </c>
       <c r="I29" t="n">
-        <v>25613.31</v>
+        <v>25898.36</v>
       </c>
       <c r="J29" t="n">
-        <v>25772.14</v>
+        <v>26032.22</v>
       </c>
       <c r="K29" t="n">
-        <v>25880.41</v>
+        <v>26110.31</v>
       </c>
       <c r="L29" t="n">
-        <v>25988.67</v>
+        <v>26188.41</v>
       </c>
       <c r="M29" t="n">
-        <v>26122.22</v>
+        <v>26294.38</v>
       </c>
       <c r="N29" t="n">
-        <v>26255.76</v>
+        <v>26400.36</v>
       </c>
       <c r="O29" t="n">
-        <v>26338.74</v>
+        <v>26450.57</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2934,12 +2934,14 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
@@ -2949,66 +2951,70 @@
       </c>
       <c r="U29" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26393.43</v>
+        <v>26116.27</v>
       </c>
       <c r="C30" t="n">
-        <v>26403.81</v>
+        <v>26229.33</v>
       </c>
       <c r="D30" t="n">
-        <v>26123.18</v>
+        <v>26081.69</v>
       </c>
       <c r="E30" t="n">
-        <v>26126.3</v>
+        <v>26140.13</v>
       </c>
       <c r="F30" t="n">
-        <v>-76.05</v>
+        <v>13.83</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0005</v>
       </c>
       <c r="H30" t="n">
-        <v>280.63</v>
+        <v>147.64</v>
       </c>
       <c r="I30" t="n">
-        <v>25898.36</v>
+        <v>25842.55</v>
       </c>
       <c r="J30" t="n">
-        <v>26032.22</v>
+        <v>25777.07</v>
       </c>
       <c r="K30" t="n">
-        <v>26110.31</v>
+        <v>25985.99</v>
       </c>
       <c r="L30" t="n">
-        <v>26188.41</v>
+        <v>26194.9</v>
       </c>
       <c r="M30" t="n">
-        <v>26294.38</v>
+        <v>26266.62</v>
       </c>
       <c r="N30" t="n">
-        <v>26400.36</v>
+        <v>26338.33</v>
       </c>
       <c r="O30" t="n">
-        <v>26450.57</v>
+        <v>26684.44</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3016,87 +3022,81 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R30" s="6" t="n">
+        <v/>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>26116.27</v>
+        <v>26235.8</v>
       </c>
       <c r="C31" t="n">
-        <v>26229.33</v>
+        <v>26445.18</v>
       </c>
       <c r="D31" t="n">
-        <v>26081.69</v>
+        <v>26223.64</v>
       </c>
       <c r="E31" t="n">
-        <v>26140.13</v>
+        <v>26319.45</v>
       </c>
       <c r="F31" t="n">
-        <v>13.83</v>
+        <v>179.32</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0069</v>
       </c>
       <c r="H31" t="n">
-        <v>147.64</v>
+        <v>221.54</v>
       </c>
       <c r="I31" t="n">
-        <v>25842.55</v>
+        <v>25934.05</v>
       </c>
       <c r="J31" t="n">
-        <v>25777.07</v>
+        <v>25984.8</v>
       </c>
       <c r="K31" t="n">
-        <v>25985.99</v>
+        <v>26066.31</v>
       </c>
       <c r="L31" t="n">
-        <v>26194.9</v>
+        <v>26147.82</v>
       </c>
       <c r="M31" t="n">
-        <v>26266.62</v>
+        <v>26213.95</v>
       </c>
       <c r="N31" t="n">
-        <v>26338.33</v>
+        <v>26280.08</v>
       </c>
       <c r="O31" t="n">
-        <v>26684.44</v>
+        <v>26376.97</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3107,78 +3107,80 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26235.8</v>
+        <v>26360.44</v>
       </c>
       <c r="C32" t="n">
-        <v>26445.18</v>
+        <v>26441.91</v>
       </c>
       <c r="D32" t="n">
-        <v>26223.64</v>
+        <v>26302.19</v>
       </c>
       <c r="E32" t="n">
-        <v>26319.45</v>
+        <v>26323.88</v>
       </c>
       <c r="F32" t="n">
-        <v>179.32</v>
+        <v>4.43</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0002</v>
       </c>
       <c r="H32" t="n">
-        <v>221.54</v>
+        <v>139.72</v>
       </c>
       <c r="I32" t="n">
-        <v>25934.05</v>
+        <v>26002.1</v>
       </c>
       <c r="J32" t="n">
-        <v>25984.8</v>
+        <v>26090.43</v>
       </c>
       <c r="K32" t="n">
-        <v>26066.31</v>
+        <v>26208.68</v>
       </c>
       <c r="L32" t="n">
-        <v>26147.82</v>
+        <v>26326.93</v>
       </c>
       <c r="M32" t="n">
-        <v>26213.95</v>
+        <v>26430.22</v>
       </c>
       <c r="N32" t="n">
-        <v>26280.08</v>
+        <v>26533.51</v>
       </c>
       <c r="O32" t="n">
-        <v>26376.97</v>
+        <v>26666.72</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3189,9 +3191,9 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
@@ -3199,70 +3201,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>26360.44</v>
+        <v>26378</v>
       </c>
       <c r="C33" t="n">
-        <v>26441.91</v>
+        <v>26504.54</v>
       </c>
       <c r="D33" t="n">
-        <v>26302.19</v>
+        <v>26245.57</v>
       </c>
       <c r="E33" t="n">
-        <v>26323.88</v>
+        <v>26391.42</v>
       </c>
       <c r="F33" t="n">
-        <v>4.43</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0026</v>
       </c>
       <c r="H33" t="n">
-        <v>139.72</v>
+        <v>258.97</v>
       </c>
       <c r="I33" t="n">
-        <v>26002.1</v>
+        <v>26162.47</v>
       </c>
       <c r="J33" t="n">
-        <v>26090.43</v>
+        <v>26160.08</v>
       </c>
       <c r="K33" t="n">
-        <v>26208.68</v>
+        <v>26254.02</v>
       </c>
       <c r="L33" t="n">
-        <v>26326.93</v>
+        <v>26347.97</v>
       </c>
       <c r="M33" t="n">
-        <v>26430.22</v>
+        <v>26393.74</v>
       </c>
       <c r="N33" t="n">
-        <v>26533.51</v>
+        <v>26439.52</v>
       </c>
       <c r="O33" t="n">
-        <v>26666.72</v>
+        <v>26581.63</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3270,26 +3272,30 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3303,50 +3309,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26378</v>
+        <v>26452</v>
       </c>
       <c r="C34" t="n">
-        <v>26504.54</v>
+        <v>26573.5</v>
       </c>
       <c r="D34" t="n">
-        <v>26245.57</v>
+        <v>26313.58</v>
       </c>
       <c r="E34" t="n">
-        <v>26391.42</v>
+        <v>26331.07</v>
       </c>
       <c r="F34" t="n">
-        <v>67.54000000000001</v>
+        <v>-60.35</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0023</v>
       </c>
       <c r="H34" t="n">
-        <v>258.97</v>
+        <v>259.92</v>
       </c>
       <c r="I34" t="n">
-        <v>26162.47</v>
+        <v>25986.6</v>
       </c>
       <c r="J34" t="n">
-        <v>26160.08</v>
+        <v>26140.63</v>
       </c>
       <c r="K34" t="n">
-        <v>26254.02</v>
+        <v>26261.94</v>
       </c>
       <c r="L34" t="n">
-        <v>26347.97</v>
+        <v>26383.24</v>
       </c>
       <c r="M34" t="n">
-        <v>26393.74</v>
+        <v>26520.9</v>
       </c>
       <c r="N34" t="n">
-        <v>26439.52</v>
+        <v>26658.57</v>
       </c>
       <c r="O34" t="n">
-        <v>26581.63</v>
+        <v>26763.51</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3354,30 +3360,26 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3391,50 +3393,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>26452</v>
+        <v>26437.35</v>
       </c>
       <c r="C35" t="n">
-        <v>26573.5</v>
+        <v>26489.78</v>
       </c>
       <c r="D35" t="n">
-        <v>26313.58</v>
+        <v>26285.23</v>
       </c>
       <c r="E35" t="n">
-        <v>26331.07</v>
+        <v>26299.74</v>
       </c>
       <c r="F35" t="n">
-        <v>-60.35</v>
+        <v>-31.33</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0012</v>
       </c>
       <c r="H35" t="n">
-        <v>259.92</v>
+        <v>204.55</v>
       </c>
       <c r="I35" t="n">
-        <v>25986.6</v>
+        <v>26053.66</v>
       </c>
       <c r="J35" t="n">
-        <v>26140.63</v>
+        <v>26014.92</v>
       </c>
       <c r="K35" t="n">
-        <v>26261.94</v>
+        <v>26201.11</v>
       </c>
       <c r="L35" t="n">
-        <v>26383.24</v>
+        <v>26387.31</v>
       </c>
       <c r="M35" t="n">
-        <v>26520.9</v>
+        <v>26461.03</v>
       </c>
       <c r="N35" t="n">
-        <v>26658.57</v>
+        <v>26534.76</v>
       </c>
       <c r="O35" t="n">
-        <v>26763.51</v>
+        <v>26833.42</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3461,64 +3463,64 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26437.35</v>
+        <v>26445.99</v>
       </c>
       <c r="C36" t="n">
-        <v>26489.78</v>
+        <v>26541.34</v>
       </c>
       <c r="D36" t="n">
-        <v>26285.23</v>
+        <v>26404.95</v>
       </c>
       <c r="E36" t="n">
-        <v>26299.74</v>
+        <v>26440.31</v>
       </c>
       <c r="F36" t="n">
-        <v>-31.33</v>
+        <v>140.57</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0053</v>
       </c>
       <c r="H36" t="n">
-        <v>204.55</v>
+        <v>136.39</v>
       </c>
       <c r="I36" t="n">
-        <v>26053.66</v>
+        <v>26080.68</v>
       </c>
       <c r="J36" t="n">
-        <v>26014.92</v>
+        <v>26051.31</v>
       </c>
       <c r="K36" t="n">
-        <v>26201.11</v>
+        <v>26197.47</v>
       </c>
       <c r="L36" t="n">
-        <v>26387.31</v>
+        <v>26343.62</v>
       </c>
       <c r="M36" t="n">
-        <v>26461.03</v>
+        <v>26402.01</v>
       </c>
       <c r="N36" t="n">
-        <v>26534.76</v>
+        <v>26460.41</v>
       </c>
       <c r="O36" t="n">
-        <v>26833.42</v>
+        <v>26694.33</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3529,9 +3531,9 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
@@ -3539,70 +3541,68 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U36" s="8" t="n">
-        <v/>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26445.99</v>
+        <v>26490.3</v>
       </c>
       <c r="C37" t="n">
-        <v>26541.34</v>
+        <v>26493.5</v>
       </c>
       <c r="D37" t="n">
-        <v>26404.95</v>
+        <v>26338.61</v>
       </c>
       <c r="E37" t="n">
-        <v>26440.31</v>
+        <v>26338.61</v>
       </c>
       <c r="F37" t="n">
-        <v>140.57</v>
+        <v>-101.7</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0038</v>
       </c>
       <c r="H37" t="n">
-        <v>136.39</v>
+        <v>154.89</v>
       </c>
       <c r="I37" t="n">
-        <v>26080.68</v>
+        <v>26268.56</v>
       </c>
       <c r="J37" t="n">
-        <v>26051.31</v>
+        <v>26287.5</v>
       </c>
       <c r="K37" t="n">
-        <v>26197.47</v>
+        <v>26372.12</v>
       </c>
       <c r="L37" t="n">
-        <v>26343.62</v>
+        <v>26456.73</v>
       </c>
       <c r="M37" t="n">
-        <v>26402.01</v>
+        <v>26508.51</v>
       </c>
       <c r="N37" t="n">
-        <v>26460.41</v>
+        <v>26560.28</v>
       </c>
       <c r="O37" t="n">
-        <v>26694.33</v>
+        <v>26677.73</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3610,91 +3610,97 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26490.3</v>
+        <v>26280.86</v>
       </c>
       <c r="C38" t="n">
-        <v>26493.5</v>
+        <v>26292.95</v>
       </c>
       <c r="D38" t="n">
-        <v>26338.61</v>
+        <v>26119.54</v>
       </c>
       <c r="E38" t="n">
-        <v>26338.61</v>
+        <v>26128.36</v>
       </c>
       <c r="F38" t="n">
-        <v>-101.7</v>
+        <v>-210.25</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.008</v>
       </c>
       <c r="H38" t="n">
-        <v>154.89</v>
+        <v>173.41</v>
       </c>
       <c r="I38" t="n">
-        <v>26268.56</v>
+        <v>26183.72</v>
       </c>
       <c r="J38" t="n">
-        <v>26287.5</v>
+        <v>26145</v>
       </c>
       <c r="K38" t="n">
-        <v>26372.12</v>
+        <v>26261.16</v>
       </c>
       <c r="L38" t="n">
-        <v>26456.73</v>
+        <v>26377.33</v>
       </c>
       <c r="M38" t="n">
-        <v>26508.51</v>
+        <v>26416.05</v>
       </c>
       <c r="N38" t="n">
-        <v>26560.28</v>
+        <v>26454.78</v>
       </c>
       <c r="O38" t="n">
-        <v>26677.73</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
+        <v>26648.39</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
@@ -3713,78 +3719,70 @@
       </c>
       <c r="W38" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26280.86</v>
+        <v>26146.12</v>
       </c>
       <c r="C39" t="n">
-        <v>26292.95</v>
+        <v>26187.82</v>
       </c>
       <c r="D39" t="n">
-        <v>26119.54</v>
+        <v>26063.37</v>
       </c>
       <c r="E39" t="n">
-        <v>26128.36</v>
+        <v>26091.33</v>
       </c>
       <c r="F39" t="n">
-        <v>-210.25</v>
+        <v>-37.03</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0014</v>
       </c>
       <c r="H39" t="n">
-        <v>173.41</v>
+        <v>124.45</v>
       </c>
       <c r="I39" t="n">
-        <v>26183.72</v>
+        <v>25946.13</v>
       </c>
       <c r="J39" t="n">
-        <v>26145</v>
+        <v>25916.01</v>
       </c>
       <c r="K39" t="n">
-        <v>26261.16</v>
+        <v>26041.65</v>
       </c>
       <c r="L39" t="n">
-        <v>26377.33</v>
+        <v>26167.3</v>
       </c>
       <c r="M39" t="n">
-        <v>26416.05</v>
+        <v>26215.06</v>
       </c>
       <c r="N39" t="n">
-        <v>26454.78</v>
+        <v>26262.83</v>
       </c>
       <c r="O39" t="n">
-        <v>26648.39</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
+        <v>26466.36</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -3799,7 +3797,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3809,60 +3807,64 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>26146.12</v>
+        <v>26050.95</v>
       </c>
       <c r="C40" t="n">
-        <v>26187.82</v>
+        <v>26062.15</v>
       </c>
       <c r="D40" t="n">
-        <v>26063.37</v>
+        <v>25914.11</v>
       </c>
       <c r="E40" t="n">
-        <v>26091.33</v>
+        <v>25983.04</v>
       </c>
       <c r="F40" t="n">
-        <v>-37.03</v>
+        <v>-108.29</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0042</v>
       </c>
       <c r="H40" t="n">
-        <v>124.45</v>
+        <v>148.04</v>
       </c>
       <c r="I40" t="n">
-        <v>25946.13</v>
+        <v>25938.92</v>
       </c>
       <c r="J40" t="n">
-        <v>25916.01</v>
+        <v>25949.75</v>
       </c>
       <c r="K40" t="n">
-        <v>26041.65</v>
+        <v>26029.1</v>
       </c>
       <c r="L40" t="n">
-        <v>26167.3</v>
+        <v>26108.46</v>
       </c>
       <c r="M40" t="n">
-        <v>26215.06</v>
+        <v>26153.56</v>
       </c>
       <c r="N40" t="n">
-        <v>26262.83</v>
+        <v>26198.65</v>
       </c>
       <c r="O40" t="n">
-        <v>26466.36</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+        <v>26312.27</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
@@ -3879,7 +3881,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3889,83 +3891,81 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26050.95</v>
+        <v>25998.95</v>
       </c>
       <c r="C41" t="n">
-        <v>26062.15</v>
+        <v>26166.25</v>
       </c>
       <c r="D41" t="n">
-        <v>25914.11</v>
+        <v>25969.52</v>
       </c>
       <c r="E41" t="n">
-        <v>25983.04</v>
+        <v>26136.56</v>
       </c>
       <c r="F41" t="n">
-        <v>-108.29</v>
+        <v>153.52</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.0059</v>
       </c>
       <c r="H41" t="n">
-        <v>148.04</v>
+        <v>196.73</v>
       </c>
       <c r="I41" t="n">
-        <v>25938.92</v>
+        <v>25766.07</v>
       </c>
       <c r="J41" t="n">
-        <v>25949.75</v>
+        <v>25832.45</v>
       </c>
       <c r="K41" t="n">
-        <v>26029.1</v>
+        <v>25909.02</v>
       </c>
       <c r="L41" t="n">
-        <v>26108.46</v>
+        <v>25985.58</v>
       </c>
       <c r="M41" t="n">
-        <v>26153.56</v>
+        <v>26057.06</v>
       </c>
       <c r="N41" t="n">
-        <v>26198.65</v>
+        <v>26128.53</v>
       </c>
       <c r="O41" t="n">
-        <v>26312.27</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
+        <v>26210.19</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr"/>
@@ -3973,50 +3973,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25998.95</v>
+        <v>26091.29</v>
       </c>
       <c r="C42" t="n">
-        <v>26166.25</v>
+        <v>26171.7</v>
       </c>
       <c r="D42" t="n">
-        <v>25969.52</v>
+        <v>26038.07</v>
       </c>
       <c r="E42" t="n">
-        <v>26136.56</v>
+        <v>26106.6</v>
       </c>
       <c r="F42" t="n">
-        <v>153.52</v>
+        <v>-29.96</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0011</v>
       </c>
       <c r="H42" t="n">
-        <v>196.73</v>
+        <v>133.63</v>
       </c>
       <c r="I42" t="n">
-        <v>25766.07</v>
+        <v>25772.79</v>
       </c>
       <c r="J42" t="n">
-        <v>25832.45</v>
+        <v>25974.17</v>
       </c>
       <c r="K42" t="n">
-        <v>25909.02</v>
+        <v>26038.2</v>
       </c>
       <c r="L42" t="n">
-        <v>25985.58</v>
+        <v>26102.22</v>
       </c>
       <c r="M42" t="n">
-        <v>26057.06</v>
+        <v>26234.93</v>
       </c>
       <c r="N42" t="n">
-        <v>26128.53</v>
+        <v>26367.63</v>
       </c>
       <c r="O42" t="n">
-        <v>26210.19</v>
+        <v>26362.98</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4024,81 +4024,83 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>26091.29</v>
+        <v>26206.01</v>
       </c>
       <c r="C43" t="n">
-        <v>26171.7</v>
+        <v>26341.52</v>
       </c>
       <c r="D43" t="n">
-        <v>26038.07</v>
+        <v>26164.11</v>
       </c>
       <c r="E43" t="n">
-        <v>26106.6</v>
+        <v>26266.14</v>
       </c>
       <c r="F43" t="n">
-        <v>-29.96</v>
+        <v>159.54</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0061</v>
       </c>
       <c r="H43" t="n">
-        <v>133.63</v>
+        <v>177.41</v>
       </c>
       <c r="I43" t="n">
-        <v>25772.79</v>
+        <v>25904.44</v>
       </c>
       <c r="J43" t="n">
-        <v>25974.17</v>
+        <v>25973.83</v>
       </c>
       <c r="K43" t="n">
-        <v>26038.2</v>
+        <v>26039.79</v>
       </c>
       <c r="L43" t="n">
-        <v>26102.22</v>
+        <v>26105.74</v>
       </c>
       <c r="M43" t="n">
-        <v>26234.93</v>
+        <v>26173.41</v>
       </c>
       <c r="N43" t="n">
-        <v>26367.63</v>
+        <v>26241.09</v>
       </c>
       <c r="O43" t="n">
-        <v>26362.98</v>
+        <v>26305.33</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4106,83 +4108,83 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R43" s="6" t="n">
+        <v/>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W43" s="11" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26206.01</v>
+        <v>26255.41</v>
       </c>
       <c r="C44" t="n">
-        <v>26341.52</v>
+        <v>26466.76</v>
       </c>
       <c r="D44" t="n">
-        <v>26164.11</v>
+        <v>26196.92</v>
       </c>
       <c r="E44" t="n">
-        <v>26266.14</v>
+        <v>26285.96</v>
       </c>
       <c r="F44" t="n">
-        <v>159.54</v>
+        <v>19.82</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0061</v>
+        <v>0.0008</v>
       </c>
       <c r="H44" t="n">
-        <v>177.41</v>
+        <v>269.84</v>
       </c>
       <c r="I44" t="n">
-        <v>25904.44</v>
+        <v>25986.7</v>
       </c>
       <c r="J44" t="n">
-        <v>25973.83</v>
+        <v>26095.39</v>
       </c>
       <c r="K44" t="n">
-        <v>26039.79</v>
+        <v>26177.44</v>
       </c>
       <c r="L44" t="n">
-        <v>26105.74</v>
+        <v>26259.48</v>
       </c>
       <c r="M44" t="n">
-        <v>26173.41</v>
+        <v>26354.85</v>
       </c>
       <c r="N44" t="n">
-        <v>26241.09</v>
+        <v>26450.21</v>
       </c>
       <c r="O44" t="n">
-        <v>26305.33</v>
+        <v>26518.93</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4195,7 +4197,7 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
@@ -4205,15 +4207,13 @@
       </c>
       <c r="U44" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W44" s="11" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4223,50 +4223,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>26255.41</v>
+        <v>26354.37</v>
       </c>
       <c r="C45" t="n">
-        <v>26466.76</v>
+        <v>26402.81</v>
       </c>
       <c r="D45" t="n">
-        <v>26196.92</v>
+        <v>26241.77</v>
       </c>
       <c r="E45" t="n">
-        <v>26285.96</v>
+        <v>26367.24</v>
       </c>
       <c r="F45" t="n">
-        <v>19.82</v>
+        <v>81.28</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0031</v>
       </c>
       <c r="H45" t="n">
-        <v>269.84</v>
+        <v>161.04</v>
       </c>
       <c r="I45" t="n">
-        <v>25986.7</v>
+        <v>25927.08</v>
       </c>
       <c r="J45" t="n">
-        <v>26095.39</v>
+        <v>25993.18</v>
       </c>
       <c r="K45" t="n">
-        <v>26177.44</v>
+        <v>26151.04</v>
       </c>
       <c r="L45" t="n">
-        <v>26259.48</v>
+        <v>26308.9</v>
       </c>
       <c r="M45" t="n">
-        <v>26354.85</v>
+        <v>26420.88</v>
       </c>
       <c r="N45" t="n">
-        <v>26450.21</v>
+        <v>26532.86</v>
       </c>
       <c r="O45" t="n">
-        <v>26518.93</v>
+        <v>26736.6</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4279,76 +4279,78 @@
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>26354.37</v>
+        <v>26494.61</v>
       </c>
       <c r="C46" t="n">
-        <v>26402.81</v>
+        <v>26618.74</v>
       </c>
       <c r="D46" t="n">
-        <v>26241.77</v>
+        <v>26467.36</v>
       </c>
       <c r="E46" t="n">
-        <v>26367.24</v>
+        <v>26569.99</v>
       </c>
       <c r="F46" t="n">
-        <v>81.28</v>
+        <v>202.75</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0077</v>
       </c>
       <c r="H46" t="n">
-        <v>161.04</v>
+        <v>151.38</v>
       </c>
       <c r="I46" t="n">
-        <v>25927.08</v>
+        <v>26080.73</v>
       </c>
       <c r="J46" t="n">
-        <v>25993.18</v>
+        <v>26228.67</v>
       </c>
       <c r="K46" t="n">
-        <v>26151.04</v>
+        <v>26286.72</v>
       </c>
       <c r="L46" t="n">
-        <v>26308.9</v>
+        <v>26344.77</v>
       </c>
       <c r="M46" t="n">
-        <v>26420.88</v>
+        <v>26447.76</v>
       </c>
       <c r="N46" t="n">
-        <v>26532.86</v>
+        <v>26550.76</v>
       </c>
       <c r="O46" t="n">
-        <v>26736.6</v>
+        <v>26563.85</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4366,106 +4368,106 @@
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>26494.61</v>
+        <v>26464.14</v>
       </c>
       <c r="C47" t="n">
-        <v>26618.74</v>
+        <v>26471.79</v>
       </c>
       <c r="D47" t="n">
-        <v>26467.36</v>
+        <v>26249.59</v>
       </c>
       <c r="E47" t="n">
-        <v>26569.99</v>
+        <v>26258.11</v>
       </c>
       <c r="F47" t="n">
-        <v>202.75</v>
+        <v>-311.88</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0117</v>
       </c>
       <c r="H47" t="n">
-        <v>151.38</v>
+        <v>222.2</v>
       </c>
       <c r="I47" t="n">
-        <v>26080.73</v>
+        <v>26315.98</v>
       </c>
       <c r="J47" t="n">
-        <v>26228.67</v>
+        <v>26432.08</v>
       </c>
       <c r="K47" t="n">
-        <v>26286.72</v>
+        <v>26494.3</v>
       </c>
       <c r="L47" t="n">
-        <v>26344.77</v>
+        <v>26556.52</v>
       </c>
       <c r="M47" t="n">
-        <v>26447.76</v>
+        <v>26645.68</v>
       </c>
       <c r="N47" t="n">
-        <v>26550.76</v>
+        <v>26734.84</v>
       </c>
       <c r="O47" t="n">
-        <v>26563.85</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
+        <v>26770.12</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v/>
+      </c>
       <c r="W47" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr"/>
@@ -4473,61 +4475,61 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>26464.14</v>
+        <v>26150.75</v>
       </c>
       <c r="C48" t="n">
-        <v>26471.79</v>
+        <v>26206.13</v>
       </c>
       <c r="D48" t="n">
-        <v>26249.59</v>
+        <v>25916.76</v>
       </c>
       <c r="E48" t="n">
-        <v>26258.11</v>
+        <v>25970.11</v>
       </c>
       <c r="F48" t="n">
-        <v>-311.88</v>
+        <v>-288</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.011</v>
       </c>
       <c r="H48" t="n">
-        <v>222.2</v>
+        <v>289.37</v>
       </c>
       <c r="I48" t="n">
-        <v>26315.98</v>
+        <v>26027.39</v>
       </c>
       <c r="J48" t="n">
-        <v>26432.08</v>
+        <v>25984.62</v>
       </c>
       <c r="K48" t="n">
-        <v>26494.3</v>
+        <v>26147.01</v>
       </c>
       <c r="L48" t="n">
-        <v>26556.52</v>
+        <v>26309.4</v>
       </c>
       <c r="M48" t="n">
-        <v>26645.68</v>
+        <v>26369.21</v>
       </c>
       <c r="N48" t="n">
-        <v>26734.84</v>
+        <v>26429.02</v>
       </c>
       <c r="O48" t="n">
-        <v>26770.12</v>
+        <v>26693.99</v>
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -4547,7 +4549,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4557,66 +4559,62 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>26150.75</v>
+        <v>25886.67</v>
       </c>
       <c r="C49" t="n">
-        <v>26206.13</v>
+        <v>25924.21</v>
       </c>
       <c r="D49" t="n">
-        <v>25916.76</v>
+        <v>25727.93</v>
       </c>
       <c r="E49" t="n">
-        <v>25970.11</v>
+        <v>25839.33</v>
       </c>
       <c r="F49" t="n">
-        <v>-288</v>
+        <v>-130.78</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.005</v>
       </c>
       <c r="H49" t="n">
-        <v>289.37</v>
+        <v>196.28</v>
       </c>
       <c r="I49" t="n">
-        <v>26027.39</v>
+        <v>25627.39</v>
       </c>
       <c r="J49" t="n">
-        <v>25984.62</v>
+        <v>25635.07</v>
       </c>
       <c r="K49" t="n">
-        <v>26147.01</v>
+        <v>25825.42</v>
       </c>
       <c r="L49" t="n">
-        <v>26309.4</v>
+        <v>26015.78</v>
       </c>
       <c r="M49" t="n">
-        <v>26369.21</v>
+        <v>26114.79</v>
       </c>
       <c r="N49" t="n">
-        <v>26429.02</v>
+        <v>26213.81</v>
       </c>
       <c r="O49" t="n">
-        <v>26693.99</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="inlineStr">
+        <v>26495.5</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4631,7 +4629,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4641,50 +4639,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25886.67</v>
+        <v>25840.92</v>
       </c>
       <c r="C50" t="n">
-        <v>25924.21</v>
+        <v>26007.79</v>
       </c>
       <c r="D50" t="n">
-        <v>25727.93</v>
+        <v>25784.84</v>
       </c>
       <c r="E50" t="n">
-        <v>25839.33</v>
+        <v>26003.32</v>
       </c>
       <c r="F50" t="n">
-        <v>-130.78</v>
+        <v>163.99</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0063</v>
       </c>
       <c r="H50" t="n">
-        <v>196.28</v>
+        <v>222.95</v>
       </c>
       <c r="I50" t="n">
-        <v>25627.39</v>
+        <v>25531.65</v>
       </c>
       <c r="J50" t="n">
-        <v>25635.07</v>
+        <v>25649.68</v>
       </c>
       <c r="K50" t="n">
-        <v>25825.42</v>
+        <v>25741.19</v>
       </c>
       <c r="L50" t="n">
-        <v>26015.78</v>
+        <v>25832.7</v>
       </c>
       <c r="M50" t="n">
-        <v>26114.79</v>
+        <v>25937.47</v>
       </c>
       <c r="N50" t="n">
-        <v>26213.81</v>
+        <v>26042.24</v>
       </c>
       <c r="O50" t="n">
-        <v>26495.5</v>
+        <v>26120.49</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4692,79 +4690,85 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25840.92</v>
+        <v>25985.86</v>
       </c>
       <c r="C51" t="n">
-        <v>26007.79</v>
+        <v>26167.93</v>
       </c>
       <c r="D51" t="n">
-        <v>25784.84</v>
+        <v>25958.7</v>
       </c>
       <c r="E51" t="n">
-        <v>26003.32</v>
+        <v>26046.4</v>
       </c>
       <c r="F51" t="n">
-        <v>163.99</v>
+        <v>43.08</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0017</v>
       </c>
       <c r="H51" t="n">
-        <v>222.95</v>
+        <v>209.23</v>
       </c>
       <c r="I51" t="n">
-        <v>25531.65</v>
+        <v>25561.89</v>
       </c>
       <c r="J51" t="n">
-        <v>25649.68</v>
+        <v>25833.87</v>
       </c>
       <c r="K51" t="n">
-        <v>25741.19</v>
+        <v>25891.85</v>
       </c>
       <c r="L51" t="n">
-        <v>25832.7</v>
+        <v>25949.82</v>
       </c>
       <c r="M51" t="n">
-        <v>25937.47</v>
+        <v>26114.79</v>
       </c>
       <c r="N51" t="n">
-        <v>26042.24</v>
+        <v>26279.77</v>
       </c>
       <c r="O51" t="n">
-        <v>26120.49</v>
+        <v>26230.74</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4782,18 +4786,16 @@
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4807,50 +4809,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25985.86</v>
+        <v>26039.54</v>
       </c>
       <c r="C52" t="n">
-        <v>26167.93</v>
+        <v>26069.99</v>
       </c>
       <c r="D52" t="n">
-        <v>25958.7</v>
+        <v>25919.61</v>
       </c>
       <c r="E52" t="n">
-        <v>26046.4</v>
+        <v>26006.53</v>
       </c>
       <c r="F52" t="n">
-        <v>43.08</v>
+        <v>-39.87</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0015</v>
       </c>
       <c r="H52" t="n">
-        <v>209.23</v>
+        <v>150.38</v>
       </c>
       <c r="I52" t="n">
-        <v>25561.89</v>
+        <v>25749.47</v>
       </c>
       <c r="J52" t="n">
-        <v>25833.87</v>
+        <v>25828.71</v>
       </c>
       <c r="K52" t="n">
-        <v>25891.85</v>
+        <v>25941.79</v>
       </c>
       <c r="L52" t="n">
-        <v>25949.82</v>
+        <v>26054.86</v>
       </c>
       <c r="M52" t="n">
-        <v>26114.79</v>
+        <v>26151.02</v>
       </c>
       <c r="N52" t="n">
-        <v>26279.77</v>
+        <v>26247.17</v>
       </c>
       <c r="O52" t="n">
-        <v>26230.74</v>
+        <v>26377.16</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4858,18 +4860,18 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4877,79 +4879,77 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>26039.54</v>
+        <v>25897.22</v>
       </c>
       <c r="C53" t="n">
-        <v>26069.99</v>
+        <v>26026.78</v>
       </c>
       <c r="D53" t="n">
-        <v>25919.61</v>
+        <v>25799.66</v>
       </c>
       <c r="E53" t="n">
-        <v>26006.53</v>
+        <v>26007.63</v>
       </c>
       <c r="F53" t="n">
-        <v>-39.87</v>
+        <v>1.1</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>150.38</v>
+        <v>227.12</v>
       </c>
       <c r="I53" t="n">
-        <v>25749.47</v>
+        <v>25769.23</v>
       </c>
       <c r="J53" t="n">
-        <v>25828.71</v>
+        <v>25862.01</v>
       </c>
       <c r="K53" t="n">
-        <v>25941.79</v>
+        <v>25931.34</v>
       </c>
       <c r="L53" t="n">
-        <v>26054.86</v>
+        <v>26000.66</v>
       </c>
       <c r="M53" t="n">
-        <v>26151.02</v>
+        <v>26081.72</v>
       </c>
       <c r="N53" t="n">
-        <v>26247.17</v>
+        <v>26162.77</v>
       </c>
       <c r="O53" t="n">
-        <v>26377.16</v>
+        <v>26220.37</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4961,63 +4961,69 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25897.22</v>
+        <v>25870.98</v>
       </c>
       <c r="C54" t="n">
-        <v>26026.78</v>
+        <v>25909.66</v>
       </c>
       <c r="D54" t="n">
-        <v>25799.66</v>
+        <v>25512.39</v>
       </c>
       <c r="E54" t="n">
-        <v>26007.63</v>
+        <v>25576.45</v>
       </c>
       <c r="F54" t="n">
-        <v>1.1</v>
+        <v>-431.18</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0</v>
+        <v>-0.0166</v>
       </c>
       <c r="H54" t="n">
-        <v>227.12</v>
+        <v>397.27</v>
       </c>
       <c r="I54" t="n">
-        <v>25769.23</v>
+        <v>25572.54</v>
       </c>
       <c r="J54" t="n">
-        <v>25862.01</v>
+        <v>25827.72</v>
       </c>
       <c r="K54" t="n">
-        <v>25931.34</v>
+        <v>25894.07</v>
       </c>
       <c r="L54" t="n">
-        <v>26000.66</v>
+        <v>25960.43</v>
       </c>
       <c r="M54" t="n">
-        <v>26081.72</v>
+        <v>26121.19</v>
       </c>
       <c r="N54" t="n">
-        <v>26162.77</v>
+        <v>26281.96</v>
       </c>
       <c r="O54" t="n">
-        <v>26220.37</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
+        <v>26253.9</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
@@ -5029,9 +5035,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5043,80 +5049,72 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25870.98</v>
+        <v>25555.66</v>
       </c>
       <c r="C55" t="n">
-        <v>25909.66</v>
+        <v>25612.09</v>
       </c>
       <c r="D55" t="n">
-        <v>25512.39</v>
+        <v>25361.15</v>
       </c>
       <c r="E55" t="n">
-        <v>25576.45</v>
+        <v>25361.15</v>
       </c>
       <c r="F55" t="n">
-        <v>-431.18</v>
+        <v>-215.3</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>397.27</v>
+        <v>250.94</v>
       </c>
       <c r="I55" t="n">
-        <v>25572.54</v>
+        <v>25115.12</v>
       </c>
       <c r="J55" t="n">
-        <v>25827.72</v>
+        <v>25111.89</v>
       </c>
       <c r="K55" t="n">
-        <v>25894.07</v>
+        <v>25377.81</v>
       </c>
       <c r="L55" t="n">
-        <v>25960.43</v>
+        <v>25643.74</v>
       </c>
       <c r="M55" t="n">
-        <v>26121.19</v>
+        <v>25775.08</v>
       </c>
       <c r="N55" t="n">
-        <v>26281.96</v>
+        <v>25906.43</v>
       </c>
       <c r="O55" t="n">
-        <v>26253.9</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
+        <v>26306.93</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5131,7 +5129,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5141,50 +5139,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25555.66</v>
+        <v>25478.84</v>
       </c>
       <c r="C56" t="n">
-        <v>25612.09</v>
+        <v>25581.22</v>
       </c>
       <c r="D56" t="n">
-        <v>25361.15</v>
+        <v>25396.38</v>
       </c>
       <c r="E56" t="n">
-        <v>25361.15</v>
+        <v>25568.56</v>
       </c>
       <c r="F56" t="n">
-        <v>-215.3</v>
+        <v>207.41</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H56" t="n">
-        <v>250.94</v>
+        <v>184.84</v>
       </c>
       <c r="I56" t="n">
-        <v>25115.12</v>
+        <v>25110.21</v>
       </c>
       <c r="J56" t="n">
-        <v>25111.89</v>
+        <v>25047.48</v>
       </c>
       <c r="K56" t="n">
-        <v>25377.81</v>
+        <v>25235.68</v>
       </c>
       <c r="L56" t="n">
-        <v>25643.74</v>
+        <v>25423.89</v>
       </c>
       <c r="M56" t="n">
-        <v>25775.08</v>
+        <v>25486.62</v>
       </c>
       <c r="N56" t="n">
-        <v>25906.43</v>
+        <v>25549.35</v>
       </c>
       <c r="O56" t="n">
-        <v>26306.93</v>
+        <v>25863.03</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5192,172 +5190,178 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
       <c r="W56" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25478.84</v>
+        <v>25498.74</v>
       </c>
       <c r="C57" t="n">
-        <v>25581.22</v>
+        <v>25548.78</v>
       </c>
       <c r="D57" t="n">
-        <v>25396.38</v>
+        <v>25325.52</v>
       </c>
       <c r="E57" t="n">
-        <v>25568.56</v>
+        <v>25440.81</v>
       </c>
       <c r="F57" t="n">
-        <v>207.41</v>
+        <v>-127.75</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.005</v>
       </c>
       <c r="H57" t="n">
-        <v>184.84</v>
+        <v>223.26</v>
       </c>
       <c r="I57" t="n">
-        <v>25110.21</v>
+        <v>25211.54</v>
       </c>
       <c r="J57" t="n">
-        <v>25047.48</v>
+        <v>25423.6</v>
       </c>
       <c r="K57" t="n">
-        <v>25235.68</v>
+        <v>25476.14</v>
       </c>
       <c r="L57" t="n">
-        <v>25423.89</v>
+        <v>25528.68</v>
       </c>
       <c r="M57" t="n">
-        <v>25486.62</v>
+        <v>25660.98</v>
       </c>
       <c r="N57" t="n">
-        <v>25549.35</v>
+        <v>25793.28</v>
       </c>
       <c r="O57" t="n">
-        <v>25863.03</v>
+        <v>25766.06</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
+      <c r="Q57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>25498.74</v>
+        <v>25360.32</v>
       </c>
       <c r="C58" t="n">
-        <v>25548.78</v>
+        <v>25478.98</v>
       </c>
       <c r="D58" t="n">
-        <v>25325.52</v>
+        <v>25172.89</v>
       </c>
       <c r="E58" t="n">
-        <v>25440.81</v>
+        <v>25402.28</v>
       </c>
       <c r="F58" t="n">
-        <v>-127.75</v>
+        <v>-38.53</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.005</v>
+        <v>-0.0015</v>
       </c>
       <c r="H58" t="n">
-        <v>223.26</v>
+        <v>306.09</v>
       </c>
       <c r="I58" t="n">
-        <v>25211.54</v>
+        <v>25102.26</v>
       </c>
       <c r="J58" t="n">
-        <v>25423.6</v>
+        <v>25219.38</v>
       </c>
       <c r="K58" t="n">
-        <v>25476.14</v>
+        <v>25329.18</v>
       </c>
       <c r="L58" t="n">
-        <v>25528.68</v>
+        <v>25438.98</v>
       </c>
       <c r="M58" t="n">
-        <v>25660.98</v>
+        <v>25552.44</v>
       </c>
       <c r="N58" t="n">
-        <v>25793.28</v>
+        <v>25665.9</v>
       </c>
       <c r="O58" t="n">
-        <v>25766.06</v>
+        <v>25772.04</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
       <c r="Q58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
@@ -5367,7 +5371,7 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5379,7 +5383,7 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5393,71 +5397,69 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25360.32</v>
+        <v>25515.96</v>
       </c>
       <c r="C59" t="n">
-        <v>25478.98</v>
+        <v>25599.07</v>
       </c>
       <c r="D59" t="n">
-        <v>25172.89</v>
+        <v>25361.7</v>
       </c>
       <c r="E59" t="n">
-        <v>25402.28</v>
+        <v>25537.75</v>
       </c>
       <c r="F59" t="n">
-        <v>-38.53</v>
+        <v>135.47</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0053</v>
       </c>
       <c r="H59" t="n">
-        <v>306.09</v>
+        <v>237.37</v>
       </c>
       <c r="I59" t="n">
-        <v>25102.26</v>
+        <v>24866.8</v>
       </c>
       <c r="J59" t="n">
-        <v>25219.38</v>
+        <v>25134.36</v>
       </c>
       <c r="K59" t="n">
-        <v>25329.18</v>
+        <v>25249.23</v>
       </c>
       <c r="L59" t="n">
-        <v>25438.98</v>
+        <v>25364.11</v>
       </c>
       <c r="M59" t="n">
-        <v>25552.44</v>
+        <v>25555.32</v>
       </c>
       <c r="N59" t="n">
-        <v>25665.9</v>
+        <v>25746.54</v>
       </c>
       <c r="O59" t="n">
-        <v>25772.04</v>
+        <v>25785.07</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5465,64 +5467,60 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="11" t="inlineStr">
+      <c r="W59" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25515.96</v>
+        <v>25681.6</v>
       </c>
       <c r="C60" t="n">
-        <v>25599.07</v>
+        <v>25800.62</v>
       </c>
       <c r="D60" t="n">
-        <v>25361.7</v>
+        <v>25596.05</v>
       </c>
       <c r="E60" t="n">
-        <v>25537.75</v>
+        <v>25716.71</v>
       </c>
       <c r="F60" t="n">
-        <v>135.47</v>
+        <v>178.96</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0053</v>
+        <v>0.007</v>
       </c>
       <c r="H60" t="n">
-        <v>237.37</v>
+        <v>204.57</v>
       </c>
       <c r="I60" t="n">
-        <v>24866.8</v>
+        <v>25124.33</v>
       </c>
       <c r="J60" t="n">
-        <v>25134.36</v>
+        <v>25329.06</v>
       </c>
       <c r="K60" t="n">
-        <v>25249.23</v>
+        <v>25419.06</v>
       </c>
       <c r="L60" t="n">
-        <v>25364.11</v>
+        <v>25509.07</v>
       </c>
       <c r="M60" t="n">
-        <v>25555.32</v>
+        <v>25656.44</v>
       </c>
       <c r="N60" t="n">
-        <v>25746.54</v>
+        <v>25803.8</v>
       </c>
       <c r="O60" t="n">
-        <v>25785.07</v>
+        <v>25836.44</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5549,7 +5547,7 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="11" t="inlineStr">
+      <c r="W60" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5559,70 +5557,74 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>25681.6</v>
+        <v>25596.46</v>
       </c>
       <c r="C61" t="n">
-        <v>25800.62</v>
+        <v>25656.22</v>
       </c>
       <c r="D61" t="n">
-        <v>25596.05</v>
+        <v>25285.9</v>
       </c>
       <c r="E61" t="n">
-        <v>25716.71</v>
+        <v>25304.06</v>
       </c>
       <c r="F61" t="n">
-        <v>178.96</v>
+        <v>-412.65</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.007</v>
+        <v>-0.016</v>
       </c>
       <c r="H61" t="n">
-        <v>204.57</v>
+        <v>370.32</v>
       </c>
       <c r="I61" t="n">
-        <v>25124.33</v>
+        <v>25391.48</v>
       </c>
       <c r="J61" t="n">
-        <v>25329.06</v>
+        <v>25521.33</v>
       </c>
       <c r="K61" t="n">
-        <v>25419.06</v>
+        <v>25614.43</v>
       </c>
       <c r="L61" t="n">
-        <v>25509.07</v>
+        <v>25707.52</v>
       </c>
       <c r="M61" t="n">
-        <v>25656.44</v>
+        <v>25819</v>
       </c>
       <c r="N61" t="n">
-        <v>25803.8</v>
+        <v>25930.47</v>
       </c>
       <c r="O61" t="n">
-        <v>25836.44</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
+        <v>26005.19</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
       <c r="U61" s="8" t="n">
         <v/>
       </c>
@@ -5631,7 +5633,7 @@
       </c>
       <c r="W61" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X61" t="inlineStr"/>
@@ -5639,147 +5641,153 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>25596.46</v>
+        <v>25491.35</v>
       </c>
       <c r="C62" t="n">
-        <v>25656.22</v>
+        <v>25617.99</v>
       </c>
       <c r="D62" t="n">
-        <v>25285.9</v>
+        <v>25434.16</v>
       </c>
       <c r="E62" t="n">
-        <v>25304.06</v>
+        <v>25575.01</v>
       </c>
       <c r="F62" t="n">
-        <v>-412.65</v>
+        <v>270.95</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.016</v>
+        <v>0.0107</v>
       </c>
       <c r="H62" t="n">
-        <v>370.32</v>
+        <v>183.83</v>
       </c>
       <c r="I62" t="n">
-        <v>25391.48</v>
+        <v>24915.58</v>
       </c>
       <c r="J62" t="n">
-        <v>25521.33</v>
+        <v>24850.24</v>
       </c>
       <c r="K62" t="n">
-        <v>25614.43</v>
+        <v>25118.9</v>
       </c>
       <c r="L62" t="n">
-        <v>25707.52</v>
+        <v>25387.56</v>
       </c>
       <c r="M62" t="n">
-        <v>25819</v>
+        <v>25489.22</v>
       </c>
       <c r="N62" t="n">
-        <v>25930.47</v>
+        <v>25590.88</v>
       </c>
       <c r="O62" t="n">
-        <v>26005.19</v>
-      </c>
-      <c r="P62" s="6" t="inlineStr">
+        <v>26026.54</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="9" t="inlineStr">
+      <c r="W62" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>25491.35</v>
+        <v>25724.13</v>
       </c>
       <c r="C63" t="n">
-        <v>25617.99</v>
+        <v>25729.05</v>
       </c>
       <c r="D63" t="n">
-        <v>25434.16</v>
+        <v>25365.21</v>
       </c>
       <c r="E63" t="n">
-        <v>25575.01</v>
+        <v>25410.63</v>
       </c>
       <c r="F63" t="n">
-        <v>270.95</v>
+        <v>-164.38</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0064</v>
       </c>
       <c r="H63" t="n">
-        <v>183.83</v>
+        <v>363.84</v>
       </c>
       <c r="I63" t="n">
-        <v>24915.58</v>
+        <v>25250.33</v>
       </c>
       <c r="J63" t="n">
-        <v>24850.24</v>
+        <v>25415.65</v>
       </c>
       <c r="K63" t="n">
-        <v>25118.9</v>
+        <v>25483.09</v>
       </c>
       <c r="L63" t="n">
-        <v>25387.56</v>
+        <v>25550.54</v>
       </c>
       <c r="M63" t="n">
-        <v>25489.22</v>
+        <v>25666.92</v>
       </c>
       <c r="N63" t="n">
-        <v>25590.88</v>
+        <v>25783.31</v>
       </c>
       <c r="O63" t="n">
-        <v>26026.54</v>
+        <v>25801.82</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
       </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T63" s="8" t="inlineStr">
@@ -5787,39 +5795,37 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U63" s="8" t="n">
+        <v/>
       </c>
       <c r="V63" s="8" t="n">
         <v/>
       </c>
-      <c r="W63" s="9" t="inlineStr">
+      <c r="W63" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>25724.13</v>
+        <v>25263.11</v>
       </c>
       <c r="C64" t="n">
-        <v>25729.05</v>
+        <v>25424.21</v>
       </c>
       <c r="D64" t="n">
-        <v>25365.21</v>
+        <v>25164.2</v>
       </c>
       <c r="E64" t="n">
         <v/>
@@ -5831,38 +5837,36 @@
         <v/>
       </c>
       <c r="H64" t="n">
-        <v>363.84</v>
+        <v>260.01</v>
       </c>
       <c r="I64" t="n">
-        <v>25250.33</v>
+        <v>25001.37</v>
       </c>
       <c r="J64" t="n">
-        <v>25415.65</v>
+        <v>24978.54</v>
       </c>
       <c r="K64" t="n">
-        <v>25483.09</v>
+        <v>25228.71</v>
       </c>
       <c r="L64" t="n">
-        <v>25550.54</v>
+        <v>25478.88</v>
       </c>
       <c r="M64" t="n">
-        <v>25666.92</v>
+        <v>25592.55</v>
       </c>
       <c r="N64" t="n">
-        <v>25783.31</v>
+        <v>25706.22</v>
       </c>
       <c r="O64" t="n">
-        <v>25801.82</v>
+        <v>26092.89</v>
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q64" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q64" s="6" t="n">
+        <v/>
       </c>
       <c r="R64" s="6" t="inlineStr">
         <is>
@@ -5874,10 +5878,8 @@
           <t>=</t>
         </is>
       </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T64" s="8" t="n">
+        <v/>
       </c>
       <c r="U64" s="8" t="n">
         <v/>
@@ -5885,16 +5887,12 @@
       <c r="V64" s="8" t="n">
         <v/>
       </c>
-      <c r="W64" s="9" t="inlineStr">
+      <c r="W64" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -104,20 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -483,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -637,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24724.34</v>
+        <v>24815.22</v>
       </c>
       <c r="C2" t="n">
-        <v>24762.24</v>
+        <v>25024.27</v>
       </c>
       <c r="D2" t="n">
-        <v>24556.78</v>
+        <v>24794.84</v>
       </c>
       <c r="E2" t="n">
-        <v>24626.89</v>
+        <v>24995.81</v>
       </c>
       <c r="F2" t="n">
-        <v>-44.33</v>
+        <v>368.92</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.015</v>
       </c>
       <c r="H2" t="n">
-        <v>205.46</v>
+        <v>229.43</v>
       </c>
       <c r="I2" t="n">
-        <v>24225.77</v>
+        <v>24351.32</v>
       </c>
       <c r="J2" t="n">
-        <v>24330.57</v>
+        <v>24405.12</v>
       </c>
       <c r="K2" t="n">
-        <v>24510.25</v>
+        <v>24524.16</v>
       </c>
       <c r="L2" t="n">
-        <v>24689.94</v>
+        <v>24643.2</v>
       </c>
       <c r="M2" t="n">
-        <v>24832.19</v>
+        <v>24729.62</v>
       </c>
       <c r="N2" t="n">
-        <v>24974.43</v>
+        <v>24816.04</v>
       </c>
       <c r="O2" t="n">
-        <v>25191.56</v>
+        <v>24967.7</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -693,76 +690,78 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24815.22</v>
+        <v>25028.93</v>
       </c>
       <c r="C3" t="n">
-        <v>25024.27</v>
+        <v>25095.66</v>
       </c>
       <c r="D3" t="n">
-        <v>24794.84</v>
+        <v>24887</v>
       </c>
       <c r="E3" t="n">
-        <v>24995.81</v>
+        <v>25040.28</v>
       </c>
       <c r="F3" t="n">
-        <v>368.92</v>
+        <v>44.47</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.015</v>
+        <v>0.0018</v>
       </c>
       <c r="H3" t="n">
-        <v>229.43</v>
+        <v>208.66</v>
       </c>
       <c r="I3" t="n">
-        <v>24351.32</v>
+        <v>24565.41</v>
       </c>
       <c r="J3" t="n">
-        <v>24405.12</v>
+        <v>24809.51</v>
       </c>
       <c r="K3" t="n">
-        <v>24524.16</v>
+        <v>24881.1</v>
       </c>
       <c r="L3" t="n">
-        <v>24643.2</v>
+        <v>24952.68</v>
       </c>
       <c r="M3" t="n">
-        <v>24729.62</v>
+        <v>25110.53</v>
       </c>
       <c r="N3" t="n">
-        <v>24816.04</v>
+        <v>25268.37</v>
       </c>
       <c r="O3" t="n">
-        <v>24967.7</v>
+        <v>25253.7</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -773,25 +772,21 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
@@ -803,50 +798,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25028.93</v>
+        <v>25025.13</v>
       </c>
       <c r="C4" t="n">
-        <v>25095.66</v>
+        <v>25655.82</v>
       </c>
       <c r="D4" t="n">
-        <v>24887</v>
+        <v>24994.64</v>
       </c>
       <c r="E4" t="n">
-        <v>25040.28</v>
+        <v>25580.88</v>
       </c>
       <c r="F4" t="n">
-        <v>44.47</v>
+        <v>540.6</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0216</v>
       </c>
       <c r="H4" t="n">
-        <v>208.66</v>
+        <v>661.1799999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>24565.41</v>
+        <v>24678.34</v>
       </c>
       <c r="J4" t="n">
-        <v>24809.51</v>
+        <v>24856.09</v>
       </c>
       <c r="K4" t="n">
-        <v>24881.1</v>
+        <v>24935.95</v>
       </c>
       <c r="L4" t="n">
-        <v>24952.68</v>
+        <v>25015.8</v>
       </c>
       <c r="M4" t="n">
-        <v>25110.53</v>
+        <v>25144.61</v>
       </c>
       <c r="N4" t="n">
-        <v>25268.37</v>
+        <v>25273.41</v>
       </c>
       <c r="O4" t="n">
-        <v>25253.7</v>
+        <v>25304.32</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -857,21 +852,25 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
@@ -883,50 +882,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25025.13</v>
+        <v>25763.97</v>
       </c>
       <c r="C5" t="n">
-        <v>25655.82</v>
+        <v>25826.78</v>
       </c>
       <c r="D5" t="n">
-        <v>24994.64</v>
+        <v>25611.69</v>
       </c>
       <c r="E5" t="n">
-        <v>25580.88</v>
+        <v>25779.31</v>
       </c>
       <c r="F5" t="n">
-        <v>540.6</v>
+        <v>198.43</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0216</v>
+        <v>0.0078</v>
       </c>
       <c r="H5" t="n">
-        <v>661.1799999999999</v>
+        <v>215.09</v>
       </c>
       <c r="I5" t="n">
-        <v>24678.34</v>
+        <v>24333.46</v>
       </c>
       <c r="J5" t="n">
-        <v>24856.09</v>
+        <v>25047.53</v>
       </c>
       <c r="K5" t="n">
-        <v>24935.95</v>
+        <v>25250.29</v>
       </c>
       <c r="L5" t="n">
-        <v>25015.8</v>
+        <v>25453.06</v>
       </c>
       <c r="M5" t="n">
-        <v>25144.61</v>
+        <v>25911.47</v>
       </c>
       <c r="N5" t="n">
-        <v>25273.41</v>
+        <v>26369.89</v>
       </c>
       <c r="O5" t="n">
-        <v>25304.32</v>
+        <v>26317</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -937,25 +936,21 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
@@ -967,50 +962,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25763.97</v>
+        <v>25811.9</v>
       </c>
       <c r="C6" t="n">
-        <v>25826.78</v>
+        <v>25900.1</v>
       </c>
       <c r="D6" t="n">
-        <v>25611.69</v>
+        <v>25698.56</v>
       </c>
       <c r="E6" t="n">
-        <v>25779.31</v>
+        <v>25817.89</v>
       </c>
       <c r="F6" t="n">
-        <v>198.43</v>
+        <v>38.58</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0078</v>
+        <v>0.0015</v>
       </c>
       <c r="H6" t="n">
-        <v>215.09</v>
+        <v>201.54</v>
       </c>
       <c r="I6" t="n">
-        <v>24333.46</v>
+        <v>25396.6</v>
       </c>
       <c r="J6" t="n">
-        <v>25047.53</v>
+        <v>25594.26</v>
       </c>
       <c r="K6" t="n">
-        <v>25250.29</v>
+        <v>25671.77</v>
       </c>
       <c r="L6" t="n">
-        <v>25453.06</v>
+        <v>25749.27</v>
       </c>
       <c r="M6" t="n">
-        <v>25911.47</v>
+        <v>25886.86</v>
       </c>
       <c r="N6" t="n">
-        <v>26369.89</v>
+        <v>26024.44</v>
       </c>
       <c r="O6" t="n">
-        <v>26317</v>
+        <v>26041.87</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1021,14 +1016,14 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U6" s="8" t="n">
@@ -1047,69 +1042,73 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25811.9</v>
+        <v>25770.45</v>
       </c>
       <c r="C7" t="n">
-        <v>25900.1</v>
+        <v>25811.97</v>
       </c>
       <c r="D7" t="n">
-        <v>25698.56</v>
+        <v>25465.12</v>
       </c>
       <c r="E7" t="n">
-        <v>25817.89</v>
+        <v>25465.25</v>
       </c>
       <c r="F7" t="n">
-        <v>38.58</v>
+        <v>-352.64</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0137</v>
       </c>
       <c r="H7" t="n">
-        <v>201.54</v>
+        <v>346.85</v>
       </c>
       <c r="I7" t="n">
-        <v>25396.6</v>
+        <v>25497.02</v>
       </c>
       <c r="J7" t="n">
-        <v>25594.26</v>
+        <v>25625.63</v>
       </c>
       <c r="K7" t="n">
-        <v>25671.77</v>
+        <v>25717.12</v>
       </c>
       <c r="L7" t="n">
-        <v>25749.27</v>
+        <v>25808.61</v>
       </c>
       <c r="M7" t="n">
-        <v>25886.86</v>
+        <v>25918.66</v>
       </c>
       <c r="N7" t="n">
-        <v>26024.44</v>
+        <v>26028.71</v>
       </c>
       <c r="O7" t="n">
-        <v>26041.87</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+        <v>26101.64</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1117,9 +1116,9 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W7" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
@@ -1127,67 +1126,67 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25770.45</v>
+        <v>25274.94</v>
       </c>
       <c r="C8" t="n">
-        <v>25811.97</v>
+        <v>25280.16</v>
       </c>
       <c r="D8" t="n">
-        <v>25465.12</v>
+        <v>24830.17</v>
       </c>
       <c r="E8" t="n">
-        <v>25465.25</v>
+        <v>24897.45</v>
       </c>
       <c r="F8" t="n">
-        <v>-352.64</v>
+        <v>-567.8</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0223</v>
       </c>
       <c r="H8" t="n">
-        <v>346.85</v>
+        <v>449.99</v>
       </c>
       <c r="I8" t="n">
-        <v>25497.02</v>
+        <v>25118.27</v>
       </c>
       <c r="J8" t="n">
-        <v>25625.63</v>
+        <v>25031.75</v>
       </c>
       <c r="K8" t="n">
-        <v>25717.12</v>
+        <v>25291.82</v>
       </c>
       <c r="L8" t="n">
-        <v>25808.61</v>
+        <v>25551.9</v>
       </c>
       <c r="M8" t="n">
-        <v>25918.66</v>
+        <v>25638.68</v>
       </c>
       <c r="N8" t="n">
-        <v>26028.71</v>
+        <v>25725.45</v>
       </c>
       <c r="O8" t="n">
-        <v>26101.64</v>
+        <v>26158.82</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1211,74 +1210,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25274.94</v>
+        <v>25097.48</v>
       </c>
       <c r="C9" t="n">
-        <v>25280.16</v>
+        <v>25127.76</v>
       </c>
       <c r="D9" t="n">
-        <v>24830.17</v>
+        <v>24867.32</v>
       </c>
       <c r="E9" t="n">
-        <v>24897.45</v>
+        <v>25118.27</v>
       </c>
       <c r="F9" t="n">
-        <v>-567.8</v>
+        <v>220.82</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0089</v>
       </c>
       <c r="H9" t="n">
-        <v>449.99</v>
+        <v>260.44</v>
       </c>
       <c r="I9" t="n">
-        <v>25118.27</v>
+        <v>24380.18</v>
       </c>
       <c r="J9" t="n">
-        <v>25031.75</v>
+        <v>24368.6</v>
       </c>
       <c r="K9" t="n">
-        <v>25291.82</v>
+        <v>24672.45</v>
       </c>
       <c r="L9" t="n">
-        <v>25551.9</v>
+        <v>24976.31</v>
       </c>
       <c r="M9" t="n">
-        <v>25638.68</v>
+        <v>25122.44</v>
       </c>
       <c r="N9" t="n">
-        <v>25725.45</v>
+        <v>25268.58</v>
       </c>
       <c r="O9" t="n">
-        <v>26158.82</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
+        <v>25730.15</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1290,55 +1285,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25097.48</v>
+        <v>25081.19</v>
       </c>
       <c r="C10" t="n">
-        <v>25127.76</v>
+        <v>25195.83</v>
       </c>
       <c r="D10" t="n">
-        <v>24867.32</v>
+        <v>24937.52</v>
       </c>
       <c r="E10" t="n">
-        <v>25118.27</v>
+        <v>25067.09</v>
       </c>
       <c r="F10" t="n">
-        <v>220.82</v>
+        <v>-51.18</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.002</v>
       </c>
       <c r="H10" t="n">
-        <v>260.44</v>
+        <v>258.31</v>
       </c>
       <c r="I10" t="n">
-        <v>24380.18</v>
+        <v>24606.88</v>
       </c>
       <c r="J10" t="n">
-        <v>24368.6</v>
+        <v>24918.19</v>
       </c>
       <c r="K10" t="n">
-        <v>24672.45</v>
+        <v>24988.05</v>
       </c>
       <c r="L10" t="n">
-        <v>24976.31</v>
+        <v>25057.9</v>
       </c>
       <c r="M10" t="n">
-        <v>25122.44</v>
+        <v>25248.49</v>
       </c>
       <c r="N10" t="n">
-        <v>25268.58</v>
+        <v>25439.07</v>
       </c>
       <c r="O10" t="n">
-        <v>25730.15</v>
+        <v>25388.2</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1346,18 +1345,18 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1379,50 +1378,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25081.19</v>
+        <v>24963.8</v>
       </c>
       <c r="C11" t="n">
-        <v>25195.83</v>
+        <v>25154.58</v>
       </c>
       <c r="D11" t="n">
-        <v>24937.52</v>
+        <v>24963.8</v>
       </c>
       <c r="E11" t="n">
-        <v>25067.09</v>
+        <v>25114.25</v>
       </c>
       <c r="F11" t="n">
-        <v>-51.18</v>
+        <v>47.16</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="H11" t="n">
-        <v>258.31</v>
+        <v>190.78</v>
       </c>
       <c r="I11" t="n">
-        <v>24606.88</v>
+        <v>24679.21</v>
       </c>
       <c r="J11" t="n">
-        <v>24918.19</v>
+        <v>24808.99</v>
       </c>
       <c r="K11" t="n">
-        <v>24988.05</v>
+        <v>24937.93</v>
       </c>
       <c r="L11" t="n">
-        <v>25057.9</v>
+        <v>25066.88</v>
       </c>
       <c r="M11" t="n">
-        <v>25248.49</v>
+        <v>25196.25</v>
       </c>
       <c r="N11" t="n">
-        <v>25439.07</v>
+        <v>25325.61</v>
       </c>
       <c r="O11" t="n">
-        <v>25388.2</v>
+        <v>25454.14</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1430,12 +1429,10 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1463,61 +1460,65 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24963.8</v>
+        <v>24932.62</v>
       </c>
       <c r="C12" t="n">
-        <v>25154.58</v>
+        <v>25204.68</v>
       </c>
       <c r="D12" t="n">
-        <v>24963.8</v>
+        <v>24869.25</v>
       </c>
       <c r="E12" t="n">
-        <v>25114.25</v>
+        <v>25147.03</v>
       </c>
       <c r="F12" t="n">
-        <v>47.16</v>
+        <v>32.78</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0013</v>
       </c>
       <c r="H12" t="n">
-        <v>190.78</v>
+        <v>335.43</v>
       </c>
       <c r="I12" t="n">
-        <v>24679.21</v>
+        <v>24773.02</v>
       </c>
       <c r="J12" t="n">
-        <v>24808.99</v>
+        <v>24951</v>
       </c>
       <c r="K12" t="n">
-        <v>24937.93</v>
+        <v>25018.86</v>
       </c>
       <c r="L12" t="n">
-        <v>25066.88</v>
+        <v>25086.72</v>
       </c>
       <c r="M12" t="n">
-        <v>25196.25</v>
+        <v>25209.64</v>
       </c>
       <c r="N12" t="n">
-        <v>25325.61</v>
+        <v>25332.56</v>
       </c>
       <c r="O12" t="n">
-        <v>25454.14</v>
+        <v>25345.36</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1545,50 +1546,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24932.62</v>
+        <v>24970.05</v>
       </c>
       <c r="C13" t="n">
-        <v>25204.68</v>
+        <v>25055.48</v>
       </c>
       <c r="D13" t="n">
-        <v>24869.25</v>
+        <v>24839.23</v>
       </c>
       <c r="E13" t="n">
-        <v>25147.03</v>
+        <v>24999.53</v>
       </c>
       <c r="F13" t="n">
-        <v>32.78</v>
+        <v>-147.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0059</v>
       </c>
       <c r="H13" t="n">
-        <v>335.43</v>
+        <v>216.25</v>
       </c>
       <c r="I13" t="n">
-        <v>24773.02</v>
+        <v>24533.82</v>
       </c>
       <c r="J13" t="n">
-        <v>24951</v>
+        <v>24866.63</v>
       </c>
       <c r="K13" t="n">
-        <v>25018.86</v>
+        <v>24979.31</v>
       </c>
       <c r="L13" t="n">
-        <v>25086.72</v>
+        <v>25092</v>
       </c>
       <c r="M13" t="n">
-        <v>25209.64</v>
+        <v>25314.74</v>
       </c>
       <c r="N13" t="n">
-        <v>25332.56</v>
+        <v>25537.49</v>
       </c>
       <c r="O13" t="n">
-        <v>25345.36</v>
+        <v>25540.11</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1600,12 +1601,12 @@
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1622,59 +1623,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24970.05</v>
+        <v>25018.95</v>
       </c>
       <c r="C14" t="n">
-        <v>25055.48</v>
+        <v>25021.51</v>
       </c>
       <c r="D14" t="n">
-        <v>24839.23</v>
+        <v>24696.17</v>
       </c>
       <c r="E14" t="n">
-        <v>24999.53</v>
+        <v>24915.49</v>
       </c>
       <c r="F14" t="n">
-        <v>-147.5</v>
+        <v>-84.04000000000001</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0059</v>
+        <v>-0.0034</v>
       </c>
       <c r="H14" t="n">
-        <v>216.25</v>
+        <v>325.34</v>
       </c>
       <c r="I14" t="n">
-        <v>24533.82</v>
+        <v>24622.98</v>
       </c>
       <c r="J14" t="n">
-        <v>24866.63</v>
+        <v>24809.37</v>
       </c>
       <c r="K14" t="n">
-        <v>24979.31</v>
+        <v>24891.4</v>
       </c>
       <c r="L14" t="n">
-        <v>25092</v>
+        <v>24973.44</v>
       </c>
       <c r="M14" t="n">
-        <v>25314.74</v>
+        <v>25107.65</v>
       </c>
       <c r="N14" t="n">
-        <v>25537.49</v>
+        <v>25241.87</v>
       </c>
       <c r="O14" t="n">
-        <v>25540.11</v>
+        <v>25271.73</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1689,7 +1686,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1713,67 +1710,65 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25018.95</v>
+        <v>24755.09</v>
       </c>
       <c r="C15" t="n">
-        <v>25021.51</v>
+        <v>24850.75</v>
       </c>
       <c r="D15" t="n">
-        <v>24696.17</v>
+        <v>24651.34</v>
       </c>
       <c r="E15" t="n">
-        <v>24915.49</v>
+        <v>24830.98</v>
       </c>
       <c r="F15" t="n">
-        <v>-84.04000000000001</v>
+        <v>-84.51000000000001</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>-0.0034</v>
       </c>
       <c r="H15" t="n">
-        <v>325.34</v>
+        <v>199.41</v>
       </c>
       <c r="I15" t="n">
-        <v>24622.98</v>
+        <v>24370.83</v>
       </c>
       <c r="J15" t="n">
-        <v>24809.37</v>
+        <v>24618.48</v>
       </c>
       <c r="K15" t="n">
-        <v>24891.4</v>
+        <v>24752.82</v>
       </c>
       <c r="L15" t="n">
-        <v>24973.44</v>
+        <v>24887.17</v>
       </c>
       <c r="M15" t="n">
-        <v>25107.65</v>
+        <v>25078.16</v>
       </c>
       <c r="N15" t="n">
-        <v>25241.87</v>
+        <v>25269.16</v>
       </c>
       <c r="O15" t="n">
-        <v>25271.73</v>
+        <v>25346.85</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q15" s="6" t="n">
+        <v/>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1795,50 +1790,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24755.09</v>
+        <v>24769.15</v>
       </c>
       <c r="C16" t="n">
-        <v>24850.75</v>
+        <v>24974.53</v>
       </c>
       <c r="D16" t="n">
-        <v>24651.34</v>
+        <v>24751.13</v>
       </c>
       <c r="E16" t="n">
-        <v>24830.98</v>
+        <v>24846.69</v>
       </c>
       <c r="F16" t="n">
-        <v>-84.51000000000001</v>
+        <v>15.71</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>199.41</v>
+        <v>223.4</v>
       </c>
       <c r="I16" t="n">
-        <v>24370.83</v>
+        <v>24451.93</v>
       </c>
       <c r="J16" t="n">
-        <v>24618.48</v>
+        <v>24671.54</v>
       </c>
       <c r="K16" t="n">
-        <v>24752.82</v>
+        <v>24731.28</v>
       </c>
       <c r="L16" t="n">
-        <v>24887.17</v>
+        <v>24791.01</v>
       </c>
       <c r="M16" t="n">
-        <v>25078.16</v>
+        <v>24930.69</v>
       </c>
       <c r="N16" t="n">
-        <v>25269.16</v>
+        <v>25070.36</v>
       </c>
       <c r="O16" t="n">
-        <v>25346.85</v>
+        <v>25050.16</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1846,18 +1841,18 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R16" s="6" t="n">
+        <v/>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1870,55 +1865,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24769.15</v>
+        <v>24922.1</v>
       </c>
       <c r="C17" t="n">
-        <v>24974.53</v>
+        <v>25011.35</v>
       </c>
       <c r="D17" t="n">
-        <v>24751.13</v>
+        <v>24817.34</v>
       </c>
       <c r="E17" t="n">
-        <v>24846.69</v>
+        <v>25011.35</v>
       </c>
       <c r="F17" t="n">
-        <v>15.71</v>
+        <v>164.66</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0066</v>
       </c>
       <c r="H17" t="n">
-        <v>223.4</v>
+        <v>194.01</v>
       </c>
       <c r="I17" t="n">
-        <v>24451.93</v>
+        <v>24527.73</v>
       </c>
       <c r="J17" t="n">
-        <v>24671.54</v>
+        <v>24615.22</v>
       </c>
       <c r="K17" t="n">
-        <v>24731.28</v>
+        <v>24734.99</v>
       </c>
       <c r="L17" t="n">
-        <v>24791.01</v>
+        <v>24854.76</v>
       </c>
       <c r="M17" t="n">
-        <v>24930.69</v>
+        <v>24958.39</v>
       </c>
       <c r="N17" t="n">
-        <v>25070.36</v>
+        <v>25062.02</v>
       </c>
       <c r="O17" t="n">
-        <v>25050.16</v>
+        <v>25197.93</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1929,9 +1928,9 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
@@ -1939,8 +1938,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1959,50 +1960,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24922.1</v>
+        <v>25001.31</v>
       </c>
       <c r="C18" t="n">
-        <v>25011.35</v>
+        <v>25271.34</v>
       </c>
       <c r="D18" t="n">
-        <v>24817.34</v>
+        <v>24984.27</v>
       </c>
       <c r="E18" t="n">
-        <v>25011.35</v>
+        <v>25155.41</v>
       </c>
       <c r="F18" t="n">
-        <v>164.66</v>
+        <v>144.06</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0058</v>
       </c>
       <c r="H18" t="n">
-        <v>194.01</v>
+        <v>287.07</v>
       </c>
       <c r="I18" t="n">
-        <v>24527.73</v>
+        <v>24623.33</v>
       </c>
       <c r="J18" t="n">
-        <v>24615.22</v>
+        <v>24865.84</v>
       </c>
       <c r="K18" t="n">
-        <v>24734.99</v>
+        <v>24914.34</v>
       </c>
       <c r="L18" t="n">
-        <v>24854.76</v>
+        <v>24962.85</v>
       </c>
       <c r="M18" t="n">
-        <v>24958.39</v>
+        <v>25108.35</v>
       </c>
       <c r="N18" t="n">
-        <v>25062.02</v>
+        <v>25253.86</v>
       </c>
       <c r="O18" t="n">
-        <v>25197.93</v>
+        <v>25205.36</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2013,23 +2014,25 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U18" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W18" s="11" t="inlineStr">
         <is>
@@ -2045,171 +2048,165 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25001.31</v>
+        <v>24994.05</v>
       </c>
       <c r="C19" t="n">
-        <v>25271.34</v>
+        <v>25074.28</v>
       </c>
       <c r="D19" t="n">
-        <v>24984.27</v>
+        <v>24696.59</v>
       </c>
       <c r="E19" t="n">
-        <v>25155.41</v>
+        <v>24763.12</v>
       </c>
       <c r="F19" t="n">
-        <v>144.06</v>
+        <v>-392.29</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0156</v>
       </c>
       <c r="H19" t="n">
-        <v>287.07</v>
+        <v>377.69</v>
       </c>
       <c r="I19" t="n">
-        <v>24623.33</v>
+        <v>24697.2</v>
       </c>
       <c r="J19" t="n">
-        <v>24865.84</v>
+        <v>24882.14</v>
       </c>
       <c r="K19" t="n">
-        <v>24914.34</v>
+        <v>25011.88</v>
       </c>
       <c r="L19" t="n">
-        <v>24962.85</v>
+        <v>25141.61</v>
       </c>
       <c r="M19" t="n">
-        <v>25108.35</v>
+        <v>25298.95</v>
       </c>
       <c r="N19" t="n">
-        <v>25253.86</v>
+        <v>25456.28</v>
       </c>
       <c r="O19" t="n">
-        <v>25205.36</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+        <v>25558.41</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24994.05</v>
+        <v>24830.41</v>
       </c>
       <c r="C20" t="n">
-        <v>25074.28</v>
+        <v>25099.68</v>
       </c>
       <c r="D20" t="n">
-        <v>24696.59</v>
+        <v>24821.67</v>
       </c>
       <c r="E20" t="n">
-        <v>24763.12</v>
+        <v>25099</v>
       </c>
       <c r="F20" t="n">
-        <v>-392.29</v>
+        <v>335.88</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0136</v>
       </c>
       <c r="H20" t="n">
-        <v>377.69</v>
+        <v>278.01</v>
       </c>
       <c r="I20" t="n">
-        <v>24697.2</v>
+        <v>24318.9</v>
       </c>
       <c r="J20" t="n">
-        <v>24882.14</v>
+        <v>24324.27</v>
       </c>
       <c r="K20" t="n">
-        <v>25011.88</v>
+        <v>24574.27</v>
       </c>
       <c r="L20" t="n">
-        <v>25141.61</v>
+        <v>24824.28</v>
       </c>
       <c r="M20" t="n">
-        <v>25298.95</v>
+        <v>24951.96</v>
       </c>
       <c r="N20" t="n">
-        <v>25456.28</v>
+        <v>25079.65</v>
       </c>
       <c r="O20" t="n">
-        <v>25558.41</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
+        <v>25451.97</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -2217,50 +2214,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24830.41</v>
+        <v>25459.32</v>
       </c>
       <c r="C21" t="n">
-        <v>25099.68</v>
+        <v>25560.4</v>
       </c>
       <c r="D21" t="n">
-        <v>24821.67</v>
+        <v>25361.03</v>
       </c>
       <c r="E21" t="n">
-        <v>25099</v>
+        <v>25361.03</v>
       </c>
       <c r="F21" t="n">
-        <v>335.88</v>
+        <v>262.03</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0104</v>
       </c>
       <c r="H21" t="n">
-        <v>278.01</v>
+        <v>199.37</v>
       </c>
       <c r="I21" t="n">
-        <v>24318.9</v>
+        <v>24543.66</v>
       </c>
       <c r="J21" t="n">
-        <v>24324.27</v>
+        <v>24890.15</v>
       </c>
       <c r="K21" t="n">
-        <v>24574.27</v>
+        <v>24960</v>
       </c>
       <c r="L21" t="n">
-        <v>24824.28</v>
+        <v>25029.84</v>
       </c>
       <c r="M21" t="n">
-        <v>24951.96</v>
+        <v>25238</v>
       </c>
       <c r="N21" t="n">
-        <v>25079.65</v>
+        <v>25446.17</v>
       </c>
       <c r="O21" t="n">
-        <v>25451.97</v>
+        <v>25377.69</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2271,7 +2268,7 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2283,11 +2280,13 @@
       </c>
       <c r="U21" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
@@ -2299,50 +2298,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25459.32</v>
+        <v>25496.13</v>
       </c>
       <c r="C22" t="n">
-        <v>25560.4</v>
+        <v>25553.47</v>
       </c>
       <c r="D22" t="n">
-        <v>25361.03</v>
+        <v>25307.17</v>
       </c>
       <c r="E22" t="n">
-        <v>25361.03</v>
+        <v>25464.01</v>
       </c>
       <c r="F22" t="n">
-        <v>262.03</v>
+        <v>102.98</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0104</v>
+        <v>0.0041</v>
       </c>
       <c r="H22" t="n">
-        <v>199.37</v>
+        <v>246.3</v>
       </c>
       <c r="I22" t="n">
-        <v>24543.66</v>
+        <v>25161.66</v>
       </c>
       <c r="J22" t="n">
-        <v>24890.15</v>
+        <v>25111.82</v>
       </c>
       <c r="K22" t="n">
-        <v>24960</v>
+        <v>25261.34</v>
       </c>
       <c r="L22" t="n">
-        <v>25029.84</v>
+        <v>25410.87</v>
       </c>
       <c r="M22" t="n">
-        <v>25238</v>
+        <v>25460.71</v>
       </c>
       <c r="N22" t="n">
-        <v>25446.17</v>
+        <v>25510.56</v>
       </c>
       <c r="O22" t="n">
-        <v>25377.69</v>
+        <v>25759.77</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2353,14 +2352,14 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U22" s="8" t="inlineStr">
@@ -2368,65 +2367,67 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25496.13</v>
+        <v>25551.97</v>
       </c>
       <c r="C23" t="n">
-        <v>25553.47</v>
+        <v>25571.45</v>
       </c>
       <c r="D23" t="n">
-        <v>25307.17</v>
+        <v>25336.39</v>
       </c>
       <c r="E23" t="n">
-        <v>25464.01</v>
+        <v>25460.48</v>
       </c>
       <c r="F23" t="n">
-        <v>102.98</v>
+        <v>-3.53</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0001</v>
       </c>
       <c r="H23" t="n">
-        <v>246.3</v>
+        <v>235.06</v>
       </c>
       <c r="I23" t="n">
-        <v>25161.66</v>
+        <v>25060.87</v>
       </c>
       <c r="J23" t="n">
-        <v>25111.82</v>
+        <v>25234.55</v>
       </c>
       <c r="K23" t="n">
-        <v>25261.34</v>
+        <v>25340.86</v>
       </c>
       <c r="L23" t="n">
-        <v>25410.87</v>
+        <v>25447.17</v>
       </c>
       <c r="M23" t="n">
-        <v>25460.71</v>
+        <v>25587.16</v>
       </c>
       <c r="N23" t="n">
-        <v>25510.56</v>
+        <v>25727.16</v>
       </c>
       <c r="O23" t="n">
-        <v>25759.77</v>
+        <v>25799.77</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2434,23 +2435,21 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2462,57 +2461,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25551.97</v>
+        <v>25487.45</v>
       </c>
       <c r="C24" t="n">
-        <v>25571.45</v>
+        <v>25651.16</v>
       </c>
       <c r="D24" t="n">
-        <v>25336.39</v>
+        <v>25303.11</v>
       </c>
       <c r="E24" t="n">
-        <v>25460.48</v>
+        <v>25612.03</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.53</v>
+        <v>151.55</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.006</v>
       </c>
       <c r="H24" t="n">
-        <v>235.06</v>
+        <v>348.05</v>
       </c>
       <c r="I24" t="n">
-        <v>25060.87</v>
+        <v>25101.33</v>
       </c>
       <c r="J24" t="n">
-        <v>25234.55</v>
+        <v>25228.7</v>
       </c>
       <c r="K24" t="n">
-        <v>25340.86</v>
+        <v>25342.95</v>
       </c>
       <c r="L24" t="n">
-        <v>25447.17</v>
+        <v>25457.2</v>
       </c>
       <c r="M24" t="n">
-        <v>25587.16</v>
+        <v>25578.01</v>
       </c>
       <c r="N24" t="n">
-        <v>25727.16</v>
+        <v>25698.82</v>
       </c>
       <c r="O24" t="n">
-        <v>25799.77</v>
+        <v>25806.51</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2525,13 +2524,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2553,50 +2554,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25487.45</v>
+        <v>25709.37</v>
       </c>
       <c r="C25" t="n">
-        <v>25651.16</v>
+        <v>25891.51</v>
       </c>
       <c r="D25" t="n">
-        <v>25303.11</v>
+        <v>25549.53</v>
       </c>
       <c r="E25" t="n">
-        <v>25612.03</v>
+        <v>25629.24</v>
       </c>
       <c r="F25" t="n">
-        <v>151.55</v>
+        <v>17.21</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0007</v>
       </c>
       <c r="H25" t="n">
-        <v>348.05</v>
+        <v>341.98</v>
       </c>
       <c r="I25" t="n">
-        <v>25101.33</v>
+        <v>24955.06</v>
       </c>
       <c r="J25" t="n">
-        <v>25228.7</v>
+        <v>25331.43</v>
       </c>
       <c r="K25" t="n">
-        <v>25342.95</v>
+        <v>25438</v>
       </c>
       <c r="L25" t="n">
-        <v>25457.2</v>
+        <v>25544.58</v>
       </c>
       <c r="M25" t="n">
-        <v>25578.01</v>
+        <v>25786.05</v>
       </c>
       <c r="N25" t="n">
-        <v>25698.82</v>
+        <v>26027.53</v>
       </c>
       <c r="O25" t="n">
-        <v>25806.51</v>
+        <v>25999.21</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2604,19 +2605,17 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U25" s="8" t="n">
@@ -2630,59 +2629,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25709.37</v>
+        <v>25855.12</v>
       </c>
       <c r="C26" t="n">
-        <v>25891.51</v>
+        <v>26096.93</v>
       </c>
       <c r="D26" t="n">
-        <v>25549.53</v>
+        <v>25855.12</v>
       </c>
       <c r="E26" t="n">
-        <v>25629.24</v>
+        <v>26001.31</v>
       </c>
       <c r="F26" t="n">
-        <v>17.21</v>
+        <v>372.07</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0145</v>
       </c>
       <c r="H26" t="n">
-        <v>341.98</v>
+        <v>241.81</v>
       </c>
       <c r="I26" t="n">
-        <v>24955.06</v>
+        <v>25207.55</v>
       </c>
       <c r="J26" t="n">
-        <v>25331.43</v>
+        <v>25241.62</v>
       </c>
       <c r="K26" t="n">
-        <v>25438</v>
+        <v>25458.25</v>
       </c>
       <c r="L26" t="n">
-        <v>25544.58</v>
+        <v>25674.88</v>
       </c>
       <c r="M26" t="n">
-        <v>25786.05</v>
+        <v>25800.23</v>
       </c>
       <c r="N26" t="n">
-        <v>26027.53</v>
+        <v>25925.58</v>
       </c>
       <c r="O26" t="n">
-        <v>25999.21</v>
+        <v>26233.49</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2693,9 +2688,9 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -2703,8 +2698,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2719,50 +2716,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25855.12</v>
+        <v>26189.62</v>
       </c>
       <c r="C27" t="n">
-        <v>26096.93</v>
+        <v>26266.5</v>
       </c>
       <c r="D27" t="n">
-        <v>25855.12</v>
+        <v>26082.43</v>
       </c>
       <c r="E27" t="n">
-        <v>26001.31</v>
+        <v>26202.35</v>
       </c>
       <c r="F27" t="n">
-        <v>372.07</v>
+        <v>201.04</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0077</v>
       </c>
       <c r="H27" t="n">
-        <v>241.81</v>
+        <v>184.07</v>
       </c>
       <c r="I27" t="n">
-        <v>25207.55</v>
+        <v>25613.31</v>
       </c>
       <c r="J27" t="n">
-        <v>25241.62</v>
+        <v>25772.14</v>
       </c>
       <c r="K27" t="n">
-        <v>25458.25</v>
+        <v>25880.41</v>
       </c>
       <c r="L27" t="n">
-        <v>25674.88</v>
+        <v>25988.67</v>
       </c>
       <c r="M27" t="n">
-        <v>25800.23</v>
+        <v>26122.22</v>
       </c>
       <c r="N27" t="n">
-        <v>25925.58</v>
+        <v>26255.76</v>
       </c>
       <c r="O27" t="n">
-        <v>26233.49</v>
+        <v>26338.74</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2773,7 +2770,7 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2801,50 +2798,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26189.62</v>
+        <v>26393.43</v>
       </c>
       <c r="C28" t="n">
-        <v>26266.5</v>
+        <v>26403.81</v>
       </c>
       <c r="D28" t="n">
-        <v>26082.43</v>
+        <v>26123.18</v>
       </c>
       <c r="E28" t="n">
-        <v>26202.35</v>
+        <v>26126.3</v>
       </c>
       <c r="F28" t="n">
-        <v>201.04</v>
+        <v>-76.05</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0029</v>
       </c>
       <c r="H28" t="n">
-        <v>184.07</v>
+        <v>280.63</v>
       </c>
       <c r="I28" t="n">
-        <v>25613.31</v>
+        <v>25898.36</v>
       </c>
       <c r="J28" t="n">
-        <v>25772.14</v>
+        <v>26032.22</v>
       </c>
       <c r="K28" t="n">
-        <v>25880.41</v>
+        <v>26110.31</v>
       </c>
       <c r="L28" t="n">
-        <v>25988.67</v>
+        <v>26188.41</v>
       </c>
       <c r="M28" t="n">
-        <v>26122.22</v>
+        <v>26294.38</v>
       </c>
       <c r="N28" t="n">
-        <v>26255.76</v>
+        <v>26400.36</v>
       </c>
       <c r="O28" t="n">
-        <v>26338.74</v>
+        <v>26450.57</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2852,12 +2849,14 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
@@ -2867,7 +2866,7 @@
       </c>
       <c r="U28" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V28" s="8" t="n">
@@ -2878,55 +2877,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>26393.43</v>
+        <v>26116.27</v>
       </c>
       <c r="C29" t="n">
-        <v>26403.81</v>
+        <v>26229.33</v>
       </c>
       <c r="D29" t="n">
-        <v>26123.18</v>
+        <v>26081.69</v>
       </c>
       <c r="E29" t="n">
-        <v>26126.3</v>
+        <v>26140.13</v>
       </c>
       <c r="F29" t="n">
-        <v>-76.05</v>
+        <v>13.83</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0005</v>
       </c>
       <c r="H29" t="n">
-        <v>280.63</v>
+        <v>147.64</v>
       </c>
       <c r="I29" t="n">
-        <v>25898.36</v>
+        <v>25842.55</v>
       </c>
       <c r="J29" t="n">
-        <v>26032.22</v>
+        <v>25777.07</v>
       </c>
       <c r="K29" t="n">
-        <v>26110.31</v>
+        <v>25985.99</v>
       </c>
       <c r="L29" t="n">
-        <v>26188.41</v>
+        <v>26194.9</v>
       </c>
       <c r="M29" t="n">
-        <v>26294.38</v>
+        <v>26266.62</v>
       </c>
       <c r="N29" t="n">
-        <v>26400.36</v>
+        <v>26338.33</v>
       </c>
       <c r="O29" t="n">
-        <v>26450.57</v>
+        <v>26684.44</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2934,25 +2937,19 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2964,57 +2961,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26116.27</v>
+        <v>26235.8</v>
       </c>
       <c r="C30" t="n">
-        <v>26229.33</v>
+        <v>26445.18</v>
       </c>
       <c r="D30" t="n">
-        <v>26081.69</v>
+        <v>26223.64</v>
       </c>
       <c r="E30" t="n">
-        <v>26140.13</v>
+        <v>26319.45</v>
       </c>
       <c r="F30" t="n">
-        <v>13.83</v>
+        <v>179.32</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0069</v>
       </c>
       <c r="H30" t="n">
-        <v>147.64</v>
+        <v>221.54</v>
       </c>
       <c r="I30" t="n">
-        <v>25842.55</v>
+        <v>25934.05</v>
       </c>
       <c r="J30" t="n">
-        <v>25777.07</v>
+        <v>25984.8</v>
       </c>
       <c r="K30" t="n">
-        <v>25985.99</v>
+        <v>26066.31</v>
       </c>
       <c r="L30" t="n">
-        <v>26194.9</v>
+        <v>26147.82</v>
       </c>
       <c r="M30" t="n">
-        <v>26266.62</v>
+        <v>26213.95</v>
       </c>
       <c r="N30" t="n">
-        <v>26338.33</v>
+        <v>26280.08</v>
       </c>
       <c r="O30" t="n">
-        <v>26684.44</v>
+        <v>26376.97</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3027,76 +3024,78 @@
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>26235.8</v>
+        <v>26360.44</v>
       </c>
       <c r="C31" t="n">
-        <v>26445.18</v>
+        <v>26441.91</v>
       </c>
       <c r="D31" t="n">
-        <v>26223.64</v>
+        <v>26302.19</v>
       </c>
       <c r="E31" t="n">
-        <v>26319.45</v>
+        <v>26323.88</v>
       </c>
       <c r="F31" t="n">
-        <v>179.32</v>
+        <v>4.43</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0002</v>
       </c>
       <c r="H31" t="n">
-        <v>221.54</v>
+        <v>139.72</v>
       </c>
       <c r="I31" t="n">
-        <v>25934.05</v>
+        <v>26002.1</v>
       </c>
       <c r="J31" t="n">
-        <v>25984.8</v>
+        <v>26090.43</v>
       </c>
       <c r="K31" t="n">
-        <v>26066.31</v>
+        <v>26208.68</v>
       </c>
       <c r="L31" t="n">
-        <v>26147.82</v>
+        <v>26326.93</v>
       </c>
       <c r="M31" t="n">
-        <v>26213.95</v>
+        <v>26430.22</v>
       </c>
       <c r="N31" t="n">
-        <v>26280.08</v>
+        <v>26533.51</v>
       </c>
       <c r="O31" t="n">
-        <v>26376.97</v>
+        <v>26666.72</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3109,7 +3108,7 @@
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
@@ -3117,70 +3116,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26360.44</v>
+        <v>26378</v>
       </c>
       <c r="C32" t="n">
-        <v>26441.91</v>
+        <v>26504.54</v>
       </c>
       <c r="D32" t="n">
-        <v>26302.19</v>
+        <v>26245.57</v>
       </c>
       <c r="E32" t="n">
-        <v>26323.88</v>
+        <v>26391.42</v>
       </c>
       <c r="F32" t="n">
-        <v>4.43</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0026</v>
       </c>
       <c r="H32" t="n">
-        <v>139.72</v>
+        <v>258.97</v>
       </c>
       <c r="I32" t="n">
-        <v>26002.1</v>
+        <v>26162.47</v>
       </c>
       <c r="J32" t="n">
-        <v>26090.43</v>
+        <v>26160.08</v>
       </c>
       <c r="K32" t="n">
-        <v>26208.68</v>
+        <v>26254.02</v>
       </c>
       <c r="L32" t="n">
-        <v>26326.93</v>
+        <v>26347.97</v>
       </c>
       <c r="M32" t="n">
-        <v>26430.22</v>
+        <v>26393.74</v>
       </c>
       <c r="N32" t="n">
-        <v>26533.51</v>
+        <v>26439.52</v>
       </c>
       <c r="O32" t="n">
-        <v>26666.72</v>
+        <v>26581.63</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3188,21 +3187,25 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3221,50 +3224,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>26378</v>
+        <v>26452</v>
       </c>
       <c r="C33" t="n">
-        <v>26504.54</v>
+        <v>26573.5</v>
       </c>
       <c r="D33" t="n">
-        <v>26245.57</v>
+        <v>26313.58</v>
       </c>
       <c r="E33" t="n">
-        <v>26391.42</v>
+        <v>26331.07</v>
       </c>
       <c r="F33" t="n">
-        <v>67.54000000000001</v>
+        <v>-60.35</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0023</v>
       </c>
       <c r="H33" t="n">
-        <v>258.97</v>
+        <v>259.92</v>
       </c>
       <c r="I33" t="n">
-        <v>26162.47</v>
+        <v>25986.6</v>
       </c>
       <c r="J33" t="n">
-        <v>26160.08</v>
+        <v>26140.63</v>
       </c>
       <c r="K33" t="n">
-        <v>26254.02</v>
+        <v>26261.94</v>
       </c>
       <c r="L33" t="n">
-        <v>26347.97</v>
+        <v>26383.24</v>
       </c>
       <c r="M33" t="n">
-        <v>26393.74</v>
+        <v>26520.9</v>
       </c>
       <c r="N33" t="n">
-        <v>26439.52</v>
+        <v>26658.57</v>
       </c>
       <c r="O33" t="n">
-        <v>26581.63</v>
+        <v>26763.51</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3272,25 +3275,21 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R33" s="6" t="n">
+        <v/>
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3309,50 +3308,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26452</v>
+        <v>26437.35</v>
       </c>
       <c r="C34" t="n">
-        <v>26573.5</v>
+        <v>26489.78</v>
       </c>
       <c r="D34" t="n">
-        <v>26313.58</v>
+        <v>26285.23</v>
       </c>
       <c r="E34" t="n">
-        <v>26331.07</v>
+        <v>26299.74</v>
       </c>
       <c r="F34" t="n">
-        <v>-60.35</v>
+        <v>-31.33</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0012</v>
       </c>
       <c r="H34" t="n">
-        <v>259.92</v>
+        <v>204.55</v>
       </c>
       <c r="I34" t="n">
-        <v>25986.6</v>
+        <v>26053.66</v>
       </c>
       <c r="J34" t="n">
-        <v>26140.63</v>
+        <v>26014.92</v>
       </c>
       <c r="K34" t="n">
-        <v>26261.94</v>
+        <v>26201.11</v>
       </c>
       <c r="L34" t="n">
-        <v>26383.24</v>
+        <v>26387.31</v>
       </c>
       <c r="M34" t="n">
-        <v>26520.9</v>
+        <v>26461.03</v>
       </c>
       <c r="N34" t="n">
-        <v>26658.57</v>
+        <v>26534.76</v>
       </c>
       <c r="O34" t="n">
-        <v>26763.51</v>
+        <v>26833.42</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3363,7 +3362,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3386,57 +3385,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>26437.35</v>
+        <v>26445.99</v>
       </c>
       <c r="C35" t="n">
-        <v>26489.78</v>
+        <v>26541.34</v>
       </c>
       <c r="D35" t="n">
-        <v>26285.23</v>
+        <v>26404.95</v>
       </c>
       <c r="E35" t="n">
-        <v>26299.74</v>
+        <v>26440.31</v>
       </c>
       <c r="F35" t="n">
-        <v>-31.33</v>
+        <v>140.57</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0053</v>
       </c>
       <c r="H35" t="n">
-        <v>204.55</v>
+        <v>136.39</v>
       </c>
       <c r="I35" t="n">
-        <v>26053.66</v>
+        <v>26080.68</v>
       </c>
       <c r="J35" t="n">
-        <v>26014.92</v>
+        <v>26051.31</v>
       </c>
       <c r="K35" t="n">
-        <v>26201.11</v>
+        <v>26197.47</v>
       </c>
       <c r="L35" t="n">
-        <v>26387.31</v>
+        <v>26343.62</v>
       </c>
       <c r="M35" t="n">
-        <v>26461.03</v>
+        <v>26402.01</v>
       </c>
       <c r="N35" t="n">
-        <v>26534.76</v>
+        <v>26460.41</v>
       </c>
       <c r="O35" t="n">
-        <v>26833.42</v>
+        <v>26694.33</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3449,7 +3448,7 @@
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
@@ -3457,8 +3456,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U35" s="8" t="n">
-        <v/>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3468,59 +3469,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26445.99</v>
+        <v>26490.3</v>
       </c>
       <c r="C36" t="n">
-        <v>26541.34</v>
+        <v>26493.5</v>
       </c>
       <c r="D36" t="n">
-        <v>26404.95</v>
+        <v>26338.61</v>
       </c>
       <c r="E36" t="n">
-        <v>26440.31</v>
+        <v>26338.61</v>
       </c>
       <c r="F36" t="n">
-        <v>140.57</v>
+        <v>-101.7</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0038</v>
       </c>
       <c r="H36" t="n">
-        <v>136.39</v>
+        <v>154.89</v>
       </c>
       <c r="I36" t="n">
-        <v>26080.68</v>
+        <v>26268.56</v>
       </c>
       <c r="J36" t="n">
-        <v>26051.31</v>
+        <v>26287.5</v>
       </c>
       <c r="K36" t="n">
-        <v>26197.47</v>
+        <v>26372.12</v>
       </c>
       <c r="L36" t="n">
-        <v>26343.62</v>
+        <v>26456.73</v>
       </c>
       <c r="M36" t="n">
-        <v>26402.01</v>
+        <v>26508.51</v>
       </c>
       <c r="N36" t="n">
-        <v>26460.41</v>
+        <v>26560.28</v>
       </c>
       <c r="O36" t="n">
-        <v>26694.33</v>
+        <v>26677.73</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3528,23 +3525,21 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3554,68 +3549,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26490.3</v>
+        <v>26280.86</v>
       </c>
       <c r="C37" t="n">
-        <v>26493.5</v>
+        <v>26292.95</v>
       </c>
       <c r="D37" t="n">
-        <v>26338.61</v>
+        <v>26119.54</v>
       </c>
       <c r="E37" t="n">
-        <v>26338.61</v>
+        <v>26128.36</v>
       </c>
       <c r="F37" t="n">
-        <v>-101.7</v>
+        <v>-210.25</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.008</v>
       </c>
       <c r="H37" t="n">
-        <v>154.89</v>
+        <v>173.41</v>
       </c>
       <c r="I37" t="n">
-        <v>26268.56</v>
+        <v>26183.72</v>
       </c>
       <c r="J37" t="n">
-        <v>26287.5</v>
+        <v>26145</v>
       </c>
       <c r="K37" t="n">
-        <v>26372.12</v>
+        <v>26261.16</v>
       </c>
       <c r="L37" t="n">
-        <v>26456.73</v>
+        <v>26377.33</v>
       </c>
       <c r="M37" t="n">
-        <v>26508.51</v>
+        <v>26416.05</v>
       </c>
       <c r="N37" t="n">
-        <v>26560.28</v>
+        <v>26454.78</v>
       </c>
       <c r="O37" t="n">
-        <v>26677.73</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
+        <v>26648.39</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3629,81 +3632,73 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W37" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26280.86</v>
+        <v>26146.12</v>
       </c>
       <c r="C38" t="n">
-        <v>26292.95</v>
+        <v>26187.82</v>
       </c>
       <c r="D38" t="n">
-        <v>26119.54</v>
+        <v>26063.37</v>
       </c>
       <c r="E38" t="n">
-        <v>26128.36</v>
+        <v>26091.33</v>
       </c>
       <c r="F38" t="n">
-        <v>-210.25</v>
+        <v>-37.03</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0014</v>
       </c>
       <c r="H38" t="n">
-        <v>173.41</v>
+        <v>124.45</v>
       </c>
       <c r="I38" t="n">
-        <v>26183.72</v>
+        <v>25946.13</v>
       </c>
       <c r="J38" t="n">
-        <v>26145</v>
+        <v>25916.01</v>
       </c>
       <c r="K38" t="n">
-        <v>26261.16</v>
+        <v>26041.65</v>
       </c>
       <c r="L38" t="n">
-        <v>26377.33</v>
+        <v>26167.3</v>
       </c>
       <c r="M38" t="n">
-        <v>26416.05</v>
+        <v>26215.06</v>
       </c>
       <c r="N38" t="n">
-        <v>26454.78</v>
+        <v>26262.83</v>
       </c>
       <c r="O38" t="n">
-        <v>26648.39</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
+        <v>26466.36</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
+      <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3727,63 +3722,67 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26146.12</v>
+        <v>26050.95</v>
       </c>
       <c r="C39" t="n">
-        <v>26187.82</v>
+        <v>26062.15</v>
       </c>
       <c r="D39" t="n">
-        <v>26063.37</v>
+        <v>25914.11</v>
       </c>
       <c r="E39" t="n">
-        <v>26091.33</v>
+        <v>25983.04</v>
       </c>
       <c r="F39" t="n">
-        <v>-37.03</v>
+        <v>-108.29</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0042</v>
       </c>
       <c r="H39" t="n">
-        <v>124.45</v>
+        <v>148.04</v>
       </c>
       <c r="I39" t="n">
-        <v>25946.13</v>
+        <v>25938.92</v>
       </c>
       <c r="J39" t="n">
-        <v>25916.01</v>
+        <v>25949.75</v>
       </c>
       <c r="K39" t="n">
-        <v>26041.65</v>
+        <v>26029.1</v>
       </c>
       <c r="L39" t="n">
-        <v>26167.3</v>
+        <v>26108.46</v>
       </c>
       <c r="M39" t="n">
-        <v>26215.06</v>
+        <v>26153.56</v>
       </c>
       <c r="N39" t="n">
-        <v>26262.83</v>
+        <v>26198.65</v>
       </c>
       <c r="O39" t="n">
-        <v>26466.36</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
+        <v>26312.27</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3807,83 +3806,81 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>26050.95</v>
+        <v>25998.95</v>
       </c>
       <c r="C40" t="n">
-        <v>26062.15</v>
+        <v>26166.25</v>
       </c>
       <c r="D40" t="n">
-        <v>25914.11</v>
+        <v>25969.52</v>
       </c>
       <c r="E40" t="n">
-        <v>25983.04</v>
+        <v>26136.56</v>
       </c>
       <c r="F40" t="n">
-        <v>-108.29</v>
+        <v>153.52</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.0059</v>
       </c>
       <c r="H40" t="n">
-        <v>148.04</v>
+        <v>196.73</v>
       </c>
       <c r="I40" t="n">
-        <v>25938.92</v>
+        <v>25766.07</v>
       </c>
       <c r="J40" t="n">
-        <v>25949.75</v>
+        <v>25832.45</v>
       </c>
       <c r="K40" t="n">
-        <v>26029.1</v>
+        <v>25909.02</v>
       </c>
       <c r="L40" t="n">
-        <v>26108.46</v>
+        <v>25985.58</v>
       </c>
       <c r="M40" t="n">
-        <v>26153.56</v>
+        <v>26057.06</v>
       </c>
       <c r="N40" t="n">
-        <v>26198.65</v>
+        <v>26128.53</v>
       </c>
       <c r="O40" t="n">
-        <v>26312.27</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
+        <v>26210.19</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W40" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr"/>
@@ -3891,50 +3888,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25998.95</v>
+        <v>26091.29</v>
       </c>
       <c r="C41" t="n">
-        <v>26166.25</v>
+        <v>26171.7</v>
       </c>
       <c r="D41" t="n">
-        <v>25969.52</v>
+        <v>26038.07</v>
       </c>
       <c r="E41" t="n">
-        <v>26136.56</v>
+        <v>26106.6</v>
       </c>
       <c r="F41" t="n">
-        <v>153.52</v>
+        <v>-29.96</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0011</v>
       </c>
       <c r="H41" t="n">
-        <v>196.73</v>
+        <v>133.63</v>
       </c>
       <c r="I41" t="n">
-        <v>25766.07</v>
+        <v>25772.79</v>
       </c>
       <c r="J41" t="n">
-        <v>25832.45</v>
+        <v>25974.17</v>
       </c>
       <c r="K41" t="n">
-        <v>25909.02</v>
+        <v>26038.2</v>
       </c>
       <c r="L41" t="n">
-        <v>25985.58</v>
+        <v>26102.22</v>
       </c>
       <c r="M41" t="n">
-        <v>26057.06</v>
+        <v>26234.93</v>
       </c>
       <c r="N41" t="n">
-        <v>26128.53</v>
+        <v>26367.63</v>
       </c>
       <c r="O41" t="n">
-        <v>26210.19</v>
+        <v>26362.98</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3942,23 +3939,21 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3968,55 +3963,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26091.29</v>
+        <v>26206.01</v>
       </c>
       <c r="C42" t="n">
-        <v>26171.7</v>
+        <v>26341.52</v>
       </c>
       <c r="D42" t="n">
-        <v>26038.07</v>
+        <v>26164.11</v>
       </c>
       <c r="E42" t="n">
-        <v>26106.6</v>
+        <v>26266.14</v>
       </c>
       <c r="F42" t="n">
-        <v>-29.96</v>
+        <v>159.54</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0061</v>
       </c>
       <c r="H42" t="n">
-        <v>133.63</v>
+        <v>177.41</v>
       </c>
       <c r="I42" t="n">
-        <v>25772.79</v>
+        <v>25904.44</v>
       </c>
       <c r="J42" t="n">
-        <v>25974.17</v>
+        <v>25973.83</v>
       </c>
       <c r="K42" t="n">
-        <v>26038.2</v>
+        <v>26039.79</v>
       </c>
       <c r="L42" t="n">
-        <v>26102.22</v>
+        <v>26105.74</v>
       </c>
       <c r="M42" t="n">
-        <v>26234.93</v>
+        <v>26173.41</v>
       </c>
       <c r="N42" t="n">
-        <v>26367.63</v>
+        <v>26241.09</v>
       </c>
       <c r="O42" t="n">
-        <v>26362.98</v>
+        <v>26305.33</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4024,83 +4023,83 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v/>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>26206.01</v>
+        <v>26255.41</v>
       </c>
       <c r="C43" t="n">
-        <v>26341.52</v>
+        <v>26466.76</v>
       </c>
       <c r="D43" t="n">
-        <v>26164.11</v>
+        <v>26196.92</v>
       </c>
       <c r="E43" t="n">
-        <v>26266.14</v>
+        <v>26285.96</v>
       </c>
       <c r="F43" t="n">
-        <v>159.54</v>
+        <v>19.82</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0061</v>
+        <v>0.0008</v>
       </c>
       <c r="H43" t="n">
-        <v>177.41</v>
+        <v>269.84</v>
       </c>
       <c r="I43" t="n">
-        <v>25904.44</v>
+        <v>25986.7</v>
       </c>
       <c r="J43" t="n">
-        <v>25973.83</v>
+        <v>26095.39</v>
       </c>
       <c r="K43" t="n">
-        <v>26039.79</v>
+        <v>26177.44</v>
       </c>
       <c r="L43" t="n">
-        <v>26105.74</v>
+        <v>26259.48</v>
       </c>
       <c r="M43" t="n">
-        <v>26173.41</v>
+        <v>26354.85</v>
       </c>
       <c r="N43" t="n">
-        <v>26241.09</v>
+        <v>26450.21</v>
       </c>
       <c r="O43" t="n">
-        <v>26305.33</v>
+        <v>26518.93</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4111,9 +4110,9 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
@@ -4123,13 +4122,11 @@
       </c>
       <c r="U43" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v/>
       </c>
       <c r="W43" s="9" t="inlineStr">
         <is>
@@ -4141,50 +4138,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26255.41</v>
+        <v>26354.37</v>
       </c>
       <c r="C44" t="n">
-        <v>26466.76</v>
+        <v>26402.81</v>
       </c>
       <c r="D44" t="n">
-        <v>26196.92</v>
+        <v>26241.77</v>
       </c>
       <c r="E44" t="n">
-        <v>26285.96</v>
+        <v>26367.24</v>
       </c>
       <c r="F44" t="n">
-        <v>19.82</v>
+        <v>81.28</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0031</v>
       </c>
       <c r="H44" t="n">
-        <v>269.84</v>
+        <v>161.04</v>
       </c>
       <c r="I44" t="n">
-        <v>25986.7</v>
+        <v>25927.08</v>
       </c>
       <c r="J44" t="n">
-        <v>26095.39</v>
+        <v>25993.18</v>
       </c>
       <c r="K44" t="n">
-        <v>26177.44</v>
+        <v>26151.04</v>
       </c>
       <c r="L44" t="n">
-        <v>26259.48</v>
+        <v>26308.9</v>
       </c>
       <c r="M44" t="n">
-        <v>26354.85</v>
+        <v>26420.88</v>
       </c>
       <c r="N44" t="n">
-        <v>26450.21</v>
+        <v>26532.86</v>
       </c>
       <c r="O44" t="n">
-        <v>26518.93</v>
+        <v>26736.6</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4195,20 +4192,18 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4218,55 +4213,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>26354.37</v>
+        <v>26494.61</v>
       </c>
       <c r="C45" t="n">
-        <v>26402.81</v>
+        <v>26618.74</v>
       </c>
       <c r="D45" t="n">
-        <v>26241.77</v>
+        <v>26467.36</v>
       </c>
       <c r="E45" t="n">
-        <v>26367.24</v>
+        <v>26569.99</v>
       </c>
       <c r="F45" t="n">
-        <v>81.28</v>
+        <v>202.75</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0077</v>
       </c>
       <c r="H45" t="n">
-        <v>161.04</v>
+        <v>151.38</v>
       </c>
       <c r="I45" t="n">
-        <v>25927.08</v>
+        <v>26080.73</v>
       </c>
       <c r="J45" t="n">
-        <v>25993.18</v>
+        <v>26228.67</v>
       </c>
       <c r="K45" t="n">
-        <v>26151.04</v>
+        <v>26286.72</v>
       </c>
       <c r="L45" t="n">
-        <v>26308.9</v>
+        <v>26344.77</v>
       </c>
       <c r="M45" t="n">
-        <v>26420.88</v>
+        <v>26447.76</v>
       </c>
       <c r="N45" t="n">
-        <v>26532.86</v>
+        <v>26550.76</v>
       </c>
       <c r="O45" t="n">
-        <v>26736.6</v>
+        <v>26563.85</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4277,113 +4276,113 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v/>
-      </c>
       <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>26494.61</v>
+        <v>26464.14</v>
       </c>
       <c r="C46" t="n">
-        <v>26618.74</v>
+        <v>26471.79</v>
       </c>
       <c r="D46" t="n">
-        <v>26467.36</v>
+        <v>26249.59</v>
       </c>
       <c r="E46" t="n">
-        <v>26569.99</v>
+        <v>26258.11</v>
       </c>
       <c r="F46" t="n">
-        <v>202.75</v>
+        <v>-311.88</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0117</v>
       </c>
       <c r="H46" t="n">
-        <v>151.38</v>
+        <v>222.2</v>
       </c>
       <c r="I46" t="n">
-        <v>26080.73</v>
+        <v>26315.98</v>
       </c>
       <c r="J46" t="n">
-        <v>26228.67</v>
+        <v>26432.08</v>
       </c>
       <c r="K46" t="n">
-        <v>26286.72</v>
+        <v>26494.3</v>
       </c>
       <c r="L46" t="n">
-        <v>26344.77</v>
+        <v>26556.52</v>
       </c>
       <c r="M46" t="n">
-        <v>26447.76</v>
+        <v>26645.68</v>
       </c>
       <c r="N46" t="n">
-        <v>26550.76</v>
+        <v>26734.84</v>
       </c>
       <c r="O46" t="n">
-        <v>26563.85</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+        <v>26770.12</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W46" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W46" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr"/>
@@ -4391,67 +4390,67 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>26464.14</v>
+        <v>26150.75</v>
       </c>
       <c r="C47" t="n">
-        <v>26471.79</v>
+        <v>26206.13</v>
       </c>
       <c r="D47" t="n">
-        <v>26249.59</v>
+        <v>25916.76</v>
       </c>
       <c r="E47" t="n">
-        <v>26258.11</v>
+        <v>25970.11</v>
       </c>
       <c r="F47" t="n">
-        <v>-311.88</v>
+        <v>-288</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.011</v>
       </c>
       <c r="H47" t="n">
-        <v>222.2</v>
+        <v>289.37</v>
       </c>
       <c r="I47" t="n">
-        <v>26315.98</v>
+        <v>26027.39</v>
       </c>
       <c r="J47" t="n">
-        <v>26432.08</v>
+        <v>25984.62</v>
       </c>
       <c r="K47" t="n">
-        <v>26494.3</v>
+        <v>26147.01</v>
       </c>
       <c r="L47" t="n">
-        <v>26556.52</v>
+        <v>26309.4</v>
       </c>
       <c r="M47" t="n">
-        <v>26645.68</v>
+        <v>26369.21</v>
       </c>
       <c r="N47" t="n">
-        <v>26734.84</v>
+        <v>26429.02</v>
       </c>
       <c r="O47" t="n">
-        <v>26770.12</v>
+        <v>26693.99</v>
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S47" s="7" t="inlineStr">
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4475,67 +4474,63 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>26150.75</v>
+        <v>25886.67</v>
       </c>
       <c r="C48" t="n">
-        <v>26206.13</v>
+        <v>25924.21</v>
       </c>
       <c r="D48" t="n">
-        <v>25916.76</v>
+        <v>25727.93</v>
       </c>
       <c r="E48" t="n">
-        <v>25970.11</v>
+        <v>25839.33</v>
       </c>
       <c r="F48" t="n">
-        <v>-288</v>
+        <v>-130.78</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.005</v>
       </c>
       <c r="H48" t="n">
-        <v>289.37</v>
+        <v>196.28</v>
       </c>
       <c r="I48" t="n">
-        <v>26027.39</v>
+        <v>25627.39</v>
       </c>
       <c r="J48" t="n">
-        <v>25984.62</v>
+        <v>25635.07</v>
       </c>
       <c r="K48" t="n">
-        <v>26147.01</v>
+        <v>25825.42</v>
       </c>
       <c r="L48" t="n">
-        <v>26309.4</v>
+        <v>26015.78</v>
       </c>
       <c r="M48" t="n">
-        <v>26369.21</v>
+        <v>26114.79</v>
       </c>
       <c r="N48" t="n">
-        <v>26429.02</v>
+        <v>26213.81</v>
       </c>
       <c r="O48" t="n">
-        <v>26693.99</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
+        <v>26495.5</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4559,50 +4554,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25886.67</v>
+        <v>25840.92</v>
       </c>
       <c r="C49" t="n">
-        <v>25924.21</v>
+        <v>26007.79</v>
       </c>
       <c r="D49" t="n">
-        <v>25727.93</v>
+        <v>25784.84</v>
       </c>
       <c r="E49" t="n">
-        <v>25839.33</v>
+        <v>26003.32</v>
       </c>
       <c r="F49" t="n">
-        <v>-130.78</v>
+        <v>163.99</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0063</v>
       </c>
       <c r="H49" t="n">
-        <v>196.28</v>
+        <v>222.95</v>
       </c>
       <c r="I49" t="n">
-        <v>25627.39</v>
+        <v>25531.65</v>
       </c>
       <c r="J49" t="n">
-        <v>25635.07</v>
+        <v>25649.68</v>
       </c>
       <c r="K49" t="n">
-        <v>25825.42</v>
+        <v>25741.19</v>
       </c>
       <c r="L49" t="n">
-        <v>26015.78</v>
+        <v>25832.7</v>
       </c>
       <c r="M49" t="n">
-        <v>26114.79</v>
+        <v>25937.47</v>
       </c>
       <c r="N49" t="n">
-        <v>26213.81</v>
+        <v>26042.24</v>
       </c>
       <c r="O49" t="n">
-        <v>26495.5</v>
+        <v>26120.49</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4610,22 +4605,24 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
@@ -4634,55 +4631,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25840.92</v>
+        <v>25985.86</v>
       </c>
       <c r="C50" t="n">
-        <v>26007.79</v>
+        <v>26167.93</v>
       </c>
       <c r="D50" t="n">
-        <v>25784.84</v>
+        <v>25958.7</v>
       </c>
       <c r="E50" t="n">
-        <v>26003.32</v>
+        <v>26046.4</v>
       </c>
       <c r="F50" t="n">
-        <v>163.99</v>
+        <v>43.08</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0017</v>
       </c>
       <c r="H50" t="n">
-        <v>222.95</v>
+        <v>209.23</v>
       </c>
       <c r="I50" t="n">
-        <v>25531.65</v>
+        <v>25561.89</v>
       </c>
       <c r="J50" t="n">
-        <v>25649.68</v>
+        <v>25833.87</v>
       </c>
       <c r="K50" t="n">
-        <v>25741.19</v>
+        <v>25891.85</v>
       </c>
       <c r="L50" t="n">
-        <v>25832.7</v>
+        <v>25949.82</v>
       </c>
       <c r="M50" t="n">
-        <v>25937.47</v>
+        <v>26114.79</v>
       </c>
       <c r="N50" t="n">
-        <v>26042.24</v>
+        <v>26279.77</v>
       </c>
       <c r="O50" t="n">
-        <v>26120.49</v>
+        <v>26230.74</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4693,20 +4694,18 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4725,50 +4724,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25985.86</v>
+        <v>26039.54</v>
       </c>
       <c r="C51" t="n">
-        <v>26167.93</v>
+        <v>26069.99</v>
       </c>
       <c r="D51" t="n">
-        <v>25958.7</v>
+        <v>25919.61</v>
       </c>
       <c r="E51" t="n">
-        <v>26046.4</v>
+        <v>26006.53</v>
       </c>
       <c r="F51" t="n">
-        <v>43.08</v>
+        <v>-39.87</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0015</v>
       </c>
       <c r="H51" t="n">
-        <v>209.23</v>
+        <v>150.38</v>
       </c>
       <c r="I51" t="n">
-        <v>25561.89</v>
+        <v>25749.47</v>
       </c>
       <c r="J51" t="n">
-        <v>25833.87</v>
+        <v>25828.71</v>
       </c>
       <c r="K51" t="n">
-        <v>25891.85</v>
+        <v>25941.79</v>
       </c>
       <c r="L51" t="n">
-        <v>25949.82</v>
+        <v>26054.86</v>
       </c>
       <c r="M51" t="n">
-        <v>26114.79</v>
+        <v>26151.02</v>
       </c>
       <c r="N51" t="n">
-        <v>26279.77</v>
+        <v>26247.17</v>
       </c>
       <c r="O51" t="n">
-        <v>26230.74</v>
+        <v>26377.16</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4776,18 +4775,18 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4800,65 +4799,63 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>26039.54</v>
+        <v>25897.22</v>
       </c>
       <c r="C52" t="n">
-        <v>26069.99</v>
+        <v>26026.78</v>
       </c>
       <c r="D52" t="n">
-        <v>25919.61</v>
+        <v>25799.66</v>
       </c>
       <c r="E52" t="n">
-        <v>26006.53</v>
+        <v>26007.63</v>
       </c>
       <c r="F52" t="n">
-        <v>-39.87</v>
+        <v>1.1</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>150.38</v>
+        <v>227.12</v>
       </c>
       <c r="I52" t="n">
-        <v>25749.47</v>
+        <v>25769.23</v>
       </c>
       <c r="J52" t="n">
-        <v>25828.71</v>
+        <v>25862.01</v>
       </c>
       <c r="K52" t="n">
-        <v>25941.79</v>
+        <v>25931.34</v>
       </c>
       <c r="L52" t="n">
-        <v>26054.86</v>
+        <v>26000.66</v>
       </c>
       <c r="M52" t="n">
-        <v>26151.02</v>
+        <v>26081.72</v>
       </c>
       <c r="N52" t="n">
-        <v>26247.17</v>
+        <v>26162.77</v>
       </c>
       <c r="O52" t="n">
-        <v>26377.16</v>
+        <v>26220.37</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
@@ -4867,7 +4864,7 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4884,58 +4881,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25897.22</v>
+        <v>25870.98</v>
       </c>
       <c r="C53" t="n">
-        <v>26026.78</v>
+        <v>25909.66</v>
       </c>
       <c r="D53" t="n">
-        <v>25799.66</v>
+        <v>25512.39</v>
       </c>
       <c r="E53" t="n">
-        <v>26007.63</v>
+        <v>25576.45</v>
       </c>
       <c r="F53" t="n">
-        <v>1.1</v>
+        <v>-431.18</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0</v>
+        <v>-0.0166</v>
       </c>
       <c r="H53" t="n">
-        <v>227.12</v>
+        <v>397.27</v>
       </c>
       <c r="I53" t="n">
-        <v>25769.23</v>
+        <v>25572.54</v>
       </c>
       <c r="J53" t="n">
-        <v>25862.01</v>
+        <v>25827.72</v>
       </c>
       <c r="K53" t="n">
-        <v>25931.34</v>
+        <v>25894.07</v>
       </c>
       <c r="L53" t="n">
-        <v>26000.66</v>
+        <v>25960.43</v>
       </c>
       <c r="M53" t="n">
-        <v>26081.72</v>
+        <v>26121.19</v>
       </c>
       <c r="N53" t="n">
-        <v>26162.77</v>
+        <v>26281.96</v>
       </c>
       <c r="O53" t="n">
-        <v>26220.37</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
+        <v>26253.9</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
@@ -4949,7 +4952,7 @@
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4966,76 +4969,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25870.98</v>
+        <v>25555.66</v>
       </c>
       <c r="C54" t="n">
-        <v>25909.66</v>
+        <v>25612.09</v>
       </c>
       <c r="D54" t="n">
-        <v>25512.39</v>
+        <v>25361.15</v>
       </c>
       <c r="E54" t="n">
-        <v>25576.45</v>
+        <v>25361.15</v>
       </c>
       <c r="F54" t="n">
-        <v>-431.18</v>
+        <v>-215.3</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>397.27</v>
+        <v>250.94</v>
       </c>
       <c r="I54" t="n">
-        <v>25572.54</v>
+        <v>25115.12</v>
       </c>
       <c r="J54" t="n">
-        <v>25827.72</v>
+        <v>25111.89</v>
       </c>
       <c r="K54" t="n">
-        <v>25894.07</v>
+        <v>25377.81</v>
       </c>
       <c r="L54" t="n">
-        <v>25960.43</v>
+        <v>25643.74</v>
       </c>
       <c r="M54" t="n">
-        <v>26121.19</v>
+        <v>25775.08</v>
       </c>
       <c r="N54" t="n">
-        <v>26281.96</v>
+        <v>25906.43</v>
       </c>
       <c r="O54" t="n">
-        <v>26253.9</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
+        <v>26306.93</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5059,50 +5054,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25555.66</v>
+        <v>25478.84</v>
       </c>
       <c r="C55" t="n">
-        <v>25612.09</v>
+        <v>25581.22</v>
       </c>
       <c r="D55" t="n">
-        <v>25361.15</v>
+        <v>25396.38</v>
       </c>
       <c r="E55" t="n">
-        <v>25361.15</v>
+        <v>25568.56</v>
       </c>
       <c r="F55" t="n">
-        <v>-215.3</v>
+        <v>207.41</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>250.94</v>
+        <v>184.84</v>
       </c>
       <c r="I55" t="n">
-        <v>25115.12</v>
+        <v>25110.21</v>
       </c>
       <c r="J55" t="n">
-        <v>25111.89</v>
+        <v>25047.48</v>
       </c>
       <c r="K55" t="n">
-        <v>25377.81</v>
+        <v>25235.68</v>
       </c>
       <c r="L55" t="n">
-        <v>25643.74</v>
+        <v>25423.89</v>
       </c>
       <c r="M55" t="n">
-        <v>25775.08</v>
+        <v>25486.62</v>
       </c>
       <c r="N55" t="n">
-        <v>25906.43</v>
+        <v>25549.35</v>
       </c>
       <c r="O55" t="n">
-        <v>26306.93</v>
+        <v>25863.03</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5110,103 +5105,109 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="W55" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25478.84</v>
+        <v>25498.74</v>
       </c>
       <c r="C56" t="n">
-        <v>25581.22</v>
+        <v>25548.78</v>
       </c>
       <c r="D56" t="n">
-        <v>25396.38</v>
+        <v>25325.52</v>
       </c>
       <c r="E56" t="n">
-        <v>25568.56</v>
+        <v>25440.81</v>
       </c>
       <c r="F56" t="n">
-        <v>207.41</v>
+        <v>-127.75</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.005</v>
       </c>
       <c r="H56" t="n">
-        <v>184.84</v>
+        <v>223.26</v>
       </c>
       <c r="I56" t="n">
-        <v>25110.21</v>
+        <v>25211.54</v>
       </c>
       <c r="J56" t="n">
-        <v>25047.48</v>
+        <v>25423.6</v>
       </c>
       <c r="K56" t="n">
-        <v>25235.68</v>
+        <v>25476.14</v>
       </c>
       <c r="L56" t="n">
-        <v>25423.89</v>
+        <v>25528.68</v>
       </c>
       <c r="M56" t="n">
-        <v>25486.62</v>
+        <v>25660.98</v>
       </c>
       <c r="N56" t="n">
-        <v>25549.35</v>
+        <v>25793.28</v>
       </c>
       <c r="O56" t="n">
-        <v>25863.03</v>
+        <v>25766.06</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5218,64 +5219,64 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25498.74</v>
+        <v>25360.32</v>
       </c>
       <c r="C57" t="n">
-        <v>25548.78</v>
+        <v>25478.98</v>
       </c>
       <c r="D57" t="n">
-        <v>25325.52</v>
+        <v>25172.89</v>
       </c>
       <c r="E57" t="n">
-        <v>25440.81</v>
+        <v>25402.28</v>
       </c>
       <c r="F57" t="n">
-        <v>-127.75</v>
+        <v>-38.53</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.005</v>
+        <v>-0.0015</v>
       </c>
       <c r="H57" t="n">
-        <v>223.26</v>
+        <v>306.09</v>
       </c>
       <c r="I57" t="n">
-        <v>25211.54</v>
+        <v>25102.26</v>
       </c>
       <c r="J57" t="n">
-        <v>25423.6</v>
+        <v>25219.38</v>
       </c>
       <c r="K57" t="n">
-        <v>25476.14</v>
+        <v>25329.18</v>
       </c>
       <c r="L57" t="n">
-        <v>25528.68</v>
+        <v>25438.98</v>
       </c>
       <c r="M57" t="n">
-        <v>25660.98</v>
+        <v>25552.44</v>
       </c>
       <c r="N57" t="n">
-        <v>25793.28</v>
+        <v>25665.9</v>
       </c>
       <c r="O57" t="n">
-        <v>25766.06</v>
+        <v>25772.04</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
       <c r="Q57" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
@@ -5283,9 +5284,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5311,71 +5312,69 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>25360.32</v>
+        <v>25515.96</v>
       </c>
       <c r="C58" t="n">
-        <v>25478.98</v>
+        <v>25599.07</v>
       </c>
       <c r="D58" t="n">
-        <v>25172.89</v>
+        <v>25361.7</v>
       </c>
       <c r="E58" t="n">
-        <v>25402.28</v>
+        <v>25537.75</v>
       </c>
       <c r="F58" t="n">
-        <v>-38.53</v>
+        <v>135.47</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0053</v>
       </c>
       <c r="H58" t="n">
-        <v>306.09</v>
+        <v>237.37</v>
       </c>
       <c r="I58" t="n">
-        <v>25102.26</v>
+        <v>24866.8</v>
       </c>
       <c r="J58" t="n">
-        <v>25219.38</v>
+        <v>25134.36</v>
       </c>
       <c r="K58" t="n">
-        <v>25329.18</v>
+        <v>25249.23</v>
       </c>
       <c r="L58" t="n">
-        <v>25438.98</v>
+        <v>25364.11</v>
       </c>
       <c r="M58" t="n">
-        <v>25552.44</v>
+        <v>25555.32</v>
       </c>
       <c r="N58" t="n">
-        <v>25665.9</v>
+        <v>25746.54</v>
       </c>
       <c r="O58" t="n">
-        <v>25772.04</v>
+        <v>25785.07</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5388,59 +5387,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25515.96</v>
+        <v>25681.6</v>
       </c>
       <c r="C59" t="n">
-        <v>25599.07</v>
+        <v>25800.62</v>
       </c>
       <c r="D59" t="n">
-        <v>25361.7</v>
+        <v>25596.05</v>
       </c>
       <c r="E59" t="n">
-        <v>25537.75</v>
+        <v>25716.71</v>
       </c>
       <c r="F59" t="n">
-        <v>135.47</v>
+        <v>178.96</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0053</v>
+        <v>0.007</v>
       </c>
       <c r="H59" t="n">
-        <v>237.37</v>
+        <v>204.57</v>
       </c>
       <c r="I59" t="n">
-        <v>24866.8</v>
+        <v>25124.33</v>
       </c>
       <c r="J59" t="n">
-        <v>25134.36</v>
+        <v>25329.06</v>
       </c>
       <c r="K59" t="n">
-        <v>25249.23</v>
+        <v>25419.06</v>
       </c>
       <c r="L59" t="n">
-        <v>25364.11</v>
+        <v>25509.07</v>
       </c>
       <c r="M59" t="n">
-        <v>25555.32</v>
+        <v>25656.44</v>
       </c>
       <c r="N59" t="n">
-        <v>25746.54</v>
+        <v>25803.8</v>
       </c>
       <c r="O59" t="n">
-        <v>25785.07</v>
+        <v>25836.44</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5451,7 +5446,7 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="10" t="inlineStr">
+      <c r="S59" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5477,69 +5472,73 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25681.6</v>
+        <v>25596.46</v>
       </c>
       <c r="C60" t="n">
-        <v>25800.62</v>
+        <v>25656.22</v>
       </c>
       <c r="D60" t="n">
-        <v>25596.05</v>
+        <v>25285.9</v>
       </c>
       <c r="E60" t="n">
-        <v>25716.71</v>
+        <v>25304.06</v>
       </c>
       <c r="F60" t="n">
-        <v>178.96</v>
+        <v>-412.65</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.007</v>
+        <v>-0.016</v>
       </c>
       <c r="H60" t="n">
-        <v>204.57</v>
+        <v>370.32</v>
       </c>
       <c r="I60" t="n">
-        <v>25124.33</v>
+        <v>25391.48</v>
       </c>
       <c r="J60" t="n">
-        <v>25329.06</v>
+        <v>25521.33</v>
       </c>
       <c r="K60" t="n">
-        <v>25419.06</v>
+        <v>25614.43</v>
       </c>
       <c r="L60" t="n">
-        <v>25509.07</v>
+        <v>25707.52</v>
       </c>
       <c r="M60" t="n">
-        <v>25656.44</v>
+        <v>25819</v>
       </c>
       <c r="N60" t="n">
-        <v>25803.8</v>
+        <v>25930.47</v>
       </c>
       <c r="O60" t="n">
-        <v>25836.44</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+        <v>26005.19</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5547,9 +5546,9 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W60" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X60" t="inlineStr"/>
@@ -5557,77 +5556,75 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>25596.46</v>
+        <v>25491.35</v>
       </c>
       <c r="C61" t="n">
-        <v>25656.22</v>
+        <v>25617.99</v>
       </c>
       <c r="D61" t="n">
-        <v>25285.9</v>
+        <v>25434.16</v>
       </c>
       <c r="E61" t="n">
-        <v>25304.06</v>
+        <v>25575.01</v>
       </c>
       <c r="F61" t="n">
-        <v>-412.65</v>
+        <v>270.95</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.016</v>
+        <v>0.0107</v>
       </c>
       <c r="H61" t="n">
-        <v>370.32</v>
+        <v>183.83</v>
       </c>
       <c r="I61" t="n">
-        <v>25391.48</v>
+        <v>24915.58</v>
       </c>
       <c r="J61" t="n">
-        <v>25521.33</v>
+        <v>24850.24</v>
       </c>
       <c r="K61" t="n">
-        <v>25614.43</v>
+        <v>25118.9</v>
       </c>
       <c r="L61" t="n">
-        <v>25707.52</v>
+        <v>25387.56</v>
       </c>
       <c r="M61" t="n">
-        <v>25819</v>
+        <v>25489.22</v>
       </c>
       <c r="N61" t="n">
-        <v>25930.47</v>
+        <v>25590.88</v>
       </c>
       <c r="O61" t="n">
-        <v>26005.19</v>
-      </c>
-      <c r="P61" s="6" t="inlineStr">
+        <v>26026.54</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
@@ -5636,55 +5633,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>25491.35</v>
+        <v>25592.98</v>
       </c>
       <c r="C62" t="n">
-        <v>25617.99</v>
+        <v>25783.16</v>
       </c>
       <c r="D62" t="n">
-        <v>25434.16</v>
+        <v>25423.07</v>
       </c>
       <c r="E62" t="n">
-        <v>25575.01</v>
+        <v>25578.85</v>
       </c>
       <c r="F62" t="n">
-        <v>270.95</v>
+        <v>3.84</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0107</v>
+        <v>0.0002</v>
       </c>
       <c r="H62" t="n">
-        <v>183.83</v>
+        <v>360.09</v>
       </c>
       <c r="I62" t="n">
-        <v>24915.58</v>
+        <v>25250.33</v>
       </c>
       <c r="J62" t="n">
-        <v>24850.24</v>
+        <v>25415.65</v>
       </c>
       <c r="K62" t="n">
-        <v>25118.9</v>
+        <v>25483.09</v>
       </c>
       <c r="L62" t="n">
-        <v>25387.56</v>
+        <v>25550.54</v>
       </c>
       <c r="M62" t="n">
-        <v>25489.22</v>
+        <v>25666.92</v>
       </c>
       <c r="N62" t="n">
-        <v>25590.88</v>
+        <v>25783.31</v>
       </c>
       <c r="O62" t="n">
-        <v>26026.54</v>
+        <v>25801.82</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5692,12 +5693,14 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T62" s="8" t="inlineStr">
@@ -5705,10 +5708,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U62" s="8" t="n">
+        <v/>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
@@ -5743,57 +5744,53 @@
         <v>25410.63</v>
       </c>
       <c r="F63" t="n">
-        <v>-164.38</v>
+        <v>-168.22</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.0066</v>
       </c>
       <c r="H63" t="n">
         <v>363.84</v>
       </c>
       <c r="I63" t="n">
-        <v>25250.33</v>
+        <v>25062.98</v>
       </c>
       <c r="J63" t="n">
-        <v>25415.65</v>
+        <v>25206.63</v>
       </c>
       <c r="K63" t="n">
-        <v>25483.09</v>
+        <v>25398.8</v>
       </c>
       <c r="L63" t="n">
-        <v>25550.54</v>
+        <v>25590.98</v>
       </c>
       <c r="M63" t="n">
-        <v>25666.92</v>
+        <v>25758.89</v>
       </c>
       <c r="N63" t="n">
-        <v>25783.31</v>
+        <v>25926.81</v>
       </c>
       <c r="O63" t="n">
-        <v>25801.82</v>
+        <v>26143.25</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
       </c>
-      <c r="Q63" s="6" t="inlineStr">
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
+      <c r="S63" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T63" s="8" t="n">
+        <v/>
       </c>
       <c r="U63" s="8" t="n">
         <v/>
@@ -5806,11 +5803,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5828,13 +5821,13 @@
         <v>25164.2</v>
       </c>
       <c r="E64" t="n">
-        <v/>
+        <v>25266.53</v>
       </c>
       <c r="F64" t="n">
-        <v/>
+        <v>-144.1</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v/>
+        <v>-0.0057</v>
       </c>
       <c r="H64" t="n">
         <v>260.01</v>
@@ -5860,22 +5853,20 @@
       <c r="O64" t="n">
         <v>26092.89</v>
       </c>
-      <c r="P64" s="6" t="inlineStr">
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R64" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S64" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T64" s="8" t="n">
@@ -5893,6 +5884,92 @@
         </is>
       </c>
       <c r="X64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>25441.79</v>
+      </c>
+      <c r="C65" t="n">
+        <v>25529.33</v>
+      </c>
+      <c r="D65" t="n">
+        <v>25347.3</v>
+      </c>
+      <c r="E65" t="n">
+        <v>25408.64</v>
+      </c>
+      <c r="F65" t="n">
+        <v>142.11</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="H65" t="n">
+        <v>182.03</v>
+      </c>
+      <c r="I65" t="n">
+        <v>24904.19</v>
+      </c>
+      <c r="J65" t="n">
+        <v>24992.68</v>
+      </c>
+      <c r="K65" t="n">
+        <v>25136.52</v>
+      </c>
+      <c r="L65" t="n">
+        <v>25280.37</v>
+      </c>
+      <c r="M65" t="n">
+        <v>25396.54</v>
+      </c>
+      <c r="N65" t="n">
+        <v>25512.7</v>
+      </c>
+      <c r="O65" t="n">
+        <v>25684.22</v>
+      </c>
+      <c r="P65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S65" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W65" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,50 +637,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24815.22</v>
+        <v>25028.93</v>
       </c>
       <c r="C2" t="n">
-        <v>25024.27</v>
+        <v>25095.66</v>
       </c>
       <c r="D2" t="n">
-        <v>24794.84</v>
+        <v>24887</v>
       </c>
       <c r="E2" t="n">
-        <v>24995.81</v>
+        <v>25040.28</v>
       </c>
       <c r="F2" t="n">
-        <v>368.92</v>
+        <v>44.47</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.015</v>
+        <v>0.0018</v>
       </c>
       <c r="H2" t="n">
-        <v>229.43</v>
+        <v>208.66</v>
       </c>
       <c r="I2" t="n">
-        <v>24351.32</v>
+        <v>24565.41</v>
       </c>
       <c r="J2" t="n">
-        <v>24405.12</v>
+        <v>24809.51</v>
       </c>
       <c r="K2" t="n">
-        <v>24524.16</v>
+        <v>24881.1</v>
       </c>
       <c r="L2" t="n">
-        <v>24643.2</v>
+        <v>24952.68</v>
       </c>
       <c r="M2" t="n">
-        <v>24729.62</v>
+        <v>25110.53</v>
       </c>
       <c r="N2" t="n">
-        <v>24816.04</v>
+        <v>25268.37</v>
       </c>
       <c r="O2" t="n">
-        <v>24967.7</v>
+        <v>25253.7</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,18 +698,14 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -718,50 +717,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25028.93</v>
+        <v>25025.13</v>
       </c>
       <c r="C3" t="n">
-        <v>25095.66</v>
+        <v>25655.82</v>
       </c>
       <c r="D3" t="n">
-        <v>24887</v>
+        <v>24994.64</v>
       </c>
       <c r="E3" t="n">
-        <v>25040.28</v>
+        <v>25580.88</v>
       </c>
       <c r="F3" t="n">
-        <v>44.47</v>
+        <v>540.6</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0216</v>
       </c>
       <c r="H3" t="n">
-        <v>208.66</v>
+        <v>661.1799999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>24565.41</v>
+        <v>24678.34</v>
       </c>
       <c r="J3" t="n">
-        <v>24809.51</v>
+        <v>24856.09</v>
       </c>
       <c r="K3" t="n">
-        <v>24881.1</v>
+        <v>24935.95</v>
       </c>
       <c r="L3" t="n">
-        <v>24952.68</v>
+        <v>25015.8</v>
       </c>
       <c r="M3" t="n">
-        <v>25110.53</v>
+        <v>25144.61</v>
       </c>
       <c r="N3" t="n">
-        <v>25268.37</v>
+        <v>25273.41</v>
       </c>
       <c r="O3" t="n">
-        <v>25253.7</v>
+        <v>25304.32</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -779,14 +778,18 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
@@ -798,50 +801,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25025.13</v>
+        <v>25763.97</v>
       </c>
       <c r="C4" t="n">
-        <v>25655.82</v>
+        <v>25826.78</v>
       </c>
       <c r="D4" t="n">
-        <v>24994.64</v>
+        <v>25611.69</v>
       </c>
       <c r="E4" t="n">
-        <v>25580.88</v>
+        <v>25779.31</v>
       </c>
       <c r="F4" t="n">
-        <v>540.6</v>
+        <v>198.43</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0216</v>
+        <v>0.0078</v>
       </c>
       <c r="H4" t="n">
-        <v>661.1799999999999</v>
+        <v>215.09</v>
       </c>
       <c r="I4" t="n">
-        <v>24678.34</v>
+        <v>24333.46</v>
       </c>
       <c r="J4" t="n">
-        <v>24856.09</v>
+        <v>25047.53</v>
       </c>
       <c r="K4" t="n">
-        <v>24935.95</v>
+        <v>25250.29</v>
       </c>
       <c r="L4" t="n">
-        <v>25015.8</v>
+        <v>25453.06</v>
       </c>
       <c r="M4" t="n">
-        <v>25144.61</v>
+        <v>25911.47</v>
       </c>
       <c r="N4" t="n">
-        <v>25273.41</v>
+        <v>26369.89</v>
       </c>
       <c r="O4" t="n">
-        <v>25304.32</v>
+        <v>26317</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -859,18 +862,14 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
@@ -882,50 +881,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25763.97</v>
+        <v>25811.9</v>
       </c>
       <c r="C5" t="n">
-        <v>25826.78</v>
+        <v>25900.1</v>
       </c>
       <c r="D5" t="n">
-        <v>25611.69</v>
+        <v>25698.56</v>
       </c>
       <c r="E5" t="n">
-        <v>25779.31</v>
+        <v>25817.89</v>
       </c>
       <c r="F5" t="n">
-        <v>198.43</v>
+        <v>38.58</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0078</v>
+        <v>0.0015</v>
       </c>
       <c r="H5" t="n">
-        <v>215.09</v>
+        <v>201.54</v>
       </c>
       <c r="I5" t="n">
-        <v>24333.46</v>
+        <v>25396.6</v>
       </c>
       <c r="J5" t="n">
-        <v>25047.53</v>
+        <v>25594.26</v>
       </c>
       <c r="K5" t="n">
-        <v>25250.29</v>
+        <v>25671.77</v>
       </c>
       <c r="L5" t="n">
-        <v>25453.06</v>
+        <v>25749.27</v>
       </c>
       <c r="M5" t="n">
-        <v>25911.47</v>
+        <v>25886.86</v>
       </c>
       <c r="N5" t="n">
-        <v>26369.89</v>
+        <v>26024.44</v>
       </c>
       <c r="O5" t="n">
-        <v>26317</v>
+        <v>26041.87</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -938,12 +937,12 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U5" s="8" t="n">
@@ -962,69 +961,73 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25811.9</v>
+        <v>25770.45</v>
       </c>
       <c r="C6" t="n">
-        <v>25900.1</v>
+        <v>25811.97</v>
       </c>
       <c r="D6" t="n">
-        <v>25698.56</v>
+        <v>25465.12</v>
       </c>
       <c r="E6" t="n">
-        <v>25817.89</v>
+        <v>25465.25</v>
       </c>
       <c r="F6" t="n">
-        <v>38.58</v>
+        <v>-352.64</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0137</v>
       </c>
       <c r="H6" t="n">
-        <v>201.54</v>
+        <v>346.85</v>
       </c>
       <c r="I6" t="n">
-        <v>25396.6</v>
+        <v>25497.02</v>
       </c>
       <c r="J6" t="n">
-        <v>25594.26</v>
+        <v>25625.63</v>
       </c>
       <c r="K6" t="n">
-        <v>25671.77</v>
+        <v>25717.12</v>
       </c>
       <c r="L6" t="n">
-        <v>25749.27</v>
+        <v>25808.61</v>
       </c>
       <c r="M6" t="n">
-        <v>25886.86</v>
+        <v>25918.66</v>
       </c>
       <c r="N6" t="n">
-        <v>26024.44</v>
+        <v>26028.71</v>
       </c>
       <c r="O6" t="n">
-        <v>26041.87</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>26101.64</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1032,9 +1035,9 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1042,59 +1045,59 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25770.45</v>
+        <v>25274.94</v>
       </c>
       <c r="C7" t="n">
-        <v>25811.97</v>
+        <v>25280.16</v>
       </c>
       <c r="D7" t="n">
-        <v>25465.12</v>
+        <v>24830.17</v>
       </c>
       <c r="E7" t="n">
-        <v>25465.25</v>
+        <v>24897.45</v>
       </c>
       <c r="F7" t="n">
-        <v>-352.64</v>
+        <v>-567.8</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0223</v>
       </c>
       <c r="H7" t="n">
-        <v>346.85</v>
+        <v>449.99</v>
       </c>
       <c r="I7" t="n">
-        <v>25497.02</v>
+        <v>25118.27</v>
       </c>
       <c r="J7" t="n">
-        <v>25625.63</v>
+        <v>25031.75</v>
       </c>
       <c r="K7" t="n">
-        <v>25717.12</v>
+        <v>25291.82</v>
       </c>
       <c r="L7" t="n">
-        <v>25808.61</v>
+        <v>25551.9</v>
       </c>
       <c r="M7" t="n">
-        <v>25918.66</v>
+        <v>25638.68</v>
       </c>
       <c r="N7" t="n">
-        <v>26028.71</v>
+        <v>25725.45</v>
       </c>
       <c r="O7" t="n">
-        <v>26101.64</v>
+        <v>26158.82</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
@@ -1126,74 +1129,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25274.94</v>
+        <v>25097.48</v>
       </c>
       <c r="C8" t="n">
-        <v>25280.16</v>
+        <v>25127.76</v>
       </c>
       <c r="D8" t="n">
-        <v>24830.17</v>
+        <v>24867.32</v>
       </c>
       <c r="E8" t="n">
-        <v>24897.45</v>
+        <v>25118.27</v>
       </c>
       <c r="F8" t="n">
-        <v>-567.8</v>
+        <v>220.82</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0089</v>
       </c>
       <c r="H8" t="n">
-        <v>449.99</v>
+        <v>260.44</v>
       </c>
       <c r="I8" t="n">
-        <v>25118.27</v>
+        <v>24380.18</v>
       </c>
       <c r="J8" t="n">
-        <v>25031.75</v>
+        <v>24368.6</v>
       </c>
       <c r="K8" t="n">
-        <v>25291.82</v>
+        <v>24672.45</v>
       </c>
       <c r="L8" t="n">
-        <v>25551.9</v>
+        <v>24976.31</v>
       </c>
       <c r="M8" t="n">
-        <v>25638.68</v>
+        <v>25122.44</v>
       </c>
       <c r="N8" t="n">
-        <v>25725.45</v>
+        <v>25268.58</v>
       </c>
       <c r="O8" t="n">
-        <v>26158.82</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
+        <v>25730.15</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1205,55 +1204,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25097.48</v>
+        <v>25081.19</v>
       </c>
       <c r="C9" t="n">
-        <v>25127.76</v>
+        <v>25195.83</v>
       </c>
       <c r="D9" t="n">
-        <v>24867.32</v>
+        <v>24937.52</v>
       </c>
       <c r="E9" t="n">
-        <v>25118.27</v>
+        <v>25067.09</v>
       </c>
       <c r="F9" t="n">
-        <v>220.82</v>
+        <v>-51.18</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.002</v>
       </c>
       <c r="H9" t="n">
-        <v>260.44</v>
+        <v>258.31</v>
       </c>
       <c r="I9" t="n">
-        <v>24380.18</v>
+        <v>24606.88</v>
       </c>
       <c r="J9" t="n">
-        <v>24368.6</v>
+        <v>24918.19</v>
       </c>
       <c r="K9" t="n">
-        <v>24672.45</v>
+        <v>24988.05</v>
       </c>
       <c r="L9" t="n">
-        <v>24976.31</v>
+        <v>25057.9</v>
       </c>
       <c r="M9" t="n">
-        <v>25122.44</v>
+        <v>25248.49</v>
       </c>
       <c r="N9" t="n">
-        <v>25268.58</v>
+        <v>25439.07</v>
       </c>
       <c r="O9" t="n">
-        <v>25730.15</v>
+        <v>25388.2</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1261,18 +1264,18 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1294,50 +1297,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25081.19</v>
+        <v>24963.8</v>
       </c>
       <c r="C10" t="n">
-        <v>25195.83</v>
+        <v>25154.58</v>
       </c>
       <c r="D10" t="n">
-        <v>24937.52</v>
+        <v>24963.8</v>
       </c>
       <c r="E10" t="n">
-        <v>25067.09</v>
+        <v>25114.25</v>
       </c>
       <c r="F10" t="n">
-        <v>-51.18</v>
+        <v>47.16</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="H10" t="n">
-        <v>258.31</v>
+        <v>190.78</v>
       </c>
       <c r="I10" t="n">
-        <v>24606.88</v>
+        <v>24679.21</v>
       </c>
       <c r="J10" t="n">
-        <v>24918.19</v>
+        <v>24808.99</v>
       </c>
       <c r="K10" t="n">
-        <v>24988.05</v>
+        <v>24937.93</v>
       </c>
       <c r="L10" t="n">
-        <v>25057.9</v>
+        <v>25066.88</v>
       </c>
       <c r="M10" t="n">
-        <v>25248.49</v>
+        <v>25196.25</v>
       </c>
       <c r="N10" t="n">
-        <v>25439.07</v>
+        <v>25325.61</v>
       </c>
       <c r="O10" t="n">
-        <v>25388.2</v>
+        <v>25454.14</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1345,10 +1348,8 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
@@ -1378,59 +1379,63 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24963.8</v>
+        <v>24932.62</v>
       </c>
       <c r="C11" t="n">
-        <v>25154.58</v>
+        <v>25204.68</v>
       </c>
       <c r="D11" t="n">
-        <v>24963.8</v>
+        <v>24869.25</v>
       </c>
       <c r="E11" t="n">
-        <v>25114.25</v>
+        <v>25147.03</v>
       </c>
       <c r="F11" t="n">
-        <v>47.16</v>
+        <v>32.78</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0013</v>
       </c>
       <c r="H11" t="n">
-        <v>190.78</v>
+        <v>335.43</v>
       </c>
       <c r="I11" t="n">
-        <v>24679.21</v>
+        <v>24773.02</v>
       </c>
       <c r="J11" t="n">
-        <v>24808.99</v>
+        <v>24951</v>
       </c>
       <c r="K11" t="n">
-        <v>24937.93</v>
+        <v>25018.86</v>
       </c>
       <c r="L11" t="n">
-        <v>25066.88</v>
+        <v>25086.72</v>
       </c>
       <c r="M11" t="n">
-        <v>25196.25</v>
+        <v>25209.64</v>
       </c>
       <c r="N11" t="n">
-        <v>25325.61</v>
+        <v>25332.56</v>
       </c>
       <c r="O11" t="n">
-        <v>25454.14</v>
+        <v>25345.36</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
@@ -1460,50 +1465,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24932.62</v>
+        <v>24970.05</v>
       </c>
       <c r="C12" t="n">
-        <v>25204.68</v>
+        <v>25055.48</v>
       </c>
       <c r="D12" t="n">
-        <v>24869.25</v>
+        <v>24839.23</v>
       </c>
       <c r="E12" t="n">
-        <v>25147.03</v>
+        <v>24999.53</v>
       </c>
       <c r="F12" t="n">
-        <v>32.78</v>
+        <v>-147.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0059</v>
       </c>
       <c r="H12" t="n">
-        <v>335.43</v>
+        <v>216.25</v>
       </c>
       <c r="I12" t="n">
-        <v>24773.02</v>
+        <v>24533.82</v>
       </c>
       <c r="J12" t="n">
-        <v>24951</v>
+        <v>24866.63</v>
       </c>
       <c r="K12" t="n">
-        <v>25018.86</v>
+        <v>24979.31</v>
       </c>
       <c r="L12" t="n">
-        <v>25086.72</v>
+        <v>25092</v>
       </c>
       <c r="M12" t="n">
-        <v>25209.64</v>
+        <v>25314.74</v>
       </c>
       <c r="N12" t="n">
-        <v>25332.56</v>
+        <v>25537.49</v>
       </c>
       <c r="O12" t="n">
-        <v>25345.36</v>
+        <v>25540.11</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1515,12 +1520,12 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1537,59 +1542,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24970.05</v>
+        <v>25018.95</v>
       </c>
       <c r="C13" t="n">
-        <v>25055.48</v>
+        <v>25021.51</v>
       </c>
       <c r="D13" t="n">
-        <v>24839.23</v>
+        <v>24696.17</v>
       </c>
       <c r="E13" t="n">
-        <v>24999.53</v>
+        <v>24915.49</v>
       </c>
       <c r="F13" t="n">
-        <v>-147.5</v>
+        <v>-84.04000000000001</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0059</v>
+        <v>-0.0034</v>
       </c>
       <c r="H13" t="n">
-        <v>216.25</v>
+        <v>325.34</v>
       </c>
       <c r="I13" t="n">
-        <v>24533.82</v>
+        <v>24622.98</v>
       </c>
       <c r="J13" t="n">
-        <v>24866.63</v>
+        <v>24809.37</v>
       </c>
       <c r="K13" t="n">
-        <v>24979.31</v>
+        <v>24891.4</v>
       </c>
       <c r="L13" t="n">
-        <v>25092</v>
+        <v>24973.44</v>
       </c>
       <c r="M13" t="n">
-        <v>25314.74</v>
+        <v>25107.65</v>
       </c>
       <c r="N13" t="n">
-        <v>25537.49</v>
+        <v>25241.87</v>
       </c>
       <c r="O13" t="n">
-        <v>25540.11</v>
+        <v>25271.73</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1628,67 +1629,65 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25018.95</v>
+        <v>24755.09</v>
       </c>
       <c r="C14" t="n">
-        <v>25021.51</v>
+        <v>24850.75</v>
       </c>
       <c r="D14" t="n">
-        <v>24696.17</v>
+        <v>24651.34</v>
       </c>
       <c r="E14" t="n">
-        <v>24915.49</v>
+        <v>24830.98</v>
       </c>
       <c r="F14" t="n">
-        <v>-84.04000000000001</v>
+        <v>-84.51000000000001</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>-0.0034</v>
       </c>
       <c r="H14" t="n">
-        <v>325.34</v>
+        <v>199.41</v>
       </c>
       <c r="I14" t="n">
-        <v>24622.98</v>
+        <v>24370.83</v>
       </c>
       <c r="J14" t="n">
-        <v>24809.37</v>
+        <v>24618.48</v>
       </c>
       <c r="K14" t="n">
-        <v>24891.4</v>
+        <v>24752.82</v>
       </c>
       <c r="L14" t="n">
-        <v>24973.44</v>
+        <v>24887.17</v>
       </c>
       <c r="M14" t="n">
-        <v>25107.65</v>
+        <v>25078.16</v>
       </c>
       <c r="N14" t="n">
-        <v>25241.87</v>
+        <v>25269.16</v>
       </c>
       <c r="O14" t="n">
-        <v>25271.73</v>
+        <v>25346.85</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q14" s="6" t="n">
+        <v/>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1710,50 +1709,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24755.09</v>
+        <v>24769.15</v>
       </c>
       <c r="C15" t="n">
-        <v>24850.75</v>
+        <v>24974.53</v>
       </c>
       <c r="D15" t="n">
-        <v>24651.34</v>
+        <v>24751.13</v>
       </c>
       <c r="E15" t="n">
-        <v>24830.98</v>
+        <v>24846.69</v>
       </c>
       <c r="F15" t="n">
-        <v>-84.51000000000001</v>
+        <v>15.71</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>199.41</v>
+        <v>223.4</v>
       </c>
       <c r="I15" t="n">
-        <v>24370.83</v>
+        <v>24451.93</v>
       </c>
       <c r="J15" t="n">
-        <v>24618.48</v>
+        <v>24671.54</v>
       </c>
       <c r="K15" t="n">
-        <v>24752.82</v>
+        <v>24731.28</v>
       </c>
       <c r="L15" t="n">
-        <v>24887.17</v>
+        <v>24791.01</v>
       </c>
       <c r="M15" t="n">
-        <v>25078.16</v>
+        <v>24930.69</v>
       </c>
       <c r="N15" t="n">
-        <v>25269.16</v>
+        <v>25070.36</v>
       </c>
       <c r="O15" t="n">
-        <v>25346.85</v>
+        <v>25050.16</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1761,18 +1760,18 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1785,55 +1784,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24769.15</v>
+        <v>24922.1</v>
       </c>
       <c r="C16" t="n">
-        <v>24974.53</v>
+        <v>25011.35</v>
       </c>
       <c r="D16" t="n">
-        <v>24751.13</v>
+        <v>24817.34</v>
       </c>
       <c r="E16" t="n">
-        <v>24846.69</v>
+        <v>25011.35</v>
       </c>
       <c r="F16" t="n">
-        <v>15.71</v>
+        <v>164.66</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0066</v>
       </c>
       <c r="H16" t="n">
-        <v>223.4</v>
+        <v>194.01</v>
       </c>
       <c r="I16" t="n">
-        <v>24451.93</v>
+        <v>24527.73</v>
       </c>
       <c r="J16" t="n">
-        <v>24671.54</v>
+        <v>24615.22</v>
       </c>
       <c r="K16" t="n">
-        <v>24731.28</v>
+        <v>24734.99</v>
       </c>
       <c r="L16" t="n">
-        <v>24791.01</v>
+        <v>24854.76</v>
       </c>
       <c r="M16" t="n">
-        <v>24930.69</v>
+        <v>24958.39</v>
       </c>
       <c r="N16" t="n">
-        <v>25070.36</v>
+        <v>25062.02</v>
       </c>
       <c r="O16" t="n">
-        <v>25050.16</v>
+        <v>25197.93</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1846,7 +1849,7 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
@@ -1854,8 +1857,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1874,50 +1879,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24922.1</v>
+        <v>25001.31</v>
       </c>
       <c r="C17" t="n">
-        <v>25011.35</v>
+        <v>25271.34</v>
       </c>
       <c r="D17" t="n">
-        <v>24817.34</v>
+        <v>24984.27</v>
       </c>
       <c r="E17" t="n">
-        <v>25011.35</v>
+        <v>25155.41</v>
       </c>
       <c r="F17" t="n">
-        <v>164.66</v>
+        <v>144.06</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0058</v>
       </c>
       <c r="H17" t="n">
-        <v>194.01</v>
+        <v>287.07</v>
       </c>
       <c r="I17" t="n">
-        <v>24527.73</v>
+        <v>24623.33</v>
       </c>
       <c r="J17" t="n">
-        <v>24615.22</v>
+        <v>24865.84</v>
       </c>
       <c r="K17" t="n">
-        <v>24734.99</v>
+        <v>24914.34</v>
       </c>
       <c r="L17" t="n">
-        <v>24854.76</v>
+        <v>24962.85</v>
       </c>
       <c r="M17" t="n">
-        <v>24958.39</v>
+        <v>25108.35</v>
       </c>
       <c r="N17" t="n">
-        <v>25062.02</v>
+        <v>25253.86</v>
       </c>
       <c r="O17" t="n">
-        <v>25197.93</v>
+        <v>25205.36</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1935,16 +1940,18 @@
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U17" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W17" s="11" t="inlineStr">
         <is>
@@ -1960,171 +1967,165 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25001.31</v>
+        <v>24994.05</v>
       </c>
       <c r="C18" t="n">
-        <v>25271.34</v>
+        <v>25074.28</v>
       </c>
       <c r="D18" t="n">
-        <v>24984.27</v>
+        <v>24696.59</v>
       </c>
       <c r="E18" t="n">
-        <v>25155.41</v>
+        <v>24763.12</v>
       </c>
       <c r="F18" t="n">
-        <v>144.06</v>
+        <v>-392.29</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0156</v>
       </c>
       <c r="H18" t="n">
-        <v>287.07</v>
+        <v>377.69</v>
       </c>
       <c r="I18" t="n">
-        <v>24623.33</v>
+        <v>24697.2</v>
       </c>
       <c r="J18" t="n">
-        <v>24865.84</v>
+        <v>24882.14</v>
       </c>
       <c r="K18" t="n">
-        <v>24914.34</v>
+        <v>25011.88</v>
       </c>
       <c r="L18" t="n">
-        <v>24962.85</v>
+        <v>25141.61</v>
       </c>
       <c r="M18" t="n">
-        <v>25108.35</v>
+        <v>25298.95</v>
       </c>
       <c r="N18" t="n">
-        <v>25253.86</v>
+        <v>25456.28</v>
       </c>
       <c r="O18" t="n">
-        <v>25205.36</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
+        <v>25558.41</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
       </c>
       <c r="W18" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24994.05</v>
+        <v>24830.41</v>
       </c>
       <c r="C19" t="n">
-        <v>25074.28</v>
+        <v>25099.68</v>
       </c>
       <c r="D19" t="n">
-        <v>24696.59</v>
+        <v>24821.67</v>
       </c>
       <c r="E19" t="n">
-        <v>24763.12</v>
+        <v>25099</v>
       </c>
       <c r="F19" t="n">
-        <v>-392.29</v>
+        <v>335.88</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0136</v>
       </c>
       <c r="H19" t="n">
-        <v>377.69</v>
+        <v>278.01</v>
       </c>
       <c r="I19" t="n">
-        <v>24697.2</v>
+        <v>24318.9</v>
       </c>
       <c r="J19" t="n">
-        <v>24882.14</v>
+        <v>24324.27</v>
       </c>
       <c r="K19" t="n">
-        <v>25011.88</v>
+        <v>24574.27</v>
       </c>
       <c r="L19" t="n">
-        <v>25141.61</v>
+        <v>24824.28</v>
       </c>
       <c r="M19" t="n">
-        <v>25298.95</v>
+        <v>24951.96</v>
       </c>
       <c r="N19" t="n">
-        <v>25456.28</v>
+        <v>25079.65</v>
       </c>
       <c r="O19" t="n">
-        <v>25558.41</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
+        <v>25451.97</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
@@ -2132,50 +2133,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24830.41</v>
+        <v>25459.32</v>
       </c>
       <c r="C20" t="n">
-        <v>25099.68</v>
+        <v>25560.4</v>
       </c>
       <c r="D20" t="n">
-        <v>24821.67</v>
+        <v>25361.03</v>
       </c>
       <c r="E20" t="n">
-        <v>25099</v>
+        <v>25361.03</v>
       </c>
       <c r="F20" t="n">
-        <v>335.88</v>
+        <v>262.03</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0104</v>
       </c>
       <c r="H20" t="n">
-        <v>278.01</v>
+        <v>199.37</v>
       </c>
       <c r="I20" t="n">
-        <v>24318.9</v>
+        <v>24543.66</v>
       </c>
       <c r="J20" t="n">
-        <v>24324.27</v>
+        <v>24890.15</v>
       </c>
       <c r="K20" t="n">
-        <v>24574.27</v>
+        <v>24960</v>
       </c>
       <c r="L20" t="n">
-        <v>24824.28</v>
+        <v>25029.84</v>
       </c>
       <c r="M20" t="n">
-        <v>24951.96</v>
+        <v>25238</v>
       </c>
       <c r="N20" t="n">
-        <v>25079.65</v>
+        <v>25446.17</v>
       </c>
       <c r="O20" t="n">
-        <v>25451.97</v>
+        <v>25377.69</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2198,11 +2199,13 @@
       </c>
       <c r="U20" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
@@ -2214,50 +2217,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25459.32</v>
+        <v>25496.13</v>
       </c>
       <c r="C21" t="n">
-        <v>25560.4</v>
+        <v>25553.47</v>
       </c>
       <c r="D21" t="n">
-        <v>25361.03</v>
+        <v>25307.17</v>
       </c>
       <c r="E21" t="n">
-        <v>25361.03</v>
+        <v>25464.01</v>
       </c>
       <c r="F21" t="n">
-        <v>262.03</v>
+        <v>102.98</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0104</v>
+        <v>0.0041</v>
       </c>
       <c r="H21" t="n">
-        <v>199.37</v>
+        <v>246.3</v>
       </c>
       <c r="I21" t="n">
-        <v>24543.66</v>
+        <v>25161.66</v>
       </c>
       <c r="J21" t="n">
-        <v>24890.15</v>
+        <v>25111.82</v>
       </c>
       <c r="K21" t="n">
-        <v>24960</v>
+        <v>25261.34</v>
       </c>
       <c r="L21" t="n">
-        <v>25029.84</v>
+        <v>25410.87</v>
       </c>
       <c r="M21" t="n">
-        <v>25238</v>
+        <v>25460.71</v>
       </c>
       <c r="N21" t="n">
-        <v>25446.17</v>
+        <v>25510.56</v>
       </c>
       <c r="O21" t="n">
-        <v>25377.69</v>
+        <v>25759.77</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2275,7 +2278,7 @@
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U21" s="8" t="inlineStr">
@@ -2283,65 +2286,67 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25496.13</v>
+        <v>25551.97</v>
       </c>
       <c r="C22" t="n">
-        <v>25553.47</v>
+        <v>25571.45</v>
       </c>
       <c r="D22" t="n">
-        <v>25307.17</v>
+        <v>25336.39</v>
       </c>
       <c r="E22" t="n">
-        <v>25464.01</v>
+        <v>25460.48</v>
       </c>
       <c r="F22" t="n">
-        <v>102.98</v>
+        <v>-3.53</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0001</v>
       </c>
       <c r="H22" t="n">
-        <v>246.3</v>
+        <v>235.06</v>
       </c>
       <c r="I22" t="n">
-        <v>25161.66</v>
+        <v>25060.87</v>
       </c>
       <c r="J22" t="n">
-        <v>25111.82</v>
+        <v>25234.55</v>
       </c>
       <c r="K22" t="n">
-        <v>25261.34</v>
+        <v>25340.86</v>
       </c>
       <c r="L22" t="n">
-        <v>25410.87</v>
+        <v>25447.17</v>
       </c>
       <c r="M22" t="n">
-        <v>25460.71</v>
+        <v>25587.16</v>
       </c>
       <c r="N22" t="n">
-        <v>25510.56</v>
+        <v>25727.16</v>
       </c>
       <c r="O22" t="n">
-        <v>25759.77</v>
+        <v>25799.77</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2349,23 +2354,21 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2377,57 +2380,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25551.97</v>
+        <v>25487.45</v>
       </c>
       <c r="C23" t="n">
-        <v>25571.45</v>
+        <v>25651.16</v>
       </c>
       <c r="D23" t="n">
-        <v>25336.39</v>
+        <v>25303.11</v>
       </c>
       <c r="E23" t="n">
-        <v>25460.48</v>
+        <v>25612.03</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.53</v>
+        <v>151.55</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.006</v>
       </c>
       <c r="H23" t="n">
-        <v>235.06</v>
+        <v>348.05</v>
       </c>
       <c r="I23" t="n">
-        <v>25060.87</v>
+        <v>25101.33</v>
       </c>
       <c r="J23" t="n">
-        <v>25234.55</v>
+        <v>25228.7</v>
       </c>
       <c r="K23" t="n">
-        <v>25340.86</v>
+        <v>25342.95</v>
       </c>
       <c r="L23" t="n">
-        <v>25447.17</v>
+        <v>25457.2</v>
       </c>
       <c r="M23" t="n">
-        <v>25587.16</v>
+        <v>25578.01</v>
       </c>
       <c r="N23" t="n">
-        <v>25727.16</v>
+        <v>25698.82</v>
       </c>
       <c r="O23" t="n">
-        <v>25799.77</v>
+        <v>25806.51</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2442,11 +2445,13 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2468,50 +2473,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25487.45</v>
+        <v>25709.37</v>
       </c>
       <c r="C24" t="n">
-        <v>25651.16</v>
+        <v>25891.51</v>
       </c>
       <c r="D24" t="n">
-        <v>25303.11</v>
+        <v>25549.53</v>
       </c>
       <c r="E24" t="n">
-        <v>25612.03</v>
+        <v>25629.24</v>
       </c>
       <c r="F24" t="n">
-        <v>151.55</v>
+        <v>17.21</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0007</v>
       </c>
       <c r="H24" t="n">
-        <v>348.05</v>
+        <v>341.98</v>
       </c>
       <c r="I24" t="n">
-        <v>25101.33</v>
+        <v>24955.06</v>
       </c>
       <c r="J24" t="n">
-        <v>25228.7</v>
+        <v>25331.43</v>
       </c>
       <c r="K24" t="n">
-        <v>25342.95</v>
+        <v>25438</v>
       </c>
       <c r="L24" t="n">
-        <v>25457.2</v>
+        <v>25544.58</v>
       </c>
       <c r="M24" t="n">
-        <v>25578.01</v>
+        <v>25786.05</v>
       </c>
       <c r="N24" t="n">
-        <v>25698.82</v>
+        <v>26027.53</v>
       </c>
       <c r="O24" t="n">
-        <v>25806.51</v>
+        <v>25999.21</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2519,19 +2524,17 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R24" s="6" t="n">
+        <v/>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U24" s="8" t="n">
@@ -2545,59 +2548,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25709.37</v>
+        <v>25855.12</v>
       </c>
       <c r="C25" t="n">
-        <v>25891.51</v>
+        <v>26096.93</v>
       </c>
       <c r="D25" t="n">
-        <v>25549.53</v>
+        <v>25855.12</v>
       </c>
       <c r="E25" t="n">
-        <v>25629.24</v>
+        <v>26001.31</v>
       </c>
       <c r="F25" t="n">
-        <v>17.21</v>
+        <v>372.07</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0145</v>
       </c>
       <c r="H25" t="n">
-        <v>341.98</v>
+        <v>241.81</v>
       </c>
       <c r="I25" t="n">
-        <v>24955.06</v>
+        <v>25207.55</v>
       </c>
       <c r="J25" t="n">
-        <v>25331.43</v>
+        <v>25241.62</v>
       </c>
       <c r="K25" t="n">
-        <v>25438</v>
+        <v>25458.25</v>
       </c>
       <c r="L25" t="n">
-        <v>25544.58</v>
+        <v>25674.88</v>
       </c>
       <c r="M25" t="n">
-        <v>25786.05</v>
+        <v>25800.23</v>
       </c>
       <c r="N25" t="n">
-        <v>26027.53</v>
+        <v>25925.58</v>
       </c>
       <c r="O25" t="n">
-        <v>25999.21</v>
+        <v>26233.49</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2610,7 +2609,7 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -2618,8 +2617,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2634,50 +2635,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25855.12</v>
+        <v>26189.62</v>
       </c>
       <c r="C26" t="n">
-        <v>26096.93</v>
+        <v>26266.5</v>
       </c>
       <c r="D26" t="n">
-        <v>25855.12</v>
+        <v>26082.43</v>
       </c>
       <c r="E26" t="n">
-        <v>26001.31</v>
+        <v>26202.35</v>
       </c>
       <c r="F26" t="n">
-        <v>372.07</v>
+        <v>201.04</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0077</v>
       </c>
       <c r="H26" t="n">
-        <v>241.81</v>
+        <v>184.07</v>
       </c>
       <c r="I26" t="n">
-        <v>25207.55</v>
+        <v>25613.31</v>
       </c>
       <c r="J26" t="n">
-        <v>25241.62</v>
+        <v>25772.14</v>
       </c>
       <c r="K26" t="n">
-        <v>25458.25</v>
+        <v>25880.41</v>
       </c>
       <c r="L26" t="n">
-        <v>25674.88</v>
+        <v>25988.67</v>
       </c>
       <c r="M26" t="n">
-        <v>25800.23</v>
+        <v>26122.22</v>
       </c>
       <c r="N26" t="n">
-        <v>25925.58</v>
+        <v>26255.76</v>
       </c>
       <c r="O26" t="n">
-        <v>26233.49</v>
+        <v>26338.74</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2716,50 +2717,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26189.62</v>
+        <v>26393.43</v>
       </c>
       <c r="C27" t="n">
-        <v>26266.5</v>
+        <v>26403.81</v>
       </c>
       <c r="D27" t="n">
-        <v>26082.43</v>
+        <v>26123.18</v>
       </c>
       <c r="E27" t="n">
-        <v>26202.35</v>
+        <v>26126.3</v>
       </c>
       <c r="F27" t="n">
-        <v>201.04</v>
+        <v>-76.05</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0029</v>
       </c>
       <c r="H27" t="n">
-        <v>184.07</v>
+        <v>280.63</v>
       </c>
       <c r="I27" t="n">
-        <v>25613.31</v>
+        <v>25898.36</v>
       </c>
       <c r="J27" t="n">
-        <v>25772.14</v>
+        <v>26032.22</v>
       </c>
       <c r="K27" t="n">
-        <v>25880.41</v>
+        <v>26110.31</v>
       </c>
       <c r="L27" t="n">
-        <v>25988.67</v>
+        <v>26188.41</v>
       </c>
       <c r="M27" t="n">
-        <v>26122.22</v>
+        <v>26294.38</v>
       </c>
       <c r="N27" t="n">
-        <v>26255.76</v>
+        <v>26400.36</v>
       </c>
       <c r="O27" t="n">
-        <v>26338.74</v>
+        <v>26450.57</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2767,12 +2768,14 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
@@ -2782,7 +2785,7 @@
       </c>
       <c r="U27" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V27" s="8" t="n">
@@ -2793,55 +2796,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26393.43</v>
+        <v>26116.27</v>
       </c>
       <c r="C28" t="n">
-        <v>26403.81</v>
+        <v>26229.33</v>
       </c>
       <c r="D28" t="n">
-        <v>26123.18</v>
+        <v>26081.69</v>
       </c>
       <c r="E28" t="n">
-        <v>26126.3</v>
+        <v>26140.13</v>
       </c>
       <c r="F28" t="n">
-        <v>-76.05</v>
+        <v>13.83</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0005</v>
       </c>
       <c r="H28" t="n">
-        <v>280.63</v>
+        <v>147.64</v>
       </c>
       <c r="I28" t="n">
-        <v>25898.36</v>
+        <v>25842.55</v>
       </c>
       <c r="J28" t="n">
-        <v>26032.22</v>
+        <v>25777.07</v>
       </c>
       <c r="K28" t="n">
-        <v>26110.31</v>
+        <v>25985.99</v>
       </c>
       <c r="L28" t="n">
-        <v>26188.41</v>
+        <v>26194.9</v>
       </c>
       <c r="M28" t="n">
-        <v>26294.38</v>
+        <v>26266.62</v>
       </c>
       <c r="N28" t="n">
-        <v>26400.36</v>
+        <v>26338.33</v>
       </c>
       <c r="O28" t="n">
-        <v>26450.57</v>
+        <v>26684.44</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2849,25 +2856,19 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R28" s="6" t="n">
+        <v/>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2879,57 +2880,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>26116.27</v>
+        <v>26235.8</v>
       </c>
       <c r="C29" t="n">
-        <v>26229.33</v>
+        <v>26445.18</v>
       </c>
       <c r="D29" t="n">
-        <v>26081.69</v>
+        <v>26223.64</v>
       </c>
       <c r="E29" t="n">
-        <v>26140.13</v>
+        <v>26319.45</v>
       </c>
       <c r="F29" t="n">
-        <v>13.83</v>
+        <v>179.32</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0069</v>
       </c>
       <c r="H29" t="n">
-        <v>147.64</v>
+        <v>221.54</v>
       </c>
       <c r="I29" t="n">
-        <v>25842.55</v>
+        <v>25934.05</v>
       </c>
       <c r="J29" t="n">
-        <v>25777.07</v>
+        <v>25984.8</v>
       </c>
       <c r="K29" t="n">
-        <v>25985.99</v>
+        <v>26066.31</v>
       </c>
       <c r="L29" t="n">
-        <v>26194.9</v>
+        <v>26147.82</v>
       </c>
       <c r="M29" t="n">
-        <v>26266.62</v>
+        <v>26213.95</v>
       </c>
       <c r="N29" t="n">
-        <v>26338.33</v>
+        <v>26280.08</v>
       </c>
       <c r="O29" t="n">
-        <v>26684.44</v>
+        <v>26376.97</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2940,78 +2941,80 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26235.8</v>
+        <v>26360.44</v>
       </c>
       <c r="C30" t="n">
-        <v>26445.18</v>
+        <v>26441.91</v>
       </c>
       <c r="D30" t="n">
-        <v>26223.64</v>
+        <v>26302.19</v>
       </c>
       <c r="E30" t="n">
-        <v>26319.45</v>
+        <v>26323.88</v>
       </c>
       <c r="F30" t="n">
-        <v>179.32</v>
+        <v>4.43</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0002</v>
       </c>
       <c r="H30" t="n">
-        <v>221.54</v>
+        <v>139.72</v>
       </c>
       <c r="I30" t="n">
-        <v>25934.05</v>
+        <v>26002.1</v>
       </c>
       <c r="J30" t="n">
-        <v>25984.8</v>
+        <v>26090.43</v>
       </c>
       <c r="K30" t="n">
-        <v>26066.31</v>
+        <v>26208.68</v>
       </c>
       <c r="L30" t="n">
-        <v>26147.82</v>
+        <v>26326.93</v>
       </c>
       <c r="M30" t="n">
-        <v>26213.95</v>
+        <v>26430.22</v>
       </c>
       <c r="N30" t="n">
-        <v>26280.08</v>
+        <v>26533.51</v>
       </c>
       <c r="O30" t="n">
-        <v>26376.97</v>
+        <v>26666.72</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3022,9 +3025,9 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
@@ -3032,70 +3035,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v/>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>26360.44</v>
+        <v>26378</v>
       </c>
       <c r="C31" t="n">
-        <v>26441.91</v>
+        <v>26504.54</v>
       </c>
       <c r="D31" t="n">
-        <v>26302.19</v>
+        <v>26245.57</v>
       </c>
       <c r="E31" t="n">
-        <v>26323.88</v>
+        <v>26391.42</v>
       </c>
       <c r="F31" t="n">
-        <v>4.43</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0026</v>
       </c>
       <c r="H31" t="n">
-        <v>139.72</v>
+        <v>258.97</v>
       </c>
       <c r="I31" t="n">
-        <v>26002.1</v>
+        <v>26162.47</v>
       </c>
       <c r="J31" t="n">
-        <v>26090.43</v>
+        <v>26160.08</v>
       </c>
       <c r="K31" t="n">
-        <v>26208.68</v>
+        <v>26254.02</v>
       </c>
       <c r="L31" t="n">
-        <v>26326.93</v>
+        <v>26347.97</v>
       </c>
       <c r="M31" t="n">
-        <v>26430.22</v>
+        <v>26393.74</v>
       </c>
       <c r="N31" t="n">
-        <v>26533.51</v>
+        <v>26439.52</v>
       </c>
       <c r="O31" t="n">
-        <v>26666.72</v>
+        <v>26581.63</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3103,21 +3106,25 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3136,50 +3143,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26378</v>
+        <v>26452</v>
       </c>
       <c r="C32" t="n">
-        <v>26504.54</v>
+        <v>26573.5</v>
       </c>
       <c r="D32" t="n">
-        <v>26245.57</v>
+        <v>26313.58</v>
       </c>
       <c r="E32" t="n">
-        <v>26391.42</v>
+        <v>26331.07</v>
       </c>
       <c r="F32" t="n">
-        <v>67.54000000000001</v>
+        <v>-60.35</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0023</v>
       </c>
       <c r="H32" t="n">
-        <v>258.97</v>
+        <v>259.92</v>
       </c>
       <c r="I32" t="n">
-        <v>26162.47</v>
+        <v>25986.6</v>
       </c>
       <c r="J32" t="n">
-        <v>26160.08</v>
+        <v>26140.63</v>
       </c>
       <c r="K32" t="n">
-        <v>26254.02</v>
+        <v>26261.94</v>
       </c>
       <c r="L32" t="n">
-        <v>26347.97</v>
+        <v>26383.24</v>
       </c>
       <c r="M32" t="n">
-        <v>26393.74</v>
+        <v>26520.9</v>
       </c>
       <c r="N32" t="n">
-        <v>26439.52</v>
+        <v>26658.57</v>
       </c>
       <c r="O32" t="n">
-        <v>26581.63</v>
+        <v>26763.51</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3187,25 +3194,21 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3224,50 +3227,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>26452</v>
+        <v>26437.35</v>
       </c>
       <c r="C33" t="n">
-        <v>26573.5</v>
+        <v>26489.78</v>
       </c>
       <c r="D33" t="n">
-        <v>26313.58</v>
+        <v>26285.23</v>
       </c>
       <c r="E33" t="n">
-        <v>26331.07</v>
+        <v>26299.74</v>
       </c>
       <c r="F33" t="n">
-        <v>-60.35</v>
+        <v>-31.33</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0012</v>
       </c>
       <c r="H33" t="n">
-        <v>259.92</v>
+        <v>204.55</v>
       </c>
       <c r="I33" t="n">
-        <v>25986.6</v>
+        <v>26053.66</v>
       </c>
       <c r="J33" t="n">
-        <v>26140.63</v>
+        <v>26014.92</v>
       </c>
       <c r="K33" t="n">
-        <v>26261.94</v>
+        <v>26201.11</v>
       </c>
       <c r="L33" t="n">
-        <v>26383.24</v>
+        <v>26387.31</v>
       </c>
       <c r="M33" t="n">
-        <v>26520.9</v>
+        <v>26461.03</v>
       </c>
       <c r="N33" t="n">
-        <v>26658.57</v>
+        <v>26534.76</v>
       </c>
       <c r="O33" t="n">
-        <v>26763.51</v>
+        <v>26833.42</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3301,57 +3304,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26437.35</v>
+        <v>26445.99</v>
       </c>
       <c r="C34" t="n">
-        <v>26489.78</v>
+        <v>26541.34</v>
       </c>
       <c r="D34" t="n">
-        <v>26285.23</v>
+        <v>26404.95</v>
       </c>
       <c r="E34" t="n">
-        <v>26299.74</v>
+        <v>26440.31</v>
       </c>
       <c r="F34" t="n">
-        <v>-31.33</v>
+        <v>140.57</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0053</v>
       </c>
       <c r="H34" t="n">
-        <v>204.55</v>
+        <v>136.39</v>
       </c>
       <c r="I34" t="n">
-        <v>26053.66</v>
+        <v>26080.68</v>
       </c>
       <c r="J34" t="n">
-        <v>26014.92</v>
+        <v>26051.31</v>
       </c>
       <c r="K34" t="n">
-        <v>26201.11</v>
+        <v>26197.47</v>
       </c>
       <c r="L34" t="n">
-        <v>26387.31</v>
+        <v>26343.62</v>
       </c>
       <c r="M34" t="n">
-        <v>26461.03</v>
+        <v>26402.01</v>
       </c>
       <c r="N34" t="n">
-        <v>26534.76</v>
+        <v>26460.41</v>
       </c>
       <c r="O34" t="n">
-        <v>26833.42</v>
+        <v>26694.33</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3362,9 +3365,9 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
@@ -3372,8 +3375,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3383,59 +3388,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>26445.99</v>
+        <v>26490.3</v>
       </c>
       <c r="C35" t="n">
-        <v>26541.34</v>
+        <v>26493.5</v>
       </c>
       <c r="D35" t="n">
-        <v>26404.95</v>
+        <v>26338.61</v>
       </c>
       <c r="E35" t="n">
-        <v>26440.31</v>
+        <v>26338.61</v>
       </c>
       <c r="F35" t="n">
-        <v>140.57</v>
+        <v>-101.7</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0038</v>
       </c>
       <c r="H35" t="n">
-        <v>136.39</v>
+        <v>154.89</v>
       </c>
       <c r="I35" t="n">
-        <v>26080.68</v>
+        <v>26268.56</v>
       </c>
       <c r="J35" t="n">
-        <v>26051.31</v>
+        <v>26287.5</v>
       </c>
       <c r="K35" t="n">
-        <v>26197.47</v>
+        <v>26372.12</v>
       </c>
       <c r="L35" t="n">
-        <v>26343.62</v>
+        <v>26456.73</v>
       </c>
       <c r="M35" t="n">
-        <v>26402.01</v>
+        <v>26508.51</v>
       </c>
       <c r="N35" t="n">
-        <v>26460.41</v>
+        <v>26560.28</v>
       </c>
       <c r="O35" t="n">
-        <v>26694.33</v>
+        <v>26677.73</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3443,24 +3444,22 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
@@ -3469,65 +3468,73 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26490.3</v>
+        <v>26280.86</v>
       </c>
       <c r="C36" t="n">
-        <v>26493.5</v>
+        <v>26292.95</v>
       </c>
       <c r="D36" t="n">
-        <v>26338.61</v>
+        <v>26119.54</v>
       </c>
       <c r="E36" t="n">
-        <v>26338.61</v>
+        <v>26128.36</v>
       </c>
       <c r="F36" t="n">
-        <v>-101.7</v>
+        <v>-210.25</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.008</v>
       </c>
       <c r="H36" t="n">
-        <v>154.89</v>
+        <v>173.41</v>
       </c>
       <c r="I36" t="n">
-        <v>26268.56</v>
+        <v>26183.72</v>
       </c>
       <c r="J36" t="n">
-        <v>26287.5</v>
+        <v>26145</v>
       </c>
       <c r="K36" t="n">
-        <v>26372.12</v>
+        <v>26261.16</v>
       </c>
       <c r="L36" t="n">
-        <v>26456.73</v>
+        <v>26377.33</v>
       </c>
       <c r="M36" t="n">
-        <v>26508.51</v>
+        <v>26416.05</v>
       </c>
       <c r="N36" t="n">
-        <v>26560.28</v>
+        <v>26454.78</v>
       </c>
       <c r="O36" t="n">
-        <v>26677.73</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
+        <v>26648.39</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
@@ -3544,78 +3551,70 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W36" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26280.86</v>
+        <v>26146.12</v>
       </c>
       <c r="C37" t="n">
-        <v>26292.95</v>
+        <v>26187.82</v>
       </c>
       <c r="D37" t="n">
-        <v>26119.54</v>
+        <v>26063.37</v>
       </c>
       <c r="E37" t="n">
-        <v>26128.36</v>
+        <v>26091.33</v>
       </c>
       <c r="F37" t="n">
-        <v>-210.25</v>
+        <v>-37.03</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0014</v>
       </c>
       <c r="H37" t="n">
-        <v>173.41</v>
+        <v>124.45</v>
       </c>
       <c r="I37" t="n">
-        <v>26183.72</v>
+        <v>25946.13</v>
       </c>
       <c r="J37" t="n">
-        <v>26145</v>
+        <v>25916.01</v>
       </c>
       <c r="K37" t="n">
-        <v>26261.16</v>
+        <v>26041.65</v>
       </c>
       <c r="L37" t="n">
-        <v>26377.33</v>
+        <v>26167.3</v>
       </c>
       <c r="M37" t="n">
-        <v>26416.05</v>
+        <v>26215.06</v>
       </c>
       <c r="N37" t="n">
-        <v>26454.78</v>
+        <v>26262.83</v>
       </c>
       <c r="O37" t="n">
-        <v>26648.39</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
+        <v>26466.36</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
@@ -3642,60 +3641,64 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26146.12</v>
+        <v>26050.95</v>
       </c>
       <c r="C38" t="n">
-        <v>26187.82</v>
+        <v>26062.15</v>
       </c>
       <c r="D38" t="n">
-        <v>26063.37</v>
+        <v>25914.11</v>
       </c>
       <c r="E38" t="n">
-        <v>26091.33</v>
+        <v>25983.04</v>
       </c>
       <c r="F38" t="n">
-        <v>-37.03</v>
+        <v>-108.29</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0042</v>
       </c>
       <c r="H38" t="n">
-        <v>124.45</v>
+        <v>148.04</v>
       </c>
       <c r="I38" t="n">
-        <v>25946.13</v>
+        <v>25938.92</v>
       </c>
       <c r="J38" t="n">
-        <v>25916.01</v>
+        <v>25949.75</v>
       </c>
       <c r="K38" t="n">
-        <v>26041.65</v>
+        <v>26029.1</v>
       </c>
       <c r="L38" t="n">
-        <v>26167.3</v>
+        <v>26108.46</v>
       </c>
       <c r="M38" t="n">
-        <v>26215.06</v>
+        <v>26153.56</v>
       </c>
       <c r="N38" t="n">
-        <v>26262.83</v>
+        <v>26198.65</v>
       </c>
       <c r="O38" t="n">
-        <v>26466.36</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
+        <v>26312.27</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
@@ -3722,83 +3725,81 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26050.95</v>
+        <v>25998.95</v>
       </c>
       <c r="C39" t="n">
-        <v>26062.15</v>
+        <v>26166.25</v>
       </c>
       <c r="D39" t="n">
-        <v>25914.11</v>
+        <v>25969.52</v>
       </c>
       <c r="E39" t="n">
-        <v>25983.04</v>
+        <v>26136.56</v>
       </c>
       <c r="F39" t="n">
-        <v>-108.29</v>
+        <v>153.52</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.0059</v>
       </c>
       <c r="H39" t="n">
-        <v>148.04</v>
+        <v>196.73</v>
       </c>
       <c r="I39" t="n">
-        <v>25938.92</v>
+        <v>25766.07</v>
       </c>
       <c r="J39" t="n">
-        <v>25949.75</v>
+        <v>25832.45</v>
       </c>
       <c r="K39" t="n">
-        <v>26029.1</v>
+        <v>25909.02</v>
       </c>
       <c r="L39" t="n">
-        <v>26108.46</v>
+        <v>25985.58</v>
       </c>
       <c r="M39" t="n">
-        <v>26153.56</v>
+        <v>26057.06</v>
       </c>
       <c r="N39" t="n">
-        <v>26198.65</v>
+        <v>26128.53</v>
       </c>
       <c r="O39" t="n">
-        <v>26312.27</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
+        <v>26210.19</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W39" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr"/>
@@ -3806,50 +3807,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25998.95</v>
+        <v>26091.29</v>
       </c>
       <c r="C40" t="n">
-        <v>26166.25</v>
+        <v>26171.7</v>
       </c>
       <c r="D40" t="n">
-        <v>25969.52</v>
+        <v>26038.07</v>
       </c>
       <c r="E40" t="n">
-        <v>26136.56</v>
+        <v>26106.6</v>
       </c>
       <c r="F40" t="n">
-        <v>153.52</v>
+        <v>-29.96</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0011</v>
       </c>
       <c r="H40" t="n">
-        <v>196.73</v>
+        <v>133.63</v>
       </c>
       <c r="I40" t="n">
-        <v>25766.07</v>
+        <v>25772.79</v>
       </c>
       <c r="J40" t="n">
-        <v>25832.45</v>
+        <v>25974.17</v>
       </c>
       <c r="K40" t="n">
-        <v>25909.02</v>
+        <v>26038.2</v>
       </c>
       <c r="L40" t="n">
-        <v>25985.58</v>
+        <v>26102.22</v>
       </c>
       <c r="M40" t="n">
-        <v>26057.06</v>
+        <v>26234.93</v>
       </c>
       <c r="N40" t="n">
-        <v>26128.53</v>
+        <v>26367.63</v>
       </c>
       <c r="O40" t="n">
-        <v>26210.19</v>
+        <v>26362.98</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3857,23 +3858,21 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3883,55 +3882,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26091.29</v>
+        <v>26206.01</v>
       </c>
       <c r="C41" t="n">
-        <v>26171.7</v>
+        <v>26341.52</v>
       </c>
       <c r="D41" t="n">
-        <v>26038.07</v>
+        <v>26164.11</v>
       </c>
       <c r="E41" t="n">
-        <v>26106.6</v>
+        <v>26266.14</v>
       </c>
       <c r="F41" t="n">
-        <v>-29.96</v>
+        <v>159.54</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0061</v>
       </c>
       <c r="H41" t="n">
-        <v>133.63</v>
+        <v>177.41</v>
       </c>
       <c r="I41" t="n">
-        <v>25772.79</v>
+        <v>25904.44</v>
       </c>
       <c r="J41" t="n">
-        <v>25974.17</v>
+        <v>25973.83</v>
       </c>
       <c r="K41" t="n">
-        <v>26038.2</v>
+        <v>26039.79</v>
       </c>
       <c r="L41" t="n">
-        <v>26102.22</v>
+        <v>26105.74</v>
       </c>
       <c r="M41" t="n">
-        <v>26234.93</v>
+        <v>26173.41</v>
       </c>
       <c r="N41" t="n">
-        <v>26367.63</v>
+        <v>26241.09</v>
       </c>
       <c r="O41" t="n">
-        <v>26362.98</v>
+        <v>26305.33</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3939,83 +3942,83 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26206.01</v>
+        <v>26255.41</v>
       </c>
       <c r="C42" t="n">
-        <v>26341.52</v>
+        <v>26466.76</v>
       </c>
       <c r="D42" t="n">
-        <v>26164.11</v>
+        <v>26196.92</v>
       </c>
       <c r="E42" t="n">
-        <v>26266.14</v>
+        <v>26285.96</v>
       </c>
       <c r="F42" t="n">
-        <v>159.54</v>
+        <v>19.82</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0061</v>
+        <v>0.0008</v>
       </c>
       <c r="H42" t="n">
-        <v>177.41</v>
+        <v>269.84</v>
       </c>
       <c r="I42" t="n">
-        <v>25904.44</v>
+        <v>25986.7</v>
       </c>
       <c r="J42" t="n">
-        <v>25973.83</v>
+        <v>26095.39</v>
       </c>
       <c r="K42" t="n">
-        <v>26039.79</v>
+        <v>26177.44</v>
       </c>
       <c r="L42" t="n">
-        <v>26105.74</v>
+        <v>26259.48</v>
       </c>
       <c r="M42" t="n">
-        <v>26173.41</v>
+        <v>26354.85</v>
       </c>
       <c r="N42" t="n">
-        <v>26241.09</v>
+        <v>26450.21</v>
       </c>
       <c r="O42" t="n">
-        <v>26305.33</v>
+        <v>26518.93</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4028,7 +4031,7 @@
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
@@ -4038,13 +4041,11 @@
       </c>
       <c r="U42" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v/>
       </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
@@ -4056,50 +4057,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>26255.41</v>
+        <v>26354.37</v>
       </c>
       <c r="C43" t="n">
-        <v>26466.76</v>
+        <v>26402.81</v>
       </c>
       <c r="D43" t="n">
-        <v>26196.92</v>
+        <v>26241.77</v>
       </c>
       <c r="E43" t="n">
-        <v>26285.96</v>
+        <v>26367.24</v>
       </c>
       <c r="F43" t="n">
-        <v>19.82</v>
+        <v>81.28</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0031</v>
       </c>
       <c r="H43" t="n">
-        <v>269.84</v>
+        <v>161.04</v>
       </c>
       <c r="I43" t="n">
-        <v>25986.7</v>
+        <v>25927.08</v>
       </c>
       <c r="J43" t="n">
-        <v>26095.39</v>
+        <v>25993.18</v>
       </c>
       <c r="K43" t="n">
-        <v>26177.44</v>
+        <v>26151.04</v>
       </c>
       <c r="L43" t="n">
-        <v>26259.48</v>
+        <v>26308.9</v>
       </c>
       <c r="M43" t="n">
-        <v>26354.85</v>
+        <v>26420.88</v>
       </c>
       <c r="N43" t="n">
-        <v>26450.21</v>
+        <v>26532.86</v>
       </c>
       <c r="O43" t="n">
-        <v>26518.93</v>
+        <v>26736.6</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4112,18 +4113,16 @@
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4133,55 +4132,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26354.37</v>
+        <v>26494.61</v>
       </c>
       <c r="C44" t="n">
-        <v>26402.81</v>
+        <v>26618.74</v>
       </c>
       <c r="D44" t="n">
-        <v>26241.77</v>
+        <v>26467.36</v>
       </c>
       <c r="E44" t="n">
-        <v>26367.24</v>
+        <v>26569.99</v>
       </c>
       <c r="F44" t="n">
-        <v>81.28</v>
+        <v>202.75</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0077</v>
       </c>
       <c r="H44" t="n">
-        <v>161.04</v>
+        <v>151.38</v>
       </c>
       <c r="I44" t="n">
-        <v>25927.08</v>
+        <v>26080.73</v>
       </c>
       <c r="J44" t="n">
-        <v>25993.18</v>
+        <v>26228.67</v>
       </c>
       <c r="K44" t="n">
-        <v>26151.04</v>
+        <v>26286.72</v>
       </c>
       <c r="L44" t="n">
-        <v>26308.9</v>
+        <v>26344.77</v>
       </c>
       <c r="M44" t="n">
-        <v>26420.88</v>
+        <v>26447.76</v>
       </c>
       <c r="N44" t="n">
-        <v>26532.86</v>
+        <v>26550.76</v>
       </c>
       <c r="O44" t="n">
-        <v>26736.6</v>
+        <v>26563.85</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4199,106 +4202,106 @@
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v/>
-      </c>
       <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>26494.61</v>
+        <v>26464.14</v>
       </c>
       <c r="C45" t="n">
-        <v>26618.74</v>
+        <v>26471.79</v>
       </c>
       <c r="D45" t="n">
-        <v>26467.36</v>
+        <v>26249.59</v>
       </c>
       <c r="E45" t="n">
-        <v>26569.99</v>
+        <v>26258.11</v>
       </c>
       <c r="F45" t="n">
-        <v>202.75</v>
+        <v>-311.88</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0117</v>
       </c>
       <c r="H45" t="n">
-        <v>151.38</v>
+        <v>222.2</v>
       </c>
       <c r="I45" t="n">
-        <v>26080.73</v>
+        <v>26315.98</v>
       </c>
       <c r="J45" t="n">
-        <v>26228.67</v>
+        <v>26432.08</v>
       </c>
       <c r="K45" t="n">
-        <v>26286.72</v>
+        <v>26494.3</v>
       </c>
       <c r="L45" t="n">
-        <v>26344.77</v>
+        <v>26556.52</v>
       </c>
       <c r="M45" t="n">
-        <v>26447.76</v>
+        <v>26645.68</v>
       </c>
       <c r="N45" t="n">
-        <v>26550.76</v>
+        <v>26734.84</v>
       </c>
       <c r="O45" t="n">
-        <v>26563.85</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V45" s="8" t="inlineStr">
+        <v>26770.12</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W45" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W45" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr"/>
@@ -4306,59 +4309,59 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>26464.14</v>
+        <v>26150.75</v>
       </c>
       <c r="C46" t="n">
-        <v>26471.79</v>
+        <v>26206.13</v>
       </c>
       <c r="D46" t="n">
-        <v>26249.59</v>
+        <v>25916.76</v>
       </c>
       <c r="E46" t="n">
-        <v>26258.11</v>
+        <v>25970.11</v>
       </c>
       <c r="F46" t="n">
-        <v>-311.88</v>
+        <v>-288</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.011</v>
       </c>
       <c r="H46" t="n">
-        <v>222.2</v>
+        <v>289.37</v>
       </c>
       <c r="I46" t="n">
-        <v>26315.98</v>
+        <v>26027.39</v>
       </c>
       <c r="J46" t="n">
-        <v>26432.08</v>
+        <v>25984.62</v>
       </c>
       <c r="K46" t="n">
-        <v>26494.3</v>
+        <v>26147.01</v>
       </c>
       <c r="L46" t="n">
-        <v>26556.52</v>
+        <v>26309.4</v>
       </c>
       <c r="M46" t="n">
-        <v>26645.68</v>
+        <v>26369.21</v>
       </c>
       <c r="N46" t="n">
-        <v>26734.84</v>
+        <v>26429.02</v>
       </c>
       <c r="O46" t="n">
-        <v>26770.12</v>
+        <v>26693.99</v>
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
@@ -4390,64 +4393,60 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>26150.75</v>
+        <v>25886.67</v>
       </c>
       <c r="C47" t="n">
-        <v>26206.13</v>
+        <v>25924.21</v>
       </c>
       <c r="D47" t="n">
-        <v>25916.76</v>
+        <v>25727.93</v>
       </c>
       <c r="E47" t="n">
-        <v>25970.11</v>
+        <v>25839.33</v>
       </c>
       <c r="F47" t="n">
-        <v>-288</v>
+        <v>-130.78</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.005</v>
       </c>
       <c r="H47" t="n">
-        <v>289.37</v>
+        <v>196.28</v>
       </c>
       <c r="I47" t="n">
-        <v>26027.39</v>
+        <v>25627.39</v>
       </c>
       <c r="J47" t="n">
-        <v>25984.62</v>
+        <v>25635.07</v>
       </c>
       <c r="K47" t="n">
-        <v>26147.01</v>
+        <v>25825.42</v>
       </c>
       <c r="L47" t="n">
-        <v>26309.4</v>
+        <v>26015.78</v>
       </c>
       <c r="M47" t="n">
-        <v>26369.21</v>
+        <v>26114.79</v>
       </c>
       <c r="N47" t="n">
-        <v>26429.02</v>
+        <v>26213.81</v>
       </c>
       <c r="O47" t="n">
-        <v>26693.99</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
+        <v>26495.5</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
@@ -4474,50 +4473,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25886.67</v>
+        <v>25840.92</v>
       </c>
       <c r="C48" t="n">
-        <v>25924.21</v>
+        <v>26007.79</v>
       </c>
       <c r="D48" t="n">
-        <v>25727.93</v>
+        <v>25784.84</v>
       </c>
       <c r="E48" t="n">
-        <v>25839.33</v>
+        <v>26003.32</v>
       </c>
       <c r="F48" t="n">
-        <v>-130.78</v>
+        <v>163.99</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0063</v>
       </c>
       <c r="H48" t="n">
-        <v>196.28</v>
+        <v>222.95</v>
       </c>
       <c r="I48" t="n">
-        <v>25627.39</v>
+        <v>25531.65</v>
       </c>
       <c r="J48" t="n">
-        <v>25635.07</v>
+        <v>25649.68</v>
       </c>
       <c r="K48" t="n">
-        <v>25825.42</v>
+        <v>25741.19</v>
       </c>
       <c r="L48" t="n">
-        <v>26015.78</v>
+        <v>25832.7</v>
       </c>
       <c r="M48" t="n">
-        <v>26114.79</v>
+        <v>25937.47</v>
       </c>
       <c r="N48" t="n">
-        <v>26213.81</v>
+        <v>26042.24</v>
       </c>
       <c r="O48" t="n">
-        <v>26495.5</v>
+        <v>26120.49</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4525,22 +4524,24 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
@@ -4549,55 +4550,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25840.92</v>
+        <v>25985.86</v>
       </c>
       <c r="C49" t="n">
-        <v>26007.79</v>
+        <v>26167.93</v>
       </c>
       <c r="D49" t="n">
-        <v>25784.84</v>
+        <v>25958.7</v>
       </c>
       <c r="E49" t="n">
-        <v>26003.32</v>
+        <v>26046.4</v>
       </c>
       <c r="F49" t="n">
-        <v>163.99</v>
+        <v>43.08</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0017</v>
       </c>
       <c r="H49" t="n">
-        <v>222.95</v>
+        <v>209.23</v>
       </c>
       <c r="I49" t="n">
-        <v>25531.65</v>
+        <v>25561.89</v>
       </c>
       <c r="J49" t="n">
-        <v>25649.68</v>
+        <v>25833.87</v>
       </c>
       <c r="K49" t="n">
-        <v>25741.19</v>
+        <v>25891.85</v>
       </c>
       <c r="L49" t="n">
-        <v>25832.7</v>
+        <v>25949.82</v>
       </c>
       <c r="M49" t="n">
-        <v>25937.47</v>
+        <v>26114.79</v>
       </c>
       <c r="N49" t="n">
-        <v>26042.24</v>
+        <v>26279.77</v>
       </c>
       <c r="O49" t="n">
-        <v>26120.49</v>
+        <v>26230.74</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4615,13 +4620,11 @@
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4640,50 +4643,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25985.86</v>
+        <v>26039.54</v>
       </c>
       <c r="C50" t="n">
-        <v>26167.93</v>
+        <v>26069.99</v>
       </c>
       <c r="D50" t="n">
-        <v>25958.7</v>
+        <v>25919.61</v>
       </c>
       <c r="E50" t="n">
-        <v>26046.4</v>
+        <v>26006.53</v>
       </c>
       <c r="F50" t="n">
-        <v>43.08</v>
+        <v>-39.87</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0015</v>
       </c>
       <c r="H50" t="n">
-        <v>209.23</v>
+        <v>150.38</v>
       </c>
       <c r="I50" t="n">
-        <v>25561.89</v>
+        <v>25749.47</v>
       </c>
       <c r="J50" t="n">
-        <v>25833.87</v>
+        <v>25828.71</v>
       </c>
       <c r="K50" t="n">
-        <v>25891.85</v>
+        <v>25941.79</v>
       </c>
       <c r="L50" t="n">
-        <v>25949.82</v>
+        <v>26054.86</v>
       </c>
       <c r="M50" t="n">
-        <v>26114.79</v>
+        <v>26151.02</v>
       </c>
       <c r="N50" t="n">
-        <v>26279.77</v>
+        <v>26247.17</v>
       </c>
       <c r="O50" t="n">
-        <v>26230.74</v>
+        <v>26377.16</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4691,18 +4694,18 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4715,74 +4718,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>26039.54</v>
+        <v>25897.22</v>
       </c>
       <c r="C51" t="n">
-        <v>26069.99</v>
+        <v>26026.78</v>
       </c>
       <c r="D51" t="n">
-        <v>25919.61</v>
+        <v>25799.66</v>
       </c>
       <c r="E51" t="n">
-        <v>26006.53</v>
+        <v>26007.63</v>
       </c>
       <c r="F51" t="n">
-        <v>-39.87</v>
+        <v>1.1</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>150.38</v>
+        <v>227.12</v>
       </c>
       <c r="I51" t="n">
-        <v>25749.47</v>
+        <v>25769.23</v>
       </c>
       <c r="J51" t="n">
-        <v>25828.71</v>
+        <v>25862.01</v>
       </c>
       <c r="K51" t="n">
-        <v>25941.79</v>
+        <v>25931.34</v>
       </c>
       <c r="L51" t="n">
-        <v>26054.86</v>
+        <v>26000.66</v>
       </c>
       <c r="M51" t="n">
-        <v>26151.02</v>
+        <v>26081.72</v>
       </c>
       <c r="N51" t="n">
-        <v>26247.17</v>
+        <v>26162.77</v>
       </c>
       <c r="O51" t="n">
-        <v>26377.16</v>
+        <v>26220.37</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4799,58 +4800,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25897.22</v>
+        <v>25870.98</v>
       </c>
       <c r="C52" t="n">
-        <v>26026.78</v>
+        <v>25909.66</v>
       </c>
       <c r="D52" t="n">
-        <v>25799.66</v>
+        <v>25512.39</v>
       </c>
       <c r="E52" t="n">
-        <v>26007.63</v>
+        <v>25576.45</v>
       </c>
       <c r="F52" t="n">
-        <v>1.1</v>
+        <v>-431.18</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0</v>
+        <v>-0.0166</v>
       </c>
       <c r="H52" t="n">
-        <v>227.12</v>
+        <v>397.27</v>
       </c>
       <c r="I52" t="n">
-        <v>25769.23</v>
+        <v>25572.54</v>
       </c>
       <c r="J52" t="n">
-        <v>25862.01</v>
+        <v>25827.72</v>
       </c>
       <c r="K52" t="n">
-        <v>25931.34</v>
+        <v>25894.07</v>
       </c>
       <c r="L52" t="n">
-        <v>26000.66</v>
+        <v>25960.43</v>
       </c>
       <c r="M52" t="n">
-        <v>26081.72</v>
+        <v>26121.19</v>
       </c>
       <c r="N52" t="n">
-        <v>26162.77</v>
+        <v>26281.96</v>
       </c>
       <c r="O52" t="n">
-        <v>26220.37</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
+        <v>26253.9</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
@@ -4862,9 +4869,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4881,73 +4888,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25870.98</v>
+        <v>25555.66</v>
       </c>
       <c r="C53" t="n">
-        <v>25909.66</v>
+        <v>25612.09</v>
       </c>
       <c r="D53" t="n">
-        <v>25512.39</v>
+        <v>25361.15</v>
       </c>
       <c r="E53" t="n">
-        <v>25576.45</v>
+        <v>25361.15</v>
       </c>
       <c r="F53" t="n">
-        <v>-431.18</v>
+        <v>-215.3</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>397.27</v>
+        <v>250.94</v>
       </c>
       <c r="I53" t="n">
-        <v>25572.54</v>
+        <v>25115.12</v>
       </c>
       <c r="J53" t="n">
-        <v>25827.72</v>
+        <v>25111.89</v>
       </c>
       <c r="K53" t="n">
-        <v>25894.07</v>
+        <v>25377.81</v>
       </c>
       <c r="L53" t="n">
-        <v>25960.43</v>
+        <v>25643.74</v>
       </c>
       <c r="M53" t="n">
-        <v>26121.19</v>
+        <v>25775.08</v>
       </c>
       <c r="N53" t="n">
-        <v>26281.96</v>
+        <v>25906.43</v>
       </c>
       <c r="O53" t="n">
-        <v>26253.9</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
+        <v>26306.93</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
@@ -4974,50 +4973,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25555.66</v>
+        <v>25478.84</v>
       </c>
       <c r="C54" t="n">
-        <v>25612.09</v>
+        <v>25581.22</v>
       </c>
       <c r="D54" t="n">
-        <v>25361.15</v>
+        <v>25396.38</v>
       </c>
       <c r="E54" t="n">
-        <v>25361.15</v>
+        <v>25568.56</v>
       </c>
       <c r="F54" t="n">
-        <v>-215.3</v>
+        <v>207.41</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>250.94</v>
+        <v>184.84</v>
       </c>
       <c r="I54" t="n">
-        <v>25115.12</v>
+        <v>25110.21</v>
       </c>
       <c r="J54" t="n">
-        <v>25111.89</v>
+        <v>25047.48</v>
       </c>
       <c r="K54" t="n">
-        <v>25377.81</v>
+        <v>25235.68</v>
       </c>
       <c r="L54" t="n">
-        <v>25643.74</v>
+        <v>25423.89</v>
       </c>
       <c r="M54" t="n">
-        <v>25775.08</v>
+        <v>25486.62</v>
       </c>
       <c r="N54" t="n">
-        <v>25906.43</v>
+        <v>25549.35</v>
       </c>
       <c r="O54" t="n">
-        <v>26306.93</v>
+        <v>25863.03</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5025,104 +5024,110 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="W54" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25478.84</v>
+        <v>25498.74</v>
       </c>
       <c r="C55" t="n">
-        <v>25581.22</v>
+        <v>25548.78</v>
       </c>
       <c r="D55" t="n">
-        <v>25396.38</v>
+        <v>25325.52</v>
       </c>
       <c r="E55" t="n">
-        <v>25568.56</v>
+        <v>25440.81</v>
       </c>
       <c r="F55" t="n">
-        <v>207.41</v>
+        <v>-127.75</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.005</v>
       </c>
       <c r="H55" t="n">
-        <v>184.84</v>
+        <v>223.26</v>
       </c>
       <c r="I55" t="n">
-        <v>25110.21</v>
+        <v>25211.54</v>
       </c>
       <c r="J55" t="n">
-        <v>25047.48</v>
+        <v>25423.6</v>
       </c>
       <c r="K55" t="n">
-        <v>25235.68</v>
+        <v>25476.14</v>
       </c>
       <c r="L55" t="n">
-        <v>25423.89</v>
+        <v>25528.68</v>
       </c>
       <c r="M55" t="n">
-        <v>25486.62</v>
+        <v>25660.98</v>
       </c>
       <c r="N55" t="n">
-        <v>25549.35</v>
+        <v>25793.28</v>
       </c>
       <c r="O55" t="n">
-        <v>25863.03</v>
+        <v>25766.06</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
+      <c r="Q55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
@@ -5133,64 +5138,64 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25498.74</v>
+        <v>25360.32</v>
       </c>
       <c r="C56" t="n">
-        <v>25548.78</v>
+        <v>25478.98</v>
       </c>
       <c r="D56" t="n">
-        <v>25325.52</v>
+        <v>25172.89</v>
       </c>
       <c r="E56" t="n">
-        <v>25440.81</v>
+        <v>25402.28</v>
       </c>
       <c r="F56" t="n">
-        <v>-127.75</v>
+        <v>-38.53</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.005</v>
+        <v>-0.0015</v>
       </c>
       <c r="H56" t="n">
-        <v>223.26</v>
+        <v>306.09</v>
       </c>
       <c r="I56" t="n">
-        <v>25211.54</v>
+        <v>25102.26</v>
       </c>
       <c r="J56" t="n">
-        <v>25423.6</v>
+        <v>25219.38</v>
       </c>
       <c r="K56" t="n">
-        <v>25476.14</v>
+        <v>25329.18</v>
       </c>
       <c r="L56" t="n">
-        <v>25528.68</v>
+        <v>25438.98</v>
       </c>
       <c r="M56" t="n">
-        <v>25660.98</v>
+        <v>25552.44</v>
       </c>
       <c r="N56" t="n">
-        <v>25793.28</v>
+        <v>25665.9</v>
       </c>
       <c r="O56" t="n">
-        <v>25766.06</v>
+        <v>25772.04</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
       <c r="Q56" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
@@ -5200,7 +5205,7 @@
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5226,71 +5231,69 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25360.32</v>
+        <v>25515.96</v>
       </c>
       <c r="C57" t="n">
-        <v>25478.98</v>
+        <v>25599.07</v>
       </c>
       <c r="D57" t="n">
-        <v>25172.89</v>
+        <v>25361.7</v>
       </c>
       <c r="E57" t="n">
-        <v>25402.28</v>
+        <v>25537.75</v>
       </c>
       <c r="F57" t="n">
-        <v>-38.53</v>
+        <v>135.47</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0053</v>
       </c>
       <c r="H57" t="n">
-        <v>306.09</v>
+        <v>237.37</v>
       </c>
       <c r="I57" t="n">
-        <v>25102.26</v>
+        <v>24866.8</v>
       </c>
       <c r="J57" t="n">
-        <v>25219.38</v>
+        <v>25134.36</v>
       </c>
       <c r="K57" t="n">
-        <v>25329.18</v>
+        <v>25249.23</v>
       </c>
       <c r="L57" t="n">
-        <v>25438.98</v>
+        <v>25364.11</v>
       </c>
       <c r="M57" t="n">
-        <v>25552.44</v>
+        <v>25555.32</v>
       </c>
       <c r="N57" t="n">
-        <v>25665.9</v>
+        <v>25746.54</v>
       </c>
       <c r="O57" t="n">
-        <v>25772.04</v>
+        <v>25785.07</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5303,59 +5306,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>25515.96</v>
+        <v>25681.6</v>
       </c>
       <c r="C58" t="n">
-        <v>25599.07</v>
+        <v>25800.62</v>
       </c>
       <c r="D58" t="n">
-        <v>25361.7</v>
+        <v>25596.05</v>
       </c>
       <c r="E58" t="n">
-        <v>25537.75</v>
+        <v>25716.71</v>
       </c>
       <c r="F58" t="n">
-        <v>135.47</v>
+        <v>178.96</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0053</v>
+        <v>0.007</v>
       </c>
       <c r="H58" t="n">
-        <v>237.37</v>
+        <v>204.57</v>
       </c>
       <c r="I58" t="n">
-        <v>24866.8</v>
+        <v>25124.33</v>
       </c>
       <c r="J58" t="n">
-        <v>25134.36</v>
+        <v>25329.06</v>
       </c>
       <c r="K58" t="n">
-        <v>25249.23</v>
+        <v>25419.06</v>
       </c>
       <c r="L58" t="n">
-        <v>25364.11</v>
+        <v>25509.07</v>
       </c>
       <c r="M58" t="n">
-        <v>25555.32</v>
+        <v>25656.44</v>
       </c>
       <c r="N58" t="n">
-        <v>25746.54</v>
+        <v>25803.8</v>
       </c>
       <c r="O58" t="n">
-        <v>25785.07</v>
+        <v>25836.44</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5392,79 +5391,83 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25681.6</v>
+        <v>25596.46</v>
       </c>
       <c r="C59" t="n">
-        <v>25800.62</v>
+        <v>25656.22</v>
       </c>
       <c r="D59" t="n">
-        <v>25596.05</v>
+        <v>25285.9</v>
       </c>
       <c r="E59" t="n">
-        <v>25716.71</v>
+        <v>25304.06</v>
       </c>
       <c r="F59" t="n">
-        <v>178.96</v>
+        <v>-412.65</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.007</v>
+        <v>-0.016</v>
       </c>
       <c r="H59" t="n">
-        <v>204.57</v>
+        <v>370.32</v>
       </c>
       <c r="I59" t="n">
-        <v>25124.33</v>
+        <v>25391.48</v>
       </c>
       <c r="J59" t="n">
-        <v>25329.06</v>
+        <v>25521.33</v>
       </c>
       <c r="K59" t="n">
-        <v>25419.06</v>
+        <v>25614.43</v>
       </c>
       <c r="L59" t="n">
-        <v>25509.07</v>
+        <v>25707.52</v>
       </c>
       <c r="M59" t="n">
-        <v>25656.44</v>
+        <v>25819</v>
       </c>
       <c r="N59" t="n">
-        <v>25803.8</v>
+        <v>25930.47</v>
       </c>
       <c r="O59" t="n">
-        <v>25836.44</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
+        <v>26005.19</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
       <c r="U59" s="8" t="n">
         <v/>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W59" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X59" t="inlineStr"/>
@@ -5472,77 +5475,75 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25596.46</v>
+        <v>25491.35</v>
       </c>
       <c r="C60" t="n">
-        <v>25656.22</v>
+        <v>25617.99</v>
       </c>
       <c r="D60" t="n">
-        <v>25285.9</v>
+        <v>25434.16</v>
       </c>
       <c r="E60" t="n">
-        <v>25304.06</v>
+        <v>25575.01</v>
       </c>
       <c r="F60" t="n">
-        <v>-412.65</v>
+        <v>270.95</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.016</v>
+        <v>0.0107</v>
       </c>
       <c r="H60" t="n">
-        <v>370.32</v>
+        <v>183.83</v>
       </c>
       <c r="I60" t="n">
-        <v>25391.48</v>
+        <v>24915.58</v>
       </c>
       <c r="J60" t="n">
-        <v>25521.33</v>
+        <v>24850.24</v>
       </c>
       <c r="K60" t="n">
-        <v>25614.43</v>
+        <v>25118.9</v>
       </c>
       <c r="L60" t="n">
-        <v>25707.52</v>
+        <v>25387.56</v>
       </c>
       <c r="M60" t="n">
-        <v>25819</v>
+        <v>25489.22</v>
       </c>
       <c r="N60" t="n">
-        <v>25930.47</v>
+        <v>25590.88</v>
       </c>
       <c r="O60" t="n">
-        <v>26005.19</v>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
+        <v>26026.54</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
@@ -5551,55 +5552,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>25491.35</v>
+        <v>25592.98</v>
       </c>
       <c r="C61" t="n">
-        <v>25617.99</v>
+        <v>25783.16</v>
       </c>
       <c r="D61" t="n">
-        <v>25434.16</v>
+        <v>25423.07</v>
       </c>
       <c r="E61" t="n">
-        <v>25575.01</v>
+        <v>25578.85</v>
       </c>
       <c r="F61" t="n">
-        <v>270.95</v>
+        <v>3.84</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0107</v>
+        <v>0.0002</v>
       </c>
       <c r="H61" t="n">
-        <v>183.83</v>
+        <v>360.09</v>
       </c>
       <c r="I61" t="n">
-        <v>24915.58</v>
+        <v>25250.33</v>
       </c>
       <c r="J61" t="n">
-        <v>24850.24</v>
+        <v>25415.65</v>
       </c>
       <c r="K61" t="n">
-        <v>25118.9</v>
+        <v>25483.09</v>
       </c>
       <c r="L61" t="n">
-        <v>25387.56</v>
+        <v>25550.54</v>
       </c>
       <c r="M61" t="n">
-        <v>25489.22</v>
+        <v>25666.92</v>
       </c>
       <c r="N61" t="n">
-        <v>25590.88</v>
+        <v>25783.31</v>
       </c>
       <c r="O61" t="n">
-        <v>26026.54</v>
+        <v>25801.82</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5607,12 +5612,14 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
@@ -5620,10 +5627,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U61" s="8" t="n">
+        <v/>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
@@ -5642,50 +5647,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>25592.98</v>
+        <v>25724.13</v>
       </c>
       <c r="C62" t="n">
-        <v>25783.16</v>
+        <v>25729.05</v>
       </c>
       <c r="D62" t="n">
-        <v>25423.07</v>
+        <v>25365.21</v>
       </c>
       <c r="E62" t="n">
-        <v>25578.85</v>
+        <v>25410.63</v>
       </c>
       <c r="F62" t="n">
-        <v>3.84</v>
+        <v>-168.22</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.0066</v>
       </c>
       <c r="H62" t="n">
-        <v>360.09</v>
+        <v>363.84</v>
       </c>
       <c r="I62" t="n">
-        <v>25250.33</v>
+        <v>25062.98</v>
       </c>
       <c r="J62" t="n">
-        <v>25415.65</v>
+        <v>25206.63</v>
       </c>
       <c r="K62" t="n">
-        <v>25483.09</v>
+        <v>25398.8</v>
       </c>
       <c r="L62" t="n">
-        <v>25550.54</v>
+        <v>25590.98</v>
       </c>
       <c r="M62" t="n">
-        <v>25666.92</v>
+        <v>25758.89</v>
       </c>
       <c r="N62" t="n">
-        <v>25783.31</v>
+        <v>25926.81</v>
       </c>
       <c r="O62" t="n">
-        <v>25801.82</v>
+        <v>26143.25</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5695,18 +5700,16 @@
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5719,59 +5722,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>25724.13</v>
+        <v>25263.11</v>
       </c>
       <c r="C63" t="n">
-        <v>25729.05</v>
+        <v>25424.21</v>
       </c>
       <c r="D63" t="n">
-        <v>25365.21</v>
+        <v>25164.2</v>
       </c>
       <c r="E63" t="n">
-        <v>25410.63</v>
+        <v>25266.53</v>
       </c>
       <c r="F63" t="n">
-        <v>-168.22</v>
+        <v>-144.1</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0066</v>
+        <v>-0.0057</v>
       </c>
       <c r="H63" t="n">
-        <v>363.84</v>
+        <v>260.01</v>
       </c>
       <c r="I63" t="n">
-        <v>25062.98</v>
+        <v>25001.37</v>
       </c>
       <c r="J63" t="n">
-        <v>25206.63</v>
+        <v>24978.54</v>
       </c>
       <c r="K63" t="n">
-        <v>25398.8</v>
+        <v>25228.71</v>
       </c>
       <c r="L63" t="n">
-        <v>25590.98</v>
+        <v>25478.88</v>
       </c>
       <c r="M63" t="n">
-        <v>25758.89</v>
+        <v>25592.55</v>
       </c>
       <c r="N63" t="n">
-        <v>25926.81</v>
+        <v>25706.22</v>
       </c>
       <c r="O63" t="n">
-        <v>26143.25</v>
+        <v>26092.89</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5808,50 +5807,50 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>25263.11</v>
+        <v>25441.79</v>
       </c>
       <c r="C64" t="n">
-        <v>25424.21</v>
+        <v>25529.33</v>
       </c>
       <c r="D64" t="n">
-        <v>25164.2</v>
+        <v>25347.3</v>
       </c>
       <c r="E64" t="n">
-        <v>25266.53</v>
+        <v>25408.64</v>
       </c>
       <c r="F64" t="n">
-        <v>-144.1</v>
+        <v>142.11</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0056</v>
       </c>
       <c r="H64" t="n">
-        <v>260.01</v>
+        <v>182.03</v>
       </c>
       <c r="I64" t="n">
-        <v>25001.37</v>
+        <v>24904.19</v>
       </c>
       <c r="J64" t="n">
-        <v>24978.54</v>
+        <v>24992.68</v>
       </c>
       <c r="K64" t="n">
-        <v>25228.71</v>
+        <v>25136.52</v>
       </c>
       <c r="L64" t="n">
-        <v>25478.88</v>
+        <v>25280.37</v>
       </c>
       <c r="M64" t="n">
-        <v>25592.55</v>
+        <v>25396.54</v>
       </c>
       <c r="N64" t="n">
-        <v>25706.22</v>
+        <v>25512.7</v>
       </c>
       <c r="O64" t="n">
-        <v>26092.89</v>
+        <v>25684.22</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5859,21 +5858,23 @@
       <c r="Q64" s="6" t="n">
         <v/>
       </c>
-      <c r="R64" s="6" t="inlineStr">
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S64" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
+      <c r="U64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V64" s="8" t="n">
         <v/>
@@ -5883,58 +5884,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>25441.79</v>
+        <v>25443.98</v>
       </c>
       <c r="C65" t="n">
-        <v>25529.33</v>
+        <v>25575.66</v>
       </c>
       <c r="D65" t="n">
-        <v>25347.3</v>
+        <v>25360.32</v>
       </c>
       <c r="E65" t="n">
-        <v>25408.64</v>
+        <v/>
       </c>
       <c r="F65" t="n">
-        <v>142.11</v>
+        <v/>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0056</v>
+        <v/>
       </c>
       <c r="H65" t="n">
-        <v>182.03</v>
+        <v>215.34</v>
       </c>
       <c r="I65" t="n">
-        <v>24904.19</v>
+        <v>25165.27</v>
       </c>
       <c r="J65" t="n">
-        <v>24992.68</v>
+        <v>25211.77</v>
       </c>
       <c r="K65" t="n">
-        <v>25136.52</v>
+        <v>25317.63</v>
       </c>
       <c r="L65" t="n">
-        <v>25280.37</v>
+        <v>25423.48</v>
       </c>
       <c r="M65" t="n">
-        <v>25396.54</v>
+        <v>25499.66</v>
       </c>
       <c r="N65" t="n">
-        <v>25512.7</v>
+        <v>25575.83</v>
       </c>
       <c r="O65" t="n">
-        <v>25684.22</v>
-      </c>
-      <c r="P65" s="6" t="n">
-        <v/>
+        <v>25711.36</v>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q65" s="6" t="n">
         <v/>
@@ -5942,20 +5949,18 @@
       <c r="R65" s="6" t="n">
         <v/>
       </c>
-      <c r="S65" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S65" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T65" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U65" s="8" t="n">
+        <v/>
       </c>
       <c r="V65" s="8" t="n">
         <v/>
@@ -5967,7 +5972,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -637,50 +637,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25028.93</v>
+        <v>25025.13</v>
       </c>
       <c r="C2" t="n">
-        <v>25095.66</v>
+        <v>25655.82</v>
       </c>
       <c r="D2" t="n">
-        <v>24887</v>
+        <v>24994.64</v>
       </c>
       <c r="E2" t="n">
-        <v>25040.28</v>
+        <v>25580.88</v>
       </c>
       <c r="F2" t="n">
-        <v>44.47</v>
+        <v>540.6</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0216</v>
       </c>
       <c r="H2" t="n">
-        <v>208.66</v>
+        <v>661.1799999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>24565.41</v>
+        <v>24678.34</v>
       </c>
       <c r="J2" t="n">
-        <v>24809.51</v>
+        <v>24856.09</v>
       </c>
       <c r="K2" t="n">
-        <v>24881.1</v>
+        <v>24935.95</v>
       </c>
       <c r="L2" t="n">
-        <v>24952.68</v>
+        <v>25015.8</v>
       </c>
       <c r="M2" t="n">
-        <v>25110.53</v>
+        <v>25144.61</v>
       </c>
       <c r="N2" t="n">
-        <v>25268.37</v>
+        <v>25273.41</v>
       </c>
       <c r="O2" t="n">
-        <v>25253.7</v>
+        <v>25304.32</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -698,14 +698,18 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -717,50 +721,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25025.13</v>
+        <v>25763.97</v>
       </c>
       <c r="C3" t="n">
-        <v>25655.82</v>
+        <v>25826.78</v>
       </c>
       <c r="D3" t="n">
-        <v>24994.64</v>
+        <v>25611.69</v>
       </c>
       <c r="E3" t="n">
-        <v>25580.88</v>
+        <v>25779.31</v>
       </c>
       <c r="F3" t="n">
-        <v>540.6</v>
+        <v>198.43</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0216</v>
+        <v>0.0078</v>
       </c>
       <c r="H3" t="n">
-        <v>661.1799999999999</v>
+        <v>215.09</v>
       </c>
       <c r="I3" t="n">
-        <v>24678.34</v>
+        <v>24333.46</v>
       </c>
       <c r="J3" t="n">
-        <v>24856.09</v>
+        <v>25047.53</v>
       </c>
       <c r="K3" t="n">
-        <v>24935.95</v>
+        <v>25250.29</v>
       </c>
       <c r="L3" t="n">
-        <v>25015.8</v>
+        <v>25453.06</v>
       </c>
       <c r="M3" t="n">
-        <v>25144.61</v>
+        <v>25911.47</v>
       </c>
       <c r="N3" t="n">
-        <v>25273.41</v>
+        <v>26369.89</v>
       </c>
       <c r="O3" t="n">
-        <v>25304.32</v>
+        <v>26317</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -778,18 +782,14 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
@@ -801,50 +801,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25763.97</v>
+        <v>25811.9</v>
       </c>
       <c r="C4" t="n">
-        <v>25826.78</v>
+        <v>25900.1</v>
       </c>
       <c r="D4" t="n">
-        <v>25611.69</v>
+        <v>25698.56</v>
       </c>
       <c r="E4" t="n">
-        <v>25779.31</v>
+        <v>25817.89</v>
       </c>
       <c r="F4" t="n">
-        <v>198.43</v>
+        <v>38.58</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0078</v>
+        <v>0.0015</v>
       </c>
       <c r="H4" t="n">
-        <v>215.09</v>
+        <v>201.54</v>
       </c>
       <c r="I4" t="n">
-        <v>24333.46</v>
+        <v>25396.6</v>
       </c>
       <c r="J4" t="n">
-        <v>25047.53</v>
+        <v>25594.26</v>
       </c>
       <c r="K4" t="n">
-        <v>25250.29</v>
+        <v>25671.77</v>
       </c>
       <c r="L4" t="n">
-        <v>25453.06</v>
+        <v>25749.27</v>
       </c>
       <c r="M4" t="n">
-        <v>25911.47</v>
+        <v>25886.86</v>
       </c>
       <c r="N4" t="n">
-        <v>26369.89</v>
+        <v>26024.44</v>
       </c>
       <c r="O4" t="n">
-        <v>26317</v>
+        <v>26041.87</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -857,12 +857,12 @@
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U4" s="8" t="n">
@@ -881,69 +881,73 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25811.9</v>
+        <v>25770.45</v>
       </c>
       <c r="C5" t="n">
-        <v>25900.1</v>
+        <v>25811.97</v>
       </c>
       <c r="D5" t="n">
-        <v>25698.56</v>
+        <v>25465.12</v>
       </c>
       <c r="E5" t="n">
-        <v>25817.89</v>
+        <v>25465.25</v>
       </c>
       <c r="F5" t="n">
-        <v>38.58</v>
+        <v>-352.64</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0137</v>
       </c>
       <c r="H5" t="n">
-        <v>201.54</v>
+        <v>346.85</v>
       </c>
       <c r="I5" t="n">
-        <v>25396.6</v>
+        <v>25497.02</v>
       </c>
       <c r="J5" t="n">
-        <v>25594.26</v>
+        <v>25625.63</v>
       </c>
       <c r="K5" t="n">
-        <v>25671.77</v>
+        <v>25717.12</v>
       </c>
       <c r="L5" t="n">
-        <v>25749.27</v>
+        <v>25808.61</v>
       </c>
       <c r="M5" t="n">
-        <v>25886.86</v>
+        <v>25918.66</v>
       </c>
       <c r="N5" t="n">
-        <v>26024.44</v>
+        <v>26028.71</v>
       </c>
       <c r="O5" t="n">
-        <v>26041.87</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>26101.64</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -951,9 +955,9 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W5" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -961,59 +965,59 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25770.45</v>
+        <v>25274.94</v>
       </c>
       <c r="C6" t="n">
-        <v>25811.97</v>
+        <v>25280.16</v>
       </c>
       <c r="D6" t="n">
-        <v>25465.12</v>
+        <v>24830.17</v>
       </c>
       <c r="E6" t="n">
-        <v>25465.25</v>
+        <v>24897.45</v>
       </c>
       <c r="F6" t="n">
-        <v>-352.64</v>
+        <v>-567.8</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0223</v>
       </c>
       <c r="H6" t="n">
-        <v>346.85</v>
+        <v>449.99</v>
       </c>
       <c r="I6" t="n">
-        <v>25497.02</v>
+        <v>25118.27</v>
       </c>
       <c r="J6" t="n">
-        <v>25625.63</v>
+        <v>25031.75</v>
       </c>
       <c r="K6" t="n">
-        <v>25717.12</v>
+        <v>25291.82</v>
       </c>
       <c r="L6" t="n">
-        <v>25808.61</v>
+        <v>25551.9</v>
       </c>
       <c r="M6" t="n">
-        <v>25918.66</v>
+        <v>25638.68</v>
       </c>
       <c r="N6" t="n">
-        <v>26028.71</v>
+        <v>25725.45</v>
       </c>
       <c r="O6" t="n">
-        <v>26101.64</v>
+        <v>26158.82</v>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
@@ -1045,74 +1049,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25274.94</v>
+        <v>25097.48</v>
       </c>
       <c r="C7" t="n">
-        <v>25280.16</v>
+        <v>25127.76</v>
       </c>
       <c r="D7" t="n">
-        <v>24830.17</v>
+        <v>24867.32</v>
       </c>
       <c r="E7" t="n">
-        <v>24897.45</v>
+        <v>25118.27</v>
       </c>
       <c r="F7" t="n">
-        <v>-567.8</v>
+        <v>220.82</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0089</v>
       </c>
       <c r="H7" t="n">
-        <v>449.99</v>
+        <v>260.44</v>
       </c>
       <c r="I7" t="n">
-        <v>25118.27</v>
+        <v>24380.18</v>
       </c>
       <c r="J7" t="n">
-        <v>25031.75</v>
+        <v>24368.6</v>
       </c>
       <c r="K7" t="n">
-        <v>25291.82</v>
+        <v>24672.45</v>
       </c>
       <c r="L7" t="n">
-        <v>25551.9</v>
+        <v>24976.31</v>
       </c>
       <c r="M7" t="n">
-        <v>25638.68</v>
+        <v>25122.44</v>
       </c>
       <c r="N7" t="n">
-        <v>25725.45</v>
+        <v>25268.58</v>
       </c>
       <c r="O7" t="n">
-        <v>26158.82</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
+        <v>25730.15</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1124,55 +1124,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25097.48</v>
+        <v>25081.19</v>
       </c>
       <c r="C8" t="n">
-        <v>25127.76</v>
+        <v>25195.83</v>
       </c>
       <c r="D8" t="n">
-        <v>24867.32</v>
+        <v>24937.52</v>
       </c>
       <c r="E8" t="n">
-        <v>25118.27</v>
+        <v>25067.09</v>
       </c>
       <c r="F8" t="n">
-        <v>220.82</v>
+        <v>-51.18</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.002</v>
       </c>
       <c r="H8" t="n">
-        <v>260.44</v>
+        <v>258.31</v>
       </c>
       <c r="I8" t="n">
-        <v>24380.18</v>
+        <v>24606.88</v>
       </c>
       <c r="J8" t="n">
-        <v>24368.6</v>
+        <v>24918.19</v>
       </c>
       <c r="K8" t="n">
-        <v>24672.45</v>
+        <v>24988.05</v>
       </c>
       <c r="L8" t="n">
-        <v>24976.31</v>
+        <v>25057.9</v>
       </c>
       <c r="M8" t="n">
-        <v>25122.44</v>
+        <v>25248.49</v>
       </c>
       <c r="N8" t="n">
-        <v>25268.58</v>
+        <v>25439.07</v>
       </c>
       <c r="O8" t="n">
-        <v>25730.15</v>
+        <v>25388.2</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1180,18 +1184,18 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1213,50 +1217,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25081.19</v>
+        <v>24963.8</v>
       </c>
       <c r="C9" t="n">
-        <v>25195.83</v>
+        <v>25154.58</v>
       </c>
       <c r="D9" t="n">
-        <v>24937.52</v>
+        <v>24963.8</v>
       </c>
       <c r="E9" t="n">
-        <v>25067.09</v>
+        <v>25114.25</v>
       </c>
       <c r="F9" t="n">
-        <v>-51.18</v>
+        <v>47.16</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="H9" t="n">
-        <v>258.31</v>
+        <v>190.78</v>
       </c>
       <c r="I9" t="n">
-        <v>24606.88</v>
+        <v>24679.21</v>
       </c>
       <c r="J9" t="n">
-        <v>24918.19</v>
+        <v>24808.99</v>
       </c>
       <c r="K9" t="n">
-        <v>24988.05</v>
+        <v>24937.93</v>
       </c>
       <c r="L9" t="n">
-        <v>25057.9</v>
+        <v>25066.88</v>
       </c>
       <c r="M9" t="n">
-        <v>25248.49</v>
+        <v>25196.25</v>
       </c>
       <c r="N9" t="n">
-        <v>25439.07</v>
+        <v>25325.61</v>
       </c>
       <c r="O9" t="n">
-        <v>25388.2</v>
+        <v>25454.14</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1264,10 +1268,8 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R9" s="6" t="n">
+        <v/>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
@@ -1297,59 +1299,63 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24963.8</v>
+        <v>24932.62</v>
       </c>
       <c r="C10" t="n">
-        <v>25154.58</v>
+        <v>25204.68</v>
       </c>
       <c r="D10" t="n">
-        <v>24963.8</v>
+        <v>24869.25</v>
       </c>
       <c r="E10" t="n">
-        <v>25114.25</v>
+        <v>25147.03</v>
       </c>
       <c r="F10" t="n">
-        <v>47.16</v>
+        <v>32.78</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0013</v>
       </c>
       <c r="H10" t="n">
-        <v>190.78</v>
+        <v>335.43</v>
       </c>
       <c r="I10" t="n">
-        <v>24679.21</v>
+        <v>24773.02</v>
       </c>
       <c r="J10" t="n">
-        <v>24808.99</v>
+        <v>24951</v>
       </c>
       <c r="K10" t="n">
-        <v>24937.93</v>
+        <v>25018.86</v>
       </c>
       <c r="L10" t="n">
-        <v>25066.88</v>
+        <v>25086.72</v>
       </c>
       <c r="M10" t="n">
-        <v>25196.25</v>
+        <v>25209.64</v>
       </c>
       <c r="N10" t="n">
-        <v>25325.61</v>
+        <v>25332.56</v>
       </c>
       <c r="O10" t="n">
-        <v>25454.14</v>
+        <v>25345.36</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
@@ -1379,50 +1385,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24932.62</v>
+        <v>24970.05</v>
       </c>
       <c r="C11" t="n">
-        <v>25204.68</v>
+        <v>25055.48</v>
       </c>
       <c r="D11" t="n">
-        <v>24869.25</v>
+        <v>24839.23</v>
       </c>
       <c r="E11" t="n">
-        <v>25147.03</v>
+        <v>24999.53</v>
       </c>
       <c r="F11" t="n">
-        <v>32.78</v>
+        <v>-147.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0059</v>
       </c>
       <c r="H11" t="n">
-        <v>335.43</v>
+        <v>216.25</v>
       </c>
       <c r="I11" t="n">
-        <v>24773.02</v>
+        <v>24533.82</v>
       </c>
       <c r="J11" t="n">
-        <v>24951</v>
+        <v>24866.63</v>
       </c>
       <c r="K11" t="n">
-        <v>25018.86</v>
+        <v>24979.31</v>
       </c>
       <c r="L11" t="n">
-        <v>25086.72</v>
+        <v>25092</v>
       </c>
       <c r="M11" t="n">
-        <v>25209.64</v>
+        <v>25314.74</v>
       </c>
       <c r="N11" t="n">
-        <v>25332.56</v>
+        <v>25537.49</v>
       </c>
       <c r="O11" t="n">
-        <v>25345.36</v>
+        <v>25540.11</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1434,12 +1440,12 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1456,59 +1462,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24970.05</v>
+        <v>25018.95</v>
       </c>
       <c r="C12" t="n">
-        <v>25055.48</v>
+        <v>25021.51</v>
       </c>
       <c r="D12" t="n">
-        <v>24839.23</v>
+        <v>24696.17</v>
       </c>
       <c r="E12" t="n">
-        <v>24999.53</v>
+        <v>24915.49</v>
       </c>
       <c r="F12" t="n">
-        <v>-147.5</v>
+        <v>-84.04000000000001</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0059</v>
+        <v>-0.0034</v>
       </c>
       <c r="H12" t="n">
-        <v>216.25</v>
+        <v>325.34</v>
       </c>
       <c r="I12" t="n">
-        <v>24533.82</v>
+        <v>24622.98</v>
       </c>
       <c r="J12" t="n">
-        <v>24866.63</v>
+        <v>24809.37</v>
       </c>
       <c r="K12" t="n">
-        <v>24979.31</v>
+        <v>24891.4</v>
       </c>
       <c r="L12" t="n">
-        <v>25092</v>
+        <v>24973.44</v>
       </c>
       <c r="M12" t="n">
-        <v>25314.74</v>
+        <v>25107.65</v>
       </c>
       <c r="N12" t="n">
-        <v>25537.49</v>
+        <v>25241.87</v>
       </c>
       <c r="O12" t="n">
-        <v>25540.11</v>
+        <v>25271.73</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1547,67 +1549,65 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25018.95</v>
+        <v>24755.09</v>
       </c>
       <c r="C13" t="n">
-        <v>25021.51</v>
+        <v>24850.75</v>
       </c>
       <c r="D13" t="n">
-        <v>24696.17</v>
+        <v>24651.34</v>
       </c>
       <c r="E13" t="n">
-        <v>24915.49</v>
+        <v>24830.98</v>
       </c>
       <c r="F13" t="n">
-        <v>-84.04000000000001</v>
+        <v>-84.51000000000001</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>-0.0034</v>
       </c>
       <c r="H13" t="n">
-        <v>325.34</v>
+        <v>199.41</v>
       </c>
       <c r="I13" t="n">
-        <v>24622.98</v>
+        <v>24370.83</v>
       </c>
       <c r="J13" t="n">
-        <v>24809.37</v>
+        <v>24618.48</v>
       </c>
       <c r="K13" t="n">
-        <v>24891.4</v>
+        <v>24752.82</v>
       </c>
       <c r="L13" t="n">
-        <v>24973.44</v>
+        <v>24887.17</v>
       </c>
       <c r="M13" t="n">
-        <v>25107.65</v>
+        <v>25078.16</v>
       </c>
       <c r="N13" t="n">
-        <v>25241.87</v>
+        <v>25269.16</v>
       </c>
       <c r="O13" t="n">
-        <v>25271.73</v>
+        <v>25346.85</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q13" s="6" t="n">
+        <v/>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1629,50 +1629,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24755.09</v>
+        <v>24769.15</v>
       </c>
       <c r="C14" t="n">
-        <v>24850.75</v>
+        <v>24974.53</v>
       </c>
       <c r="D14" t="n">
-        <v>24651.34</v>
+        <v>24751.13</v>
       </c>
       <c r="E14" t="n">
-        <v>24830.98</v>
+        <v>24846.69</v>
       </c>
       <c r="F14" t="n">
-        <v>-84.51000000000001</v>
+        <v>15.71</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>199.41</v>
+        <v>223.4</v>
       </c>
       <c r="I14" t="n">
-        <v>24370.83</v>
+        <v>24451.93</v>
       </c>
       <c r="J14" t="n">
-        <v>24618.48</v>
+        <v>24671.54</v>
       </c>
       <c r="K14" t="n">
-        <v>24752.82</v>
+        <v>24731.28</v>
       </c>
       <c r="L14" t="n">
-        <v>24887.17</v>
+        <v>24791.01</v>
       </c>
       <c r="M14" t="n">
-        <v>25078.16</v>
+        <v>24930.69</v>
       </c>
       <c r="N14" t="n">
-        <v>25269.16</v>
+        <v>25070.36</v>
       </c>
       <c r="O14" t="n">
-        <v>25346.85</v>
+        <v>25050.16</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1680,18 +1680,18 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1704,55 +1704,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24769.15</v>
+        <v>24922.1</v>
       </c>
       <c r="C15" t="n">
-        <v>24974.53</v>
+        <v>25011.35</v>
       </c>
       <c r="D15" t="n">
-        <v>24751.13</v>
+        <v>24817.34</v>
       </c>
       <c r="E15" t="n">
-        <v>24846.69</v>
+        <v>25011.35</v>
       </c>
       <c r="F15" t="n">
-        <v>15.71</v>
+        <v>164.66</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0066</v>
       </c>
       <c r="H15" t="n">
-        <v>223.4</v>
+        <v>194.01</v>
       </c>
       <c r="I15" t="n">
-        <v>24451.93</v>
+        <v>24527.73</v>
       </c>
       <c r="J15" t="n">
-        <v>24671.54</v>
+        <v>24615.22</v>
       </c>
       <c r="K15" t="n">
-        <v>24731.28</v>
+        <v>24734.99</v>
       </c>
       <c r="L15" t="n">
-        <v>24791.01</v>
+        <v>24854.76</v>
       </c>
       <c r="M15" t="n">
-        <v>24930.69</v>
+        <v>24958.39</v>
       </c>
       <c r="N15" t="n">
-        <v>25070.36</v>
+        <v>25062.02</v>
       </c>
       <c r="O15" t="n">
-        <v>25050.16</v>
+        <v>25197.93</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1765,7 +1769,7 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
@@ -1773,8 +1777,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1793,50 +1799,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24922.1</v>
+        <v>25001.31</v>
       </c>
       <c r="C16" t="n">
-        <v>25011.35</v>
+        <v>25271.34</v>
       </c>
       <c r="D16" t="n">
-        <v>24817.34</v>
+        <v>24984.27</v>
       </c>
       <c r="E16" t="n">
-        <v>25011.35</v>
+        <v>25155.41</v>
       </c>
       <c r="F16" t="n">
-        <v>164.66</v>
+        <v>144.06</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0058</v>
       </c>
       <c r="H16" t="n">
-        <v>194.01</v>
+        <v>287.07</v>
       </c>
       <c r="I16" t="n">
-        <v>24527.73</v>
+        <v>24623.33</v>
       </c>
       <c r="J16" t="n">
-        <v>24615.22</v>
+        <v>24865.84</v>
       </c>
       <c r="K16" t="n">
-        <v>24734.99</v>
+        <v>24914.34</v>
       </c>
       <c r="L16" t="n">
-        <v>24854.76</v>
+        <v>24962.85</v>
       </c>
       <c r="M16" t="n">
-        <v>24958.39</v>
+        <v>25108.35</v>
       </c>
       <c r="N16" t="n">
-        <v>25062.02</v>
+        <v>25253.86</v>
       </c>
       <c r="O16" t="n">
-        <v>25197.93</v>
+        <v>25205.36</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1854,16 +1860,18 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U16" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W16" s="11" t="inlineStr">
         <is>
@@ -1879,171 +1887,165 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25001.31</v>
+        <v>24994.05</v>
       </c>
       <c r="C17" t="n">
-        <v>25271.34</v>
+        <v>25074.28</v>
       </c>
       <c r="D17" t="n">
-        <v>24984.27</v>
+        <v>24696.59</v>
       </c>
       <c r="E17" t="n">
-        <v>25155.41</v>
+        <v>24763.12</v>
       </c>
       <c r="F17" t="n">
-        <v>144.06</v>
+        <v>-392.29</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0156</v>
       </c>
       <c r="H17" t="n">
-        <v>287.07</v>
+        <v>377.69</v>
       </c>
       <c r="I17" t="n">
-        <v>24623.33</v>
+        <v>24697.2</v>
       </c>
       <c r="J17" t="n">
-        <v>24865.84</v>
+        <v>24882.14</v>
       </c>
       <c r="K17" t="n">
-        <v>24914.34</v>
+        <v>25011.88</v>
       </c>
       <c r="L17" t="n">
-        <v>24962.85</v>
+        <v>25141.61</v>
       </c>
       <c r="M17" t="n">
-        <v>25108.35</v>
+        <v>25298.95</v>
       </c>
       <c r="N17" t="n">
-        <v>25253.86</v>
+        <v>25456.28</v>
       </c>
       <c r="O17" t="n">
-        <v>25205.36</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
+        <v>25558.41</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24994.05</v>
+        <v>24830.41</v>
       </c>
       <c r="C18" t="n">
-        <v>25074.28</v>
+        <v>25099.68</v>
       </c>
       <c r="D18" t="n">
-        <v>24696.59</v>
+        <v>24821.67</v>
       </c>
       <c r="E18" t="n">
-        <v>24763.12</v>
+        <v>25099</v>
       </c>
       <c r="F18" t="n">
-        <v>-392.29</v>
+        <v>335.88</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0136</v>
       </c>
       <c r="H18" t="n">
-        <v>377.69</v>
+        <v>278.01</v>
       </c>
       <c r="I18" t="n">
-        <v>24697.2</v>
+        <v>24318.9</v>
       </c>
       <c r="J18" t="n">
-        <v>24882.14</v>
+        <v>24324.27</v>
       </c>
       <c r="K18" t="n">
-        <v>25011.88</v>
+        <v>24574.27</v>
       </c>
       <c r="L18" t="n">
-        <v>25141.61</v>
+        <v>24824.28</v>
       </c>
       <c r="M18" t="n">
-        <v>25298.95</v>
+        <v>24951.96</v>
       </c>
       <c r="N18" t="n">
-        <v>25456.28</v>
+        <v>25079.65</v>
       </c>
       <c r="O18" t="n">
-        <v>25558.41</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
+        <v>25451.97</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -2051,50 +2053,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24830.41</v>
+        <v>25459.32</v>
       </c>
       <c r="C19" t="n">
-        <v>25099.68</v>
+        <v>25560.4</v>
       </c>
       <c r="D19" t="n">
-        <v>24821.67</v>
+        <v>25361.03</v>
       </c>
       <c r="E19" t="n">
-        <v>25099</v>
+        <v>25361.03</v>
       </c>
       <c r="F19" t="n">
-        <v>335.88</v>
+        <v>262.03</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0104</v>
       </c>
       <c r="H19" t="n">
-        <v>278.01</v>
+        <v>199.37</v>
       </c>
       <c r="I19" t="n">
-        <v>24318.9</v>
+        <v>24543.66</v>
       </c>
       <c r="J19" t="n">
-        <v>24324.27</v>
+        <v>24890.15</v>
       </c>
       <c r="K19" t="n">
-        <v>24574.27</v>
+        <v>24960</v>
       </c>
       <c r="L19" t="n">
-        <v>24824.28</v>
+        <v>25029.84</v>
       </c>
       <c r="M19" t="n">
-        <v>24951.96</v>
+        <v>25238</v>
       </c>
       <c r="N19" t="n">
-        <v>25079.65</v>
+        <v>25446.17</v>
       </c>
       <c r="O19" t="n">
-        <v>25451.97</v>
+        <v>25377.69</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2117,11 +2119,13 @@
       </c>
       <c r="U19" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
@@ -2133,50 +2137,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25459.32</v>
+        <v>25496.13</v>
       </c>
       <c r="C20" t="n">
-        <v>25560.4</v>
+        <v>25553.47</v>
       </c>
       <c r="D20" t="n">
-        <v>25361.03</v>
+        <v>25307.17</v>
       </c>
       <c r="E20" t="n">
-        <v>25361.03</v>
+        <v>25464.01</v>
       </c>
       <c r="F20" t="n">
-        <v>262.03</v>
+        <v>102.98</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0104</v>
+        <v>0.0041</v>
       </c>
       <c r="H20" t="n">
-        <v>199.37</v>
+        <v>246.3</v>
       </c>
       <c r="I20" t="n">
-        <v>24543.66</v>
+        <v>25161.66</v>
       </c>
       <c r="J20" t="n">
-        <v>24890.15</v>
+        <v>25111.82</v>
       </c>
       <c r="K20" t="n">
-        <v>24960</v>
+        <v>25261.34</v>
       </c>
       <c r="L20" t="n">
-        <v>25029.84</v>
+        <v>25410.87</v>
       </c>
       <c r="M20" t="n">
-        <v>25238</v>
+        <v>25460.71</v>
       </c>
       <c r="N20" t="n">
-        <v>25446.17</v>
+        <v>25510.56</v>
       </c>
       <c r="O20" t="n">
-        <v>25377.69</v>
+        <v>25759.77</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2194,7 +2198,7 @@
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U20" s="8" t="inlineStr">
@@ -2202,65 +2206,67 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V20" s="8" t="n">
+        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25496.13</v>
+        <v>25551.97</v>
       </c>
       <c r="C21" t="n">
-        <v>25553.47</v>
+        <v>25571.45</v>
       </c>
       <c r="D21" t="n">
-        <v>25307.17</v>
+        <v>25336.39</v>
       </c>
       <c r="E21" t="n">
-        <v>25464.01</v>
+        <v>25460.48</v>
       </c>
       <c r="F21" t="n">
-        <v>102.98</v>
+        <v>-3.53</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0001</v>
       </c>
       <c r="H21" t="n">
-        <v>246.3</v>
+        <v>235.06</v>
       </c>
       <c r="I21" t="n">
-        <v>25161.66</v>
+        <v>25060.87</v>
       </c>
       <c r="J21" t="n">
-        <v>25111.82</v>
+        <v>25234.55</v>
       </c>
       <c r="K21" t="n">
-        <v>25261.34</v>
+        <v>25340.86</v>
       </c>
       <c r="L21" t="n">
-        <v>25410.87</v>
+        <v>25447.17</v>
       </c>
       <c r="M21" t="n">
-        <v>25460.71</v>
+        <v>25587.16</v>
       </c>
       <c r="N21" t="n">
-        <v>25510.56</v>
+        <v>25727.16</v>
       </c>
       <c r="O21" t="n">
-        <v>25759.77</v>
+        <v>25799.77</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2268,23 +2274,21 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2296,57 +2300,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25551.97</v>
+        <v>25487.45</v>
       </c>
       <c r="C22" t="n">
-        <v>25571.45</v>
+        <v>25651.16</v>
       </c>
       <c r="D22" t="n">
-        <v>25336.39</v>
+        <v>25303.11</v>
       </c>
       <c r="E22" t="n">
-        <v>25460.48</v>
+        <v>25612.03</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.53</v>
+        <v>151.55</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.006</v>
       </c>
       <c r="H22" t="n">
-        <v>235.06</v>
+        <v>348.05</v>
       </c>
       <c r="I22" t="n">
-        <v>25060.87</v>
+        <v>25101.33</v>
       </c>
       <c r="J22" t="n">
-        <v>25234.55</v>
+        <v>25228.7</v>
       </c>
       <c r="K22" t="n">
-        <v>25340.86</v>
+        <v>25342.95</v>
       </c>
       <c r="L22" t="n">
-        <v>25447.17</v>
+        <v>25457.2</v>
       </c>
       <c r="M22" t="n">
-        <v>25587.16</v>
+        <v>25578.01</v>
       </c>
       <c r="N22" t="n">
-        <v>25727.16</v>
+        <v>25698.82</v>
       </c>
       <c r="O22" t="n">
-        <v>25799.77</v>
+        <v>25806.51</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2361,11 +2365,13 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2387,50 +2393,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25487.45</v>
+        <v>25709.37</v>
       </c>
       <c r="C23" t="n">
-        <v>25651.16</v>
+        <v>25891.51</v>
       </c>
       <c r="D23" t="n">
-        <v>25303.11</v>
+        <v>25549.53</v>
       </c>
       <c r="E23" t="n">
-        <v>25612.03</v>
+        <v>25629.24</v>
       </c>
       <c r="F23" t="n">
-        <v>151.55</v>
+        <v>17.21</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0007</v>
       </c>
       <c r="H23" t="n">
-        <v>348.05</v>
+        <v>341.98</v>
       </c>
       <c r="I23" t="n">
-        <v>25101.33</v>
+        <v>24955.06</v>
       </c>
       <c r="J23" t="n">
-        <v>25228.7</v>
+        <v>25331.43</v>
       </c>
       <c r="K23" t="n">
-        <v>25342.95</v>
+        <v>25438</v>
       </c>
       <c r="L23" t="n">
-        <v>25457.2</v>
+        <v>25544.58</v>
       </c>
       <c r="M23" t="n">
-        <v>25578.01</v>
+        <v>25786.05</v>
       </c>
       <c r="N23" t="n">
-        <v>25698.82</v>
+        <v>26027.53</v>
       </c>
       <c r="O23" t="n">
-        <v>25806.51</v>
+        <v>25999.21</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2438,19 +2444,17 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U23" s="8" t="n">
@@ -2464,59 +2468,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25709.37</v>
+        <v>25855.12</v>
       </c>
       <c r="C24" t="n">
-        <v>25891.51</v>
+        <v>26096.93</v>
       </c>
       <c r="D24" t="n">
-        <v>25549.53</v>
+        <v>25855.12</v>
       </c>
       <c r="E24" t="n">
-        <v>25629.24</v>
+        <v>26001.31</v>
       </c>
       <c r="F24" t="n">
-        <v>17.21</v>
+        <v>372.07</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0145</v>
       </c>
       <c r="H24" t="n">
-        <v>341.98</v>
+        <v>241.81</v>
       </c>
       <c r="I24" t="n">
-        <v>24955.06</v>
+        <v>25207.55</v>
       </c>
       <c r="J24" t="n">
-        <v>25331.43</v>
+        <v>25241.62</v>
       </c>
       <c r="K24" t="n">
-        <v>25438</v>
+        <v>25458.25</v>
       </c>
       <c r="L24" t="n">
-        <v>25544.58</v>
+        <v>25674.88</v>
       </c>
       <c r="M24" t="n">
-        <v>25786.05</v>
+        <v>25800.23</v>
       </c>
       <c r="N24" t="n">
-        <v>26027.53</v>
+        <v>25925.58</v>
       </c>
       <c r="O24" t="n">
-        <v>25999.21</v>
+        <v>26233.49</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
@@ -2537,8 +2537,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2553,50 +2555,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25855.12</v>
+        <v>26189.62</v>
       </c>
       <c r="C25" t="n">
-        <v>26096.93</v>
+        <v>26266.5</v>
       </c>
       <c r="D25" t="n">
-        <v>25855.12</v>
+        <v>26082.43</v>
       </c>
       <c r="E25" t="n">
-        <v>26001.31</v>
+        <v>26202.35</v>
       </c>
       <c r="F25" t="n">
-        <v>372.07</v>
+        <v>201.04</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0077</v>
       </c>
       <c r="H25" t="n">
-        <v>241.81</v>
+        <v>184.07</v>
       </c>
       <c r="I25" t="n">
-        <v>25207.55</v>
+        <v>25613.31</v>
       </c>
       <c r="J25" t="n">
-        <v>25241.62</v>
+        <v>25772.14</v>
       </c>
       <c r="K25" t="n">
-        <v>25458.25</v>
+        <v>25880.41</v>
       </c>
       <c r="L25" t="n">
-        <v>25674.88</v>
+        <v>25988.67</v>
       </c>
       <c r="M25" t="n">
-        <v>25800.23</v>
+        <v>26122.22</v>
       </c>
       <c r="N25" t="n">
-        <v>25925.58</v>
+        <v>26255.76</v>
       </c>
       <c r="O25" t="n">
-        <v>26233.49</v>
+        <v>26338.74</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2635,50 +2637,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>26189.62</v>
+        <v>26393.43</v>
       </c>
       <c r="C26" t="n">
-        <v>26266.5</v>
+        <v>26403.81</v>
       </c>
       <c r="D26" t="n">
-        <v>26082.43</v>
+        <v>26123.18</v>
       </c>
       <c r="E26" t="n">
-        <v>26202.35</v>
+        <v>26126.3</v>
       </c>
       <c r="F26" t="n">
-        <v>201.04</v>
+        <v>-76.05</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0029</v>
       </c>
       <c r="H26" t="n">
-        <v>184.07</v>
+        <v>280.63</v>
       </c>
       <c r="I26" t="n">
-        <v>25613.31</v>
+        <v>25898.36</v>
       </c>
       <c r="J26" t="n">
-        <v>25772.14</v>
+        <v>26032.22</v>
       </c>
       <c r="K26" t="n">
-        <v>25880.41</v>
+        <v>26110.31</v>
       </c>
       <c r="L26" t="n">
-        <v>25988.67</v>
+        <v>26188.41</v>
       </c>
       <c r="M26" t="n">
-        <v>26122.22</v>
+        <v>26294.38</v>
       </c>
       <c r="N26" t="n">
-        <v>26255.76</v>
+        <v>26400.36</v>
       </c>
       <c r="O26" t="n">
-        <v>26338.74</v>
+        <v>26450.57</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2686,12 +2688,14 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -2701,7 +2705,7 @@
       </c>
       <c r="U26" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V26" s="8" t="n">
@@ -2712,55 +2716,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26393.43</v>
+        <v>26116.27</v>
       </c>
       <c r="C27" t="n">
-        <v>26403.81</v>
+        <v>26229.33</v>
       </c>
       <c r="D27" t="n">
-        <v>26123.18</v>
+        <v>26081.69</v>
       </c>
       <c r="E27" t="n">
-        <v>26126.3</v>
+        <v>26140.13</v>
       </c>
       <c r="F27" t="n">
-        <v>-76.05</v>
+        <v>13.83</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0005</v>
       </c>
       <c r="H27" t="n">
-        <v>280.63</v>
+        <v>147.64</v>
       </c>
       <c r="I27" t="n">
-        <v>25898.36</v>
+        <v>25842.55</v>
       </c>
       <c r="J27" t="n">
-        <v>26032.22</v>
+        <v>25777.07</v>
       </c>
       <c r="K27" t="n">
-        <v>26110.31</v>
+        <v>25985.99</v>
       </c>
       <c r="L27" t="n">
-        <v>26188.41</v>
+        <v>26194.9</v>
       </c>
       <c r="M27" t="n">
-        <v>26294.38</v>
+        <v>26266.62</v>
       </c>
       <c r="N27" t="n">
-        <v>26400.36</v>
+        <v>26338.33</v>
       </c>
       <c r="O27" t="n">
-        <v>26450.57</v>
+        <v>26684.44</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2768,25 +2776,19 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2798,57 +2800,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26116.27</v>
+        <v>26235.8</v>
       </c>
       <c r="C28" t="n">
-        <v>26229.33</v>
+        <v>26445.18</v>
       </c>
       <c r="D28" t="n">
-        <v>26081.69</v>
+        <v>26223.64</v>
       </c>
       <c r="E28" t="n">
-        <v>26140.13</v>
+        <v>26319.45</v>
       </c>
       <c r="F28" t="n">
-        <v>13.83</v>
+        <v>179.32</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0069</v>
       </c>
       <c r="H28" t="n">
-        <v>147.64</v>
+        <v>221.54</v>
       </c>
       <c r="I28" t="n">
-        <v>25842.55</v>
+        <v>25934.05</v>
       </c>
       <c r="J28" t="n">
-        <v>25777.07</v>
+        <v>25984.8</v>
       </c>
       <c r="K28" t="n">
-        <v>25985.99</v>
+        <v>26066.31</v>
       </c>
       <c r="L28" t="n">
-        <v>26194.9</v>
+        <v>26147.82</v>
       </c>
       <c r="M28" t="n">
-        <v>26266.62</v>
+        <v>26213.95</v>
       </c>
       <c r="N28" t="n">
-        <v>26338.33</v>
+        <v>26280.08</v>
       </c>
       <c r="O28" t="n">
-        <v>26684.44</v>
+        <v>26376.97</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2859,78 +2861,80 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>26235.8</v>
+        <v>26360.44</v>
       </c>
       <c r="C29" t="n">
-        <v>26445.18</v>
+        <v>26441.91</v>
       </c>
       <c r="D29" t="n">
-        <v>26223.64</v>
+        <v>26302.19</v>
       </c>
       <c r="E29" t="n">
-        <v>26319.45</v>
+        <v>26323.88</v>
       </c>
       <c r="F29" t="n">
-        <v>179.32</v>
+        <v>4.43</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0002</v>
       </c>
       <c r="H29" t="n">
-        <v>221.54</v>
+        <v>139.72</v>
       </c>
       <c r="I29" t="n">
-        <v>25934.05</v>
+        <v>26002.1</v>
       </c>
       <c r="J29" t="n">
-        <v>25984.8</v>
+        <v>26090.43</v>
       </c>
       <c r="K29" t="n">
-        <v>26066.31</v>
+        <v>26208.68</v>
       </c>
       <c r="L29" t="n">
-        <v>26147.82</v>
+        <v>26326.93</v>
       </c>
       <c r="M29" t="n">
-        <v>26213.95</v>
+        <v>26430.22</v>
       </c>
       <c r="N29" t="n">
-        <v>26280.08</v>
+        <v>26533.51</v>
       </c>
       <c r="O29" t="n">
-        <v>26376.97</v>
+        <v>26666.72</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2941,9 +2945,9 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
@@ -2951,70 +2955,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26360.44</v>
+        <v>26378</v>
       </c>
       <c r="C30" t="n">
-        <v>26441.91</v>
+        <v>26504.54</v>
       </c>
       <c r="D30" t="n">
-        <v>26302.19</v>
+        <v>26245.57</v>
       </c>
       <c r="E30" t="n">
-        <v>26323.88</v>
+        <v>26391.42</v>
       </c>
       <c r="F30" t="n">
-        <v>4.43</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0026</v>
       </c>
       <c r="H30" t="n">
-        <v>139.72</v>
+        <v>258.97</v>
       </c>
       <c r="I30" t="n">
-        <v>26002.1</v>
+        <v>26162.47</v>
       </c>
       <c r="J30" t="n">
-        <v>26090.43</v>
+        <v>26160.08</v>
       </c>
       <c r="K30" t="n">
-        <v>26208.68</v>
+        <v>26254.02</v>
       </c>
       <c r="L30" t="n">
-        <v>26326.93</v>
+        <v>26347.97</v>
       </c>
       <c r="M30" t="n">
-        <v>26430.22</v>
+        <v>26393.74</v>
       </c>
       <c r="N30" t="n">
-        <v>26533.51</v>
+        <v>26439.52</v>
       </c>
       <c r="O30" t="n">
-        <v>26666.72</v>
+        <v>26581.63</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3022,21 +3026,25 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3055,50 +3063,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>26378</v>
+        <v>26452</v>
       </c>
       <c r="C31" t="n">
-        <v>26504.54</v>
+        <v>26573.5</v>
       </c>
       <c r="D31" t="n">
-        <v>26245.57</v>
+        <v>26313.58</v>
       </c>
       <c r="E31" t="n">
-        <v>26391.42</v>
+        <v>26331.07</v>
       </c>
       <c r="F31" t="n">
-        <v>67.54000000000001</v>
+        <v>-60.35</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0023</v>
       </c>
       <c r="H31" t="n">
-        <v>258.97</v>
+        <v>259.92</v>
       </c>
       <c r="I31" t="n">
-        <v>26162.47</v>
+        <v>25986.6</v>
       </c>
       <c r="J31" t="n">
-        <v>26160.08</v>
+        <v>26140.63</v>
       </c>
       <c r="K31" t="n">
-        <v>26254.02</v>
+        <v>26261.94</v>
       </c>
       <c r="L31" t="n">
-        <v>26347.97</v>
+        <v>26383.24</v>
       </c>
       <c r="M31" t="n">
-        <v>26393.74</v>
+        <v>26520.9</v>
       </c>
       <c r="N31" t="n">
-        <v>26439.52</v>
+        <v>26658.57</v>
       </c>
       <c r="O31" t="n">
-        <v>26581.63</v>
+        <v>26763.51</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3106,25 +3114,21 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3143,50 +3147,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26452</v>
+        <v>26437.35</v>
       </c>
       <c r="C32" t="n">
-        <v>26573.5</v>
+        <v>26489.78</v>
       </c>
       <c r="D32" t="n">
-        <v>26313.58</v>
+        <v>26285.23</v>
       </c>
       <c r="E32" t="n">
-        <v>26331.07</v>
+        <v>26299.74</v>
       </c>
       <c r="F32" t="n">
-        <v>-60.35</v>
+        <v>-31.33</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0012</v>
       </c>
       <c r="H32" t="n">
-        <v>259.92</v>
+        <v>204.55</v>
       </c>
       <c r="I32" t="n">
-        <v>25986.6</v>
+        <v>26053.66</v>
       </c>
       <c r="J32" t="n">
-        <v>26140.63</v>
+        <v>26014.92</v>
       </c>
       <c r="K32" t="n">
-        <v>26261.94</v>
+        <v>26201.11</v>
       </c>
       <c r="L32" t="n">
-        <v>26383.24</v>
+        <v>26387.31</v>
       </c>
       <c r="M32" t="n">
-        <v>26520.9</v>
+        <v>26461.03</v>
       </c>
       <c r="N32" t="n">
-        <v>26658.57</v>
+        <v>26534.76</v>
       </c>
       <c r="O32" t="n">
-        <v>26763.51</v>
+        <v>26833.42</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3220,57 +3224,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>26437.35</v>
+        <v>26445.99</v>
       </c>
       <c r="C33" t="n">
-        <v>26489.78</v>
+        <v>26541.34</v>
       </c>
       <c r="D33" t="n">
-        <v>26285.23</v>
+        <v>26404.95</v>
       </c>
       <c r="E33" t="n">
-        <v>26299.74</v>
+        <v>26440.31</v>
       </c>
       <c r="F33" t="n">
-        <v>-31.33</v>
+        <v>140.57</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0053</v>
       </c>
       <c r="H33" t="n">
-        <v>204.55</v>
+        <v>136.39</v>
       </c>
       <c r="I33" t="n">
-        <v>26053.66</v>
+        <v>26080.68</v>
       </c>
       <c r="J33" t="n">
-        <v>26014.92</v>
+        <v>26051.31</v>
       </c>
       <c r="K33" t="n">
-        <v>26201.11</v>
+        <v>26197.47</v>
       </c>
       <c r="L33" t="n">
-        <v>26387.31</v>
+        <v>26343.62</v>
       </c>
       <c r="M33" t="n">
-        <v>26461.03</v>
+        <v>26402.01</v>
       </c>
       <c r="N33" t="n">
-        <v>26534.76</v>
+        <v>26460.41</v>
       </c>
       <c r="O33" t="n">
-        <v>26833.42</v>
+        <v>26694.33</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3281,9 +3285,9 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
@@ -3291,8 +3295,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3302,59 +3308,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26445.99</v>
+        <v>26490.3</v>
       </c>
       <c r="C34" t="n">
-        <v>26541.34</v>
+        <v>26493.5</v>
       </c>
       <c r="D34" t="n">
-        <v>26404.95</v>
+        <v>26338.61</v>
       </c>
       <c r="E34" t="n">
-        <v>26440.31</v>
+        <v>26338.61</v>
       </c>
       <c r="F34" t="n">
-        <v>140.57</v>
+        <v>-101.7</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0038</v>
       </c>
       <c r="H34" t="n">
-        <v>136.39</v>
+        <v>154.89</v>
       </c>
       <c r="I34" t="n">
-        <v>26080.68</v>
+        <v>26268.56</v>
       </c>
       <c r="J34" t="n">
-        <v>26051.31</v>
+        <v>26287.5</v>
       </c>
       <c r="K34" t="n">
-        <v>26197.47</v>
+        <v>26372.12</v>
       </c>
       <c r="L34" t="n">
-        <v>26343.62</v>
+        <v>26456.73</v>
       </c>
       <c r="M34" t="n">
-        <v>26402.01</v>
+        <v>26508.51</v>
       </c>
       <c r="N34" t="n">
-        <v>26460.41</v>
+        <v>26560.28</v>
       </c>
       <c r="O34" t="n">
-        <v>26694.33</v>
+        <v>26677.73</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3362,24 +3364,22 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
+      <c r="R34" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
@@ -3388,65 +3388,73 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>26490.3</v>
+        <v>26280.86</v>
       </c>
       <c r="C35" t="n">
-        <v>26493.5</v>
+        <v>26292.95</v>
       </c>
       <c r="D35" t="n">
-        <v>26338.61</v>
+        <v>26119.54</v>
       </c>
       <c r="E35" t="n">
-        <v>26338.61</v>
+        <v>26128.36</v>
       </c>
       <c r="F35" t="n">
-        <v>-101.7</v>
+        <v>-210.25</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.008</v>
       </c>
       <c r="H35" t="n">
-        <v>154.89</v>
+        <v>173.41</v>
       </c>
       <c r="I35" t="n">
-        <v>26268.56</v>
+        <v>26183.72</v>
       </c>
       <c r="J35" t="n">
-        <v>26287.5</v>
+        <v>26145</v>
       </c>
       <c r="K35" t="n">
-        <v>26372.12</v>
+        <v>26261.16</v>
       </c>
       <c r="L35" t="n">
-        <v>26456.73</v>
+        <v>26377.33</v>
       </c>
       <c r="M35" t="n">
-        <v>26508.51</v>
+        <v>26416.05</v>
       </c>
       <c r="N35" t="n">
-        <v>26560.28</v>
+        <v>26454.78</v>
       </c>
       <c r="O35" t="n">
-        <v>26677.73</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
+        <v>26648.39</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
@@ -3463,78 +3471,70 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W35" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26280.86</v>
+        <v>26146.12</v>
       </c>
       <c r="C36" t="n">
-        <v>26292.95</v>
+        <v>26187.82</v>
       </c>
       <c r="D36" t="n">
-        <v>26119.54</v>
+        <v>26063.37</v>
       </c>
       <c r="E36" t="n">
-        <v>26128.36</v>
+        <v>26091.33</v>
       </c>
       <c r="F36" t="n">
-        <v>-210.25</v>
+        <v>-37.03</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0014</v>
       </c>
       <c r="H36" t="n">
-        <v>173.41</v>
+        <v>124.45</v>
       </c>
       <c r="I36" t="n">
-        <v>26183.72</v>
+        <v>25946.13</v>
       </c>
       <c r="J36" t="n">
-        <v>26145</v>
+        <v>25916.01</v>
       </c>
       <c r="K36" t="n">
-        <v>26261.16</v>
+        <v>26041.65</v>
       </c>
       <c r="L36" t="n">
-        <v>26377.33</v>
+        <v>26167.3</v>
       </c>
       <c r="M36" t="n">
-        <v>26416.05</v>
+        <v>26215.06</v>
       </c>
       <c r="N36" t="n">
-        <v>26454.78</v>
+        <v>26262.83</v>
       </c>
       <c r="O36" t="n">
-        <v>26648.39</v>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q36" s="6" t="inlineStr">
+        <v>26466.36</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
@@ -3561,60 +3561,64 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26146.12</v>
+        <v>26050.95</v>
       </c>
       <c r="C37" t="n">
-        <v>26187.82</v>
+        <v>26062.15</v>
       </c>
       <c r="D37" t="n">
-        <v>26063.37</v>
+        <v>25914.11</v>
       </c>
       <c r="E37" t="n">
-        <v>26091.33</v>
+        <v>25983.04</v>
       </c>
       <c r="F37" t="n">
-        <v>-37.03</v>
+        <v>-108.29</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0042</v>
       </c>
       <c r="H37" t="n">
-        <v>124.45</v>
+        <v>148.04</v>
       </c>
       <c r="I37" t="n">
-        <v>25946.13</v>
+        <v>25938.92</v>
       </c>
       <c r="J37" t="n">
-        <v>25916.01</v>
+        <v>25949.75</v>
       </c>
       <c r="K37" t="n">
-        <v>26041.65</v>
+        <v>26029.1</v>
       </c>
       <c r="L37" t="n">
-        <v>26167.3</v>
+        <v>26108.46</v>
       </c>
       <c r="M37" t="n">
-        <v>26215.06</v>
+        <v>26153.56</v>
       </c>
       <c r="N37" t="n">
-        <v>26262.83</v>
+        <v>26198.65</v>
       </c>
       <c r="O37" t="n">
-        <v>26466.36</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
+        <v>26312.27</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
@@ -3641,83 +3645,81 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26050.95</v>
+        <v>25998.95</v>
       </c>
       <c r="C38" t="n">
-        <v>26062.15</v>
+        <v>26166.25</v>
       </c>
       <c r="D38" t="n">
-        <v>25914.11</v>
+        <v>25969.52</v>
       </c>
       <c r="E38" t="n">
-        <v>25983.04</v>
+        <v>26136.56</v>
       </c>
       <c r="F38" t="n">
-        <v>-108.29</v>
+        <v>153.52</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.0059</v>
       </c>
       <c r="H38" t="n">
-        <v>148.04</v>
+        <v>196.73</v>
       </c>
       <c r="I38" t="n">
-        <v>25938.92</v>
+        <v>25766.07</v>
       </c>
       <c r="J38" t="n">
-        <v>25949.75</v>
+        <v>25832.45</v>
       </c>
       <c r="K38" t="n">
-        <v>26029.1</v>
+        <v>25909.02</v>
       </c>
       <c r="L38" t="n">
-        <v>26108.46</v>
+        <v>25985.58</v>
       </c>
       <c r="M38" t="n">
-        <v>26153.56</v>
+        <v>26057.06</v>
       </c>
       <c r="N38" t="n">
-        <v>26198.65</v>
+        <v>26128.53</v>
       </c>
       <c r="O38" t="n">
-        <v>26312.27</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
+        <v>26210.19</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W38" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr"/>
@@ -3725,50 +3727,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25998.95</v>
+        <v>26091.29</v>
       </c>
       <c r="C39" t="n">
-        <v>26166.25</v>
+        <v>26171.7</v>
       </c>
       <c r="D39" t="n">
-        <v>25969.52</v>
+        <v>26038.07</v>
       </c>
       <c r="E39" t="n">
-        <v>26136.56</v>
+        <v>26106.6</v>
       </c>
       <c r="F39" t="n">
-        <v>153.52</v>
+        <v>-29.96</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0011</v>
       </c>
       <c r="H39" t="n">
-        <v>196.73</v>
+        <v>133.63</v>
       </c>
       <c r="I39" t="n">
-        <v>25766.07</v>
+        <v>25772.79</v>
       </c>
       <c r="J39" t="n">
-        <v>25832.45</v>
+        <v>25974.17</v>
       </c>
       <c r="K39" t="n">
-        <v>25909.02</v>
+        <v>26038.2</v>
       </c>
       <c r="L39" t="n">
-        <v>25985.58</v>
+        <v>26102.22</v>
       </c>
       <c r="M39" t="n">
-        <v>26057.06</v>
+        <v>26234.93</v>
       </c>
       <c r="N39" t="n">
-        <v>26128.53</v>
+        <v>26367.63</v>
       </c>
       <c r="O39" t="n">
-        <v>26210.19</v>
+        <v>26362.98</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3776,23 +3778,21 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3802,55 +3802,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>26091.29</v>
+        <v>26206.01</v>
       </c>
       <c r="C40" t="n">
-        <v>26171.7</v>
+        <v>26341.52</v>
       </c>
       <c r="D40" t="n">
-        <v>26038.07</v>
+        <v>26164.11</v>
       </c>
       <c r="E40" t="n">
-        <v>26106.6</v>
+        <v>26266.14</v>
       </c>
       <c r="F40" t="n">
-        <v>-29.96</v>
+        <v>159.54</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0061</v>
       </c>
       <c r="H40" t="n">
-        <v>133.63</v>
+        <v>177.41</v>
       </c>
       <c r="I40" t="n">
-        <v>25772.79</v>
+        <v>25904.44</v>
       </c>
       <c r="J40" t="n">
-        <v>25974.17</v>
+        <v>25973.83</v>
       </c>
       <c r="K40" t="n">
-        <v>26038.2</v>
+        <v>26039.79</v>
       </c>
       <c r="L40" t="n">
-        <v>26102.22</v>
+        <v>26105.74</v>
       </c>
       <c r="M40" t="n">
-        <v>26234.93</v>
+        <v>26173.41</v>
       </c>
       <c r="N40" t="n">
-        <v>26367.63</v>
+        <v>26241.09</v>
       </c>
       <c r="O40" t="n">
-        <v>26362.98</v>
+        <v>26305.33</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3858,83 +3862,83 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26206.01</v>
+        <v>26255.41</v>
       </c>
       <c r="C41" t="n">
-        <v>26341.52</v>
+        <v>26466.76</v>
       </c>
       <c r="D41" t="n">
-        <v>26164.11</v>
+        <v>26196.92</v>
       </c>
       <c r="E41" t="n">
-        <v>26266.14</v>
+        <v>26285.96</v>
       </c>
       <c r="F41" t="n">
-        <v>159.54</v>
+        <v>19.82</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0061</v>
+        <v>0.0008</v>
       </c>
       <c r="H41" t="n">
-        <v>177.41</v>
+        <v>269.84</v>
       </c>
       <c r="I41" t="n">
-        <v>25904.44</v>
+        <v>25986.7</v>
       </c>
       <c r="J41" t="n">
-        <v>25973.83</v>
+        <v>26095.39</v>
       </c>
       <c r="K41" t="n">
-        <v>26039.79</v>
+        <v>26177.44</v>
       </c>
       <c r="L41" t="n">
-        <v>26105.74</v>
+        <v>26259.48</v>
       </c>
       <c r="M41" t="n">
-        <v>26173.41</v>
+        <v>26354.85</v>
       </c>
       <c r="N41" t="n">
-        <v>26241.09</v>
+        <v>26450.21</v>
       </c>
       <c r="O41" t="n">
-        <v>26305.33</v>
+        <v>26518.93</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3947,7 +3951,7 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
@@ -3957,13 +3961,11 @@
       </c>
       <c r="U41" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v/>
       </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
@@ -3975,50 +3977,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26255.41</v>
+        <v>26354.37</v>
       </c>
       <c r="C42" t="n">
-        <v>26466.76</v>
+        <v>26402.81</v>
       </c>
       <c r="D42" t="n">
-        <v>26196.92</v>
+        <v>26241.77</v>
       </c>
       <c r="E42" t="n">
-        <v>26285.96</v>
+        <v>26367.24</v>
       </c>
       <c r="F42" t="n">
-        <v>19.82</v>
+        <v>81.28</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0031</v>
       </c>
       <c r="H42" t="n">
-        <v>269.84</v>
+        <v>161.04</v>
       </c>
       <c r="I42" t="n">
-        <v>25986.7</v>
+        <v>25927.08</v>
       </c>
       <c r="J42" t="n">
-        <v>26095.39</v>
+        <v>25993.18</v>
       </c>
       <c r="K42" t="n">
-        <v>26177.44</v>
+        <v>26151.04</v>
       </c>
       <c r="L42" t="n">
-        <v>26259.48</v>
+        <v>26308.9</v>
       </c>
       <c r="M42" t="n">
-        <v>26354.85</v>
+        <v>26420.88</v>
       </c>
       <c r="N42" t="n">
-        <v>26450.21</v>
+        <v>26532.86</v>
       </c>
       <c r="O42" t="n">
-        <v>26518.93</v>
+        <v>26736.6</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4031,18 +4033,16 @@
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4052,55 +4052,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>26354.37</v>
+        <v>26494.61</v>
       </c>
       <c r="C43" t="n">
-        <v>26402.81</v>
+        <v>26618.74</v>
       </c>
       <c r="D43" t="n">
-        <v>26241.77</v>
+        <v>26467.36</v>
       </c>
       <c r="E43" t="n">
-        <v>26367.24</v>
+        <v>26569.99</v>
       </c>
       <c r="F43" t="n">
-        <v>81.28</v>
+        <v>202.75</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0077</v>
       </c>
       <c r="H43" t="n">
-        <v>161.04</v>
+        <v>151.38</v>
       </c>
       <c r="I43" t="n">
-        <v>25927.08</v>
+        <v>26080.73</v>
       </c>
       <c r="J43" t="n">
-        <v>25993.18</v>
+        <v>26228.67</v>
       </c>
       <c r="K43" t="n">
-        <v>26151.04</v>
+        <v>26286.72</v>
       </c>
       <c r="L43" t="n">
-        <v>26308.9</v>
+        <v>26344.77</v>
       </c>
       <c r="M43" t="n">
-        <v>26420.88</v>
+        <v>26447.76</v>
       </c>
       <c r="N43" t="n">
-        <v>26532.86</v>
+        <v>26550.76</v>
       </c>
       <c r="O43" t="n">
-        <v>26736.6</v>
+        <v>26563.85</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4118,106 +4122,106 @@
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v/>
-      </c>
       <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26494.61</v>
+        <v>26464.14</v>
       </c>
       <c r="C44" t="n">
-        <v>26618.74</v>
+        <v>26471.79</v>
       </c>
       <c r="D44" t="n">
-        <v>26467.36</v>
+        <v>26249.59</v>
       </c>
       <c r="E44" t="n">
-        <v>26569.99</v>
+        <v>26258.11</v>
       </c>
       <c r="F44" t="n">
-        <v>202.75</v>
+        <v>-311.88</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0117</v>
       </c>
       <c r="H44" t="n">
-        <v>151.38</v>
+        <v>222.2</v>
       </c>
       <c r="I44" t="n">
-        <v>26080.73</v>
+        <v>26315.98</v>
       </c>
       <c r="J44" t="n">
-        <v>26228.67</v>
+        <v>26432.08</v>
       </c>
       <c r="K44" t="n">
-        <v>26286.72</v>
+        <v>26494.3</v>
       </c>
       <c r="L44" t="n">
-        <v>26344.77</v>
+        <v>26556.52</v>
       </c>
       <c r="M44" t="n">
-        <v>26447.76</v>
+        <v>26645.68</v>
       </c>
       <c r="N44" t="n">
-        <v>26550.76</v>
+        <v>26734.84</v>
       </c>
       <c r="O44" t="n">
-        <v>26563.85</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
+        <v>26770.12</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W44" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W44" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr"/>
@@ -4225,59 +4229,59 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>26464.14</v>
+        <v>26150.75</v>
       </c>
       <c r="C45" t="n">
-        <v>26471.79</v>
+        <v>26206.13</v>
       </c>
       <c r="D45" t="n">
-        <v>26249.59</v>
+        <v>25916.76</v>
       </c>
       <c r="E45" t="n">
-        <v>26258.11</v>
+        <v>25970.11</v>
       </c>
       <c r="F45" t="n">
-        <v>-311.88</v>
+        <v>-288</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.011</v>
       </c>
       <c r="H45" t="n">
-        <v>222.2</v>
+        <v>289.37</v>
       </c>
       <c r="I45" t="n">
-        <v>26315.98</v>
+        <v>26027.39</v>
       </c>
       <c r="J45" t="n">
-        <v>26432.08</v>
+        <v>25984.62</v>
       </c>
       <c r="K45" t="n">
-        <v>26494.3</v>
+        <v>26147.01</v>
       </c>
       <c r="L45" t="n">
-        <v>26556.52</v>
+        <v>26309.4</v>
       </c>
       <c r="M45" t="n">
-        <v>26645.68</v>
+        <v>26369.21</v>
       </c>
       <c r="N45" t="n">
-        <v>26734.84</v>
+        <v>26429.02</v>
       </c>
       <c r="O45" t="n">
-        <v>26770.12</v>
+        <v>26693.99</v>
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
@@ -4309,64 +4313,60 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>26150.75</v>
+        <v>25886.67</v>
       </c>
       <c r="C46" t="n">
-        <v>26206.13</v>
+        <v>25924.21</v>
       </c>
       <c r="D46" t="n">
-        <v>25916.76</v>
+        <v>25727.93</v>
       </c>
       <c r="E46" t="n">
-        <v>25970.11</v>
+        <v>25839.33</v>
       </c>
       <c r="F46" t="n">
-        <v>-288</v>
+        <v>-130.78</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.005</v>
       </c>
       <c r="H46" t="n">
-        <v>289.37</v>
+        <v>196.28</v>
       </c>
       <c r="I46" t="n">
-        <v>26027.39</v>
+        <v>25627.39</v>
       </c>
       <c r="J46" t="n">
-        <v>25984.62</v>
+        <v>25635.07</v>
       </c>
       <c r="K46" t="n">
-        <v>26147.01</v>
+        <v>25825.42</v>
       </c>
       <c r="L46" t="n">
-        <v>26309.4</v>
+        <v>26015.78</v>
       </c>
       <c r="M46" t="n">
-        <v>26369.21</v>
+        <v>26114.79</v>
       </c>
       <c r="N46" t="n">
-        <v>26429.02</v>
+        <v>26213.81</v>
       </c>
       <c r="O46" t="n">
-        <v>26693.99</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
+        <v>26495.5</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
@@ -4393,50 +4393,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25886.67</v>
+        <v>25840.92</v>
       </c>
       <c r="C47" t="n">
-        <v>25924.21</v>
+        <v>26007.79</v>
       </c>
       <c r="D47" t="n">
-        <v>25727.93</v>
+        <v>25784.84</v>
       </c>
       <c r="E47" t="n">
-        <v>25839.33</v>
+        <v>26003.32</v>
       </c>
       <c r="F47" t="n">
-        <v>-130.78</v>
+        <v>163.99</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0063</v>
       </c>
       <c r="H47" t="n">
-        <v>196.28</v>
+        <v>222.95</v>
       </c>
       <c r="I47" t="n">
-        <v>25627.39</v>
+        <v>25531.65</v>
       </c>
       <c r="J47" t="n">
-        <v>25635.07</v>
+        <v>25649.68</v>
       </c>
       <c r="K47" t="n">
-        <v>25825.42</v>
+        <v>25741.19</v>
       </c>
       <c r="L47" t="n">
-        <v>26015.78</v>
+        <v>25832.7</v>
       </c>
       <c r="M47" t="n">
-        <v>26114.79</v>
+        <v>25937.47</v>
       </c>
       <c r="N47" t="n">
-        <v>26213.81</v>
+        <v>26042.24</v>
       </c>
       <c r="O47" t="n">
-        <v>26495.5</v>
+        <v>26120.49</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4444,22 +4444,24 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
@@ -4468,55 +4470,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25840.92</v>
+        <v>25985.86</v>
       </c>
       <c r="C48" t="n">
-        <v>26007.79</v>
+        <v>26167.93</v>
       </c>
       <c r="D48" t="n">
-        <v>25784.84</v>
+        <v>25958.7</v>
       </c>
       <c r="E48" t="n">
-        <v>26003.32</v>
+        <v>26046.4</v>
       </c>
       <c r="F48" t="n">
-        <v>163.99</v>
+        <v>43.08</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0017</v>
       </c>
       <c r="H48" t="n">
-        <v>222.95</v>
+        <v>209.23</v>
       </c>
       <c r="I48" t="n">
-        <v>25531.65</v>
+        <v>25561.89</v>
       </c>
       <c r="J48" t="n">
-        <v>25649.68</v>
+        <v>25833.87</v>
       </c>
       <c r="K48" t="n">
-        <v>25741.19</v>
+        <v>25891.85</v>
       </c>
       <c r="L48" t="n">
-        <v>25832.7</v>
+        <v>25949.82</v>
       </c>
       <c r="M48" t="n">
-        <v>25937.47</v>
+        <v>26114.79</v>
       </c>
       <c r="N48" t="n">
-        <v>26042.24</v>
+        <v>26279.77</v>
       </c>
       <c r="O48" t="n">
-        <v>26120.49</v>
+        <v>26230.74</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4534,13 +4540,11 @@
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4559,50 +4563,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25985.86</v>
+        <v>26039.54</v>
       </c>
       <c r="C49" t="n">
-        <v>26167.93</v>
+        <v>26069.99</v>
       </c>
       <c r="D49" t="n">
-        <v>25958.7</v>
+        <v>25919.61</v>
       </c>
       <c r="E49" t="n">
-        <v>26046.4</v>
+        <v>26006.53</v>
       </c>
       <c r="F49" t="n">
-        <v>43.08</v>
+        <v>-39.87</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0015</v>
       </c>
       <c r="H49" t="n">
-        <v>209.23</v>
+        <v>150.38</v>
       </c>
       <c r="I49" t="n">
-        <v>25561.89</v>
+        <v>25749.47</v>
       </c>
       <c r="J49" t="n">
-        <v>25833.87</v>
+        <v>25828.71</v>
       </c>
       <c r="K49" t="n">
-        <v>25891.85</v>
+        <v>25941.79</v>
       </c>
       <c r="L49" t="n">
-        <v>25949.82</v>
+        <v>26054.86</v>
       </c>
       <c r="M49" t="n">
-        <v>26114.79</v>
+        <v>26151.02</v>
       </c>
       <c r="N49" t="n">
-        <v>26279.77</v>
+        <v>26247.17</v>
       </c>
       <c r="O49" t="n">
-        <v>26230.74</v>
+        <v>26377.16</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4610,18 +4614,18 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4634,74 +4638,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>26039.54</v>
+        <v>25897.22</v>
       </c>
       <c r="C50" t="n">
-        <v>26069.99</v>
+        <v>26026.78</v>
       </c>
       <c r="D50" t="n">
-        <v>25919.61</v>
+        <v>25799.66</v>
       </c>
       <c r="E50" t="n">
-        <v>26006.53</v>
+        <v>26007.63</v>
       </c>
       <c r="F50" t="n">
-        <v>-39.87</v>
+        <v>1.1</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>150.38</v>
+        <v>227.12</v>
       </c>
       <c r="I50" t="n">
-        <v>25749.47</v>
+        <v>25769.23</v>
       </c>
       <c r="J50" t="n">
-        <v>25828.71</v>
+        <v>25862.01</v>
       </c>
       <c r="K50" t="n">
-        <v>25941.79</v>
+        <v>25931.34</v>
       </c>
       <c r="L50" t="n">
-        <v>26054.86</v>
+        <v>26000.66</v>
       </c>
       <c r="M50" t="n">
-        <v>26151.02</v>
+        <v>26081.72</v>
       </c>
       <c r="N50" t="n">
-        <v>26247.17</v>
+        <v>26162.77</v>
       </c>
       <c r="O50" t="n">
-        <v>26377.16</v>
+        <v>26220.37</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4718,58 +4720,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25897.22</v>
+        <v>25870.98</v>
       </c>
       <c r="C51" t="n">
-        <v>26026.78</v>
+        <v>25909.66</v>
       </c>
       <c r="D51" t="n">
-        <v>25799.66</v>
+        <v>25512.39</v>
       </c>
       <c r="E51" t="n">
-        <v>26007.63</v>
+        <v>25576.45</v>
       </c>
       <c r="F51" t="n">
-        <v>1.1</v>
+        <v>-431.18</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0</v>
+        <v>-0.0166</v>
       </c>
       <c r="H51" t="n">
-        <v>227.12</v>
+        <v>397.27</v>
       </c>
       <c r="I51" t="n">
-        <v>25769.23</v>
+        <v>25572.54</v>
       </c>
       <c r="J51" t="n">
-        <v>25862.01</v>
+        <v>25827.72</v>
       </c>
       <c r="K51" t="n">
-        <v>25931.34</v>
+        <v>25894.07</v>
       </c>
       <c r="L51" t="n">
-        <v>26000.66</v>
+        <v>25960.43</v>
       </c>
       <c r="M51" t="n">
-        <v>26081.72</v>
+        <v>26121.19</v>
       </c>
       <c r="N51" t="n">
-        <v>26162.77</v>
+        <v>26281.96</v>
       </c>
       <c r="O51" t="n">
-        <v>26220.37</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
+        <v>26253.9</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
@@ -4781,9 +4789,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4800,73 +4808,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25870.98</v>
+        <v>25555.66</v>
       </c>
       <c r="C52" t="n">
-        <v>25909.66</v>
+        <v>25612.09</v>
       </c>
       <c r="D52" t="n">
-        <v>25512.39</v>
+        <v>25361.15</v>
       </c>
       <c r="E52" t="n">
-        <v>25576.45</v>
+        <v>25361.15</v>
       </c>
       <c r="F52" t="n">
-        <v>-431.18</v>
+        <v>-215.3</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>397.27</v>
+        <v>250.94</v>
       </c>
       <c r="I52" t="n">
-        <v>25572.54</v>
+        <v>25115.12</v>
       </c>
       <c r="J52" t="n">
-        <v>25827.72</v>
+        <v>25111.89</v>
       </c>
       <c r="K52" t="n">
-        <v>25894.07</v>
+        <v>25377.81</v>
       </c>
       <c r="L52" t="n">
-        <v>25960.43</v>
+        <v>25643.74</v>
       </c>
       <c r="M52" t="n">
-        <v>26121.19</v>
+        <v>25775.08</v>
       </c>
       <c r="N52" t="n">
-        <v>26281.96</v>
+        <v>25906.43</v>
       </c>
       <c r="O52" t="n">
-        <v>26253.9</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
+        <v>26306.93</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
@@ -4893,50 +4893,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25555.66</v>
+        <v>25478.84</v>
       </c>
       <c r="C53" t="n">
-        <v>25612.09</v>
+        <v>25581.22</v>
       </c>
       <c r="D53" t="n">
-        <v>25361.15</v>
+        <v>25396.38</v>
       </c>
       <c r="E53" t="n">
-        <v>25361.15</v>
+        <v>25568.56</v>
       </c>
       <c r="F53" t="n">
-        <v>-215.3</v>
+        <v>207.41</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>250.94</v>
+        <v>184.84</v>
       </c>
       <c r="I53" t="n">
-        <v>25115.12</v>
+        <v>25110.21</v>
       </c>
       <c r="J53" t="n">
-        <v>25111.89</v>
+        <v>25047.48</v>
       </c>
       <c r="K53" t="n">
-        <v>25377.81</v>
+        <v>25235.68</v>
       </c>
       <c r="L53" t="n">
-        <v>25643.74</v>
+        <v>25423.89</v>
       </c>
       <c r="M53" t="n">
-        <v>25775.08</v>
+        <v>25486.62</v>
       </c>
       <c r="N53" t="n">
-        <v>25906.43</v>
+        <v>25549.35</v>
       </c>
       <c r="O53" t="n">
-        <v>26306.93</v>
+        <v>25863.03</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4944,104 +4944,110 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="W53" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25478.84</v>
+        <v>25498.74</v>
       </c>
       <c r="C54" t="n">
-        <v>25581.22</v>
+        <v>25548.78</v>
       </c>
       <c r="D54" t="n">
-        <v>25396.38</v>
+        <v>25325.52</v>
       </c>
       <c r="E54" t="n">
-        <v>25568.56</v>
+        <v>25440.81</v>
       </c>
       <c r="F54" t="n">
-        <v>207.41</v>
+        <v>-127.75</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.005</v>
       </c>
       <c r="H54" t="n">
-        <v>184.84</v>
+        <v>223.26</v>
       </c>
       <c r="I54" t="n">
-        <v>25110.21</v>
+        <v>25211.54</v>
       </c>
       <c r="J54" t="n">
-        <v>25047.48</v>
+        <v>25423.6</v>
       </c>
       <c r="K54" t="n">
-        <v>25235.68</v>
+        <v>25476.14</v>
       </c>
       <c r="L54" t="n">
-        <v>25423.89</v>
+        <v>25528.68</v>
       </c>
       <c r="M54" t="n">
-        <v>25486.62</v>
+        <v>25660.98</v>
       </c>
       <c r="N54" t="n">
-        <v>25549.35</v>
+        <v>25793.28</v>
       </c>
       <c r="O54" t="n">
-        <v>25863.03</v>
+        <v>25766.06</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
+      <c r="Q54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
@@ -5052,64 +5058,64 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25498.74</v>
+        <v>25360.32</v>
       </c>
       <c r="C55" t="n">
-        <v>25548.78</v>
+        <v>25478.98</v>
       </c>
       <c r="D55" t="n">
-        <v>25325.52</v>
+        <v>25172.89</v>
       </c>
       <c r="E55" t="n">
-        <v>25440.81</v>
+        <v>25402.28</v>
       </c>
       <c r="F55" t="n">
-        <v>-127.75</v>
+        <v>-38.53</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.005</v>
+        <v>-0.0015</v>
       </c>
       <c r="H55" t="n">
-        <v>223.26</v>
+        <v>306.09</v>
       </c>
       <c r="I55" t="n">
-        <v>25211.54</v>
+        <v>25102.26</v>
       </c>
       <c r="J55" t="n">
-        <v>25423.6</v>
+        <v>25219.38</v>
       </c>
       <c r="K55" t="n">
-        <v>25476.14</v>
+        <v>25329.18</v>
       </c>
       <c r="L55" t="n">
-        <v>25528.68</v>
+        <v>25438.98</v>
       </c>
       <c r="M55" t="n">
-        <v>25660.98</v>
+        <v>25552.44</v>
       </c>
       <c r="N55" t="n">
-        <v>25793.28</v>
+        <v>25665.9</v>
       </c>
       <c r="O55" t="n">
-        <v>25766.06</v>
+        <v>25772.04</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
       <c r="Q55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
@@ -5119,7 +5125,7 @@
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5145,71 +5151,69 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25360.32</v>
+        <v>25515.96</v>
       </c>
       <c r="C56" t="n">
-        <v>25478.98</v>
+        <v>25599.07</v>
       </c>
       <c r="D56" t="n">
-        <v>25172.89</v>
+        <v>25361.7</v>
       </c>
       <c r="E56" t="n">
-        <v>25402.28</v>
+        <v>25537.75</v>
       </c>
       <c r="F56" t="n">
-        <v>-38.53</v>
+        <v>135.47</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0053</v>
       </c>
       <c r="H56" t="n">
-        <v>306.09</v>
+        <v>237.37</v>
       </c>
       <c r="I56" t="n">
-        <v>25102.26</v>
+        <v>24866.8</v>
       </c>
       <c r="J56" t="n">
-        <v>25219.38</v>
+        <v>25134.36</v>
       </c>
       <c r="K56" t="n">
-        <v>25329.18</v>
+        <v>25249.23</v>
       </c>
       <c r="L56" t="n">
-        <v>25438.98</v>
+        <v>25364.11</v>
       </c>
       <c r="M56" t="n">
-        <v>25552.44</v>
+        <v>25555.32</v>
       </c>
       <c r="N56" t="n">
-        <v>25665.9</v>
+        <v>25746.54</v>
       </c>
       <c r="O56" t="n">
-        <v>25772.04</v>
+        <v>25785.07</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5222,59 +5226,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25515.96</v>
+        <v>25681.6</v>
       </c>
       <c r="C57" t="n">
-        <v>25599.07</v>
+        <v>25800.62</v>
       </c>
       <c r="D57" t="n">
-        <v>25361.7</v>
+        <v>25596.05</v>
       </c>
       <c r="E57" t="n">
-        <v>25537.75</v>
+        <v>25716.71</v>
       </c>
       <c r="F57" t="n">
-        <v>135.47</v>
+        <v>178.96</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0053</v>
+        <v>0.007</v>
       </c>
       <c r="H57" t="n">
-        <v>237.37</v>
+        <v>204.57</v>
       </c>
       <c r="I57" t="n">
-        <v>24866.8</v>
+        <v>25124.33</v>
       </c>
       <c r="J57" t="n">
-        <v>25134.36</v>
+        <v>25329.06</v>
       </c>
       <c r="K57" t="n">
-        <v>25249.23</v>
+        <v>25419.06</v>
       </c>
       <c r="L57" t="n">
-        <v>25364.11</v>
+        <v>25509.07</v>
       </c>
       <c r="M57" t="n">
-        <v>25555.32</v>
+        <v>25656.44</v>
       </c>
       <c r="N57" t="n">
-        <v>25746.54</v>
+        <v>25803.8</v>
       </c>
       <c r="O57" t="n">
-        <v>25785.07</v>
+        <v>25836.44</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5311,79 +5311,83 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>25681.6</v>
+        <v>25596.46</v>
       </c>
       <c r="C58" t="n">
-        <v>25800.62</v>
+        <v>25656.22</v>
       </c>
       <c r="D58" t="n">
-        <v>25596.05</v>
+        <v>25285.9</v>
       </c>
       <c r="E58" t="n">
-        <v>25716.71</v>
+        <v>25304.06</v>
       </c>
       <c r="F58" t="n">
-        <v>178.96</v>
+        <v>-412.65</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.007</v>
+        <v>-0.016</v>
       </c>
       <c r="H58" t="n">
-        <v>204.57</v>
+        <v>370.32</v>
       </c>
       <c r="I58" t="n">
-        <v>25124.33</v>
+        <v>25391.48</v>
       </c>
       <c r="J58" t="n">
-        <v>25329.06</v>
+        <v>25521.33</v>
       </c>
       <c r="K58" t="n">
-        <v>25419.06</v>
+        <v>25614.43</v>
       </c>
       <c r="L58" t="n">
-        <v>25509.07</v>
+        <v>25707.52</v>
       </c>
       <c r="M58" t="n">
-        <v>25656.44</v>
+        <v>25819</v>
       </c>
       <c r="N58" t="n">
-        <v>25803.8</v>
+        <v>25930.47</v>
       </c>
       <c r="O58" t="n">
-        <v>25836.44</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
+        <v>26005.19</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X58" t="inlineStr"/>
@@ -5391,77 +5395,75 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25596.46</v>
+        <v>25491.35</v>
       </c>
       <c r="C59" t="n">
-        <v>25656.22</v>
+        <v>25617.99</v>
       </c>
       <c r="D59" t="n">
-        <v>25285.9</v>
+        <v>25434.16</v>
       </c>
       <c r="E59" t="n">
-        <v>25304.06</v>
+        <v>25575.01</v>
       </c>
       <c r="F59" t="n">
-        <v>-412.65</v>
+        <v>270.95</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.016</v>
+        <v>0.0107</v>
       </c>
       <c r="H59" t="n">
-        <v>370.32</v>
+        <v>183.83</v>
       </c>
       <c r="I59" t="n">
-        <v>25391.48</v>
+        <v>24915.58</v>
       </c>
       <c r="J59" t="n">
-        <v>25521.33</v>
+        <v>24850.24</v>
       </c>
       <c r="K59" t="n">
-        <v>25614.43</v>
+        <v>25118.9</v>
       </c>
       <c r="L59" t="n">
-        <v>25707.52</v>
+        <v>25387.56</v>
       </c>
       <c r="M59" t="n">
-        <v>25819</v>
+        <v>25489.22</v>
       </c>
       <c r="N59" t="n">
-        <v>25930.47</v>
+        <v>25590.88</v>
       </c>
       <c r="O59" t="n">
-        <v>26005.19</v>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
+        <v>26026.54</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
       <c r="V59" s="8" t="n">
         <v/>
       </c>
@@ -5470,55 +5472,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25491.35</v>
+        <v>25592.98</v>
       </c>
       <c r="C60" t="n">
-        <v>25617.99</v>
+        <v>25783.16</v>
       </c>
       <c r="D60" t="n">
-        <v>25434.16</v>
+        <v>25423.07</v>
       </c>
       <c r="E60" t="n">
-        <v>25575.01</v>
+        <v>25578.85</v>
       </c>
       <c r="F60" t="n">
-        <v>270.95</v>
+        <v>3.84</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0107</v>
+        <v>0.0002</v>
       </c>
       <c r="H60" t="n">
-        <v>183.83</v>
+        <v>360.09</v>
       </c>
       <c r="I60" t="n">
-        <v>24915.58</v>
+        <v>25250.33</v>
       </c>
       <c r="J60" t="n">
-        <v>24850.24</v>
+        <v>25415.65</v>
       </c>
       <c r="K60" t="n">
-        <v>25118.9</v>
+        <v>25483.09</v>
       </c>
       <c r="L60" t="n">
-        <v>25387.56</v>
+        <v>25550.54</v>
       </c>
       <c r="M60" t="n">
-        <v>25489.22</v>
+        <v>25666.92</v>
       </c>
       <c r="N60" t="n">
-        <v>25590.88</v>
+        <v>25783.31</v>
       </c>
       <c r="O60" t="n">
-        <v>26026.54</v>
+        <v>25801.82</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5526,12 +5532,14 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T60" s="8" t="inlineStr">
@@ -5539,10 +5547,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U60" s="8" t="n">
+        <v/>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
@@ -5561,50 +5567,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>25592.98</v>
+        <v>25724.13</v>
       </c>
       <c r="C61" t="n">
-        <v>25783.16</v>
+        <v>25729.05</v>
       </c>
       <c r="D61" t="n">
-        <v>25423.07</v>
+        <v>25365.21</v>
       </c>
       <c r="E61" t="n">
-        <v>25578.85</v>
+        <v>25410.63</v>
       </c>
       <c r="F61" t="n">
-        <v>3.84</v>
+        <v>-168.22</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.0066</v>
       </c>
       <c r="H61" t="n">
-        <v>360.09</v>
+        <v>363.84</v>
       </c>
       <c r="I61" t="n">
-        <v>25250.33</v>
+        <v>25062.98</v>
       </c>
       <c r="J61" t="n">
-        <v>25415.65</v>
+        <v>25206.63</v>
       </c>
       <c r="K61" t="n">
-        <v>25483.09</v>
+        <v>25398.8</v>
       </c>
       <c r="L61" t="n">
-        <v>25550.54</v>
+        <v>25590.98</v>
       </c>
       <c r="M61" t="n">
-        <v>25666.92</v>
+        <v>25758.89</v>
       </c>
       <c r="N61" t="n">
-        <v>25783.31</v>
+        <v>25926.81</v>
       </c>
       <c r="O61" t="n">
-        <v>25801.82</v>
+        <v>26143.25</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5614,18 +5620,16 @@
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5638,59 +5642,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>25724.13</v>
+        <v>25263.11</v>
       </c>
       <c r="C62" t="n">
-        <v>25729.05</v>
+        <v>25424.21</v>
       </c>
       <c r="D62" t="n">
-        <v>25365.21</v>
+        <v>25164.2</v>
       </c>
       <c r="E62" t="n">
-        <v>25410.63</v>
+        <v>25266.53</v>
       </c>
       <c r="F62" t="n">
-        <v>-168.22</v>
+        <v>-144.1</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0066</v>
+        <v>-0.0057</v>
       </c>
       <c r="H62" t="n">
-        <v>363.84</v>
+        <v>260.01</v>
       </c>
       <c r="I62" t="n">
-        <v>25062.98</v>
+        <v>25001.37</v>
       </c>
       <c r="J62" t="n">
-        <v>25206.63</v>
+        <v>24978.54</v>
       </c>
       <c r="K62" t="n">
-        <v>25398.8</v>
+        <v>25228.71</v>
       </c>
       <c r="L62" t="n">
-        <v>25590.98</v>
+        <v>25478.88</v>
       </c>
       <c r="M62" t="n">
-        <v>25758.89</v>
+        <v>25592.55</v>
       </c>
       <c r="N62" t="n">
-        <v>25926.81</v>
+        <v>25706.22</v>
       </c>
       <c r="O62" t="n">
-        <v>26143.25</v>
+        <v>26092.89</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5727,50 +5727,50 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>25263.11</v>
+        <v>25441.79</v>
       </c>
       <c r="C63" t="n">
-        <v>25424.21</v>
+        <v>25529.33</v>
       </c>
       <c r="D63" t="n">
-        <v>25164.2</v>
+        <v>25347.3</v>
       </c>
       <c r="E63" t="n">
-        <v>25266.53</v>
+        <v>25408.64</v>
       </c>
       <c r="F63" t="n">
-        <v>-144.1</v>
+        <v>142.11</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0056</v>
       </c>
       <c r="H63" t="n">
-        <v>260.01</v>
+        <v>182.03</v>
       </c>
       <c r="I63" t="n">
-        <v>25001.37</v>
+        <v>24904.19</v>
       </c>
       <c r="J63" t="n">
-        <v>24978.54</v>
+        <v>24992.68</v>
       </c>
       <c r="K63" t="n">
-        <v>25228.71</v>
+        <v>25136.52</v>
       </c>
       <c r="L63" t="n">
-        <v>25478.88</v>
+        <v>25280.37</v>
       </c>
       <c r="M63" t="n">
-        <v>25592.55</v>
+        <v>25396.54</v>
       </c>
       <c r="N63" t="n">
-        <v>25706.22</v>
+        <v>25512.7</v>
       </c>
       <c r="O63" t="n">
-        <v>26092.89</v>
+        <v>25684.22</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5778,21 +5778,23 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="inlineStr">
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V63" s="8" t="n">
         <v/>
@@ -5802,55 +5804,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>25441.79</v>
+        <v>25443.98</v>
       </c>
       <c r="C64" t="n">
-        <v>25529.33</v>
+        <v>25575.66</v>
       </c>
       <c r="D64" t="n">
-        <v>25347.3</v>
+        <v>25360.32</v>
       </c>
       <c r="E64" t="n">
-        <v>25408.64</v>
+        <v>25374.42</v>
       </c>
       <c r="F64" t="n">
-        <v>142.11</v>
+        <v>-34.22</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0056</v>
+        <v>-0.0013</v>
       </c>
       <c r="H64" t="n">
-        <v>182.03</v>
+        <v>215.34</v>
       </c>
       <c r="I64" t="n">
-        <v>24904.19</v>
+        <v>25165.27</v>
       </c>
       <c r="J64" t="n">
-        <v>24992.68</v>
+        <v>25211.77</v>
       </c>
       <c r="K64" t="n">
-        <v>25136.52</v>
+        <v>25317.63</v>
       </c>
       <c r="L64" t="n">
-        <v>25280.37</v>
+        <v>25423.48</v>
       </c>
       <c r="M64" t="n">
-        <v>25396.54</v>
+        <v>25499.66</v>
       </c>
       <c r="N64" t="n">
-        <v>25512.7</v>
+        <v>25575.83</v>
       </c>
       <c r="O64" t="n">
-        <v>25684.22</v>
+        <v>25711.36</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5861,20 +5867,18 @@
       <c r="R64" s="6" t="n">
         <v/>
       </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T64" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
       </c>
       <c r="V64" s="8" t="n">
         <v/>
@@ -5886,24 +5890,24 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>25443.98</v>
+        <v>25374.34</v>
       </c>
       <c r="C65" t="n">
-        <v>25575.66</v>
+        <v>25617.31</v>
       </c>
       <c r="D65" t="n">
-        <v>25360.32</v>
+        <v>25338.03</v>
       </c>
       <c r="E65" t="n">
         <v/>
@@ -5915,28 +5919,28 @@
         <v/>
       </c>
       <c r="H65" t="n">
-        <v>215.34</v>
+        <v>279.28</v>
       </c>
       <c r="I65" t="n">
-        <v>25165.27</v>
+        <v>25144.98</v>
       </c>
       <c r="J65" t="n">
-        <v>25211.77</v>
+        <v>25112.29</v>
       </c>
       <c r="K65" t="n">
-        <v>25317.63</v>
+        <v>25266.75</v>
       </c>
       <c r="L65" t="n">
-        <v>25423.48</v>
+        <v>25421.21</v>
       </c>
       <c r="M65" t="n">
-        <v>25499.66</v>
+        <v>25482.09</v>
       </c>
       <c r="N65" t="n">
-        <v>25575.83</v>
+        <v>25542.97</v>
       </c>
       <c r="O65" t="n">
-        <v>25711.36</v>
+        <v>25791</v>
       </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
@@ -5959,8 +5963,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U65" s="8" t="n">
-        <v/>
+      <c r="U65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V65" s="8" t="n">
         <v/>
@@ -5972,7 +5978,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -637,50 +637,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25025.13</v>
+        <v>25763.97</v>
       </c>
       <c r="C2" t="n">
-        <v>25655.82</v>
+        <v>25826.78</v>
       </c>
       <c r="D2" t="n">
-        <v>24994.64</v>
+        <v>25611.69</v>
       </c>
       <c r="E2" t="n">
-        <v>25580.88</v>
+        <v>25779.31</v>
       </c>
       <c r="F2" t="n">
-        <v>540.6</v>
+        <v>198.43</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0216</v>
+        <v>0.0078</v>
       </c>
       <c r="H2" t="n">
-        <v>661.1799999999999</v>
+        <v>215.09</v>
       </c>
       <c r="I2" t="n">
-        <v>24678.34</v>
+        <v>24333.46</v>
       </c>
       <c r="J2" t="n">
-        <v>24856.09</v>
+        <v>25047.53</v>
       </c>
       <c r="K2" t="n">
-        <v>24935.95</v>
+        <v>25250.29</v>
       </c>
       <c r="L2" t="n">
-        <v>25015.8</v>
+        <v>25453.06</v>
       </c>
       <c r="M2" t="n">
-        <v>25144.61</v>
+        <v>25911.47</v>
       </c>
       <c r="N2" t="n">
-        <v>25273.41</v>
+        <v>26369.89</v>
       </c>
       <c r="O2" t="n">
-        <v>25304.32</v>
+        <v>26317</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -698,18 +698,14 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -721,50 +717,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25763.97</v>
+        <v>25811.9</v>
       </c>
       <c r="C3" t="n">
-        <v>25826.78</v>
+        <v>25900.1</v>
       </c>
       <c r="D3" t="n">
-        <v>25611.69</v>
+        <v>25698.56</v>
       </c>
       <c r="E3" t="n">
-        <v>25779.31</v>
+        <v>25817.89</v>
       </c>
       <c r="F3" t="n">
-        <v>198.43</v>
+        <v>38.58</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0078</v>
+        <v>0.0015</v>
       </c>
       <c r="H3" t="n">
-        <v>215.09</v>
+        <v>201.54</v>
       </c>
       <c r="I3" t="n">
-        <v>24333.46</v>
+        <v>25396.6</v>
       </c>
       <c r="J3" t="n">
-        <v>25047.53</v>
+        <v>25594.26</v>
       </c>
       <c r="K3" t="n">
-        <v>25250.29</v>
+        <v>25671.77</v>
       </c>
       <c r="L3" t="n">
-        <v>25453.06</v>
+        <v>25749.27</v>
       </c>
       <c r="M3" t="n">
-        <v>25911.47</v>
+        <v>25886.86</v>
       </c>
       <c r="N3" t="n">
-        <v>26369.89</v>
+        <v>26024.44</v>
       </c>
       <c r="O3" t="n">
-        <v>26317</v>
+        <v>26041.87</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -777,12 +773,12 @@
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U3" s="8" t="n">
@@ -801,69 +797,73 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25811.9</v>
+        <v>25770.45</v>
       </c>
       <c r="C4" t="n">
-        <v>25900.1</v>
+        <v>25811.97</v>
       </c>
       <c r="D4" t="n">
-        <v>25698.56</v>
+        <v>25465.12</v>
       </c>
       <c r="E4" t="n">
-        <v>25817.89</v>
+        <v>25465.25</v>
       </c>
       <c r="F4" t="n">
-        <v>38.58</v>
+        <v>-352.64</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0137</v>
       </c>
       <c r="H4" t="n">
-        <v>201.54</v>
+        <v>346.85</v>
       </c>
       <c r="I4" t="n">
-        <v>25396.6</v>
+        <v>25497.02</v>
       </c>
       <c r="J4" t="n">
-        <v>25594.26</v>
+        <v>25625.63</v>
       </c>
       <c r="K4" t="n">
-        <v>25671.77</v>
+        <v>25717.12</v>
       </c>
       <c r="L4" t="n">
-        <v>25749.27</v>
+        <v>25808.61</v>
       </c>
       <c r="M4" t="n">
-        <v>25886.86</v>
+        <v>25918.66</v>
       </c>
       <c r="N4" t="n">
-        <v>26024.44</v>
+        <v>26028.71</v>
       </c>
       <c r="O4" t="n">
-        <v>26041.87</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>26101.64</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -871,9 +871,9 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -881,59 +881,59 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25770.45</v>
+        <v>25274.94</v>
       </c>
       <c r="C5" t="n">
-        <v>25811.97</v>
+        <v>25280.16</v>
       </c>
       <c r="D5" t="n">
-        <v>25465.12</v>
+        <v>24830.17</v>
       </c>
       <c r="E5" t="n">
-        <v>25465.25</v>
+        <v>24897.45</v>
       </c>
       <c r="F5" t="n">
-        <v>-352.64</v>
+        <v>-567.8</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0223</v>
       </c>
       <c r="H5" t="n">
-        <v>346.85</v>
+        <v>449.99</v>
       </c>
       <c r="I5" t="n">
-        <v>25497.02</v>
+        <v>25118.27</v>
       </c>
       <c r="J5" t="n">
-        <v>25625.63</v>
+        <v>25031.75</v>
       </c>
       <c r="K5" t="n">
-        <v>25717.12</v>
+        <v>25291.82</v>
       </c>
       <c r="L5" t="n">
-        <v>25808.61</v>
+        <v>25551.9</v>
       </c>
       <c r="M5" t="n">
-        <v>25918.66</v>
+        <v>25638.68</v>
       </c>
       <c r="N5" t="n">
-        <v>26028.71</v>
+        <v>25725.45</v>
       </c>
       <c r="O5" t="n">
-        <v>26101.64</v>
+        <v>26158.82</v>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
@@ -965,74 +965,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25274.94</v>
+        <v>25097.48</v>
       </c>
       <c r="C6" t="n">
-        <v>25280.16</v>
+        <v>25127.76</v>
       </c>
       <c r="D6" t="n">
-        <v>24830.17</v>
+        <v>24867.32</v>
       </c>
       <c r="E6" t="n">
-        <v>24897.45</v>
+        <v>25118.27</v>
       </c>
       <c r="F6" t="n">
-        <v>-567.8</v>
+        <v>220.82</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0089</v>
       </c>
       <c r="H6" t="n">
-        <v>449.99</v>
+        <v>260.44</v>
       </c>
       <c r="I6" t="n">
-        <v>25118.27</v>
+        <v>24380.18</v>
       </c>
       <c r="J6" t="n">
-        <v>25031.75</v>
+        <v>24368.6</v>
       </c>
       <c r="K6" t="n">
-        <v>25291.82</v>
+        <v>24672.45</v>
       </c>
       <c r="L6" t="n">
-        <v>25551.9</v>
+        <v>24976.31</v>
       </c>
       <c r="M6" t="n">
-        <v>25638.68</v>
+        <v>25122.44</v>
       </c>
       <c r="N6" t="n">
-        <v>25725.45</v>
+        <v>25268.58</v>
       </c>
       <c r="O6" t="n">
-        <v>26158.82</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
+        <v>25730.15</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1044,55 +1040,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25097.48</v>
+        <v>25081.19</v>
       </c>
       <c r="C7" t="n">
-        <v>25127.76</v>
+        <v>25195.83</v>
       </c>
       <c r="D7" t="n">
-        <v>24867.32</v>
+        <v>24937.52</v>
       </c>
       <c r="E7" t="n">
-        <v>25118.27</v>
+        <v>25067.09</v>
       </c>
       <c r="F7" t="n">
-        <v>220.82</v>
+        <v>-51.18</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.002</v>
       </c>
       <c r="H7" t="n">
-        <v>260.44</v>
+        <v>258.31</v>
       </c>
       <c r="I7" t="n">
-        <v>24380.18</v>
+        <v>24606.88</v>
       </c>
       <c r="J7" t="n">
-        <v>24368.6</v>
+        <v>24918.19</v>
       </c>
       <c r="K7" t="n">
-        <v>24672.45</v>
+        <v>24988.05</v>
       </c>
       <c r="L7" t="n">
-        <v>24976.31</v>
+        <v>25057.9</v>
       </c>
       <c r="M7" t="n">
-        <v>25122.44</v>
+        <v>25248.49</v>
       </c>
       <c r="N7" t="n">
-        <v>25268.58</v>
+        <v>25439.07</v>
       </c>
       <c r="O7" t="n">
-        <v>25730.15</v>
+        <v>25388.2</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1100,18 +1100,18 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1133,50 +1133,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25081.19</v>
+        <v>24963.8</v>
       </c>
       <c r="C8" t="n">
-        <v>25195.83</v>
+        <v>25154.58</v>
       </c>
       <c r="D8" t="n">
-        <v>24937.52</v>
+        <v>24963.8</v>
       </c>
       <c r="E8" t="n">
-        <v>25067.09</v>
+        <v>25114.25</v>
       </c>
       <c r="F8" t="n">
-        <v>-51.18</v>
+        <v>47.16</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="H8" t="n">
-        <v>258.31</v>
+        <v>190.78</v>
       </c>
       <c r="I8" t="n">
-        <v>24606.88</v>
+        <v>24679.21</v>
       </c>
       <c r="J8" t="n">
-        <v>24918.19</v>
+        <v>24808.99</v>
       </c>
       <c r="K8" t="n">
-        <v>24988.05</v>
+        <v>24937.93</v>
       </c>
       <c r="L8" t="n">
-        <v>25057.9</v>
+        <v>25066.88</v>
       </c>
       <c r="M8" t="n">
-        <v>25248.49</v>
+        <v>25196.25</v>
       </c>
       <c r="N8" t="n">
-        <v>25439.07</v>
+        <v>25325.61</v>
       </c>
       <c r="O8" t="n">
-        <v>25388.2</v>
+        <v>25454.14</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1184,10 +1184,8 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R8" s="6" t="n">
+        <v/>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
@@ -1217,59 +1215,63 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24963.8</v>
+        <v>24932.62</v>
       </c>
       <c r="C9" t="n">
-        <v>25154.58</v>
+        <v>25204.68</v>
       </c>
       <c r="D9" t="n">
-        <v>24963.8</v>
+        <v>24869.25</v>
       </c>
       <c r="E9" t="n">
-        <v>25114.25</v>
+        <v>25147.03</v>
       </c>
       <c r="F9" t="n">
-        <v>47.16</v>
+        <v>32.78</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0013</v>
       </c>
       <c r="H9" t="n">
-        <v>190.78</v>
+        <v>335.43</v>
       </c>
       <c r="I9" t="n">
-        <v>24679.21</v>
+        <v>24773.02</v>
       </c>
       <c r="J9" t="n">
-        <v>24808.99</v>
+        <v>24951</v>
       </c>
       <c r="K9" t="n">
-        <v>24937.93</v>
+        <v>25018.86</v>
       </c>
       <c r="L9" t="n">
-        <v>25066.88</v>
+        <v>25086.72</v>
       </c>
       <c r="M9" t="n">
-        <v>25196.25</v>
+        <v>25209.64</v>
       </c>
       <c r="N9" t="n">
-        <v>25325.61</v>
+        <v>25332.56</v>
       </c>
       <c r="O9" t="n">
-        <v>25454.14</v>
+        <v>25345.36</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
@@ -1299,50 +1301,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24932.62</v>
+        <v>24970.05</v>
       </c>
       <c r="C10" t="n">
-        <v>25204.68</v>
+        <v>25055.48</v>
       </c>
       <c r="D10" t="n">
-        <v>24869.25</v>
+        <v>24839.23</v>
       </c>
       <c r="E10" t="n">
-        <v>25147.03</v>
+        <v>24999.53</v>
       </c>
       <c r="F10" t="n">
-        <v>32.78</v>
+        <v>-147.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0059</v>
       </c>
       <c r="H10" t="n">
-        <v>335.43</v>
+        <v>216.25</v>
       </c>
       <c r="I10" t="n">
-        <v>24773.02</v>
+        <v>24533.82</v>
       </c>
       <c r="J10" t="n">
-        <v>24951</v>
+        <v>24866.63</v>
       </c>
       <c r="K10" t="n">
-        <v>25018.86</v>
+        <v>24979.31</v>
       </c>
       <c r="L10" t="n">
-        <v>25086.72</v>
+        <v>25092</v>
       </c>
       <c r="M10" t="n">
-        <v>25209.64</v>
+        <v>25314.74</v>
       </c>
       <c r="N10" t="n">
-        <v>25332.56</v>
+        <v>25537.49</v>
       </c>
       <c r="O10" t="n">
-        <v>25345.36</v>
+        <v>25540.11</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1354,12 +1356,12 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1376,59 +1378,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24970.05</v>
+        <v>25018.95</v>
       </c>
       <c r="C11" t="n">
-        <v>25055.48</v>
+        <v>25021.51</v>
       </c>
       <c r="D11" t="n">
-        <v>24839.23</v>
+        <v>24696.17</v>
       </c>
       <c r="E11" t="n">
-        <v>24999.53</v>
+        <v>24915.49</v>
       </c>
       <c r="F11" t="n">
-        <v>-147.5</v>
+        <v>-84.04000000000001</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0059</v>
+        <v>-0.0034</v>
       </c>
       <c r="H11" t="n">
-        <v>216.25</v>
+        <v>325.34</v>
       </c>
       <c r="I11" t="n">
-        <v>24533.82</v>
+        <v>24622.98</v>
       </c>
       <c r="J11" t="n">
-        <v>24866.63</v>
+        <v>24809.37</v>
       </c>
       <c r="K11" t="n">
-        <v>24979.31</v>
+        <v>24891.4</v>
       </c>
       <c r="L11" t="n">
-        <v>25092</v>
+        <v>24973.44</v>
       </c>
       <c r="M11" t="n">
-        <v>25314.74</v>
+        <v>25107.65</v>
       </c>
       <c r="N11" t="n">
-        <v>25537.49</v>
+        <v>25241.87</v>
       </c>
       <c r="O11" t="n">
-        <v>25540.11</v>
+        <v>25271.73</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1467,67 +1465,65 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25018.95</v>
+        <v>24755.09</v>
       </c>
       <c r="C12" t="n">
-        <v>25021.51</v>
+        <v>24850.75</v>
       </c>
       <c r="D12" t="n">
-        <v>24696.17</v>
+        <v>24651.34</v>
       </c>
       <c r="E12" t="n">
-        <v>24915.49</v>
+        <v>24830.98</v>
       </c>
       <c r="F12" t="n">
-        <v>-84.04000000000001</v>
+        <v>-84.51000000000001</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>-0.0034</v>
       </c>
       <c r="H12" t="n">
-        <v>325.34</v>
+        <v>199.41</v>
       </c>
       <c r="I12" t="n">
-        <v>24622.98</v>
+        <v>24370.83</v>
       </c>
       <c r="J12" t="n">
-        <v>24809.37</v>
+        <v>24618.48</v>
       </c>
       <c r="K12" t="n">
-        <v>24891.4</v>
+        <v>24752.82</v>
       </c>
       <c r="L12" t="n">
-        <v>24973.44</v>
+        <v>24887.17</v>
       </c>
       <c r="M12" t="n">
-        <v>25107.65</v>
+        <v>25078.16</v>
       </c>
       <c r="N12" t="n">
-        <v>25241.87</v>
+        <v>25269.16</v>
       </c>
       <c r="O12" t="n">
-        <v>25271.73</v>
+        <v>25346.85</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q12" s="6" t="n">
+        <v/>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1549,50 +1545,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24755.09</v>
+        <v>24769.15</v>
       </c>
       <c r="C13" t="n">
-        <v>24850.75</v>
+        <v>24974.53</v>
       </c>
       <c r="D13" t="n">
-        <v>24651.34</v>
+        <v>24751.13</v>
       </c>
       <c r="E13" t="n">
-        <v>24830.98</v>
+        <v>24846.69</v>
       </c>
       <c r="F13" t="n">
-        <v>-84.51000000000001</v>
+        <v>15.71</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>199.41</v>
+        <v>223.4</v>
       </c>
       <c r="I13" t="n">
-        <v>24370.83</v>
+        <v>24451.93</v>
       </c>
       <c r="J13" t="n">
-        <v>24618.48</v>
+        <v>24671.54</v>
       </c>
       <c r="K13" t="n">
-        <v>24752.82</v>
+        <v>24731.28</v>
       </c>
       <c r="L13" t="n">
-        <v>24887.17</v>
+        <v>24791.01</v>
       </c>
       <c r="M13" t="n">
-        <v>25078.16</v>
+        <v>24930.69</v>
       </c>
       <c r="N13" t="n">
-        <v>25269.16</v>
+        <v>25070.36</v>
       </c>
       <c r="O13" t="n">
-        <v>25346.85</v>
+        <v>25050.16</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1600,18 +1596,18 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1624,55 +1620,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24769.15</v>
+        <v>24922.1</v>
       </c>
       <c r="C14" t="n">
-        <v>24974.53</v>
+        <v>25011.35</v>
       </c>
       <c r="D14" t="n">
-        <v>24751.13</v>
+        <v>24817.34</v>
       </c>
       <c r="E14" t="n">
-        <v>24846.69</v>
+        <v>25011.35</v>
       </c>
       <c r="F14" t="n">
-        <v>15.71</v>
+        <v>164.66</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0066</v>
       </c>
       <c r="H14" t="n">
-        <v>223.4</v>
+        <v>194.01</v>
       </c>
       <c r="I14" t="n">
-        <v>24451.93</v>
+        <v>24527.73</v>
       </c>
       <c r="J14" t="n">
-        <v>24671.54</v>
+        <v>24615.22</v>
       </c>
       <c r="K14" t="n">
-        <v>24731.28</v>
+        <v>24734.99</v>
       </c>
       <c r="L14" t="n">
-        <v>24791.01</v>
+        <v>24854.76</v>
       </c>
       <c r="M14" t="n">
-        <v>24930.69</v>
+        <v>24958.39</v>
       </c>
       <c r="N14" t="n">
-        <v>25070.36</v>
+        <v>25062.02</v>
       </c>
       <c r="O14" t="n">
-        <v>25050.16</v>
+        <v>25197.93</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
@@ -1693,8 +1693,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1713,50 +1715,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24922.1</v>
+        <v>25001.31</v>
       </c>
       <c r="C15" t="n">
-        <v>25011.35</v>
+        <v>25271.34</v>
       </c>
       <c r="D15" t="n">
-        <v>24817.34</v>
+        <v>24984.27</v>
       </c>
       <c r="E15" t="n">
-        <v>25011.35</v>
+        <v>25155.41</v>
       </c>
       <c r="F15" t="n">
-        <v>164.66</v>
+        <v>144.06</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0058</v>
       </c>
       <c r="H15" t="n">
-        <v>194.01</v>
+        <v>287.07</v>
       </c>
       <c r="I15" t="n">
-        <v>24527.73</v>
+        <v>24623.33</v>
       </c>
       <c r="J15" t="n">
-        <v>24615.22</v>
+        <v>24865.84</v>
       </c>
       <c r="K15" t="n">
-        <v>24734.99</v>
+        <v>24914.34</v>
       </c>
       <c r="L15" t="n">
-        <v>24854.76</v>
+        <v>24962.85</v>
       </c>
       <c r="M15" t="n">
-        <v>24958.39</v>
+        <v>25108.35</v>
       </c>
       <c r="N15" t="n">
-        <v>25062.02</v>
+        <v>25253.86</v>
       </c>
       <c r="O15" t="n">
-        <v>25197.93</v>
+        <v>25205.36</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1774,16 +1776,18 @@
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U15" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W15" s="11" t="inlineStr">
         <is>
@@ -1799,171 +1803,165 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25001.31</v>
+        <v>24994.05</v>
       </c>
       <c r="C16" t="n">
-        <v>25271.34</v>
+        <v>25074.28</v>
       </c>
       <c r="D16" t="n">
-        <v>24984.27</v>
+        <v>24696.59</v>
       </c>
       <c r="E16" t="n">
-        <v>25155.41</v>
+        <v>24763.12</v>
       </c>
       <c r="F16" t="n">
-        <v>144.06</v>
+        <v>-392.29</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0156</v>
       </c>
       <c r="H16" t="n">
-        <v>287.07</v>
+        <v>377.69</v>
       </c>
       <c r="I16" t="n">
-        <v>24623.33</v>
+        <v>24697.2</v>
       </c>
       <c r="J16" t="n">
-        <v>24865.84</v>
+        <v>24882.14</v>
       </c>
       <c r="K16" t="n">
-        <v>24914.34</v>
+        <v>25011.88</v>
       </c>
       <c r="L16" t="n">
-        <v>24962.85</v>
+        <v>25141.61</v>
       </c>
       <c r="M16" t="n">
-        <v>25108.35</v>
+        <v>25298.95</v>
       </c>
       <c r="N16" t="n">
-        <v>25253.86</v>
+        <v>25456.28</v>
       </c>
       <c r="O16" t="n">
-        <v>25205.36</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
+        <v>25558.41</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
       </c>
       <c r="W16" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24994.05</v>
+        <v>24830.41</v>
       </c>
       <c r="C17" t="n">
-        <v>25074.28</v>
+        <v>25099.68</v>
       </c>
       <c r="D17" t="n">
-        <v>24696.59</v>
+        <v>24821.67</v>
       </c>
       <c r="E17" t="n">
-        <v>24763.12</v>
+        <v>25099</v>
       </c>
       <c r="F17" t="n">
-        <v>-392.29</v>
+        <v>335.88</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0136</v>
       </c>
       <c r="H17" t="n">
-        <v>377.69</v>
+        <v>278.01</v>
       </c>
       <c r="I17" t="n">
-        <v>24697.2</v>
+        <v>24318.9</v>
       </c>
       <c r="J17" t="n">
-        <v>24882.14</v>
+        <v>24324.27</v>
       </c>
       <c r="K17" t="n">
-        <v>25011.88</v>
+        <v>24574.27</v>
       </c>
       <c r="L17" t="n">
-        <v>25141.61</v>
+        <v>24824.28</v>
       </c>
       <c r="M17" t="n">
-        <v>25298.95</v>
+        <v>24951.96</v>
       </c>
       <c r="N17" t="n">
-        <v>25456.28</v>
+        <v>25079.65</v>
       </c>
       <c r="O17" t="n">
-        <v>25558.41</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
+        <v>25451.97</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -1971,50 +1969,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24830.41</v>
+        <v>25459.32</v>
       </c>
       <c r="C18" t="n">
-        <v>25099.68</v>
+        <v>25560.4</v>
       </c>
       <c r="D18" t="n">
-        <v>24821.67</v>
+        <v>25361.03</v>
       </c>
       <c r="E18" t="n">
-        <v>25099</v>
+        <v>25361.03</v>
       </c>
       <c r="F18" t="n">
-        <v>335.88</v>
+        <v>262.03</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0104</v>
       </c>
       <c r="H18" t="n">
-        <v>278.01</v>
+        <v>199.37</v>
       </c>
       <c r="I18" t="n">
-        <v>24318.9</v>
+        <v>24543.66</v>
       </c>
       <c r="J18" t="n">
-        <v>24324.27</v>
+        <v>24890.15</v>
       </c>
       <c r="K18" t="n">
-        <v>24574.27</v>
+        <v>24960</v>
       </c>
       <c r="L18" t="n">
-        <v>24824.28</v>
+        <v>25029.84</v>
       </c>
       <c r="M18" t="n">
-        <v>24951.96</v>
+        <v>25238</v>
       </c>
       <c r="N18" t="n">
-        <v>25079.65</v>
+        <v>25446.17</v>
       </c>
       <c r="O18" t="n">
-        <v>25451.97</v>
+        <v>25377.69</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2037,11 +2035,13 @@
       </c>
       <c r="U18" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
@@ -2053,50 +2053,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25459.32</v>
+        <v>25496.13</v>
       </c>
       <c r="C19" t="n">
-        <v>25560.4</v>
+        <v>25553.47</v>
       </c>
       <c r="D19" t="n">
-        <v>25361.03</v>
+        <v>25307.17</v>
       </c>
       <c r="E19" t="n">
-        <v>25361.03</v>
+        <v>25464.01</v>
       </c>
       <c r="F19" t="n">
-        <v>262.03</v>
+        <v>102.98</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0104</v>
+        <v>0.0041</v>
       </c>
       <c r="H19" t="n">
-        <v>199.37</v>
+        <v>246.3</v>
       </c>
       <c r="I19" t="n">
-        <v>24543.66</v>
+        <v>25161.66</v>
       </c>
       <c r="J19" t="n">
-        <v>24890.15</v>
+        <v>25111.82</v>
       </c>
       <c r="K19" t="n">
-        <v>24960</v>
+        <v>25261.34</v>
       </c>
       <c r="L19" t="n">
-        <v>25029.84</v>
+        <v>25410.87</v>
       </c>
       <c r="M19" t="n">
-        <v>25238</v>
+        <v>25460.71</v>
       </c>
       <c r="N19" t="n">
-        <v>25446.17</v>
+        <v>25510.56</v>
       </c>
       <c r="O19" t="n">
-        <v>25377.69</v>
+        <v>25759.77</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U19" s="8" t="inlineStr">
@@ -2122,65 +2122,67 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25496.13</v>
+        <v>25551.97</v>
       </c>
       <c r="C20" t="n">
-        <v>25553.47</v>
+        <v>25571.45</v>
       </c>
       <c r="D20" t="n">
-        <v>25307.17</v>
+        <v>25336.39</v>
       </c>
       <c r="E20" t="n">
-        <v>25464.01</v>
+        <v>25460.48</v>
       </c>
       <c r="F20" t="n">
-        <v>102.98</v>
+        <v>-3.53</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0001</v>
       </c>
       <c r="H20" t="n">
-        <v>246.3</v>
+        <v>235.06</v>
       </c>
       <c r="I20" t="n">
-        <v>25161.66</v>
+        <v>25060.87</v>
       </c>
       <c r="J20" t="n">
-        <v>25111.82</v>
+        <v>25234.55</v>
       </c>
       <c r="K20" t="n">
-        <v>25261.34</v>
+        <v>25340.86</v>
       </c>
       <c r="L20" t="n">
-        <v>25410.87</v>
+        <v>25447.17</v>
       </c>
       <c r="M20" t="n">
-        <v>25460.71</v>
+        <v>25587.16</v>
       </c>
       <c r="N20" t="n">
-        <v>25510.56</v>
+        <v>25727.16</v>
       </c>
       <c r="O20" t="n">
-        <v>25759.77</v>
+        <v>25799.77</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2188,23 +2190,21 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2216,57 +2216,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25551.97</v>
+        <v>25487.45</v>
       </c>
       <c r="C21" t="n">
-        <v>25571.45</v>
+        <v>25651.16</v>
       </c>
       <c r="D21" t="n">
-        <v>25336.39</v>
+        <v>25303.11</v>
       </c>
       <c r="E21" t="n">
-        <v>25460.48</v>
+        <v>25612.03</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.53</v>
+        <v>151.55</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.006</v>
       </c>
       <c r="H21" t="n">
-        <v>235.06</v>
+        <v>348.05</v>
       </c>
       <c r="I21" t="n">
-        <v>25060.87</v>
+        <v>25101.33</v>
       </c>
       <c r="J21" t="n">
-        <v>25234.55</v>
+        <v>25228.7</v>
       </c>
       <c r="K21" t="n">
-        <v>25340.86</v>
+        <v>25342.95</v>
       </c>
       <c r="L21" t="n">
-        <v>25447.17</v>
+        <v>25457.2</v>
       </c>
       <c r="M21" t="n">
-        <v>25587.16</v>
+        <v>25578.01</v>
       </c>
       <c r="N21" t="n">
-        <v>25727.16</v>
+        <v>25698.82</v>
       </c>
       <c r="O21" t="n">
-        <v>25799.77</v>
+        <v>25806.51</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2281,11 +2281,13 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2307,50 +2309,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25487.45</v>
+        <v>25709.37</v>
       </c>
       <c r="C22" t="n">
-        <v>25651.16</v>
+        <v>25891.51</v>
       </c>
       <c r="D22" t="n">
-        <v>25303.11</v>
+        <v>25549.53</v>
       </c>
       <c r="E22" t="n">
-        <v>25612.03</v>
+        <v>25629.24</v>
       </c>
       <c r="F22" t="n">
-        <v>151.55</v>
+        <v>17.21</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0007</v>
       </c>
       <c r="H22" t="n">
-        <v>348.05</v>
+        <v>341.98</v>
       </c>
       <c r="I22" t="n">
-        <v>25101.33</v>
+        <v>24955.06</v>
       </c>
       <c r="J22" t="n">
-        <v>25228.7</v>
+        <v>25331.43</v>
       </c>
       <c r="K22" t="n">
-        <v>25342.95</v>
+        <v>25438</v>
       </c>
       <c r="L22" t="n">
-        <v>25457.2</v>
+        <v>25544.58</v>
       </c>
       <c r="M22" t="n">
-        <v>25578.01</v>
+        <v>25786.05</v>
       </c>
       <c r="N22" t="n">
-        <v>25698.82</v>
+        <v>26027.53</v>
       </c>
       <c r="O22" t="n">
-        <v>25806.51</v>
+        <v>25999.21</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2358,19 +2360,17 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U22" s="8" t="n">
@@ -2384,59 +2384,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25709.37</v>
+        <v>25855.12</v>
       </c>
       <c r="C23" t="n">
-        <v>25891.51</v>
+        <v>26096.93</v>
       </c>
       <c r="D23" t="n">
-        <v>25549.53</v>
+        <v>25855.12</v>
       </c>
       <c r="E23" t="n">
-        <v>25629.24</v>
+        <v>26001.31</v>
       </c>
       <c r="F23" t="n">
-        <v>17.21</v>
+        <v>372.07</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0145</v>
       </c>
       <c r="H23" t="n">
-        <v>341.98</v>
+        <v>241.81</v>
       </c>
       <c r="I23" t="n">
-        <v>24955.06</v>
+        <v>25207.55</v>
       </c>
       <c r="J23" t="n">
-        <v>25331.43</v>
+        <v>25241.62</v>
       </c>
       <c r="K23" t="n">
-        <v>25438</v>
+        <v>25458.25</v>
       </c>
       <c r="L23" t="n">
-        <v>25544.58</v>
+        <v>25674.88</v>
       </c>
       <c r="M23" t="n">
-        <v>25786.05</v>
+        <v>25800.23</v>
       </c>
       <c r="N23" t="n">
-        <v>26027.53</v>
+        <v>25925.58</v>
       </c>
       <c r="O23" t="n">
-        <v>25999.21</v>
+        <v>26233.49</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2449,7 +2445,7 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
@@ -2457,8 +2453,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2473,50 +2471,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25855.12</v>
+        <v>26189.62</v>
       </c>
       <c r="C24" t="n">
-        <v>26096.93</v>
+        <v>26266.5</v>
       </c>
       <c r="D24" t="n">
-        <v>25855.12</v>
+        <v>26082.43</v>
       </c>
       <c r="E24" t="n">
-        <v>26001.31</v>
+        <v>26202.35</v>
       </c>
       <c r="F24" t="n">
-        <v>372.07</v>
+        <v>201.04</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0077</v>
       </c>
       <c r="H24" t="n">
-        <v>241.81</v>
+        <v>184.07</v>
       </c>
       <c r="I24" t="n">
-        <v>25207.55</v>
+        <v>25613.31</v>
       </c>
       <c r="J24" t="n">
-        <v>25241.62</v>
+        <v>25772.14</v>
       </c>
       <c r="K24" t="n">
-        <v>25458.25</v>
+        <v>25880.41</v>
       </c>
       <c r="L24" t="n">
-        <v>25674.88</v>
+        <v>25988.67</v>
       </c>
       <c r="M24" t="n">
-        <v>25800.23</v>
+        <v>26122.22</v>
       </c>
       <c r="N24" t="n">
-        <v>25925.58</v>
+        <v>26255.76</v>
       </c>
       <c r="O24" t="n">
-        <v>26233.49</v>
+        <v>26338.74</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2555,50 +2553,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26189.62</v>
+        <v>26393.43</v>
       </c>
       <c r="C25" t="n">
-        <v>26266.5</v>
+        <v>26403.81</v>
       </c>
       <c r="D25" t="n">
-        <v>26082.43</v>
+        <v>26123.18</v>
       </c>
       <c r="E25" t="n">
-        <v>26202.35</v>
+        <v>26126.3</v>
       </c>
       <c r="F25" t="n">
-        <v>201.04</v>
+        <v>-76.05</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0029</v>
       </c>
       <c r="H25" t="n">
-        <v>184.07</v>
+        <v>280.63</v>
       </c>
       <c r="I25" t="n">
-        <v>25613.31</v>
+        <v>25898.36</v>
       </c>
       <c r="J25" t="n">
-        <v>25772.14</v>
+        <v>26032.22</v>
       </c>
       <c r="K25" t="n">
-        <v>25880.41</v>
+        <v>26110.31</v>
       </c>
       <c r="L25" t="n">
-        <v>25988.67</v>
+        <v>26188.41</v>
       </c>
       <c r="M25" t="n">
-        <v>26122.22</v>
+        <v>26294.38</v>
       </c>
       <c r="N25" t="n">
-        <v>26255.76</v>
+        <v>26400.36</v>
       </c>
       <c r="O25" t="n">
-        <v>26338.74</v>
+        <v>26450.57</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2606,12 +2604,14 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="U25" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V25" s="8" t="n">
@@ -2632,55 +2632,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>26393.43</v>
+        <v>26116.27</v>
       </c>
       <c r="C26" t="n">
-        <v>26403.81</v>
+        <v>26229.33</v>
       </c>
       <c r="D26" t="n">
-        <v>26123.18</v>
+        <v>26081.69</v>
       </c>
       <c r="E26" t="n">
-        <v>26126.3</v>
+        <v>26140.13</v>
       </c>
       <c r="F26" t="n">
-        <v>-76.05</v>
+        <v>13.83</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0005</v>
       </c>
       <c r="H26" t="n">
-        <v>280.63</v>
+        <v>147.64</v>
       </c>
       <c r="I26" t="n">
-        <v>25898.36</v>
+        <v>25842.55</v>
       </c>
       <c r="J26" t="n">
-        <v>26032.22</v>
+        <v>25777.07</v>
       </c>
       <c r="K26" t="n">
-        <v>26110.31</v>
+        <v>25985.99</v>
       </c>
       <c r="L26" t="n">
-        <v>26188.41</v>
+        <v>26194.9</v>
       </c>
       <c r="M26" t="n">
-        <v>26294.38</v>
+        <v>26266.62</v>
       </c>
       <c r="N26" t="n">
-        <v>26400.36</v>
+        <v>26338.33</v>
       </c>
       <c r="O26" t="n">
-        <v>26450.57</v>
+        <v>26684.44</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2688,25 +2692,19 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2718,57 +2716,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26116.27</v>
+        <v>26235.8</v>
       </c>
       <c r="C27" t="n">
-        <v>26229.33</v>
+        <v>26445.18</v>
       </c>
       <c r="D27" t="n">
-        <v>26081.69</v>
+        <v>26223.64</v>
       </c>
       <c r="E27" t="n">
-        <v>26140.13</v>
+        <v>26319.45</v>
       </c>
       <c r="F27" t="n">
-        <v>13.83</v>
+        <v>179.32</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0069</v>
       </c>
       <c r="H27" t="n">
-        <v>147.64</v>
+        <v>221.54</v>
       </c>
       <c r="I27" t="n">
-        <v>25842.55</v>
+        <v>25934.05</v>
       </c>
       <c r="J27" t="n">
-        <v>25777.07</v>
+        <v>25984.8</v>
       </c>
       <c r="K27" t="n">
-        <v>25985.99</v>
+        <v>26066.31</v>
       </c>
       <c r="L27" t="n">
-        <v>26194.9</v>
+        <v>26147.82</v>
       </c>
       <c r="M27" t="n">
-        <v>26266.62</v>
+        <v>26213.95</v>
       </c>
       <c r="N27" t="n">
-        <v>26338.33</v>
+        <v>26280.08</v>
       </c>
       <c r="O27" t="n">
-        <v>26684.44</v>
+        <v>26376.97</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2779,78 +2777,80 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26235.8</v>
+        <v>26360.44</v>
       </c>
       <c r="C28" t="n">
-        <v>26445.18</v>
+        <v>26441.91</v>
       </c>
       <c r="D28" t="n">
-        <v>26223.64</v>
+        <v>26302.19</v>
       </c>
       <c r="E28" t="n">
-        <v>26319.45</v>
+        <v>26323.88</v>
       </c>
       <c r="F28" t="n">
-        <v>179.32</v>
+        <v>4.43</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0002</v>
       </c>
       <c r="H28" t="n">
-        <v>221.54</v>
+        <v>139.72</v>
       </c>
       <c r="I28" t="n">
-        <v>25934.05</v>
+        <v>26002.1</v>
       </c>
       <c r="J28" t="n">
-        <v>25984.8</v>
+        <v>26090.43</v>
       </c>
       <c r="K28" t="n">
-        <v>26066.31</v>
+        <v>26208.68</v>
       </c>
       <c r="L28" t="n">
-        <v>26147.82</v>
+        <v>26326.93</v>
       </c>
       <c r="M28" t="n">
-        <v>26213.95</v>
+        <v>26430.22</v>
       </c>
       <c r="N28" t="n">
-        <v>26280.08</v>
+        <v>26533.51</v>
       </c>
       <c r="O28" t="n">
-        <v>26376.97</v>
+        <v>26666.72</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2861,9 +2861,9 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
@@ -2871,70 +2871,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>26360.44</v>
+        <v>26378</v>
       </c>
       <c r="C29" t="n">
-        <v>26441.91</v>
+        <v>26504.54</v>
       </c>
       <c r="D29" t="n">
-        <v>26302.19</v>
+        <v>26245.57</v>
       </c>
       <c r="E29" t="n">
-        <v>26323.88</v>
+        <v>26391.42</v>
       </c>
       <c r="F29" t="n">
-        <v>4.43</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0026</v>
       </c>
       <c r="H29" t="n">
-        <v>139.72</v>
+        <v>258.97</v>
       </c>
       <c r="I29" t="n">
-        <v>26002.1</v>
+        <v>26162.47</v>
       </c>
       <c r="J29" t="n">
-        <v>26090.43</v>
+        <v>26160.08</v>
       </c>
       <c r="K29" t="n">
-        <v>26208.68</v>
+        <v>26254.02</v>
       </c>
       <c r="L29" t="n">
-        <v>26326.93</v>
+        <v>26347.97</v>
       </c>
       <c r="M29" t="n">
-        <v>26430.22</v>
+        <v>26393.74</v>
       </c>
       <c r="N29" t="n">
-        <v>26533.51</v>
+        <v>26439.52</v>
       </c>
       <c r="O29" t="n">
-        <v>26666.72</v>
+        <v>26581.63</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2942,21 +2942,25 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2975,50 +2979,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26378</v>
+        <v>26452</v>
       </c>
       <c r="C30" t="n">
-        <v>26504.54</v>
+        <v>26573.5</v>
       </c>
       <c r="D30" t="n">
-        <v>26245.57</v>
+        <v>26313.58</v>
       </c>
       <c r="E30" t="n">
-        <v>26391.42</v>
+        <v>26331.07</v>
       </c>
       <c r="F30" t="n">
-        <v>67.54000000000001</v>
+        <v>-60.35</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0023</v>
       </c>
       <c r="H30" t="n">
-        <v>258.97</v>
+        <v>259.92</v>
       </c>
       <c r="I30" t="n">
-        <v>26162.47</v>
+        <v>25986.6</v>
       </c>
       <c r="J30" t="n">
-        <v>26160.08</v>
+        <v>26140.63</v>
       </c>
       <c r="K30" t="n">
-        <v>26254.02</v>
+        <v>26261.94</v>
       </c>
       <c r="L30" t="n">
-        <v>26347.97</v>
+        <v>26383.24</v>
       </c>
       <c r="M30" t="n">
-        <v>26393.74</v>
+        <v>26520.9</v>
       </c>
       <c r="N30" t="n">
-        <v>26439.52</v>
+        <v>26658.57</v>
       </c>
       <c r="O30" t="n">
-        <v>26581.63</v>
+        <v>26763.51</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3026,25 +3030,21 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3063,50 +3063,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>26452</v>
+        <v>26437.35</v>
       </c>
       <c r="C31" t="n">
-        <v>26573.5</v>
+        <v>26489.78</v>
       </c>
       <c r="D31" t="n">
-        <v>26313.58</v>
+        <v>26285.23</v>
       </c>
       <c r="E31" t="n">
-        <v>26331.07</v>
+        <v>26299.74</v>
       </c>
       <c r="F31" t="n">
-        <v>-60.35</v>
+        <v>-31.33</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0012</v>
       </c>
       <c r="H31" t="n">
-        <v>259.92</v>
+        <v>204.55</v>
       </c>
       <c r="I31" t="n">
-        <v>25986.6</v>
+        <v>26053.66</v>
       </c>
       <c r="J31" t="n">
-        <v>26140.63</v>
+        <v>26014.92</v>
       </c>
       <c r="K31" t="n">
-        <v>26261.94</v>
+        <v>26201.11</v>
       </c>
       <c r="L31" t="n">
-        <v>26383.24</v>
+        <v>26387.31</v>
       </c>
       <c r="M31" t="n">
-        <v>26520.9</v>
+        <v>26461.03</v>
       </c>
       <c r="N31" t="n">
-        <v>26658.57</v>
+        <v>26534.76</v>
       </c>
       <c r="O31" t="n">
-        <v>26763.51</v>
+        <v>26833.42</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3140,57 +3140,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26437.35</v>
+        <v>26445.99</v>
       </c>
       <c r="C32" t="n">
-        <v>26489.78</v>
+        <v>26541.34</v>
       </c>
       <c r="D32" t="n">
-        <v>26285.23</v>
+        <v>26404.95</v>
       </c>
       <c r="E32" t="n">
-        <v>26299.74</v>
+        <v>26440.31</v>
       </c>
       <c r="F32" t="n">
-        <v>-31.33</v>
+        <v>140.57</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0053</v>
       </c>
       <c r="H32" t="n">
-        <v>204.55</v>
+        <v>136.39</v>
       </c>
       <c r="I32" t="n">
-        <v>26053.66</v>
+        <v>26080.68</v>
       </c>
       <c r="J32" t="n">
-        <v>26014.92</v>
+        <v>26051.31</v>
       </c>
       <c r="K32" t="n">
-        <v>26201.11</v>
+        <v>26197.47</v>
       </c>
       <c r="L32" t="n">
-        <v>26387.31</v>
+        <v>26343.62</v>
       </c>
       <c r="M32" t="n">
-        <v>26461.03</v>
+        <v>26402.01</v>
       </c>
       <c r="N32" t="n">
-        <v>26534.76</v>
+        <v>26460.41</v>
       </c>
       <c r="O32" t="n">
-        <v>26833.42</v>
+        <v>26694.33</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3201,9 +3201,9 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
@@ -3211,8 +3211,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3222,59 +3224,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>26445.99</v>
+        <v>26490.3</v>
       </c>
       <c r="C33" t="n">
-        <v>26541.34</v>
+        <v>26493.5</v>
       </c>
       <c r="D33" t="n">
-        <v>26404.95</v>
+        <v>26338.61</v>
       </c>
       <c r="E33" t="n">
-        <v>26440.31</v>
+        <v>26338.61</v>
       </c>
       <c r="F33" t="n">
-        <v>140.57</v>
+        <v>-101.7</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0038</v>
       </c>
       <c r="H33" t="n">
-        <v>136.39</v>
+        <v>154.89</v>
       </c>
       <c r="I33" t="n">
-        <v>26080.68</v>
+        <v>26268.56</v>
       </c>
       <c r="J33" t="n">
-        <v>26051.31</v>
+        <v>26287.5</v>
       </c>
       <c r="K33" t="n">
-        <v>26197.47</v>
+        <v>26372.12</v>
       </c>
       <c r="L33" t="n">
-        <v>26343.62</v>
+        <v>26456.73</v>
       </c>
       <c r="M33" t="n">
-        <v>26402.01</v>
+        <v>26508.51</v>
       </c>
       <c r="N33" t="n">
-        <v>26460.41</v>
+        <v>26560.28</v>
       </c>
       <c r="O33" t="n">
-        <v>26694.33</v>
+        <v>26677.73</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3282,24 +3280,22 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
+      <c r="R33" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
@@ -3308,65 +3304,73 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26490.3</v>
+        <v>26280.86</v>
       </c>
       <c r="C34" t="n">
-        <v>26493.5</v>
+        <v>26292.95</v>
       </c>
       <c r="D34" t="n">
-        <v>26338.61</v>
+        <v>26119.54</v>
       </c>
       <c r="E34" t="n">
-        <v>26338.61</v>
+        <v>26128.36</v>
       </c>
       <c r="F34" t="n">
-        <v>-101.7</v>
+        <v>-210.25</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.008</v>
       </c>
       <c r="H34" t="n">
-        <v>154.89</v>
+        <v>173.41</v>
       </c>
       <c r="I34" t="n">
-        <v>26268.56</v>
+        <v>26183.72</v>
       </c>
       <c r="J34" t="n">
-        <v>26287.5</v>
+        <v>26145</v>
       </c>
       <c r="K34" t="n">
-        <v>26372.12</v>
+        <v>26261.16</v>
       </c>
       <c r="L34" t="n">
-        <v>26456.73</v>
+        <v>26377.33</v>
       </c>
       <c r="M34" t="n">
-        <v>26508.51</v>
+        <v>26416.05</v>
       </c>
       <c r="N34" t="n">
-        <v>26560.28</v>
+        <v>26454.78</v>
       </c>
       <c r="O34" t="n">
-        <v>26677.73</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
+        <v>26648.39</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
@@ -3383,78 +3387,70 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W34" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>26280.86</v>
+        <v>26146.12</v>
       </c>
       <c r="C35" t="n">
-        <v>26292.95</v>
+        <v>26187.82</v>
       </c>
       <c r="D35" t="n">
-        <v>26119.54</v>
+        <v>26063.37</v>
       </c>
       <c r="E35" t="n">
-        <v>26128.36</v>
+        <v>26091.33</v>
       </c>
       <c r="F35" t="n">
-        <v>-210.25</v>
+        <v>-37.03</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0014</v>
       </c>
       <c r="H35" t="n">
-        <v>173.41</v>
+        <v>124.45</v>
       </c>
       <c r="I35" t="n">
-        <v>26183.72</v>
+        <v>25946.13</v>
       </c>
       <c r="J35" t="n">
-        <v>26145</v>
+        <v>25916.01</v>
       </c>
       <c r="K35" t="n">
-        <v>26261.16</v>
+        <v>26041.65</v>
       </c>
       <c r="L35" t="n">
-        <v>26377.33</v>
+        <v>26167.3</v>
       </c>
       <c r="M35" t="n">
-        <v>26416.05</v>
+        <v>26215.06</v>
       </c>
       <c r="N35" t="n">
-        <v>26454.78</v>
+        <v>26262.83</v>
       </c>
       <c r="O35" t="n">
-        <v>26648.39</v>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
+        <v>26466.36</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
@@ -3481,60 +3477,64 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26146.12</v>
+        <v>26050.95</v>
       </c>
       <c r="C36" t="n">
-        <v>26187.82</v>
+        <v>26062.15</v>
       </c>
       <c r="D36" t="n">
-        <v>26063.37</v>
+        <v>25914.11</v>
       </c>
       <c r="E36" t="n">
-        <v>26091.33</v>
+        <v>25983.04</v>
       </c>
       <c r="F36" t="n">
-        <v>-37.03</v>
+        <v>-108.29</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0042</v>
       </c>
       <c r="H36" t="n">
-        <v>124.45</v>
+        <v>148.04</v>
       </c>
       <c r="I36" t="n">
-        <v>25946.13</v>
+        <v>25938.92</v>
       </c>
       <c r="J36" t="n">
-        <v>25916.01</v>
+        <v>25949.75</v>
       </c>
       <c r="K36" t="n">
-        <v>26041.65</v>
+        <v>26029.1</v>
       </c>
       <c r="L36" t="n">
-        <v>26167.3</v>
+        <v>26108.46</v>
       </c>
       <c r="M36" t="n">
-        <v>26215.06</v>
+        <v>26153.56</v>
       </c>
       <c r="N36" t="n">
-        <v>26262.83</v>
+        <v>26198.65</v>
       </c>
       <c r="O36" t="n">
-        <v>26466.36</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
+        <v>26312.27</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
@@ -3561,83 +3561,81 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26050.95</v>
+        <v>25998.95</v>
       </c>
       <c r="C37" t="n">
-        <v>26062.15</v>
+        <v>26166.25</v>
       </c>
       <c r="D37" t="n">
-        <v>25914.11</v>
+        <v>25969.52</v>
       </c>
       <c r="E37" t="n">
-        <v>25983.04</v>
+        <v>26136.56</v>
       </c>
       <c r="F37" t="n">
-        <v>-108.29</v>
+        <v>153.52</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.0059</v>
       </c>
       <c r="H37" t="n">
-        <v>148.04</v>
+        <v>196.73</v>
       </c>
       <c r="I37" t="n">
-        <v>25938.92</v>
+        <v>25766.07</v>
       </c>
       <c r="J37" t="n">
-        <v>25949.75</v>
+        <v>25832.45</v>
       </c>
       <c r="K37" t="n">
-        <v>26029.1</v>
+        <v>25909.02</v>
       </c>
       <c r="L37" t="n">
-        <v>26108.46</v>
+        <v>25985.58</v>
       </c>
       <c r="M37" t="n">
-        <v>26153.56</v>
+        <v>26057.06</v>
       </c>
       <c r="N37" t="n">
-        <v>26198.65</v>
+        <v>26128.53</v>
       </c>
       <c r="O37" t="n">
-        <v>26312.27</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
+        <v>26210.19</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W37" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr"/>
@@ -3645,50 +3643,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25998.95</v>
+        <v>26091.29</v>
       </c>
       <c r="C38" t="n">
-        <v>26166.25</v>
+        <v>26171.7</v>
       </c>
       <c r="D38" t="n">
-        <v>25969.52</v>
+        <v>26038.07</v>
       </c>
       <c r="E38" t="n">
-        <v>26136.56</v>
+        <v>26106.6</v>
       </c>
       <c r="F38" t="n">
-        <v>153.52</v>
+        <v>-29.96</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0011</v>
       </c>
       <c r="H38" t="n">
-        <v>196.73</v>
+        <v>133.63</v>
       </c>
       <c r="I38" t="n">
-        <v>25766.07</v>
+        <v>25772.79</v>
       </c>
       <c r="J38" t="n">
-        <v>25832.45</v>
+        <v>25974.17</v>
       </c>
       <c r="K38" t="n">
-        <v>25909.02</v>
+        <v>26038.2</v>
       </c>
       <c r="L38" t="n">
-        <v>25985.58</v>
+        <v>26102.22</v>
       </c>
       <c r="M38" t="n">
-        <v>26057.06</v>
+        <v>26234.93</v>
       </c>
       <c r="N38" t="n">
-        <v>26128.53</v>
+        <v>26367.63</v>
       </c>
       <c r="O38" t="n">
-        <v>26210.19</v>
+        <v>26362.98</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3696,23 +3694,21 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3722,55 +3718,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26091.29</v>
+        <v>26206.01</v>
       </c>
       <c r="C39" t="n">
-        <v>26171.7</v>
+        <v>26341.52</v>
       </c>
       <c r="D39" t="n">
-        <v>26038.07</v>
+        <v>26164.11</v>
       </c>
       <c r="E39" t="n">
-        <v>26106.6</v>
+        <v>26266.14</v>
       </c>
       <c r="F39" t="n">
-        <v>-29.96</v>
+        <v>159.54</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0061</v>
       </c>
       <c r="H39" t="n">
-        <v>133.63</v>
+        <v>177.41</v>
       </c>
       <c r="I39" t="n">
-        <v>25772.79</v>
+        <v>25904.44</v>
       </c>
       <c r="J39" t="n">
-        <v>25974.17</v>
+        <v>25973.83</v>
       </c>
       <c r="K39" t="n">
-        <v>26038.2</v>
+        <v>26039.79</v>
       </c>
       <c r="L39" t="n">
-        <v>26102.22</v>
+        <v>26105.74</v>
       </c>
       <c r="M39" t="n">
-        <v>26234.93</v>
+        <v>26173.41</v>
       </c>
       <c r="N39" t="n">
-        <v>26367.63</v>
+        <v>26241.09</v>
       </c>
       <c r="O39" t="n">
-        <v>26362.98</v>
+        <v>26305.33</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3778,83 +3778,83 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>26206.01</v>
+        <v>26255.41</v>
       </c>
       <c r="C40" t="n">
-        <v>26341.52</v>
+        <v>26466.76</v>
       </c>
       <c r="D40" t="n">
-        <v>26164.11</v>
+        <v>26196.92</v>
       </c>
       <c r="E40" t="n">
-        <v>26266.14</v>
+        <v>26285.96</v>
       </c>
       <c r="F40" t="n">
-        <v>159.54</v>
+        <v>19.82</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0061</v>
+        <v>0.0008</v>
       </c>
       <c r="H40" t="n">
-        <v>177.41</v>
+        <v>269.84</v>
       </c>
       <c r="I40" t="n">
-        <v>25904.44</v>
+        <v>25986.7</v>
       </c>
       <c r="J40" t="n">
-        <v>25973.83</v>
+        <v>26095.39</v>
       </c>
       <c r="K40" t="n">
-        <v>26039.79</v>
+        <v>26177.44</v>
       </c>
       <c r="L40" t="n">
-        <v>26105.74</v>
+        <v>26259.48</v>
       </c>
       <c r="M40" t="n">
-        <v>26173.41</v>
+        <v>26354.85</v>
       </c>
       <c r="N40" t="n">
-        <v>26241.09</v>
+        <v>26450.21</v>
       </c>
       <c r="O40" t="n">
-        <v>26305.33</v>
+        <v>26518.93</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
@@ -3877,13 +3877,11 @@
       </c>
       <c r="U40" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v/>
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
@@ -3895,50 +3893,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26255.41</v>
+        <v>26354.37</v>
       </c>
       <c r="C41" t="n">
-        <v>26466.76</v>
+        <v>26402.81</v>
       </c>
       <c r="D41" t="n">
-        <v>26196.92</v>
+        <v>26241.77</v>
       </c>
       <c r="E41" t="n">
-        <v>26285.96</v>
+        <v>26367.24</v>
       </c>
       <c r="F41" t="n">
-        <v>19.82</v>
+        <v>81.28</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0031</v>
       </c>
       <c r="H41" t="n">
-        <v>269.84</v>
+        <v>161.04</v>
       </c>
       <c r="I41" t="n">
-        <v>25986.7</v>
+        <v>25927.08</v>
       </c>
       <c r="J41" t="n">
-        <v>26095.39</v>
+        <v>25993.18</v>
       </c>
       <c r="K41" t="n">
-        <v>26177.44</v>
+        <v>26151.04</v>
       </c>
       <c r="L41" t="n">
-        <v>26259.48</v>
+        <v>26308.9</v>
       </c>
       <c r="M41" t="n">
-        <v>26354.85</v>
+        <v>26420.88</v>
       </c>
       <c r="N41" t="n">
-        <v>26450.21</v>
+        <v>26532.86</v>
       </c>
       <c r="O41" t="n">
-        <v>26518.93</v>
+        <v>26736.6</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3951,18 +3949,16 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3972,55 +3968,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26354.37</v>
+        <v>26494.61</v>
       </c>
       <c r="C42" t="n">
-        <v>26402.81</v>
+        <v>26618.74</v>
       </c>
       <c r="D42" t="n">
-        <v>26241.77</v>
+        <v>26467.36</v>
       </c>
       <c r="E42" t="n">
-        <v>26367.24</v>
+        <v>26569.99</v>
       </c>
       <c r="F42" t="n">
-        <v>81.28</v>
+        <v>202.75</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0077</v>
       </c>
       <c r="H42" t="n">
-        <v>161.04</v>
+        <v>151.38</v>
       </c>
       <c r="I42" t="n">
-        <v>25927.08</v>
+        <v>26080.73</v>
       </c>
       <c r="J42" t="n">
-        <v>25993.18</v>
+        <v>26228.67</v>
       </c>
       <c r="K42" t="n">
-        <v>26151.04</v>
+        <v>26286.72</v>
       </c>
       <c r="L42" t="n">
-        <v>26308.9</v>
+        <v>26344.77</v>
       </c>
       <c r="M42" t="n">
-        <v>26420.88</v>
+        <v>26447.76</v>
       </c>
       <c r="N42" t="n">
-        <v>26532.86</v>
+        <v>26550.76</v>
       </c>
       <c r="O42" t="n">
-        <v>26736.6</v>
+        <v>26563.85</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4038,106 +4038,106 @@
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v/>
-      </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>26494.61</v>
+        <v>26464.14</v>
       </c>
       <c r="C43" t="n">
-        <v>26618.74</v>
+        <v>26471.79</v>
       </c>
       <c r="D43" t="n">
-        <v>26467.36</v>
+        <v>26249.59</v>
       </c>
       <c r="E43" t="n">
-        <v>26569.99</v>
+        <v>26258.11</v>
       </c>
       <c r="F43" t="n">
-        <v>202.75</v>
+        <v>-311.88</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0117</v>
       </c>
       <c r="H43" t="n">
-        <v>151.38</v>
+        <v>222.2</v>
       </c>
       <c r="I43" t="n">
-        <v>26080.73</v>
+        <v>26315.98</v>
       </c>
       <c r="J43" t="n">
-        <v>26228.67</v>
+        <v>26432.08</v>
       </c>
       <c r="K43" t="n">
-        <v>26286.72</v>
+        <v>26494.3</v>
       </c>
       <c r="L43" t="n">
-        <v>26344.77</v>
+        <v>26556.52</v>
       </c>
       <c r="M43" t="n">
-        <v>26447.76</v>
+        <v>26645.68</v>
       </c>
       <c r="N43" t="n">
-        <v>26550.76</v>
+        <v>26734.84</v>
       </c>
       <c r="O43" t="n">
-        <v>26563.85</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
+        <v>26770.12</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W43" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W43" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr"/>
@@ -4145,59 +4145,59 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26464.14</v>
+        <v>26150.75</v>
       </c>
       <c r="C44" t="n">
-        <v>26471.79</v>
+        <v>26206.13</v>
       </c>
       <c r="D44" t="n">
-        <v>26249.59</v>
+        <v>25916.76</v>
       </c>
       <c r="E44" t="n">
-        <v>26258.11</v>
+        <v>25970.11</v>
       </c>
       <c r="F44" t="n">
-        <v>-311.88</v>
+        <v>-288</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.011</v>
       </c>
       <c r="H44" t="n">
-        <v>222.2</v>
+        <v>289.37</v>
       </c>
       <c r="I44" t="n">
-        <v>26315.98</v>
+        <v>26027.39</v>
       </c>
       <c r="J44" t="n">
-        <v>26432.08</v>
+        <v>25984.62</v>
       </c>
       <c r="K44" t="n">
-        <v>26494.3</v>
+        <v>26147.01</v>
       </c>
       <c r="L44" t="n">
-        <v>26556.52</v>
+        <v>26309.4</v>
       </c>
       <c r="M44" t="n">
-        <v>26645.68</v>
+        <v>26369.21</v>
       </c>
       <c r="N44" t="n">
-        <v>26734.84</v>
+        <v>26429.02</v>
       </c>
       <c r="O44" t="n">
-        <v>26770.12</v>
+        <v>26693.99</v>
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
@@ -4229,64 +4229,60 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>26150.75</v>
+        <v>25886.67</v>
       </c>
       <c r="C45" t="n">
-        <v>26206.13</v>
+        <v>25924.21</v>
       </c>
       <c r="D45" t="n">
-        <v>25916.76</v>
+        <v>25727.93</v>
       </c>
       <c r="E45" t="n">
-        <v>25970.11</v>
+        <v>25839.33</v>
       </c>
       <c r="F45" t="n">
-        <v>-288</v>
+        <v>-130.78</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.005</v>
       </c>
       <c r="H45" t="n">
-        <v>289.37</v>
+        <v>196.28</v>
       </c>
       <c r="I45" t="n">
-        <v>26027.39</v>
+        <v>25627.39</v>
       </c>
       <c r="J45" t="n">
-        <v>25984.62</v>
+        <v>25635.07</v>
       </c>
       <c r="K45" t="n">
-        <v>26147.01</v>
+        <v>25825.42</v>
       </c>
       <c r="L45" t="n">
-        <v>26309.4</v>
+        <v>26015.78</v>
       </c>
       <c r="M45" t="n">
-        <v>26369.21</v>
+        <v>26114.79</v>
       </c>
       <c r="N45" t="n">
-        <v>26429.02</v>
+        <v>26213.81</v>
       </c>
       <c r="O45" t="n">
-        <v>26693.99</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
+        <v>26495.5</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
@@ -4313,50 +4309,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25886.67</v>
+        <v>25840.92</v>
       </c>
       <c r="C46" t="n">
-        <v>25924.21</v>
+        <v>26007.79</v>
       </c>
       <c r="D46" t="n">
-        <v>25727.93</v>
+        <v>25784.84</v>
       </c>
       <c r="E46" t="n">
-        <v>25839.33</v>
+        <v>26003.32</v>
       </c>
       <c r="F46" t="n">
-        <v>-130.78</v>
+        <v>163.99</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0063</v>
       </c>
       <c r="H46" t="n">
-        <v>196.28</v>
+        <v>222.95</v>
       </c>
       <c r="I46" t="n">
-        <v>25627.39</v>
+        <v>25531.65</v>
       </c>
       <c r="J46" t="n">
-        <v>25635.07</v>
+        <v>25649.68</v>
       </c>
       <c r="K46" t="n">
-        <v>25825.42</v>
+        <v>25741.19</v>
       </c>
       <c r="L46" t="n">
-        <v>26015.78</v>
+        <v>25832.7</v>
       </c>
       <c r="M46" t="n">
-        <v>26114.79</v>
+        <v>25937.47</v>
       </c>
       <c r="N46" t="n">
-        <v>26213.81</v>
+        <v>26042.24</v>
       </c>
       <c r="O46" t="n">
-        <v>26495.5</v>
+        <v>26120.49</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4364,22 +4360,24 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
@@ -4388,55 +4386,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25840.92</v>
+        <v>25985.86</v>
       </c>
       <c r="C47" t="n">
-        <v>26007.79</v>
+        <v>26167.93</v>
       </c>
       <c r="D47" t="n">
-        <v>25784.84</v>
+        <v>25958.7</v>
       </c>
       <c r="E47" t="n">
-        <v>26003.32</v>
+        <v>26046.4</v>
       </c>
       <c r="F47" t="n">
-        <v>163.99</v>
+        <v>43.08</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0017</v>
       </c>
       <c r="H47" t="n">
-        <v>222.95</v>
+        <v>209.23</v>
       </c>
       <c r="I47" t="n">
-        <v>25531.65</v>
+        <v>25561.89</v>
       </c>
       <c r="J47" t="n">
-        <v>25649.68</v>
+        <v>25833.87</v>
       </c>
       <c r="K47" t="n">
-        <v>25741.19</v>
+        <v>25891.85</v>
       </c>
       <c r="L47" t="n">
-        <v>25832.7</v>
+        <v>25949.82</v>
       </c>
       <c r="M47" t="n">
-        <v>25937.47</v>
+        <v>26114.79</v>
       </c>
       <c r="N47" t="n">
-        <v>26042.24</v>
+        <v>26279.77</v>
       </c>
       <c r="O47" t="n">
-        <v>26120.49</v>
+        <v>26230.74</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4454,13 +4456,11 @@
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4479,50 +4479,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25985.86</v>
+        <v>26039.54</v>
       </c>
       <c r="C48" t="n">
-        <v>26167.93</v>
+        <v>26069.99</v>
       </c>
       <c r="D48" t="n">
-        <v>25958.7</v>
+        <v>25919.61</v>
       </c>
       <c r="E48" t="n">
-        <v>26046.4</v>
+        <v>26006.53</v>
       </c>
       <c r="F48" t="n">
-        <v>43.08</v>
+        <v>-39.87</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0015</v>
       </c>
       <c r="H48" t="n">
-        <v>209.23</v>
+        <v>150.38</v>
       </c>
       <c r="I48" t="n">
-        <v>25561.89</v>
+        <v>25749.47</v>
       </c>
       <c r="J48" t="n">
-        <v>25833.87</v>
+        <v>25828.71</v>
       </c>
       <c r="K48" t="n">
-        <v>25891.85</v>
+        <v>25941.79</v>
       </c>
       <c r="L48" t="n">
-        <v>25949.82</v>
+        <v>26054.86</v>
       </c>
       <c r="M48" t="n">
-        <v>26114.79</v>
+        <v>26151.02</v>
       </c>
       <c r="N48" t="n">
-        <v>26279.77</v>
+        <v>26247.17</v>
       </c>
       <c r="O48" t="n">
-        <v>26230.74</v>
+        <v>26377.16</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4530,18 +4530,18 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4554,74 +4554,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>26039.54</v>
+        <v>25897.22</v>
       </c>
       <c r="C49" t="n">
-        <v>26069.99</v>
+        <v>26026.78</v>
       </c>
       <c r="D49" t="n">
-        <v>25919.61</v>
+        <v>25799.66</v>
       </c>
       <c r="E49" t="n">
-        <v>26006.53</v>
+        <v>26007.63</v>
       </c>
       <c r="F49" t="n">
-        <v>-39.87</v>
+        <v>1.1</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>150.38</v>
+        <v>227.12</v>
       </c>
       <c r="I49" t="n">
-        <v>25749.47</v>
+        <v>25769.23</v>
       </c>
       <c r="J49" t="n">
-        <v>25828.71</v>
+        <v>25862.01</v>
       </c>
       <c r="K49" t="n">
-        <v>25941.79</v>
+        <v>25931.34</v>
       </c>
       <c r="L49" t="n">
-        <v>26054.86</v>
+        <v>26000.66</v>
       </c>
       <c r="M49" t="n">
-        <v>26151.02</v>
+        <v>26081.72</v>
       </c>
       <c r="N49" t="n">
-        <v>26247.17</v>
+        <v>26162.77</v>
       </c>
       <c r="O49" t="n">
-        <v>26377.16</v>
+        <v>26220.37</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4638,58 +4636,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25897.22</v>
+        <v>25870.98</v>
       </c>
       <c r="C50" t="n">
-        <v>26026.78</v>
+        <v>25909.66</v>
       </c>
       <c r="D50" t="n">
-        <v>25799.66</v>
+        <v>25512.39</v>
       </c>
       <c r="E50" t="n">
-        <v>26007.63</v>
+        <v>25576.45</v>
       </c>
       <c r="F50" t="n">
-        <v>1.1</v>
+        <v>-431.18</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0</v>
+        <v>-0.0166</v>
       </c>
       <c r="H50" t="n">
-        <v>227.12</v>
+        <v>397.27</v>
       </c>
       <c r="I50" t="n">
-        <v>25769.23</v>
+        <v>25572.54</v>
       </c>
       <c r="J50" t="n">
-        <v>25862.01</v>
+        <v>25827.72</v>
       </c>
       <c r="K50" t="n">
-        <v>25931.34</v>
+        <v>25894.07</v>
       </c>
       <c r="L50" t="n">
-        <v>26000.66</v>
+        <v>25960.43</v>
       </c>
       <c r="M50" t="n">
-        <v>26081.72</v>
+        <v>26121.19</v>
       </c>
       <c r="N50" t="n">
-        <v>26162.77</v>
+        <v>26281.96</v>
       </c>
       <c r="O50" t="n">
-        <v>26220.37</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
+        <v>26253.9</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q50" s="6" t="inlineStr">
         <is>
@@ -4701,9 +4705,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4720,73 +4724,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25870.98</v>
+        <v>25555.66</v>
       </c>
       <c r="C51" t="n">
-        <v>25909.66</v>
+        <v>25612.09</v>
       </c>
       <c r="D51" t="n">
-        <v>25512.39</v>
+        <v>25361.15</v>
       </c>
       <c r="E51" t="n">
-        <v>25576.45</v>
+        <v>25361.15</v>
       </c>
       <c r="F51" t="n">
-        <v>-431.18</v>
+        <v>-215.3</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>397.27</v>
+        <v>250.94</v>
       </c>
       <c r="I51" t="n">
-        <v>25572.54</v>
+        <v>25115.12</v>
       </c>
       <c r="J51" t="n">
-        <v>25827.72</v>
+        <v>25111.89</v>
       </c>
       <c r="K51" t="n">
-        <v>25894.07</v>
+        <v>25377.81</v>
       </c>
       <c r="L51" t="n">
-        <v>25960.43</v>
+        <v>25643.74</v>
       </c>
       <c r="M51" t="n">
-        <v>26121.19</v>
+        <v>25775.08</v>
       </c>
       <c r="N51" t="n">
-        <v>26281.96</v>
+        <v>25906.43</v>
       </c>
       <c r="O51" t="n">
-        <v>26253.9</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
+        <v>26306.93</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
@@ -4813,50 +4809,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25555.66</v>
+        <v>25478.84</v>
       </c>
       <c r="C52" t="n">
-        <v>25612.09</v>
+        <v>25581.22</v>
       </c>
       <c r="D52" t="n">
-        <v>25361.15</v>
+        <v>25396.38</v>
       </c>
       <c r="E52" t="n">
-        <v>25361.15</v>
+        <v>25568.56</v>
       </c>
       <c r="F52" t="n">
-        <v>-215.3</v>
+        <v>207.41</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>250.94</v>
+        <v>184.84</v>
       </c>
       <c r="I52" t="n">
-        <v>25115.12</v>
+        <v>25110.21</v>
       </c>
       <c r="J52" t="n">
-        <v>25111.89</v>
+        <v>25047.48</v>
       </c>
       <c r="K52" t="n">
-        <v>25377.81</v>
+        <v>25235.68</v>
       </c>
       <c r="L52" t="n">
-        <v>25643.74</v>
+        <v>25423.89</v>
       </c>
       <c r="M52" t="n">
-        <v>25775.08</v>
+        <v>25486.62</v>
       </c>
       <c r="N52" t="n">
-        <v>25906.43</v>
+        <v>25549.35</v>
       </c>
       <c r="O52" t="n">
-        <v>26306.93</v>
+        <v>25863.03</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4864,104 +4860,110 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="W52" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25478.84</v>
+        <v>25498.74</v>
       </c>
       <c r="C53" t="n">
-        <v>25581.22</v>
+        <v>25548.78</v>
       </c>
       <c r="D53" t="n">
-        <v>25396.38</v>
+        <v>25325.52</v>
       </c>
       <c r="E53" t="n">
-        <v>25568.56</v>
+        <v>25440.81</v>
       </c>
       <c r="F53" t="n">
-        <v>207.41</v>
+        <v>-127.75</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.005</v>
       </c>
       <c r="H53" t="n">
-        <v>184.84</v>
+        <v>223.26</v>
       </c>
       <c r="I53" t="n">
-        <v>25110.21</v>
+        <v>25211.54</v>
       </c>
       <c r="J53" t="n">
-        <v>25047.48</v>
+        <v>25423.6</v>
       </c>
       <c r="K53" t="n">
-        <v>25235.68</v>
+        <v>25476.14</v>
       </c>
       <c r="L53" t="n">
-        <v>25423.89</v>
+        <v>25528.68</v>
       </c>
       <c r="M53" t="n">
-        <v>25486.62</v>
+        <v>25660.98</v>
       </c>
       <c r="N53" t="n">
-        <v>25549.35</v>
+        <v>25793.28</v>
       </c>
       <c r="O53" t="n">
-        <v>25863.03</v>
+        <v>25766.06</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
+      <c r="Q53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
@@ -4972,64 +4974,64 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25498.74</v>
+        <v>25360.32</v>
       </c>
       <c r="C54" t="n">
-        <v>25548.78</v>
+        <v>25478.98</v>
       </c>
       <c r="D54" t="n">
-        <v>25325.52</v>
+        <v>25172.89</v>
       </c>
       <c r="E54" t="n">
-        <v>25440.81</v>
+        <v>25402.28</v>
       </c>
       <c r="F54" t="n">
-        <v>-127.75</v>
+        <v>-38.53</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.005</v>
+        <v>-0.0015</v>
       </c>
       <c r="H54" t="n">
-        <v>223.26</v>
+        <v>306.09</v>
       </c>
       <c r="I54" t="n">
-        <v>25211.54</v>
+        <v>25102.26</v>
       </c>
       <c r="J54" t="n">
-        <v>25423.6</v>
+        <v>25219.38</v>
       </c>
       <c r="K54" t="n">
-        <v>25476.14</v>
+        <v>25329.18</v>
       </c>
       <c r="L54" t="n">
-        <v>25528.68</v>
+        <v>25438.98</v>
       </c>
       <c r="M54" t="n">
-        <v>25660.98</v>
+        <v>25552.44</v>
       </c>
       <c r="N54" t="n">
-        <v>25793.28</v>
+        <v>25665.9</v>
       </c>
       <c r="O54" t="n">
-        <v>25766.06</v>
+        <v>25772.04</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
@@ -5039,7 +5041,7 @@
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5065,71 +5067,69 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25360.32</v>
+        <v>25515.96</v>
       </c>
       <c r="C55" t="n">
-        <v>25478.98</v>
+        <v>25599.07</v>
       </c>
       <c r="D55" t="n">
-        <v>25172.89</v>
+        <v>25361.7</v>
       </c>
       <c r="E55" t="n">
-        <v>25402.28</v>
+        <v>25537.75</v>
       </c>
       <c r="F55" t="n">
-        <v>-38.53</v>
+        <v>135.47</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0053</v>
       </c>
       <c r="H55" t="n">
-        <v>306.09</v>
+        <v>237.37</v>
       </c>
       <c r="I55" t="n">
-        <v>25102.26</v>
+        <v>24866.8</v>
       </c>
       <c r="J55" t="n">
-        <v>25219.38</v>
+        <v>25134.36</v>
       </c>
       <c r="K55" t="n">
-        <v>25329.18</v>
+        <v>25249.23</v>
       </c>
       <c r="L55" t="n">
-        <v>25438.98</v>
+        <v>25364.11</v>
       </c>
       <c r="M55" t="n">
-        <v>25552.44</v>
+        <v>25555.32</v>
       </c>
       <c r="N55" t="n">
-        <v>25665.9</v>
+        <v>25746.54</v>
       </c>
       <c r="O55" t="n">
-        <v>25772.04</v>
+        <v>25785.07</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5142,59 +5142,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25515.96</v>
+        <v>25681.6</v>
       </c>
       <c r="C56" t="n">
-        <v>25599.07</v>
+        <v>25800.62</v>
       </c>
       <c r="D56" t="n">
-        <v>25361.7</v>
+        <v>25596.05</v>
       </c>
       <c r="E56" t="n">
-        <v>25537.75</v>
+        <v>25716.71</v>
       </c>
       <c r="F56" t="n">
-        <v>135.47</v>
+        <v>178.96</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0053</v>
+        <v>0.007</v>
       </c>
       <c r="H56" t="n">
-        <v>237.37</v>
+        <v>204.57</v>
       </c>
       <c r="I56" t="n">
-        <v>24866.8</v>
+        <v>25124.33</v>
       </c>
       <c r="J56" t="n">
-        <v>25134.36</v>
+        <v>25329.06</v>
       </c>
       <c r="K56" t="n">
-        <v>25249.23</v>
+        <v>25419.06</v>
       </c>
       <c r="L56" t="n">
-        <v>25364.11</v>
+        <v>25509.07</v>
       </c>
       <c r="M56" t="n">
-        <v>25555.32</v>
+        <v>25656.44</v>
       </c>
       <c r="N56" t="n">
-        <v>25746.54</v>
+        <v>25803.8</v>
       </c>
       <c r="O56" t="n">
-        <v>25785.07</v>
+        <v>25836.44</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5231,79 +5227,83 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25681.6</v>
+        <v>25596.46</v>
       </c>
       <c r="C57" t="n">
-        <v>25800.62</v>
+        <v>25656.22</v>
       </c>
       <c r="D57" t="n">
-        <v>25596.05</v>
+        <v>25285.9</v>
       </c>
       <c r="E57" t="n">
-        <v>25716.71</v>
+        <v>25304.06</v>
       </c>
       <c r="F57" t="n">
-        <v>178.96</v>
+        <v>-412.65</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.007</v>
+        <v>-0.016</v>
       </c>
       <c r="H57" t="n">
-        <v>204.57</v>
+        <v>370.32</v>
       </c>
       <c r="I57" t="n">
-        <v>25124.33</v>
+        <v>25391.48</v>
       </c>
       <c r="J57" t="n">
-        <v>25329.06</v>
+        <v>25521.33</v>
       </c>
       <c r="K57" t="n">
-        <v>25419.06</v>
+        <v>25614.43</v>
       </c>
       <c r="L57" t="n">
-        <v>25509.07</v>
+        <v>25707.52</v>
       </c>
       <c r="M57" t="n">
-        <v>25656.44</v>
+        <v>25819</v>
       </c>
       <c r="N57" t="n">
-        <v>25803.8</v>
+        <v>25930.47</v>
       </c>
       <c r="O57" t="n">
-        <v>25836.44</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
+        <v>26005.19</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W57" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
@@ -5311,77 +5311,75 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>25596.46</v>
+        <v>25491.35</v>
       </c>
       <c r="C58" t="n">
-        <v>25656.22</v>
+        <v>25617.99</v>
       </c>
       <c r="D58" t="n">
-        <v>25285.9</v>
+        <v>25434.16</v>
       </c>
       <c r="E58" t="n">
-        <v>25304.06</v>
+        <v>25575.01</v>
       </c>
       <c r="F58" t="n">
-        <v>-412.65</v>
+        <v>270.95</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.016</v>
+        <v>0.0107</v>
       </c>
       <c r="H58" t="n">
-        <v>370.32</v>
+        <v>183.83</v>
       </c>
       <c r="I58" t="n">
-        <v>25391.48</v>
+        <v>24915.58</v>
       </c>
       <c r="J58" t="n">
-        <v>25521.33</v>
+        <v>24850.24</v>
       </c>
       <c r="K58" t="n">
-        <v>25614.43</v>
+        <v>25118.9</v>
       </c>
       <c r="L58" t="n">
-        <v>25707.52</v>
+        <v>25387.56</v>
       </c>
       <c r="M58" t="n">
-        <v>25819</v>
+        <v>25489.22</v>
       </c>
       <c r="N58" t="n">
-        <v>25930.47</v>
+        <v>25590.88</v>
       </c>
       <c r="O58" t="n">
-        <v>26005.19</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
+        <v>26026.54</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
@@ -5390,55 +5388,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25491.35</v>
+        <v>25592.98</v>
       </c>
       <c r="C59" t="n">
-        <v>25617.99</v>
+        <v>25783.16</v>
       </c>
       <c r="D59" t="n">
-        <v>25434.16</v>
+        <v>25423.07</v>
       </c>
       <c r="E59" t="n">
-        <v>25575.01</v>
+        <v>25578.85</v>
       </c>
       <c r="F59" t="n">
-        <v>270.95</v>
+        <v>3.84</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0107</v>
+        <v>0.0002</v>
       </c>
       <c r="H59" t="n">
-        <v>183.83</v>
+        <v>360.09</v>
       </c>
       <c r="I59" t="n">
-        <v>24915.58</v>
+        <v>25250.33</v>
       </c>
       <c r="J59" t="n">
-        <v>24850.24</v>
+        <v>25415.65</v>
       </c>
       <c r="K59" t="n">
-        <v>25118.9</v>
+        <v>25483.09</v>
       </c>
       <c r="L59" t="n">
-        <v>25387.56</v>
+        <v>25550.54</v>
       </c>
       <c r="M59" t="n">
-        <v>25489.22</v>
+        <v>25666.92</v>
       </c>
       <c r="N59" t="n">
-        <v>25590.88</v>
+        <v>25783.31</v>
       </c>
       <c r="O59" t="n">
-        <v>26026.54</v>
+        <v>25801.82</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5446,12 +5448,14 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T59" s="8" t="inlineStr">
@@ -5459,10 +5463,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U59" s="8" t="n">
+        <v/>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
@@ -5481,50 +5483,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25592.98</v>
+        <v>25724.13</v>
       </c>
       <c r="C60" t="n">
-        <v>25783.16</v>
+        <v>25729.05</v>
       </c>
       <c r="D60" t="n">
-        <v>25423.07</v>
+        <v>25365.21</v>
       </c>
       <c r="E60" t="n">
-        <v>25578.85</v>
+        <v>25410.63</v>
       </c>
       <c r="F60" t="n">
-        <v>3.84</v>
+        <v>-168.22</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.0066</v>
       </c>
       <c r="H60" t="n">
-        <v>360.09</v>
+        <v>363.84</v>
       </c>
       <c r="I60" t="n">
-        <v>25250.33</v>
+        <v>25062.98</v>
       </c>
       <c r="J60" t="n">
-        <v>25415.65</v>
+        <v>25206.63</v>
       </c>
       <c r="K60" t="n">
-        <v>25483.09</v>
+        <v>25398.8</v>
       </c>
       <c r="L60" t="n">
-        <v>25550.54</v>
+        <v>25590.98</v>
       </c>
       <c r="M60" t="n">
-        <v>25666.92</v>
+        <v>25758.89</v>
       </c>
       <c r="N60" t="n">
-        <v>25783.31</v>
+        <v>25926.81</v>
       </c>
       <c r="O60" t="n">
-        <v>25801.82</v>
+        <v>26143.25</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5534,18 +5536,16 @@
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5558,59 +5558,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>25724.13</v>
+        <v>25263.11</v>
       </c>
       <c r="C61" t="n">
-        <v>25729.05</v>
+        <v>25424.21</v>
       </c>
       <c r="D61" t="n">
-        <v>25365.21</v>
+        <v>25164.2</v>
       </c>
       <c r="E61" t="n">
-        <v>25410.63</v>
+        <v>25266.53</v>
       </c>
       <c r="F61" t="n">
-        <v>-168.22</v>
+        <v>-144.1</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0066</v>
+        <v>-0.0057</v>
       </c>
       <c r="H61" t="n">
-        <v>363.84</v>
+        <v>260.01</v>
       </c>
       <c r="I61" t="n">
-        <v>25062.98</v>
+        <v>25001.37</v>
       </c>
       <c r="J61" t="n">
-        <v>25206.63</v>
+        <v>24978.54</v>
       </c>
       <c r="K61" t="n">
-        <v>25398.8</v>
+        <v>25228.71</v>
       </c>
       <c r="L61" t="n">
-        <v>25590.98</v>
+        <v>25478.88</v>
       </c>
       <c r="M61" t="n">
-        <v>25758.89</v>
+        <v>25592.55</v>
       </c>
       <c r="N61" t="n">
-        <v>25926.81</v>
+        <v>25706.22</v>
       </c>
       <c r="O61" t="n">
-        <v>26143.25</v>
+        <v>26092.89</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5647,50 +5643,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>25263.11</v>
+        <v>25441.79</v>
       </c>
       <c r="C62" t="n">
-        <v>25424.21</v>
+        <v>25529.33</v>
       </c>
       <c r="D62" t="n">
-        <v>25164.2</v>
+        <v>25347.3</v>
       </c>
       <c r="E62" t="n">
-        <v>25266.53</v>
+        <v>25408.64</v>
       </c>
       <c r="F62" t="n">
-        <v>-144.1</v>
+        <v>142.11</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0056</v>
       </c>
       <c r="H62" t="n">
-        <v>260.01</v>
+        <v>182.03</v>
       </c>
       <c r="I62" t="n">
-        <v>25001.37</v>
+        <v>24904.19</v>
       </c>
       <c r="J62" t="n">
-        <v>24978.54</v>
+        <v>24992.68</v>
       </c>
       <c r="K62" t="n">
-        <v>25228.71</v>
+        <v>25136.52</v>
       </c>
       <c r="L62" t="n">
-        <v>25478.88</v>
+        <v>25280.37</v>
       </c>
       <c r="M62" t="n">
-        <v>25592.55</v>
+        <v>25396.54</v>
       </c>
       <c r="N62" t="n">
-        <v>25706.22</v>
+        <v>25512.7</v>
       </c>
       <c r="O62" t="n">
-        <v>26092.89</v>
+        <v>25684.22</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5698,21 +5694,23 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
@@ -5722,55 +5720,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>25441.79</v>
+        <v>25443.98</v>
       </c>
       <c r="C63" t="n">
-        <v>25529.33</v>
+        <v>25575.66</v>
       </c>
       <c r="D63" t="n">
-        <v>25347.3</v>
+        <v>25360.32</v>
       </c>
       <c r="E63" t="n">
-        <v>25408.64</v>
+        <v>25374.42</v>
       </c>
       <c r="F63" t="n">
-        <v>142.11</v>
+        <v>-34.22</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0056</v>
+        <v>-0.0013</v>
       </c>
       <c r="H63" t="n">
-        <v>182.03</v>
+        <v>215.34</v>
       </c>
       <c r="I63" t="n">
-        <v>24904.19</v>
+        <v>25165.27</v>
       </c>
       <c r="J63" t="n">
-        <v>24992.68</v>
+        <v>25211.77</v>
       </c>
       <c r="K63" t="n">
-        <v>25136.52</v>
+        <v>25317.63</v>
       </c>
       <c r="L63" t="n">
-        <v>25280.37</v>
+        <v>25423.48</v>
       </c>
       <c r="M63" t="n">
-        <v>25396.54</v>
+        <v>25499.66</v>
       </c>
       <c r="N63" t="n">
-        <v>25512.7</v>
+        <v>25575.83</v>
       </c>
       <c r="O63" t="n">
-        <v>25684.22</v>
+        <v>25711.36</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5781,20 +5783,18 @@
       <c r="R63" s="6" t="n">
         <v/>
       </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T63" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
       </c>
       <c r="V63" s="8" t="n">
         <v/>
@@ -5806,57 +5806,57 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>25443.98</v>
+        <v>25374.34</v>
       </c>
       <c r="C64" t="n">
-        <v>25575.66</v>
+        <v>25617.31</v>
       </c>
       <c r="D64" t="n">
-        <v>25360.32</v>
+        <v>25338.03</v>
       </c>
       <c r="E64" t="n">
-        <v>25374.42</v>
+        <v>25399.21</v>
       </c>
       <c r="F64" t="n">
-        <v>-34.22</v>
+        <v>24.79</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.001</v>
       </c>
       <c r="H64" t="n">
-        <v>215.34</v>
+        <v>279.28</v>
       </c>
       <c r="I64" t="n">
-        <v>25165.27</v>
+        <v>25144.98</v>
       </c>
       <c r="J64" t="n">
-        <v>25211.77</v>
+        <v>25112.29</v>
       </c>
       <c r="K64" t="n">
-        <v>25317.63</v>
+        <v>25266.75</v>
       </c>
       <c r="L64" t="n">
-        <v>25423.48</v>
+        <v>25421.21</v>
       </c>
       <c r="M64" t="n">
-        <v>25499.66</v>
+        <v>25482.09</v>
       </c>
       <c r="N64" t="n">
-        <v>25575.83</v>
+        <v>25542.97</v>
       </c>
       <c r="O64" t="n">
-        <v>25711.36</v>
+        <v>25791</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5877,8 +5877,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U64" s="8" t="n">
-        <v/>
+      <c r="U64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V64" s="8" t="n">
         <v/>
@@ -5897,17 +5899,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>25374.34</v>
+        <v>25490.67</v>
       </c>
       <c r="C65" t="n">
-        <v>25617.31</v>
+        <v>25584.5</v>
       </c>
       <c r="D65" t="n">
-        <v>25338.03</v>
+        <v>25190.33</v>
       </c>
       <c r="E65" t="n">
         <v/>
@@ -5919,28 +5921,28 @@
         <v/>
       </c>
       <c r="H65" t="n">
-        <v>279.28</v>
+        <v>394.17</v>
       </c>
       <c r="I65" t="n">
-        <v>25144.98</v>
+        <v>25058.75</v>
       </c>
       <c r="J65" t="n">
-        <v>25112.29</v>
+        <v>25080.7</v>
       </c>
       <c r="K65" t="n">
-        <v>25266.75</v>
+        <v>25259.57</v>
       </c>
       <c r="L65" t="n">
-        <v>25421.21</v>
+        <v>25438.44</v>
       </c>
       <c r="M65" t="n">
-        <v>25482.09</v>
+        <v>25538.85</v>
       </c>
       <c r="N65" t="n">
-        <v>25542.97</v>
+        <v>25639.26</v>
       </c>
       <c r="O65" t="n">
-        <v>25791</v>
+        <v>25896.59</v>
       </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
@@ -5950,8 +5952,10 @@
       <c r="Q65" s="6" t="n">
         <v/>
       </c>
-      <c r="R65" s="6" t="n">
-        <v/>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S65" s="12" t="inlineStr">
         <is>
@@ -5963,10 +5967,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U65" s="8" t="n">
+        <v/>
       </c>
       <c r="V65" s="8" t="n">
         <v/>
@@ -5976,11 +5978,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -637,50 +637,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25763.97</v>
+        <v>25811.9</v>
       </c>
       <c r="C2" t="n">
-        <v>25826.78</v>
+        <v>25900.1</v>
       </c>
       <c r="D2" t="n">
-        <v>25611.69</v>
+        <v>25698.56</v>
       </c>
       <c r="E2" t="n">
-        <v>25779.31</v>
+        <v>25817.89</v>
       </c>
       <c r="F2" t="n">
-        <v>198.43</v>
+        <v>38.58</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0078</v>
+        <v>0.0015</v>
       </c>
       <c r="H2" t="n">
-        <v>215.09</v>
+        <v>201.54</v>
       </c>
       <c r="I2" t="n">
-        <v>24333.46</v>
+        <v>25396.6</v>
       </c>
       <c r="J2" t="n">
-        <v>25047.53</v>
+        <v>25594.26</v>
       </c>
       <c r="K2" t="n">
-        <v>25250.29</v>
+        <v>25671.77</v>
       </c>
       <c r="L2" t="n">
-        <v>25453.06</v>
+        <v>25749.27</v>
       </c>
       <c r="M2" t="n">
-        <v>25911.47</v>
+        <v>25886.86</v>
       </c>
       <c r="N2" t="n">
-        <v>26369.89</v>
+        <v>26024.44</v>
       </c>
       <c r="O2" t="n">
-        <v>26317</v>
+        <v>26041.87</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -693,12 +693,12 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U2" s="8" t="n">
@@ -717,69 +717,73 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25811.9</v>
+        <v>25770.45</v>
       </c>
       <c r="C3" t="n">
-        <v>25900.1</v>
+        <v>25811.97</v>
       </c>
       <c r="D3" t="n">
-        <v>25698.56</v>
+        <v>25465.12</v>
       </c>
       <c r="E3" t="n">
-        <v>25817.89</v>
+        <v>25465.25</v>
       </c>
       <c r="F3" t="n">
-        <v>38.58</v>
+        <v>-352.64</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0137</v>
       </c>
       <c r="H3" t="n">
-        <v>201.54</v>
+        <v>346.85</v>
       </c>
       <c r="I3" t="n">
-        <v>25396.6</v>
+        <v>25497.02</v>
       </c>
       <c r="J3" t="n">
-        <v>25594.26</v>
+        <v>25625.63</v>
       </c>
       <c r="K3" t="n">
-        <v>25671.77</v>
+        <v>25717.12</v>
       </c>
       <c r="L3" t="n">
-        <v>25749.27</v>
+        <v>25808.61</v>
       </c>
       <c r="M3" t="n">
-        <v>25886.86</v>
+        <v>25918.66</v>
       </c>
       <c r="N3" t="n">
-        <v>26024.44</v>
+        <v>26028.71</v>
       </c>
       <c r="O3" t="n">
-        <v>26041.87</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>26101.64</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -787,9 +791,9 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -797,59 +801,59 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25770.45</v>
+        <v>25274.94</v>
       </c>
       <c r="C4" t="n">
-        <v>25811.97</v>
+        <v>25280.16</v>
       </c>
       <c r="D4" t="n">
-        <v>25465.12</v>
+        <v>24830.17</v>
       </c>
       <c r="E4" t="n">
-        <v>25465.25</v>
+        <v>24897.45</v>
       </c>
       <c r="F4" t="n">
-        <v>-352.64</v>
+        <v>-567.8</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0223</v>
       </c>
       <c r="H4" t="n">
-        <v>346.85</v>
+        <v>449.99</v>
       </c>
       <c r="I4" t="n">
-        <v>25497.02</v>
+        <v>25118.27</v>
       </c>
       <c r="J4" t="n">
-        <v>25625.63</v>
+        <v>25031.75</v>
       </c>
       <c r="K4" t="n">
-        <v>25717.12</v>
+        <v>25291.82</v>
       </c>
       <c r="L4" t="n">
-        <v>25808.61</v>
+        <v>25551.9</v>
       </c>
       <c r="M4" t="n">
-        <v>25918.66</v>
+        <v>25638.68</v>
       </c>
       <c r="N4" t="n">
-        <v>26028.71</v>
+        <v>25725.45</v>
       </c>
       <c r="O4" t="n">
-        <v>26101.64</v>
+        <v>26158.82</v>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
@@ -881,74 +885,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25274.94</v>
+        <v>25097.48</v>
       </c>
       <c r="C5" t="n">
-        <v>25280.16</v>
+        <v>25127.76</v>
       </c>
       <c r="D5" t="n">
-        <v>24830.17</v>
+        <v>24867.32</v>
       </c>
       <c r="E5" t="n">
-        <v>24897.45</v>
+        <v>25118.27</v>
       </c>
       <c r="F5" t="n">
-        <v>-567.8</v>
+        <v>220.82</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0089</v>
       </c>
       <c r="H5" t="n">
-        <v>449.99</v>
+        <v>260.44</v>
       </c>
       <c r="I5" t="n">
-        <v>25118.27</v>
+        <v>24380.18</v>
       </c>
       <c r="J5" t="n">
-        <v>25031.75</v>
+        <v>24368.6</v>
       </c>
       <c r="K5" t="n">
-        <v>25291.82</v>
+        <v>24672.45</v>
       </c>
       <c r="L5" t="n">
-        <v>25551.9</v>
+        <v>24976.31</v>
       </c>
       <c r="M5" t="n">
-        <v>25638.68</v>
+        <v>25122.44</v>
       </c>
       <c r="N5" t="n">
-        <v>25725.45</v>
+        <v>25268.58</v>
       </c>
       <c r="O5" t="n">
-        <v>26158.82</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
+        <v>25730.15</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -960,55 +960,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25097.48</v>
+        <v>25081.19</v>
       </c>
       <c r="C6" t="n">
-        <v>25127.76</v>
+        <v>25195.83</v>
       </c>
       <c r="D6" t="n">
-        <v>24867.32</v>
+        <v>24937.52</v>
       </c>
       <c r="E6" t="n">
-        <v>25118.27</v>
+        <v>25067.09</v>
       </c>
       <c r="F6" t="n">
-        <v>220.82</v>
+        <v>-51.18</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.002</v>
       </c>
       <c r="H6" t="n">
-        <v>260.44</v>
+        <v>258.31</v>
       </c>
       <c r="I6" t="n">
-        <v>24380.18</v>
+        <v>24606.88</v>
       </c>
       <c r="J6" t="n">
-        <v>24368.6</v>
+        <v>24918.19</v>
       </c>
       <c r="K6" t="n">
-        <v>24672.45</v>
+        <v>24988.05</v>
       </c>
       <c r="L6" t="n">
-        <v>24976.31</v>
+        <v>25057.9</v>
       </c>
       <c r="M6" t="n">
-        <v>25122.44</v>
+        <v>25248.49</v>
       </c>
       <c r="N6" t="n">
-        <v>25268.58</v>
+        <v>25439.07</v>
       </c>
       <c r="O6" t="n">
-        <v>25730.15</v>
+        <v>25388.2</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1016,18 +1020,18 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1049,50 +1053,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25081.19</v>
+        <v>24963.8</v>
       </c>
       <c r="C7" t="n">
-        <v>25195.83</v>
+        <v>25154.58</v>
       </c>
       <c r="D7" t="n">
-        <v>24937.52</v>
+        <v>24963.8</v>
       </c>
       <c r="E7" t="n">
-        <v>25067.09</v>
+        <v>25114.25</v>
       </c>
       <c r="F7" t="n">
-        <v>-51.18</v>
+        <v>47.16</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="H7" t="n">
-        <v>258.31</v>
+        <v>190.78</v>
       </c>
       <c r="I7" t="n">
-        <v>24606.88</v>
+        <v>24679.21</v>
       </c>
       <c r="J7" t="n">
-        <v>24918.19</v>
+        <v>24808.99</v>
       </c>
       <c r="K7" t="n">
-        <v>24988.05</v>
+        <v>24937.93</v>
       </c>
       <c r="L7" t="n">
-        <v>25057.9</v>
+        <v>25066.88</v>
       </c>
       <c r="M7" t="n">
-        <v>25248.49</v>
+        <v>25196.25</v>
       </c>
       <c r="N7" t="n">
-        <v>25439.07</v>
+        <v>25325.61</v>
       </c>
       <c r="O7" t="n">
-        <v>25388.2</v>
+        <v>25454.14</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1100,10 +1104,8 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R7" s="6" t="n">
+        <v/>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
@@ -1133,59 +1135,63 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24963.8</v>
+        <v>24932.62</v>
       </c>
       <c r="C8" t="n">
-        <v>25154.58</v>
+        <v>25204.68</v>
       </c>
       <c r="D8" t="n">
-        <v>24963.8</v>
+        <v>24869.25</v>
       </c>
       <c r="E8" t="n">
-        <v>25114.25</v>
+        <v>25147.03</v>
       </c>
       <c r="F8" t="n">
-        <v>47.16</v>
+        <v>32.78</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0013</v>
       </c>
       <c r="H8" t="n">
-        <v>190.78</v>
+        <v>335.43</v>
       </c>
       <c r="I8" t="n">
-        <v>24679.21</v>
+        <v>24773.02</v>
       </c>
       <c r="J8" t="n">
-        <v>24808.99</v>
+        <v>24951</v>
       </c>
       <c r="K8" t="n">
-        <v>24937.93</v>
+        <v>25018.86</v>
       </c>
       <c r="L8" t="n">
-        <v>25066.88</v>
+        <v>25086.72</v>
       </c>
       <c r="M8" t="n">
-        <v>25196.25</v>
+        <v>25209.64</v>
       </c>
       <c r="N8" t="n">
-        <v>25325.61</v>
+        <v>25332.56</v>
       </c>
       <c r="O8" t="n">
-        <v>25454.14</v>
+        <v>25345.36</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
@@ -1215,50 +1221,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24932.62</v>
+        <v>24970.05</v>
       </c>
       <c r="C9" t="n">
-        <v>25204.68</v>
+        <v>25055.48</v>
       </c>
       <c r="D9" t="n">
-        <v>24869.25</v>
+        <v>24839.23</v>
       </c>
       <c r="E9" t="n">
-        <v>25147.03</v>
+        <v>24999.53</v>
       </c>
       <c r="F9" t="n">
-        <v>32.78</v>
+        <v>-147.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0059</v>
       </c>
       <c r="H9" t="n">
-        <v>335.43</v>
+        <v>216.25</v>
       </c>
       <c r="I9" t="n">
-        <v>24773.02</v>
+        <v>24533.82</v>
       </c>
       <c r="J9" t="n">
-        <v>24951</v>
+        <v>24866.63</v>
       </c>
       <c r="K9" t="n">
-        <v>25018.86</v>
+        <v>24979.31</v>
       </c>
       <c r="L9" t="n">
-        <v>25086.72</v>
+        <v>25092</v>
       </c>
       <c r="M9" t="n">
-        <v>25209.64</v>
+        <v>25314.74</v>
       </c>
       <c r="N9" t="n">
-        <v>25332.56</v>
+        <v>25537.49</v>
       </c>
       <c r="O9" t="n">
-        <v>25345.36</v>
+        <v>25540.11</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1270,12 +1276,12 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1292,59 +1298,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24970.05</v>
+        <v>25018.95</v>
       </c>
       <c r="C10" t="n">
-        <v>25055.48</v>
+        <v>25021.51</v>
       </c>
       <c r="D10" t="n">
-        <v>24839.23</v>
+        <v>24696.17</v>
       </c>
       <c r="E10" t="n">
-        <v>24999.53</v>
+        <v>24915.49</v>
       </c>
       <c r="F10" t="n">
-        <v>-147.5</v>
+        <v>-84.04000000000001</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0059</v>
+        <v>-0.0034</v>
       </c>
       <c r="H10" t="n">
-        <v>216.25</v>
+        <v>325.34</v>
       </c>
       <c r="I10" t="n">
-        <v>24533.82</v>
+        <v>24622.98</v>
       </c>
       <c r="J10" t="n">
-        <v>24866.63</v>
+        <v>24809.37</v>
       </c>
       <c r="K10" t="n">
-        <v>24979.31</v>
+        <v>24891.4</v>
       </c>
       <c r="L10" t="n">
-        <v>25092</v>
+        <v>24973.44</v>
       </c>
       <c r="M10" t="n">
-        <v>25314.74</v>
+        <v>25107.65</v>
       </c>
       <c r="N10" t="n">
-        <v>25537.49</v>
+        <v>25241.87</v>
       </c>
       <c r="O10" t="n">
-        <v>25540.11</v>
+        <v>25271.73</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1383,67 +1385,65 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25018.95</v>
+        <v>24755.09</v>
       </c>
       <c r="C11" t="n">
-        <v>25021.51</v>
+        <v>24850.75</v>
       </c>
       <c r="D11" t="n">
-        <v>24696.17</v>
+        <v>24651.34</v>
       </c>
       <c r="E11" t="n">
-        <v>24915.49</v>
+        <v>24830.98</v>
       </c>
       <c r="F11" t="n">
-        <v>-84.04000000000001</v>
+        <v>-84.51000000000001</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>-0.0034</v>
       </c>
       <c r="H11" t="n">
-        <v>325.34</v>
+        <v>199.41</v>
       </c>
       <c r="I11" t="n">
-        <v>24622.98</v>
+        <v>24370.83</v>
       </c>
       <c r="J11" t="n">
-        <v>24809.37</v>
+        <v>24618.48</v>
       </c>
       <c r="K11" t="n">
-        <v>24891.4</v>
+        <v>24752.82</v>
       </c>
       <c r="L11" t="n">
-        <v>24973.44</v>
+        <v>24887.17</v>
       </c>
       <c r="M11" t="n">
-        <v>25107.65</v>
+        <v>25078.16</v>
       </c>
       <c r="N11" t="n">
-        <v>25241.87</v>
+        <v>25269.16</v>
       </c>
       <c r="O11" t="n">
-        <v>25271.73</v>
+        <v>25346.85</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q11" s="6" t="n">
+        <v/>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1465,50 +1465,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24755.09</v>
+        <v>24769.15</v>
       </c>
       <c r="C12" t="n">
-        <v>24850.75</v>
+        <v>24974.53</v>
       </c>
       <c r="D12" t="n">
-        <v>24651.34</v>
+        <v>24751.13</v>
       </c>
       <c r="E12" t="n">
-        <v>24830.98</v>
+        <v>24846.69</v>
       </c>
       <c r="F12" t="n">
-        <v>-84.51000000000001</v>
+        <v>15.71</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>199.41</v>
+        <v>223.4</v>
       </c>
       <c r="I12" t="n">
-        <v>24370.83</v>
+        <v>24451.93</v>
       </c>
       <c r="J12" t="n">
-        <v>24618.48</v>
+        <v>24671.54</v>
       </c>
       <c r="K12" t="n">
-        <v>24752.82</v>
+        <v>24731.28</v>
       </c>
       <c r="L12" t="n">
-        <v>24887.17</v>
+        <v>24791.01</v>
       </c>
       <c r="M12" t="n">
-        <v>25078.16</v>
+        <v>24930.69</v>
       </c>
       <c r="N12" t="n">
-        <v>25269.16</v>
+        <v>25070.36</v>
       </c>
       <c r="O12" t="n">
-        <v>25346.85</v>
+        <v>25050.16</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1516,18 +1516,18 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1540,55 +1540,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24769.15</v>
+        <v>24922.1</v>
       </c>
       <c r="C13" t="n">
-        <v>24974.53</v>
+        <v>25011.35</v>
       </c>
       <c r="D13" t="n">
-        <v>24751.13</v>
+        <v>24817.34</v>
       </c>
       <c r="E13" t="n">
-        <v>24846.69</v>
+        <v>25011.35</v>
       </c>
       <c r="F13" t="n">
-        <v>15.71</v>
+        <v>164.66</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0066</v>
       </c>
       <c r="H13" t="n">
-        <v>223.4</v>
+        <v>194.01</v>
       </c>
       <c r="I13" t="n">
-        <v>24451.93</v>
+        <v>24527.73</v>
       </c>
       <c r="J13" t="n">
-        <v>24671.54</v>
+        <v>24615.22</v>
       </c>
       <c r="K13" t="n">
-        <v>24731.28</v>
+        <v>24734.99</v>
       </c>
       <c r="L13" t="n">
-        <v>24791.01</v>
+        <v>24854.76</v>
       </c>
       <c r="M13" t="n">
-        <v>24930.69</v>
+        <v>24958.39</v>
       </c>
       <c r="N13" t="n">
-        <v>25070.36</v>
+        <v>25062.02</v>
       </c>
       <c r="O13" t="n">
-        <v>25050.16</v>
+        <v>25197.93</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1601,7 +1605,7 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
@@ -1609,8 +1613,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U13" s="8" t="n">
-        <v/>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1629,50 +1635,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24922.1</v>
+        <v>25001.31</v>
       </c>
       <c r="C14" t="n">
-        <v>25011.35</v>
+        <v>25271.34</v>
       </c>
       <c r="D14" t="n">
-        <v>24817.34</v>
+        <v>24984.27</v>
       </c>
       <c r="E14" t="n">
-        <v>25011.35</v>
+        <v>25155.41</v>
       </c>
       <c r="F14" t="n">
-        <v>164.66</v>
+        <v>144.06</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0058</v>
       </c>
       <c r="H14" t="n">
-        <v>194.01</v>
+        <v>287.07</v>
       </c>
       <c r="I14" t="n">
-        <v>24527.73</v>
+        <v>24623.33</v>
       </c>
       <c r="J14" t="n">
-        <v>24615.22</v>
+        <v>24865.84</v>
       </c>
       <c r="K14" t="n">
-        <v>24734.99</v>
+        <v>24914.34</v>
       </c>
       <c r="L14" t="n">
-        <v>24854.76</v>
+        <v>24962.85</v>
       </c>
       <c r="M14" t="n">
-        <v>24958.39</v>
+        <v>25108.35</v>
       </c>
       <c r="N14" t="n">
-        <v>25062.02</v>
+        <v>25253.86</v>
       </c>
       <c r="O14" t="n">
-        <v>25197.93</v>
+        <v>25205.36</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1690,16 +1696,18 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U14" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W14" s="11" t="inlineStr">
         <is>
@@ -1715,171 +1723,165 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25001.31</v>
+        <v>24994.05</v>
       </c>
       <c r="C15" t="n">
-        <v>25271.34</v>
+        <v>25074.28</v>
       </c>
       <c r="D15" t="n">
-        <v>24984.27</v>
+        <v>24696.59</v>
       </c>
       <c r="E15" t="n">
-        <v>25155.41</v>
+        <v>24763.12</v>
       </c>
       <c r="F15" t="n">
-        <v>144.06</v>
+        <v>-392.29</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0156</v>
       </c>
       <c r="H15" t="n">
-        <v>287.07</v>
+        <v>377.69</v>
       </c>
       <c r="I15" t="n">
-        <v>24623.33</v>
+        <v>24697.2</v>
       </c>
       <c r="J15" t="n">
-        <v>24865.84</v>
+        <v>24882.14</v>
       </c>
       <c r="K15" t="n">
-        <v>24914.34</v>
+        <v>25011.88</v>
       </c>
       <c r="L15" t="n">
-        <v>24962.85</v>
+        <v>25141.61</v>
       </c>
       <c r="M15" t="n">
-        <v>25108.35</v>
+        <v>25298.95</v>
       </c>
       <c r="N15" t="n">
-        <v>25253.86</v>
+        <v>25456.28</v>
       </c>
       <c r="O15" t="n">
-        <v>25205.36</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
+        <v>25558.41</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
       </c>
       <c r="W15" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24994.05</v>
+        <v>24830.41</v>
       </c>
       <c r="C16" t="n">
-        <v>25074.28</v>
+        <v>25099.68</v>
       </c>
       <c r="D16" t="n">
-        <v>24696.59</v>
+        <v>24821.67</v>
       </c>
       <c r="E16" t="n">
-        <v>24763.12</v>
+        <v>25099</v>
       </c>
       <c r="F16" t="n">
-        <v>-392.29</v>
+        <v>335.88</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0136</v>
       </c>
       <c r="H16" t="n">
-        <v>377.69</v>
+        <v>278.01</v>
       </c>
       <c r="I16" t="n">
-        <v>24697.2</v>
+        <v>24318.9</v>
       </c>
       <c r="J16" t="n">
-        <v>24882.14</v>
+        <v>24324.27</v>
       </c>
       <c r="K16" t="n">
-        <v>25011.88</v>
+        <v>24574.27</v>
       </c>
       <c r="L16" t="n">
-        <v>25141.61</v>
+        <v>24824.28</v>
       </c>
       <c r="M16" t="n">
-        <v>25298.95</v>
+        <v>24951.96</v>
       </c>
       <c r="N16" t="n">
-        <v>25456.28</v>
+        <v>25079.65</v>
       </c>
       <c r="O16" t="n">
-        <v>25558.41</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
+        <v>25451.97</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
@@ -1887,50 +1889,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24830.41</v>
+        <v>25459.32</v>
       </c>
       <c r="C17" t="n">
-        <v>25099.68</v>
+        <v>25560.4</v>
       </c>
       <c r="D17" t="n">
-        <v>24821.67</v>
+        <v>25361.03</v>
       </c>
       <c r="E17" t="n">
-        <v>25099</v>
+        <v>25361.03</v>
       </c>
       <c r="F17" t="n">
-        <v>335.88</v>
+        <v>262.03</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0104</v>
       </c>
       <c r="H17" t="n">
-        <v>278.01</v>
+        <v>199.37</v>
       </c>
       <c r="I17" t="n">
-        <v>24318.9</v>
+        <v>24543.66</v>
       </c>
       <c r="J17" t="n">
-        <v>24324.27</v>
+        <v>24890.15</v>
       </c>
       <c r="K17" t="n">
-        <v>24574.27</v>
+        <v>24960</v>
       </c>
       <c r="L17" t="n">
-        <v>24824.28</v>
+        <v>25029.84</v>
       </c>
       <c r="M17" t="n">
-        <v>24951.96</v>
+        <v>25238</v>
       </c>
       <c r="N17" t="n">
-        <v>25079.65</v>
+        <v>25446.17</v>
       </c>
       <c r="O17" t="n">
-        <v>25451.97</v>
+        <v>25377.69</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1953,11 +1955,13 @@
       </c>
       <c r="U17" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
@@ -1969,50 +1973,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25459.32</v>
+        <v>25496.13</v>
       </c>
       <c r="C18" t="n">
-        <v>25560.4</v>
+        <v>25553.47</v>
       </c>
       <c r="D18" t="n">
-        <v>25361.03</v>
+        <v>25307.17</v>
       </c>
       <c r="E18" t="n">
-        <v>25361.03</v>
+        <v>25464.01</v>
       </c>
       <c r="F18" t="n">
-        <v>262.03</v>
+        <v>102.98</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0104</v>
+        <v>0.0041</v>
       </c>
       <c r="H18" t="n">
-        <v>199.37</v>
+        <v>246.3</v>
       </c>
       <c r="I18" t="n">
-        <v>24543.66</v>
+        <v>25161.66</v>
       </c>
       <c r="J18" t="n">
-        <v>24890.15</v>
+        <v>25111.82</v>
       </c>
       <c r="K18" t="n">
-        <v>24960</v>
+        <v>25261.34</v>
       </c>
       <c r="L18" t="n">
-        <v>25029.84</v>
+        <v>25410.87</v>
       </c>
       <c r="M18" t="n">
-        <v>25238</v>
+        <v>25460.71</v>
       </c>
       <c r="N18" t="n">
-        <v>25446.17</v>
+        <v>25510.56</v>
       </c>
       <c r="O18" t="n">
-        <v>25377.69</v>
+        <v>25759.77</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2030,7 +2034,7 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U18" s="8" t="inlineStr">
@@ -2038,65 +2042,67 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V18" s="8" t="n">
+        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25496.13</v>
+        <v>25551.97</v>
       </c>
       <c r="C19" t="n">
-        <v>25553.47</v>
+        <v>25571.45</v>
       </c>
       <c r="D19" t="n">
-        <v>25307.17</v>
+        <v>25336.39</v>
       </c>
       <c r="E19" t="n">
-        <v>25464.01</v>
+        <v>25460.48</v>
       </c>
       <c r="F19" t="n">
-        <v>102.98</v>
+        <v>-3.53</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0001</v>
       </c>
       <c r="H19" t="n">
-        <v>246.3</v>
+        <v>235.06</v>
       </c>
       <c r="I19" t="n">
-        <v>25161.66</v>
+        <v>25060.87</v>
       </c>
       <c r="J19" t="n">
-        <v>25111.82</v>
+        <v>25234.55</v>
       </c>
       <c r="K19" t="n">
-        <v>25261.34</v>
+        <v>25340.86</v>
       </c>
       <c r="L19" t="n">
-        <v>25410.87</v>
+        <v>25447.17</v>
       </c>
       <c r="M19" t="n">
-        <v>25460.71</v>
+        <v>25587.16</v>
       </c>
       <c r="N19" t="n">
-        <v>25510.56</v>
+        <v>25727.16</v>
       </c>
       <c r="O19" t="n">
-        <v>25759.77</v>
+        <v>25799.77</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2104,23 +2110,21 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2132,57 +2136,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25551.97</v>
+        <v>25487.45</v>
       </c>
       <c r="C20" t="n">
-        <v>25571.45</v>
+        <v>25651.16</v>
       </c>
       <c r="D20" t="n">
-        <v>25336.39</v>
+        <v>25303.11</v>
       </c>
       <c r="E20" t="n">
-        <v>25460.48</v>
+        <v>25612.03</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.53</v>
+        <v>151.55</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.006</v>
       </c>
       <c r="H20" t="n">
-        <v>235.06</v>
+        <v>348.05</v>
       </c>
       <c r="I20" t="n">
-        <v>25060.87</v>
+        <v>25101.33</v>
       </c>
       <c r="J20" t="n">
-        <v>25234.55</v>
+        <v>25228.7</v>
       </c>
       <c r="K20" t="n">
-        <v>25340.86</v>
+        <v>25342.95</v>
       </c>
       <c r="L20" t="n">
-        <v>25447.17</v>
+        <v>25457.2</v>
       </c>
       <c r="M20" t="n">
-        <v>25587.16</v>
+        <v>25578.01</v>
       </c>
       <c r="N20" t="n">
-        <v>25727.16</v>
+        <v>25698.82</v>
       </c>
       <c r="O20" t="n">
-        <v>25799.77</v>
+        <v>25806.51</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2197,11 +2201,13 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2223,50 +2229,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25487.45</v>
+        <v>25709.37</v>
       </c>
       <c r="C21" t="n">
-        <v>25651.16</v>
+        <v>25891.51</v>
       </c>
       <c r="D21" t="n">
-        <v>25303.11</v>
+        <v>25549.53</v>
       </c>
       <c r="E21" t="n">
-        <v>25612.03</v>
+        <v>25629.24</v>
       </c>
       <c r="F21" t="n">
-        <v>151.55</v>
+        <v>17.21</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0007</v>
       </c>
       <c r="H21" t="n">
-        <v>348.05</v>
+        <v>341.98</v>
       </c>
       <c r="I21" t="n">
-        <v>25101.33</v>
+        <v>24955.06</v>
       </c>
       <c r="J21" t="n">
-        <v>25228.7</v>
+        <v>25331.43</v>
       </c>
       <c r="K21" t="n">
-        <v>25342.95</v>
+        <v>25438</v>
       </c>
       <c r="L21" t="n">
-        <v>25457.2</v>
+        <v>25544.58</v>
       </c>
       <c r="M21" t="n">
-        <v>25578.01</v>
+        <v>25786.05</v>
       </c>
       <c r="N21" t="n">
-        <v>25698.82</v>
+        <v>26027.53</v>
       </c>
       <c r="O21" t="n">
-        <v>25806.51</v>
+        <v>25999.21</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2274,19 +2280,17 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R21" s="6" t="n">
+        <v/>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U21" s="8" t="n">
@@ -2300,59 +2304,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25709.37</v>
+        <v>25855.12</v>
       </c>
       <c r="C22" t="n">
-        <v>25891.51</v>
+        <v>26096.93</v>
       </c>
       <c r="D22" t="n">
-        <v>25549.53</v>
+        <v>25855.12</v>
       </c>
       <c r="E22" t="n">
-        <v>25629.24</v>
+        <v>26001.31</v>
       </c>
       <c r="F22" t="n">
-        <v>17.21</v>
+        <v>372.07</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0145</v>
       </c>
       <c r="H22" t="n">
-        <v>341.98</v>
+        <v>241.81</v>
       </c>
       <c r="I22" t="n">
-        <v>24955.06</v>
+        <v>25207.55</v>
       </c>
       <c r="J22" t="n">
-        <v>25331.43</v>
+        <v>25241.62</v>
       </c>
       <c r="K22" t="n">
-        <v>25438</v>
+        <v>25458.25</v>
       </c>
       <c r="L22" t="n">
-        <v>25544.58</v>
+        <v>25674.88</v>
       </c>
       <c r="M22" t="n">
-        <v>25786.05</v>
+        <v>25800.23</v>
       </c>
       <c r="N22" t="n">
-        <v>26027.53</v>
+        <v>25925.58</v>
       </c>
       <c r="O22" t="n">
-        <v>25999.21</v>
+        <v>26233.49</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -2373,8 +2373,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2389,50 +2391,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25855.12</v>
+        <v>26189.62</v>
       </c>
       <c r="C23" t="n">
-        <v>26096.93</v>
+        <v>26266.5</v>
       </c>
       <c r="D23" t="n">
-        <v>25855.12</v>
+        <v>26082.43</v>
       </c>
       <c r="E23" t="n">
-        <v>26001.31</v>
+        <v>26202.35</v>
       </c>
       <c r="F23" t="n">
-        <v>372.07</v>
+        <v>201.04</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0077</v>
       </c>
       <c r="H23" t="n">
-        <v>241.81</v>
+        <v>184.07</v>
       </c>
       <c r="I23" t="n">
-        <v>25207.55</v>
+        <v>25613.31</v>
       </c>
       <c r="J23" t="n">
-        <v>25241.62</v>
+        <v>25772.14</v>
       </c>
       <c r="K23" t="n">
-        <v>25458.25</v>
+        <v>25880.41</v>
       </c>
       <c r="L23" t="n">
-        <v>25674.88</v>
+        <v>25988.67</v>
       </c>
       <c r="M23" t="n">
-        <v>25800.23</v>
+        <v>26122.22</v>
       </c>
       <c r="N23" t="n">
-        <v>25925.58</v>
+        <v>26255.76</v>
       </c>
       <c r="O23" t="n">
-        <v>26233.49</v>
+        <v>26338.74</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2471,50 +2473,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>26189.62</v>
+        <v>26393.43</v>
       </c>
       <c r="C24" t="n">
-        <v>26266.5</v>
+        <v>26403.81</v>
       </c>
       <c r="D24" t="n">
-        <v>26082.43</v>
+        <v>26123.18</v>
       </c>
       <c r="E24" t="n">
-        <v>26202.35</v>
+        <v>26126.3</v>
       </c>
       <c r="F24" t="n">
-        <v>201.04</v>
+        <v>-76.05</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0029</v>
       </c>
       <c r="H24" t="n">
-        <v>184.07</v>
+        <v>280.63</v>
       </c>
       <c r="I24" t="n">
-        <v>25613.31</v>
+        <v>25898.36</v>
       </c>
       <c r="J24" t="n">
-        <v>25772.14</v>
+        <v>26032.22</v>
       </c>
       <c r="K24" t="n">
-        <v>25880.41</v>
+        <v>26110.31</v>
       </c>
       <c r="L24" t="n">
-        <v>25988.67</v>
+        <v>26188.41</v>
       </c>
       <c r="M24" t="n">
-        <v>26122.22</v>
+        <v>26294.38</v>
       </c>
       <c r="N24" t="n">
-        <v>26255.76</v>
+        <v>26400.36</v>
       </c>
       <c r="O24" t="n">
-        <v>26338.74</v>
+        <v>26450.57</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2522,12 +2524,14 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
@@ -2537,7 +2541,7 @@
       </c>
       <c r="U24" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V24" s="8" t="n">
@@ -2548,55 +2552,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26393.43</v>
+        <v>26116.27</v>
       </c>
       <c r="C25" t="n">
-        <v>26403.81</v>
+        <v>26229.33</v>
       </c>
       <c r="D25" t="n">
-        <v>26123.18</v>
+        <v>26081.69</v>
       </c>
       <c r="E25" t="n">
-        <v>26126.3</v>
+        <v>26140.13</v>
       </c>
       <c r="F25" t="n">
-        <v>-76.05</v>
+        <v>13.83</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0005</v>
       </c>
       <c r="H25" t="n">
-        <v>280.63</v>
+        <v>147.64</v>
       </c>
       <c r="I25" t="n">
-        <v>25898.36</v>
+        <v>25842.55</v>
       </c>
       <c r="J25" t="n">
-        <v>26032.22</v>
+        <v>25777.07</v>
       </c>
       <c r="K25" t="n">
-        <v>26110.31</v>
+        <v>25985.99</v>
       </c>
       <c r="L25" t="n">
-        <v>26188.41</v>
+        <v>26194.9</v>
       </c>
       <c r="M25" t="n">
-        <v>26294.38</v>
+        <v>26266.62</v>
       </c>
       <c r="N25" t="n">
-        <v>26400.36</v>
+        <v>26338.33</v>
       </c>
       <c r="O25" t="n">
-        <v>26450.57</v>
+        <v>26684.44</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2604,25 +2612,19 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2634,57 +2636,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>26116.27</v>
+        <v>26235.8</v>
       </c>
       <c r="C26" t="n">
-        <v>26229.33</v>
+        <v>26445.18</v>
       </c>
       <c r="D26" t="n">
-        <v>26081.69</v>
+        <v>26223.64</v>
       </c>
       <c r="E26" t="n">
-        <v>26140.13</v>
+        <v>26319.45</v>
       </c>
       <c r="F26" t="n">
-        <v>13.83</v>
+        <v>179.32</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0069</v>
       </c>
       <c r="H26" t="n">
-        <v>147.64</v>
+        <v>221.54</v>
       </c>
       <c r="I26" t="n">
-        <v>25842.55</v>
+        <v>25934.05</v>
       </c>
       <c r="J26" t="n">
-        <v>25777.07</v>
+        <v>25984.8</v>
       </c>
       <c r="K26" t="n">
-        <v>25985.99</v>
+        <v>26066.31</v>
       </c>
       <c r="L26" t="n">
-        <v>26194.9</v>
+        <v>26147.82</v>
       </c>
       <c r="M26" t="n">
-        <v>26266.62</v>
+        <v>26213.95</v>
       </c>
       <c r="N26" t="n">
-        <v>26338.33</v>
+        <v>26280.08</v>
       </c>
       <c r="O26" t="n">
-        <v>26684.44</v>
+        <v>26376.97</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2695,78 +2697,80 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26235.8</v>
+        <v>26360.44</v>
       </c>
       <c r="C27" t="n">
-        <v>26445.18</v>
+        <v>26441.91</v>
       </c>
       <c r="D27" t="n">
-        <v>26223.64</v>
+        <v>26302.19</v>
       </c>
       <c r="E27" t="n">
-        <v>26319.45</v>
+        <v>26323.88</v>
       </c>
       <c r="F27" t="n">
-        <v>179.32</v>
+        <v>4.43</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0002</v>
       </c>
       <c r="H27" t="n">
-        <v>221.54</v>
+        <v>139.72</v>
       </c>
       <c r="I27" t="n">
-        <v>25934.05</v>
+        <v>26002.1</v>
       </c>
       <c r="J27" t="n">
-        <v>25984.8</v>
+        <v>26090.43</v>
       </c>
       <c r="K27" t="n">
-        <v>26066.31</v>
+        <v>26208.68</v>
       </c>
       <c r="L27" t="n">
-        <v>26147.82</v>
+        <v>26326.93</v>
       </c>
       <c r="M27" t="n">
-        <v>26213.95</v>
+        <v>26430.22</v>
       </c>
       <c r="N27" t="n">
-        <v>26280.08</v>
+        <v>26533.51</v>
       </c>
       <c r="O27" t="n">
-        <v>26376.97</v>
+        <v>26666.72</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2777,9 +2781,9 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
@@ -2787,70 +2791,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26360.44</v>
+        <v>26378</v>
       </c>
       <c r="C28" t="n">
-        <v>26441.91</v>
+        <v>26504.54</v>
       </c>
       <c r="D28" t="n">
-        <v>26302.19</v>
+        <v>26245.57</v>
       </c>
       <c r="E28" t="n">
-        <v>26323.88</v>
+        <v>26391.42</v>
       </c>
       <c r="F28" t="n">
-        <v>4.43</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0026</v>
       </c>
       <c r="H28" t="n">
-        <v>139.72</v>
+        <v>258.97</v>
       </c>
       <c r="I28" t="n">
-        <v>26002.1</v>
+        <v>26162.47</v>
       </c>
       <c r="J28" t="n">
-        <v>26090.43</v>
+        <v>26160.08</v>
       </c>
       <c r="K28" t="n">
-        <v>26208.68</v>
+        <v>26254.02</v>
       </c>
       <c r="L28" t="n">
-        <v>26326.93</v>
+        <v>26347.97</v>
       </c>
       <c r="M28" t="n">
-        <v>26430.22</v>
+        <v>26393.74</v>
       </c>
       <c r="N28" t="n">
-        <v>26533.51</v>
+        <v>26439.52</v>
       </c>
       <c r="O28" t="n">
-        <v>26666.72</v>
+        <v>26581.63</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2858,21 +2862,25 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2891,50 +2899,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>26378</v>
+        <v>26452</v>
       </c>
       <c r="C29" t="n">
-        <v>26504.54</v>
+        <v>26573.5</v>
       </c>
       <c r="D29" t="n">
-        <v>26245.57</v>
+        <v>26313.58</v>
       </c>
       <c r="E29" t="n">
-        <v>26391.42</v>
+        <v>26331.07</v>
       </c>
       <c r="F29" t="n">
-        <v>67.54000000000001</v>
+        <v>-60.35</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0023</v>
       </c>
       <c r="H29" t="n">
-        <v>258.97</v>
+        <v>259.92</v>
       </c>
       <c r="I29" t="n">
-        <v>26162.47</v>
+        <v>25986.6</v>
       </c>
       <c r="J29" t="n">
-        <v>26160.08</v>
+        <v>26140.63</v>
       </c>
       <c r="K29" t="n">
-        <v>26254.02</v>
+        <v>26261.94</v>
       </c>
       <c r="L29" t="n">
-        <v>26347.97</v>
+        <v>26383.24</v>
       </c>
       <c r="M29" t="n">
-        <v>26393.74</v>
+        <v>26520.9</v>
       </c>
       <c r="N29" t="n">
-        <v>26439.52</v>
+        <v>26658.57</v>
       </c>
       <c r="O29" t="n">
-        <v>26581.63</v>
+        <v>26763.51</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2942,25 +2950,21 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2979,50 +2983,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26452</v>
+        <v>26437.35</v>
       </c>
       <c r="C30" t="n">
-        <v>26573.5</v>
+        <v>26489.78</v>
       </c>
       <c r="D30" t="n">
-        <v>26313.58</v>
+        <v>26285.23</v>
       </c>
       <c r="E30" t="n">
-        <v>26331.07</v>
+        <v>26299.74</v>
       </c>
       <c r="F30" t="n">
-        <v>-60.35</v>
+        <v>-31.33</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0012</v>
       </c>
       <c r="H30" t="n">
-        <v>259.92</v>
+        <v>204.55</v>
       </c>
       <c r="I30" t="n">
-        <v>25986.6</v>
+        <v>26053.66</v>
       </c>
       <c r="J30" t="n">
-        <v>26140.63</v>
+        <v>26014.92</v>
       </c>
       <c r="K30" t="n">
-        <v>26261.94</v>
+        <v>26201.11</v>
       </c>
       <c r="L30" t="n">
-        <v>26383.24</v>
+        <v>26387.31</v>
       </c>
       <c r="M30" t="n">
-        <v>26520.9</v>
+        <v>26461.03</v>
       </c>
       <c r="N30" t="n">
-        <v>26658.57</v>
+        <v>26534.76</v>
       </c>
       <c r="O30" t="n">
-        <v>26763.51</v>
+        <v>26833.42</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3056,57 +3060,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>26437.35</v>
+        <v>26445.99</v>
       </c>
       <c r="C31" t="n">
-        <v>26489.78</v>
+        <v>26541.34</v>
       </c>
       <c r="D31" t="n">
-        <v>26285.23</v>
+        <v>26404.95</v>
       </c>
       <c r="E31" t="n">
-        <v>26299.74</v>
+        <v>26440.31</v>
       </c>
       <c r="F31" t="n">
-        <v>-31.33</v>
+        <v>140.57</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0053</v>
       </c>
       <c r="H31" t="n">
-        <v>204.55</v>
+        <v>136.39</v>
       </c>
       <c r="I31" t="n">
-        <v>26053.66</v>
+        <v>26080.68</v>
       </c>
       <c r="J31" t="n">
-        <v>26014.92</v>
+        <v>26051.31</v>
       </c>
       <c r="K31" t="n">
-        <v>26201.11</v>
+        <v>26197.47</v>
       </c>
       <c r="L31" t="n">
-        <v>26387.31</v>
+        <v>26343.62</v>
       </c>
       <c r="M31" t="n">
-        <v>26461.03</v>
+        <v>26402.01</v>
       </c>
       <c r="N31" t="n">
-        <v>26534.76</v>
+        <v>26460.41</v>
       </c>
       <c r="O31" t="n">
-        <v>26833.42</v>
+        <v>26694.33</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3117,9 +3121,9 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
@@ -3127,8 +3131,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3138,59 +3144,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26445.99</v>
+        <v>26490.3</v>
       </c>
       <c r="C32" t="n">
-        <v>26541.34</v>
+        <v>26493.5</v>
       </c>
       <c r="D32" t="n">
-        <v>26404.95</v>
+        <v>26338.61</v>
       </c>
       <c r="E32" t="n">
-        <v>26440.31</v>
+        <v>26338.61</v>
       </c>
       <c r="F32" t="n">
-        <v>140.57</v>
+        <v>-101.7</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0053</v>
+        <v>-0.0038</v>
       </c>
       <c r="H32" t="n">
-        <v>136.39</v>
+        <v>154.89</v>
       </c>
       <c r="I32" t="n">
-        <v>26080.68</v>
+        <v>26268.56</v>
       </c>
       <c r="J32" t="n">
-        <v>26051.31</v>
+        <v>26287.5</v>
       </c>
       <c r="K32" t="n">
-        <v>26197.47</v>
+        <v>26372.12</v>
       </c>
       <c r="L32" t="n">
-        <v>26343.62</v>
+        <v>26456.73</v>
       </c>
       <c r="M32" t="n">
-        <v>26402.01</v>
+        <v>26508.51</v>
       </c>
       <c r="N32" t="n">
-        <v>26460.41</v>
+        <v>26560.28</v>
       </c>
       <c r="O32" t="n">
-        <v>26694.33</v>
+        <v>26677.73</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3198,24 +3200,22 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
@@ -3224,65 +3224,73 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>26490.3</v>
+        <v>26280.86</v>
       </c>
       <c r="C33" t="n">
-        <v>26493.5</v>
+        <v>26292.95</v>
       </c>
       <c r="D33" t="n">
-        <v>26338.61</v>
+        <v>26119.54</v>
       </c>
       <c r="E33" t="n">
-        <v>26338.61</v>
+        <v>26128.36</v>
       </c>
       <c r="F33" t="n">
-        <v>-101.7</v>
+        <v>-210.25</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.008</v>
       </c>
       <c r="H33" t="n">
-        <v>154.89</v>
+        <v>173.41</v>
       </c>
       <c r="I33" t="n">
-        <v>26268.56</v>
+        <v>26183.72</v>
       </c>
       <c r="J33" t="n">
-        <v>26287.5</v>
+        <v>26145</v>
       </c>
       <c r="K33" t="n">
-        <v>26372.12</v>
+        <v>26261.16</v>
       </c>
       <c r="L33" t="n">
-        <v>26456.73</v>
+        <v>26377.33</v>
       </c>
       <c r="M33" t="n">
-        <v>26508.51</v>
+        <v>26416.05</v>
       </c>
       <c r="N33" t="n">
-        <v>26560.28</v>
+        <v>26454.78</v>
       </c>
       <c r="O33" t="n">
-        <v>26677.73</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
+        <v>26648.39</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S33" s="10" t="inlineStr">
@@ -3299,78 +3307,70 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W33" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26280.86</v>
+        <v>26146.12</v>
       </c>
       <c r="C34" t="n">
-        <v>26292.95</v>
+        <v>26187.82</v>
       </c>
       <c r="D34" t="n">
-        <v>26119.54</v>
+        <v>26063.37</v>
       </c>
       <c r="E34" t="n">
-        <v>26128.36</v>
+        <v>26091.33</v>
       </c>
       <c r="F34" t="n">
-        <v>-210.25</v>
+        <v>-37.03</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0014</v>
       </c>
       <c r="H34" t="n">
-        <v>173.41</v>
+        <v>124.45</v>
       </c>
       <c r="I34" t="n">
-        <v>26183.72</v>
+        <v>25946.13</v>
       </c>
       <c r="J34" t="n">
-        <v>26145</v>
+        <v>25916.01</v>
       </c>
       <c r="K34" t="n">
-        <v>26261.16</v>
+        <v>26041.65</v>
       </c>
       <c r="L34" t="n">
-        <v>26377.33</v>
+        <v>26167.3</v>
       </c>
       <c r="M34" t="n">
-        <v>26416.05</v>
+        <v>26215.06</v>
       </c>
       <c r="N34" t="n">
-        <v>26454.78</v>
+        <v>26262.83</v>
       </c>
       <c r="O34" t="n">
-        <v>26648.39</v>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q34" s="6" t="inlineStr">
+        <v>26466.36</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
@@ -3397,60 +3397,64 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>26146.12</v>
+        <v>26050.95</v>
       </c>
       <c r="C35" t="n">
-        <v>26187.82</v>
+        <v>26062.15</v>
       </c>
       <c r="D35" t="n">
-        <v>26063.37</v>
+        <v>25914.11</v>
       </c>
       <c r="E35" t="n">
-        <v>26091.33</v>
+        <v>25983.04</v>
       </c>
       <c r="F35" t="n">
-        <v>-37.03</v>
+        <v>-108.29</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0042</v>
       </c>
       <c r="H35" t="n">
-        <v>124.45</v>
+        <v>148.04</v>
       </c>
       <c r="I35" t="n">
-        <v>25946.13</v>
+        <v>25938.92</v>
       </c>
       <c r="J35" t="n">
-        <v>25916.01</v>
+        <v>25949.75</v>
       </c>
       <c r="K35" t="n">
-        <v>26041.65</v>
+        <v>26029.1</v>
       </c>
       <c r="L35" t="n">
-        <v>26167.3</v>
+        <v>26108.46</v>
       </c>
       <c r="M35" t="n">
-        <v>26215.06</v>
+        <v>26153.56</v>
       </c>
       <c r="N35" t="n">
-        <v>26262.83</v>
+        <v>26198.65</v>
       </c>
       <c r="O35" t="n">
-        <v>26466.36</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
+        <v>26312.27</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
@@ -3477,83 +3481,81 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26050.95</v>
+        <v>25998.95</v>
       </c>
       <c r="C36" t="n">
-        <v>26062.15</v>
+        <v>26166.25</v>
       </c>
       <c r="D36" t="n">
-        <v>25914.11</v>
+        <v>25969.52</v>
       </c>
       <c r="E36" t="n">
-        <v>25983.04</v>
+        <v>26136.56</v>
       </c>
       <c r="F36" t="n">
-        <v>-108.29</v>
+        <v>153.52</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.0059</v>
       </c>
       <c r="H36" t="n">
-        <v>148.04</v>
+        <v>196.73</v>
       </c>
       <c r="I36" t="n">
-        <v>25938.92</v>
+        <v>25766.07</v>
       </c>
       <c r="J36" t="n">
-        <v>25949.75</v>
+        <v>25832.45</v>
       </c>
       <c r="K36" t="n">
-        <v>26029.1</v>
+        <v>25909.02</v>
       </c>
       <c r="L36" t="n">
-        <v>26108.46</v>
+        <v>25985.58</v>
       </c>
       <c r="M36" t="n">
-        <v>26153.56</v>
+        <v>26057.06</v>
       </c>
       <c r="N36" t="n">
-        <v>26198.65</v>
+        <v>26128.53</v>
       </c>
       <c r="O36" t="n">
-        <v>26312.27</v>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q36" s="6" t="inlineStr">
+        <v>26210.19</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W36" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr"/>
@@ -3561,50 +3563,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25998.95</v>
+        <v>26091.29</v>
       </c>
       <c r="C37" t="n">
-        <v>26166.25</v>
+        <v>26171.7</v>
       </c>
       <c r="D37" t="n">
-        <v>25969.52</v>
+        <v>26038.07</v>
       </c>
       <c r="E37" t="n">
-        <v>26136.56</v>
+        <v>26106.6</v>
       </c>
       <c r="F37" t="n">
-        <v>153.52</v>
+        <v>-29.96</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0011</v>
       </c>
       <c r="H37" t="n">
-        <v>196.73</v>
+        <v>133.63</v>
       </c>
       <c r="I37" t="n">
-        <v>25766.07</v>
+        <v>25772.79</v>
       </c>
       <c r="J37" t="n">
-        <v>25832.45</v>
+        <v>25974.17</v>
       </c>
       <c r="K37" t="n">
-        <v>25909.02</v>
+        <v>26038.2</v>
       </c>
       <c r="L37" t="n">
-        <v>25985.58</v>
+        <v>26102.22</v>
       </c>
       <c r="M37" t="n">
-        <v>26057.06</v>
+        <v>26234.93</v>
       </c>
       <c r="N37" t="n">
-        <v>26128.53</v>
+        <v>26367.63</v>
       </c>
       <c r="O37" t="n">
-        <v>26210.19</v>
+        <v>26362.98</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3612,23 +3614,21 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3638,55 +3638,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26091.29</v>
+        <v>26206.01</v>
       </c>
       <c r="C38" t="n">
-        <v>26171.7</v>
+        <v>26341.52</v>
       </c>
       <c r="D38" t="n">
-        <v>26038.07</v>
+        <v>26164.11</v>
       </c>
       <c r="E38" t="n">
-        <v>26106.6</v>
+        <v>26266.14</v>
       </c>
       <c r="F38" t="n">
-        <v>-29.96</v>
+        <v>159.54</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0061</v>
       </c>
       <c r="H38" t="n">
-        <v>133.63</v>
+        <v>177.41</v>
       </c>
       <c r="I38" t="n">
-        <v>25772.79</v>
+        <v>25904.44</v>
       </c>
       <c r="J38" t="n">
-        <v>25974.17</v>
+        <v>25973.83</v>
       </c>
       <c r="K38" t="n">
-        <v>26038.2</v>
+        <v>26039.79</v>
       </c>
       <c r="L38" t="n">
-        <v>26102.22</v>
+        <v>26105.74</v>
       </c>
       <c r="M38" t="n">
-        <v>26234.93</v>
+        <v>26173.41</v>
       </c>
       <c r="N38" t="n">
-        <v>26367.63</v>
+        <v>26241.09</v>
       </c>
       <c r="O38" t="n">
-        <v>26362.98</v>
+        <v>26305.33</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3694,83 +3698,83 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26206.01</v>
+        <v>26255.41</v>
       </c>
       <c r="C39" t="n">
-        <v>26341.52</v>
+        <v>26466.76</v>
       </c>
       <c r="D39" t="n">
-        <v>26164.11</v>
+        <v>26196.92</v>
       </c>
       <c r="E39" t="n">
-        <v>26266.14</v>
+        <v>26285.96</v>
       </c>
       <c r="F39" t="n">
-        <v>159.54</v>
+        <v>19.82</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0061</v>
+        <v>0.0008</v>
       </c>
       <c r="H39" t="n">
-        <v>177.41</v>
+        <v>269.84</v>
       </c>
       <c r="I39" t="n">
-        <v>25904.44</v>
+        <v>25986.7</v>
       </c>
       <c r="J39" t="n">
-        <v>25973.83</v>
+        <v>26095.39</v>
       </c>
       <c r="K39" t="n">
-        <v>26039.79</v>
+        <v>26177.44</v>
       </c>
       <c r="L39" t="n">
-        <v>26105.74</v>
+        <v>26259.48</v>
       </c>
       <c r="M39" t="n">
-        <v>26173.41</v>
+        <v>26354.85</v>
       </c>
       <c r="N39" t="n">
-        <v>26241.09</v>
+        <v>26450.21</v>
       </c>
       <c r="O39" t="n">
-        <v>26305.33</v>
+        <v>26518.93</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3783,7 +3787,7 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
@@ -3793,13 +3797,11 @@
       </c>
       <c r="U39" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
@@ -3811,50 +3813,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>26255.41</v>
+        <v>26354.37</v>
       </c>
       <c r="C40" t="n">
-        <v>26466.76</v>
+        <v>26402.81</v>
       </c>
       <c r="D40" t="n">
-        <v>26196.92</v>
+        <v>26241.77</v>
       </c>
       <c r="E40" t="n">
-        <v>26285.96</v>
+        <v>26367.24</v>
       </c>
       <c r="F40" t="n">
-        <v>19.82</v>
+        <v>81.28</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0031</v>
       </c>
       <c r="H40" t="n">
-        <v>269.84</v>
+        <v>161.04</v>
       </c>
       <c r="I40" t="n">
-        <v>25986.7</v>
+        <v>25927.08</v>
       </c>
       <c r="J40" t="n">
-        <v>26095.39</v>
+        <v>25993.18</v>
       </c>
       <c r="K40" t="n">
-        <v>26177.44</v>
+        <v>26151.04</v>
       </c>
       <c r="L40" t="n">
-        <v>26259.48</v>
+        <v>26308.9</v>
       </c>
       <c r="M40" t="n">
-        <v>26354.85</v>
+        <v>26420.88</v>
       </c>
       <c r="N40" t="n">
-        <v>26450.21</v>
+        <v>26532.86</v>
       </c>
       <c r="O40" t="n">
-        <v>26518.93</v>
+        <v>26736.6</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3867,18 +3869,16 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3888,55 +3888,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26354.37</v>
+        <v>26494.61</v>
       </c>
       <c r="C41" t="n">
-        <v>26402.81</v>
+        <v>26618.74</v>
       </c>
       <c r="D41" t="n">
-        <v>26241.77</v>
+        <v>26467.36</v>
       </c>
       <c r="E41" t="n">
-        <v>26367.24</v>
+        <v>26569.99</v>
       </c>
       <c r="F41" t="n">
-        <v>81.28</v>
+        <v>202.75</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0077</v>
       </c>
       <c r="H41" t="n">
-        <v>161.04</v>
+        <v>151.38</v>
       </c>
       <c r="I41" t="n">
-        <v>25927.08</v>
+        <v>26080.73</v>
       </c>
       <c r="J41" t="n">
-        <v>25993.18</v>
+        <v>26228.67</v>
       </c>
       <c r="K41" t="n">
-        <v>26151.04</v>
+        <v>26286.72</v>
       </c>
       <c r="L41" t="n">
-        <v>26308.9</v>
+        <v>26344.77</v>
       </c>
       <c r="M41" t="n">
-        <v>26420.88</v>
+        <v>26447.76</v>
       </c>
       <c r="N41" t="n">
-        <v>26532.86</v>
+        <v>26550.76</v>
       </c>
       <c r="O41" t="n">
-        <v>26736.6</v>
+        <v>26563.85</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3954,106 +3958,106 @@
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v/>
-      </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26494.61</v>
+        <v>26464.14</v>
       </c>
       <c r="C42" t="n">
-        <v>26618.74</v>
+        <v>26471.79</v>
       </c>
       <c r="D42" t="n">
-        <v>26467.36</v>
+        <v>26249.59</v>
       </c>
       <c r="E42" t="n">
-        <v>26569.99</v>
+        <v>26258.11</v>
       </c>
       <c r="F42" t="n">
-        <v>202.75</v>
+        <v>-311.88</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0117</v>
       </c>
       <c r="H42" t="n">
-        <v>151.38</v>
+        <v>222.2</v>
       </c>
       <c r="I42" t="n">
-        <v>26080.73</v>
+        <v>26315.98</v>
       </c>
       <c r="J42" t="n">
-        <v>26228.67</v>
+        <v>26432.08</v>
       </c>
       <c r="K42" t="n">
-        <v>26286.72</v>
+        <v>26494.3</v>
       </c>
       <c r="L42" t="n">
-        <v>26344.77</v>
+        <v>26556.52</v>
       </c>
       <c r="M42" t="n">
-        <v>26447.76</v>
+        <v>26645.68</v>
       </c>
       <c r="N42" t="n">
-        <v>26550.76</v>
+        <v>26734.84</v>
       </c>
       <c r="O42" t="n">
-        <v>26563.85</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V42" s="8" t="inlineStr">
+        <v>26770.12</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W42" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W42" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr"/>
@@ -4061,59 +4065,59 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>26464.14</v>
+        <v>26150.75</v>
       </c>
       <c r="C43" t="n">
-        <v>26471.79</v>
+        <v>26206.13</v>
       </c>
       <c r="D43" t="n">
-        <v>26249.59</v>
+        <v>25916.76</v>
       </c>
       <c r="E43" t="n">
-        <v>26258.11</v>
+        <v>25970.11</v>
       </c>
       <c r="F43" t="n">
-        <v>-311.88</v>
+        <v>-288</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.011</v>
       </c>
       <c r="H43" t="n">
-        <v>222.2</v>
+        <v>289.37</v>
       </c>
       <c r="I43" t="n">
-        <v>26315.98</v>
+        <v>26027.39</v>
       </c>
       <c r="J43" t="n">
-        <v>26432.08</v>
+        <v>25984.62</v>
       </c>
       <c r="K43" t="n">
-        <v>26494.3</v>
+        <v>26147.01</v>
       </c>
       <c r="L43" t="n">
-        <v>26556.52</v>
+        <v>26309.4</v>
       </c>
       <c r="M43" t="n">
-        <v>26645.68</v>
+        <v>26369.21</v>
       </c>
       <c r="N43" t="n">
-        <v>26734.84</v>
+        <v>26429.02</v>
       </c>
       <c r="O43" t="n">
-        <v>26770.12</v>
+        <v>26693.99</v>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
@@ -4145,64 +4149,60 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26150.75</v>
+        <v>25886.67</v>
       </c>
       <c r="C44" t="n">
-        <v>26206.13</v>
+        <v>25924.21</v>
       </c>
       <c r="D44" t="n">
-        <v>25916.76</v>
+        <v>25727.93</v>
       </c>
       <c r="E44" t="n">
-        <v>25970.11</v>
+        <v>25839.33</v>
       </c>
       <c r="F44" t="n">
-        <v>-288</v>
+        <v>-130.78</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.005</v>
       </c>
       <c r="H44" t="n">
-        <v>289.37</v>
+        <v>196.28</v>
       </c>
       <c r="I44" t="n">
-        <v>26027.39</v>
+        <v>25627.39</v>
       </c>
       <c r="J44" t="n">
-        <v>25984.62</v>
+        <v>25635.07</v>
       </c>
       <c r="K44" t="n">
-        <v>26147.01</v>
+        <v>25825.42</v>
       </c>
       <c r="L44" t="n">
-        <v>26309.4</v>
+        <v>26015.78</v>
       </c>
       <c r="M44" t="n">
-        <v>26369.21</v>
+        <v>26114.79</v>
       </c>
       <c r="N44" t="n">
-        <v>26429.02</v>
+        <v>26213.81</v>
       </c>
       <c r="O44" t="n">
-        <v>26693.99</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
+        <v>26495.5</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
@@ -4229,50 +4229,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>25886.67</v>
+        <v>25840.92</v>
       </c>
       <c r="C45" t="n">
-        <v>25924.21</v>
+        <v>26007.79</v>
       </c>
       <c r="D45" t="n">
-        <v>25727.93</v>
+        <v>25784.84</v>
       </c>
       <c r="E45" t="n">
-        <v>25839.33</v>
+        <v>26003.32</v>
       </c>
       <c r="F45" t="n">
-        <v>-130.78</v>
+        <v>163.99</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0063</v>
       </c>
       <c r="H45" t="n">
-        <v>196.28</v>
+        <v>222.95</v>
       </c>
       <c r="I45" t="n">
-        <v>25627.39</v>
+        <v>25531.65</v>
       </c>
       <c r="J45" t="n">
-        <v>25635.07</v>
+        <v>25649.68</v>
       </c>
       <c r="K45" t="n">
-        <v>25825.42</v>
+        <v>25741.19</v>
       </c>
       <c r="L45" t="n">
-        <v>26015.78</v>
+        <v>25832.7</v>
       </c>
       <c r="M45" t="n">
-        <v>26114.79</v>
+        <v>25937.47</v>
       </c>
       <c r="N45" t="n">
-        <v>26213.81</v>
+        <v>26042.24</v>
       </c>
       <c r="O45" t="n">
-        <v>26495.5</v>
+        <v>26120.49</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4280,22 +4280,24 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
@@ -4304,55 +4306,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25840.92</v>
+        <v>25985.86</v>
       </c>
       <c r="C46" t="n">
-        <v>26007.79</v>
+        <v>26167.93</v>
       </c>
       <c r="D46" t="n">
-        <v>25784.84</v>
+        <v>25958.7</v>
       </c>
       <c r="E46" t="n">
-        <v>26003.32</v>
+        <v>26046.4</v>
       </c>
       <c r="F46" t="n">
-        <v>163.99</v>
+        <v>43.08</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0017</v>
       </c>
       <c r="H46" t="n">
-        <v>222.95</v>
+        <v>209.23</v>
       </c>
       <c r="I46" t="n">
-        <v>25531.65</v>
+        <v>25561.89</v>
       </c>
       <c r="J46" t="n">
-        <v>25649.68</v>
+        <v>25833.87</v>
       </c>
       <c r="K46" t="n">
-        <v>25741.19</v>
+        <v>25891.85</v>
       </c>
       <c r="L46" t="n">
-        <v>25832.7</v>
+        <v>25949.82</v>
       </c>
       <c r="M46" t="n">
-        <v>25937.47</v>
+        <v>26114.79</v>
       </c>
       <c r="N46" t="n">
-        <v>26042.24</v>
+        <v>26279.77</v>
       </c>
       <c r="O46" t="n">
-        <v>26120.49</v>
+        <v>26230.74</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4370,13 +4376,11 @@
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4395,50 +4399,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25985.86</v>
+        <v>26039.54</v>
       </c>
       <c r="C47" t="n">
-        <v>26167.93</v>
+        <v>26069.99</v>
       </c>
       <c r="D47" t="n">
-        <v>25958.7</v>
+        <v>25919.61</v>
       </c>
       <c r="E47" t="n">
-        <v>26046.4</v>
+        <v>26006.53</v>
       </c>
       <c r="F47" t="n">
-        <v>43.08</v>
+        <v>-39.87</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0015</v>
       </c>
       <c r="H47" t="n">
-        <v>209.23</v>
+        <v>150.38</v>
       </c>
       <c r="I47" t="n">
-        <v>25561.89</v>
+        <v>25749.47</v>
       </c>
       <c r="J47" t="n">
-        <v>25833.87</v>
+        <v>25828.71</v>
       </c>
       <c r="K47" t="n">
-        <v>25891.85</v>
+        <v>25941.79</v>
       </c>
       <c r="L47" t="n">
-        <v>25949.82</v>
+        <v>26054.86</v>
       </c>
       <c r="M47" t="n">
-        <v>26114.79</v>
+        <v>26151.02</v>
       </c>
       <c r="N47" t="n">
-        <v>26279.77</v>
+        <v>26247.17</v>
       </c>
       <c r="O47" t="n">
-        <v>26230.74</v>
+        <v>26377.16</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4446,18 +4450,18 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4470,74 +4474,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>26039.54</v>
+        <v>25897.22</v>
       </c>
       <c r="C48" t="n">
-        <v>26069.99</v>
+        <v>26026.78</v>
       </c>
       <c r="D48" t="n">
-        <v>25919.61</v>
+        <v>25799.66</v>
       </c>
       <c r="E48" t="n">
-        <v>26006.53</v>
+        <v>26007.63</v>
       </c>
       <c r="F48" t="n">
-        <v>-39.87</v>
+        <v>1.1</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>150.38</v>
+        <v>227.12</v>
       </c>
       <c r="I48" t="n">
-        <v>25749.47</v>
+        <v>25769.23</v>
       </c>
       <c r="J48" t="n">
-        <v>25828.71</v>
+        <v>25862.01</v>
       </c>
       <c r="K48" t="n">
-        <v>25941.79</v>
+        <v>25931.34</v>
       </c>
       <c r="L48" t="n">
-        <v>26054.86</v>
+        <v>26000.66</v>
       </c>
       <c r="M48" t="n">
-        <v>26151.02</v>
+        <v>26081.72</v>
       </c>
       <c r="N48" t="n">
-        <v>26247.17</v>
+        <v>26162.77</v>
       </c>
       <c r="O48" t="n">
-        <v>26377.16</v>
+        <v>26220.37</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4554,58 +4556,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25897.22</v>
+        <v>25870.98</v>
       </c>
       <c r="C49" t="n">
-        <v>26026.78</v>
+        <v>25909.66</v>
       </c>
       <c r="D49" t="n">
-        <v>25799.66</v>
+        <v>25512.39</v>
       </c>
       <c r="E49" t="n">
-        <v>26007.63</v>
+        <v>25576.45</v>
       </c>
       <c r="F49" t="n">
-        <v>1.1</v>
+        <v>-431.18</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0</v>
+        <v>-0.0166</v>
       </c>
       <c r="H49" t="n">
-        <v>227.12</v>
+        <v>397.27</v>
       </c>
       <c r="I49" t="n">
-        <v>25769.23</v>
+        <v>25572.54</v>
       </c>
       <c r="J49" t="n">
-        <v>25862.01</v>
+        <v>25827.72</v>
       </c>
       <c r="K49" t="n">
-        <v>25931.34</v>
+        <v>25894.07</v>
       </c>
       <c r="L49" t="n">
-        <v>26000.66</v>
+        <v>25960.43</v>
       </c>
       <c r="M49" t="n">
-        <v>26081.72</v>
+        <v>26121.19</v>
       </c>
       <c r="N49" t="n">
-        <v>26162.77</v>
+        <v>26281.96</v>
       </c>
       <c r="O49" t="n">
-        <v>26220.37</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
+        <v>26253.9</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q49" s="6" t="inlineStr">
         <is>
@@ -4617,9 +4625,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4636,73 +4644,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25870.98</v>
+        <v>25555.66</v>
       </c>
       <c r="C50" t="n">
-        <v>25909.66</v>
+        <v>25612.09</v>
       </c>
       <c r="D50" t="n">
-        <v>25512.39</v>
+        <v>25361.15</v>
       </c>
       <c r="E50" t="n">
-        <v>25576.45</v>
+        <v>25361.15</v>
       </c>
       <c r="F50" t="n">
-        <v>-431.18</v>
+        <v>-215.3</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>397.27</v>
+        <v>250.94</v>
       </c>
       <c r="I50" t="n">
-        <v>25572.54</v>
+        <v>25115.12</v>
       </c>
       <c r="J50" t="n">
-        <v>25827.72</v>
+        <v>25111.89</v>
       </c>
       <c r="K50" t="n">
-        <v>25894.07</v>
+        <v>25377.81</v>
       </c>
       <c r="L50" t="n">
-        <v>25960.43</v>
+        <v>25643.74</v>
       </c>
       <c r="M50" t="n">
-        <v>26121.19</v>
+        <v>25775.08</v>
       </c>
       <c r="N50" t="n">
-        <v>26281.96</v>
+        <v>25906.43</v>
       </c>
       <c r="O50" t="n">
-        <v>26253.9</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
+        <v>26306.93</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
@@ -4729,50 +4729,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25555.66</v>
+        <v>25478.84</v>
       </c>
       <c r="C51" t="n">
-        <v>25612.09</v>
+        <v>25581.22</v>
       </c>
       <c r="D51" t="n">
-        <v>25361.15</v>
+        <v>25396.38</v>
       </c>
       <c r="E51" t="n">
-        <v>25361.15</v>
+        <v>25568.56</v>
       </c>
       <c r="F51" t="n">
-        <v>-215.3</v>
+        <v>207.41</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>250.94</v>
+        <v>184.84</v>
       </c>
       <c r="I51" t="n">
-        <v>25115.12</v>
+        <v>25110.21</v>
       </c>
       <c r="J51" t="n">
-        <v>25111.89</v>
+        <v>25047.48</v>
       </c>
       <c r="K51" t="n">
-        <v>25377.81</v>
+        <v>25235.68</v>
       </c>
       <c r="L51" t="n">
-        <v>25643.74</v>
+        <v>25423.89</v>
       </c>
       <c r="M51" t="n">
-        <v>25775.08</v>
+        <v>25486.62</v>
       </c>
       <c r="N51" t="n">
-        <v>25906.43</v>
+        <v>25549.35</v>
       </c>
       <c r="O51" t="n">
-        <v>26306.93</v>
+        <v>25863.03</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4780,104 +4780,110 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="W51" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25478.84</v>
+        <v>25498.74</v>
       </c>
       <c r="C52" t="n">
-        <v>25581.22</v>
+        <v>25548.78</v>
       </c>
       <c r="D52" t="n">
-        <v>25396.38</v>
+        <v>25325.52</v>
       </c>
       <c r="E52" t="n">
-        <v>25568.56</v>
+        <v>25440.81</v>
       </c>
       <c r="F52" t="n">
-        <v>207.41</v>
+        <v>-127.75</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.005</v>
       </c>
       <c r="H52" t="n">
-        <v>184.84</v>
+        <v>223.26</v>
       </c>
       <c r="I52" t="n">
-        <v>25110.21</v>
+        <v>25211.54</v>
       </c>
       <c r="J52" t="n">
-        <v>25047.48</v>
+        <v>25423.6</v>
       </c>
       <c r="K52" t="n">
-        <v>25235.68</v>
+        <v>25476.14</v>
       </c>
       <c r="L52" t="n">
-        <v>25423.89</v>
+        <v>25528.68</v>
       </c>
       <c r="M52" t="n">
-        <v>25486.62</v>
+        <v>25660.98</v>
       </c>
       <c r="N52" t="n">
-        <v>25549.35</v>
+        <v>25793.28</v>
       </c>
       <c r="O52" t="n">
-        <v>25863.03</v>
+        <v>25766.06</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
+      <c r="Q52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
@@ -4888,64 +4894,64 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25498.74</v>
+        <v>25360.32</v>
       </c>
       <c r="C53" t="n">
-        <v>25548.78</v>
+        <v>25478.98</v>
       </c>
       <c r="D53" t="n">
-        <v>25325.52</v>
+        <v>25172.89</v>
       </c>
       <c r="E53" t="n">
-        <v>25440.81</v>
+        <v>25402.28</v>
       </c>
       <c r="F53" t="n">
-        <v>-127.75</v>
+        <v>-38.53</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.005</v>
+        <v>-0.0015</v>
       </c>
       <c r="H53" t="n">
-        <v>223.26</v>
+        <v>306.09</v>
       </c>
       <c r="I53" t="n">
-        <v>25211.54</v>
+        <v>25102.26</v>
       </c>
       <c r="J53" t="n">
-        <v>25423.6</v>
+        <v>25219.38</v>
       </c>
       <c r="K53" t="n">
-        <v>25476.14</v>
+        <v>25329.18</v>
       </c>
       <c r="L53" t="n">
-        <v>25528.68</v>
+        <v>25438.98</v>
       </c>
       <c r="M53" t="n">
-        <v>25660.98</v>
+        <v>25552.44</v>
       </c>
       <c r="N53" t="n">
-        <v>25793.28</v>
+        <v>25665.9</v>
       </c>
       <c r="O53" t="n">
-        <v>25766.06</v>
+        <v>25772.04</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
@@ -4955,7 +4961,7 @@
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4981,71 +4987,69 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25360.32</v>
+        <v>25515.96</v>
       </c>
       <c r="C54" t="n">
-        <v>25478.98</v>
+        <v>25599.07</v>
       </c>
       <c r="D54" t="n">
-        <v>25172.89</v>
+        <v>25361.7</v>
       </c>
       <c r="E54" t="n">
-        <v>25402.28</v>
+        <v>25537.75</v>
       </c>
       <c r="F54" t="n">
-        <v>-38.53</v>
+        <v>135.47</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0015</v>
+        <v>0.0053</v>
       </c>
       <c r="H54" t="n">
-        <v>306.09</v>
+        <v>237.37</v>
       </c>
       <c r="I54" t="n">
-        <v>25102.26</v>
+        <v>24866.8</v>
       </c>
       <c r="J54" t="n">
-        <v>25219.38</v>
+        <v>25134.36</v>
       </c>
       <c r="K54" t="n">
-        <v>25329.18</v>
+        <v>25249.23</v>
       </c>
       <c r="L54" t="n">
-        <v>25438.98</v>
+        <v>25364.11</v>
       </c>
       <c r="M54" t="n">
-        <v>25552.44</v>
+        <v>25555.32</v>
       </c>
       <c r="N54" t="n">
-        <v>25665.9</v>
+        <v>25746.54</v>
       </c>
       <c r="O54" t="n">
-        <v>25772.04</v>
+        <v>25785.07</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5058,59 +5062,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25515.96</v>
+        <v>25681.6</v>
       </c>
       <c r="C55" t="n">
-        <v>25599.07</v>
+        <v>25800.62</v>
       </c>
       <c r="D55" t="n">
-        <v>25361.7</v>
+        <v>25596.05</v>
       </c>
       <c r="E55" t="n">
-        <v>25537.75</v>
+        <v>25716.71</v>
       </c>
       <c r="F55" t="n">
-        <v>135.47</v>
+        <v>178.96</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0053</v>
+        <v>0.007</v>
       </c>
       <c r="H55" t="n">
-        <v>237.37</v>
+        <v>204.57</v>
       </c>
       <c r="I55" t="n">
-        <v>24866.8</v>
+        <v>25124.33</v>
       </c>
       <c r="J55" t="n">
-        <v>25134.36</v>
+        <v>25329.06</v>
       </c>
       <c r="K55" t="n">
-        <v>25249.23</v>
+        <v>25419.06</v>
       </c>
       <c r="L55" t="n">
-        <v>25364.11</v>
+        <v>25509.07</v>
       </c>
       <c r="M55" t="n">
-        <v>25555.32</v>
+        <v>25656.44</v>
       </c>
       <c r="N55" t="n">
-        <v>25746.54</v>
+        <v>25803.8</v>
       </c>
       <c r="O55" t="n">
-        <v>25785.07</v>
+        <v>25836.44</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5147,79 +5147,83 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25681.6</v>
+        <v>25596.46</v>
       </c>
       <c r="C56" t="n">
-        <v>25800.62</v>
+        <v>25656.22</v>
       </c>
       <c r="D56" t="n">
-        <v>25596.05</v>
+        <v>25285.9</v>
       </c>
       <c r="E56" t="n">
-        <v>25716.71</v>
+        <v>25304.06</v>
       </c>
       <c r="F56" t="n">
-        <v>178.96</v>
+        <v>-412.65</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.007</v>
+        <v>-0.016</v>
       </c>
       <c r="H56" t="n">
-        <v>204.57</v>
+        <v>370.32</v>
       </c>
       <c r="I56" t="n">
-        <v>25124.33</v>
+        <v>25391.48</v>
       </c>
       <c r="J56" t="n">
-        <v>25329.06</v>
+        <v>25521.33</v>
       </c>
       <c r="K56" t="n">
-        <v>25419.06</v>
+        <v>25614.43</v>
       </c>
       <c r="L56" t="n">
-        <v>25509.07</v>
+        <v>25707.52</v>
       </c>
       <c r="M56" t="n">
-        <v>25656.44</v>
+        <v>25819</v>
       </c>
       <c r="N56" t="n">
-        <v>25803.8</v>
+        <v>25930.47</v>
       </c>
       <c r="O56" t="n">
-        <v>25836.44</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
+        <v>26005.19</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W56" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X56" t="inlineStr"/>
@@ -5227,77 +5231,75 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25596.46</v>
+        <v>25491.35</v>
       </c>
       <c r="C57" t="n">
-        <v>25656.22</v>
+        <v>25617.99</v>
       </c>
       <c r="D57" t="n">
-        <v>25285.9</v>
+        <v>25434.16</v>
       </c>
       <c r="E57" t="n">
-        <v>25304.06</v>
+        <v>25575.01</v>
       </c>
       <c r="F57" t="n">
-        <v>-412.65</v>
+        <v>270.95</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.016</v>
+        <v>0.0107</v>
       </c>
       <c r="H57" t="n">
-        <v>370.32</v>
+        <v>183.83</v>
       </c>
       <c r="I57" t="n">
-        <v>25391.48</v>
+        <v>24915.58</v>
       </c>
       <c r="J57" t="n">
-        <v>25521.33</v>
+        <v>24850.24</v>
       </c>
       <c r="K57" t="n">
-        <v>25614.43</v>
+        <v>25118.9</v>
       </c>
       <c r="L57" t="n">
-        <v>25707.52</v>
+        <v>25387.56</v>
       </c>
       <c r="M57" t="n">
-        <v>25819</v>
+        <v>25489.22</v>
       </c>
       <c r="N57" t="n">
-        <v>25930.47</v>
+        <v>25590.88</v>
       </c>
       <c r="O57" t="n">
-        <v>26005.19</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
+        <v>26026.54</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
@@ -5306,55 +5308,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>25491.35</v>
+        <v>25592.98</v>
       </c>
       <c r="C58" t="n">
-        <v>25617.99</v>
+        <v>25783.16</v>
       </c>
       <c r="D58" t="n">
-        <v>25434.16</v>
+        <v>25423.07</v>
       </c>
       <c r="E58" t="n">
-        <v>25575.01</v>
+        <v>25578.85</v>
       </c>
       <c r="F58" t="n">
-        <v>270.95</v>
+        <v>3.84</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0107</v>
+        <v>0.0002</v>
       </c>
       <c r="H58" t="n">
-        <v>183.83</v>
+        <v>360.09</v>
       </c>
       <c r="I58" t="n">
-        <v>24915.58</v>
+        <v>25250.33</v>
       </c>
       <c r="J58" t="n">
-        <v>24850.24</v>
+        <v>25415.65</v>
       </c>
       <c r="K58" t="n">
-        <v>25118.9</v>
+        <v>25483.09</v>
       </c>
       <c r="L58" t="n">
-        <v>25387.56</v>
+        <v>25550.54</v>
       </c>
       <c r="M58" t="n">
-        <v>25489.22</v>
+        <v>25666.92</v>
       </c>
       <c r="N58" t="n">
-        <v>25590.88</v>
+        <v>25783.31</v>
       </c>
       <c r="O58" t="n">
-        <v>26026.54</v>
+        <v>25801.82</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5362,12 +5368,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5375,10 +5383,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U58" s="8" t="n">
+        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5397,50 +5403,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25592.98</v>
+        <v>25724.13</v>
       </c>
       <c r="C59" t="n">
-        <v>25783.16</v>
+        <v>25729.05</v>
       </c>
       <c r="D59" t="n">
-        <v>25423.07</v>
+        <v>25365.21</v>
       </c>
       <c r="E59" t="n">
-        <v>25578.85</v>
+        <v>25410.63</v>
       </c>
       <c r="F59" t="n">
-        <v>3.84</v>
+        <v>-168.22</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.0066</v>
       </c>
       <c r="H59" t="n">
-        <v>360.09</v>
+        <v>363.84</v>
       </c>
       <c r="I59" t="n">
-        <v>25250.33</v>
+        <v>25062.98</v>
       </c>
       <c r="J59" t="n">
-        <v>25415.65</v>
+        <v>25206.63</v>
       </c>
       <c r="K59" t="n">
-        <v>25483.09</v>
+        <v>25398.8</v>
       </c>
       <c r="L59" t="n">
-        <v>25550.54</v>
+        <v>25590.98</v>
       </c>
       <c r="M59" t="n">
-        <v>25666.92</v>
+        <v>25758.89</v>
       </c>
       <c r="N59" t="n">
-        <v>25783.31</v>
+        <v>25926.81</v>
       </c>
       <c r="O59" t="n">
-        <v>25801.82</v>
+        <v>26143.25</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5450,18 +5456,16 @@
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5474,59 +5478,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25724.13</v>
+        <v>25263.11</v>
       </c>
       <c r="C60" t="n">
-        <v>25729.05</v>
+        <v>25424.21</v>
       </c>
       <c r="D60" t="n">
-        <v>25365.21</v>
+        <v>25164.2</v>
       </c>
       <c r="E60" t="n">
-        <v>25410.63</v>
+        <v>25266.53</v>
       </c>
       <c r="F60" t="n">
-        <v>-168.22</v>
+        <v>-144.1</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0066</v>
+        <v>-0.0057</v>
       </c>
       <c r="H60" t="n">
-        <v>363.84</v>
+        <v>260.01</v>
       </c>
       <c r="I60" t="n">
-        <v>25062.98</v>
+        <v>25001.37</v>
       </c>
       <c r="J60" t="n">
-        <v>25206.63</v>
+        <v>24978.54</v>
       </c>
       <c r="K60" t="n">
-        <v>25398.8</v>
+        <v>25228.71</v>
       </c>
       <c r="L60" t="n">
-        <v>25590.98</v>
+        <v>25478.88</v>
       </c>
       <c r="M60" t="n">
-        <v>25758.89</v>
+        <v>25592.55</v>
       </c>
       <c r="N60" t="n">
-        <v>25926.81</v>
+        <v>25706.22</v>
       </c>
       <c r="O60" t="n">
-        <v>26143.25</v>
+        <v>26092.89</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5563,50 +5563,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>25263.11</v>
+        <v>25441.79</v>
       </c>
       <c r="C61" t="n">
-        <v>25424.21</v>
+        <v>25529.33</v>
       </c>
       <c r="D61" t="n">
-        <v>25164.2</v>
+        <v>25347.3</v>
       </c>
       <c r="E61" t="n">
-        <v>25266.53</v>
+        <v>25408.64</v>
       </c>
       <c r="F61" t="n">
-        <v>-144.1</v>
+        <v>142.11</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0056</v>
       </c>
       <c r="H61" t="n">
-        <v>260.01</v>
+        <v>182.03</v>
       </c>
       <c r="I61" t="n">
-        <v>25001.37</v>
+        <v>24904.19</v>
       </c>
       <c r="J61" t="n">
-        <v>24978.54</v>
+        <v>24992.68</v>
       </c>
       <c r="K61" t="n">
-        <v>25228.71</v>
+        <v>25136.52</v>
       </c>
       <c r="L61" t="n">
-        <v>25478.88</v>
+        <v>25280.37</v>
       </c>
       <c r="M61" t="n">
-        <v>25592.55</v>
+        <v>25396.54</v>
       </c>
       <c r="N61" t="n">
-        <v>25706.22</v>
+        <v>25512.7</v>
       </c>
       <c r="O61" t="n">
-        <v>26092.89</v>
+        <v>25684.22</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5614,21 +5614,23 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
@@ -5638,55 +5640,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>25441.79</v>
+        <v>25443.98</v>
       </c>
       <c r="C62" t="n">
-        <v>25529.33</v>
+        <v>25575.66</v>
       </c>
       <c r="D62" t="n">
-        <v>25347.3</v>
+        <v>25360.32</v>
       </c>
       <c r="E62" t="n">
-        <v>25408.64</v>
+        <v>25374.42</v>
       </c>
       <c r="F62" t="n">
-        <v>142.11</v>
+        <v>-34.22</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0056</v>
+        <v>-0.0013</v>
       </c>
       <c r="H62" t="n">
-        <v>182.03</v>
+        <v>215.34</v>
       </c>
       <c r="I62" t="n">
-        <v>24904.19</v>
+        <v>25165.27</v>
       </c>
       <c r="J62" t="n">
-        <v>24992.68</v>
+        <v>25211.77</v>
       </c>
       <c r="K62" t="n">
-        <v>25136.52</v>
+        <v>25317.63</v>
       </c>
       <c r="L62" t="n">
-        <v>25280.37</v>
+        <v>25423.48</v>
       </c>
       <c r="M62" t="n">
-        <v>25396.54</v>
+        <v>25499.66</v>
       </c>
       <c r="N62" t="n">
-        <v>25512.7</v>
+        <v>25575.83</v>
       </c>
       <c r="O62" t="n">
-        <v>25684.22</v>
+        <v>25711.36</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5697,20 +5703,18 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
@@ -5722,57 +5726,57 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>25443.98</v>
+        <v>25374.34</v>
       </c>
       <c r="C63" t="n">
-        <v>25575.66</v>
+        <v>25617.31</v>
       </c>
       <c r="D63" t="n">
-        <v>25360.32</v>
+        <v>25338.03</v>
       </c>
       <c r="E63" t="n">
-        <v>25374.42</v>
+        <v>25399.21</v>
       </c>
       <c r="F63" t="n">
-        <v>-34.22</v>
+        <v>24.79</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.001</v>
       </c>
       <c r="H63" t="n">
-        <v>215.34</v>
+        <v>279.28</v>
       </c>
       <c r="I63" t="n">
-        <v>25165.27</v>
+        <v>25144.98</v>
       </c>
       <c r="J63" t="n">
-        <v>25211.77</v>
+        <v>25112.29</v>
       </c>
       <c r="K63" t="n">
-        <v>25317.63</v>
+        <v>25266.75</v>
       </c>
       <c r="L63" t="n">
-        <v>25423.48</v>
+        <v>25421.21</v>
       </c>
       <c r="M63" t="n">
-        <v>25499.66</v>
+        <v>25482.09</v>
       </c>
       <c r="N63" t="n">
-        <v>25575.83</v>
+        <v>25542.97</v>
       </c>
       <c r="O63" t="n">
-        <v>25711.36</v>
+        <v>25791</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5793,8 +5797,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U63" s="8" t="n">
-        <v/>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V63" s="8" t="n">
         <v/>
@@ -5813,50 +5819,50 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>25374.34</v>
+        <v>25490.67</v>
       </c>
       <c r="C64" t="n">
-        <v>25617.31</v>
+        <v>25584.5</v>
       </c>
       <c r="D64" t="n">
-        <v>25338.03</v>
+        <v>25190.33</v>
       </c>
       <c r="E64" t="n">
-        <v>25399.21</v>
+        <v>25199.19</v>
       </c>
       <c r="F64" t="n">
-        <v>24.79</v>
+        <v>-200.02</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H64" t="n">
-        <v>279.28</v>
+        <v>394.17</v>
       </c>
       <c r="I64" t="n">
-        <v>25144.98</v>
+        <v>25058.75</v>
       </c>
       <c r="J64" t="n">
-        <v>25112.29</v>
+        <v>25080.7</v>
       </c>
       <c r="K64" t="n">
-        <v>25266.75</v>
+        <v>25259.57</v>
       </c>
       <c r="L64" t="n">
-        <v>25421.21</v>
+        <v>25438.44</v>
       </c>
       <c r="M64" t="n">
-        <v>25482.09</v>
+        <v>25538.85</v>
       </c>
       <c r="N64" t="n">
-        <v>25542.97</v>
+        <v>25639.26</v>
       </c>
       <c r="O64" t="n">
-        <v>25791</v>
+        <v>25896.59</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5864,12 +5870,14 @@
       <c r="Q64" s="6" t="n">
         <v/>
       </c>
-      <c r="R64" s="6" t="n">
-        <v/>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S64" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T64" s="8" t="inlineStr">
@@ -5877,10 +5885,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U64" s="8" t="n">
+        <v/>
       </c>
       <c r="V64" s="8" t="n">
         <v/>
@@ -5890,26 +5896,22 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>25490.67</v>
+        <v>25058.08</v>
       </c>
       <c r="C65" t="n">
-        <v>25584.5</v>
+        <v>25232.18</v>
       </c>
       <c r="D65" t="n">
-        <v>25190.33</v>
+        <v>24831.6</v>
       </c>
       <c r="E65" t="n">
         <v/>
@@ -5921,28 +5923,28 @@
         <v/>
       </c>
       <c r="H65" t="n">
-        <v>394.17</v>
+        <v>400.58</v>
       </c>
       <c r="I65" t="n">
-        <v>25058.75</v>
+        <v>24796.16</v>
       </c>
       <c r="J65" t="n">
-        <v>25080.7</v>
+        <v>24710.91</v>
       </c>
       <c r="K65" t="n">
-        <v>25259.57</v>
+        <v>25002.1</v>
       </c>
       <c r="L65" t="n">
-        <v>25438.44</v>
+        <v>25293.3</v>
       </c>
       <c r="M65" t="n">
-        <v>25538.85</v>
+        <v>25396.27</v>
       </c>
       <c r="N65" t="n">
-        <v>25639.26</v>
+        <v>25499.25</v>
       </c>
       <c r="O65" t="n">
-        <v>25896.59</v>
+        <v>25978.67</v>
       </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
@@ -5962,10 +5964,8 @@
           <t>=</t>
         </is>
       </c>
-      <c r="T65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T65" s="8" t="n">
+        <v/>
       </c>
       <c r="U65" s="8" t="n">
         <v/>

--- a/three_gate/analysis/DAX_daily.xlsx
+++ b/three_gate/analysis/DAX_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -104,20 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -637,69 +634,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25811.9</v>
+        <v>25770.45</v>
       </c>
       <c r="C2" t="n">
-        <v>25900.1</v>
+        <v>25811.97</v>
       </c>
       <c r="D2" t="n">
-        <v>25698.56</v>
+        <v>25465.12</v>
       </c>
       <c r="E2" t="n">
-        <v>25817.89</v>
+        <v>25465.25</v>
       </c>
       <c r="F2" t="n">
-        <v>38.58</v>
+        <v>-352.64</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0137</v>
       </c>
       <c r="H2" t="n">
-        <v>201.54</v>
+        <v>346.85</v>
       </c>
       <c r="I2" t="n">
-        <v>25396.6</v>
+        <v>25497.02</v>
       </c>
       <c r="J2" t="n">
-        <v>25594.26</v>
+        <v>25625.63</v>
       </c>
       <c r="K2" t="n">
-        <v>25671.77</v>
+        <v>25717.12</v>
       </c>
       <c r="L2" t="n">
-        <v>25749.27</v>
+        <v>25808.61</v>
       </c>
       <c r="M2" t="n">
-        <v>25886.86</v>
+        <v>25918.66</v>
       </c>
       <c r="N2" t="n">
-        <v>26024.44</v>
+        <v>26028.71</v>
       </c>
       <c r="O2" t="n">
-        <v>26041.87</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+        <v>26101.64</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -709,7 +710,7 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -717,67 +718,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25770.45</v>
+        <v>25274.94</v>
       </c>
       <c r="C3" t="n">
-        <v>25811.97</v>
+        <v>25280.16</v>
       </c>
       <c r="D3" t="n">
-        <v>25465.12</v>
+        <v>24830.17</v>
       </c>
       <c r="E3" t="n">
-        <v>25465.25</v>
+        <v>24897.45</v>
       </c>
       <c r="F3" t="n">
-        <v>-352.64</v>
+        <v>-567.8</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0223</v>
       </c>
       <c r="H3" t="n">
-        <v>346.85</v>
+        <v>449.99</v>
       </c>
       <c r="I3" t="n">
-        <v>25497.02</v>
+        <v>25118.27</v>
       </c>
       <c r="J3" t="n">
-        <v>25625.63</v>
+        <v>25031.75</v>
       </c>
       <c r="K3" t="n">
-        <v>25717.12</v>
+        <v>25291.82</v>
       </c>
       <c r="L3" t="n">
-        <v>25808.61</v>
+        <v>25551.9</v>
       </c>
       <c r="M3" t="n">
-        <v>25918.66</v>
+        <v>25638.68</v>
       </c>
       <c r="N3" t="n">
-        <v>26028.71</v>
+        <v>25725.45</v>
       </c>
       <c r="O3" t="n">
-        <v>26101.64</v>
+        <v>26158.82</v>
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -791,7 +792,7 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -801,134 +802,134 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25274.94</v>
+        <v>25097.48</v>
       </c>
       <c r="C4" t="n">
-        <v>25280.16</v>
+        <v>25127.76</v>
       </c>
       <c r="D4" t="n">
-        <v>24830.17</v>
+        <v>24867.32</v>
       </c>
       <c r="E4" t="n">
-        <v>24897.45</v>
+        <v>25118.27</v>
       </c>
       <c r="F4" t="n">
-        <v>-567.8</v>
+        <v>220.82</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0089</v>
       </c>
       <c r="H4" t="n">
-        <v>449.99</v>
+        <v>260.44</v>
       </c>
       <c r="I4" t="n">
-        <v>25118.27</v>
+        <v>24380.18</v>
       </c>
       <c r="J4" t="n">
-        <v>25031.75</v>
+        <v>24368.6</v>
       </c>
       <c r="K4" t="n">
-        <v>25291.82</v>
+        <v>24672.45</v>
       </c>
       <c r="L4" t="n">
-        <v>25551.9</v>
+        <v>24976.31</v>
       </c>
       <c r="M4" t="n">
-        <v>25638.68</v>
+        <v>25122.44</v>
       </c>
       <c r="N4" t="n">
-        <v>25725.45</v>
+        <v>25268.58</v>
       </c>
       <c r="O4" t="n">
-        <v>26158.82</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
+        <v>25730.15</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25097.48</v>
+        <v>25081.19</v>
       </c>
       <c r="C5" t="n">
-        <v>25127.76</v>
+        <v>25195.83</v>
       </c>
       <c r="D5" t="n">
-        <v>24867.32</v>
+        <v>24937.52</v>
       </c>
       <c r="E5" t="n">
-        <v>25118.27</v>
+        <v>25067.09</v>
       </c>
       <c r="F5" t="n">
-        <v>220.82</v>
+        <v>-51.18</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.002</v>
       </c>
       <c r="H5" t="n">
-        <v>260.44</v>
+        <v>258.31</v>
       </c>
       <c r="I5" t="n">
-        <v>24380.18</v>
+        <v>24606.88</v>
       </c>
       <c r="J5" t="n">
-        <v>24368.6</v>
+        <v>24918.19</v>
       </c>
       <c r="K5" t="n">
-        <v>24672.45</v>
+        <v>24988.05</v>
       </c>
       <c r="L5" t="n">
-        <v>24976.31</v>
+        <v>25057.9</v>
       </c>
       <c r="M5" t="n">
-        <v>25122.44</v>
+        <v>25248.49</v>
       </c>
       <c r="N5" t="n">
-        <v>25268.58</v>
+        <v>25439.07</v>
       </c>
       <c r="O5" t="n">
-        <v>25730.15</v>
+        <v>25388.2</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -936,18 +937,18 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -955,7 +956,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -969,50 +970,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25081.19</v>
+        <v>24963.8</v>
       </c>
       <c r="C6" t="n">
-        <v>25195.83</v>
+        <v>25154.58</v>
       </c>
       <c r="D6" t="n">
-        <v>24937.52</v>
+        <v>24963.8</v>
       </c>
       <c r="E6" t="n">
-        <v>25067.09</v>
+        <v>25114.25</v>
       </c>
       <c r="F6" t="n">
-        <v>-51.18</v>
+        <v>47.16</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="H6" t="n">
-        <v>258.31</v>
+        <v>190.78</v>
       </c>
       <c r="I6" t="n">
-        <v>24606.88</v>
+        <v>24679.21</v>
       </c>
       <c r="J6" t="n">
-        <v>24918.19</v>
+        <v>24808.99</v>
       </c>
       <c r="K6" t="n">
-        <v>24988.05</v>
+        <v>24937.93</v>
       </c>
       <c r="L6" t="n">
-        <v>25057.9</v>
+        <v>25066.88</v>
       </c>
       <c r="M6" t="n">
-        <v>25248.49</v>
+        <v>25196.25</v>
       </c>
       <c r="N6" t="n">
-        <v>25439.07</v>
+        <v>25325.61</v>
       </c>
       <c r="O6" t="n">
-        <v>25388.2</v>
+        <v>25454.14</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1020,12 +1021,10 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1039,7 +1038,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1053,61 +1052,65 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24963.8</v>
+        <v>24932.62</v>
       </c>
       <c r="C7" t="n">
-        <v>25154.58</v>
+        <v>25204.68</v>
       </c>
       <c r="D7" t="n">
-        <v>24963.8</v>
+        <v>24869.25</v>
       </c>
       <c r="E7" t="n">
-        <v>25114.25</v>
+        <v>25147.03</v>
       </c>
       <c r="F7" t="n">
-        <v>47.16</v>
+        <v>32.78</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0013</v>
       </c>
       <c r="H7" t="n">
-        <v>190.78</v>
+        <v>335.43</v>
       </c>
       <c r="I7" t="n">
-        <v>24679.21</v>
+        <v>24773.02</v>
       </c>
       <c r="J7" t="n">
-        <v>24808.99</v>
+        <v>24951</v>
       </c>
       <c r="K7" t="n">
-        <v>24937.93</v>
+        <v>25018.86</v>
       </c>
       <c r="L7" t="n">
-        <v>25066.88</v>
+        <v>25086.72</v>
       </c>
       <c r="M7" t="n">
-        <v>25196.25</v>
+        <v>25209.64</v>
       </c>
       <c r="N7" t="n">
-        <v>25325.61</v>
+        <v>25332.56</v>
       </c>
       <c r="O7" t="n">
-        <v>25454.14</v>
+        <v>25345.36</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1121,7 +1124,7 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1135,50 +1138,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
  